--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -80,7 +80,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -137,6 +137,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -328,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -751,6 +757,42 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1166,13 +1208,13 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D5" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в том, что каждый пользователь и представитель эксплуатационного персонала осуществляет логический доступ к ресурсам финансовой организации исключительно под собственной учётной записью, однозначно идентифицирующей конкретного субъекта, а не под общими (групповыми), анонимными или обезличенными учётными записями.
+      <c r="D5" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы каждый пользователь и представитель эксплуатационного персонала осуществлял логический доступ к ресурсам финансовой организации исключительно под собственной учётной записью, однозначно идентифицирующей конкретного субъекта, а не под общими (групповыми), анонимными или обезличенными учётными записями.
 Главная цель меры — обеспечить персональную ответственность каждого субъекта логического доступа за совершённые им действия: без уникальной персонификации невозможно достоверно установить, кто именно выполнил то или иное действие в информационной системе, что делает бессмысленным любое последующее расследование инцидентов и обесценивает результаты регистрации событий.</t>
         </is>
       </c>
-      <c r="E5" s="125" t="inlineStr">
+      <c r="E5" s="145" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1183,23 +1225,12 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает:
-1. Настройку операционных систем, СУБД, прикладного и сетевого программного обеспечения (ПО) таким образом, чтобы вход в систему и выполнение любых операций были возможны только после успешной идентификации и аутентификации под персональной учётной записью;
+Так как мера носит сугубо технический характер, её внедрение сводится к следующим шагам:
+1. Настройка операционных систем, СУБД, прикладного и сетевого программного обеспечения (ПО) таким образом, чтобы вход в систему и выполнение любых операций были возможны только после успешной идентификации и аутентификации под персональной учётной записью;
 2. Технический запрет создания и использования групповых, общих, анонимных и гостевых учётных записей для логического доступа пользователей и эксплуатационного персонала (за исключением технологических учётных записей, для которых персонализируется ответственный за их использование);
 3. Централизованное управление учётными записями через каталог (например, Active Directory, LDAP-каталог) или систему класса IdM (Identity Management), обеспечивающее уникальность идентификаторов и исключающее их повторное использование;
 4. Технический контроль (блокировку) попыток входа под неперсонифицированными или разделяемыми учётными записями с регистрацией таких попыток в журнале событий.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и каталогами (IdM, службы каталогов), средства защиты от несанкционированного доступа (СЗИ от НСД).
+Применимый класс средств — системы управления учётными записями и каталогами (IdM, службы каталогов), средства защиты от несанкционированного доступа (СЗИ от НСД).
 Иностранные: Microsoft Active Directory, Oracle Identity Manager, One Identity Manager и пр.
 Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К, Avanpost IDM и др.
 Открытый код: FreeIPA, OpenLDAP и др.</t>
@@ -1249,13 +1280,13 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D6" s="127" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в периодическом сопоставлении перечня разблокированных (активных) учётных записей в информационных системах с перечнем легальных субъектов логического доступа — то есть работников, состоящих в трудовых отношениях с организацией, и представителей внешних (подрядных) организаций, имеющих действующие основания для доступа.
+      <c r="D6" s="146" t="inlineStr">
+        <is>
+          <t>Речь идёт о периодическом сопоставлении перечня разблокированных (активных) учётных записей в информационных системах с перечнем легальных субъектов логического доступа — то есть работников, состоящих в трудовых отношениях с организацией, и представителей внешних (подрядных) организаций, имеющих действующие основания для доступа.
 Главная цель меры — своевременно выявлять учётные записи, которые остаются разблокированными, хотя субъект, которому они принадлежат, уже утратил основания для логического доступа (уволен, переведён, истёк срок договора), и тем самым исключить возможность использования таких учётных записей для несанкционированного доступа.</t>
         </is>
       </c>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="147" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1266,7 +1297,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает проведение периодических сверок перечня активных учётных записей с кадровыми данными и данными о действующих договорах с внешними организациями. Для этого необходимо:
+На организационном уровне необходимо проводить периодические сверки перечня активных учётных записей с кадровыми данными и данными о действующих договорах с внешними организациями:
 1. Утвердить регламент, определяющий периодичность сверки (например, ежемесячно), источники данных о легальных субъектах (кадровая система, реестр договоров с подрядчиками) и ответственных за проведение сверки лиц;
 2. Проводить сверку выгрузки активных учётных записей с данными кадрового учёта и реестром действующих подрядных организаций;
 3. По фактам расхождений инициировать блокирование избыточных учётных записей и фиксировать результат сверки в акте.</t>
@@ -1281,21 +1312,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает автоматизацию процесса сверки за счёт интеграции системы управления учётными записями с источниками кадровых данных. Для этого используются:
+Технически процесс сверки можно и нужно автоматизировать за счёт интеграции системы управления учётными записями с источниками кадровых данных:
 1. Системы класса IdM, автоматически формирующие перечень легальных субъектов на основании данных кадровой системы (HRM) и реестра подрядчиков и сверяющие его с фактическим составом разблокированных учётных записей в подключённых информационных системах;
 2. Автоматизированные отчёты (скрипты, задания по расписанию), сопоставляющие выгрузку из каталога (AD/LDAP) с данными кадровой системы и формирующие список расхождений для передачи ответственным лицам.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM).
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM).
 Иностранные: Microsoft Identity Manager, SailPoint IdentityIQ, One Identity Manager и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: FreeIPA, midPoint и др.</t>
@@ -1365,16 +1385,16 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D7" s="131" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в контроле отсутствия в информационных системах незаблокированных учётных записей следующих категорий субъектов, фактически утративших основания для логического доступа:
+      <c r="D7" s="148" t="inlineStr">
+        <is>
+          <t>Мера предполагает контроль отсутствия в информационных системах незаблокированных учётных записей следующих категорий субъектов, фактически утративших основания для логического доступа:
 1. Уволенных работников;
 2. Работников, отсутствующих на рабочем месте более 90 календарных дней (например, в связи с длительным отпуском, отпуском по уходу за ребёнком, длительной болезнью);
 3. Работников внешних (подрядных) организаций, прекративших свою деятельность в организации (истёк срок договора, договор расторгнут, завершены работы).
 Главная цель меры — исключить существование «мёртвых» учётных записей, формально всё ещё активных, но принадлежащих субъектам, у которых больше нет законных оснований для доступа, поскольку такие учётные записи представляют собой канал несанкционированного доступа, использование которого крайне сложно связать с конкретным нарушителем.</t>
         </is>
       </c>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="149" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1385,7 +1405,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка информирования подразделения, ответственного за управление учётными записями, о наступлении перечисленных событий. Для этого необходимо:
+Со стороны организационных мер требуется регламентировать порядок информирования подразделения, ответственного за управление учётными записями, о наступлении перечисленных событий:
 1. Утвердить регламент взаимодействия кадровой службы, подразделений — заказчиков услуг подрядных организаций и подразделения информационной безопасности, определяющий сроки и порядок передачи сведений об увольнении, длительном отсутствии работника или прекращении деятельности подрядной организации;
 2. Установить предельный срок блокирования учётной записи с момента наступления события (например, не позднее следующего рабочего дня);
 3. Проводить периодические контрольные сверки перечня активных учётных записей с кадровыми данными и данными о завершённых договорах.</t>
@@ -1400,22 +1420,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает автоматизацию блокирования учётных записей при наступлении контролируемых событий. Для этого используются:
+В части технических средств необходимо автоматизировать блокирование учётных записей при наступлении контролируемых событий:
 1. Интеграция системы управления учётными записями (IdM, каталог) с кадровой системой для автоматического блокирования учётной записи при регистрации в кадровой системе факта увольнения или длительного отсутствия работника;
 2. Автоматизированный контроль срока действия учётных записей подрядных организаций, привязанный к дате окончания действия договора, с автоматическим блокированием по её наступлении;
 3. Регулярные автоматизированные отчёты (задания по расписанию) о неразблокированных учётных записях уволенных и длительно отсутствующих работников для оперативного реагирования.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM).
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM).
 Иностранные: Microsoft Identity Manager, SailPoint IdentityIQ и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: FreeIPA, midPoint и др.</t>
@@ -1483,13 +1492,13 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D8" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в периодическом контроле того, что в информационных системах отсутствуют разблокированные учётные записи, назначение которых невозможно однозначно определить — то есть учётные записи, не привязанные к конкретному субъекту логического доступа (работнику, представителю подрядной организации) или к документированному технологическому процессу.
+      <c r="D8" s="144" t="inlineStr">
+        <is>
+          <t>Данная мера касается контроля отсутствия в информационных системах разблокированных учётных записей, назначение которых невозможно однозначно определить — то есть учётных записей, не привязанных к конкретному субъекту логического доступа (работнику, представителю подрядной организации) или к документированному технологическому процессу.
 Главная цель меры — исключить существование «бесхозных» учётных записей с неясной принадлежностью и назначением, поскольку такие учётные записи не позволяют установить ответственного за их использование и создают неконтролируемый канал доступа, привлекательный для нарушителя.</t>
         </is>
       </c>
-      <c r="E8" s="134" t="inlineStr">
+      <c r="E8" s="150" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1500,7 +1509,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает проведение периодической инвентаризации учётных записей с определением назначения каждой из них. Для этого необходимо:
+Организационно это выражается в проведении периодической инвентаризации учётных записей с определением назначения каждой из них:
 1. Утвердить регламент, определяющий периодичность и порядок инвентаризации учётных записей (например, ежеквартально);
 2. В ходе инвентаризации для каждой активной учётной записи установить, принадлежит ли она конкретному субъекту логического доступа либо документированному технологическому процессу (сервисная, техническая учётная запись), и кто является ответственным за её использование;
 3. По итогам инвентаризации учётные записи, назначение которых установить не удалось, блокировать до выяснения обстоятельств, а результаты инвентаризации и принятые решения фиксировать в акте.</t>
@@ -1567,13 +1576,13 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D10" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в разработке и утверждении внутреннего документа, устанавливающего правила предоставления, отзыва и блокирования логического доступа субъектов к ресурсам доступа финансовой организации.
+      <c r="D10" s="144" t="inlineStr">
+        <is>
+          <t>Мера сводится к разработке и утверждению внутреннего документа, устанавливающего правила предоставления, отзыва и блокирования логического доступа субъектов к ресурсам доступа финансовой организации.
 Главная цель меры — обеспечить, чтобы процессы управления логическим доступом выполнялись по единым, заранее определённым и утверждённым правилам, а не по усмотрению отдельных сотрудников, что делает управление доступом предсказуемым, воспроизводимым и проверяемым.</t>
         </is>
       </c>
-      <c r="E10" s="126" t="inlineStr">
+      <c r="E10" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1584,7 +1593,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Мера реализуется исключительно организационными методами и предполагает разработку и утверждение внутреннего нормативного документа (например, положения или регламента по управлению логическим доступом), в котором закрепляются:
+Поскольку мера реализуется только организационными методами, её внедрение предполагает разработку и утверждение внутреннего нормативного документа (например, положения или регламента по управлению логическим доступом), в котором закрепляются:
 1. Порядок и основания предоставления логического доступа (инициирование заявки, согласование распорядителем логического доступа, фактическое предоставление прав);
 2. Порядок и основания отзыва ранее предоставленных прав логического доступа;
 3. Порядок и основания блокирования учётных записей (плановое — при увольнении, истечении срока доступа; внеплановое — при выявлении инцидента);
@@ -1641,13 +1650,13 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D11" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в назначении для каждого ресурса доступа (информационной системы, базы данных, сетевого ресурса, отдельной функции автоматизированной системы (АС)) распорядителя логического доступа — должностного лица (владельца ресурса), уполномоченного принимать решения о предоставлении, изменении и отзыве прав логического доступа к данному ресурсу.
+      <c r="D11" s="144" t="inlineStr">
+        <is>
+          <t>Смысл меры — в назначении для каждого ресурса доступа (информационной системы, базы данных, сетевого ресурса, отдельной функции автоматизированной системы (АС)) распорядителя логического доступа — должностного лица (владельца ресурса), уполномоченного принимать решения о предоставлении, изменении и отзыве прав логического доступа к данному ресурсу.
 Главная цель меры — обеспечить персональную ответственность за принятие решений о доступе к каждому конкретному ресурсу, поскольку без явно определённого распорядителя решения о предоставлении доступа принимаются бессистемно (например, только силами IT-подразделения), без учёта реальной необходимости доступа для выполнения бизнес-функций.</t>
         </is>
       </c>
-      <c r="E11" s="126" t="inlineStr">
+      <c r="E11" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1658,7 +1667,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает документальное закрепление распорядителей логического доступа для всех ресурсов доступа. Для этого необходимо:
+Организационная составляющая сводится к документальному закреплению распорядителей логического доступа для всех ресурсов доступа:
 1. Составить и поддерживать в актуальном состоянии перечень ресурсов доступа организации;
 2. Для каждого ресурса доступа определить и документально закрепить (приказом, распоряжением либо в положении о ресурсе) распорядителя логического доступа из числа руководителей подразделений, в чьей зоне ответственности находится соответствующий ресурс;
 3. Довести до распорядителей логического доступа их обязанности и ответственность за принятие решений о предоставлении, изменении и отзыве прав доступа к закреплённому ресурсу;
@@ -1713,13 +1722,13 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D12" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в том, что предоставление прав логического доступа к ресурсу осуществляется только на основании решения распорядителя логического доступа (владельца соответствующего ресурса доступа), назначенного в рамках меры УЗП.6.
+      <c r="D12" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает, что предоставление прав логического доступа к ресурсу осуществляется только на основании решения распорядителя логического доступа (владельца соответствующего ресурса доступа), назначенного в рамках меры УЗП.6.
 Главная цель меры — исключить предоставление прав доступа в обход лица, ответственного за ресурс, поскольку только распорядитель обладает необходимыми знаниями о служебной необходимости доступа для конкретного субъекта, а предоставление прав без его санкции ведёт к избыточному и неконтролируемому расширению доступа.</t>
         </is>
       </c>
-      <c r="E12" s="126" t="inlineStr">
+      <c r="E12" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1730,7 +1739,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка согласования заявок на предоставление логического доступа с распорядителем логического доступа. Для этого необходимо:
+В организационном плане реализация включает регламентацию порядка согласования заявок на предоставление логического доступа с распорядителем логического доступа:
 1. Установить обязательный порядок, при котором любое предоставление (изменение) прав логического доступа к ресурсу инициируется заявкой и требует явного согласования (утверждения) со стороны распорядителя логического доступа, закреплённого за данным ресурсом;
 2. Определить форму и способ фиксации решения распорядителя (подпись на бумажном носителе, согласование в системе электронного документооборота или service desk);
 3. Установить запрет на предоставление прав логического доступа администратором (исполнителем) без документально зафиксированного решения распорядителя;
@@ -1786,13 +1795,13 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D13" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в ведении эталонного (авторитетного) источника информации о фактически предоставленных субъектам правах логического доступа, а также в обеспечении целостности этой информации — то есть её защищённости от несанкционированного или бесконтрольного изменения.
+      <c r="D13" s="144" t="inlineStr">
+        <is>
+          <t>В основе меры лежит ведение эталонного (авторитетного) источника информации о фактически предоставленных субъектам правах логического доступа, а также обеспечение целостности этой информации — то есть её защищённости от несанкционированного или бесконтрольного изменения.
 Главная цель меры — обеспечить наличие достоверного и защищённого от подмены источника данных о предоставленных правах доступа, поскольку без такого эталона невозможно достоверно контролировать соответствие фактических прав доступа санкционированным (мера УЗП.9), а искажение эталонных данных способно скрыть факт несанкционированного расширения прав.</t>
         </is>
       </c>
-      <c r="E13" s="126" t="inlineStr">
+      <c r="E13" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1803,7 +1812,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка ведения и защиты эталонной информации о предоставленных правах логического доступа. Для этого необходимо:
+Со стороны организационных мер требуется регламентировать порядок ведения и защиты эталонной информации о предоставленных правах логического доступа:
 1. Определить источник (систему), являющийся эталонным хранилищем информации о предоставленных правах логического доступа (например, система IdM, реестр заявок на доступ);
 2. Установить порядок внесения изменений в эталонную информацию исключительно на основании документально оформленных и согласованных решений распорядителей логического доступа;
 3. Ограничить круг лиц, имеющих право вносить изменения в эталонную информацию, минимально необходимым составом;
@@ -1819,22 +1828,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает применение технических средств для хранения эталонной информации и контроля её целостности. Для этого используются:
+Технически это обеспечивается применением средств хранения эталонной информации и контроля её целостности:
 1. Хранение эталонной информации о предоставленных правах в специализированной системе (IdM, система управления доступом) с разграничением прав доступа к самой этой информации на уровне операционной системы и приложения;
 2. Технические механизмы контроля целостности данных (контрольные суммы, электронная подпись записей, версионирование изменений) с автоматическим выявлением фактов несанкционированного изменения эталонной информации;
 3. Регистрация в журнале событий всех операций изменения эталонной информации о предоставленных правах доступа.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM) со встроенным контролем целостности.
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM) со встроенным контролем целостности.
 Иностранные: SailPoint IdentityIQ, One Identity Manager и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: midPoint и др.</t>
@@ -1902,13 +1900,13 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D14" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в периодическом сопоставлении фактических прав логического доступа, действующих в информационных системах, с эталонной информацией о предоставленных правах, которая ведётся и защищается в рамках меры УЗП.8.
+      <c r="D14" s="144" t="inlineStr">
+        <is>
+          <t>Мера заключается в периодическом сопоставлении фактических прав логического доступа, действующих в информационных системах, с эталонной информацией о предоставленных правах, которая ведётся и защищается в рамках меры УЗП.8.
 Главная цель меры — своевременно выявлять расхождения между тем, какие права доступа должны быть предоставлены субъекту согласно эталонным (санкционированным) данным, и тем, какие права фактически действуют в информационных системах, поскольку такие расхождения могут свидетельствовать как об ошибках администрирования, так и о несанкционированном изменении прав доступа.</t>
         </is>
       </c>
-      <c r="E14" s="126" t="inlineStr">
+      <c r="E14" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1919,7 +1917,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает проведение периодических ручных сверок фактических прав доступа с эталонной информацией. Для этого необходимо:
+Организационно мера реализуется через периодические ручные сверки фактических прав доступа с эталонной информацией:
 1. Утвердить регламент проведения сверки с указанием периодичности, перечня проверяемых ресурсов доступа и ответственных лиц;
 2. Провести сверку выгрузки фактических прав доступа из информационных систем с эталонной информацией;
 3. По фактам выявленных расхождений инициировать служебное разбирательство и корректировку прав доступа до соответствия эталонным данным;
@@ -1935,21 +1933,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает автоматизацию сверки фактических прав доступа с эталонными данными. Для этого используются:
+На техническом уровне сверку целесообразно автоматизировать:
 1. Средства автоматической сверки (recertification, access review), формирующие отчёты о расхождениях между эталонными данными системы IdM и фактическими правами, действующими в подключённых информационных системах;
 2. Настройка регулярных автоматических заданий (скриптов, коннекторов), сравнивающих выгрузку прав доступа из целевых систем с эталонным источником и оповещающих ответственных лиц о выявленных расхождениях.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM) с функцией пересертификации доступа.
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM) с функцией пересертификации доступа.
 Иностранные: SailPoint IdentityIQ, Saviynt и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: midPoint и др.</t>
@@ -2016,13 +2003,13 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D15" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в исключении технической возможности для пользователей самостоятельно, без санкции распорядителя логического доступа, расширять предоставленные им права логического доступа — то есть предоставлять себе дополнительные полномочия, изменять состав ролей, повышать уровень привилегий.
+      <c r="D15" s="144" t="inlineStr">
+        <is>
+          <t>Мера исключает техническую возможность для пользователей самостоятельно, без санкции распорядителя логического доступа, расширять предоставленные им права логического доступа — то есть предоставлять себе дополнительные полномочия, изменять состав ролей, повышать уровень привилегий.
 Главная цель меры — не допустить ситуации, при которой пользователь фактически становится собственным распорядителем доступа, поскольку возможность бесконтрольного самостоятельного расширения прав полностью обесценивает всю систему санкционирования доступа, реализованную в рамках мер УЗП.6 и УЗП.7.</t>
         </is>
       </c>
-      <c r="E15" s="135" t="inlineStr">
+      <c r="E15" s="152" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2033,22 +2020,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку технических средств таким образом, чтобы пользователи не имели возможности самостоятельно изменять состав предоставленных им прав. Основные направления реализации:
+Ввиду сугубо технического характера меры её внедрение сводится к настройке технических средств таким образом, чтобы пользователи не имели возможности самостоятельно изменять состав предоставленных им прав:
 1. Разграничение полномочий на уровне операционных систем, СУБД и прикладного ПО, при котором функции управления собственными правами доступа (назначение ролей, изменение членства в группах, предоставление привилегий) недоступны обычным пользователям и закреплены исключительно за администраторами и системами управления доступом;
 2. Технический запрет на изменение пользователем собственных атрибутов в системе управления учётными записями (каталоге, IdM), связанных с правами доступа;
 3. Контроль целостности и регистрация попыток изменения параметров прав доступа с оповещением администратора безопасности при выявлении попытки самостоятельного расширения прав пользователем.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — средства защиты от несанкционированного доступа (СЗИ от НСД), системы управления учётными записями и правами доступа (IdM).
+Применимый класс средств — средства защиты от несанкционированного доступа (СЗИ от НСД), системы управления учётными записями и правами доступа (IdM).
 Иностранные: Microsoft Active Directory (разграничение делегирования прав), One Identity Manager и пр.
 Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К, Avanpost IDM и др.
 Открытый код: FreeIPA, midPoint и др.</t>
@@ -2098,15 +2074,15 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D16" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в исключении технической возможности для пользователей бесконтрольно, без санкции уполномоченных лиц, изменять:
+      <c r="D16" s="144" t="inlineStr">
+        <is>
+          <t>Речь идёт об исключении технической возможности для пользователей бесконтрольно, без санкции уполномоченных лиц, изменять:
 1. Параметры настроек средств и систем защиты информации;
 2. Параметры настроек автоматизированных систем (АС), связанные с защитой информации.
 Главная цель меры — обеспечить целостность и контролируемость конфигураций всех защищаемых компонентов информационной инфраструктуры, исключив ситуации, когда изменение критических параметров безопасности может быть выполнено неуполномоченным лицом как умышленно, так и по ошибке.</t>
         </is>
       </c>
-      <c r="E16" s="126" t="inlineStr">
+      <c r="E16" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2117,23 +2093,12 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает разграничение прав доступа к параметрам настроек средств защиты информации и АС и контроль их изменения. Основные направления реализации:
+Так как мера реализуется только техническими средствами, необходимо разграничить права доступа к параметрам настроек средств защиты информации и АС и наладить контроль их изменения:
 1. Выделение привилегированных учётных записей с минимально необходимыми правами на изменение параметров настроек СЗИ и АС, использование ролевых моделей доступа;
 2. Технический запрет на изменение защищаемых параметров настроек для учётных записей обычных пользователей на уровне операционной системы, приложений и самих средств защиты информации;
 3. Принудительное применение эталонных параметров настроек средствами централизованного управления конфигурациями (например, групповыми политиками) с автоматическим выявлением и блокированием отклонений;
 4. Регистрация всех попыток изменения защищаемых параметров настроек в журнале событий средства защиты информации или операционной системы.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — средства защиты от несанкционированного доступа (СЗИ от НСД), системы управления конфигурациями и контроля целостности.
+Применимый класс средств — средства защиты от несанкционированного доступа (СЗИ от НСД), системы управления конфигурациями и контроля целостности.
 Иностранные: Tripwire Enterprise, Microsoft Group Policy (AD GPO), Ivanti Endpoint Manager и пр.
 Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К, ViPNet Coordinator и др.
 Открытый код: Osquery, OSSEC и др.</t>
@@ -2181,13 +2146,13 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D17" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в контроле того, что при изменении должностных обязанностей субъекта логического доступа (перевод на другую должность, изменение зоны ответственности, временное исполнение обязанностей по другой должности) проводится анализ необходимости отзыва ранее предоставленных ему прав доступа, переставших соответствовать новым обязанностям.
+      <c r="D17" s="144" t="inlineStr">
+        <is>
+          <t>Мера обязывает контролировать необходимость отзыва прав субъекта логического доступа при изменении его должностных обязанностей (перевод на другую должность, изменение зоны ответственности, временное исполнение обязанностей по другой должности).
 Главная цель меры — не допустить накопления у субъекта избыточных прав доступа при должностных перемещениях внутри организации, поскольку без такого контроля права доступа со временем только добавляются, но не отзываются, что приводит к формированию у отдельных сотрудников чрезмерно широкого, несоответствующего текущим обязанностям набора полномочий.</t>
         </is>
       </c>
-      <c r="E17" s="126" t="inlineStr">
+      <c r="E17" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2198,7 +2163,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка контроля прав доступа при кадровых перемещениях. Для этого необходимо:
+Организационно это выражается в регламентации порядка контроля прав доступа при кадровых перемещениях:
 1. Установить обязанность подразделения, ответственного за управление учётными записями (или распорядителя логического доступа), проводить анализ ранее предоставленных прав доступа субъекта при получении сведений об изменении его должностных обязанностей;
 2. Определить порядок и сроки проведения такого анализа с момента получения кадровой информации об изменении должности (перевода);
 3. По результатам анализа инициировать отзыв прав доступа, не соответствующих новым должностным обязанностям, и предоставление новых прав при необходимости;
@@ -2253,13 +2218,13 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D18" s="137" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в контроле того, что логический доступ, предоставленный субъекту на определённый период (срок) — например, для выполнения временных задач, представителям подрядных организаций на срок действия договора, — фактически прекращается, а соответствующая учётная запись блокируется по истечении установленного срока.
+      <c r="D18" s="153" t="inlineStr">
+        <is>
+          <t>Суть меры — в контроле того, что логический доступ, предоставленный субъекту на определённый период (срок) — например, для выполнения временных задач, представителям подрядных организаций на срок действия договора, — фактически прекращается, а соответствующая учётная запись блокируется по истечении установленного срока.
 Главная цель меры — исключить продолжение действия прав логического доступа после истечения оснований, на которых эти права были предоставлены, поскольку доступ, предоставленный на ограниченный срок, но не прекращённый по его истечении, фактически превращается в бессрочный и бесконтрольный.</t>
         </is>
       </c>
-      <c r="E18" s="138" t="inlineStr">
+      <c r="E18" s="154" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2270,7 +2235,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка контроля сроков предоставленного доступа. Для этого необходимо:
+С организационной стороны мера реализуется через регламентацию порядка контроля сроков предоставленного доступа:
 1. Установить обязательное указание срока действия прав логического доступа в заявке на предоставление доступа для всех случаев срочного (временного) доступа;
 2. Определить ответственных за контроль соблюдения указанных сроков и порядок их действий по истечении срока (блокирование учётной записи, продление доступа по обоснованной заявке);
 3. Проводить периодические проверки перечня учётных записей с истёкшим сроком предоставленного доступа на предмет фактического блокирования.</t>
@@ -2285,22 +2250,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает автоматизацию контроля и применения ограничения сроков действия доступа. Для этого используются:
+Технически контроль сроков и применение ограничений реализуются так:
 1. Установка технического срока действия учётной записи (account expiration) или отдельных прав доступа непосредственно при их предоставлении в информационной системе или системе управления доступом (IdM, каталог);
 2. Автоматическое блокирование учётной записи или отзыв прав доступа средствами информационной системы по наступлении установленной даты без необходимости ручного вмешательства;
 3. Автоматизированные отчёты (оповещения) о приближающемся или наступившем истечении срока предоставленного доступа для ответственных лиц.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM), службы каталогов.
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM), службы каталогов.
 Иностранные: Microsoft Active Directory (срок действия учётной записи), One Identity Manager и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: FreeIPA, midPoint и др.</t>
@@ -2375,7 +2329,7 @@
 Главная цель меры — своевременно выявлять «мёртвые» учётные записи и избыточные права доступа.</t>
         </is>
       </c>
-      <c r="E19" s="138" t="inlineStr">
+      <c r="E19" s="154" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2386,7 +2340,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает проведение периодических ручных проверок с использованием отчётов из систем учёта доступа. Для этого формируются протоколы (акты) о субъектах, которые не осуществляли логический доступ в течение 90 и более дней, по итогам которых распорядителями логического доступа принимается решение о целесообразности дальнейшего предоставления неиспользуемых прав (см. меру УЗП.16).</t>
+Организационно мера реализуется через периодические ручные проверки с использованием отчётов из систем учёта доступа: формируются протоколы (акты) о субъектах, которые не осуществляли логический доступ в течение 90 и более дней, по итогам которых распорядителями логического доступа принимается решение о целесообразности дальнейшего предоставления неиспользуемых прав (см. меру УЗП.16).</t>
           </r>
           <r>
             <rPr>
@@ -2398,19 +2352,8 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает настройку сбора и хранения событий аутентификации и авторизации (успешные и неудачные входы, использование прав доступа, запуск привилегированных команд) в системных журналах, базе данных Active Directory или специализированных системах управления доступом. Для автоматизированного выявления неиспользуемых прав применяются средства анализа журналов или SIEM-системы, формирующие отчёты по учётным записям с отсутствием активности за период, превышающий 90 дней.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM), средства анализа журналов и SIEM.
+На техническом уровне необходима настройка сбора и хранения событий аутентификации и авторизации (успешные и неудачные входы, использование прав доступа, запуск привилегированных команд) в системных журналах, базе данных Active Directory или специализированных системах управления доступом. Для автоматизированного выявления неиспользуемых прав применяются средства анализа журналов или SIEM-системы, формирующие отчёты по учётным записям с отсутствием активности за период, превышающий 90 дней.
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM), средства анализа журналов и SIEM.
 Иностранные: Microsoft Active Directory, ManageEngine ADManager Plus, SolarWinds Access Rights Manager и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: Osquery, Graylog и др.</t>
@@ -2473,13 +2416,13 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D20" s="137" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в выявлении учётных записей и прав логического доступа, которые были предоставлены субъектам, но фактически не использовались ими на протяжении периода, превышающего 45 дней. Мера аналогична УЗП.14, но применяется к более короткому контрольному периоду и, в отличие от УЗП.14, требует исключительно технической (автоматизированной) реализации.
+      <c r="D20" s="153" t="inlineStr">
+        <is>
+          <t>Как и УЗП.14, данная мера направлена на выявление учётных записей и прав логического доступа, которые были предоставлены субъектам, но фактически не использовались ими — только контрольный период здесь короче (45, а не 90 дней), и, в отличие от УЗП.14, мера требует исключительно технической (автоматизированной) реализации.
 Главная цель меры — обеспечить более оперативное, чем в рамках УЗП.14, выявление неиспользуемых прав доступа для организаций (уровней защиты), где повышенные требования к оперативности контроля не позволяют полагаться на периодические ручные проверки.</t>
         </is>
       </c>
-      <c r="E20" s="138" t="inlineStr">
+      <c r="E20" s="154" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2490,22 +2433,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает автоматизированный, без участия оператора, контроль активности использования прав логического доступа. Основные направления реализации:
+Поскольку организационные меры здесь неприменимы, реализация строится исключительно на автоматизированном, без участия оператора, контроле активности использования прав логического доступа:
 1. Автоматизированный сбор и хранение событий аутентификации и авторизации (успешные и неудачные входы, использование прав доступа) в журналах информационных систем, каталоге (AD/LDAP) или системе управления доступом;
 2. Автоматическое формирование средствами анализа журналов или SIEM-системой перечня учётных записей, не проявлявших активности на протяжении более 45 дней, без необходимости запуска проверки вручную;
 3. Автоматическое оповещение ответственных лиц (администратора безопасности, распорядителя логического доступа) о выявленных фактах неиспользования прав для принятия решения в рамках меры УЗП.16.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM), средства анализа журналов и SIEM.
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM), средства анализа журналов и SIEM.
 Иностранные: Microsoft Active Directory, SolarWinds Access Rights Manager и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: Osquery, Graylog и др.</t>
@@ -2559,13 +2491,13 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D21" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в том, что по фактам неиспользования прав логического доступа, выявленным в рамках мер УЗП.14 и УЗП.15, распорядитель логического доступа (владелец ресурса доступа) проводит анализ и принимает решение о целесообразности дальнейшего предоставления субъекту этих прав.
+      <c r="D21" s="144" t="inlineStr">
+        <is>
+          <t>Мера предусматривает, что по фактам неиспользования прав логического доступа, выявленным в рамках мер УЗП.14 и УЗП.15, распорядитель логического доступа (владелец ресурса доступа) проводит анализ и принимает решение о целесообразности дальнейшего предоставления субъекту этих прав.
 Главная цель меры — обеспечить, чтобы выявление неиспользуемых прав доступа не оставалось формальной процедурой без последствий, а завершалось содержательным решением лица, ответственного за ресурс: сохранить права за субъектом (при наличии обоснованной необходимости) либо отозвать их как избыточные.</t>
         </is>
       </c>
-      <c r="E21" s="126" t="inlineStr">
+      <c r="E21" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2576,7 +2508,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка рассмотрения распорядителем логического доступа фактов, выявленных в рамках мер УЗП.14 и УЗП.15. Для этого необходимо:
+Поскольку мера реализуется только организационными методами, требуется регламентировать порядок рассмотрения распорядителем логического доступа фактов, выявленных в рамках мер УЗП.14 и УЗП.15:
 1. Установить обязанность передачи распорядителю логического доступа перечня неиспользуемых прав, выявленных по конкретному ресурсу доступа, с определённой периодичностью;
 2. Установить срок, в течение которого распорядитель обязан рассмотреть полученные сведения и принять решение (сохранить права, отозвать права, запросить обоснование у субъекта);
 3. Зафиксировать порядок документального оформления принятого решения и передачи его для исполнения (отзыва прав) подразделению, ответственному за управление доступом;
@@ -2632,13 +2564,13 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D22" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в обеспечении технической и организационной возможности в любой момент времени однозначно определить полный состав субъектов и прав логического доступа, предоставленных к конкретному ресурсу доступа (информационной системе, базе данных, сетевому ресурсу).
+      <c r="D22" s="144" t="inlineStr">
+        <is>
+          <t>Мера обеспечивает техническую и организационную возможность в любой момент времени однозначно определить полный состав субъектов и прав логического доступа, предоставленных к конкретному ресурсу доступа (информационной системе, базе данных, сетевому ресурсу).
 Главная цель меры — дать распорядителю логического доступа, подразделению информационной безопасности и внешним проверяющим возможность оперативно получить достоверный ответ на вопрос «кто и какими правами обладает в отношении данного ресурса», без чего невозможны ни контроль соответствия прав эталонной информации (УЗП.9), ни расследование инцидентов, связанных с этим ресурсом.</t>
         </is>
       </c>
-      <c r="E22" s="126" t="inlineStr">
+      <c r="E22" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2649,7 +2581,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка получения сведений о составе предоставленных прав доступа к ресурсу. Для этого необходимо:
+Организационно это выражается в регламентации порядка получения сведений о составе предоставленных прав доступа к ресурсу:
 1. Определить порядок и сроки предоставления по запросу распорядителя логического доступа, подразделения информационной безопасности или проверяющих лиц выгрузки (отчёта) о составе субъектов и прав доступа к конкретному ресурсу;
 2. Закрепить ответственного (администратора ресурса или системы управления доступом) за формирование такой выгрузки.</t>
           </r>
@@ -2663,21 +2595,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает наличие в информационной системе или системе управления доступом функции формирования отчёта о правах доступа в разрезе ресурса. Для этого используются:
+Технически это требует наличия в информационной системе или системе управления доступом функции формирования отчёта о правах доступа в разрезе ресурса:
 1. Встроенные средства информационной системы (АС, СУБД) или системы управления учётными записями и правами доступа (IdM), позволяющие сформировать перечень субъектов и предоставленных им прав для выбранного ресурса доступа;
 2. Средства выгрузки списков контроля доступа (ACL) сетевого оборудования, файловых ресурсов и иных технических ресурсов доступа.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM), средства защиты от НСД со встроенной отчётностью.
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM), средства защиты от НСД со встроенной отчётностью.
 Иностранные: SailPoint IdentityIQ, Netwrix Access Analyzer и пр.
 Российские сертифицированные (ФСТЭК): Secret Net Studio, Avanpost IDM, Solar inRights и др.
 Открытый код: midPoint и др.</t>
@@ -2743,13 +2664,13 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D23" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в обеспечении технической и организационной возможности в любой момент времени однозначно определить полный состав ресурсов доступа и прав логического доступа, предоставленных конкретному субъекту (работнику, представителю эксплуатационного персонала).
+      <c r="D23" s="144" t="inlineStr">
+        <is>
+          <t>Зеркально мере УЗП.17, данная мера обеспечивает техническую и организационную возможность в любой момент времени однозначно определить полный состав ресурсов доступа и прав логического доступа, предоставленных конкретному субъекту (работнику, представителю эксплуатационного персонала).
 Главная цель меры — дать распорядителям логического доступа и подразделению информационной безопасности возможность оперативно получить достоверный ответ на вопрос «какими правами доступа в отношении каких ресурсов обладает данный субъект», что необходимо как для контроля обоснованности объёма прав (принцип минимально необходимых прав), так и для оперативного реагирования на инциденты, связанные с конкретным субъектом.</t>
         </is>
       </c>
-      <c r="E23" s="126" t="inlineStr">
+      <c r="E23" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2760,7 +2681,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает регламентацию порядка получения сведений о составе прав доступа субъекта. Для этого необходимо:
+С организационной стороны требуется регламентировать порядок получения сведений о составе прав доступа субъекта:
 1. Определить порядок и сроки предоставления по запросу руководителя субъекта, распорядителей логического доступа или подразделения информационной безопасности выгрузки (отчёта) о составе ресурсов доступа и прав, предоставленных конкретному субъекту;
 2. Закрепить ответственного (подразделение, отвечающее за управление учётными записями) за формирование такой выгрузки.</t>
           </r>
@@ -2774,21 +2695,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает наличие в системе управления учётными записями и правами доступа функции формирования сводного отчёта о правах конкретного субъекта. Для этого используются:
+На техническом уровне требуется наличие в системе управления учётными записями и правами доступа функции формирования сводного отчёта о правах конкретного субъекта:
 1. Система класса IdM, консолидирующая сведения о правах доступа субъекта во всех подключённых информационных системах и позволяющая сформировать единый («профильный») отчёт по конкретной учётной записи;
 2. При отсутствии централизованной системы IdM — совокупность встроенных средств формирования отчётов в каждой отдельной информационной системе.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM).
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM).
 Иностранные: SailPoint IdentityIQ, One Identity Manager и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: midPoint и др.</t>
@@ -2854,16 +2764,16 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D24" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в:
-1. Определении состава ролей логического доступа, связанных с непосредственным выполнением операций (транзакций) в автоматизированных системах (АС), имеющих финансовые последствия для финансовой организации, её клиентов и контрагентов;
-2. Определении состава ролей, связанных с контролем выполнения указанных операций (транзакций);
-3. Установлении запрета на совмещение указанных ролей одним и тем же субъектом логического доступа.
+      <c r="D24" s="144" t="inlineStr">
+        <is>
+          <t>Мера охватывает сразу три взаимосвязанных требования:
+1. Определение состава ролей логического доступа, связанных с непосредственным выполнением операций (транзакций) в автоматизированных системах (АС), имеющих финансовые последствия для финансовой организации, её клиентов и контрагентов;
+2. Определение состава ролей, связанных с контролем выполнения указанных операций (транзакций);
+3. Установление запрета на совмещение указанных ролей одним и тем же субъектом логического доступа.
 Главная цель меры — реализовать принцип разделения обязанностей (segregation of duties) применительно к финансово значимым операциям: не допустить ситуации, при которой один и тот же субъект одновременно совершает операцию и контролирует её выполнение, поскольку совмещение этих ролей делает контроль фиктивным и создаёт условия для совершения и сокрытия мошеннических действий.</t>
         </is>
       </c>
-      <c r="E24" s="126" t="inlineStr">
+      <c r="E24" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2874,7 +2784,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает документальное определение состава ролей и закрепление запрета на их совмещение. Для этого необходимо:
+Организационно мера реализуется через документальное определение состава ролей и закрепление запрета на их совмещение:
 1. Совместно с владельцами бизнес-процессов и распорядителями логического доступа провести анализ автоматизированных систем и операций (транзакций), имеющих финансовые последствия для организации, клиентов и контрагентов;
 2. Сформировать и утвердить перечень ролей логического доступа, связанных с выполнением таких операций, и отдельно — перечень ролей, связанных с контролем их выполнения;
 3. Закрепить во внутреннем нормативном документе прямой запрет на предоставление одному субъекту логического доступа ролей из обеих категорий одновременно;
@@ -2890,21 +2800,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает применение технических средств для контроля состава ролей и недопущения их совмещения. Для этого используются:
+Технические средства применяются для контроля состава ролей и недопущения их совмещения:
 1. Ролевая модель управления доступом (RBAC), реализованная в АС или системе управления доступом (IdM), в которой роли, связанные с выполнением и с контролем финансово значимых операций, технически обособлены друг от друга;
 2. Функционал контроля разделения полномочий (Segregation of Duties, SoD), встроенный в систему IdM или GRC-платформу, автоматически выявляющий и блокирующий попытки предоставления субъекту конфликтующих ролей.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM) и GRC-платформы с функцией контроля разделения полномочий (SoD).
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM) и GRC-платформы с функцией контроля разделения полномочий (SoD).
 Иностранные: SAP GRC Access Control, SailPoint IdentityIQ и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights (с модулем контроля SoD) и др.
 Открытый код: midPoint и др.</t>
@@ -2972,13 +2871,13 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D25" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в практической реализации в процессах управления логическим доступом правил, обеспечивающих соблюдение запрета на совмещение одним субъектом ролей выполнения и контроля финансово значимых операций, состав которых определён в рамках меры УЗП.19.
-Главная цель меры — обеспечить, чтобы запрет на совмещение ролей, зафиксированный документально в рамках УЗП.19, реально соблюдался на всех этапах жизненного цикла прав доступа — при первичном предоставлении доступа, при последующих изменениях и при периодическом контроле, а не оставался декларацией, не подкреплённой действующими процедурами управления доступом.</t>
-        </is>
-      </c>
-      <c r="E25" s="126" t="inlineStr">
+      <c r="D25" s="144" t="inlineStr">
+        <is>
+          <t>Мера переводит в практическую плоскость запрет на совмещение одним субъектом ролей выполнения и контроля финансово значимых операций, состав которых определён в рамках меры УЗП.19.
+Главная цель меры — обеспечить, чтобы этот запрет реально соблюдался на всех этапах жизненного цикла прав доступа — при первичном предоставлении доступа, при последующих изменениях и при периодическом контроле, а не оставался декларацией, не подкреплённой действующими процедурами управления доступом.</t>
+        </is>
+      </c>
+      <c r="E25" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2989,7 +2888,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает встраивание проверки соблюдения запрета на совмещение ролей в процессы предоставления и изменения прав логического доступа. Для этого необходимо:
+С организационной стороны требуется встроить проверку соблюдения запрета на совмещение ролей в процессы предоставления и изменения прав логического доступа:
 1. Установить обязательную проверку заявки на предоставление (изменение) прав логического доступа на предмет потенциального конфликта с ролями, предусмотренными мерой УЗП.19, до её согласования распорядителем логического доступа;
 2. Определить порядок действий при выявлении конфликта ролей (отказ в предоставлении, требование обоснования и утверждения компенсирующей меры на уровне руководства);
 3. Периодически проводить ручные проверки фактического состава ролей субъектов на предмет соблюдения запрета совмещения.</t>
@@ -3004,21 +2903,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает автоматизацию проверки заявок и фактических прав доступа на предмет конфликта ролей. Для этого используются:
+Технически проверку заявок и фактических прав доступа на предмет конфликта ролей целесообразно автоматизировать:
 1. Автоматическая проверка каждой заявки на предоставление или изменение прав логического доступа на предмет конфликта с ролями, предусмотренными мерой УЗП.19, средствами системы IdM или GRC-платформы, с технической блокировкой предоставления конфликтующих прав;
 2. Периодические автоматизированные проверки (recertification) фактического состава прав всех субъектов на предмет выявления совмещения ролей, с формированием отчёта о выявленных конфликтах.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM) и GRC-платформы с функцией контроля разделения полномочий (SoD).
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM) и GRC-платформы с функцией контроля разделения полномочий (SoD).
 Иностранные: SAP GRC Access Control, SailPoint IdentityIQ и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights (с модулем контроля SoD) и др.
 Открытый код: midPoint и др.</t>
@@ -3090,9 +2978,9 @@
           <t>Н-О-Т</t>
         </is>
       </c>
-      <c r="D26" s="141" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в реализации правил управления правами логического доступа, обеспечивающих запрет на совмещение одним субъектом логического доступа следующих несовместимых функций:
+      <c r="D26" s="155" t="inlineStr">
+        <is>
+          <t>Мера закрепляет запрет на совмещение одним субъектом логического доступа следующих несовместимых функций:
 1. Эксплуатация и (или) контроль эксплуатации ресурса доступа, в том числе АС, одновременно с использованием этого же ресурса по назначению в рамках бизнес-процесса финансовой организации;
 2. Создание и (или) модернизация ресурса доступа, в том числе АС, одновременно с использованием этого же ресурса по назначению в рамках бизнес-процесса финансовой организации;
 3. Эксплуатация средств и систем защиты информации одновременно с контролем эксплуатации средств и систем защиты информации;
@@ -3100,7 +2988,7 @@
 Главная цель меры — реализовать принцип разделения обязанностей в отношении технического персонала и администраторов: не допустить сосредоточения в руках одного субъекта функций, взаимный контроль которых является необходимым элементом системы защиты информации, поскольку их совмещение позволяет субъекту скрыть собственные неправомерные действия.</t>
         </is>
       </c>
-      <c r="E26" s="126" t="inlineStr">
+      <c r="E26" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3111,7 +2999,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает документальное закрепление и соблюдение перечисленных запретов при формировании штатной структуры и распределении обязанностей. Для этого необходимо:
+Организационная составляющая сводится к документальному закреплению и соблюдению перечисленных запретов при формировании штатной структуры и распределении обязанностей:
 1. Закрепить во внутреннем нормативном документе перечень несовместимых функций, приведённый в описании меры;
 2. При формировании должностных инструкций и распределении обязанностей между сотрудниками (подразделениями) обеспечивать, чтобы ни один субъект не наделялся одновременно взаимоисключающими функциями;
 3. При предоставлении прав логического доступа проверять заявку на предмет соответствия установленным запретам до её согласования распорядителем логического доступа;
@@ -3127,23 +3015,12 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация предполагает разграничение прав логического доступа таким образом, чтобы техническая возможность совмещения перечисленных функций у одного субъекта отсутствовала. Для этого используются:
+Технически права логического доступа разграничиваются так, чтобы возможность совмещения перечисленных функций у одного субъекта отсутствовала:
 1. Ролевая модель управления доступом, в которой роли администрирования ресурсов доступа (АС) и роли их использования по назначению технически обособлены и не могут быть назначены одному субъекту;
 2. Ролевая модель, разделяющая права на эксплуатацию средств и систем защиты информации и права на контроль (аудит) их эксплуатации;
 3. Техническое разделение функций управления учётными записями (создание, блокирование) и функций управления правами доступа (назначение ролей, прав) между разными субъектами на уровне системы управления доступом (IdM);
 4. Функционал контроля разделения полномочий (SoD) в IdM/GRC-платформе, автоматически выявляющий и блокирующий попытки назначения субъекту несовместимых функций.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM) и GRC-платформы с функцией контроля разделения полномочий (SoD).
+Применимый класс средств — системы управления учётными записями и правами доступа (IdM) и GRC-платформы с функцией контроля разделения полномочий (SoD).
 Иностранные: SAP GRC Access Control, One Identity Manager и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
 Открытый код: midPoint и др.</t>
@@ -22891,8 +22768,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -793,6 +793,10 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3767,10 +3771,60 @@
           <t>Т-Т-Н</t>
         </is>
       </c>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="31" t="n"/>
-      <c r="G37" s="31" t="n"/>
+      <c r="D37" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает базовое требование: перед предоставлением логического доступа пользователь должен пройти идентификацию (предъявление уникального идентификатора — логина, номера учётной записи) и однофакторную аутентификацию (подтверждение подлинности с использованием одного фактора — как правило, пароля).
+Главная цель меры — исключить анонимный или неаутентифицированный доступ к ресурсам финансовой организации: без этой базовой процедуры невозможно связать действия в системе с конкретным субъектом, а любые более сложные меры защиты логического доступа (в том числе разграничение прав) теряют смысл.</t>
+        </is>
+      </c>
+      <c r="E37" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера носит сугубо технический характер, её внедрение сводится к настройке штатных механизмов идентификации и аутентификации:
+1. Настройка операционных систем, СУБД, прикладного программного обеспечения (ПО) и сетевого оборудования таким образом, чтобы вход в систему был невозможен без предъявления уникального идентификатора и прохождения проверки подлинности (пароля);
+2. Централизованное управление учётными данными через каталог (Active Directory, LDAP) либо локальные механизмы аутентификации для систем, не подключённых к каталогу;
+3. Технический запрет анонимного доступа и доступа без прохождения процедуры аутентификации.
+Применимый класс средств — операционные системы и прикладное ПО со встроенными механизмами идентификации и аутентификации, службы каталогов, средства защиты от несанкционированного доступа (СЗИ от НСД).
+Иностранные: Microsoft Active Directory, Cisco ISE (для сетевого доступа) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К и др.
+Открытый код: FreeIPA, OpenLDAP и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F37" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты настроек, подтверждающие обязательность идентификации и аутентификации при входе в информационные системы;
+3. Результаты тестирования (попытка входа без учётных данных или под неизвестным идентификатором), подтверждающие невозможность анонимного доступа;
+4. Журналы событий, подтверждающие регистрацию фактов идентификации и аутентификации пользователей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G37" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельные информационные системы или сервисы допускают вход без идентификации и аутентификации (например, тестовые или устаревшие системы);
+2. Идентификация не является уникальной — несколько пользователей используют один и тот же идентификатор;
+3. Настройки, требующие обязательной аутентификации, применены не на всех точках входа (например, отсутствуют на резервных или альтернативных интерфейсах доступа);
+4. Отсутствует регистрация фактов идентификации и аутентификации, что не позволяет подтвердить соблюдение меры.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="213.75" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
@@ -3794,9 +3848,55 @@
 Главная цель меры — значительно повысить уровень защищённости процесса аутентификации по сравнению с однофакторными методами (например, только паролем). Даже если один из факторов будет скомпрометирован (например, пароль украден), злоумышленник не сможет получить доступ, так как ему потребуется предъявить второй (и/или третий) независимый фактор.</t>
         </is>
       </c>
-      <c r="E38" s="31" t="n"/>
-      <c r="F38" s="31" t="n"/>
-      <c r="G38" s="31" t="n"/>
+      <c r="E38" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит чисто технический характер и включает:
+1. Настройку систем многофакторной аутентификации (МФА), требующих последовательного предъявления как минимум двух независимых факторов (например, пароль и одноразовый код, пароль и аппаратный токен, пароль и биометрия);
+2. Интеграцию средств МФА со всеми информационными системами контура безопасности, к которым пользователи осуществляют логический доступ, включая удалённый доступ (VPN, терминальные сессии);
+3. Технический запрет входа в систему при успешном прохождении только одного из факторов;
+4. Регистрацию событий прохождения (и неуспешных попыток прохождения) многофакторной аутентификации.
+Класс используемых средств — средства многофакторной аутентификации (МФА).
+Иностранные: RSA SecurID, Duo Security и пр.
+Российские сертифицированные (ФСТЭК): «Мультифактор», JaCarta (программные компоненты), Рутокен (в связке с ПО аутентификации) и др.
+Открытый код: privacyIDEA и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F38" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами систем аутентификации;
+2. Скриншоты настроек систем МФА, подтверждающие требование не менее двух факторов для входа пользователей;
+3. Результаты тестирования (попытка входа с предъявлением только одного фактора), подтверждающие блокирование такого входа;
+4. Журналы событий, подтверждающие успешные и неуспешные попытки многофакторной аутентификации пользователей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G38" s="151" t="inlineStr">
+        <is>
+          <t>1. МФА подключена не ко всем информационным системам, к которым пользователи осуществляют логический доступ (например, отсутствует для удалённого доступа);
+2. Отдельные категории пользователей исключены из периметра действия МФА без документированного обоснования;
+3. В качестве второго фактора используется метод, не являющийся независимым от первого (например, код приходит на то же устройство, с которого вводится пароль, без дополнительной защиты канала);
+4. Технически возможен обход МФА через альтернативные точки входа (legacy-интерфейсы, API), не охваченные требованием.</t>
+        </is>
+      </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -3819,10 +3919,60 @@
           <t>Т-Н-Н</t>
         </is>
       </c>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="31" t="n"/>
-      <c r="G39" s="31" t="n"/>
+      <c r="D39" s="144" t="inlineStr">
+        <is>
+          <t>Мера — зеркальное отражение РД.1, но применительно к эксплуатационному персоналу: перед предоставлением логического доступа представитель эксплуатационного персонала (администратор) должен пройти идентификацию и однофакторную аутентификацию.
+Главная цель меры — обеспечить минимально необходимый уровень контроля доступа для технического персонала на тех уровнях защиты, где многофакторная аутентификация для этой категории субъектов (мера РД.4) ещё не требуется, не допуская анонимного администрирования систем.</t>
+        </is>
+      </c>
+      <c r="E39" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера подразумевает исключительно технические меры защиты, а именно:
+1. Настройку операционных систем, СУБД, средств виртуализации, сетевого оборудования и средств защиты информации таким образом, чтобы административный доступ был невозможен без предъявления уникального идентификатора и прохождения проверки подлинности;
+2. Использование персональных привилегированных учётных записей для каждого представителя эксплуатационного персонала (без общих административных учётных записей — см. также меру РД.10);
+3. Технический запрет анонимного или неаутентифицированного административного доступа ко всем управляемым компонентам инфраструктуры.
+Класс используемых средств — операционные системы, средства виртуализации и сетевое оборудование со встроенными механизмами идентификации и аутентификации, системы управления привилегированным доступом (PAM).
+Иностранные: Microsoft Active Directory, CyberArk PAM и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Indeed Privileged Access Manager и др.
+Открытый код: FreeIPA, Teleport и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F39" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем и подразделением информационной безопасности;
+2. Скриншоты настроек, подтверждающие обязательность идентификации и аутентификации при административном доступе;
+3. Выгрузка перечня учётных записей эксплуатационного персонала, подтверждающая их персональный (не групповой) характер;
+4. Журналы событий, подтверждающие регистрацию фактов идентификации и аутентификации эксплуатационного персонала.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G39" s="151" t="inlineStr">
+        <is>
+          <t>1. Часть оборудования (сетевые устройства, гипервизоры, встроенные консоли управления) администрируется без персональной идентификации, через общую учётную запись производителя по умолчанию;
+2. Для отдельных унаследованных систем аутентификация технически не реализована и компенсируется только организационными мерами;
+3. Журналы идентификации и аутентификации эксплуатационного персонала не собираются централизованно;
+4. Отсутствует контроль за тем, что все административные интерфейсы (включая консольный и физический доступ) охвачены требованием аутентификации.</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -3845,10 +3995,61 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="31" t="n"/>
-      <c r="F40" s="31" t="n"/>
-      <c r="G40" s="31" t="n"/>
+      <c r="D40" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична РД.2, но распространяется на эксплуатационный персонал: администраторы и иные представители эксплуатационного персонала обязаны проходить многофакторную аутентификацию для получения логического доступа к управляемым ими системам.
+Главная цель меры — усилить защиту административного доступа, поскольку компрометация учётных данных эксплуатационного персонала (обладающего расширенными, зачастую критичными правами) несёт существенно больший риск, чем компрометация учётной записи рядового пользователя, а однофакторной аутентификации для этой категории субъектов недостаточно.</t>
+        </is>
+      </c>
+      <c r="E40" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Внедрение и настройку средств многофакторной аутентификации для всех административных интерфейсов доступа (консоли управления, средства удалённого администрирования, системы виртуализации, PAM-системы);
+2. Обязательное прохождение МФА для доступа к средствам и системам защиты информации, сетевому оборудованию, СУБД и иным критичным компонентам инфраструктуры;
+3. Технический запрет административного доступа при прохождении только одного фактора аутентификации;
+4. Регистрацию событий успешного и неуспешного прохождения многофакторной аутентификации эксплуатационным персоналом.
+Класс используемых средств — средства многофакторной аутентификации (МФА), системы контроля действий привилегированных пользователей (PAM).
+Иностранные: RSA SecurID, CyberArk PAM (со встроенной МФА) и пр.
+Российские сертифицированные (ФСТЭК): «Мультифактор», Indeed Privileged Access Manager и др.
+Открытый код: privacyIDEA, Teleport и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F40" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами систем аутентификации и представителями эксплуатационного персонала;
+2. Скриншоты настроек, подтверждающие требование МФА для всех административных интерфейсов;
+3. Результаты тестирования (попытка административного входа с предъявлением только одного фактора), подтверждающие блокирование такого входа;
+4. Журналы событий, подтверждающие успешные и неуспешные попытки многофакторной аутентификации эксплуатационного персонала.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G40" s="151" t="inlineStr">
+        <is>
+          <t>1. МФА для эксплуатационного персонала подключена не ко всем административным интерфейсам (например, отсутствует для консольного или физического доступа к оборудованию);
+2. Встроенные (сервисные) учётные записи производителей оборудования не охвачены требованием МФА;
+3. Резервные («аварийные») способы административного доступа позволяют обойти требование многофакторной аутентификации;
+4. Журналы прохождения МФА эксплуатационным персоналом не анализируются на предмет аномалий (например, множественных неуспешных попыток).</t>
+        </is>
+      </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -3871,10 +4072,66 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="31" t="n"/>
-      <c r="F41" s="31" t="n"/>
-      <c r="G41" s="31" t="n"/>
+      <c r="D41" s="144" t="inlineStr">
+        <is>
+          <t>Речь идёт об обязательной аутентификации программных сервисов (служб, приложений, скриптов автоматизации), которые осуществляют логический доступ к информационным ресурсам от имени технических (сервисных) учётных записей, а не от имени конкретного физического пользователя.
+Главная цель меры — исключить возможность взаимодействия с информационными ресурсами со стороны неаутентифицированных или подменённых программных компонентов, поскольку технические учётные записи зачастую обладают широкими правами доступа и представляют собой привлекательную цель для компрометации, если аутентификация не контролируется так же строго, как для обычных пользователей.</t>
+        </is>
+      </c>
+      <c r="E41" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационный компонент в этой мере отсутствует, поэтому применяются технические средства:
+1. Настройка обязательной аутентификации технических учётных записей при каждом обращении программного сервиса к информационному ресурсу (по паролю, сертификату, ключу API или иному аутентификационному признаку);
+2. Использование строгих методов аутентификации сервисов — сертификатов (PKI), ключей доступа с ограниченным сроком действия, токенов OAuth и аналогичных механизмов, минимизирующих риск компрометации;
+3. Технический запрет обращения к ресурсам доступа от имени технической учётной записи без предъявления соответствующих аутентификационных данных;
+4. Регистрация событий аутентификации технических учётных записей, включая неуспешные попытки.
+Класс используемых средств — средства управления секретами и сертификатами (Secrets Management, PKI), встроенные механизмы аутентификации СУБД и промежуточного ПО.
+Иностранные: HashiCorp Vault, Microsoft Active Directory Certificate Services и пр.
+Российские сертифицированные (ФСТЭК): ViPNet PKI, «КриптоПро PKI» (программные компоненты) и др.
+Открытый код: HashiCorp Vault (Community Edition), EJBCA и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F41" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с разработчиками и администраторами интеграционных сервисов;
+2. Скриншоты (конфигурации) настроек аутентификации технических учётных записей в подключаемых сервисах;
+3. Результаты тестирования (попытка обращения к ресурсу от имени технической учётной записи без аутентификационных данных), подтверждающие блокирование такого обращения;
+4. Журналы событий, подтверждающие регистрацию аутентификации программных сервисов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G41" s="151" t="inlineStr">
+        <is>
+          <t>1. Часть программных сервисов обращается к ресурсам доступа с использованием технических учётных записей без аутентификации (например, по доверенному сетевому адресу без проверки подлинности);
+2. Аутентификационные данные технических учётных записей (пароли, ключи) хранятся в открытом виде в конфигурационных файлах или коде интеграции;
+3. Сроки действия сертификатов или ключей технических учётных записей не контролируются и не обновляются регулярно;
+4. Инвентаризация технических учётных записей и используемых ими методов аутентификации не ведётся, часть таких записей может быть не выявлена.</t>
+        </is>
+      </c>
+      <c r="H41" s="156" t="inlineStr">
+        <is>
+          <t>Средства криптографической защиты информации и компоненты PKI в Российской Федерации сертифицируются преимущественно ФСБ России, а не ФСТЭК России. При подборе конкретного продукта для реализации меры необходимо сверяться также с реестром сертифицированных ФСБ России СКЗИ, а не только с реестром ФСТЭК.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="28.5" customHeight="1">
       <c r="A42" s="20" t="inlineStr">
@@ -3892,10 +4149,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="31" t="n"/>
-      <c r="F42" s="31" t="n"/>
-      <c r="G42" s="31" t="n"/>
+      <c r="D42" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует аутентификации не только субъекта (представителя эксплуатационного персонала), но и самого автоматизированного рабочего места (АРМ), с которого осуществляется логический доступ, — то есть подтверждения того, что доступ выполняется именно с доверенного, легитимного устройства.
+Главная цель меры — исключить возможность администрирования информационной инфраструктуры с посторонних, неучтённых или скомпрометированных устройств, даже если аутентификационные данные самого сотрудника были предъявлены корректно: без аутентификации устройства кража или подбор пароля администратора позволили бы выполнить вход с любого компьютера.</t>
+        </is>
+      </c>
+      <c r="E42" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как организационных мер здесь не предусмотрено, всё сводится к техническим настройкам:
+1. Использование сертификатов устройств (машинных сертификатов, выпущенных внутренним удостоверяющим центром) или иных технических признаков (например, привязки по MAC-адресу совместно с сертификатом, доменного членства АРМ), подтверждающих легитимность АРМ эксплуатационного персонала;
+2. Настройка средств сетевого доступа (VPN-шлюзов, систем контроля доступа к сети — NAC) таким образом, чтобы административный доступ предоставлялся только с АРМ, прошедших аутентификацию устройства;
+3. Технический запрет административного доступа с устройств, не прошедших аутентификацию (в том числе с личных и неучтённых устройств).
+Класс используемых средств — средства контроля доступа к сети (NAC), инфраструктура открытых ключей (PKI) для аутентификации устройств, VPN-шлюзы с проверкой сертификата устройства.
+Иностранные: Cisco ISE, Palo Alto GlobalProtect и пр.
+Российские сертифицированные (ФСТЭК): «С-Терра Шлюз», ViPNet Coordinator и др.
+Открытый код: FreeRADIUS (совместно с PKI) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F42" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Скриншоты настроек NAC/VPN, подтверждающие проверку сертификата (иного признака) АРМ перед предоставлением административного доступа;
+3. Результаты тестирования (попытка административного подключения с непривязанного устройства), подтверждающие блокирование такого подключения;
+4. Журналы событий аутентификации устройств.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G42" s="151" t="inlineStr">
+        <is>
+          <t>1. Аутентификация АРМ эксплуатационного персонала не охватывает все каналы административного доступа (например, отсутствует для локального/консольного подключения);
+2. Сертификаты устройств выпускаются без строгой проверки принадлежности АРМ конкретному сотруднику или подразделению;
+3. Просроченные или отозванные сертификаты устройств не блокируются автоматически;
+4. Допускается административный доступ с личных устройств при условии установки VPN-клиента, без полноценной проверки соответствия корпоративным требованиям (compliance-проверки).</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="28.5" customHeight="1">
       <c r="A43" s="20" t="inlineStr">
@@ -3913,10 +4220,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="31" t="n"/>
-      <c r="F43" s="31" t="n"/>
-      <c r="G43" s="31" t="n"/>
+      <c r="D43" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична РД.6, но распространяется на рабочие места рядовых пользователей: логический доступ должен предоставляться только с АРМ, прошедшего аутентификацию как доверенное устройство, а не с произвольного компьютера.
+Главная цель меры — снизить риск доступа к информационным ресурсам с непроверенных, личных или скомпрометированных устройств, даже при наличии у пользователя корректных аутентификационных данных.</t>
+        </is>
+      </c>
+      <c r="E43" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Здесь требуются только технические решения:
+1. Использование сертификатов устройств или доменного членства АРМ пользователей как условия для предоставления логического доступа к информационным ресурсам;
+2. Настройка средств контроля доступа к сети (NAC) или VPN-шлюзов таким образом, чтобы доступ предоставлялся только с АРМ, прошедших проверку принадлежности к корпоративному парку устройств;
+3. Технический запрет доступа с личных, неучтённых или не прошедших проверку устройств.
+Класс используемых средств — средства контроля доступа к сети (NAC), инфраструктура открытых ключей (PKI) для аутентификации устройств, службы каталогов с привязкой устройств к домену.
+Иностранные: Microsoft Active Directory (доменное членство), Cisco ISE и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, ViPNet Coordinator и др.
+Открытый код: FreeRADIUS, FreeIPA и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F43" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и рабочих мест;
+2. Скриншоты настроек, подтверждающие проверку принадлежности АРМ пользователя к корпоративному парку устройств перед предоставлением доступа;
+3. Результаты тестирования (попытка входа с непривязанного устройства), подтверждающие блокирование доступа;
+4. Журналы событий аутентификации АРМ пользователей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G43" s="151" t="inlineStr">
+        <is>
+          <t>1. Аутентификация АРМ пользователей реализована не для всех способов подключения (например, отсутствует для доступа через мобильные приложения или веб-интерфейс);
+2. Часть пользователей работает с личных устройств (BYOD) без применения к ним требований аутентификации устройства;
+3. Учёт (инвентаризация) АРМ пользователей неполон, часть устройств не привязана к домену или системе NAC;
+4. Компрометация сертификата устройства не приводит к его оперативному отзыву.</t>
+        </is>
+      </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -3939,10 +4296,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="31" t="n"/>
-      <c r="F44" s="31" t="n"/>
-      <c r="G44" s="31" t="n"/>
+      <c r="D44" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает техническое требование: при вводе пароля (и иных аутентификационных данных) символы не должны отображаться на экране в открытом виде — вместо них показываются символы-заменители (точки, звёздочки) либо поле ввода вовсе не отображает введённые символы.
+Главная цель меры — исключить возможность визуального подглядывания пароля (так называемый shoulder surfing) посторонними лицами, находящимися рядом с субъектом доступа в момент ввода аутентификационных данных.</t>
+        </is>
+      </c>
+      <c r="E44" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера не имеет организационной составляющей — её выполнение обеспечивается техническими средствами:
+1. Использование штатных элементов интерфейса операционных систем, прикладного программного обеспечения (ПО) и веб-приложений, которые маскируют вводимые символы пароля (отображают точки, звёздочки или пустое поле вместо самих символов);
+2. Контроль того, что это требование распространяется на все точки ввода аутентификационных данных — локальный вход в систему, удалённый доступ, веб-интерфейсы, мобильные приложения, консоли администрирования;
+3. Технический запрет на использование или кастомизацию форм ввода, в которых пароль отображается в открытом (незамаскированном) виде.
+Поскольку сокрытие вводимых символов пароля — базовая функция подавляющего большинства современных операционных систем, СУБД, веб-фреймворков и прикладного ПО, отдельного специализированного средства защиты для реализации меры, как правило, не требуется: задача сводится к контролю того, что данная штатная функция не отключена и не обойдена в кастомных интерфейсах.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F44" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем и разработчиками внутренних приложений;
+2. Скриншоты экранов ввода пароля в различных информационных системах и интерфейсах, подтверждающие маскирование вводимых символов;
+3. Результаты выборочной проверки нестандартных (самописных) интерфейсов входа на предмет корректного сокрытия пароля при вводе.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G44" s="151" t="inlineStr">
+        <is>
+          <t>1. В отдельных самописных или устаревших приложениях пароль при вводе отображается в открытом виде;
+2. Требование не распространяется на консоли администрирования специализированного оборудования (например, интерфейсы управления через последовательный порт);
+3. Мобильные приложения временно отображают последний введённый символ пароля дольше, чем это оправдано с точки зрения безопасности, без возможности отключения такого поведения;
+4. Проверка соблюдения требования на нестандартных интерфейсах не проводится.</t>
+        </is>
+      </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -3965,10 +4368,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="31" t="n"/>
-      <c r="F45" s="31" t="n"/>
-      <c r="G45" s="31" t="n"/>
+      <c r="D45" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает эксплуатацию учётных записей, для которых аутентификационные данные (пароли) либо вовсе не заданы, либо оставлены такими, какими их установил производитель (разработчик) ресурса доступа или автоматизированной системы (АС) «по умолчанию» — то есть широко известными или предсказуемыми значениями (admin/admin, admin/password и подобными).
+Главная цель меры — устранить один из самых распространённых и легко эксплуатируемых векторов атаки: учётные данные «по умолчанию» известны из документации производителя, находятся в открытом доступе и, как правило, являются первым, что пробует злоумышленник или автоматизированный сканер уязвимостей.</t>
+        </is>
+      </c>
+      <c r="E45" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная составляющая сводится к следующим шагам:
+1. Включить в регламент ввода в эксплуатацию информационных систем и оборудования обязательный этап смены (или первичного задания) аутентификационных данных, отличных от заводских (заданных по умолчанию), до подключения ресурса к рабочей среде;
+2. Закрепить ответственность за выполнение данного этапа за конкретным подразделением (администраторами, инженерами по внедрению);
+3. Проводить периодические проверки (инвентаризацию) эксплуатируемых ресурсов доступа и АС на предмет использования заводских или незаданных аутентификационных данных;
+4. Фиксировать факт смены аутентификационных данных по умолчанию в акте ввода в эксплуатацию или ином документе.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F45" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент ввода в эксплуатацию, содержащий обязательный этап смены аутентификационных данных по умолчанию;
+2. Акты ввода в эксплуатацию информационных систем и оборудования с отметкой о выполнении данного этапа;
+3. Акты (отчёты) периодических проверок на предмет использования заводских или незаданных аутентификационных данных.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G45" s="151" t="inlineStr">
+        <is>
+          <t>1. Регламент ввода в эксплуатацию не содержит явного требования о смене аутентификационных данных по умолчанию;
+2. Проверки на предмет использования заводских учётных данных охватывают не все классы оборудования и ПО (например, забывают про сетевое оборудование, IoT-устройства, встраиваемые системы);
+3. Тестовые или демонстрационные учётные записи, поставляемые с ресурсом «по умолчанию», не отключаются и не удаляются при вводе в эксплуатацию;
+4. Периодическая проверка отсутствия заводских учётных данных не проводится, факт их использования выявляется только по результатам инцидента или внешнего аудита.</t>
+        </is>
+      </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -3991,10 +4440,55 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="31" t="n"/>
-      <c r="F46" s="31" t="n"/>
-      <c r="G46" s="31" t="n"/>
+      <c r="D46" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает использование групповых (используемых несколькими субъектами одновременно), общих и стандартных учётных записей и паролей, а также любых иных методов идентификации и аутентификации, которые не позволяют однозначно определить, какой именно конкретный субъект осуществил логический доступ.
+Главная цель меры — обеспечить персональную идентифицируемость каждого субъекта доступа на уровне самого процесса аутентификации: мера дополняет требование УЗП.1 (уникальные персонифицированные учётные записи), явно запрещая типичные обходные пути — совместное использование одной учётной записи несколькими людьми, стандартные («сервисные») учётные записи для интерактивного входа и подобные практики.</t>
+        </is>
+      </c>
+      <c r="E46" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит организационный характер и включает:
+1. Закрепление во внутреннем нормативном документе прямого запрета на создание и использование групповых, общих и стандартных учётных записей и паролей для интерактивного логического доступа субъектов;
+2. Проведение периодической инвентаризации учётных записей на предмет выявления групповых, общих или стандартных учётных записей, используемых в нарушение установленного запрета;
+3. При выявлении нарушений — инициирование их устранения (замены на персональные учётные записи) и, при необходимости, служебного разбирательства.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F46" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, содержащий запрет на использование групповых, общих и стандартных учётных записей и паролей;
+2. Акты (отчёты) инвентаризации учётных записей на предмет выявления нарушений установленного запрета;
+3. Свидетельства устранения выявленных нарушений (замены групповых учётных записей на персональные).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G46" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельные технологические процессы (например, эксплуатация унаследованных систем) продолжают использовать групповые учётные записи в нарушение запрета, без документированного компенсирующего решения;
+2. Инвентаризация учётных записей на предмет выявления групповых и общих учётных записей не проводится или проводится формально;
+3. Запрет закреплён документально, но не доводится до сведения сотрудников, ответственных за создание учётных записей;
+4. Выявленные нарушения не устраняются в разумный срок.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42.75" customHeight="1">
       <c r="A47" s="20" t="inlineStr">
@@ -4012,10 +4506,61 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="31" t="n"/>
-      <c r="F47" s="31" t="n"/>
-      <c r="G47" s="31" t="n"/>
+      <c r="D47" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает техническое требование к автоматической временной блокировке учётной записи пользователя после определённого числа последовательных неуспешных попыток аутентификации, причём период такой блокировки должен составлять не менее 30 минут.
+Главная цель меры — противодействовать атакам подбора пароля (brute-force, перебор по словарю): ограничение числа попыток и введение задержки перед следующей возможной попыткой делает подбор пароля вычислительно нецелесообразным для злоумышленника, при этом сохраняя для легитимного пользователя возможность восстановить доступ по истечении установленного времени.</t>
+        </is>
+      </c>
+      <c r="E47" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация меры лежит полностью в технической плоскости и включает:
+1. Настройку политики блокировки учётных записей в операционной системе, каталоге (Active Directory, LDAP) или ином средстве аутентификации: задание порогового числа неуспешных последовательных попыток аутентификации, после которого учётная запись автоматически блокируется;
+2. Установку длительности временной блокировки не менее 30 минут (либо снятие блокировки только по обращению к администратору — при более строгих требованиях к безопасности);
+3. Применение данной политики единообразно ко всем информационным системам, где осуществляется аутентификация пользователей, включая веб-интерфейсы и удалённый доступ;
+4. Регистрацию событий блокировки учётной записи в журнале для последующего анализа (в том числе на предмет выявления попыток подбора пароля).
+Класс используемых средств — службы каталогов и системы управления учётными записями (IdM) со встроенной политикой блокировки, средства защиты от несанкционированного доступа (СЗИ от НСД).
+Иностранные: Microsoft Active Directory (Account Lockout Policy) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К и др.
+Открытый код: FreeIPA и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F47" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты настроек политики блокировки учётных записей (пороговое число попыток, длительность блокировки);
+3. Результаты тестирования (несколько последовательных неуспешных попыток входа), подтверждающие фактическую блокировку учётной записи на период не менее 30 минут;
+4. Журналы событий, подтверждающие регистрацию фактов блокировки учётных записей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G47" s="151" t="inlineStr">
+        <is>
+          <t>1. Пороговое число неуспешных попыток аутентификации либо длительность блокировки не настроены или не соответствуют установленным требованиям (блокировка короче 30 минут);
+2. Политика блокировки применена не ко всем информационным системам (например, отсутствует для веб-интерфейсов или устаревших приложений);
+3. Механизм блокировки технически реализован, но фактическое тестирование его срабатывания не проводится;
+4. События блокировки учётных записей не анализируются на предмет выявления целенаправленных попыток подбора паролей.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="57" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
@@ -4033,10 +4578,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="31" t="n"/>
-      <c r="F48" s="31" t="n"/>
-      <c r="G48" s="31" t="n"/>
+      <c r="D48" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает одновременное открытие нескольких параллельных сессий логического доступа под одной и той же учётной записью с разных автоматизированных рабочих мест (АРМ), включая виртуальные машины.
+Главная цель меры — исключить ситуацию, при которой скомпрометированная учётная запись используется злоумышленником параллельно с легитимным пользователем (что затрудняет своевременное обнаружение компрометации), а также предотвратить намеренное совместное использование одной учётной записи несколькими сотрудниками одновременно.</t>
+        </is>
+      </c>
+      <c r="E48" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими средствами, необходимо:
+1. Настройку информационных систем и служб каталогов таким образом, чтобы при попытке открытия новой сессии под учётной записью, уже имеющей активную сессию с другого АРМ, происходил отказ в доступе либо принудительное завершение предыдущей сессии;
+2. Централизованный контроль активных сессий (Single Session Enforcement) через систему управления доступом или средства терминального доступа;
+3. Регистрацию попыток открытия параллельных сессий под одной учётной записью для последующего анализа на предмет возможной компрометации.
+Класс используемых средств — средства терминального доступа и виртуализации рабочих столов (VDI), системы контроля сессий, службы каталогов с политикой ограничения одновременных сеансов.
+Иностранные: Citrix Virtual Apps and Desktops, Microsoft Remote Desktop Services (ограничение сессий) и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», Astra Linux (совместно со средствами разграничения сессий) и др.
+Открытый код: FreeRDP (с ограничениями на стороне сервера) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F48" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты настроек, ограничивающих количество одновременных сессий под одной учётной записью;
+3. Результаты тестирования (попытка одновременного входа под одной учётной записью с двух разных АРМ), подтверждающие срабатывание запрета;
+4. Журналы событий, подтверждающие регистрацию попыток открытия параллельных сессий.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G48" s="151" t="inlineStr">
+        <is>
+          <t>1. Ограничение параллельных сессий настроено не для всех информационных систем (например, отсутствует для веб-приложений или мобильного доступа);
+2. Технические учётные записи и учётные записи для автоматизированных процессов исключены из-под действия запрета без документированного обоснования;
+3. При обнаружении попытки открытия параллельной сессии система не уведомляет администратора безопасности;
+4. Виртуальные АРМ (в инфраструктуре VDI) не учитываются при определении количества активных сессий наравне с физическими.</t>
+        </is>
+      </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4065,9 +4660,50 @@
 Главная цель меры — защита информации от несанкционированного доступа в ситуациях, когда сотрудник временно покидает рабочее место, но не хочет или не может завершить все текущие операции. Возможность быстро заблокировать экран или завершить сессию позволяет предотвратить доступ посторонних лиц к конфиденциальной информации.</t>
         </is>
       </c>
-      <c r="E49" s="31" t="n"/>
-      <c r="F49" s="31" t="n"/>
-      <c r="G49" s="31" t="n"/>
+      <c r="E49" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технический характер меры предполагает следующий набор действий:
+1. Настройку операционных систем и прикладного ПО таким образом, чтобы субъект логического доступа мог самостоятельно инициировать блокировку экрана (приостановку сессии) сочетанием клавиш или соответствующим элементом интерфейса;
+2. Настройку возможности принудительного завершения сессии логического доступа (выхода из системы) по инициативе пользователя, с корректным закрытием всех активных приложений и соединений;
+3. Обеспечение того, что при блокировке экрана прекращается отображение любой информации, полученной в рамках сессии, до момента повторной аутентификации (см. меру РД.15).
+Отдельное специализированное средство защиты для реализации этой меры, как правило, не требуется — функция блокировки экрана и завершения сессии входит в базовую поставку современных операционных систем и прикладного ПО.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F49" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с пользователями и администраторами АРМ;
+2. Результаты тестирования (инициирование блокировки экрана и завершения сессии пользователем), подтверждающие корректную работу функции;
+3. Скриншоты настроек операционной системы (прикладного ПО), подтверждающие доступность данной функции пользователю.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G49" s="151" t="inlineStr">
+        <is>
+          <t>1. Функция принудительной блокировки экрана недоступна пользователю на части АРМ (например, отключена локальными настройками);
+2. При блокировке экрана часть информации (уведомления, превью писем) продолжает отображаться поверх экрана блокировки;
+3. Пользователи не осведомлены о наличии и способе использования данной функции, что снижает практическую эффективность меры;
+4. Функция реализована не для всех типов АРМ (например, отсутствует в терминальных сессиях или на тонких клиентах).</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="199.5" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
@@ -4091,9 +4727,55 @@
 Главная цель меры — исключить возможность несанкционированного доступа к информационным ресурсам в случае, когда пользователь оставил рабочее место без присмотра, забыв заблокировать экран. Автоматическая блокировка предотвращает доступ посторонних лиц к открытым сессиям и выполнение любых операций от имени авторизованного пользователя в его отсутствие.</t>
         </is>
       </c>
-      <c r="E50" s="31" t="n"/>
-      <c r="F50" s="31" t="n"/>
-      <c r="G50" s="31" t="n"/>
+      <c r="E50" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно техническими средствами:
+1. Настройку операционных систем и (или) средств защиты информации на автоматическое включение блокировки экрана (приостановку сессии) по истечении периода бездействия пользователя, не превышающего 15 минут;
+2. Обеспечение прекращения отображения информации, полученной в рамках сессии, сразу после срабатывания автоматической блокировки;
+3. Единообразное применение данной настройки ко всем АРМ пользователей и эксплуатационного персонала, включая терминальные и удалённые сессии;
+4. Технический запрет на изменение пользователем установленного времени бездействия в сторону увеличения (см. также меру УЗП.11).
+Класс используемых средств — операционные системы с политиками блокировки экрана (screen lock), средства централизованного управления конфигурациями (групповые политики).
+Иностранные: Microsoft Group Policy (Interactive logon: Machine inactivity limit) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К и др.
+Открытый код: настройки экранной заставки (блокировки) дистрибутивов Linux (gsettings, loginctl) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F50" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами АРМ;
+2. Скриншоты (выгрузки) групповых политик или иных настроек, подтверждающие установленное время бездействия не более 15 минут;
+3. Результаты тестирования (оставление сессии без активности) на выборке АРМ, подтверждающие фактическое срабатывание автоматической блокировки в установленное время;
+4. Результаты выборочной проверки, подтверждающие, что пользователи технически не могут увеличить установленное время бездействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G50" s="151" t="inlineStr">
+        <is>
+          <t>1. Время автоматической блокировки экрана превышает установленные 15 минут на части АРМ;
+2. Настройка применена не ко всем категориям устройств (например, отсутствует для терминальных серверов, серверов приложений с интерактивным входом);
+3. Пользователи технически имеют возможность изменить (увеличить или отключить) установленное время бездействия;
+4. Фактическое тестирование срабатывания автоматической блокировки не проводится, контроль ограничивается проверкой конфигурации.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="228" customHeight="1">
       <c r="A51" s="20" t="inlineStr">
@@ -4117,9 +4799,48 @@
 Главная цель меры — исключить возможность несанкционированного доступа к информационным ресурсам в ситуациях, когда сессия была прервана (автоматически или по инициативе пользователя), но рабочая станция осталась физически доступной для посторонних лиц. Повторная аутентификация гарантирует, что продолжить работу сможет только тот пользователь, который знает (или имеет) соответствующие аутентификационные данные.</t>
         </is>
       </c>
-      <c r="E51" s="31" t="n"/>
-      <c r="F51" s="31" t="n"/>
-      <c r="G51" s="31" t="n"/>
+      <c r="E51" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера выполняется силами технических средств защиты информации, а именно:
+1. Настройку операционных систем и прикладного ПО таким образом, чтобы после принудительного (мера РД.13) или автоматического (мера РД.14) прерывания сессии продолжение работы было технически невозможно без повторного прохождения процедуры аутентификации;
+2. Обеспечение того, что повторная аутентификация выполняется с той же строгостью, что и первичная (в том числе с соблюдением требования многофакторности, если оно применимо к соответствующей категории субъектов);
+3. Технический запрет на автоматическое (без участия пользователя) возобновление сессии в обход процедуры аутентификации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F51" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами АРМ и информационных систем;
+2. Результаты тестирования (попытка продолжить работу после блокировки экрана без ввода аутентификационных данных), подтверждающие невозможность такого продолжения;
+3. Скриншоты настроек, подтверждающие обязательность повторной аутентификации после прерывания сессии.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G51" s="151" t="inlineStr">
+        <is>
+          <t>1. На части АРМ возможно продолжение работы после блокировки экрана без повторной аутентификации (например, из-за настроек энергосбережения, отключающих экран без блокировки сессии);
+2. Повторная аутентификация после прерывания сессии не требует того же уровня строгости, что и первичная (например, не запрашивается второй фактор МФА);
+3. Тестирование фактической невозможности обхода повторной аутентификации не проводится.</t>
+        </is>
+      </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4142,17 +4863,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D52" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Суть меры заключается в использовании на автоматизированных рабочих местах (АРМ) субъектов логического доступа встроенных механизмов контроля изменения базовой конфигурации оборудования. Таким механизмом является пароль на изменение параметров конфигурации системы, хранящихся в энергонезависимой памяти.
+      <c r="D52" s="153" t="inlineStr">
+        <is>
+          <t>Суть меры заключается в использовании на автоматизированных рабочих местах (АРМ) субъектов логического доступа встроенных механизмов контроля изменения базовой конфигурации оборудования. Таким механизмом является пароль на изменение параметров конфигурации системы, хранящихся в энергонезависимой памяти.
 Под «базовой конфигурацией оборудования» понимаются настройки, хранящиеся в энергонезависимой памяти (например, BIOS/UEFI), которые определяют параметры загрузки системы, порядок загрузки устройств, включение/отключение интерфейсов и портов, настройки безопасности процессора и другие низкоуровневые параметры оборудования.
-Главная цель меры — защитить базовые настройки оборудования от несанкционированного изменения со стороны пользователей или злоумышленников. .
-</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="n"/>
-      <c r="F52" s="31" t="n"/>
-      <c r="G52" s="31" t="n"/>
+Главная цель меры — защитить базовые настройки оборудования от несанкционированного изменения со стороны пользователей или злоумышленников.</t>
+        </is>
+      </c>
+      <c r="E52" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационные меры для данного требования не предусмотрены — реализация строится на технических решениях:
+1. Использование встроенных в BIOS/UEFI механизмов защиты паролем изменения параметров базовой конфигурации оборудования (порядка загрузки устройств, включения/отключения портов и интерфейсов, параметров безопасности процессора);
+2. Установку уникальных паролей BIOS/UEFI на каждом АРМ силами эксплуатационного персонала при вводе оборудования в эксплуатацию;
+3. Технический запрет на сброс пароля BIOS/UEFI пользователем без физического вмешательства эксплуатационного персонала (например, без вскрытия корпуса и работы с перемычками на материнской плате);
+4. Периодическую проверку того, что защита BIOS/UEFI паролем не отключена и не обойдена.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F52" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами АРМ и эксплуатационным персоналом, отвечающим за настройку оборудования;
+2. Результаты выборочной проверки настроек BIOS/UEFI на предмет наличия установленного пароля на изменение конфигурации;
+3. Акты ввода в эксплуатацию АРМ с отметкой о выполнении настройки защиты BIOS/UEFI паролем.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G52" s="151" t="inlineStr">
+        <is>
+          <t>1. Пароль BIOS/UEFI установлен не на всех АРМ, часть оборудования эксплуатируется с заводскими настройками;
+2. Используется единый (одинаковый) пароль BIOS/UEFI для всего парка оборудования, что снижает эффективность меры при компрометации одного устройства;
+3. Периодическая проверка наличия и действия пароля BIOS/UEFI не проводится;
+4. Пароль BIOS/UEFI известен широкому кругу лиц, включая пользователей АРМ, что обесценивает ограничение.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
@@ -4183,10 +4944,59 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="53" t="n"/>
-      <c r="F54" s="53" t="n"/>
-      <c r="G54" s="53" t="n"/>
+      <c r="D54" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает применение технологий аутентификации, при которых аутентификационные данные (пароли) сохраняются в средствах вычислительной техники (СВТ) — операционных системах, базах данных, конфигурационных файлах приложений — в открытом (незашифрованном, нехешированном) виде.
+Главная цель меры — исключить возможность непосредственного хищения паролей в случае получения злоумышленником доступа к файловой системе, базе данных или памяти СВТ: при правильном хранении (хеширование с солью либо шифрование) компрометация носителя данных сама по себе не раскрывает пароли субъектов доступа.</t>
+        </is>
+      </c>
+      <c r="E54" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввиду того, что мера реализуется только технически, необходимо:
+1. Использование операционных систем, СУБД и прикладного ПО, хранящих аутентификационные данные исключительно в виде криптографических хешей (с применением «соли» и стойких алгоритмов хеширования), либо в зашифрованном виде с использованием сертифицированных средств криптографической защиты информации (СКЗИ);
+2. Технический запрет на применение устаревших или заведомо небезопасных механизмов хранения паролей (обратимое шифрование слабыми алгоритмами, хранение в открытом виде в конфигурационных файлах, базах данных или реестре);
+3. Периодический технический контроль (сканирование конфигураций и хранилищ данных) на предмет выявления аутентификационных данных, сохранённых в открытом виде.
+Класс используемых средств — средства сканирования конфигураций и анализа уязвимостей, встроенные механизмы хранения учётных данных операционных систем и СУБД.
+Иностранные: Microsoft Active Directory (хранение хешей паролей), Tenable Nessus (для выявления небезопасного хранения) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol (сканер защищённости), Secret Net Studio и др.
+Открытый код: OpenLDAP (с современными схемами хеширования), OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F54" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем и разработчиками внутренних приложений;
+2. Результаты сканирования (анализа конфигураций) информационных систем на предмет выявления аутентификационных данных, хранящихся в открытом виде;
+3. Выгрузки настроек СУБД и прикладного ПО, подтверждающие применение хеширования (шифрования) для хранения аутентификационных данных.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G54" s="157" t="inlineStr">
+        <is>
+          <t>1. Отдельные (как правило, устаревшие или самописные) приложения хранят пароли в открытом виде в конфигурационных файлах или базе данных;
+2. Используются слабые или устаревшие алгоритмы хеширования, не обеспечивающие достаточной криптографической стойкости;
+3. Периодическое сканирование на предмет небезопасного хранения аутентификационных данных не проводится;
+4. Резервные копии баз данных и конфигурационных файлов, содержащие аутентификационные данные, не защищены так же строго, как основные системы хранения.</t>
+        </is>
+      </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4209,15 +5019,63 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D55" s="44" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в том, что чтобы при любой передаче по сети идентификаторов и паролей (аутентификационных данных) использовались только защищённые протоколы, исключающие возможность их перехвата в незашифрованном виде, что исключает компрометацию учётных данных при перехвате трафика или в результате ошибочной настройки приложений. 
-Главная цель меры — предотвратить перехват и компрометацию аутентификационных данных злоумышленниками при их передаче по сетям, а также исключить случаи, когда аутентификационные данные оказываются в системах, не имеющих отношения к аутентификации, и становятся доступными для несанкционированного ознакомления.</t>
-        </is>
-      </c>
-      <c r="E55" s="53" t="n"/>
-      <c r="F55" s="53" t="n"/>
-      <c r="G55" s="53" t="n"/>
+      <c r="D55" s="153" t="inlineStr">
+        <is>
+          <t>Мера объединяет два взаимосвязанных запрета:
+1. Запрет на передачу аутентификационных данных (паролей, идентификаторов) по каналам и линиям связи в открытом (незашифрованном) виде — для этого должны использоваться только защищённые протоколы;
+2. Запрет на передачу (направление, копирование) аутентификационных данных куда-либо, кроме непосредственно средств или систем аутентификации, — то есть исключение ситуаций, при которых пароли попадают в журналы приложений, системы мониторинга, аналитические системы или иные хранилища, не предназначенные для хранения аутентификационных данных.
+Главная цель меры — предотвратить перехват и компрометацию аутентификационных данных при их передаче по сети, а также исключить их «утечку» в системы, не имеющие отношения к процессу аутентификации и не обеспечивающие для этого надлежащей защиты.</t>
+        </is>
+      </c>
+      <c r="E55" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация меры лежит полностью в технической плоскости и включает:
+1. Использование защищённых (шифрованных) протоколов передачи данных (TLS/SSL, SSH и аналогичных) для всех каналов, по которым передаются аутентификационные данные, включая внутреннюю сетевую инфраструктуру;
+2. Технический запрет на применение протоколов, передающих аутентификационные данные в открытом виде (устаревшие версии Telnet, FTP, HTTP без TLS, ранние версии протоколов аутентификации);
+3. Настройку систем логирования и мониторинга таким образом, чтобы аутентификационные данные не попадали в журналы событий, системы аналитики и иные хранилища, не относящиеся непосредственно к средствам аутентификации (маскирование или исключение полей с паролями при логировании);
+4. Периодический технический контроль (анализ сетевого трафика, аудит конфигураций) на предмет использования незащищённых протоколов или утечки аутентификационных данных в посторонние системы.
+Класс используемых средств — средства криптографической защиты каналов связи (VPN, TLS-терминаторы), средства анализа сетевого трафика и выявления утечек данных (DLP).
+Иностранные: F5 BIG-IP (TLS-терминация), Wireshark (для контрольного анализа трафика) и пр.
+Российские сертифицированные (ФСТЭК): «С-Терра Шлюз», ViPNet Coordinator, InfoWatch Traffic Monitor и др.
+Открытый код: OpenSSL/OpenVPN, Wireshark и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F55" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и разработчиками внутренних приложений;
+2. Результаты анализа сетевого трафика (или конфигураций протоколов), подтверждающие отсутствие передачи аутентификационных данных в открытом виде;
+3. Выгрузки настроек систем логирования, подтверждающие маскирование или исключение аутентификационных данных из журналов событий;
+4. Результаты выборочной проверки (аудита) конфигураций информационных систем на предмет использования незащищённых протоколов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G55" s="157" t="inlineStr">
+        <is>
+          <t>1. Отдельные внутренние сервисы или устаревшее оборудование продолжают использовать незащищённые протоколы передачи данных (Telnet, HTTP без TLS);
+2. Пароли или их фрагменты попадают в журналы событий приложений или систем мониторинга без маскирования;
+3. Анализ сетевого трафика и конфигураций на предмет утечки аутентификационных данных не проводится на регулярной основе;
+4. Аутентификационные данные передаются по электронной почте или в мессенджерах при первичной выдаче пользователю без последующей обязательной смены.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="99.75" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
@@ -4241,9 +5099,55 @@
 Главная цель меры — снизить риски компрометации паролей за счёт ограничения времени их использования.</t>
         </is>
       </c>
-      <c r="E56" s="31" t="n"/>
-      <c r="F56" s="31" t="n"/>
-      <c r="G56" s="31" t="n"/>
+      <c r="E56" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера подразумевает исключительно технические меры защиты, а именно:
+1. Настройку в операционных системах, каталогах (Active Directory, LDAP) и прикладных информационных системах политики максимального срока действия пароля пользователя, не превышающего 365 дней;
+2. Автоматическое информирование пользователя (уведомление) о приближающемся истечении срока действия пароля;
+3. Технический запрет на продолжение работы под учётной записью с истёкшим сроком действия пароля без его обязательной смены;
+4. Технический запрет на установку пользователем нового пароля, совпадающего с одним из ранее использовавшихся (история паролей).
+Класс используемых средств — службы каталогов и системы управления учётными записями (IdM) со встроенной политикой паролей.
+Иностранные: Microsoft Active Directory (Password Policy) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Avanpost IDM и др.
+Открытый код: FreeIPA, OpenLDAP (совместно с модулями контроля срока действия пароля) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F56" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты (выгрузки) настроек политики паролей, подтверждающие максимальный срок действия пароля не более 365 дней;
+3. Выгрузка отчёта о датах последней смены паролей пользователей, подтверждающая соблюдение установленной периодичности;
+4. Результаты тестирования (попытка входа под учётной записью с истёкшим сроком действия пароля без его смены), подтверждающие срабатывание требования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G56" s="151" t="inlineStr">
+        <is>
+          <t>1. Политика максимального срока действия пароля настроена не для всех информационных систем, к которым пользователи осуществляют логический доступ;
+2. Отдельные учётные записи (например, технические или редко используемые) исключены из-под действия политики без документированного обоснования;
+3. Пользователи обходят требование, меняя пароль формально (на очень похожий) при отсутствии контроля истории паролей;
+4. Отчётность о соблюдении срока действия паролей не формируется, нарушения выявляются только по факту инцидента.</t>
+        </is>
+      </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4272,9 +5176,55 @@
 Главная цель меры — снизить риски компрометации паролей эксплуатационного персонала за счёт более частой (по сравнению с рядовыми пользователями) смены паролей. Эксплуатационный персонал обладает привилегированными правами доступа, и компрометация их учётных данных может привести к наиболее серьёзным последствиям для организации.</t>
         </is>
       </c>
-      <c r="E57" s="31" t="n"/>
-      <c r="F57" s="31" t="n"/>
-      <c r="G57" s="31" t="n"/>
+      <c r="E57" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как речь идёт о чисто технической мере, реализация включает:
+1. Настройку в системах управления привилегированным доступом, службах каталогов и на управляемом оборудовании политики максимального срока действия пароля эксплуатационного персонала, не превышающего 90 дней;
+2. Применение более строгого контроля соблюдения данной политики по сравнению с учётными записями рядовых пользователей — с учётом повышенной критичности привилегированных прав доступа;
+3. Технический запрет на продолжение административной работы под учётной записью с истёкшим сроком действия пароля;
+4. Технический запрет на повторное использование ранее применявшихся паролей (история паролей) для привилегированных учётных записей.
+Класс используемых средств — системы управления привилегированным доступом (PAM), службы каталогов с политикой паролей.
+Иностранные: CyberArk PAM, Microsoft Active Directory (Fine-Grained Password Policy) и пр.
+Российские сертифицированные (ФСТЭК): Indeed Privileged Access Manager, «Система контроля привилегированных пользователей SafeInspect» и др.
+Открытый код: Teleport и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F57" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с эксплуатационным персоналом и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек политики паролей для привилегированных учётных записей, подтверждающие максимальный срок действия не более 90 дней;
+3. Выгрузка отчёта о датах последней смены паролей эксплуатационного персонала;
+4. Результаты тестирования (попытка административного входа под учётной записью с истёкшим сроком действия пароля), подтверждающие срабатывание требования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G57" s="151" t="inlineStr">
+        <is>
+          <t>1. Политика срока действия пароля для эксплуатационного персонала не отличается от политики для рядовых пользователей (не учитывает более строгий квартальный порог);
+2. Встроенные (сервисные) учётные записи оборудования не охвачены политикой смены паролей;
+3. Смена паролей выполняется формально, без фактического изменения сложности пароля;
+4. Контроль соблюдения квартальной периодичности не формализован, нарушения выявляются несистемно.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="128.25" customHeight="1">
       <c r="A58" s="20" t="inlineStr">
@@ -4298,9 +5248,52 @@
 Главная цель меры — повысить устойчивость паролей к подбору (методами перебора, атаками по словарю и т.п.) за счёт увеличения их длины. Чем длиннее пароль, тем больше возможных комбинаций и тем сложнее его подобрать злоумышленнику.</t>
         </is>
       </c>
-      <c r="E58" s="31" t="n"/>
-      <c r="F58" s="31" t="n"/>
-      <c r="G58" s="31" t="n"/>
+      <c r="E58" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется на техническом уровне без организационной составляющей:
+1. Настройку в операционных системах, каталогах и прикладных информационных системах политики минимальной длины пароля пользователей — не менее восьми символов;
+2. Технический запрет на установку (сохранение) пользователем пароля короче установленного минимума;
+3. Распространение данной настройки на все информационные системы, к которым пользователи осуществляют логический доступ.
+Класс используемых средств — службы каталогов и системы управления учётными записями (IdM) со встроенной политикой паролей.
+Иностранные: Microsoft Active Directory (Minimum Password Length) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Avanpost IDM и др.
+Открытый код: FreeIPA, OpenLDAP и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F58" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты (выгрузки) настроек политики паролей, подтверждающие минимальную длину не менее восьми символов;
+3. Результаты тестирования (попытка установки пароля короче восьми символов), подтверждающие блокирование такой попытки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G58" s="151" t="inlineStr">
+        <is>
+          <t>1. Политика минимальной длины пароля настроена не для всех информационных систем;
+2. Требование к длине пароля установлено на уровне регламента, но технически не контролируется (пользователь фактически может задать более короткий пароль);
+3. Отдельные унаследованные системы технически не поддерживают установку минимальной длины пароля восемь и более символов, компенсирующие меры не приняты.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="256.5" customHeight="1">
       <c r="A59" s="20" t="inlineStr">
@@ -4324,9 +5317,52 @@
 Главная цель меры — существенно повысить устойчивость паролей эксплуатационного персонала к подбору (методами перебора, атаками по словарю и т.п.) за счёт значительного увеличения их длины. Пароль длиной 16 символов экспоненциально сложнее подобрать, чем 8-символьный, что критически важно для защиты привилегированных учётных записей.</t>
         </is>
       </c>
-      <c r="E59" s="31" t="n"/>
-      <c r="F59" s="31" t="n"/>
-      <c r="G59" s="31" t="n"/>
+      <c r="E59" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационные меры для данного требования не предусмотрены — реализация строится на технических решениях:
+1. Настройку отдельной (более строгой) политики паролей для привилегированных (административных) учётных записей — минимальная длина пароля не менее шестнадцати символов;
+2. Технический запрет на установку эксплуатационным персоналом пароля короче установленного минимума;
+3. Распространение данной настройки на все административные интерфейсы и системы, к которым эксплуатационный персонал осуществляет логический доступ, включая сетевое оборудование и средства защиты информации.
+Класс используемых средств — системы управления привилегированным доступом (PAM), службы каталогов с раздельными политиками паролей (Fine-Grained Password Policy).
+Иностранные: CyberArk PAM, Microsoft Active Directory (Fine-Grained Password Policy) и пр.
+Российские сертифицированные (ФСТЭК): Indeed Privileged Access Manager, Secret Net Studio и др.
+Открытый код: Teleport и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F59" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с эксплуатационным персоналом и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек политики паролей для привилегированных учётных записей, подтверждающие минимальную длину не менее шестнадцати символов;
+3. Результаты тестирования (попытка установки административного пароля короче шестнадцати символов), подтверждающие блокирование такой попытки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G59" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельная (более строгая) политика длины пароля для эксплуатационного персонала не настроена, применяется общая политика для рядовых пользователей;
+2. Требование распространяется не на все административные интерфейсы (например, отсутствует для встроенных консолей управления сетевым оборудованием);
+3. Встроенные (сервисные) учётные записи производителей оборудования используют пароли короче установленного минимума.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="199.5" customHeight="1">
       <c r="A60" s="20" t="inlineStr">
@@ -4350,9 +5386,52 @@
 Главная цель меры — существенно повысить устойчивость паролей к подбору (методами перебора, атаками по словарю и т.п.) за счёт увеличения их сложности. Пароль, состоящий только из букв одного регистра, значительно легче подобрать, чем пароль, содержащий буквы разных регистров и цифры. Использование символов из разных групп расширяет пространство возможных комбинаций, что делает перебор паролей вычислительно трудоёмким для злоумышленника.</t>
         </is>
       </c>
-      <c r="E60" s="31" t="n"/>
-      <c r="F60" s="31" t="n"/>
-      <c r="G60" s="31" t="n"/>
+      <c r="E60" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера выполняется силами технических средств защиты информации, а именно:
+1. Настройку в операционных системах, каталогах и прикладных информационных системах политики сложности пароля, требующей одновременного использования заглавных и строчных букв, а также цифр;
+2. Технический запрет на установку пароля, не соответствующего установленным требованиям сложности;
+3. Распространение данной настройки на все информационные системы, к которым субъекты логического доступа осуществляют вход.
+Класс используемых средств — службы каталогов и системы управления учётными записями (IdM) со встроенной политикой сложности паролей.
+Иностранные: Microsoft Active Directory (Password must meet complexity requirements) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Avanpost IDM и др.
+Открытый код: FreeIPA, pam_pwquality (Linux) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F60" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты (выгрузки) настроек политики сложности паролей;
+3. Результаты тестирования (попытка установки пароля без цифр или без букв разных регистров), подтверждающие блокирование такой попытки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G60" s="151" t="inlineStr">
+        <is>
+          <t>1. Политика сложности пароля настроена не для всех информационных систем;
+2. Требование к сложности пароля декларировано в регламенте, но технически не контролируется;
+3. Отдельные унаследованные системы не поддерживают проверку сложности пароля, компенсирующие меры не приняты.</t>
+        </is>
+      </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4375,10 +5454,55 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D61" s="21" t="n"/>
-      <c r="E61" s="31" t="n"/>
-      <c r="F61" s="31" t="n"/>
-      <c r="G61" s="31" t="n"/>
+      <c r="D61" s="144" t="inlineStr">
+        <is>
+          <t>Мера дополняет требования к длине и сложности паролей (РД.21—РД.23) запретом на использование легко вычисляемых (предсказуемых) комбинаций — личных данных субъекта (имени, фамилии, даты рождения), наименований организации или её подразделений, общепринятых сокращений и иных сочетаний, которые злоумышленник может подобрать не перебором, а логическим предположением или методами социальной инженерии.
+Главная цель меры — исключить класс паролей, формально соответствующих требованиям длины и сложности, но фактически легко угадываемых, поскольку такие пароли сводят на нет эффект от остальных парольных требований.</t>
+        </is>
+      </c>
+      <c r="E61" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе (парольной политике) прямого запрета на использование в паролях личных данных субъекта, наименований организации, общепринятых сокращений и иных легко вычисляемых сочетаний, с приведением показательных примеров недопустимых паролей;
+2. Информирование (инструктаж) субъектов логического доступа об этом требовании при первичном допуске к работе и периодически в рамках повышения осведомлённости по вопросам информационной безопасности;
+3. Включение данного требования в памятки и инструкции по формированию надёжных паролей, доводимые до сведения пользователей и эксплуатационного персонала.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F61" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ (парольная политика), содержащий запрет на использование легко вычисляемых сочетаний в паролях;
+2. Листы ознакомления субъектов логического доступа с требованиями к формированию паролей;
+3. Материалы инструктажа (памятки) по формированию надёжных паролей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G61" s="151" t="inlineStr">
+        <is>
+          <t>1. Запрет декларирован в документе, но не проверяется на практике — технические средства контроля «слабых» паролей на основе словарей и типовых шаблонов не используются;
+2. Субъекты логического доступа не информируются о данном требовании при первичном допуске;
+3. Инструктаж проводится формально, без разъяснения конкретных примеров недопустимых паролей;
+4. Требование не пересматривается и не актуализируется с учётом современных методов подбора паролей (атаки по маскам, использование утёкших баз данных).</t>
+        </is>
+      </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4407,9 +5531,54 @@
 Главная цель меры — снизить нагрузку на административный персонал и повысить оперативность смены паролей пользователями (например, при подозрении на компрометацию, по требованию политики безопасности, при забывании пароля с использованием механизмов самовосстановления или по истечении срока действия). Это также способствует повышению безопасности, так как пользователи могут незамедлительно сменить пароль при возникновении подозрений на его компрометацию, не дожидаясь администратора.</t>
         </is>
       </c>
-      <c r="E62" s="31" t="n"/>
-      <c r="F62" s="31" t="n"/>
-      <c r="G62" s="31" t="n"/>
+      <c r="E62" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Предоставление субъектам логического доступа штатной технической возможности самостоятельно изменить свой пароль без обращения к администратору (стандартная функция смены пароля в операционной системе, каталоге или портале самообслуживания);
+2. Реализацию механизма самостоятельного восстановления доступа при утрате (забывании) пароля — с обязательным подтверждением личности субъекта дополнительным способом (секретные вопросы, одноразовый код, обращение к service desk);
+3. Применение к самостоятельно устанавливаемому пользователем паролю тех же требований сложности, длины и истории паролей, что предусмотрены мерами РД.19—РД.23.
+Класс используемых средств — службы каталогов и системы управления учётными записями (IdM) с функцией самообслуживания пользователей (self-service password reset).
+Иностранные: Microsoft Identity Manager (Self-Service Password Reset), Okta и пр.
+Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
+Открытый код: FreeIPA (портал самообслуживания) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F62" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с пользователями и администраторами информационных систем;
+2. Результаты тестирования (самостоятельная смена пароля пользователем), подтверждающие доступность и корректную работу функции;
+3. Скриншоты интерфейса самостоятельной смены (восстановления) пароля;
+4. Результаты выборочной проверки, подтверждающие применение к самостоятельно устанавливаемому паролю требований сложности, длины и истории паролей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G62" s="151" t="inlineStr">
+        <is>
+          <t>1. Функция самостоятельной смены пароля доступна не для всех информационных систем, к части систем пароль меняет только администратор;
+2. Механизм восстановления пароля при его утрате не предусматривает достаточного подтверждения личности субъекта, что создаёт риск социальной инженерии;
+3. При самостоятельной смене пароля не проверяется его соответствие требованиям сложности и истории паролей;
+4. Пользователи не осведомлены о наличии функции самостоятельной смены пароля и продолжают обращаться к администраторам.</t>
+        </is>
+      </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4432,10 +5601,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D63" s="21" t="n"/>
-      <c r="E63" s="31" t="n"/>
-      <c r="F63" s="31" t="n"/>
-      <c r="G63" s="31" t="n"/>
+      <c r="D63" s="144" t="inlineStr">
+        <is>
+          <t>Мера предполагает создание и хранение резервных копий аутентификационных данных эксплуатационного персонала (в первую очередь — паролей от критичных привилегированных учётных записей, в том числе аварийных «break-glass» учётных записей) на выделенных машинных носителях информации (МНИ) либо на бумажных носителях, отдельно от систем, в которых эти данные используются.
+Главная цель меры — обеспечить возможность восстановления доступа к критичным системам в аварийной ситуации (например, при недоступности эксплуатационного персонала, владеющего паролем, или при отказе средств централизованного управления доступом), не полагаясь исключительно на память конкретных сотрудников или на системы, которые сами могут быть недоступны в момент аварии.</t>
+        </is>
+      </c>
+      <c r="E63" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационно это выражается в следующем:
+1. Определение перечня критичных привилегированных учётных записей, аутентификационные данные которых подлежат резервному хранению (аварийные учётные записи, учётные записи с полномочиями восстановления систем управления доступом);
+2. Утверждение порядка формирования, хранения и обновления резервных копий аутентификационных данных на выделенных МНИ или бумажных носителях (конвертах с печатью, сейф-пакетах);
+3. Определение места хранения (сейф, иное защищённое хранилище) и круга лиц, имеющих право доступа к резервным копиям аутентификационных данных;
+4. Установление порядка обновления резервных копий при плановой смене аутентификационных данных (см. также меры РД.19—РД.20, РД.29).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F63" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) формирования, хранения и обновления резервных копий аутентификационных данных эксплуатационного персонала;
+2. Перечень критичных привилегированных учётных записей, аутентификационные данные которых подлежат резервному хранению;
+3. Акты закладки (обновления) резервных копий аутентификационных данных на МНИ или бумажных носителях.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G63" s="151" t="inlineStr">
+        <is>
+          <t>1. Перечень критичных учётных записей, подлежащих резервному хранению аутентификационных данных, не определён или неполон;
+2. Резервные копии аутентификационных данных не обновляются при плановой или внеплановой смене паролей, что делает их фактически бесполезными;
+3. Место хранения резервных копий не защищено надлежащим образом (общедоступный сейф, отсутствие контроля доступа);
+4. Факты обращения к резервным копиям (в аварийных ситуациях) не фиксируются документально.</t>
+        </is>
+      </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4458,10 +5673,58 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D64" s="21" t="n"/>
-      <c r="E64" s="31" t="n"/>
-      <c r="F64" s="31" t="n"/>
-      <c r="G64" s="31" t="n"/>
+      <c r="D64" s="144" t="inlineStr">
+        <is>
+          <t>Мера дополняет требование РД.26 и устанавливает необходимость защиты самих резервных копий аутентификационных данных эксплуатационного персонала от несанкционированного доступа (НСД) в процессе их хранения на машинных носителях информации (МНИ) или бумажных носителях.
+Главная цель меры — исключить ситуацию, при которой резервные копии критичных паролей, созданные во исполнение меры РД.26 для аварийных случаев, сами становятся уязвимым звеном — то есть хранятся без надлежащей защиты и могут быть скомпрометированы лицом, не имеющим полномочий на доступ к ним.</t>
+        </is>
+      </c>
+      <c r="E64" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Со стороны организационных мер требуется:
+1. Определение требований к физической защите места хранения резервных копий аутентификационных данных (сейф с ограниченным кругом лиц, имеющих доступ, помещение с контролем доступа);
+2. Использование для бумажных носителей опечатанных конвертов (сейф-пакетов) с индикацией вскрытия, позволяющих визуально определить факт несанкционированного доступа;
+3. Для машинных носителей информации — применение шифрования содержимого носителя с ограничением круга лиц, обладающих ключом расшифрования;
+4. Ведение учёта (журнала) доступа к резервным копиям аутентификационных данных с фиксацией даты, времени, лица и цели обращения;
+5. Периодический контроль целостности хранения (проверка сохранности пломб (печатей), инвентаризация МНИ).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F64" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент, устанавливающий требования к защите резервных копий аутентификационных данных от несанкционированного доступа;
+2. Акты проверки состояния мест хранения (сейфов), опечатанных конвертов и сейф-пакетов;
+3. Журнал учёта доступа к резервным копиям аутентификационных данных;
+4. Свидетельства применения шифрования для машинных носителей информации, содержащих резервные копии аутентификационных данных.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G64" s="151" t="inlineStr">
+        <is>
+          <t>1. Резервные копии аутентификационных данных хранятся в местах с широким кругом доступа (незапираемый шкаф, общий сейф без разграничения доступа);
+2. Бумажные носители не опечатываются способом, позволяющим выявить факт вскрытия;
+3. Машинные носители информации с резервными копиями аутентификационных данных не зашифрованы;
+4. Журнал учёта доступа к резервным копиям не ведётся или ведётся формально, не позволяя восстановить историю обращений.</t>
+        </is>
+      </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -4484,10 +5747,57 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="31" t="n"/>
-      <c r="F65" s="31" t="n"/>
-      <c r="G65" s="31" t="n"/>
+      <c r="D65" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует ведения учёта (регистрации) всего жизненного цикла персональных технических устройств аутентификации, используемых для многофакторной аутентификации (аппаратных токенов, смарт-карт, USB-ключей и подобных устройств): их персонализации (привязки к конкретному субъекту), выдачи (передачи) субъекту и последующего уничтожения (вывода из эксплуатации).
+Главная цель меры — обеспечить полную прослеживаемость обращения физических устройств аутентификации, поскольку без такого учёта невозможно достоверно установить, какому субъекту принадлежит конкретное устройство, находится ли оно у него на руках либо утрачено или не возвращено при увольнении, а также подтвердить факт надлежащего уничтожения выведенных из эксплуатации устройств.</t>
+        </is>
+      </c>
+      <c r="E65" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Ведение реестра (журнала) персональных технических устройств аутентификации с указанием серийного (уникального) номера устройства, субъекта, за которым оно закреплено, и статуса устройства (выдано, возвращено, уничтожено);
+2. Оформление факта выдачи (передачи) устройства субъекту актом или иным документом с подписью получателя;
+3. Оформление факта возврата устройства (при увольнении, замене, окончании срока действия) и его последующего уничтожения актом с участием комиссии или ответственного лица;
+4. Периодическую сверку данных реестра с фактическим наличием устройств у субъектов и фактическим статусом многофакторной аутентификации в соответствующих системах.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F65" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) регистрации персонификации, выдачи и уничтожения персональных технических устройств аутентификации;
+2. Реестр (журнал) персональных технических устройств аутентификации;
+3. Акты выдачи (передачи) устройств субъектам;
+4. Акты уничтожения (списания) устройств, выведенных из эксплуатации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G65" s="151" t="inlineStr">
+        <is>
+          <t>1. Реестр устройств аутентификации ведётся не по всем выданным устройствам либо содержит устаревшие данные;
+2. Факт выдачи устройства субъекту не оформляется документально (акт отсутствует);
+3. При увольнении сотрудника устройство аутентификации не изымается и не деактивируется своевременно;
+4. Уничтожение выведенных из эксплуатации устройств не оформляется актом, что не позволяет подтвердить их фактическую утилизацию.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="20" t="inlineStr">
@@ -4505,10 +5815,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="31" t="n"/>
-      <c r="F66" s="31" t="n"/>
-      <c r="G66" s="31" t="n"/>
+      <c r="D66" s="144" t="inlineStr">
+        <is>
+          <t>Мера обязывает незамедлительно менять аутентификационные данные (пароли, а для устройств многофакторной аутентификации — переоформлять либо блокировать устройство) при выявлении факта их компрометации — то есть в случаях, когда есть основания полагать, что аутентификационные данные стали известны или могли стать известны лицу, не имеющему на это полномочий.
+Главная цель меры — минимизировать время, в течение которого скомпрометированные аутентификационные данные остаются действующими и потенциально могут использоваться злоумышленником, независимо от того, наступил ли для этого плановый срок смены пароля по мерам РД.19—РД.20.</t>
+        </is>
+      </c>
+      <c r="E66" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит организационный характер и включает:
+1. Определение во внутреннем нормативном документе признаков (событий), при которых аутентификационные данные считаются скомпрометированными или потенциально скомпрометированными (утеря устройства аутентификации, подозрение на фишинг, ввод пароля на постороннем ресурсе, инцидент информационной безопасности);
+2. Установление обязанности субъекта логического доступа немедленно сообщать о подозрении на компрометацию своих аутентификационных данных в подразделение информационной безопасности или service desk;
+3. Установление порядка и предельного срока внеплановой смены аутентификационных данных (или блокирования/переоформления устройства аутентификации) при получении сигнала о компрометации;
+4. Фиксацию факта компрометации и принятых мер в журнале инцидентов информационной безопасности.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F66" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, определяющий признаки компрометации аутентификационных данных и порядок реагирования;
+2. Журнал (реестр) инцидентов, связанных с компрометацией аутентификационных данных, с указанием принятых мер;
+3. Свидетельства внеплановой смены аутентификационных данных (журналы смены паролей, акты переоформления устройств аутентификации) по зафиксированным случаям компрометации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G66" s="151" t="inlineStr">
+        <is>
+          <t>1. Субъекты логического доступа не осведомлены о необходимости и порядке сообщения о подозрении на компрометацию своих аутентификационных данных;
+2. Сроки внеплановой смены аутентификационных данных при подтверждённой компрометации не соблюдаются;
+3. Факты компрометации не фиксируются в едином журнале (реестре) инцидентов, что не позволяет оценить масштаб и повторяемость таких случаев;
+4. При компрометации пароля не проводится анализ возможных последствий (например, не проверяется, использовался ли этот же пароль для доступа к другим ресурсам).</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
@@ -22768,8 +24124,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -797,6 +797,9 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -5895,10 +5898,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="31" t="n"/>
-      <c r="F68" s="31" t="n"/>
-      <c r="G68" s="31" t="n"/>
+      <c r="D68" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает базовое техническое требование: любое обращение субъекта логического доступа к ресурсу доступа (в том числе к автоматизированной системе (АС)) должно сопровождаться процедурой авторизации — проверкой того, что данному субъекту действительно предоставлены права на запрашиваемое действие.
+Главная цель меры — гарантировать, что успешного прохождения идентификации и аутентификации (мер РД.1—РД.7) недостаточно для получения доступа к конкретному ресурсу: должна выполняться отдельная проверка полномочий, без которой любой аутентифицированный субъект мог бы обращаться к любым ресурсам вне зависимости от предоставленных ему прав.</t>
+        </is>
+      </c>
+      <c r="E68" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется на техническом уровне без организационной составляющей:
+1. Настройку операционных систем, СУБД, прикладного ПО и сетевого оборудования таким образом, чтобы каждое обращение к ресурсу доступа проверялось на соответствие фактически предоставленным правам, независимо от факта успешной аутентификации;
+2. Использование встроенных механизмов авторизации ресурсов доступа (списки контроля доступа — ACL, ролевые модели, политики доступа) в каждой информационной системе;
+3. Технический запрет на выполнение операций, не охваченных явно предоставленными правами субъекта («запрет по умолчанию» — default deny).
+Класс используемых средств — встроенные механизмы авторизации операционных систем, СУБД и прикладного ПО, средства защиты от несанкционированного доступа (СЗИ от НСД).
+Иностранные: Microsoft Active Directory (списки контроля доступа), Oracle Database (Fine-Grained Access Control) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К и др.
+Открытый код: SELinux, PostgreSQL (Row-Level Security) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F68" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты настроек авторизации (списков контроля доступа, ролевых моделей) в информационных системах;
+3. Результаты тестирования (попытка обращения аутентифицированного, но не авторизованного субъекта к ресурсу), подтверждающие срабатывание запрета;
+4. Журналы событий, подтверждающие регистрацию решений об авторизации (разрешении/отказе в доступе).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G68" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельные ресурсы доступа (в том числе АС) не проверяют права субъекта при обращении, полагаясь только на факт успешной аутентификации;
+2. Модель авторизации построена по принципу «разрешено по умолчанию», а не «запрещено по умолчанию», что создаёт риск избыточного доступа к неучтённым функциям;
+3. Настройки авторизации не покрывают все точки доступа к ресурсу (например, отсутствуют для программных интерфейсов — API);
+4. Тестирование фактического срабатывания механизма авторизации не проводится.</t>
+        </is>
+      </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -5921,10 +5974,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="31" t="n"/>
-      <c r="F69" s="31" t="n"/>
-      <c r="G69" s="31" t="n"/>
+      <c r="D69" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы в каждом ресурсе доступа применялся метод разграничения логического доступа, соответствующий характеру обрабатываемой информации и уровню защиты, — дискреционный (управление доступом на основе прав, назначаемых владельцем ресурса), мандатный (управление доступом на основе меток конфиденциальности) или ролевой (управление доступом на основе ролей субъектов), либо иной обоснованный метод.
+Главная цель меры — обеспечить осознанный и соответствующий специфике ресурса выбор модели разграничения доступа, а не бессистемное предоставление прав, поскольку выбор неподходящего или отсутствие какого-либо формализованного метода делает управление доступом непрозрачным и труднопроверяемым.</t>
+        </is>
+      </c>
+      <c r="E69" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими средствами, необходимо:
+1. Определение для каждого ресурса доступа (АС, СУБД, файлового ресурса и т. д.) применимого метода разграничения доступа исходя из специфики обрабатываемой информации и архитектуры ресурса;
+2. Настройку выбранного метода средствами самого ресурса доступа (дискреционные списки контроля доступа, мандатные метки конфиденциальности, ролевые модели);
+3. Технический контроль того, что разграничение доступа выполняется именно выбранным методом, а не в обход него (например, через прямой доступ к данным на уровне файловой системы или СУБД, минуя прикладную логику авторизации).
+Класс используемых средств — встроенные механизмы разграничения доступа операционных систем и СУБД, средства защиты от несанкционированного доступа (СЗИ от НСД) с поддержкой мандатного управления доступом.
+Иностранные: Microsoft Active Directory (дискреционная модель), Oracle Label Security (мандатная модель) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Astra Linux Special Edition (мандатное управление доступом) и др.
+Открытый код: SELinux (мандатное управление доступом) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F69" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Проектная (эксплуатационная) документация ресурсов доступа, содержащая описание применяемого метода разграничения доступа;
+3. Скриншоты настроек, подтверждающие фактическую реализацию выбранного метода;
+4. Результаты тестирования, подтверждающие невозможность обхода выбранного метода разграничения доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G69" s="151" t="inlineStr">
+        <is>
+          <t>1. Метод разграничения доступа не определён и не обоснован документально для части ресурсов доступа;
+2. Заявленный метод (например, мандатный) реализован не в полном объёме, фактически используется упрощённая дискреционная модель;
+3. Существуют технические пути обхода установленного метода разграничения доступа (прямой доступ к данным в обход прикладной логики);
+4. Настройки метода разграничения доступа не пересматриваются при изменении состава обрабатываемой информации.</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -5947,10 +6050,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D70" s="21" t="n"/>
-      <c r="E70" s="31" t="n"/>
-      <c r="F70" s="31" t="n"/>
-      <c r="G70" s="31" t="n"/>
+      <c r="D70" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует РД.31 применительно к автоматизированным системам (АС): в них должен применяться именно ролевой метод разграничения доступа (Role-Based Access Control, RBAC), при котором для каждой роли заранее определён чётко зафиксированный набор прав доступа, а субъектам права предоставляются через назначение соответствующей роли, а не по отдельности.
+Главная цель меры — упростить и сделать прозрачным управление правами доступа в АС за счёт группировки прав в типовые роли, соответствующие производственным функциям субъектов, что снижает риск ошибок при назначении прав и облегчает последующий контроль (в том числе в рамках мер УЗП.8—УЗП.9).</t>
+        </is>
+      </c>
+      <c r="E70" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера подразумевает исключительно технические меры защиты, а именно:
+1. Разработку и настройку в АС ролевой модели: определение перечня ролей, соответствующих производственным функциям субъектов, и фиксацию для каждой роли конкретного набора прав доступа к функциям и данным АС;
+2. Настройку АС таким образом, чтобы предоставление прав доступа субъекту выполнялось исключительно через назначение ему одной или нескольких ролей, без возможности точечного (вне ролевой модели) назначения отдельных прав;
+3. Технический контроль соответствия фактически предоставленных прав заявленному составу прав для назначенных субъекту ролей.
+Класс используемых средств — встроенные механизмы ролевого управления доступом (RBAC) прикладного ПО и АС, системы управления учётными записями и правами доступа (IdM) с поддержкой ролевых моделей.
+Иностранные: SAP (ролевая модель авторизаций), Microsoft Dynamics (RBAC) и пр.
+Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights и др.
+Открытый код: Keycloak (Role-Based Access Control) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F70" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами АС;
+2. Проектная документация АС, содержащая описание ролевой модели и состава прав каждой роли;
+3. Скриншоты настроек ролевой модели в АС;
+4. Результаты тестирования (сопоставление фактических прав субъекта с заявленным составом прав его роли (ролей)).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G70" s="151" t="inlineStr">
+        <is>
+          <t>1. Ролевая модель в АС не охватывает все функции и данные, часть прав предоставляется точечно, в обход ролей;
+2. Роли определены нечётко, их состав пересекается, что затрудняет контроль фактически предоставленных прав;
+3. Роли не пересматриваются при изменении функциональности АС, актуальность состава прав каждой роли не подтверждается;
+4. Одному субъекту назначено избыточное количество ролей без документированного обоснования служебной необходимости.</t>
+        </is>
+      </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -5973,10 +6126,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="31" t="n"/>
-      <c r="F71" s="31" t="n"/>
-      <c r="G71" s="31" t="n"/>
+      <c r="D71" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы разграничение логического доступа выполнялось не только на уровне «есть доступ / нет доступа» к ресурсу в целом, но и по конкретным типам операций — чтению, записи, выполнению или иным применимым типам, — с определением правил, по которым тот или иной тип доступа предоставляется субъекту.
+Главная цель меры — реализовать принцип минимально необходимых прав на уровне операций: субъект должен получать только те типы доступа к ресурсу, которые действительно необходимы ему для выполнения служебных обязанностей (например, право только на чтение данных без права их изменения), а не полный доступ ко всем операциям с ресурсом.</t>
+        </is>
+      </c>
+      <c r="E71" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввиду того, что мера реализуется только технически, необходимо:
+1. Настройку ресурсов доступа (файловых систем, СУБД, прикладного ПО) таким образом, чтобы для субъекта можно было раздельно предоставлять права на чтение, запись, выполнение и иные применимые операции;
+2. Определение и документальное закрепление правил, по которым субъектам предоставляется тот или иной тип доступа (например, право на запись предоставляется только субъектам, ответственным за ввод и изменение данных, право на чтение — более широкому кругу субъектов);
+3. Технический контроль того, что субъекту не предоставлен более широкий тип доступа, чем это предусмотрено установленными правилами (например, исключение случаев, когда право на чтение фактически сопровождается и правом на запись).
+Класс используемых средств — встроенные механизмы разграничения доступа операционных систем, файловых систем и СУБД (списки контроля доступа — ACL, права на уровне объектов).
+Иностранные: Microsoft NTFS (права на уровне файлов и папок), Oracle Database (системные и объектные привилегии) и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Astra Linux Special Edition и др.
+Открытый код: файловые права POSIX (ACL), PostgreSQL (GRANT/REVOKE) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F71" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Внутренний документ, определяющий правила предоставления субъектам различных типов доступа (чтение, запись, выполнение);
+3. Скриншоты настроек, подтверждающие раздельное разграничение типов доступа к ресурсу;
+4. Результаты тестирования (проверка фактического типа доступа субъекта к ресурсу на соответствие установленным правилам).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G71" s="151" t="inlineStr">
+        <is>
+          <t>1. Правила предоставления различных типов доступа не формализованы документально;
+2. Субъектам систематически предоставляется более широкий тип доступа, чем необходимо (например, право на запись вместо права только на чтение);
+3. Отдельные ресурсы доступа не поддерживают раздельное разграничение по типам операций, что вынуждает предоставлять полный доступ;
+4. Соответствие фактически предоставленных типов доступа установленным правилам не проверяется на регулярной основе.</t>
+        </is>
+      </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -5999,10 +6202,89 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="31" t="n"/>
-      <c r="F72" s="31" t="n"/>
-      <c r="G72" s="31" t="n"/>
+      <c r="D72" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает пользователям выполнять бизнес-процессы и технологические процессы (то есть их обычную рабочую деятельность) под учётными записями эксплуатационного персонала — привилегированными административными учётными записями, предназначенными для эксплуатации и администрирования систем, а не для выполнения повседневных операций.
+Главная цель меры — предотвратить смешение ролей пользователя и администратора: использование привилегированной учётной записи для рутинных операций резко увеличивает потенциальный ущерб от компрометации такой учётной записи или от ошибки пользователя, а также обесценивает разграничение прав, установленное мерами УЗП.19—УЗП.21.</t>
+        </is>
+      </c>
+      <c r="E72" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная составляющая сводится к следующим шагам:
+1. Закрепление во внутреннем нормативном документе прямого запрета на использование учётных записей эксплуатационного персонала для выполнения бизнес-процессов и технологических процессов, не относящихся к эксплуатации и администрированию систем;
+2. Информирование эксплуатационного персонала о данном запрете и о необходимости использования отдельной персональной пользовательской учётной записи для непроизводственных (не связанных с администрированием) операций;
+3. Периодический контроль (анализ журналов, выборочные проверки) фактического использования привилегированных учётных записей на предмет выполнения под ними операций бизнес- и технологических процессов.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически права логического доступа разграничиваются так:
+1. Предоставление эксплуатационному персоналу двух раздельных учётных записей — привилегированной (административной) для задач эксплуатации и обычной пользовательской для выполнения непроизводственных операций (при их наличии у данного сотрудника);
+2. Технический запрет использования привилегированных учётных записей для входа в АС и выполнения в них функций, относящихся к бизнес-процессам и технологическим процессам (например, ограничение состава ролей, доступных привилегированной учётной записи, только административными функциями);
+3. Регистрацию и автоматизированный анализ фактов выполнения под привилегированными учётными записями операций, типичных для бизнес-процессов, с оповещением подразделения информационной безопасности при выявлении таких фактов.
+Класс используемых средств — системы управления привилегированным доступом (PAM), системы управления событиями информационной безопасности (SIEM).
+Иностранные: CyberArk PAM, Splunk (для анализа журналов) и пр.
+Российские сертифицированные (ФСТЭК): Indeed Privileged Access Manager, MaxPatrol SIEM и др.
+Открытый код: Teleport, Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F72" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, содержащий запрет на использование учётных записей эксплуатационного персонала для выполнения бизнес- и технологических процессов;
+2. Материалы информирования (инструктажа) эксплуатационного персонала о данном запрете;
+3. Акты (отчёты) периодического контроля фактического использования привилегированных учётных записей.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Выгрузка перечня учётных записей эксплуатационного персонала, подтверждающая наличие раздельных привилегированной и пользовательской учётных записей;
+3. Скриншоты настроек, ограничивающих состав ролей, доступных привилегированной учётной записи, административными функциями;
+4. Журналы событий (отчёты SIEM), подтверждающие анализ фактов выполнения бизнес-операций под привилегированными учётными записями.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G72" s="151" t="inlineStr">
+        <is>
+          <t>1. Эксплуатационному персоналу не выделяется отдельная пользовательская учётная запись, вся деятельность (включая непроизводственную) выполняется под привилегированной учётной записью;
+2. Технический запрет на выполнение бизнес-операций под привилегированными учётными записями не реализован, ограничение носит только организационный (декларативный) характер;
+3. Анализ журналов на предмет выполнения бизнес-операций под привилегированными учётными записями не проводится;
+4. Запрет не доведён до сведения эксплуатационного персонала.</t>
+        </is>
+      </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6025,10 +6307,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D73" s="21" t="n"/>
-      <c r="E73" s="31" t="n"/>
-      <c r="F73" s="31" t="n"/>
-      <c r="G73" s="31" t="n"/>
+      <c r="D73" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает пользователям выполнять бизнес-процессы, обладая привилегированными правами логического доступа, — в частности, запрещает повседневную работу пользователя на автоматизированном рабочем месте (АРМ) под учётной записью с правами локального администратора.
+Главная цель меры — минимизировать потенциальный ущерб от компрометации рабочей станции пользователя (например, в результате заражения вредоносным ПО или фишинговой атаки): если пользователь работает без привилегированных прав, вредоносный код, запущенный от его имени, также не получает административных полномочий на АРМ, что существенно ограничивает возможности злоумышленника закрепиться в системе или распространиться на другие ресурсы.</t>
+        </is>
+      </c>
+      <c r="E73" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Настройку учётных записей пользователей таким образом, чтобы для повседневной работы (выполнения бизнес-процессов) использовалась учётная запись без прав локального администратора и без иных привилегированных прав логического доступа;
+2. Реализацию отдельного, контролируемого механизма временного повышения привилегий для случаев, когда пользователю действительно необходимо выполнить операцию, требующую административных прав (запрос повышения привилегий с санкционированием и регистрацией);
+3. Технический контроль (аудит состава локальных администраторов АРМ), выявляющий и устраняющий случаи, когда обычные пользователи фактически обладают правами локального администратора.
+Класс используемых средств — средства управления привилегиями на конечных точках (Endpoint Privilege Management), системы управления конфигурациями.
+Иностранные: Microsoft Defender for Endpoint (совместно с политиками ограничения прав), CyberArk Endpoint Privilege Manager и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К и др.
+Открытый код: групповые политики Linux/Windows без выделенных общепринятых открытых аналогов и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F73" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами АРМ;
+2. Выгрузка перечня локальных администраторов АРМ, подтверждающая отсутствие среди них рядовых пользователей;
+3. Скриншоты настроек механизма временного повышения привилегий (при его наличии);
+4. Результаты аудита (сканирования) АРМ на предмет фактического состава локальных администраторов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G73" s="151" t="inlineStr">
+        <is>
+          <t>1. Часть пользователей продолжает работать с правами локального администратора АРМ по факту исторически сложившейся практики;
+2. Механизм временного контролируемого повышения привилегий отсутствует, что вынуждает администраторов постоянно предоставлять пользователям административные права «про запас»;
+3. Аудит фактического состава локальных администраторов АРМ не проводится на регулярной основе;
+4. Выявленные случаи наличия у пользователя прав локального администратора не устраняются в разумный срок.</t>
+        </is>
+      </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6057,9 +6389,50 @@
 Главная цель меры — снижение риска несанкционированного доступа и своевременное выявление факта компрометации учётной записи. Если пользователь видит, что его предыдущий вход был совершён в то время, когда он точно не работал в системе, это является явным признаком того, что его учётные данные были использованы злоумышленником. Пользователь может оперативно среагировать: сменить пароль и сообщить о случившемся в службу информационной безопасности.</t>
         </is>
       </c>
-      <c r="E74" s="31" t="n"/>
-      <c r="F74" s="31" t="n"/>
-      <c r="G74" s="31" t="n"/>
+      <c r="E74" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит чисто технический характер и включает:
+1. Настройку АС таким образом, чтобы после успешной авторизации субъекту отображалось информационное сообщение с датой и временем его предыдущего успешного входа в данную АС;
+2. Хранение в системе сведений о дате и времени предыдущих успешных авторизаций каждого субъекта в объёме, достаточном для формирования такого уведомления;
+3. Обеспечение того, что данное уведомление не может быть отключено или скрыто самим пользователем.
+Отдельного специализированного средства защиты для реализации меры, как правило, не требуется: функция реализуется на уровне логики самой АС и её встроенных механизмов идентификации и аутентификации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F74" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с пользователями и разработчиками (администраторами) АС;
+2. Скриншоты интерфейса АС, подтверждающие отображение уведомления о дате и времени предыдущей авторизации;
+3. Результаты тестирования (последовательный вход под одной учётной записью), подтверждающие корректность отображаемых даты и времени.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G74" s="151" t="inlineStr">
+        <is>
+          <t>1. Функция реализована не во всех АС, к которым субъекты осуществляют логический доступ;
+2. Отображаемые дата и время предыдущей авторизации не соответствуют фактическим (ошибка логики учёта);
+3. Уведомление отображается слишком кратковременно или в неприметном месте интерфейса, из-за чего пользователи его не замечают;
+4. Пользователи не проинформированы о значении данного уведомления и о необходимых действиях в случае обнаружения несоответствия.</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6088,9 +6461,48 @@
 Главная цель меры — минимизировать риски несанкционированных действий и атак на этапе, когда личность пользователя ещё не подтверждена. Это предотвращает возможность получения доступа к защищённым ресурсам, выполнения операций или сбора информации о системе до прохождения аутентификации.</t>
         </is>
       </c>
-      <c r="E75" s="31" t="n"/>
-      <c r="F75" s="31" t="n"/>
-      <c r="G75" s="31" t="n"/>
+      <c r="E75" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера выполняется силами технических средств защиты информации, а именно:
+1. Настройку АС таким образом, чтобы до прохождения идентификации и аутентификации субъекту были доступны исключительно минимально необходимые функции (например, отображение формы входа, общая информация об организации без раскрытия структуры системы);
+2. Технический запрет на получение до аутентификации какой-либо информации о внутренней архитектуре АС, версиях используемого ПО, структуре базы данных и иных технических деталях, которые могут быть использованы для подготовки атаки;
+3. Настройку обработки ошибок таким образом, чтобы сообщения об ошибках на этапе входа не раскрывали избыточные технические подробности (например, обобщённое сообщение «неверный логин или пароль» вместо детализации, какая именно часть учётных данных неверна).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F75" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с разработчиками и администраторами АС;
+2. Результаты тестирования (попытка получить доступ к функциям или информации АС до прохождения аутентификации), подтверждающие ограничение состава доступных действий;
+3. Скриншоты сообщений об ошибках на этапе входа, подтверждающие отсутствие избыточной технической детализации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G75" s="151" t="inlineStr">
+        <is>
+          <t>1. До прохождения аутентификации пользователю доступны отдельные функции АС сверх необходимого минимума (например, часть справочной информации, раскрывающей структуру системы);
+2. Сообщения об ошибках на этапе входа раскрывают избыточные технические подробности (версии ПО, структуру базы данных, стек трассировки);
+3. Тестирование состава действий, доступных до аутентификации, не проводится на регулярной основе.</t>
+        </is>
+      </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6113,10 +6525,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D76" s="21" t="n"/>
-      <c r="E76" s="53" t="n"/>
-      <c r="F76" s="53" t="n"/>
-      <c r="G76" s="53" t="n"/>
+      <c r="D76" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует такого физического размещения устройств вывода (отображения) информации — мониторов, экранов, панелей — при котором исключается возможность несанкционированного просмотра отображаемой на них защищаемой информации посторонними лицами (так называемый visual hacking, shoulder surfing).
+Главная цель меры — исключить утечку защищаемой информации через простое визуальное наблюдение за экраном, поскольку такой канал утечки не требует от нарушителя никаких технических средств или специальных знаний — достаточно оказаться в поле зрения экрана.</t>
+        </is>
+      </c>
+      <c r="E76" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационно это выражается в следующем:
+1. Определение требований к размещению устройств вывода информации, исключающих просмотр экрана с мест, доступных посторонним лицам (например, разворот мониторов от окон, дверных проёмов, зон обслуживания клиентов);
+2. Учёт данных требований при планировке рабочих мест, на которых обрабатывается защищаемая информация, а также при организации рабочих мест эксплуатационного персонала;
+3. Применение дополнительных организационных мер там, где оптимальное размещение технически невозможно (например, временное затемнение, использование перегородок);
+4. Периодический контроль соблюдения установленных требований к размещению устройств вывода информации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F76" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний документ, определяющий требования к размещению устройств вывода информации;
+2. Результаты выборочного визуального осмотра рабочих мест на предмет соблюдения установленных требований;
+3. Акты (отчёты) периодического контроля соблюдения требований к размещению устройств вывода информации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G76" s="157" t="inlineStr">
+        <is>
+          <t>1. Требования к размещению устройств вывода информации не формализованы документально;
+2. Мониторы отдельных рабочих мест обращены в сторону зон, доступных клиентам или посторонним лицам (зоны обслуживания, коридоры, окна первого этажа);
+3. Периодический контроль соблюдения требований не проводится;
+4. Требования не учитываются при организации новых рабочих мест или при перепланировке помещений.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
@@ -6147,17 +6605,62 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D78" s="44" t="inlineStr">
+      <c r="D78" s="153" t="inlineStr">
         <is>
           <t>Суть меры заключается в обязательной фиксации в журналах событий всех случаев, когда субъект логического доступа (пользователь, эксплуатационный персонал или программный сервис) совершает ряд неуспешных последовательных попыток аутентификации.
 Главная цель меры — создание доказательной базы для:
-- cсвоевременного выявления атак на подбор паролей и иных попыток несанкционированного доступа;
+- своевременного выявления атак на подбор паролей и иных попыток несанкционированного доступа;
 - расследования инцидентов безопасности, связанных с компрометацией учётных записей.</t>
         </is>
       </c>
-      <c r="E78" s="31" t="n"/>
-      <c r="F78" s="31" t="n"/>
-      <c r="G78" s="31" t="n"/>
+      <c r="E78" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как речь идёт о чисто технической мере, реализация включает:
+1. Настройку операционных систем, каталогов (Active Directory, LDAP) и прикладных информационных систем на регистрацию событий каждой неуспешной попытки аутентификации субъекта;
+2. Настройку правил (например, в SIEM-системе) для выявления последовательных неуспешных попыток аутентификации, указывающих на возможную атаку подбора пароля;
+3. Обеспечение достаточного срока хранения журналов регистрации таких событий для последующего анализа и расследования инцидентов.
+Класс используемых средств — системы управления событиями информационной безопасности (SIEM), встроенные средства аудита операционных систем и служб каталогов.
+Иностранные: Splunk, Microsoft Active Directory (Audit Logon Events) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, RuSIEM и др.
+Открытый код: Wazuh, ELK Stack (Elasticsearch, Logstash, Kibana) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F78" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем и подразделением информационной безопасности;
+2. Скриншоты настроек, подтверждающие регистрацию неуспешных попыток аутентификации;
+3. Выгрузка журналов событий с зафиксированными неуспешными попытками аутентификации за проверяемый период;
+4. Правила корреляции SIEM-системы (при наличии), настроенные на выявление последовательных неуспешных попыток аутентификации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G78" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация неуспешных попыток аутентификации включена не для всех информационных систем;
+2. События неуспешных попыток аутентификации собираются, но не анализируются на предмет выявления атак подбора пароля;
+3. Журналы событий хранятся менее срока, необходимого для расследования инцидентов;
+4. Отсутствуют настроенные оповещения о превышении порогового числа неуспешных попыток аутентификации в единицу времени.</t>
+        </is>
+      </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6180,18 +6683,62 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D79" s="56" t="inlineStr">
-        <is>
-          <t>Мера требует фиксирования в журналах регистрации событий всех фактов идентификации и аутентификации (логина и пароля) при входе в ресурс доступа (СУБД, АС и т.п.) пользователями логического доступа, что снижает возможность фильтрации нелегитимных действий в нерабочее время. 
+      <c r="D79" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует фиксирования в журналах регистрации событий всех фактов идентификации и аутентификации (логина и пароля) при входе субъектов логического доступа в ресурс доступа (СУБД, АС и т. п.), что позволяет впоследствии выявлять факты входа в систему в нехарактерное для субъекта время (например, в нерабочие часы).
 Главная цель меры — создание доказательной базы для:
 - подтверждения факта входа конкретного субъекта в систему в определённое время;
 - расследования инцидентов безопасности;
 - обеспечения прозрачности и подотчётности всех действий субъектов логического доступа.</t>
         </is>
       </c>
-      <c r="E79" s="31" t="n"/>
-      <c r="F79" s="31" t="n"/>
-      <c r="G79" s="31" t="n"/>
+      <c r="E79" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера не имеет организационной составляющей — её выполнение обеспечивается техническими средствами:
+1. Настройку встроенных механизмов аудита операционных систем, СУБД, АС и служб каталогов на регистрацию каждого факта успешной идентификации и аутентификации субъекта;
+2. Фиксацию в журнале как минимум даты и времени события, идентификатора субъекта и результата (успешно/неуспешно);
+3. Централизованный сбор данных журналов идентификации и аутентификации из различных источников для последующего анализа.
+Класс используемых средств — системы управления событиями информационной безопасности (SIEM), встроенные средства аудита операционных систем, СУБД и служб каталогов.
+Иностранные: Splunk, Microsoft Active Directory (Audit Logon Events) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, RuSIEM и др.
+Открытый код: Wazuh, ELK Stack и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F79" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты настроек аудита, подтверждающие регистрацию фактов идентификации и аутентификации;
+3. Выгрузка журналов событий идентификации и аутентификации за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G79" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация фактов идентификации и аутентификации включена не для всех информационных систем;
+2. Журналы не содержат достаточного набора атрибутов (например, отсутствует точное время события);
+3. Журналы событий разных систем не собираются централизованно, что затрудняет их анализ;
+4. Журналы хранятся менее установленного срока, что не позволяет предоставить свидетельства за требуемый период.</t>
+        </is>
+      </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6214,15 +6761,59 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D80" s="56" t="inlineStr">
-        <is>
-          <t>Мера требует фиксирования в журналах регистрации событий всех событий, связанных с предоставлением доступа (авторизацией), с завершением или принудительным прерыванием сеанса работы пользователей и эксплуатационного персонала в ресурс доступа (СУБД, АС и т.п.), что снижает риск создания полной цепочки событий в рамках сессии логического доступа нелегитимным пользователем.
+      <c r="D80" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует фиксирования в журналах регистрации событий всех событий, связанных с предоставлением доступа (авторизацией), с завершением или принудительным прерыванием сеанса работы пользователей и эксплуатационного персонала в ресурсе доступа (СУБД, АС и т. п.), что позволяет восстановить полную и непрерывную цепочку событий в рамках каждой сессии логического доступа.
 Главная цель меры — создание полной и непрерывной доказательной базы всех этапов сессии логического доступа: от предоставления прав (авторизация) до её завершения или прерывания.</t>
         </is>
       </c>
-      <c r="E80" s="31" t="n"/>
-      <c r="F80" s="31" t="n"/>
-      <c r="G80" s="31" t="n"/>
+      <c r="E80" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит организационно необременительный, полностью технический характер:
+1. Настройку АС и иных ресурсов доступа на регистрацию события авторизации сессии (момента предоставления доступа после успешной идентификации и аутентификации);
+2. Настройку регистрации события завершения сессии — как штатного (выход пользователя), так и принудительного или автоматического прерывания (в том числе в рамках мер РД.13—РД.14);
+3. Обеспечение возможности сопоставления событий начала и завершения сессии по единому идентификатору (идентификатору сессии), позволяющего восстановить полную хронологию сессии.
+Класс используемых средств — системы управления событиями информационной безопасности (SIEM), встроенные средства аудита АС и служб каталогов.
+Иностранные: Splunk, Microsoft Active Directory (Audit Logon/Logoff Events) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, RuSIEM и др.
+Открытый код: Wazuh, ELK Stack и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F80" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами АС;
+2. Скриншоты настроек, подтверждающие регистрацию событий авторизации, завершения и прерывания сессии;
+3. Выгрузка журналов событий, подтверждающая возможность сопоставления начала и завершения одной и той же сессии.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G80" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация событий завершения (прерывания) сессии реализована не для всех АС, где регистрируется её начало;
+2. События начала и завершения сессии невозможно сопоставить между собой (отсутствует единый идентификатор сессии);
+3. Принудительное или аварийное прерывание сессии (например, при сбое) не регистрируется;
+4. Журналы событий сессий разных систем не собираются централизованно.</t>
+        </is>
+      </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6251,9 +6842,53 @@
 Главная цель меры — обеспечить прозрачность и подотчётность всех автоматизированных процессов, которые взаимодействуют с информационными системами. Это критически важно, так как программные сервисы, как правило, обладают высокими привилегиями и их деятельность часто остаётся вне поля зрения администраторов.</t>
         </is>
       </c>
-      <c r="E81" s="31" t="n"/>
-      <c r="F81" s="31" t="n"/>
-      <c r="G81" s="31" t="n"/>
+      <c r="E81" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как организационных мер здесь не предусмотрено, всё сводится к техническим настройкам:
+1. Настройку регистрации события запуска каждого программного сервиса (службы, приложения, скрипта автоматизации), осуществляющего логический доступ к информационным ресурсам от имени технической учётной записи;
+2. Фиксацию в журнале как минимум даты и времени запуска, идентификатора сервиса и технической учётной записи, от имени которой он запущен;
+3. Централизованный сбор данных о запуске программных сервисов для последующего анализа на предмет выявления несанкционированного или аномального запуска.
+Класс используемых средств — системы управления событиями информационной безопасности (SIEM), средства мониторинга процессов и служб операционных систем.
+Иностранные: Splunk, Microsoft Sysmon (мониторинг запуска процессов) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, RuSIEM и др.
+Открытый код: Wazuh, osquery и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F81" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты настроек, подтверждающие регистрацию событий запуска программных сервисов;
+3. Выгрузка журналов событий запуска программных сервисов за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G81" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация запуска программных сервисов включена не для всех технических учётных записей;
+2. Журналы запуска сервисов не анализируются на предмет выявления аномального (незапланированного) запуска;
+3. Запуск сервисов с непредусмотренными правами (эскалация привилегий при старте) не выявляется;
+4. Журналы запуска программных сервисов хранятся менее установленного срока.</t>
+        </is>
+      </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6276,18 +6911,62 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D82" s="56" t="inlineStr">
+      <c r="D82" s="158" t="inlineStr">
         <is>
           <t>Суть меры заключается в обязательной фиксации в журналах событий всех случаев изменения аутентификационных данных, используемых субъектами логического доступа для входа в информационные системы.
 Главная цель меры — создание полной и непрерывной доказательной базы всех изменений аутентификационных данных для:
-- расследования инцидентов безопасности, связанных с компрометацией учётных записей.
-- выявления аномалий (например, массовая смена паролей, смена пароля администратором без ведома пользователя).
+- расследования инцидентов безопасности, связанных с компрометацией учётных записей;
+- выявления аномалий (например, массовая смена паролей, смена пароля администратором без ведома пользователя);
 - подтверждения факта выполнения регламентных процедур смены аутентификационных данных.</t>
         </is>
       </c>
-      <c r="E82" s="31" t="n"/>
-      <c r="F82" s="31" t="n"/>
-      <c r="G82" s="31" t="n"/>
+      <c r="E82" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно техническими средствами:
+1. Настройку операционных систем, каталогов, СУБД и прикладных информационных систем на регистрацию каждого факта изменения аутентификационных данных субъекта (смены пароля, перевыпуска сертификата, привязки/отвязки фактора МФА);
+2. Фиксацию в журнале как минимум даты и времени изменения, идентификатора субъекта, инициатора изменения (сам субъект или администратор) и результата операции;
+3. Централизованный сбор данных об изменениях аутентификационных данных для последующего анализа на предмет аномалий.
+Класс используемых средств — системы управления событиями информационной безопасности (SIEM), службы каталогов и системы управления учётными записями (IdM) со встроенным аудитом.
+Иностранные: Splunk, Microsoft Active Directory (Audit Credential Validation) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, Avanpost IDM и др.
+Открытый код: Wazuh, ELK Stack и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F82" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами информационных систем;
+2. Скриншоты настроек, подтверждающие регистрацию событий изменения аутентификационных данных;
+3. Выгрузка журналов событий изменения аутентификационных данных за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G82" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация изменений аутентификационных данных включена не для всех информационных систем;
+2. Журналы не позволяют определить, кто инициировал изменение — сам субъект или администратор от его имени;
+3. Массовые (аномальные) изменения аутентификационных данных не выявляются автоматически;
+4. Журналы событий изменения аутентификационных данных хранятся менее установленного срока.</t>
+        </is>
+      </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -6310,10 +6989,53 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D83" s="21" t="n"/>
-      <c r="E83" s="31" t="n"/>
-      <c r="F83" s="31" t="n"/>
-      <c r="G83" s="31" t="n"/>
+      <c r="D83" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации (документальной фиксации) действий, которые субъект логического доступа и вовлечённые сотрудники обязаны выполнить в случае компрометации его аутентификационных данных, — то есть действий, предусмотренных мерой РД.29 (сообщение о компрометации, внеплановая смена аутентификационных данных, иные реагирующие мероприятия).
+Главная цель меры — обеспечить документальное подтверждение того, что при каждом зафиксированном случае компрометации аутентификационных данных предусмотренные действия были выполнены фактически, а не только формально предписаны регламентом (мера РД.29).</t>
+        </is>
+      </c>
+      <c r="E83" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Фиксацию в журнале (реестре) инцидентов, связанных с компрометацией аутентификационных данных (см. также меру РД.29), не только факта самой компрометации, но и перечня конкретных действий, выполненных субъектом и вовлечёнными сотрудниками в связи с этим случаем;
+2. Указание в такой записи даты и времени выполнения каждого действия (сообщение о компрометации, смена аутентификационных данных, иные реагирующие мероприятия) и ответственного за его выполнение;
+3. Периодический контроль подразделением информационной безопасности полноты и своевременности регистрации предусмотренных действий по зафиксированным случаям компрометации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F83" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Журнал (реестр) инцидентов, связанных с компрометацией аутентификационных данных, содержащий записи о выполненных действиях;
+2. Акты (отчёты) периодического контроля полноты и своевременности регистрации таких действий.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G83" s="151" t="inlineStr">
+        <is>
+          <t>1. В журнале инцидентов фиксируется только факт компрометации, но не перечень выполненных в связи с этим действий;
+2. Действия, предусмотренные на случай компрометации, регистрируются несвоевременно (со значительной задержкой относительно их фактического выполнения);
+3. Периодический контроль полноты и своевременности регистрации таких действий не проводится.</t>
+        </is>
+      </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -24124,8 +24846,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -800,6 +800,9 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -7071,16 +7074,55 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D85" s="44" t="inlineStr">
-        <is>
-          <t>Суть в меры заключается в наличии разработанных, утверждённых и введённых в действие внутренних нормативных документов, которые чётко определяют: кому, на каких условиях и в каком порядке предоставляется физический доступ в помещения и к объектам информатизации, что снижает риск неконтролируемого порядка допуска лиц к оборудованию, серверам, системам хранения данных и другим объектам физического доступа.</t>
-        </is>
-      </c>
-      <c r="E85" s="31" t="n"/>
-      <c r="F85" s="31" t="n"/>
-      <c r="G85" s="46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Отсутствует документ регламентирующий правила предоставления физического доступа.    </t>
+      <c r="D85" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует наличия разработанных, утверждённых и введённых в действие внутренних нормативных документов, которые чётко определяют: кому, на каких условиях и в каком порядке предоставляется физический доступ в помещения и к объектам информатизации финансовой организации.
+Главная цель меры — обеспечить, чтобы решения о допуске лиц к оборудованию, серверам, системам хранения данных и другим объектам физического доступа принимались по единым, заранее определённым правилам, а не бессистемно, что исключает неконтролируемое расширение круга лиц, имеющих физический доступ к критичным объектам.</t>
+        </is>
+      </c>
+      <c r="E85" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только организационными методами, её внедрение предполагает разработку и утверждение внутреннего нормативного документа (положения, регламента), в котором закрепляются:
+1. Категории помещений и объектов доступа, физический доступ к которым подлежит регламентации;
+2. Порядок и основания предоставления, изменения и прекращения права физического доступа (самостоятельного и в сопровождении);
+3. Роли и ответственность участников процесса (распорядитель физического доступа, служба безопасности, подразделение, эксплуатирующее СКУД);
+4. Требования к учёту и контролю предоставленных прав физического доступа.
+Утверждённый документ доводится до сведения ответственных сотрудников под подпись (лист ознакомления).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F85" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Утверждённый внутренний нормативный документ, определяющий правила предоставления физического доступа;
+2. Лист ознакомления ответственных сотрудников с указанным документом;
+3. Итоги интервью с сотрудниками, ответственными за предоставление физического доступа, подтверждающие знание и применение установленных правил.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G85" s="154" t="inlineStr">
+        <is>
+          <t>1. Документ, регламентирующий правила предоставления физического доступа, отсутствует или не утверждён;
+2. Документ не охватывает все категории помещений и объектов доступа (например, не распространяется на серверные удалённых подразделений);
+3. Документ не пересматривался длительное время и не отражает фактически применяемый порядок;
+4. Ответственные сотрудники не ознакомлены с документом либо ознакомлены формально.</t>
         </is>
       </c>
     </row>
@@ -7100,13 +7142,79 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D86" s="56" t="inlineStr">
-        <is>
-          <t>Суть в меры заключается в разработать, утвердить и ввести перечень лиц, которым предоставлено право самостоятельного физического доступа в помещения (серверные, технические помещения, архивы и т. п.), и вести контроль за этим перечнем. Это означает его регулярную проверку на предмет соответствия текущим кадровым изменениям (приёмы, увольнения, переводы).</t>
-        </is>
-      </c>
-      <c r="E86" s="31" t="n"/>
-      <c r="F86" s="31" t="n"/>
+      <c r="D86" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует разработки, утверждения и ведения перечня лиц, которым предоставлено право самостоятельного физического доступа в помещения (серверные, технические помещения, архивы и т. п.), а также регулярного контроля этого перечня — проверки его соответствия текущим кадровым изменениям (приёмам на работу, увольнениям, переводам).
+Главная цель меры — не допустить расхождения между документально закреплённым и фактическим составом лиц, имеющих самостоятельный физический доступ, поскольку без регулярного контроля перечень со временем перестаёт отражать реальное положение дел и начинает включать лиц, уже утративших основания для такого доступа.</t>
+        </is>
+      </c>
+      <c r="E86" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Ведение перечня лиц, которым предоставлено право самостоятельного физического доступа в помещения, с указанием помещений (зон), к которым предоставлен доступ;
+2. Проведение периодических сверок перечня с кадровыми данными (приёмы, увольнения, переводы) с определённой во внутреннем документе периодичностью;
+3. Оформление результатов сверки актом с фиксацией выявленных расхождений и принятых мер по их устранению.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически данный контроль дополняется:
+1. Использованием системы контроля и управления доступом (СКУД) для автоматизированного ведения перечня лиц с активными правами физического доступа и автоматического формирования отчёта о расхождениях с кадровой системой;
+2. Автоматическим блокированием пропуска (карты доступа) при поступлении в СКУД сведений об увольнении или переводе сотрудника (при наличии интеграции с кадровой системой).
+Класс используемых средств — системы контроля и управления доступом (СКУД).
+Иностранные: HID Global, Honeywell Access Control и пр.
+Российские сертифицированные (ФСТЭК): «Болид» (Orion), PERCo и др.
+Открытый код: специализированных открытых решений класса СКУД, как правило, не применяется; функция реализуется коммерческими или собственными аппаратно-программными комплексами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F86" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень лиц, которым предоставлено право самостоятельного физического доступа в помещения;
+2. Акты (отчёты) периодической сверки перечня с кадровыми данными;
+3. Свидетельства устранения выявленных расхождений (заявки на блокирование доступа уволенных/переведённых сотрудников).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Настройки СКУД, подтверждающие ведение перечня лиц с активными правами доступа;
+2. Автоматически сформированные отчёты СКУД о расхождениях с кадровыми данными;
+3. Журналы блокирования пропусков уволенных или переведённых сотрудников.</t>
+          </r>
+        </is>
+      </c>
       <c r="G86" s="57" t="inlineStr">
         <is>
           <t>1. Отсутствует утверждённый перечень лиц, имеющих право самостоятельного физического доступа в помещения, либо его актуальная версия не поддерживается;
@@ -7138,14 +7246,80 @@
 Главная цель меры — обеспечить контролируемый доступ для всех категорий посетителей, не являющихся работниками организации, с целью предотвращения несанкционированного проникновения и обеспечения безопасности объектов информационной инфраструктуры. Мера направлена на то, чтобы доступ таких лиц был строго регламентирован, а их перемещение по помещениям — контролируемым.</t>
         </is>
       </c>
-      <c r="E87" s="31" t="n"/>
-      <c r="F87" s="31" t="n"/>
-      <c r="G87" s="46" t="inlineStr">
+      <c r="E87" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Определение во внутреннем нормативном документе порядка допуска лиц, не являющихся работниками организации (представителей контролирующих органов, аудиторов, курьеров, сотрудников подрядных и клининговых организаций), к самостоятельному физическому доступу в помещения;
+2. Ведение журнала учёта таких лиц с фиксацией даты, времени, цели визита и лица, санкционировавшего доступ;
+3. Установление ограниченного срока действия временного пропуска, выдаваемого таким лицам, и порядка его возврата (аннулирования) по окончании визита или работ.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль реализуется так:
+1. Оформление временных пропусков (карт доступа) в СКУД с ограничением зон доступа и сроком действия, соответствующим цели визита;
+2. Автоматическое аннулирование (блокирование) временного пропуска в СКУД по истечении установленного срока действия без необходимости ручного отзыва;
+3. Регистрация в СКУД всех фактов прохода лиц, не являющихся работниками организации, с возможностью формирования отчёта за выбранный период.
+Класс используемых средств — системы контроля и управления доступом (СКУД) с поддержкой временных (ограниченных по сроку) пропусков.
+Иностранные: HID Global, Honeywell Access Control и пр.
+Российские сертифицированные (ФСТЭК): «Болид» (Orion), PERCo и др.
+Открытый код: специализированных открытых решений класса СКУД, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F87" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний документ, регламентирующий порядок допуска лиц, не являющихся работниками организации;
+2. Журнал учёта посетителей (либо выгрузка из СКУД) с записями о визитах таких лиц;
+3. Образцы (реестр) выданных временных пропусков.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Настройки СКУД, подтверждающие ограничение зон и срока действия временных пропусков;
+2. Журналы (выгрузки) СКУД, подтверждающие автоматическое аннулирование пропусков по истечении срока действия;
+3. Отчёты СКУД о фактах прохода лиц, не являющихся работниками организации, за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G87" s="154" t="inlineStr">
         <is>
           <t>1. Отсутствует регламентация порядка контроля самостоятельного физического доступа для лиц, не являющихся работниками финансовой организации, во внутренних нормативных документах;
-2. Не ведётся учёт и регистрация входа/выхода лиц, не являющихся работниками (отсутствует Журнал учёта посетителей или выгрузка из СКУД);
+2. Не ведётся учёт и регистрация входа/выхода лиц, не являющихся работниками (отсутствует журнал учёта посетителей или выгрузка из СКУД);
 3. Не используется система контроля и управления доступом (СКУД) или иная техническая система для автоматизированного контроля доступа посторонних лиц (для 1-УЗ);
-4) Временные пропуска не имеют ограниченного срока действия или не блокируются после завершения визита.</t>
+4. Временные пропуска не имеют ограниченного срока действия или не блокируются после завершения визита.</t>
         </is>
       </c>
     </row>
@@ -7171,14 +7345,80 @@
 Главная цель меры — обеспечить контролируемый доступ для технического (вспомогательного) персонала, который, в отличие от штатных сотрудников, не является работником организации, но регулярно посещает её помещения для выполнения своих обязанностей. Это позволяет предотвратить бесконтрольное перемещение таких лиц и обеспечить безопасность объектов информационной инфраструктуры.</t>
         </is>
       </c>
-      <c r="E88" s="31" t="n"/>
-      <c r="F88" s="31" t="n"/>
-      <c r="G88" s="46" t="inlineStr">
+      <c r="E88" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Определение во внутреннем нормативном документе порядка допуска технического (вспомогательного) персонала (обслуживающего инженерные системы, кондиционирование, электропитание и т. п.) к самостоятельному физическому доступу в помещения;
+2. Ведение учёта выдачи и возврата ключей или карт доступа техническому персоналу;
+3. Периодический пересмотр состава помещений и зон, доступных техническому персоналу, на предмет соответствия фактически выполняемым работам.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически данный контроль реализуется так:
+1. Оформление доступа технического персонала в СКУД с ограничением по конкретным зонам и, при необходимости, по времени суток (например, только в часы проведения регламентных работ);
+2. Автоматическое исключение прав доступа технического персонала в СКУД по завершении договора (работ) без необходимости ручного отзыва;
+3. Регистрация в СКУД всех фактов прохода технического персонала с возможностью формирования отчёта за выбранный период.
+Класс используемых средств — системы контроля и управления доступом (СКУД).
+Иностранные: HID Global, Honeywell Access Control и пр.
+Российские сертифицированные (ФСТЭК): «Болид» (Orion), PERCo и др.
+Открытый код: специализированных открытых решений класса СКУД, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F88" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний документ, регламентирующий порядок допуска технического (вспомогательного) персонала;
+2. Журнал учёта выдачи и возврата ключей или карт доступа техническому персоналу;
+3. Акты пересмотра состава зон, доступных техническому персоналу.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Настройки СКУД, подтверждающие ограничение зон и (при необходимости) времени доступа технического персонала;
+2. Журналы (выгрузки) СКУД, подтверждающие исключение прав доступа технического персонала по завершении работ;
+3. Отчёты СКУД о фактах прохода технического персонала за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G88" s="154" t="inlineStr">
         <is>
           <t>1. Отсутствует регламентация порядка контроля самостоятельного физического доступа для технического (вспомогательного) персонала во внутренних нормативных документах;
-2. Не ведётся учёт выдачи и возврата ключей или карт-доступа техническому персоналу (отсутствует Журнал учёта или выгрузка из СКУД);
+2. Не ведётся учёт выдачи и возврата ключей или карт-доступа техническому персоналу (отсутствует журнал учёта или выгрузка из СКУД);
 3. Не используется система контроля и управления доступом (СКУД) или иная техническая система для автоматизированного контроля доступа технического персонала (для 1-УЗ);
-4) Права доступа технического персонала в СКУД не ограничены по времени и зонам (например, не удаляются после завершения работ).</t>
+4. Права доступа технического персонала в СКУД не ограничены по времени и зонам (например, не удаляются после завершения работ).</t>
         </is>
       </c>
     </row>
@@ -7198,13 +7438,48 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D89" s="34" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в запрете на самостоятельный проход в помещения для лиц, не имеющих на это права. Их физический доступ разрешён исключительно под контролем уполномоченного сотрудника финансовой организации. Это предотвращает потенциальные инциденты, связанные с несанкционированным доступом к объектам информационной инфраструктуры.</t>
-        </is>
-      </c>
-      <c r="E89" s="31" t="n"/>
-      <c r="F89" s="31" t="n"/>
+      <c r="D89" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает самостоятельный (без сопровождения) проход в помещения лицам, которым такое право не предоставлено; их физический доступ допускается исключительно под контролем работника финансовой организации, обладающего правом самостоятельного доступа.
+Главная цель меры — исключить бесконтрольное перемещение по защищаемым помещениям лиц, не имеющих на это самостоятельного права, поскольку сопровождение уполномоченным сотрудником обеспечивает постоянный контроль за действиями такого лица в течение всего времени его нахождения в помещении.</t>
+        </is>
+      </c>
+      <c r="E89" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе прямого запрета на самостоятельный проход лиц, не имеющих на это права, и требования обязательного сопровождения таких лиц уполномоченным сотрудником;
+2. Определение обязанностей сопровождающего сотрудника (постоянное нахождение рядом с сопровождаемым лицом, недопущение его самостоятельных перемещений по помещению);
+3. Информирование (инструктаж) сотрудников, имеющих право самостоятельного доступа, об их обязанностях при сопровождении посторонних лиц;
+4. Периодический контроль соблюдения процедуры сопровождения (выборочные проверки, анализ инцидентов).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F89" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий требование обязательного сопровождения лиц, не имеющих права самостоятельного доступа;
+2. Материалы инструктажа сотрудников по порядку сопровождения посторонних лиц;
+3. Акты (результаты) выборочных проверок соблюдения процедуры сопровождения.</t>
+          </r>
+        </is>
+      </c>
       <c r="G89" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Отсутствует документ регламентирующий правила предоставления физического доступа;
@@ -7236,12 +7511,48 @@
 Главная цель меры — закрепить персональную ответственность за принятие решений о допуске лиц в контролируемые помещения.</t>
         </is>
       </c>
-      <c r="E90" s="31" t="n"/>
-      <c r="F90" s="31" t="n"/>
-      <c r="G90" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Отсутствует документы подтверждающие назначение роли распорядителя физического доступа;
-2. Назначение роли распорядителя физического доступа реализовано не для всех помещений организации. </t>
+      <c r="E90" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная составляющая сводится к следующим шагам:
+1. Составить и поддерживать в актуальном состоянии перечень помещений организации, в которых расположены объекты доступа;
+2. Для каждого помещения определить и документально закрепить (приказом, распоряжением) распорядителя физического доступа из числа руководителей подразделений, в чьей зоне ответственности находится помещение;
+3. Довести до распорядителей физического доступа их обязанности и ответственность за принятие решений о допуске лиц в закреплённое помещение;
+4. Актуализировать назначения распорядителей при вводе новых помещений в эксплуатацию, реорганизации подразделений или кадровых изменениях.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F90" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень помещений организации с указанием закреплённых за ними распорядителей физического доступа;
+2. Приказы (распоряжения) о назначении распорядителей физического доступа;
+3. Итоги интервью с назначенными распорядителями, подтверждающие их осведомлённость о своих обязанностях.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G90" s="159" t="inlineStr">
+        <is>
+          <t>1. Документы, подтверждающие назначение роли распорядителя физического доступа, отсутствуют для части помещений;
+2. Назначение роли распорядителя физического доступа реализовано не для всех помещений организации;
+3. Распорядитель назначен формально и фактически не принимает решений о допуске (решения принимает служба безопасности самостоятельно);
+4. Назначения распорядителей не актуализируются при вводе новых помещений или организационных изменениях.</t>
         </is>
       </c>
     </row>
@@ -7268,8 +7579,42 @@
 Главная цель меры — централизовать и упорядочить процесс выдачи прав доступа, исключив ситуации, когда такие права предоставляются бесконтрольно или неуполномоченными лицами. Это гарантирует, что право на самостоятельный вход в помещения получают только те сотрудники, которым это действительно необходимо для работы.</t>
         </is>
       </c>
-      <c r="E91" s="31" t="n"/>
-      <c r="F91" s="31" t="n"/>
+      <c r="E91" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Установление обязательного порядка, при котором предоставление права самостоятельного физического доступа в помещение инициируется заявкой и требует явного решения (согласования) распорядителя физического доступа, закреплённого за данным помещением;
+2. Определение формы и способа фиксации решения распорядителя (подпись на заявке, резолюция, согласование в системе электронного документооборота);
+3. Установление запрета на предоставление права физического доступа службой безопасности или иным исполнителем без документально зафиксированного решения распорядителя;
+4. Периодический контроль соблюдения установленного порядка согласования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F91" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент, устанавливающий обязательность согласования предоставления права физического доступа с распорядителем физического доступа;
+2. Заявки на предоставление физического доступа с зафиксированным решением (согласованием) распорядителя за выборочный период;
+3. Итоги интервью со службой безопасности и распорядителями физического доступа, подтверждающие соблюдение установленного порядка.</t>
+          </r>
+        </is>
+      </c>
       <c r="G91" s="58" t="inlineStr">
         <is>
           <t>1. Право доступа предоставляется, но не определено лицо, ответственное за принятие таких решений;
@@ -7295,13 +7640,47 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D92" s="34" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в оборудовании входных дверей помещений механическими замками, которые обеспечивают их надежное закрытие в нерабочее время. Это базовое, но критически важное требование для предотвращения несанкционированного доступа в помещения, где обрабатывается или хранится защищаемая информация, а также размещены объекты информационной инфраструктуры.</t>
-        </is>
-      </c>
-      <c r="E92" s="53" t="n"/>
-      <c r="F92" s="53" t="n"/>
+      <c r="D92" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает базовое требование к физической защите помещений: входные двери должны быть оборудованы механическими замками, обеспечивающими их надёжное закрытие в нерабочее время.
+Главная цель меры — создать базовый, не зависящий от электропитания и работоспособности электронных систем рубеж физической защиты помещений, где обрабатывается или хранится защищаемая информация либо размещены объекты информационной инфраструктуры, от несанкционированного проникновения в периоды, когда помещение не контролируется присутствующими в нём сотрудниками.</t>
+        </is>
+      </c>
+      <c r="E92" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационно это выражается в следующем:
+1. Оснащение входных дверей всех помещений, подпадающих под действие меры, механическими замками, соответствующими классу взломостойкости, обоснованному моделью угроз;
+2. Установление обязанности ответственных сотрудников закрывать помещение на замок по окончании рабочего дня (при уходе последнего сотрудника);
+3. Периодический контроль исправности замков и фактического соблюдения требования о закрытии помещений в нерабочее время.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F92" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний документ, устанавливающий требования к оснащению помещений механическими замками;
+2. Результаты выборочной проверки исправности замков на входных дверях помещений;
+3. Акты (результаты) контроля фактического закрытия помещений в нерабочее время (например, по итогам обхода в конце рабочего дня).</t>
+          </r>
+        </is>
+      </c>
       <c r="G92" s="46" t="inlineStr">
         <is>
           <t>1. Отсутствие замков на входных дверях или их неисправность;
@@ -7326,17 +7705,58 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D93" s="44" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в оснащении помещений финансовой организации средствами (системами) контроля и управления доступом (СКУД) для предотвращения несанкционированного физического проникновения в зоны, где обрабатывается или хранится защищаемая информация, а также размещены объекты информационной инфраструктуры.</t>
-        </is>
-      </c>
-      <c r="E93" s="31" t="n"/>
-      <c r="F93" s="31" t="n"/>
-      <c r="G93" s="46" t="inlineStr">
-        <is>
-          <t>1. Помещения, где обрабатывается защищаемая информация, не оборудованы средствами контроля доступа;
-2. СКУД установлена не на всех входах в контролируемые зоны.</t>
+      <c r="D93" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует оснащения помещений финансовой организации, в которых обрабатывается или хранится защищаемая информация либо размещены объекты информационной инфраструктуры, средствами (системами) контроля и управления доступом (СКУД).
+Главная цель меры — обеспечить автоматизированный, не зависящий от человеческого фактора контроль физического доступа в защищаемые помещения: СКУД позволяет достоверно ограничивать круг лиц, имеющих доступ, и одновременно формирует объективные данные о каждом факте прохода, необходимые для реализации иных мер (в том числе ФД.14, ФД.21).</t>
+        </is>
+      </c>
+      <c r="E93" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Установку на входах в защищаемые помещения технических средств идентификации (карт доступа, биометрических считывателей и т. п.), сопряжённых с контроллером СКУД;
+2. Настройку СКУД таким образом, чтобы проход был возможен только для лиц, обладающих правом самостоятельного физического доступа (см. меру ФД.2), с автоматическим отказом в проходе лицам, такого права не имеющим;
+3. Резервирование электропитания СКУД (источники бесперебойного питания) для сохранения работоспособности контроля доступа при отключении основного электроснабжения.
+Класс используемых средств — системы контроля и управления доступом (СКУД).
+Иностранные: HID Global, Honeywell Access Control и пр.
+Российские сертифицированные (ФСТЭК): «Болид» (Orion), PERCo и др.
+Открытый код: специализированных открытых решений класса СКУД, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F93" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами СКУД и службой безопасности;
+2. Схема размещения точек контроля СКУД на входах в защищаемые помещения;
+3. Результаты тестирования (попытка прохода лицом, не имеющим права доступа), подтверждающие срабатывание отказа в проходе;
+4. Сведения о резервировании электропитания СКУД.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G93" s="154" t="inlineStr">
+        <is>
+          <t>1. Часть помещений, где обрабатывается защищаемая информация, не оборудована средствами контроля доступа;
+2. СКУД установлена не на всех входах в контролируемые зоны (например, отсутствует на запасных или технических входах);
+3. При отключении электропитания СКУД переходит в состояние, допускающее свободный проход, без резервного питания;
+4. Настройки СКУД не пересматриваются при изменении состава лиц, имеющих право доступа в помещение.</t>
         </is>
       </c>
     </row>
@@ -7362,12 +7782,51 @@
 Главная цель меры — обеспечить визуальный контроль и документирование всех случаев доступа к критичным объектам информационной инфраструктуры.</t>
         </is>
       </c>
-      <c r="E94" s="53" t="n"/>
-      <c r="F94" s="53" t="n"/>
-      <c r="G94" s="46" t="inlineStr">
-        <is>
-          <t>1. Помещения с объектами доступа не оборудованы системами видеонаблюдения (камеры отсутствуют на входах или внутри критических зон (серверных и пр.);
-2. Система видеонаблюдения не обеспечивает качественную идентификацию лиц (низкое разрешение, недостаточная частота кадров, неправильно выбранные зоны обзора).</t>
+      <c r="E94" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера носит сугубо технический характер, её внедрение сводится к:
+1. Установке камер видеонаблюдения на входах в помещения, где расположены объекты доступа, и внутри критичных зон (серверных, технических помещений);
+2. Настройке параметров видеозаписи (разрешение, частота кадров, зоны обзора), обеспечивающих возможность идентификации лиц и совершаемых ими действий;
+3. Обеспечению непрерывной либо событийно-активируемой (по детектору движения) видеозаписи в зависимости от критичности контролируемой зоны.
+Класс используемых средств — системы видеонаблюдения (CCTV).
+Иностранные: Hikvision, Dahua и пр.
+Российские сертифицированные (ФСТЭК): «Форт», TRASSIR и др.
+Открытый код: ZoneMinder, Shinobi и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F94" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами системы видеонаблюдения и службой безопасности;
+2. Схема размещения камер видеонаблюдения относительно помещений с объектами доступа;
+3. Скриншоты (выгрузки) настроек видеозаписи, подтверждающие параметры, достаточные для идентификации лиц.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G94" s="154" t="inlineStr">
+        <is>
+          <t>1. Помещения с объектами доступа не оборудованы системами видеонаблюдения (камеры отсутствуют на входах или внутри критических зон, включая серверные);
+2. Система видеонаблюдения не обеспечивает качественную идентификацию лиц (низкое разрешение, недостаточная частота кадров, неправильно выбранные зоны обзора);
+3. Отдельные зоны обзора камер перекрыты посторонними объектами или засвечены;
+4. Работоспособность камер видеонаблюдения не проверяется на регулярной основе, часть камер фактически неисправна.</t>
         </is>
       </c>
     </row>
@@ -7393,12 +7852,51 @@
 Главная цель меры — обеспечить своевременное обнаружение и оповещение о попытках несанкционированного проникновения в помещения, а также о возникновении пожара, что позволяет оперативно принять меры по защите объектов информационной инфраструктуры и минимизировать возможный ущерб.</t>
         </is>
       </c>
-      <c r="E95" s="53" t="n"/>
-      <c r="F95" s="53" t="n"/>
-      <c r="G95" s="46" t="inlineStr">
-        <is>
-          <t>1. Помещения с объектами доступа не оборудованы средствами охранной и пожарной сигнализации (извещатели отсутствуют на входах или внутри критических зон);
-2. Система сигнализации не обеспечивает автоматическую передачу тревожных сообщений на пульт охраны или в систему мониторинга (например, сигнализация работает только в локальном режиме без оповещения).</t>
+      <c r="E95" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввиду того, что мера реализуется только технически, необходимо:
+1. Оснащение помещений финансовой организации, где расположены объекты доступа, средствами охранной сигнализации (датчиками движения, открытия дверей, разбития стекла) и средствами пожарной сигнализации (дымовыми, тепловыми извещателями);
+2. Настройку автоматической передачи тревожных сообщений на пульт централизованного наблюдения или в систему мониторинга, обеспечивающую оперативное реагирование;
+3. Обеспечение резервного электропитания систем сигнализации на случай отключения основного электроснабжения.
+Класс используемых средств — средства охранной и пожарной сигнализации.
+Иностранные: Bosch Security Systems, Honeywell Fire Systems и пр.
+Российские сертифицированные (ФСТЭК): «Болид» (Орион), «Рубеж» и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F95" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью со службой безопасности и администраторами систем сигнализации;
+2. Схема размещения извещателей охранной и пожарной сигнализации;
+3. Результаты тестирования (контрольное срабатывание датчика), подтверждающие передачу тревожного сообщения на пульт (в систему мониторинга).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G95" s="154" t="inlineStr">
+        <is>
+          <t>1. Помещения с объектами доступа не оборудованы средствами охранной и (или) пожарной сигнализации (извещатели отсутствуют на входах или внутри критических зон);
+2. Система сигнализации не обеспечивает автоматическую передачу тревожных сообщений на пульт охраны или в систему мониторинга (например, работает только в локальном режиме без оповещения);
+3. Резервное электропитание систем сигнализации отсутствует или неисправно;
+4. Работоспособность извещателей не проверяется на регулярной основе.</t>
         </is>
       </c>
     </row>
@@ -7424,8 +7922,41 @@
 Главная цель меры — ограничить физический доступ к критически важному оборудованию только уполномоченными лицами, предотвратив возможность несанкционированного подключения, модификации или вывода из строя серверного и сетевого оборудования.</t>
         </is>
       </c>
-      <c r="E96" s="31" t="n"/>
-      <c r="F96" s="31" t="n"/>
+      <c r="E96" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Определение требования об обязательном размещении серверного и сетевого оборудования в запираемых стоечных шкафах при проектировании и вводе в эксплуатацию серверных и технических помещений;
+2. Проведение инвентаризации существующего оборудования на предмет соответствия данному требованию с составлением плана устранения выявленных несоответствий;
+3. Контроль соблюдения требования при вводе в эксплуатацию нового оборудования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F96" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний документ (регламент), устанавливающий требование о размещении серверного и сетевого оборудования в запираемых стоечных шкафах;
+2. Результаты выборочного визуального осмотра серверных помещений, подтверждающие фактическое размещение оборудования в запираемых шкафах;
+3. Акты ввода оборудования в эксплуатацию с отметкой о его размещении в соответствии с установленным требованием.</t>
+          </r>
+        </is>
+      </c>
       <c r="G96" s="36" t="inlineStr">
         <is>
           <t>1. Оборудование размещено в открытых стойках или на столах;
@@ -7456,8 +7987,41 @@
 Главная цель меры — обеспечить, чтобы доступ к критически важному оборудованию (серверы, сетевое оборудование, системы хранения данных и т.д.) осуществлялся только уполномоченными лицами, а все случаи доступа регистрировались и контролировались.</t>
         </is>
       </c>
-      <c r="E97" s="31" t="n"/>
-      <c r="F97" s="31" t="n"/>
+      <c r="E97" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Определение перечня лиц, имеющих право доступа к запираемым серверным стоечным шкафам (ключи, коды доступа);
+2. Ведение учёта выдачи ключей (кодов доступа) к шкафам и фактов открытия шкафов;
+3. Периодический контроль соответствия фактического круга лиц, имеющих доступ к шкафам, установленному перечню.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F97" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень лиц, имеющих право доступа к запираемым серверным стоечным шкафам;
+2. Журнал учёта выдачи ключей (кодов доступа) и фактов открытия шкафов;
+3. Акты (результаты) периодического контроля соответствия фактического круга лиц установленному перечню.</t>
+          </r>
+        </is>
+      </c>
       <c r="G97" s="46" t="inlineStr">
         <is>
           <t>1. Доступ в серверную предоставляется без надлежащего учёта (не ведётся журнал, не используются ключи или карты доступа);
@@ -7482,16 +8046,58 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D98" s="44" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в обеспечении сохранности и доступности архивов событий, регистрируемых системами контроля и управления доступом (СКУД), в течение срока не менее трех лет. Архивы СКУД содержат записи о всех событиях, связанных с физическим доступом в помещения финансовой организации: входы и выходы сотрудников, посетителей, технического персонала, попытки несанкционированного доступа, а также действия администраторов СКУД.</t>
-        </is>
-      </c>
-      <c r="E98" s="53" t="n"/>
-      <c r="F98" s="53" t="n"/>
-      <c r="G98" s="46" t="inlineStr">
-        <is>
-          <t>1. В настройках СКУД установлен срок хранения менее 3 лет.</t>
+      <c r="D98" s="153" t="inlineStr">
+        <is>
+          <t>Мера устанавливает минимальный срок хранения архивов событий, регистрируемых системами контроля и управления доступом (СКУД), — не менее трёх лет. Архивы СКУД содержат записи обо всех событиях, связанных с физическим доступом в помещения финансовой организации: входы и выходы сотрудников, посетителей, технического персонала, попытки несанкционированного доступа, а также действия администраторов СКУД.
+Главная цель меры — обеспечить наличие исторических данных о физическом доступе на срок, достаточный для расследования инцидентов информационной безопасности, которые могут быть выявлены спустя продолжительное время после их совершения, а также для предоставления объективных свидетельств контроля физического доступа регулятору и внешним аудиторам.</t>
+        </is>
+      </c>
+      <c r="E98" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Настройку сервера (базы данных) СКУД на хранение архива событий физического доступа в течение срока не менее трёх лет;
+2. Обеспечение достаточной ёмкости системы хранения данных с учётом фактического объёма событий, генерируемых СКУД, и выбранного срока хранения;
+3. Организацию резервного копирования архива событий СКУД для защиты от утраты данных вследствие сбоя оборудования.
+Класс используемых средств — системы контроля и управления доступом (СКУД) и системы хранения данных для их архивов.
+Иностранные: HID Global, Honeywell Access Control и пр.
+Российские сертифицированные (ФСТЭК): «Болид» (Orion), PERCo и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F98" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами СКУД;
+2. Скриншоты (выгрузки) настроек срока хранения архива событий СКУД;
+3. Выгрузка архивных записей СКУД трёхлетней давности, подтверждающая фактическую доступность данных за установленный срок;
+4. Сведения о резервном копировании архива событий СКУД.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G98" s="154" t="inlineStr">
+        <is>
+          <t>1. В настройках СКУД установлен срок хранения архива менее 3 лет;
+2. Ёмкость системы хранения данных не рассчитана на фактический объём событий за 3 года, что приводит к досрочной перезаписи (потере) старых записей;
+3. Резервное копирование архива событий СКУД не выполняется, при сбое сервера архив может быть безвозвратно утрачен;
+4. Фактическая доступность архивных записей трёхлетней давности не проверяется (не тестируется возможность их выгрузки).</t>
         </is>
       </c>
       <c r="H98" s="59" t="n"/>
@@ -7512,18 +8118,57 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D99" s="44" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в обеспечении сохранности и доступности архивов видеозаписей систем видеонаблюдения в течение срока не менее 14 дней.
-Архивы видеонаблюдения содержат записи доступа к общедоступным объектам доступа — банкоматам, платёжным терминалам, общедоступным рабочим местам, зонам клиентского обслуживания.</t>
-        </is>
-      </c>
-      <c r="E99" s="53" t="n"/>
-      <c r="F99" s="53" t="n"/>
-      <c r="G99" s="46" t="inlineStr">
+      <c r="D99" s="153" t="inlineStr">
+        <is>
+          <t>Мера устанавливает минимальный срок хранения архивов видеозаписей систем видеонаблюдения — не менее 14 дней. Архивы видеонаблюдения содержат записи доступа к общедоступным объектам доступа — банкоматам, платёжным терминалам, общедоступным рабочим местам, зонам клиентского обслуживания.
+Главная цель меры — обеспечить наличие видеофиксации за период, достаточный для оперативного расследования инцидентов и обращений клиентов, связанных с использованием общедоступных объектов доступа, учитывая, что о таких инцидентах, как правило, становится известно вскоре после их совершения.</t>
+        </is>
+      </c>
+      <c r="E99" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Настройку видеорегистратора (сервера видеонаблюдения) на хранение архива видеозаписей в течение срока не менее 14 дней;
+2. Расчёт и обеспечение необходимой ёмкости дискового пространства с учётом количества камер, разрешения, частоты кадров и параметров сжатия;
+3. Организацию автоматической ротации (перезаписи) архива по достижении установленного срока хранения без ручного вмешательства.
+Класс используемых средств — системы видеонаблюдения (CCTV) с архивированием.
+Иностранные: Hikvision, Dahua и пр.
+Российские сертифицированные (ФСТЭК): «Форт», TRASSIR и др.
+Открытый код: ZoneMinder, Shinobi и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F99" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами системы видеонаблюдения;
+2. Скриншоты (выгрузки) настроек срока хранения архива видеозаписей;
+3. Выгрузка архивной видеозаписи 14-дневной давности, подтверждающая фактическую доступность данных за установленный срок.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G99" s="154" t="inlineStr">
         <is>
           <t>1. В настройках системы видеонаблюдения установлен срок хранения менее 14 дней;
-2. Дисковое пространство не позволяет хранить архивы в течение 14 дней (особенно при высоком разрешении и частоте кадров).</t>
+2. Дисковое пространство не позволяет фактически хранить архивы в течение 14 дней (особенно при высоком разрешении и частоте кадров), архив перезаписывается раньше установленного срока;
+3. Расчёт необходимой ёмкости дискового пространства не выполнялся или не актуализировался при изменении параметров видеозаписи;
+4. Фактическая доступность архивной записи 14-дневной давности не проверяется.</t>
         </is>
       </c>
     </row>
@@ -7543,17 +8188,57 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D100" s="44" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в обеспечении сохранности и доступности архивов видеозаписей систем видеонаблюдения, которые фиксируют доступ к общедоступным объектам (банкоматы, платёжные терминалы, зоны клиентского обслуживания), в течение срока не менее 14 дней.</t>
-        </is>
-      </c>
-      <c r="E100" s="53" t="n"/>
-      <c r="F100" s="53" t="n"/>
-      <c r="G100" s="46" t="inlineStr">
+      <c r="D100" s="153" t="inlineStr">
+        <is>
+          <t>Мера устанавливает минимальный срок хранения архивов видеозаписей систем видеонаблюдения, фиксирующих доступ к общедоступным объектам (банкоматам, платёжным терминалам, зонам клиентского обслуживания), — не менее 90 дней.
+Главная цель меры — обеспечить более длительный, по сравнению с мерой ФД.15, срок хранения видеоархива для тех уровней защиты, где это необходимо для расследования инцидентов и рассмотрения обращений клиентов, поступивших со значительной задержкой относительно момента совершения операции (например, при оспаривании клиентом транзакции).</t>
+        </is>
+      </c>
+      <c r="E100" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера подразумевает исключительно технические меры защиты, а именно:
+1. Настройку видеорегистратора (сервера видеонаблюдения) на хранение архива видеозаписей в течение срока не менее 90 дней;
+2. Расчёт и обеспечение необходимой ёмкости дискового пространства с учётом количества камер, разрешения, частоты кадров, параметров сжатия и увеличенного (по сравнению с ФД.15) срока хранения;
+3. Организацию автоматической ротации (перезаписи) архива по достижении установленного срока хранения.
+Класс используемых средств — системы видеонаблюдения (CCTV) с архивированием.
+Иностранные: Hikvision, Dahua и пр.
+Российские сертифицированные (ФСТЭК): «Форт», TRASSIR и др.
+Открытый код: ZoneMinder, Shinobi и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F100" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами системы видеонаблюдения;
+2. Скриншоты (выгрузки) настроек срока хранения архива видеозаписей;
+3. Выгрузка архивной видеозаписи 90-дневной давности, подтверждающая фактическую доступность данных за установленный срок.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G100" s="154" t="inlineStr">
         <is>
           <t>1. В настройках системы видеонаблюдения (видеорегистратора или сервера) задан срок хранения архива менее 90 дней;
-2. Не выполнен расчёт ёмкости дискового пространства для хранения видеоархива в течение 90 дней (не учтены количество камер, разрешение, частота кадров, параметры сжатия).</t>
+2. Не выполнен расчёт ёмкости дискового пространства для хранения видеоархива в течение 90 дней (не учтены количество камер, разрешение, частота кадров, параметры сжатия);
+3. Архив фактически перезаписывается раньше установленного срока из-за недостатка дискового пространства;
+4. Фактическая доступность архивной записи 90-дневной давности не проверяется.</t>
         </is>
       </c>
     </row>
@@ -7592,8 +8277,45 @@
 Главная цель меры — обеспечить визуальную фиксацию и документирование всех случаев доступа к критичным объектам информационной инфраструктуры, расположенным в общедоступных местах.</t>
         </is>
       </c>
-      <c r="E102" s="31" t="n"/>
-      <c r="F102" s="31" t="n"/>
+      <c r="E102" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Установку камер видеонаблюдения, фиксирующих зону непосредственного доступа к каждому общедоступному объекту доступа (банкомату, платёжному терминалу, общедоступному рабочему месту);
+2. Настройку параметров видеозаписи, обеспечивающих возможность идентификации лица, осуществляющего доступ к объекту, и совершаемых им действий;
+3. Обеспечение непрерывной либо событийно-активируемой видеозаписи, синхронизированной по времени с журналом операций самого общедоступного объекта доступа (для последующего сопоставления).
+Класс используемых средств — системы видеонаблюдения (CCTV).
+Иностранные: Hikvision, Dahua и пр.
+Российские сертифицированные (ФСТЭК): «Форт», TRASSIR и др.
+Открытый код: ZoneMinder, Shinobi и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F102" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами системы видеонаблюдения;
+2. Схема размещения камер относительно общедоступных объектов доступа;
+3. Результаты выборочной проверки записей, подтверждающие возможность идентификации лица и его действий у конкретного объекта.</t>
+          </r>
+        </is>
+      </c>
       <c r="G102" s="46" t="inlineStr">
         <is>
           <t>1. Отсутствие системы видеонаблюдения в местах, где расположены общедоступные объекты доступа;
@@ -7625,12 +8347,51 @@
 Главная цель меры — обеспечить наличие доказательной базы за двухнедельный период для расследования инцидентов, связанных с несанкционированным доступом к общедоступным объектам.</t>
         </is>
       </c>
-      <c r="E103" s="31" t="n"/>
-      <c r="F103" s="31" t="n"/>
-      <c r="G103" s="44" t="inlineStr">
+      <c r="E103" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Настройку видеорегистратора (сервера видеонаблюдения), обслуживающего камеры общедоступных объектов доступа, на хранение архива в течение срока не менее 14 дней;
+2. Обеспечение необходимой ёмкости дискового пространства для соответствующего числа камер с учётом выбранных параметров записи;
+3. Организацию автоматической ротации архива по достижении установленного срока хранения.
+Класс используемых средств — системы видеонаблюдения (CCTV) с архивированием.
+Иностранные: Hikvision, Dahua и пр.
+Российские сертифицированные (ФСТЭК): «Форт», TRASSIR и др.
+Открытый код: ZoneMinder, Shinobi и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F103" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами системы видеонаблюдения;
+2. Скриншоты (выгрузки) настроек срока хранения архива для камер общедоступных объектов доступа;
+3. Выгрузка архивной видеозаписи 14-дневной давности, подтверждающая фактическую доступность данных.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G103" s="153" t="inlineStr">
         <is>
           <t>1. В настройках системы видеонаблюдения установлен срок хранения менее 14 дней;
-2. Дисковое пространство не позволяет хранить архивы в течение 14 дней (особенно при высоком разрешении и частоте кадров).</t>
+2. Дисковое пространство не позволяет фактически хранить архивы в течение 14 дней (особенно при высоком разрешении и частоте кадров);
+3. Архив по камерам общедоступных объектов доступа хранится по общей политике видеонаблюдения, без учёта специфики требования именно к этим камерам;
+4. Фактическая доступность архивной записи 14-дневной давности не проверяется.</t>
         </is>
       </c>
     </row>
@@ -7656,8 +8417,42 @@
 Главная цель меры — обеспечить целостность общедоступных объектов доступа, предотвратив возможность использования скомпрометированных устройств для совершения несанкционированных операций. Выявление изменений в аппаратном или программном обеспечении позволяет своевременно вывести устройство из эксплуатации до устранения нарушений.</t>
         </is>
       </c>
-      <c r="E104" s="31" t="n"/>
-      <c r="F104" s="31" t="n"/>
+      <c r="E104" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Разработку и утверждение регламента периодического контроля состояния общедоступных объектов доступа (банкоматов, платёжных терминалов, общедоступных рабочих мест) на предмет несанкционированных изменений в аппаратном обеспечении (скиммеры, посторонние устройства) и программном обеспечении;
+2. Проведение контрольных мероприятий (визуальный осмотр, проверку целостности пломб, сверку версий ПО) с определённой периодичностью, охватывающей все общедоступные объекты доступа;
+3. Оформление результатов каждой проверки актом с фиксацией выявленных отклонений;
+4. Установление порядка эскалации при выявлении признаков несанкционированного изменения (немедленное информирование службы безопасности).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F104" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент проведения контроля состояния общедоступных объектов доступа;
+2. Акты (чек-листы) проведённых проверок с указанием даты, объекта и результата контроля;
+3. Свидетельства эскалации (уведомления службы безопасности) по фактам выявленных отклонений.</t>
+          </r>
+        </is>
+      </c>
       <c r="G104" s="54" t="inlineStr">
         <is>
           <t>1. Не разработан порядок контроля состояния общедоступных объектов;
@@ -7693,8 +8488,42 @@
 Главная цель меры — минимизировать риски для клиентов и организации, предотвратив возможность использования скомпрометированного устройства для совершения мошеннических операций, кражи данных или нанесения иного финансового ущерба.</t>
         </is>
       </c>
-      <c r="E105" s="31" t="n"/>
-      <c r="F105" s="31" t="n"/>
+      <c r="E105" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Определение во внутреннем нормативном документе порядка немедленных действий при выявлении признаков несанкционированного изменения аппаратного обеспечения или ПО общедоступного объекта доступа (приостановка обслуживания, физическое отключение, блокирование в процессинговой системе);
+2. Установление ответственных лиц и предельного времени реагирования с момента выявления отклонения до фактического приведения объекта в нерабочее состояние;
+3. Определение порядка возобновления эксплуатации объекта только после устранения выявленных несанкционированных изменений и подтверждения его целостности;
+4. Документальную фиксацию каждого случая приостановки эксплуатации объекта.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F105" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, определяющий порядок немедленного приведения общедоступного объекта доступа в нерабочее состояние при выявлении несанкционированных изменений;
+2. Акты (записи) о приостановке эксплуатации объектов по зафиксированным случаям выявленных отклонений;
+3. Акты возобновления эксплуатации объектов после устранения выявленных несанкционированных изменений.</t>
+          </r>
+        </is>
+      </c>
       <c r="G105" s="46" t="inlineStr">
         <is>
           <t>1. Не определён порядок действий при обнаружении изменений;
@@ -7742,12 +8571,52 @@
 - выявлять аномалии (например, доступ в нерабочее время, несанкционированные попытки входа).</t>
         </is>
       </c>
-      <c r="E107" s="31" t="n"/>
-      <c r="F107" s="31" t="n"/>
-      <c r="G107" s="46" t="inlineStr">
-        <is>
-          <t>1. Входные двери помещений с объектами доступа не оборудованы СКУД (регистрация событий отсутствует);
-2. В настройках СКУД не включена функция регистрации всех событий входа/выхода (журнал не ведётся или ведётся не для всех точек доступа).</t>
+      <c r="E107" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Оснащение входных дверей помещений, в которых расположены объекты доступа, системой контроля и управления доступом (СКУД), автоматически регистрирующей каждый факт входа и выхода;
+2. Настройку СКУД на фиксацию как минимум даты, времени, идентификатора субъекта и точки доступа для каждого события входа (выхода);
+3. Централизованный сбор и хранение указанных событий для последующего анализа, расследования инцидентов и предоставления свидетельств проверяющим.
+Класс используемых средств — системы контроля и управления доступом (СКУД).
+Иностранные: HID Global, Honeywell Access Control и пр.
+Российские сертифицированные (ФСТЭК): «Болид» (Orion), PERCo и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F107" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами СКУД и службой безопасности;
+2. Скриншоты настроек СКУД, подтверждающие регистрацию событий входа/выхода по всем точкам доступа в защищаемые помещения;
+3. Выгрузка журнала событий СКУД за проверяемый период;
+4. Результаты тестирования (контрольный проход), подтверждающие корректность регистрации события.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G107" s="154" t="inlineStr">
+        <is>
+          <t>1. Входные двери отдельных помещений с объектами доступа не оборудованы СКУД, регистрация событий для них отсутствует;
+2. В настройках СКУД не включена функция регистрации всех событий входа/выхода (журнал не ведётся или ведётся не для всех точек доступа);
+3. События входа и выхода не сопоставляются между собой, что не позволяет достоверно определить время фактического нахождения субъекта в помещении;
+4. Журнал событий СКУД не анализируется на предмет аномалий (доступ в нерабочее время, повторные попытки прохода).</t>
         </is>
       </c>
     </row>
@@ -24846,8 +25715,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -803,6 +803,15 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -8655,30 +8664,82 @@
 Главная цель меры — создать единый достоверный источник информации обо всех ресурсах доступа.</t>
         </is>
       </c>
-      <c r="E109" s="60" t="n"/>
-      <c r="F109" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Проверочные процедуры (свидетельства) - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>1. Инвентарные описи используемых ресурсов доступа;
+      <c r="E109" s="154" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Ведение реестра (описи) созданных, используемых и эксплуатируемых ресурсов доступа с указанием типа ресурса, наименования, ответственного подразделения и статуса (в эксплуатации, выведен из эксплуатации);
+2. Установление обязанности подразделений, создающих или вводящих в эксплуатацию новые ресурсы доступа, регистрировать их в реестре до начала фактического использования;
+3. Периодическую сверку реестра с фактическим состоянием инфраструктуры и актуализацию записей при выводе ресурсов из эксплуатации.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически учёт дополняется:
+1. Внедрением автоматизированных средств инвентаризации активов (класса IT Asset Management, CMDB), автоматически собирающих данные о фактически используемых ресурсах доступа;
+2. Настройкой интеграции системы учёта с источниками данных — гипервизорами (для виртуальных машин), СУБД (для баз данных), средствами сканирования сети (для сетевых файловых ресурсов);
+3. Настройкой автоматического сравнения данных реестра с результатами сканирования и выгрузками из систем-источников для выявления расхождений и несанкционированно созданных ресурсов.
+Класс используемых средств — системы инвентаризации и управления IT-активами (Asset Management, CMDB).
+Иностранные: ServiceNow, BMC Helix CMDB и пр.
+Российские сертифицированные (ФСТЭК): ViPNet Asset Management, «1С:ИТС Управление IT-активами» и др.
+Открытый код: OCS Inventory NG, GLPI и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F109" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) ведения реестра ресурсов доступа;
+2. Реестр (опись) созданных, используемых и эксплуатируемых ресурсов доступа за проверяемый период;
+3. Акты (отчёты) периодической сверки реестра с фактическим состоянием инфраструктуры.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Инвентарные описи используемых ресурсов доступа;
 2. Выгрузка из системы учета ресурсов доступа (инвентаризационная база данных, CMDB, экспорт из специализированного ПО) за проверяемый период с наименованием и типом ресурсов (АС, базы данных, сетевые файловые ресурсы, виртуальные машины, почтовые и веб-сервисы);
 3. Выгрузка из систем-источников: список виртуальных машин из гипервизора (например, VMware vCenter, Hyper-V), список баз данных из СУБД (например, из системного каталога), список сетевых ресурсов из Active Directory или результатов сканирования сети (например, Nmap) и пр.</t>
           </r>
         </is>
       </c>
-      <c r="G109" s="31" t="n"/>
+      <c r="G109" s="151" t="inlineStr">
+        <is>
+          <t>1. Реестр ресурсов доступа не обновляется при создании новых или выводе из эксплуатации старых ресурсов;
+2. Учёт охватывает не все типы ресурсов доступа (например, забыли про сетевые файловые ресурсы или почтовые сервисы);
+3. Автоматизированное сравнение реестра с фактическим состоянием инфраструктуры не выполняется, расхождения выявляются только случайно;
+4. Ответственные за ведение реестра не определены или определены формально.</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
@@ -8696,10 +8757,88 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D110" s="21" t="n"/>
-      <c r="E110" s="31" t="n"/>
-      <c r="F110" s="31" t="n"/>
-      <c r="G110" s="31" t="n"/>
+      <c r="D110" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает требования к учёту используемых и (или) эксплуатируемых объектов доступа финансовой организации — автоматизированных рабочих мест (АРМ), серверов, сетевого оборудования и иных технических средств, участвующих в обработке, хранении или передаче защищаемой информации.
+Главная цель меры — создать единый достоверный источник информации обо всех объектах доступа, без которого невозможны ни контроль их фактического состава и размещения (мера ИУ.6), ни иные меры, опирающиеся на точные данные об инфраструктуре организации.</t>
+        </is>
+      </c>
+      <c r="E110" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Ведение реестра (описи) объектов доступа с указанием типа объекта, инвентарного номера, места размещения (сегмента сети), ответственного подразделения и статуса эксплуатации;
+2. Установление обязанности подразделений, вводящих в эксплуатацию новые объекты доступа, регистрировать их в реестре до подключения к вычислительной сети организации;
+3. Периодическую сверку реестра с фактическим составом объектов доступа и актуализацию записей при выводе объектов из эксплуатации.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая составляющая дополняет организационный учёт:
+1. Внедрением средств автоматизированной инвентаризации объектов доступа (сканирование сети, агенты инвентаризации на АРМ и серверах), обеспечивающих автоматическое обнаружение подключённых устройств;
+2. Настройкой регулярного сопоставления данных реестра с результатами автоматического сканирования для выявления несанкционированно подключённых или неучтённых объектов;
+3. Формированием автоматизированных отчётов о расхождениях между реестром и фактическим составом объектов доступа для передачи ответственным лицам.
+Класс используемых средств — системы инвентаризации и управления IT-активами (Asset Management), средства сканирования сети.
+Иностранные: ServiceNow, Lansweeper и пр.
+Российские сертифицированные (ФСТЭК): ViPNet Asset Management, «Платформа НЕЙРОСС» и др.
+Открытый код: OCS Inventory NG, GLPI, Nmap (для сканирования) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F110" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) ведения реестра объектов доступа;
+2. Реестр (опись) объектов доступа за проверяемый период;
+3. Акты (отчёты) периодической сверки реестра с фактическим составом объектов доступа.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Настройки автоматизированных средств инвентаризации объектов доступа;
+2. Отчёты автоматизированного сканирования сети (выгрузки Nmap, агентов инвентаризации);
+3. Отчёты о выявленных расхождениях между реестром и результатами сканирования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G110" s="151" t="inlineStr">
+        <is>
+          <t>1. Реестр объектов доступа не обновляется при вводе новых или выводе из эксплуатации старых объектов;
+2. Учёт охватывает не все сегменты сети (например, забыли про гостевые или технологические сегменты);
+3. Автоматизированное сканирование для выявления неучтённых объектов не проводится или проводится нерегулярно;
+4. Выявленные несанкционированно подключённые объекты не расследуются и не удаляются из сети.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="409.5" customHeight="1">
       <c r="A111" s="20" t="inlineStr">
@@ -8717,114 +8856,82 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D111" s="44" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в ведении достоверного и актуального учета всех эксплуатируемых общедоступных объектов доступа, в том числе:
-- банкоматы;
-- платежные терминалы (следует отличать от POS-терминалов оплаты картами);
-- общедоступные рабочие места с ограниченным набором систем.
-Под общедоступными объектами доступа понимаются объекты, расположенные в публичных (общедоступных) местах, физический доступ к которым не ограничивается специальным кругом лиц и не требует дополнительной аутентификации. К таким местам относятся, в том числе, зоны клиентского обслуживания.
-Главная цель меры — обеспечить полную и достоверную инвентаризацию всех общедоступных объектов доступа</t>
-        </is>
-      </c>
-      <c r="E111" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - О
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Разработка и утверждение внутренних нормативных документов (ВНД), регламентирующих порядок учета общедоступных объектов доступа (например, в инструкции по эксплуатации банкоматов и платежных терминалов). В документах определяются:
-1. Перечень общедоступных объектов, подлежащих учету (банкоматы, платежные терминалы, общедоступные рабочие места с ограниченным набором систем); 
-2. Состав учетных данных по каждому объекту (уникальный идентификатор, серийный номер, место размещения, версия ПО, ответственное);
-3. Порядок регистрации новых объектов, снятия с учета и внесения изменений при модернизации; 
+      <c r="D111" s="153" t="inlineStr">
+        <is>
+          <t>Суть меры заключается в ведении достоверного и актуального учёта всех эксплуатируемых общедоступных объектов доступа, в том числе:
+1. Банкоматов;
+2. Платёжных терминалов (следует отличать от POS-терминалов оплаты картами);
+3. Общедоступных рабочих мест с ограниченным набором систем.
+Под общедоступными объектами доступа понимаются объекты, расположенные в публичных (общедоступных) местах, физический доступ к которым не ограничивается специальным кругом лиц и не требует дополнительной аутентификации, — в том числе зоны клиентского обслуживания.
+Главная цель меры — обеспечить полную и достоверную инвентаризацию всех общедоступных объектов доступа.</t>
+        </is>
+      </c>
+      <c r="E111" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Разработка и утверждение внутренних нормативных документов (ВНД), регламентирующих порядок учета общедоступных объектов доступа (например, в инструкции по эксплуатации банкоматов и платежных терминалов). В документах определяются:
+1. Перечень общедоступных объектов, подлежащих учету (банкоматы, платежные терминалы, общедоступные рабочие места с ограниченным набором систем);
+2. Состав учетных данных по каждому объекту (уникальный идентификатор, серийный номер, место размещения, версия ПО, ответственное подразделение);
+3. Порядок регистрации новых объектов, снятия с учета и внесения изменений при модернизации;
 4. Периодичность и процедуры сверки фактического состава объектов с данными реестра;
-5. Перечень лиц, ответственных за ведение учета. 
-Ответственность за ведение учета может быть возложена на IT-отдел или назначенных ответственных сотрудников. Ведение инвентарной описи возможно в формате Excel-таблицы.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Должно быть обеспечено внедрение автоматизированной системы учета общедоступных объектов доступа (например, модуля учета активов в составе системы управления IT-инфраструктурой или инвентаризационного модуля системы защиты информации). Настройка автоматического сбора данных об общедоступных объектах из различных источников: систем мониторинга банкоматной сети, платформ управления терминалами и другие. Настройка механизмов контроля — автоматическое сравнение данных системы учета с фактическим состоянием инфраструктуры (результатами сканирования сети, выгрузками из систем управления) для выявления расхождений и несанкционированных объектов.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Иностранные: ServiceNow, Jira Service Management, Open AudIT и пр.
-Российские сертифицированные (ФСТЭК): ViPNet Asset Management, «1С:ИТС Управление IT-активами», «Платформа НЕЙРОСС» и пр.
-Открытый код: OCS Inventory NG, GLPI и пр.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F111" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Проверочные процедуры (свидетельства) - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">1. ВНД, регламентирующий порядок учета общедоступных объектов доступа (положение о системе учета, инструкция по эксплуатации банкоматов и терминалов);
-2. Инвентарная опись общедоступных объектов доступа за проверяемый период. 
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Проверочные процедуры (свидетельства) - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">1. Конфигурация автоматизированной системы учета: источники данных для сбора информации об общедоступных объектах (системы мониторинга банкоматной сети, платформы управления терминалами);
-2.  Инвентарная опись общедоступных объектов доступа за проверяемый период. </t>
+5. Перечень лиц, ответственных за ведение учета.
+Ответственность за ведение учета может быть возложена на IT-отдел или назначенных ответственных сотрудников. Ведение инвентарной описи возможно в формате Excel-таблицы.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически учёт дополняется:
+1. Внедрением автоматизированной системы учёта общедоступных объектов доступа (например, модуля учёта активов в составе системы управления IT-инфраструктурой или инвентаризационного модуля средства защиты информации);
+2. Настройкой автоматического сбора данных об общедоступных объектах из специализированных источников — систем мониторинга банкоматной сети, платформ управления терминалами;
+3. Настройкой механизмов контроля — автоматического сравнения данных системы учёта с фактическим состоянием инфраструктуры (результатами сканирования сети, выгрузками из систем управления) для выявления расхождений и несанкционированных объектов.
+Класс используемых средств — системы инвентаризации и управления IT-активами (Asset Management).
+Иностранные: ServiceNow, Jira Service Management, Open-AudIT и пр.
+Российские сертифицированные (ФСТЭК): ViPNet Asset Management, «1С:ИТС Управление IT-активами», «Платформа НЕЙРОСС» и др.
+Открытый код: OCS Inventory NG, GLPI и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F111" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. ВНД, регламентирующий порядок учёта общедоступных объектов доступа (положение о системе учёта, инструкция по эксплуатации банкоматов и терминалов);
+2. Инвентарная опись общедоступных объектов доступа за проверяемый период.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация автоматизированной системы учёта: источники данных для сбора информации об общедоступных объектах (системы мониторинга банкоматной сети, платформы управления терминалами);
+2. Инвентарная опись общедоступных объектов доступа за проверяемый период, сформированная автоматизированной системой учёта.</t>
           </r>
         </is>
       </c>
@@ -8980,15 +9087,61 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D113" s="21" t="n"/>
-      <c r="E113" s="31" t="n"/>
-      <c r="F113" s="31" t="n"/>
-      <c r="G113" s="31" t="n"/>
-      <c r="H113" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="D113" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует контроля выполнения операций по созданию, удалению и резервному копированию ресурсов доступа — баз данных, сетевых файловых ресурсов, виртуальных машин, — то есть проверки того, что такие операции выполняются санкционированно и в соответствии с установленным порядком.
+Главная цель меры — не допустить бесконтрольного создания, удаления или резервного копирования ресурсов доступа, поскольку каждая из этих операций способна существенно повлиять на доступность и целостность информации: несанкционированное удаление приводит к потере данных, несанкционированное создание — к появлению неучтённых ресурсов (см. также меры ИУ.1—ИУ.2), а нарушение порядка резервного копирования — к невозможности восстановления информации при инциденте.</t>
+        </is>
+      </c>
+      <c r="E113" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Разграничение прав на выполнение операций создания, удаления и резервного копирования ресурсов доступа — предоставление таких прав ограниченному кругу лиц (администраторам соответствующих систем) в соответствии с их должностными обязанностями;
+2. Настройку автоматизированного контроля выполнения плановых операций резервного копирования (мониторинг успешности выполнения заданий резервного копирования по расписанию, оповещение при сбое или пропуске задания);
+3. Настройку автоматизированной сверки фактически выполненных операций создания и удаления ресурсов доступа с санкционированными заявками (при их наличии), выявляющей операции, выполненные в обход установленного порядка.
+Класс используемых средств — системы резервного копирования, средства управления виртуализацией и СУБД со встроенным контролем операций.
+Иностранные: Veeam Backup &amp; Replication, Commvault и пр.
+Российские сертифицированные (ФСТЭК): «Кибер Бэкап», РЕД АДМ (совместно со средствами резервного копирования) и др.
+Открытый код: Bacula, Restic и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F113" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами систем хранения данных, виртуализации и СУБД;
+2. Скриншоты настроек разграничения прав на создание, удаление и резервное копирование ресурсов доступа;
+3. Отчёты систем резервного копирования об успешности выполнения плановых заданий за проверяемый период;
+4. Результаты сверки операций создания и удаления ресурсов доступа с санкционированными заявками.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G113" s="151" t="inlineStr">
+        <is>
+          <t>1. Права на выполнение операций создания, удаления и резервного копирования ресурсов доступа не ограничены кругом ответственных администраторов;
+2. Сбои резервного копирования не отслеживаются автоматически, факт невыполнения планового задания выявляется только при попытке восстановления;
+3. Сверка фактически выполненных операций с санкционированными заявками не проводится;
+4. Тестовое восстановление из резервных копий не выполняется, что не позволяет подтвердить их фактическую пригодность.</t>
+        </is>
+      </c>
+      <c r="H113" s="161" t="inlineStr"/>
     </row>
     <row r="114" ht="85.5" customHeight="1">
       <c r="A114" s="20" t="inlineStr">
@@ -9012,16 +9165,77 @@
 Главная цель меры — своевременно выявлять расхождения между учтёнными и фактическими объектами доступа.</t>
         </is>
       </c>
-      <c r="E114" s="62" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F114" s="63" t="n"/>
-      <c r="G114" s="61" t="inlineStr">
-        <is>
-          <t>1. Не определен порядок проведения контроля; 
-2. Контролируются не все типы объекты доступа (например, забыли про СХД или принтеры);
+      <c r="E114" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Разработку и утверждение регламента проведения контроля фактического состава эксплуатируемых объектов доступа и их размещения в сегментах вычислительных сетей, с указанием периодичности контроля, перечня проверяемых типов объектов и ответственных лиц;
+2. Проведение периодических проверок фактического состава объектов доступа и их размещения с установленной периодичностью;
+3. Оформление результатов каждой проверки актом с фиксацией выявленных расхождений и принятых мер по их устранению.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль дополняется:
+1. Внедрением автоматизированных средств инвентаризации объектов доступа и анализа топологии сети (средств сканирования сети), обеспечивающих автоматический сбор данных о фактическом составе и размещении объектов;
+2. Настройкой автоматического сопоставления результатов сканирования сети с реестром объектов доступа (мера ИУ.2) и эталонной схемой размещения по сегментам для выявления расхождений;
+3. Формированием автоматизированных отчётов о выявленных несоответствиях (неучтённые объекты, объекты не в своём сегменте) для передачи ответственным лицам.
+Класс используемых средств — системы инвентаризации активов и анализа сетевой топологии.
+Иностранные: ServiceNow, Lansweeper и пр.
+Российские сертифицированные (ФСТЭК): ViPNet Asset Management, «Платформа НЕЙРОСС» и др.
+Открытый код: OCS Inventory NG, Nmap (для сканирования и анализа топологии) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F114" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент проведения контроля фактического состава объектов доступа и их размещения в сегментах сети;
+2. Акты (отчёты) периодических проверок с фиксацией выявленных расхождений и принятых мер.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Настройки автоматизированных средств инвентаризации и сканирования сети;
+2. Результаты сопоставления выгрузки из реестра объектов доступа с результатами сканирования сети;
+3. Отчёты о выявленных несоответствиях в составе и размещении объектов доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G114" s="160" t="inlineStr">
+        <is>
+          <t>1. Не определён порядок проведения контроля;
+2. Контролируются не все типы объектов доступа (например, забыли про СХД или принтеры);
 3. Контроль реализуется, но не фиксируются его результаты.</t>
         </is>
       </c>
@@ -9061,42 +9275,26 @@
 Главная цель меры — обеспечить прозрачность, подотчётность и контролируемость всех операций с ресурсами доступа.</t>
         </is>
       </c>
-      <c r="E116" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Настройка аудита операций с ресурсами доступа на всех системах, обеспечивающих их создание, копирование и удаление. Для ВМ регистрация событий настраивается в системах управления виртуализацией (VMware vCenter, Microsoft SCVMM) с включением аудита операций создания, клонирования, удаления ВМ. Для баз данных (БД) настройка аудита выполняется средствами СУБД (Microsoft SQL Server, Oracle, PostgreSQL) с фиксацией событий создания, удаления БД, а также операций резервного копирования (BACKUP, RESTORE) и копирования данных (BULK INSERT, SELECT INTO). Для сетевых файловых ресурсов регистрация настраивается на файловых серверах (Windows Server, Samba) с включением аудита доступа к файлам и папкам, включая создание, копирование, перемещение и удаление. Журналы должны содержать: идентификатор пользователя или процесса, инициировавшего операцию; временную метку, тип операции (создание, копирование, резервное копирование, удаление), идентификатор ресурса (имя БД, путь к файловому ресурсу, имя ВМ).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Иностранные: VMware vCenter, Microsoft SQL Server, Splunk Enterprise Security и пр.
-Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0, ViPNet Coordinator и пр.
-Открытый код: Osquery, Graylog и пр.</t>
+      <c r="E116" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку аудита операций с ресурсами доступа на всех системах, обеспечивающих их создание, копирование и удаление:
+1. Для виртуальных машин — регистрацию событий в системах управления виртуализацией (VMware vCenter, Microsoft SCVMM) с включением аудита операций создания, клонирования и удаления виртуальных машин;
+2. Для баз данных — настройку аудита средствами СУБД (Microsoft SQL Server, Oracle, PostgreSQL) с фиксацией событий создания и удаления баз данных, а также операций резервного копирования (BACKUP, RESTORE) и массового копирования данных (BULK INSERT, SELECT INTO);
+3. Для сетевых файловых ресурсов — настройку регистрации на файловых серверах (Windows Server, Samba) с включением аудита создания, копирования, перемещения и удаления файлов и папок.
+Журналы должны содержать как минимум: идентификатор пользователя или процесса, инициировавшего операцию; временную метку; тип операции (создание, копирование, резервное копирование, удаление); идентификатор ресурса (имя базы данных, путь к файловому ресурсу, имя виртуальной машины).
+Класс используемых средств — встроенные средства аудита систем управления виртуализацией и СУБД, системы управления событиями информационной безопасности (SIEM).
+Иностранные: VMware vCenter, Microsoft SQL Server (Audit), Splunk Enterprise Security и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К, ViPNet Coordinator и др.
+Открытый код: Osquery, Graylog и др.</t>
           </r>
         </is>
       </c>
@@ -9123,10 +9321,12 @@
           </r>
         </is>
       </c>
-      <c r="G116" s="61" t="inlineStr">
+      <c r="G116" s="160" t="inlineStr">
         <is>
           <t>1. Регистрация операций с ресурсами доступа не включена или настроена не на все типы событий;
-2. Журналирование настроено не для всех типов ресурсов доступа (например, забыли про резервное копирование баз данных или копирование образов виртуальных машин).</t>
+2. Журналирование настроено не для всех типов ресурсов доступа (например, забыли про резервное копирование баз данных или копирование образов виртуальных машин);
+3. Журналы событий разных систем (виртуализации, СУБД, файловых серверов) не собираются централизованно, что затрудняет их анализ;
+4. Журналы не содержат достаточного набора атрибутов (например, отсутствует идентификатор инициатора операции).</t>
         </is>
       </c>
     </row>
@@ -9152,46 +9352,25 @@
 Главная цель меры — обеспечить прозрачность, подотчётность и контролируемость всех процессов подключения объектов доступа к вычислительной сети.</t>
         </is>
       </c>
-      <c r="E117" s="64" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация меры предполагает настройку журналирования событий на всех компонентах сетевой инфраструктуры, где происходит подключение объектов доступа, например:
-1. Настройка средств контроля сетевого доступа (NAC — Network Access Control) или систем обнаружения сетевых устройств, обеспечивающих автоматическую регистрацию появления новых объектов доступа в вычислительных сетях организации;
-2. Настройка регистрации событий подключения объектов доступа (включая серверы, рабочие станции, сетевое оборудование, банкоматы и платёжные терминалы) в журналах безопасности сетевых устройств (коммутаторов с поддержкой SNMP, систем управления IP-адресами — IPAM) и системах NAC (например, Cisco ISE, ForeScout, PacketFence);
-3. Настройка протоколирования фактов установления сетевого соединения с фиксацией MAC-адреса и IP-адреса подключаемого объекта, временной метки, порта коммутатора, к которому выполнено подключение;
-4. и пр.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Иностранные: Cisco ISE, ForeScout CounterACT, Aruba ClearPass и пр.
-Российские сертифицированные (ФСТЭК): ViPNet Asset Management, Ideco NAC, «Solar inCode» и пр.
-Открытый код: PacketFence, OpenNAC и пр.</t>
+      <c r="E117" s="162" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация меры предполагает настройку журналирования событий на всех компонентах сетевой инфраструктуры, где происходит подключение объектов доступа:
+1. Настройку средств контроля сетевого доступа (NAC — Network Access Control) или систем обнаружения сетевых устройств, обеспечивающих автоматическую регистрацию появления новых объектов доступа в вычислительных сетях организации;
+2. Настройку регистрации событий подключения объектов доступа (серверов, рабочих станций, сетевого оборудования, банкоматов и платёжных терминалов) в журналах безопасности сетевых устройств (коммутаторов с поддержкой SNMP, систем управления IP-адресами — IPAM) и системах NAC (например, Cisco ISE, ForeScout, PacketFence);
+3. Настройку протоколирования фактов установления сетевого соединения с фиксацией MAC-адреса и IP-адреса подключаемого объекта, временной метки и порта коммутатора, к которому выполнено подключение.
+Класс используемых средств — средства контроля сетевого доступа (NAC), активное сетевое оборудование со встроенным журналированием.
+Иностранные: Cisco ISE, ForeScout CounterACT, Aruba ClearPass и пр.
+Российские сертифицированные (ФСТЭК): Ideco NAC, «Solar inCode» и др.
+Открытый код: PacketFence, OpenNAC и др.</t>
           </r>
         </is>
       </c>
@@ -25715,8 +25894,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -812,6 +812,9 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -9447,14 +9450,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D120" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует разделить корпоративную вычислительную сеть организации на изолированные сетевые сегменты, каждый из которых предназначен для размещения информационной инфраструктуры, относящейся к конкретному контуру безопасности, состоящих из объектов информатизации, используемых для реализации бизнес-процессов единой степени критичности, для которых применяется единая политика защиты информации. Это снижает риск несанкционированного распространения угроз между сегментами контура безопасности.</t>
-        </is>
-      </c>
-      <c r="E120" s="31" t="n"/>
-      <c r="F120" s="31" t="n"/>
-      <c r="G120" s="31" t="n"/>
+      <c r="D120" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует разделить корпоративную вычислительную сеть организации на изолированные сетевые сегменты, каждый из которых предназначен для размещения информационной инфраструктуры, относящейся к конкретному контуру безопасности, — то есть состоящей из объектов информатизации, используемых для реализации бизнес-процессов единой степени критичности, для которых применяется единая политика защиты информации.
+Главная цель меры — снизить риск несанкционированного распространения угроз между контурами безопасности за счёт их сетевой изоляции: без выделения отдельных сегментов компрометация одного участка инфраструктуры (например, тестового контура) открывает злоумышленнику прямой сетевой доступ ко всем остальным контурам.</t>
+        </is>
+      </c>
+      <c r="E120" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Проектирование схемы сегментации вычислительной сети с выделением отдельных сегментов (групп сегментов) для каждого контура безопасности исходя из критичности размещаемых в них бизнес-процессов;
+2. Техническую реализацию выделенных сегментов средствами VLAN (Virtual Local Area Network), физического разделения каналов связи либо иных технологий сетевой изоляции;
+3. Документальное закрепление (в схеме сети) соответствия между контурами безопасности и выделенными для них сетевыми сегментами.
+Класс используемых средств — активное сетевое оборудование (коммутаторы, маршрутизаторы) с поддержкой сегментации сети.
+Иностранные: Cisco Catalyst, Juniper EX и пр.
+Российские сертифицированные (ФСТЭК): «Элтекс», Eltex ESR (коммутаторы и маршрутизаторы) и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется; функция реализуется аппаратными коммутаторами и маршрутизаторами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F120" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема (карта) сети с указанием сегментов, выделенных для каждого контура безопасности;
+3. Скриншоты (выгрузки) настроек сетевого оборудования, подтверждающие фактическую реализацию сегментации (настройки VLAN);
+4. Результаты сетевого сканирования, подтверждающие соответствие фактической топологии заявленной схеме сегментации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G120" s="151" t="inlineStr">
+        <is>
+          <t>1. Схема сегментации сети не документирована или не актуализирована;
+2. Часть информационной инфраструктуры контура безопасности фактически размещена вне выделенного для него сегмента;
+3. Разные контуры безопасности, требующие разного уровня защиты, размещены в одном сетевом сегменте;
+4. Фактическая топология сети не сверяется со схемой сегментации на регулярной основе.</t>
+        </is>
+      </c>
       <c r="H120" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9485,9 +9534,54 @@
 Главная цель меры — обеспечить изоляцию контуров безопасности от иных внутренних сетей на сетевом уровне, предотвращая несанкционированное взаимодействие и распространение угроз между сегментами. При этом сетевое взаимодействие должно осуществляться в соответствии с установленными правилами и протоколами.</t>
         </is>
       </c>
-      <c r="E121" s="31" t="n"/>
-      <c r="F121" s="31" t="n"/>
-      <c r="G121" s="31" t="n"/>
+      <c r="E121" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими средствами, необходимо:
+1. Реализацию сетевой изоляции сегментов контуров безопасности от иных внутренних вычислительных сетей на уровне не выше третьего (сетевого) уровня модели OSI — средствами VLAN (канальный уровень), маршрутизации и фильтрации по IP-адресам (сетевой уровень) либо физического разделения сред передачи;
+2. Технический запрет прямого сетевого взаимодействия между сегментами контуров безопасности и иными внутренними сетями в обход средств изоляции (например, исключение общих широковещательных доменов, немаршрутизируемых напрямую сегментов);
+3. Периодический контроль (сканирование, анализ конфигураций сетевого оборудования) фактического соблюдения установленного уровня изоляции.
+Класс используемых средств — активное сетевое оборудование с поддержкой VLAN и маршрутизации, средства межсетевого экранирования.
+Иностранные: Cisco Catalyst, Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F121" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети с указанием уровня (VLAN, маршрутизация, физическое разделение), на котором реализована изоляция сегментов;
+3. Скриншоты (выгрузки) настроек сетевого оборудования, подтверждающие фактическую реализацию изоляции;
+4. Результаты тестирования (попытка сетевого взаимодействия в обход установленной изоляции), подтверждающие её эффективность.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G121" s="151" t="inlineStr">
+        <is>
+          <t>1. Изоляция сегментов реализована на уровне, менее строгом, чем требуется (например, только фильтрация по IP-адресам при необходимости физического разделения);
+2. Отдельные участки сети сохраняют прямую связность между сегментами контуров безопасности и иными внутренними сетями в обход установленных правил изоляции;
+3. Изоляция реализована не для всех сегментов контуров безопасности, а только для части из них;
+4. Периодический контроль фактического уровня изоляции не проводится.</t>
+        </is>
+      </c>
       <c r="H121" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9518,9 +9612,54 @@
 Главная цель меры — обеспечить контролируемое и защищённое информационное взаимодействие между сегментами контуров безопасности, предотвращая несанкционированный доступ и распространение угроз между сегментами сети.</t>
         </is>
       </c>
-      <c r="E122" s="31" t="n"/>
-      <c r="F122" s="31" t="n"/>
-      <c r="G122" s="31" t="n"/>
+      <c r="E122" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввиду того, что мера реализуется только технически, необходимо:
+1. Внедрение межсетевых экранов на границах сегментов контуров безопасности, обеспечивающих фильтрацию трафика на сетевом уровне — по IP-адресам, маскам подсетей и номерам портов TCP/UDP;
+2. Внедрение функционала фильтрации на прикладном уровне (Layer 7) — анализа и контроля протоколов прикладного уровня (HTTP, FTP, SMTP, DNS и др.), проходящих через границы сегментов;
+3. Разработку и применение правил межсетевого экранирования по принципу «запрещено по умолчанию», разрешающих только необходимое для бизнес-процессов взаимодействие.
+Класс используемых средств — межсетевые экраны (в том числе следующего поколения, NGFW) с поддержкой фильтрации на прикладном уровне.
+Иностранные: Palo Alto Networks, Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate, «Ideco UTM» и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F122" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами межсетевых экранов;
+2. Выгрузка правил межсетевого экранирования на границах сегментов контуров безопасности;
+3. Результаты тестирования (попытка взаимодействия по незапланированному протоколу или порту), подтверждающие срабатывание правил фильтрации;
+4. Скриншоты настроек, подтверждающие фильтрацию на прикладном уровне.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G122" s="151" t="inlineStr">
+        <is>
+          <t>1. Межсетевое экранирование реализовано только на сетевом уровне, без контроля на прикладном уровне;
+2. Правила межсетевого экранирования построены по принципу «разрешено по умолчанию», а не «запрещено по умолчанию»;
+3. Правила межсетевого экранирования не пересматриваются при изменении состава систем и бизнес-процессов, содержат неактуальные (избыточные) разрешения;
+4. Межсетевое экранирование реализовано не на всех границах сегментов контуров безопасности.</t>
+        </is>
+      </c>
       <c r="H122" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9551,9 +9690,54 @@
 Главная цель меры — обеспечить контролируемое и защищённое информационное взаимодействие между сегментами сети, предотвращая несанкционированный доступ и распространение угроз между сегментами.</t>
         </is>
       </c>
-      <c r="E123" s="31" t="n"/>
-      <c r="F123" s="31" t="n"/>
-      <c r="G123" s="31" t="n"/>
+      <c r="E123" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется на техническом уровне без организационной составляющей:
+1. Документальное закрепление правил и разрешённых протоколов сетевого взаимодействия между сегментами контуров безопасности и иными внутренними сетями (матрица сетевого взаимодействия);
+2. Настройку сетевого оборудования и средств межсетевого экранирования в строгом соответствии с утверждённой матрицей сетевого взаимодействия;
+3. Периодический технический контроль (сканирование, анализ конфигураций) соответствия фактически разрешённого сетевого взаимодействия утверждённой матрице.
+Класс используемых средств — межсетевые экраны, системы анализа и контроля соответствия конфигураций сетевой политике.
+Иностранные: Palo Alto Networks, Tufin (управление политиками МЭ) и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F123" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Утверждённая матрица сетевого взаимодействия между сегментами и внутренними сетями;
+3. Результаты сопоставления фактических правил межсетевого экранирования с утверждённой матрицей;
+4. Результаты тестирования (попытка взаимодействия, не предусмотренного матрицей), подтверждающие блокирование такого взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G123" s="151" t="inlineStr">
+        <is>
+          <t>1. Матрица сетевого взаимодействия не документирована или не актуализирована;
+2. Фактически разрешённое сетевое взаимодействие не соответствует утверждённой матрице (присутствуют незадокументированные правила);
+3. Сопоставление фактических правил межсетевого экранирования с матрицей не проводится на регулярной основе;
+4. Контроль соблюдения установленных правил ограничивается моментом первоначальной настройки, без последующих проверок.</t>
+        </is>
+      </c>
       <c r="H123" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9577,15 +9761,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D124" s="65" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы обмен данными между сегментами контуров безопасности и остальными внутренними сетями организации осуществлялся исключительно через программные шлюзы (proxy-серверы), которые выступают в качестве посредников и контролируют передачу данных, инициируемую пользователями, что обеспечивает детальный контроль прикладного трафика, фильтрации содержимого, предотвращения утечек данных.
-Главная цель — обеспечить контролируемый обмен данными между сегментами сети и предотвратить несанкционированные передачи, инициированные пользователями или процессами</t>
-        </is>
-      </c>
-      <c r="E124" s="31" t="n"/>
-      <c r="F124" s="31" t="n"/>
-      <c r="G124" s="31" t="n"/>
+      <c r="D124" s="163" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы обмен данными между сегментами контуров безопасности и остальными внутренними сетями организации осуществлялся исключительно через программные шлюзы (proxy-серверы), которые выступают в качестве посредников и контролируют передачу данных, инициируемую пользователями, что обеспечивает детальный контроль прикладного трафика, фильтрацию содержимого, предотвращение утечек данных.
+Главная цель меры — обеспечить контролируемый обмен данными между сегментами сети и предотвратить несанкционированные передачи, инициированные пользователями или процессами.</t>
+        </is>
+      </c>
+      <c r="E124" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Развёртывание программных шлюзов (прокси-серверов) на границах между сегментами контуров безопасности и иными внутренними сетями для протоколов, по которым субъекты логического доступа инициируют передачу данных (HTTP/HTTPS, FTP, SMTP и др.);
+2. Настройку прокси-серверов таким образом, чтобы прямое (в обход шлюза) сетевое взаимодействие между сегментами было технически невозможно;
+3. Настройку функций контроля передаваемого содержимого на прокси-серверах (фильтрация содержимого, контроль передаваемых типов файлов) для предотвращения несанкционированной передачи данных.
+Класс используемых средств — программные шлюзы (прокси-серверы), средства предотвращения утечек данных (DLP).
+Иностранные: Squid, Blue Coat ProxySG и пр.
+Российские сертифицированные (ФСТЭК): «Континент», InfoWatch Traffic Monitor и др.
+Открытый код: Squid, HAProxy и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F124" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети, подтверждающая размещение программных шлюзов на границах сегментов;
+3. Скриншоты настроек прокси-серверов, подтверждающие контроль передаваемого содержимого;
+4. Результаты тестирования (попытка прямого взаимодействия в обход шлюза), подтверждающие невозможность такого взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G124" s="151" t="inlineStr">
+        <is>
+          <t>1. Программные шлюзы развёрнуты не для всех протоколов, по которым возможна инициируемая пользователями передача данных;
+2. Существует техническая возможность прямого (в обход шлюза) сетевого взаимодействия между сегментами;
+3. Контроль передаваемого содержимого на прокси-серверах не настроен либо настроен формально;
+4. Журналы прокси-серверов не анализируются на предмет выявления попыток несанкционированной передачи данных.</t>
+        </is>
+      </c>
       <c r="H124" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9615,9 +9844,53 @@
 Главная цель меры — исключить возможность несанкционированного доступа, утечки или искажения защищаемой информации из сегмента разработки и тестирования, а также предотвратить нарушение работы промышленных систем из-за некорректного взаимодействия с тестовой средой.</t>
         </is>
       </c>
-      <c r="E125" s="31" t="n"/>
-      <c r="F125" s="31" t="n"/>
-      <c r="G125" s="31" t="n"/>
+      <c r="E125" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Выделение отдельного сетевого сегмента (группы сегментов) для размещения инфраструктуры разработки, создания и модернизации автоматизированных систем (АС), включая тестирование программного обеспечения и средств вычислительной техники;
+2. Техническую реализацию выделенного сегмента разработки и тестирования средствами VLAN, маршрутизации либо физического разделения, отдельно от сегментов контуров безопасности, используемых для промышленной эксплуатации;
+3. Документальное закрепление в схеме сети границ и состава сегмента разработки и тестирования.
+Класс используемых средств — активное сетевое оборудование с поддержкой сегментации сети.
+Иностранные: Cisco Catalyst, Juniper EX и пр.
+Российские сертифицированные (ФСТЭК): «Элтекс», Eltex ESR и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F125" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением разработки;
+2. Схема сети с указанием границ и состава сегмента разработки и тестирования;
+3. Скриншоты (выгрузки) настроек сетевого оборудования, подтверждающие фактическое выделение сегмента разработки и тестирования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G125" s="151" t="inlineStr">
+        <is>
+          <t>1. Инфраструктура разработки и тестирования фактически размещена в одном сегменте с промышленными системами;
+2. Границы сегмента разработки и тестирования не задокументированы и не совпадают с фактической топологией;
+3. В сегмент разработки и тестирования попадают отдельные компоненты, задействованные также в промышленной эксплуатации;
+4. Состав сегмента разработки и тестирования не пересматривается при изменении используемых для этого систем.</t>
+        </is>
+      </c>
       <c r="H125" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9641,15 +9914,59 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D126" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы сегмент разработки и тестирования не мог инициировать сетевое взаимодействие с другими внутренними сетями (сегментами) контуров безопасности. 
-Это снижает риск несанкционированного доступа и распространения ошибок и сбоев из нестабильной тестовой среды к продуктивным системам.</t>
-        </is>
-      </c>
-      <c r="E126" s="31" t="n"/>
-      <c r="F126" s="31" t="n"/>
-      <c r="G126" s="31" t="n"/>
+      <c r="D126" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы сегмент разработки и тестирования не мог инициировать сетевое взаимодействие с другими внутренними сетями (сегментами) контуров безопасности.
+Главная цель меры — снизить риск несанкционированного доступа и распространения ошибок и сбоев из нестабильной тестовой среды к продуктивным системам: тестовый сегмент по своей природе менее контролируем и более подвержен экспериментальным изменениям, поэтому инициатива сетевого взаимодействия с его стороны представляет повышенный риск.</t>
+        </is>
+      </c>
+      <c r="E126" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит чисто технический характер и включает:
+1. Настройку сетевого оборудования (маршрутизаторов, межсетевых экранов) на границе сегмента разработки и тестирования таким образом, чтобы сетевые соединения могли инициироваться только со стороны иных внутренних сетей к сегменту разработки и тестирования (при наличии обоснованной необходимости), но не в обратном направлении;
+2. Технический запрет (правилами межсетевого экранирования) на инициирование сетевых соединений из сегмента разработки и тестирования к сегментам контуров безопасности и иным внутренним сетям;
+3. Периодический технический контроль (тестирование, анализ конфигураций) фактического соблюдения запрета на инициирование соединений со стороны сегмента разработки и тестирования.
+Класс используемых средств — межсетевые экраны с поддержкой направленной (stateful) фильтрации соединений.
+Иностранные: Palo Alto Networks, Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F126" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Выгрузка правил межсетевого экранирования на границе сегмента разработки и тестирования;
+3. Результаты тестирования (попытка инициировать соединение из сегмента разработки и тестирования наружу), подтверждающие блокирование такой попытки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G126" s="151" t="inlineStr">
+        <is>
+          <t>1. Запрет на инициирование соединений из сегмента разработки и тестирования реализован не на всех точках его подключения к остальной сети;
+2. Правила межсетевого экранирования допускают отдельные исключения (например, для обновлений ПО), не задокументированные и не пересматриваемые;
+3. Тестирование фактического соблюдения запрета не проводится на регулярной основе;
+4. Изменения в конфигурации сетевого оборудования сегмента разработки и тестирования вносятся без проверки на предмет сохранения установленного запрета.</t>
+        </is>
+      </c>
       <c r="H126" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9673,14 +9990,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D127" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы в рамках контура безопасности автоматизированные рабочие места (АРМ) пользователей были выделены в отдельный сегмент сети, изолированный от серверного оборудования и средств управления. Это снижает риск распространения угроз из пользовательской среды (например, через вредоносное ПО или фишинг).</t>
-        </is>
-      </c>
-      <c r="E127" s="31" t="n"/>
-      <c r="F127" s="31" t="n"/>
-      <c r="G127" s="31" t="n"/>
+      <c r="D127" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы в рамках контура безопасности автоматизированные рабочие места (АРМ) пользователей были выделены в отдельный сегмент сети, изолированный от серверного оборудования и средств управления.
+Главная цель меры — снизить риск распространения угроз из пользовательской среды (например, через вредоносное ПО, полученное в результате фишинговой атаки на АРМ пользователя) на серверную инфраструктуру и средства управления, поскольку именно пользовательские рабочие места, как правило, наиболее подвержены компрометации через внешние каналы (электронную почту, веб-браузинг, съёмные носители).</t>
+        </is>
+      </c>
+      <c r="E127" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера подразумевает исключительно технические меры защиты, а именно:
+1. Выделение отдельного сетевого сегмента для размещения автоматизированных рабочих мест (АРМ) пользователей в рамках каждого контура безопасности;
+2. Техническую реализацию выделенного пользовательского сегмента средствами VLAN, изолированного от сегментов серверного оборудования, хранения данных и управления (см. также меры СМЭ.9—СМЭ.10);
+3. Настройку межсетевого экранирования на границе пользовательского сегмента, ограничивающего сетевое взаимодействие пользовательских АРМ с серверными сегментами минимально необходимым набором протоколов и портов.
+Класс используемых средств — активное сетевое оборудование с поддержкой VLAN, межсетевые экраны.
+Иностранные: Cisco Catalyst, Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F127" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети с указанием пользовательского сегмента и его границ;
+3. Выгрузка правил межсетевого экранирования на границе пользовательского сегмента;
+4. Результаты тестирования (попытка сетевого взаимодействия пользовательского АРМ с серверным сегментом за пределами разрешённых протоколов), подтверждающие блокирование такого взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G127" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельные АРМ пользователей размещены вне выделенного пользовательского сегмента;
+2. Межсетевое экранирование на границе пользовательского сегмента настроено избыточно разрешительно (допускает взаимодействие сверх необходимого);
+3. В пользовательском сегменте присутствуют серверные компоненты или средства управления, не относящиеся к пользовательским АРМ;
+4. Состав пользовательского сегмента не пересматривается при изменении парка АРМ.</t>
+        </is>
+      </c>
       <c r="H127" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9704,14 +10067,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D128" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы в рамках контура безопасности были выделены отдельные сегменты сети, в которых размещаются только автоматизированные рабочие места (АРМ) эксплуатационного персонала (администраторов), используемые для управления информационной инфраструктурой. Это минимизирует риск несанкционированного доступа и компрометации учётных записей с высокими привилегиями через пользовательские АРМ.</t>
-        </is>
-      </c>
-      <c r="E128" s="31" t="n"/>
-      <c r="F128" s="31" t="n"/>
-      <c r="G128" s="31" t="n"/>
+      <c r="D128" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы в рамках контура безопасности были выделены отдельные сегменты сети, в которых размещаются только автоматизированные рабочие места (АРМ) эксплуатационного персонала (администраторов), используемые для управления информационной инфраструктурой.
+Главная цель меры — минимизировать риск несанкционированного доступа и компрометации учётных записей с высокими привилегиями через пользовательские АРМ: размещение административных рабочих мест в отдельном, более строго контролируемом сегменте снижает вероятность того, что компрометация обычного пользовательского АРМ повлечёт за собой захват административного доступа ко всей инфраструктуре.</t>
+        </is>
+      </c>
+      <c r="E128" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как речь идёт о чисто технической мере, реализация включает:
+1. Выделение отдельного сетевого сегмента (сегмента управления) для размещения АРМ эксплуатационного персонала, используемых для администрирования информационной инфраструктуры;
+2. Техническую реализацию сегмента управления средствами VLAN, изолированного от пользовательского сегмента (СМЭ.8) и иных сегментов контура безопасности;
+3. Настройку межсетевого экранирования на границе сегмента управления, ограничивающего доступ к нему минимально необходимым кругом административных протоколов (SSH, RDP, HTTPS для консолей управления) исключительно с АРМ эксплуатационного персонала.
+Класс используемых средств — активное сетевое оборудование с поддержкой VLAN, межсетевые экраны, системы контроля привилегированного доступа (PAM).
+Иностранные: Cisco Catalyst, CyberArk PAM и пр.
+Российские сертифицированные (ФСТЭК): «Континент», Indeed Privileged Access Manager и др.
+Открытый код: pfSense, Teleport и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F128" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети с указанием сегмента управления и его границ;
+3. Выгрузка правил межсетевого экранирования на границе сегмента управления;
+4. Результаты тестирования (попытка административного подключения к инфраструктуре не из сегмента управления), подтверждающие блокирование такого подключения.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G128" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельные АРМ эксплуатационного персонала подключаются к управляемой инфраструктуре не из выделенного сегмента управления;
+2. Сегмент управления не изолирован от пользовательского сегмента на сетевом уровне;
+3. Правила межсетевого экранирования на границе сегмента управления допускают избыточно широкий доступ (не ограничены административными протоколами);
+4. Состав сегмента управления не пересматривается при кадровых изменениях среди эксплуатационного персонала.</t>
+        </is>
+      </c>
       <c r="H128" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9735,14 +10144,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D129" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует в рамках каждого контура безопасности выделять отдельные сетевые сегменты, в которых размещаются только серверы, системы хранения данных (СХД) и иные ресурсы, предназначенные для обработки и хранения информации. Это  минимизирует риск несанкционированного доступа к данным и распространения вредоносного ПО из менее защищённых сегментов.</t>
-        </is>
-      </c>
-      <c r="E129" s="31" t="n"/>
-      <c r="F129" s="31" t="n"/>
-      <c r="G129" s="31" t="n"/>
+      <c r="D129" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует в рамках каждого контура безопасности выделять отдельные сетевые сегменты, в которых размещаются только серверы, системы хранения данных (СХД) и иные ресурсы, предназначенные для обработки и хранения информации.
+Главная цель меры — минимизировать риск несанкционированного доступа к данным и распространения вредоносного ПО из менее защищённых сегментов (пользовательского, управления) на серверную инфраструктуру и системы хранения данных, представляющие собой наиболее критичную с точки зрения защищаемой информации часть инфраструктуры.</t>
+        </is>
+      </c>
+      <c r="E129" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Выделение отдельного сетевого сегмента (сегмента хранения и обработки данных) для размещения серверов, систем хранения данных и иных ресурсов доступа, предназначенных для обработки и хранения информации;
+2. Техническую реализацию сегмента хранения и обработки данных средствами VLAN, изолированного от пользовательского сегмента (СМЭ.8) и сегмента управления (СМЭ.9);
+3. Настройку межсетевого экранирования на границе сегмента, ограничивающего доступ к серверам и системам хранения данных минимально необходимым набором протоколов, соответствующих реальным потребностям бизнес-процессов.
+Класс используемых средств — активное сетевое оборудование с поддержкой VLAN, межсетевые экраны.
+Иностранные: Cisco Catalyst, Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F129" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети с указанием сегмента хранения и обработки данных и его границ;
+3. Выгрузка правил межсетевого экранирования на границе данного сегмента;
+4. Результаты тестирования (попытка прямого доступа к серверам или СХД из пользовательского сегмента в обход разрешённых протоколов), подтверждающие блокирование такого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G129" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельные серверы или системы хранения данных размещены вне выделенного сегмента хранения и обработки данных;
+2. Межсетевое экранирование на границе сегмента настроено избыточно разрешительно;
+3. Пользовательский сегмент имеет прямой сетевой доступ к серверам без прохождения через контролируемую границу;
+4. Состав сегмента не пересматривается при вводе новых серверов или систем хранения данных.</t>
+        </is>
+      </c>
       <c r="H129" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9766,14 +10221,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D130" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мера требует, чтобы общедоступные объекты доступа (банкоматы, платёжные терминалы, общедоступные рабочие места) были выделены в отдельные сетевые сегменты, изолированные от внутренней инфраструктуры организации. Это минимизирует распространение угроз из общедоступной среды (менее защищённой и физически доступной для посторонних лиц) на внутренние сегменты контуров безопасности. </t>
-        </is>
-      </c>
-      <c r="E130" s="31" t="n"/>
-      <c r="F130" s="31" t="n"/>
-      <c r="G130" s="31" t="n"/>
+      <c r="D130" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы общедоступные объекты доступа (банкоматы, платёжные терминалы, общедоступные рабочие места) были выделены в отдельные сетевые сегменты, изолированные от внутренней инфраструктуры организации.
+Главная цель меры — минимизировать распространение угроз из общедоступной среды на внутренние сегменты контуров безопасности: общедоступные объекты доступа физически находятся в местах, доступных посторонним лицам, и в силу этого подвержены существенно более высокому риску физического и сетевого воздействия, чем оборудование, размещённое во внутренних, контролируемых помещениях организации.</t>
+        </is>
+      </c>
+      <c r="E130" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера не имеет организационной составляющей — её выполнение обеспечивается техническими средствами:
+1. Выделение отдельного сетевого сегмента (группы сегментов) для размещения общедоступных объектов доступа — банкоматов, платёжных терминалов, общедоступных рабочих мест;
+2. Техническую реализацию сегмента общедоступных объектов средствами VLAN, VPN-туннелирования (для территориально удалённых объектов) либо физического разделения каналов связи, изолированного от внутренних сегментов контуров безопасности;
+3. Настройку межсетевого экранирования на границе сегмента общедоступных объектов, ограничивающего его сетевое взаимодействие с внутренней инфраструктурой минимально необходимым набором протоколов (как правило, взаимодействие с процессинговым центром).
+Класс используемых средств — активное сетевое оборудование с поддержкой VLAN и VPN, межсетевые экраны.
+Иностранные: Cisco Catalyst, Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», ViPNet Coordinator и др.
+Открытый код: pfSense, OpenVPN и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F130" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети с указанием сегмента общедоступных объектов доступа и его границ;
+3. Выгрузка правил межсетевого экранирования на границе данного сегмента;
+4. Результаты тестирования (попытка сетевого взаимодействия из сегмента общедоступных объектов за пределами разрешённого протокола), подтверждающие блокирование такого взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G130" s="151" t="inlineStr">
+        <is>
+          <t>1. Отдельные общедоступные объекты доступа подключены к сети организации в обход выделенного сегмента;
+2. Межсетевое экранирование на границе сегмента общедоступных объектов допускает избыточно широкое взаимодействие с внутренней инфраструктурой;
+3. Территориально удалённые общедоступные объекты доступа подключаются по незащищённым каналам связи, без VPN-туннелирования;
+4. Состав сегмента общедоступных объектов не пересматривается при вводе новых устройств (банкоматов, терминалов).</t>
+        </is>
+      </c>
       <c r="H130" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9797,14 +10298,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D131" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мера требует организовать сетевое взаимодействие между специальными сегментами контуров безопасности — пользовательским (СМЭ.8), управления (СМЭ.9), хранения и обработки данных (СМЭ.10), а также сегментом общедоступных объектов (СМЭ.11) — и остальными внутренними сетями организации строго в соответствии с заранее утверждёнными правилами (матрица доступа протоколов и портов между сегментами). Это минимизирует риск распространения угроз между различными частями сети. </t>
-        </is>
-      </c>
-      <c r="E131" s="31" t="n"/>
-      <c r="F131" s="31" t="n"/>
-      <c r="G131" s="31" t="n"/>
+      <c r="D131" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует организовать сетевое взаимодействие между специальными сегментами контуров безопасности — пользовательским (СМЭ.8), управления (СМЭ.9), хранения и обработки данных (СМЭ.10), а также сегментом общедоступных объектов (СМЭ.11) — и остальными внутренними сетями организации строго в соответствии с заранее утверждёнными правилами (матрицей доступа протоколов и портов между сегментами).
+Главная цель меры — минимизировать риск распространения угроз между специализированными сегментами контура безопасности за счёт того, что их сетевое взаимодействие ограничено конкретным, документированным и контролируемым набором правил, а не осуществляется бесконтрольно.</t>
+        </is>
+      </c>
+      <c r="E131" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввиду того, что мера реализуется только технически, необходимо:
+1. Разработку и утверждение матрицы сетевого взаимодействия, определяющей разрешённые протоколы и порты для каждой пары взаимодействующих сегментов (пользовательского, управления, хранения и обработки данных, общедоступных объектов) и остальных внутренних сетей;
+2. Настройку правил межсетевого экранирования на границах указанных сегментов в строгом соответствии с утверждённой матрицей;
+3. Периодический технический контроль (сопоставление фактических правил межсетевого экранирования с утверждённой матрицей) соблюдения установленных правил взаимодействия.
+Класс используемых средств — межсетевые экраны, системы анализа и контроля соответствия конфигураций сетевой политике.
+Иностранные: Palo Alto Networks, Tufin и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F131" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Утверждённая матрица сетевого взаимодействия между специализированными сегментами;
+3. Результаты сопоставления фактических правил межсетевого экранирования с утверждённой матрицей;
+4. Результаты тестирования (попытка взаимодействия, не предусмотренного матрицей), подтверждающие блокирование такого взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G131" s="151" t="inlineStr">
+        <is>
+          <t>1. Матрица сетевого взаимодействия между специализированными сегментами не документирована или не актуализирована;
+2. Фактически разрешённое взаимодействие между сегментами не соответствует утверждённой матрице;
+3. Сопоставление фактических правил с матрицей проводится нерегулярно;
+4. Матрица не пересматривается при вводе новых сегментов или изменении бизнес-процессов.</t>
+        </is>
+      </c>
       <c r="H131" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9833,9 +10380,81 @@
           <t>Мера требует проверять содержимое данных, записываемых на переносные (отчуждаемые) носители информации (USB-флеш-накопители, внешние жёсткие диски, оптические диски) при их переносе между сегментами контуров безопасности и другими внутренними сетями организации. Это предотвращает перенос информации с разными уровнями конфиденциальности между сегментами.</t>
         </is>
       </c>
-      <c r="E132" s="31" t="n"/>
-      <c r="F132" s="31" t="n"/>
-      <c r="G132" s="31" t="n"/>
+      <c r="E132" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Разработку и утверждение регламента использования переносных (отчуждаемых) носителей информации при переносе данных в сегменты контуров безопасности и из них, определяющего порядок согласования такого переноса и категории допустимой к переносу информации;
+2. Установление обязанности проверки содержимого переносного носителя перед его использованием (визуальная проверка перечня файлов, сверка с заявкой на перенос информации);
+3. Определение ответственных лиц, уполномоченных согласовывать и контролировать перенос информации с использованием переносных носителей.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль дополняется:
+1. Применением специализированных станций контроля переносных носителей, обеспечивающих антивирусную проверку и контроль содержимого перед подключением носителя к оборудованию сегмента контура безопасности;
+2. Настройкой технического запрета подключения переносных носителей информации к оборудованию сегментов контуров безопасности в обход станции контроля (например, через политики контроля устройств — Device Control);
+3. Регистрацией всех фактов подключения переносных носителей и результатов их проверки для последующего анализа.
+Класс используемых средств — средства контроля устройств (Device Control), станции проверки съёмных носителей.
+Иностранные: Kaspersky Endpoint Security (Device Control), Symantec Endpoint Protection и пр.
+Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F132" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент использования переносных (отчуждаемых) носителей информации при переносе данных в сегменты контуров безопасности и из них;
+2. Заявки на перенос информации с использованием переносных носителей за выборочный период.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Скриншоты настроек станций контроля переносных носителей и политик контроля устройств (Device Control);
+2. Журналы регистрации фактов подключения переносных носителей и результатов их проверки;
+3. Результаты тестирования (попытка подключения непроверенного носителя к оборудованию сегмента контура безопасности), подтверждающие блокирование такой попытки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G132" s="151" t="inlineStr">
+        <is>
+          <t>1. Технический запрет подключения непроверенных переносных носителей реализован не на всём оборудовании сегментов контуров безопасности;
+2. Проверка содержимого переносных носителей ограничивается визуальным осмотром без применения технических средств контроля;
+3. Факты подключения переносных носителей не регистрируются;
+4. Заявки на перенос информации не сопоставляются с фактически перенесённым содержимым.</t>
+        </is>
+      </c>
       <c r="H132" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9872,14 +10491,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D134" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует организовать разделение трафика между внутренними вычислительными сетями организации и сетью Интернет с использованием средств сетевой изоляции, работающих на уровне коммутации и VLAN/VPN взаимодействие (на канальном (втором) уровне модели OSI), исключая IP-спуфинг с дальнейшем проникновением во внутреннюю сеть.</t>
-        </is>
-      </c>
-      <c r="E134" s="31" t="n"/>
-      <c r="F134" s="31" t="n"/>
-      <c r="G134" s="31" t="n"/>
+      <c r="D134" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует разделения трафика между внутренними вычислительными сетями организации и сетью Интернет с использованием средств сетевой изоляции, действующих на уровне не выше второго (канального) уровня модели OSI, — например, средствами коммутации и организации VLAN/VPN-взаимодействия, исключающими прямую маршрутизацию (IP-спуфинг) с последующим проникновением во внутреннюю сеть.
+Главная цель меры — обеспечить более строгий, по сравнению с сетевым (третьим) уровнем (см. меру СМЭ.15), уровень изоляции внутренних сетей от сети Интернет для тех уровней защиты, где риски, связанные с прямым сетевым взаимодействием на IP-уровне, признаются неприемлемыми.</t>
+        </is>
+      </c>
+      <c r="E134" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими средствами, необходимо:
+1. Реализацию сетевой изоляции внутренних вычислительных сетей и сети Интернет средствами, действующими не выше канального уровня модели OSI (организация выделенных VLAN, туннелей VPN на канальном уровне, физическое разделение сред передачи);
+2. Технический запрет прямой IP-маршрутизации между внутренними сетями и сетью Интернет в обход средств изоляции;
+3. Периодический технический контроль (тестирование, анализ конфигураций) фактического уровня реализованной изоляции.
+Класс используемых средств — активное сетевое оборудование с поддержкой VLAN и VPN на канальном уровне.
+Иностранные: Cisco Catalyst, Juniper EX и пр.
+Российские сертифицированные (ФСТЭК): «Элтекс», «С-Терра Шлюз» и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F134" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети, подтверждающая уровень (канальный) реализованной изоляции между внутренними сетями и сетью Интернет;
+3. Скриншоты (выгрузки) настроек сетевого оборудования, подтверждающие отсутствие прямой IP-маршрутизации в обход средств изоляции;
+4. Результаты тестирования, подтверждающие фактический уровень изоляции.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G134" s="151" t="inlineStr">
+        <is>
+          <t>1. Изоляция внутренних сетей и сети Интернет фактически реализована на более высоком (менее строгом) уровне, чем канальный, — например, только фильтрацией по IP-адресам;
+2. Существуют технические пути прямой IP-маршрутизации между внутренней сетью и сетью Интернет в обход средств изоляции;
+3. Периодический контроль фактического уровня изоляции не проводится;
+4. Настройки средств изоляции не пересматриваются при изменении сетевой топологии.</t>
+        </is>
+      </c>
       <c r="H134" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9904,14 +10569,60 @@
           <t>Т-Н-Н</t>
         </is>
       </c>
-      <c r="D135" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мера требует, чтобы сетевое взаимодействие между внутренними вычислительными сетями финансовой организации и сетью Интернет осуществлялось с использованием средств фильтрации на сетевом (третьем) уровне модели OSI, а не на более высоких уровнях (например, прикладном). Это обеспечивает контролируемый доступ из внутренней сети в Интернет и из Интернета во внутреннюю сеть на основе IP-адресов и портов, исключая IP-спуфинг. </t>
-        </is>
-      </c>
-      <c r="E135" s="31" t="n"/>
-      <c r="F135" s="31" t="n"/>
-      <c r="G135" s="31" t="n"/>
+      <c r="D135" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы сетевое взаимодействие между внутренними вычислительными сетями финансовой организации и сетью Интернет осуществлялось с использованием средств фильтрации на сетевом (третьем) уровне модели OSI, а не на более высоких уровнях (например, прикладном).
+Главная цель меры — обеспечить контролируемый доступ из внутренней сети в Интернет и из Интернета во внутреннюю сеть на основе IP-адресов и портов, исключающий IP-спуфинг, для тех уровней защиты, где сетевой (а не канальный, как в мере СМЭ.14) уровень изоляции признаётся достаточным.</t>
+        </is>
+      </c>
+      <c r="E135" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит организационно необременительный, полностью технический характер:
+1. Реализацию фильтрации сетевого взаимодействия между внутренними сетями и сетью Интернет средствами, действующими на сетевом (третьем) уровне модели OSI, — по IP-адресам источника и назначения, портам TCP/UDP;
+2. Настройку защиты от подмены сетевых адресов (IP-спуфинга) — фильтрацию пакетов с недопустимыми (не принадлежащими соответствующей сети) исходными адресами (anti-spoofing, uRPF);
+3. Периодический технический контроль (тестирование, анализ конфигураций) фактически реализованного уровня фильтрации сетевого взаимодействия.
+Класс используемых средств — межсетевые экраны и маршрутизаторы с функцией фильтрации на сетевом уровне и защитой от подмены адресов.
+Иностранные: Cisco ASA, Juniper SRX и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, iptables/nftables и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F135" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Скриншоты (выгрузки) настроек фильтрации сетевого взаимодействия по IP-адресам и портам;
+3. Скриншоты настроек защиты от подмены сетевых адресов (anti-spoofing);
+4. Результаты тестирования (попытка отправки пакета с поддельным исходным адресом), подтверждающие блокирование такой попытки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G135" s="151" t="inlineStr">
+        <is>
+          <t>1. Фильтрация сетевого взаимодействия с Интернетом реализована только по IP-адресам без учёта портов, что расширяет разрешённое взаимодействие сверх необходимого;
+2. Защита от подмены сетевых адресов (anti-spoofing) не настроена;
+3. Правила фильтрации не пересматриваются при изменении состава систем, взаимодействующих с сетью Интернет;
+4. Периодическое тестирование эффективности фильтрации не проводится.</t>
+        </is>
+      </c>
       <c r="H135" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9936,14 +10647,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D136" s="56" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы весь трафик, проходящий через границы внутренних вычислительных сетей организации (включая границы между сегментами контуров безопасности и внешними сетями, а также между контуром и иными внутренними сетями), контролировался межсетевыми экранами с фильтрацией не только по IP-адресам и портам (сетевой уровень), но и по содержимому пакетов и протоколам (прикладной уровень). Это необходимо для обнаружения и блокировки недопустимых команд, несанкционированных действий в разрешённых протоколах.</t>
-        </is>
-      </c>
-      <c r="E136" s="31" t="n"/>
-      <c r="F136" s="31" t="n"/>
-      <c r="G136" s="31" t="n"/>
+      <c r="D136" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы весь трафик, проходящий через границы внутренних вычислительных сетей организации (включая границы между сегментами контуров безопасности и внешними сетями, а также между контуром и иными внутренними сетями), контролировался межсетевыми экранами с фильтрацией не только по IP-адресам и портам (сетевой уровень), но и по содержимому пакетов и протоколам (прикладной уровень).
+Главная цель меры — обеспечить обнаружение и блокировку недопустимых команд и несанкционированных действий в рамках разрешённых протоколов, поскольку фильтрация только по IP-адресам и портам не защищает от атак, использующих легитимные, но незапланированные операции внутри разрешённого протокола (например, недопустимые HTTP-методы, встроенные в трафик вредоносные вложения).</t>
+        </is>
+      </c>
+      <c r="E136" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Внедрение межсетевых экранов следующего поколения (NGFW) на всех границах внутренних вычислительных сетей организации, обеспечивающих фильтрацию как на сетевом (по IP-адресам, портам), так и на прикладном уровне (по содержимому и особенностям протоколов);
+2. Настройку функционала глубокого анализа пакетов (Deep Packet Inspection) и контроля соответствия трафика заявленному протоколу (protocol conformance checking) для выявления недопустимых команд и аномалий внутри разрешённых протоколов;
+3. Регулярное обновление сигнатурных баз и правил анализа прикладного уровня межсетевого экрана для поддержания актуальности контроля.
+Класс используемых средств — межсетевые экраны следующего поколения (NGFW).
+Иностранные: Palo Alto Networks, Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate, «Ideco UTM» и др.
+Открытый код: pfSense (с ограниченным функционалом NGFW), Suricata (IDS/IPS-модуль) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F136" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами межсетевых экранов;
+2. Выгрузка правил межсетевого экранирования на всех контролируемых границах сетей;
+3. Скриншоты настроек, подтверждающие фильтрацию на прикладном уровне;
+4. Результаты тестирования (передача недопустимой команды в рамках разрешённого протокола), подтверждающие её блокирование.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G136" s="151" t="inlineStr">
+        <is>
+          <t>1. Межсетевое экранирование на прикладном уровне реализовано не на всех границах внутренних сетей;
+2. Сигнатурные базы и правила анализа прикладного уровня не обновляются на регулярной основе;
+3. Функционал глубокого анализа пакетов включён не для всех проходящих через границу протоколов;
+4. Тестирование эффективности контроля на прикладном уровне не проводится.</t>
+        </is>
+      </c>
       <c r="H136" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9967,14 +10724,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D137" s="56" t="inlineStr">
-        <is>
-          <t>Мера требует реализовать и контролировать сетевое взаимодействия между внутренними вычислительными сетями финансовой организации и сетью Интернет строго в соответствии с утверждёнными правилами доступа (например, матрица сетевого взаимодействия). Это минимизирует риск несанкционированного доступа из внешней сети во внутреннюю и предотвращения утечек данных из внутренней сети во внешнюю.</t>
-        </is>
-      </c>
-      <c r="E137" s="31" t="n"/>
-      <c r="F137" s="31" t="n"/>
-      <c r="G137" s="31" t="n"/>
+      <c r="D137" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует реализовать и контролировать сетевое взаимодействие между внутренними вычислительными сетями финансовой организации и сетью Интернет строго в соответствии с утверждёнными правилами доступа (матрицей сетевого взаимодействия).
+Главная цель меры — минимизировать риск несанкционированного доступа из внешней сети во внутреннюю и предотвратить утечки данных из внутренней сети во внешнюю за счёт того, что любое взаимодействие с сетью Интернет опирается на документированный, заранее согласованный перечень разрешённых протоколов и направлений, а не осуществляется произвольно.</t>
+        </is>
+      </c>
+      <c r="E137" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера выполняется силами технических средств защиты информации, а именно:
+1. Разработку и утверждение матрицы сетевого взаимодействия между внутренними сетями и сетью Интернет, определяющей разрешённые протоколы, порты и направления (входящее, исходящее) для каждого класса систем;
+2. Настройку правил межсетевого экранирования на границе с сетью Интернет в строгом соответствии с утверждённой матрицей;
+3. Периодический технический контроль (сопоставление фактических правил межсетевого экранирования с утверждённой матрицей) соблюдения установленных правил взаимодействия.
+Класс используемых средств — межсетевые экраны, системы анализа и контроля соответствия конфигураций сетевой политике.
+Иностранные: Palo Alto Networks, Tufin и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F137" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Утверждённая матрица сетевого взаимодействия с сетью Интернет;
+3. Результаты сопоставления фактических правил межсетевого экранирования с утверждённой матрицей;
+4. Результаты тестирования (попытка взаимодействия, не предусмотренного матрицей), подтверждающие блокирование такого взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G137" s="151" t="inlineStr">
+        <is>
+          <t>1. Матрица сетевого взаимодействия с сетью Интернет не документирована или не актуализирована;
+2. Фактически разрешённое взаимодействие с Интернетом не соответствует утверждённой матрице (присутствуют незадокументированные правила);
+3. Сопоставление фактических правил с матрицей проводится нерегулярно;
+4. Матрица не пересматривается при вводе новых систем, взаимодействующих с сетью Интернет.</t>
+        </is>
+      </c>
       <c r="H137" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -9999,14 +10802,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D138" s="56" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы внешние устройства не имели возможности получить информацию о структуре внутренней сети организации, то есть чтобы применялась технология трансляции сетевых адресов (NAT). Это позволяет замаскировать реальные IP-адреса внутренних устройств за одним или несколькими публичными адресами.</t>
-        </is>
-      </c>
-      <c r="E138" s="31" t="n"/>
-      <c r="F138" s="31" t="n"/>
-      <c r="G138" s="31" t="n"/>
+      <c r="D138" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы внешние устройства не имели возможности получить информацию о структуре внутренней сети организации — то есть чтобы применялась технология трансляции сетевых адресов (NAT), маскирующая реальные IP-адреса внутренних устройств за одним или несколькими публичными адресами.
+Главная цель меры — затруднить злоумышленнику разведку (reconnaissance) внутренней сетевой инфраструктуры организации: без сокрытия топологии внешний наблюдатель способен по прямым IP-адресам внутренних узлов оценить масштаб и структуру сети, что облегчает планирование целенаправленной атаки.</t>
+        </is>
+      </c>
+      <c r="E138" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Применение технологии трансляции сетевых адресов (NAT) на границе внутренней сети и сети Интернет, скрывающей реальные IP-адреса внутренних узлов за публичным адресом (адресами) организации;
+2. Настройку сетевого оборудования и служб (DNS, маршрутизации) таким образом, чтобы информация о внутренней адресации и топологии сети не передавалась во внешнюю сеть в открытом виде (в том числе через служебные заголовки протоколов, сообщения об ошибках);
+3. Периодический технический контроль (сканирование извне, анализ исходящего трафика) на предмет непреднамеренного раскрытия сведений о внутренней топологии сети.
+Класс используемых средств — межсетевые экраны и маршрутизаторы с функцией трансляции сетевых адресов (NAT).
+Иностранные: Cisco ASA, Juniper SRX и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, iptables/nftables и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F138" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Скриншоты (выгрузки) настроек трансляции сетевых адресов (NAT) на границе с сетью Интернет;
+3. Результаты сканирования сети организации извне, подтверждающие отсутствие видимых реальных внутренних адресов;
+4. Результаты анализа исходящего трафика на предмет утечки сведений о внутренней топологии.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G138" s="151" t="inlineStr">
+        <is>
+          <t>1. Часть внешних сервисов организации опубликована с прямым (без NAT) внутренним адресом;
+2. Служебные заголовки или сообщения об ошибках внешних сервисов раскрывают сведения о внутренней сетевой топологии;
+3. Периодическая проверка (сканирование извне) на предмет раскрытия топологии не проводится;
+4. Настройки NAT не пересматриваются при изменении состава внешних сервисов.</t>
+        </is>
+      </c>
       <c r="H138" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -10031,14 +10880,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D139" s="56" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы обмен данными между внутренней инфраструктурой организации и глобальной сетью осуществлялся только через строго определённые, минимально необходимые точки входа/выхода, что позволяет централизованно контролировать и фильтровать весь внешний трафик. Это снижает риск несанкционированного доступа к внутренним ресурсам извне.</t>
-        </is>
-      </c>
-      <c r="E139" s="31" t="n"/>
-      <c r="F139" s="31" t="n"/>
-      <c r="G139" s="31" t="n"/>
+      <c r="D139" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы обмен данными между внутренней инфраструктурой организации и глобальной сетью осуществлялся только через строго определённые, минимально необходимые точки входа/выхода, что позволяет централизованно контролировать и фильтровать весь внешний трафик.
+Главная цель меры — исключить возможность бесконтрольного, неучтённого подключения внутренних сегментов сети напрямую к сети Интернет в обход централизованных точек контроля, поскольку каждая дополнительная нерегламентированная точка выхода в Интернет — это ещё один потенциальный канал для несанкционированного доступа или утечки данных, не охваченный установленными правилами фильтрации и мониторинга (мерами СМЭ.16—СМЭ.17).</t>
+        </is>
+      </c>
+      <c r="E139" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как речь идёт о чисто технической мере, реализация включает:
+1. Определение и документальное закрепление ограниченного перечня точек подключения внутренней сети организации к сети Интернет (пограничных маршрутизаторов, межсетевых экранов);
+2. Техническое исключение иных, нерегламентированных каналов выхода в сеть Интернет (например, точек доступа Wi-Fi с прямым выходом в Интернет, модемов, мобильного интернета на серверном оборудовании);
+3. Периодический технический контроль (сканирование, анализ конфигураций сетевого оборудования) на предмет выявления несанкционированных точек подключения к сети Интернет.
+Класс используемых средств — межсетевые экраны и маршрутизаторы, средства контроля сетевого периметра.
+Иностранные: Cisco ASA, Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: pfSense, OPNsense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F139" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Схема сети с указанием утверждённых точек подключения к сети Интернет;
+3. Результаты сканирования (аудита) сети на предмет выявления несанкционированных точек выхода в Интернет;
+4. Скриншоты (выгрузки) настроек сетевого оборудования, подтверждающие отсутствие незадокументированных каналов подключения.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G139" s="151" t="inlineStr">
+        <is>
+          <t>1. Перечень утверждённых точек подключения к сети Интернет не документирован;
+2. Выявляются нерегламентированные каналы выхода в Интернет (например, через мобильные модемы или незарегистрированные точки доступа Wi-Fi);
+3. Периодический контроль (сканирование) на предмет несанкционированных точек подключения не проводится;
+4. Перечень утверждённых точек подключения не пересматривается при изменении сетевой инфраструктуры.</t>
+        </is>
+      </c>
       <c r="H139" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -10062,14 +10957,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D140" s="56" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы весь почтовый трафик между организацией и сетью Интернет проходил через строго определённые контролируемые узлы, состоящие из внешнего почтового сервера и внутреннего почтового сервера. Это снижает риск получения спам-сообщений и вредоносных вложений на внутренний сервер.</t>
-        </is>
-      </c>
-      <c r="E140" s="31" t="n"/>
-      <c r="F140" s="31" t="n"/>
-      <c r="G140" s="31" t="n"/>
+      <c r="D140" s="158" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы весь почтовый трафик между организацией и сетью Интернет проходил через строго определённые контролируемые узлы, состоящие из внешнего почтового сервера (подключённого к сети Интернет) и внутреннего почтового сервера (размещённого во внутренних сетях организации) с безопасной репликацией почтовых сообщений между ними.
+Главная цель меры — снизить риск получения спам-сообщений и вредоносных вложений непосредственно на внутренний почтовый сервер за счёт промежуточной обработки (фильтрации) корреспонденции на внешнем сервере, физически и логически отделённом от внутренней инфраструктуры, прежде чем сообщения будут реплицированы во внутренний контур.</t>
+        </is>
+      </c>
+      <c r="E140" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Развёртывание внешнего почтового сервера (шлюза), принимающего и отправляющего почту непосредственно из (в) сеть Интернет, и внутреннего почтового сервера, обслуживающего почтовые ящики пользователей организации;
+2. Настройку безопасной репликации (передачи) почтовых сообщений между внешним и внутренним почтовыми серверами по защищённому каналу связи, без предоставления внутреннему серверу прямого доступа к сети Интернет;
+3. Настройку на внешнем почтовом сервере функций фильтрации (антиспам, антивирусная проверка вложений) до передачи сообщений во внутренний контур.
+Класс используемых средств — почтовые шлюзы с функцией фильтрации (Secure Email Gateway).
+Иностранные: Proofpoint Email Security, Cisco Secure Email и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для почтовых серверов, Dr.Web Mail Security Suite и др.
+Открытый код: Postfix (совместно с SpamAssassin, ClamAV) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F140" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами почтовой инфраструктуры;
+2. Схема почтовой инфраструктуры, подтверждающая наличие раздельных внешнего и внутреннего почтовых серверов;
+3. Скриншоты настроек репликации почты между внешним и внутренним серверами;
+4. Скриншоты настроек фильтрации (антиспам, антивирусная проверка) на внешнем почтовом сервере.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G140" s="151" t="inlineStr">
+        <is>
+          <t>1. Внутренний почтовый сервер имеет прямой доступ к сети Интернет в обход внешнего сервера-шлюза;
+2. Фильтрация (антиспам, антивирусная проверка) на внешнем почтовом сервере отключена либо настроена не в полном объёме;
+3. Канал репликации почты между внешним и внутренним серверами не защищён (передача в открытом виде);
+4. Сигнатурные базы средств фильтрации почты не обновляются на регулярной основе.</t>
+        </is>
+      </c>
       <c r="H140" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -10106,14 +11047,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D142" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует фиксировать в системных журналах все события, связанные с изменением конфигураций сетевого оборудования и средств защиты, отвечающих за сегментацию сети, фильтрацию трафика и защиту вычислительных сетей (например, модификацию правил межсетевого экранирования, настроек VLAN, параметров маршрутизации, списков контроля доступа (ACL) и т. п.). Это  необходимо для выявления несанкционированных или ошибочных изменений, нарушений изоляции сегментов.</t>
-        </is>
-      </c>
-      <c r="E142" s="31" t="n"/>
-      <c r="F142" s="31" t="n"/>
-      <c r="G142" s="31" t="n"/>
+      <c r="D142" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует фиксировать в системных журналах все события, связанные с изменением конфигураций сетевого оборудования и средств защиты, отвечающих за сегментацию сети, фильтрацию трафика и защиту вычислительных сетей (модификацию правил межсетевого экранирования, настроек VLAN, параметров маршрутизации, списков контроля доступа (ACL) и т. п.).
+Главная цель меры — обеспечить возможность выявления несанкционированных или ошибочных изменений сетевой конфигурации, способных нарушить изоляцию сегментов (меры СМЭ.1—СМЭ.13) или ослабить фильтрацию трафика (меры СМЭ.3, СМЭ.16), поскольку без регистрации таких изменений факт нарушения сетевой защиты может долгое время оставаться незамеченным.</t>
+        </is>
+      </c>
+      <c r="E142" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Настройку встроенных средств аудита сетевого оборудования и средств защиты информации (межсетевых экранов, коммутаторов, маршрутизаторов), регистрирующих каждое изменение параметров настроек, влияющих на сегментацию, фильтрацию и защиту сети;
+2. Фиксацию в журнале как минимум даты и времени изменения, идентификатора администратора, выполнившего изменение, и содержания изменённого параметра (старое и новое значение);
+3. Централизованный сбор журналов изменений конфигураций сетевого оборудования и средств защиты в SIEM-системе для последующего анализа и длительного хранения.
+Класс используемых средств — системы управления событиями информационной безопасности (SIEM), системы управления конфигурациями сетевого оборудования.
+Иностранные: Splunk, SolarWinds Network Configuration Manager и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, RuSIEM и др.
+Открытый код: Wazuh, RANCID (для контроля конфигураций) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F142" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты настроек аудита на сетевом оборудовании и средствах защиты, подтверждающие регистрацию изменений конфигураций;
+3. Выгрузка журналов событий изменения конфигураций за проверяемый период;
+4. Настройки SIEM-системы, подтверждающие централизованный сбор указанных событий.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G142" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация изменений конфигураций включена не для всего сетевого оборудования и средств защиты, отвечающих за сегментацию и фильтрацию;
+2. Журналы не содержат достаточного набора атрибутов для определения того, кто и какое именно изменение внёс;
+3. Журналы изменений конфигураций не собираются централизованно, что затрудняет их анализ;
+4. Журналы не анализируются на предмет выявления несанкционированных или ошибочных изменений.</t>
+        </is>
+      </c>
       <c r="H142" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -25894,8 +26881,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -815,6 +815,9 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1492,11 +1495,7 @@
 4. Автоматическая интеграция с кадровой системой настроена не для всех информационных систем, в части из них блокирование выполняется вручную и с нарушением сроков.</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H7" s="161" t="inlineStr"/>
     </row>
     <row r="8" ht="28.5" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
@@ -1563,11 +1562,7 @@
 4. Выявленные учётные записи неопределённого назначения не блокируются либо блокируются с существенной задержкой.</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H8" s="161" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -1650,11 +1645,7 @@
 4. Ответственные сотрудники не ознакомлены с документом либо ознакомлены формально.</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H10" s="161" t="inlineStr"/>
     </row>
     <row r="11" ht="28.5" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
@@ -1722,11 +1713,7 @@
 4. Распорядитель не осведомлён о своей роли и ответственности.</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H11" s="161" t="inlineStr"/>
     </row>
     <row r="12" ht="28.5" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
@@ -1795,11 +1782,7 @@
 4. Выборочная проверка заявок выявляет случаи предоставления доступа без согласования.</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H12" s="161" t="inlineStr"/>
     </row>
     <row r="13" ht="42.75" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
@@ -1900,11 +1883,7 @@
 4. Изменения эталонной информации не регистрируются, что не позволяет установить факт и автора несанкционированного изменения.</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H13" s="161" t="inlineStr"/>
     </row>
     <row r="14" ht="42.75" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
@@ -2003,11 +1982,7 @@
 4. Результаты сверки не документируются.</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H14" s="161" t="inlineStr"/>
     </row>
     <row r="15" ht="42.75" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
@@ -2145,9 +2120,11 @@
           </r>
         </is>
       </c>
-      <c r="G16" s="36" t="inlineStr">
-        <is>
-          <t>1. Пользователям предоставлены избыточные права на изменение настроек СЗИ и АС, не соответствующие ролевой модели;                                               2. Непривилегированный пользователь может изменить настройку СЗИ или АС.</t>
+      <c r="G16" s="151" t="inlineStr">
+        <is>
+          <t>1. Пользователям предоставлены избыточные права на изменение настроек СЗИ и АС, не соответствующие ролевой модели;
+2. Непривилегированный пользователь может изменить настройку СЗИ или АС;
+3. Принудительное применение эталонных параметров настроек через централизованные политики не реализовано, из-за чего несанкционированные изменения сохраняются после перезагрузки или обновления системы.</t>
         </is>
       </c>
       <c r="H16" s="38" t="n"/>
@@ -2218,11 +2195,7 @@
 4. Отзыву подлежат только явно упомянутые в заявке права, при этом анализ полного набора прав субъекта не проводится.</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H17" s="161" t="inlineStr"/>
     </row>
     <row r="18" ht="42.75" customHeight="1">
       <c r="A18" s="39" t="inlineStr">
@@ -2322,11 +2295,7 @@
 4. Проверки фактического блокирования учётных записей с истёкшим сроком доступа не проводятся.</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H18" s="161" t="inlineStr"/>
     </row>
     <row r="19" ht="315.75" customHeight="1">
       <c r="A19" s="43" t="inlineStr">
@@ -2491,11 +2460,7 @@
 4. Технические средства настроены на выявление неактивности только по факту входа в систему, без учёта использования отдельных прав доступа (обращений к ресурсам).</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H20" s="161" t="inlineStr"/>
     </row>
     <row r="21" ht="71.25" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
@@ -2564,11 +2529,7 @@
 4. Принятые решения об отзыве прав фактически не исполняются подразделением, ответственным за управление доступом.</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H21" s="161" t="inlineStr"/>
     </row>
     <row r="22" ht="28.5" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
@@ -2664,11 +2625,7 @@
 4. Запросы на предоставление информации о правах доступа к ресурсу выполняются с нарушением установленных сроков.</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H22" s="161" t="inlineStr"/>
     </row>
     <row r="23" ht="42.75" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
@@ -2764,11 +2721,7 @@
 4. Запросы на предоставление сведений о правах субъекта выполняются с нарушением установленных сроков.</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H23" s="161" t="inlineStr"/>
     </row>
     <row r="24" ht="85.5" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
@@ -2974,11 +2927,7 @@
 4. Выявленные факты совмещения ролей не приводят к отзыву конфликтующих прав в разумный срок.</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H25" s="161" t="inlineStr"/>
     </row>
     <row r="26" ht="242.25" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
@@ -3089,11 +3038,7 @@
 4. Проверка заявок на предоставление доступа на предмет конфликта функций не проводится либо носит формальный характер.</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H26" s="161" t="inlineStr"/>
     </row>
     <row r="27" ht="85.5" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
@@ -3111,13 +3056,13 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D27" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в организации автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего привилегированными правами логического доступа, использование которых потенциально может привести к деструктивному воздействию — то есть к нарушению штатного выполнения бизнес-процессов или технологических процессов финансовой организации, а также в контроле таких действий.
+      <c r="D27" s="144" t="inlineStr">
+        <is>
+          <t>Мера охватывает организацию автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего привилегированными правами логического доступа, использование которых потенциально может привести к деструктивному воздействию, — то есть к нарушению штатного выполнения бизнес-процессов или технологических процессов финансовой организации, а также с контролем таких действий.
 Главная цель меры — обеспечить возможность выявления и расследования случаев злоупотребления привилегированными полномочиями администраторами и иным эксплуатационным персоналом, поскольку именно эта категория субъектов обладает техническими возможностями, достаточными для причинения наиболее существенного ущерба, и потому нуждается в усиленном контроле её действий.</t>
         </is>
       </c>
-      <c r="E27" s="126" t="inlineStr">
+      <c r="E27" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3128,22 +3073,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку регистрации и контроля действий привилегированных пользователей. Основные направления технической реализации:
+Реализация носит сугубо технический характер и охватывает настройку регистрации и контроля действий привилегированных пользователей. Основные направления технической реализации:
 1. Настройка расширенного аудита действий привилегированных учётных записей на уровне операционных систем, СУБД, сетевого оборудования и прикладного ПО, охватывающая операции, способные привести к деструктивному воздействию (остановка сервисов, изменение критичных конфигураций, удаление данных, отключение средств защиты);
 2. Применение специализированных систем контроля действий привилегированных пользователей (PAM, Privileged Access Management), обеспечивающих запись сессий привилегированного доступа и журналирование выполненных команд;
 3. Централизованный сбор событий, связанных с действиями эксплуатационного персонала, в SIEM-системе с настройкой правил корреляции для выявления потенциально деструктивных операций.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы контроля действий привилегированных пользователей (PAM), системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — системы контроля действий привилегированных пользователей (PAM), системы управления событиями информационной безопасности (SIEM).
 Иностранные: CyberArk PAM, BeyondTrust Privileged Remote Access и пр.
 Российские сертифицированные (ФСТЭК): «Система контроля привилегированных пользователей SafeInspect», Indeed Privileged Access Manager, MaxPatrol SIEM и др.
 Открытый код: Teleport, Wazuh и др.</t>
@@ -3168,10 +3102,11 @@
           </r>
         </is>
       </c>
-      <c r="G27" s="36" t="inlineStr">
+      <c r="G27" s="151" t="inlineStr">
         <is>
           <t>1. Регистрация действий привилегированного персонала не включена или настроена не на все критичные события;
-2. Журналирование настроено не на всех компонентах инфраструктуры, где работают привилегированные пользователи.</t>
+2. Журналирование настроено не на всех компонентах инфраструктуры, где работают привилегированные пользователи;
+3. Записи сессий привилегированного доступа не анализируются, а хранятся только для факта, без реального контроля действий.</t>
         </is>
       </c>
       <c r="H27" s="142" t="inlineStr">
@@ -3196,13 +3131,13 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D28" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в организации автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала и пользователей, обладающих правами логического доступа (в том числе в автоматизированных системах), позволяющими осуществлять операции (транзакции), приводящие к финансовым последствиям для финансовой организации, её клиентов и контрагентов, а также в контроле таких действий.
+      <c r="D28" s="144" t="inlineStr">
+        <is>
+          <t>Настоящая мера предполагает организацию автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала и пользователей, обладающих правами логического доступа (в том числе в автоматизированных системах), позволяющими осуществлять операции (транзакции), приводящие к финансовым последствиям для финансовой организации, её клиентов и контрагентов, а также с контролем таких действий.
 Главная цель меры — обеспечить полную прослеживаемость финансово значимых операций до конкретного субъекта, их совершившего, что необходимо как для расследования мошеннических операций и операционных ошибок, так и для подтверждения правомерности проведённых операций перед клиентами, контрагентами и регуляторами.</t>
         </is>
       </c>
-      <c r="E28" s="126" t="inlineStr">
+      <c r="E28" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3213,22 +3148,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку регистрации операций (транзакций), имеющих финансовые последствия, во всех АС, где такие операции выполняются. Основные направления технической реализации:
+Внедрение меры выполняется исключительно техническими средствами и предполагает настройку регистрации операций (транзакций), имеющих финансовые последствия, во всех АС, где такие операции выполняются. Основные направления технической реализации:
 1. Настройка встроенного аудита автоматизированных банковских систем (АБС) и иных прикладных систем, обеспечивающая регистрацию каждой финансово значимой операции с указанием инициировавшего её субъекта;
 2. Применение средств мониторинга активности в базах данных (DAM, Database Activity Monitoring) для регистрации операций на уровне СУБД, минуя штатный интерфейс прикладной системы;
 3. Централизованный сбор и хранение журналов финансово значимых операций в SIEM-системе с ограничением доступа персонала, чьи действия регистрируются, к этим журналам.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — средства мониторинга активности в базах данных (DAM), системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — средства мониторинга активности в базах данных (DAM), системы управления событиями информационной безопасности (SIEM).
 Иностранные: Imperva Database Security, IBM Guardium и пр.
 Российские сертифицированные (ФСТЭК): «Гарда БД», MaxPatrol SIEM, RuSIEM и др.
 Открытый код: Wazuh, Apache Kafka (для централизованного сбора событий) и др.</t>
@@ -3278,13 +3202,13 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D29" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в организации автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего правами по управлению логическим доступом (администраторов учётных записей, администраторов систем IdM, лиц, исполняющих решения распорядителей логического доступа), а также в контроле таких действий.
+      <c r="D29" s="144" t="inlineStr">
+        <is>
+          <t>В рамках данной меры организуется автоматизированная регистрация (журналирование) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего правами по управлению логическим доступом (администраторов учётных записей, администраторов систем IdM, лиц, исполняющих решения распорядителей логического доступа), а также контроль таких действий.
 Главная цель меры — обеспечить подотчётность лиц, непосредственно управляющих доступом других субъектов, поскольку от корректности и добросовестности их действий зависит достоверность всей системы управления логическим доступом, включая меры УЗП.6—УЗП.9, и злоупотребления на этом уровне способны обесценить эффективность остальных мер.</t>
         </is>
       </c>
-      <c r="E29" s="143" t="inlineStr">
+      <c r="E29" s="157" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3295,22 +3219,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку регистрации операций управления доступом. Основные направления технической реализации:
+Мера полностью реализуется на техническом уровне: её внедрение предполагает настройку регистрации операций управления доступом. Основные направления технической реализации:
 1. Настройка аудита операций управления учётными записями и правами доступа (создание, изменение, блокирование учётных записей, назначение и отзыв ролей) в системе управления доступом (IdM) и в каталоге (AD/LDAP);
 2. Централизованный сбор журналов действий администраторов учётных записей и системы IdM в SIEM-системе с ограничением доступа таких администраторов к собственным журналам аудита;
 3. Настройка регистрации действий администраторов, выполняемых в обход штатного процесса IdM (прямые изменения в целевых системах), с сопоставлением этих действий с санкционированными заявками.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM), системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — системы управления учётными записями и правами доступа (IdM), системы управления событиями информационной безопасности (SIEM).
 Иностранные: Microsoft Active Directory (аудит изменений), SailPoint IdentityIQ и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights, MaxPatrol SIEM и др.
 Открытый код: FreeIPA (аудит), Wazuh и др.</t>
@@ -3335,10 +3248,11 @@
           </r>
         </is>
       </c>
-      <c r="G29" s="36" t="inlineStr">
+      <c r="G29" s="151" t="inlineStr">
         <is>
           <t>1. Регистрация действий по управлению логическим доступом не включена или настроена не на все типы операций;
-2. Журналирование настроено не на всех системах, где осуществляется управление логическим доступом (например, забыли про резервные IdM-системы или отдельные АС).</t>
+2. Журналирование настроено не на всех системах, где осуществляется управление логическим доступом (например, забыли про резервные IdM-системы или отдельные АС);
+3. Журналы действий администраторов доступны для изменения самим администраторам, что позволяет скрыть следы несанкционированных операций.</t>
         </is>
       </c>
       <c r="H29" s="52" t="n"/>
@@ -3372,13 +3286,13 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D31" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в организации автоматизированной регистрации (журналирования) событий защиты информации, связанных непосредственно с операциями управления учётными записями и правами субъектов логического доступа — созданием, изменением, блокированием и удалением учётных записей, а также предоставлением, изменением и отзывом прав логического доступа.
+      <c r="D31" s="144" t="inlineStr">
+        <is>
+          <t>В основе меры — организация автоматизированной регистрации (журналирования) событий защиты информации, связанных непосредственно с операциями управления учётными записями и правами субъектов логического доступа: созданием, изменением, блокированием и удалением учётных записей, а также предоставлением, изменением и отзывом прав логического доступа.
 Главная цель меры — сформировать полную и достоверную доказательную базу всех изменений в составе учётных записей и прав логического доступа организации, обеспечивающую возможность контроля соответствия фактических прав эталонной информации (мера УЗП.9) и расследования инцидентов, связанных с несанкционированным изменением прав доступа.</t>
         </is>
       </c>
-      <c r="E31" s="143" t="inlineStr">
+      <c r="E31" s="157" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3389,23 +3303,12 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку автоматической регистрации всех операций управления учётными записями и правами доступа. Основные направления технической реализации:
+Поскольку организационная составляющая для этой меры не предусмотрена, реализация сводится к настройке автоматической регистрации всех операций управления учётными записями и правами доступа. Основные направления технической реализации:
 1. Использование встроенных средств аудита каталога (Active Directory, LDAP-каталог) и системы управления доступом (IdM), регистрирующих создание, изменение, блокирование и удаление учётных записей, а также предоставление и отзыв прав доступа;
 2. Централизованный сбор данных о таких операциях в SIEM-системе для последующего анализа и длительного хранения;
 3. Настройка оповещений о нештатных операциях управления учётными записями и правами (например, о предоставлении прав в обход штатного процесса согласования).
 Для каждой операции должны фиксироваться как минимум: дата и время операции, идентификатор субъекта (администратора), выполнившего операцию, идентификатор учётной записи или субъекта, в отношении которого выполнена операция, вид операции (создание, изменение, блокирование, предоставление прав, отзыв прав), результат операции.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — системы управления учётными записями и правами доступа (IdM), системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — системы управления учётными записями и правами доступа (IdM), системы управления событиями информационной безопасности (SIEM).
 Иностранные: Microsoft Active Directory, SailPoint IdentityIQ и пр.
 Российские сертифицированные (ФСТЭК): Avanpost IDM, Solar inRights, MaxPatrol SIEM и др.
 Открытый код: FreeIPA, Wazuh и др.</t>
@@ -3430,10 +3333,11 @@
           </r>
         </is>
       </c>
-      <c r="G31" s="37" t="inlineStr">
+      <c r="G31" s="164" t="inlineStr">
         <is>
           <t>1. Регистрация действий по управлению логическим доступом не включена или настроена не на все типы операций;
-2. Журналирование настроено не на всех системах, где осуществляется управление логическим доступом (например, забыли про резервные IdM-системы или отдельные АС).</t>
+2. Журналирование настроено не на всех системах, где осуществляется управление логическим доступом (например, забыли про резервные IdM-системы или отдельные АС);
+3. Журналы операций управления учётными записями и правами не анализируются на предмет выявления нештатных (несогласованных) изменений.</t>
         </is>
       </c>
       <c r="H31" s="52" t="n"/>
@@ -3454,13 +3358,13 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D32" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в организации автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего правами по управлению техническими средствами многофакторной аутентификации (МФА) — их настройкой, привязкой и отвязкой факторов аутентификации субъектов, отключением требования МФА, а также в контроле таких действий.
+      <c r="D32" s="144" t="inlineStr">
+        <is>
+          <t>Данная мера обязывает организовать автоматизированную регистрацию (журналирование) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего правами по управлению техническими средствами многофакторной аутентификации (МФА), — их настройкой, привязкой и отвязкой факторов аутентификации субъектов, отключением требования МФА, а также с контролем таких действий.
 Главная цель меры — исключить возможность необнаруживаемого ослабления защиты, обеспечиваемой многофакторной аутентификацией, поскольку получение контроля над средствами управления МФА фактически эквивалентно возможности обойти этот рубеж защиты в отношении любого субъекта, а без регистрации таких действий подобное вмешательство останется незамеченным.</t>
         </is>
       </c>
-      <c r="E32" s="143" t="inlineStr">
+      <c r="E32" s="157" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3471,22 +3375,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку регистрации операций управления средствами МФА. Основные направления технической реализации:
+Технически данная мера реализуется через настройку регистрации операций управления средствами МФА. Основные направления технической реализации:
 1. Настройка аудита средств (сервера, платформы) многофакторной аутентификации, регистрирующего операции привязки и отвязки факторов аутентификации (токенов, приложений-аутентификаторов, биометрических данных) к учётным записям субъектов, а также операции изменения политик МФА и временного отключения требования дополнительного фактора;
 2. Централизованный сбор журналов действий администраторов средств МФА в SIEM-системе с ограничением доступа таких администраторов к собственным журналам аудита;
 3. Настройка оповещений о критичных операциях (отключение МФА для учётной записи, массовая отвязка факторов) для оперативного реагирования подразделения информационной безопасности.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — средства многофакторной аутентификации, системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — средства многофакторной аутентификации, системы управления событиями информационной безопасности (SIEM).
 Иностранные: RSA SecurID, Duo Security и пр.
 Российские сертифицированные (ФСТЭК): «Мультифактор», JaCarta (программные компоненты), MaxPatrol SIEM и др.
 Открытый код: privacyIDEA, Wazuh и др.</t>
@@ -3511,10 +3404,11 @@
           </r>
         </is>
       </c>
-      <c r="G32" s="36" t="inlineStr">
+      <c r="G32" s="151" t="inlineStr">
         <is>
           <t>1. Регистрация действий по управлению MFA не включена или настроена не на все типы операций;
-2. Журналирование настроено не на всех MFA-системах (например, забыли про резервные MFA-серверы или отдельные компоненты).</t>
+2. Журналирование настроено не на всех MFA-системах (например, забыли про резервные MFA-серверы или отдельные компоненты);
+3. Оповещения о критичных операциях управления МФА (отключение МФА, массовая отвязка факторов) не настроены.</t>
         </is>
       </c>
       <c r="H32" s="52" t="n"/>
@@ -3535,14 +3429,14 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D33" s="124" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в организации автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего правами по изменению параметров настроек средств и систем защиты информации, а также параметров настроек автоматизированных систем (АС), связанных с защитой информации, и в контроле таких действий.
+      <c r="D33" s="144" t="inlineStr">
+        <is>
+          <t>Мера сводится к организации автоматизированной регистрации (журналирования) событий защиты информации, связанных с действиями эксплуатационного персонала, обладающего правами по изменению параметров настроек средств и систем защиты информации, а также параметров настроек автоматизированных систем (АС), связанных с защитой информации, а также с контролем таких действий.
 Мера дополняет меру УЗП.11 (техническое исключение бесконтрольного изменения таких параметров пользователями): если УЗП.11 закрывает возможность несанкционированного изменения со стороны обычных пользователей, то настоящая мера обеспечивает регистрацию и контроль изменений, правомерно вносимых уполномоченным эксплуатационным персоналом (администраторами).
 Главная цель меры — обеспечить полную прослеживаемость изменений конфигурации СЗИ и защищаемых параметров АС, вносимых администраторами, поскольку у этой категории персонала есть законные полномочия на такие изменения, но их бесконтрольное использование (в том числе ошибочное) способно снизить уровень защищённости информационной инфраструктуры.</t>
         </is>
       </c>
-      <c r="E33" s="143" t="inlineStr">
+      <c r="E33" s="157" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3553,22 +3447,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку автоматической регистрации операций изменения параметров настроек СЗИ и АС, выполняемых эксплуатационным персоналом. Основные направления технической реализации:
+Реализация меры целиком лежит в технической плоскости: необходима настройка автоматической регистрации операций изменения параметров настроек СЗИ и АС, выполняемых эксплуатационным персоналом. Основные направления технической реализации:
 1. Использование встроенных средств журналирования средств и систем защиты информации (антивирусов, межсетевых экранов, СКЗИ, средств защиты от НСД), регистрирующих изменения параметров их настроек с указанием субъекта, внёсшего изменение;
 2. Использование систем централизованного управления конфигурациями (например, групповых политик, систем управления СЗИ), в которых все изменения защищаемых параметров настроек автоматически фиксируются в журнале системы управления;
 3. Централизованный сбор журналов изменения параметров настроек СЗИ и АС в SIEM-системе с настройкой правил выявления изменений, внесённых в обход регламентированного порядка.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — средства защиты от несанкционированного доступа (СЗИ от НСД), системы управления конфигурациями, системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — средства защиты от несанкционированного доступа (СЗИ от НСД), системы управления конфигурациями, системы управления событиями информационной безопасности (SIEM).
 Иностранные: Tripwire Enterprise, Microsoft Group Policy (AD GPO) и пр.
 Российские сертифицированные (ФСТЭК): Secret Net Studio, Dallas Lock 8.0-К, MaxPatrol SIEM и др.
 Открытый код: Osquery, OSSEC, Wazuh и др.</t>
@@ -3592,10 +3475,11 @@
           </r>
         </is>
       </c>
-      <c r="G33" s="36" t="inlineStr">
+      <c r="G33" s="151" t="inlineStr">
         <is>
           <t>1. Регистрация изменений параметров настроек не включена или настроена не на все типы операций;
-2. Журналирование настроено не на всех СЗИ и АС (например, забыли про резервные системы или отдельные компоненты инфраструктуры).</t>
+2. Журналирование настроено не на всех СЗИ и АС (например, забыли про резервные системы или отдельные компоненты инфраструктуры);
+3. Журналы изменений параметров настроек не сопоставляются с санкционированными заявками на изменение конфигурации.</t>
         </is>
       </c>
       <c r="H33" s="52" t="n"/>
@@ -3616,16 +3500,15 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D34" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Суть меры заключается в организации автоматизированной регистрации (журналирования) всех событий, связанных с действиями эксплуатационного персонала (администраторы, сотрудники ИБ, операторы АБС и т.д.), обладающего правами по управлению криптографическими ключами, а также в контроле этих действий. 
+      <c r="D34" s="153" t="inlineStr">
+        <is>
+          <t>Мера предусматривает организацию автоматизированной регистрации (журналирования) всех событий, связанных с действиями эксплуатационного персонала (администраторы, сотрудники ИБ, операторы АБС и т. д.), обладающего правами по управлению криптографическими ключами, а также в контроле этих действий.
 Регистрация событий означает, что каждое действие такого персонала с криптографическими ключами автоматически фиксируется в журнале регистрации событий.
-Контроль действий означает, что зарегистрированные события должны анализироваться на предмет выявления аномалий, подозрительных или несанкционированных действий (например, попытки несанкционированной генерации или экспорта ключей вне установленного регламента, действия в нерабочее время и т.п.).
-Главная цель меры — обеспечить прозрачность, подотчётность и контролируемость всех операций с криптографическими ключами.
-</t>
-        </is>
-      </c>
-      <c r="E34" s="126" t="inlineStr">
+Контроль действий означает, что зарегистрированные события должны анализироваться на предмет выявления аномалий, подозрительных или несанкционированных действий (например, попытки несанкционированной генерации или экспорта ключей вне установленного регламента, действия в нерабочее время и т. п.).
+Главная цель меры — обеспечить прозрачность, подотчётность и контролируемость всех операций с криптографическими ключами.</t>
+        </is>
+      </c>
+      <c r="E34" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3636,23 +3519,12 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку автоматической регистрации операций управления криптографическими ключами. Основные направления технической реализации:
+Мера реализуется исключительно техническими средствами защиты информации: необходима настройка автоматической регистрации операций управления криптографическими ключами. Основные направления технической реализации:
 1. Использование встроенных средств аудита криптографических провайдеров и средств криптографической защиты информации (СКЗИ), регистрирующих операции генерации, распределения (передачи), смены, вывода из действия (компрометации) и уничтожения криптографических ключей;
 2. Использование систем централизованного управления ключевой информацией (Key Management System) для организаций с развитой криптографической инфраструктурой, обеспечивающих единый журнал операций со всеми ключами независимо от использующей их системы;
 3. Централизованный сбор журналов операций управления криптографическими ключами в SIEM-системе с ограничением доступа к этим журналам лицам, ответственным за управление ключами.
 Для каждой операции с криптографическим ключом должны фиксироваться как минимум: дата и время операции, идентификатор ключа, тип операции (генерация, распределение, смена, компрометация, уничтожение), идентификатор субъекта, выполнившего операцию, результат операции.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <t xml:space="preserve">
-Класс средств — средства криптографической защиты информации (СКЗИ), системы управления ключевой информацией.
+Класс используемых средств — средства криптографической защиты информации (СКЗИ), системы управления ключевой информацией.
 Иностранные: Thales CipherTrust Manager, HashiCorp Vault (Enterprise) и пр.
 Российские сертифицированные (ФСТЭК): ViPNet Coordinator, «С-Терра Шлюз» и др.
 Открытый код: HashiCorp Vault (Community Edition), EJBCA и др.</t>
@@ -3915,11 +3787,7 @@
 4. Технически возможен обход МФА через альтернативные точки входа (legacy-интерфейсы, API), не охваченные требованием.</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H38" s="161" t="inlineStr"/>
     </row>
     <row r="39" ht="28.5" customHeight="1">
       <c r="A39" s="20" t="inlineStr">
@@ -3991,11 +3859,7 @@
 4. Отсутствует контроль за тем, что все административные интерфейсы (включая консольный и физический доступ) охвачены требованием аутентификации.</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H39" s="161" t="inlineStr"/>
     </row>
     <row r="40" ht="28.5" customHeight="1">
       <c r="A40" s="20" t="inlineStr">
@@ -4068,11 +3932,7 @@
 4. Журналы прохождения МФА эксплуатационным персоналом не анализируются на предмет аномалий (например, множественных неуспешных попыток).</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H40" s="161" t="inlineStr"/>
     </row>
     <row r="41" ht="28.5" customHeight="1">
       <c r="A41" s="20" t="inlineStr">
@@ -4292,11 +4152,7 @@
 4. Компрометация сертификата устройства не приводит к его оперативному отзыву.</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H43" s="161" t="inlineStr"/>
     </row>
     <row r="44" ht="28.5" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
@@ -4364,11 +4220,7 @@
 4. Проверка соблюдения требования на нестандартных интерфейсах не проводится.</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H44" s="161" t="inlineStr"/>
     </row>
     <row r="45" ht="57" customHeight="1">
       <c r="A45" s="20" t="inlineStr">
@@ -4436,11 +4288,7 @@
 4. Периодическая проверка отсутствия заводских учётных данных не проводится, факт их использования выявляется только по результатам инцидента или внешнего аудита.</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H45" s="161" t="inlineStr"/>
     </row>
     <row r="46" ht="57" customHeight="1">
       <c r="A46" s="20" t="inlineStr">
@@ -4650,11 +4498,7 @@
 4. Виртуальные АРМ (в инфраструктуре VDI) не учитываются при определении количества активных сессий наравне с физическими.</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H48" s="161" t="inlineStr"/>
     </row>
     <row r="49" ht="185.25" customHeight="1">
       <c r="A49" s="20" t="inlineStr">
@@ -4859,11 +4703,7 @@
 3. Тестирование фактической невозможности обхода повторной аутентификации не проводится.</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H51" s="161" t="inlineStr"/>
     </row>
     <row r="52" ht="242.25" customHeight="1">
       <c r="A52" s="55" t="inlineStr">
@@ -5015,11 +4855,7 @@
 4. Резервные копии баз данных и конфигурационных файлов, содержащие аутентификационные данные, не защищены так же строго, как основные системы хранения.</t>
         </is>
       </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H54" s="161" t="inlineStr"/>
     </row>
     <row r="55" ht="199.5" customHeight="1">
       <c r="A55" s="20" t="inlineStr">
@@ -5166,11 +5002,7 @@
 4. Отчётность о соблюдении срока действия паролей не формируется, нарушения выявляются только по факту инцидента.</t>
         </is>
       </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H56" s="161" t="inlineStr"/>
     </row>
     <row r="57" ht="142.5" customHeight="1">
       <c r="A57" s="20" t="inlineStr">
@@ -5450,11 +5282,7 @@
 3. Отдельные унаследованные системы не поддерживают проверку сложности пароля, компенсирующие меры не приняты.</t>
         </is>
       </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H60" s="161" t="inlineStr"/>
     </row>
     <row r="61" ht="42.75" customHeight="1">
       <c r="A61" s="20" t="inlineStr">
@@ -5521,11 +5349,7 @@
 4. Требование не пересматривается и не актуализируется с учётом современных методов подбора паролей (атаки по маскам, использование утёкших баз данных).</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H61" s="161" t="inlineStr"/>
     </row>
     <row r="62" ht="199.5" customHeight="1">
       <c r="A62" s="20" t="inlineStr">
@@ -5597,11 +5421,7 @@
 4. Пользователи не осведомлены о наличии функции самостоятельной смены пароля и продолжают обращаться к администраторам.</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H62" s="161" t="inlineStr"/>
     </row>
     <row r="63" ht="28.5" customHeight="1">
       <c r="A63" s="20" t="inlineStr">
@@ -5669,11 +5489,7 @@
 4. Факты обращения к резервным копиям (в аварийных ситуациях) не фиксируются документально.</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H63" s="161" t="inlineStr"/>
     </row>
     <row r="64" ht="42.75" customHeight="1">
       <c r="A64" s="20" t="inlineStr">
@@ -5743,11 +5559,7 @@
 4. Журнал учёта доступа к резервным копиям не ведётся или ведётся формально, не позволяя восстановить историю обращений.</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H64" s="161" t="inlineStr"/>
     </row>
     <row r="65" ht="42.75" customHeight="1">
       <c r="A65" s="20" t="inlineStr">
@@ -5967,11 +5779,7 @@
 4. Тестирование фактического срабатывания механизма авторизации не проводится.</t>
         </is>
       </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H68" s="161" t="inlineStr"/>
     </row>
     <row r="69" ht="42.75" customHeight="1">
       <c r="A69" s="20" t="inlineStr">
@@ -6043,11 +5851,7 @@
 4. Настройки метода разграничения доступа не пересматриваются при изменении состава обрабатываемой информации.</t>
         </is>
       </c>
-      <c r="H69" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H69" s="161" t="inlineStr"/>
     </row>
     <row r="70" ht="28.5" customHeight="1">
       <c r="A70" s="20" t="inlineStr">
@@ -6119,11 +5923,7 @@
 4. Одному субъекту назначено избыточное количество ролей без документированного обоснования служебной необходимости.</t>
         </is>
       </c>
-      <c r="H70" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H70" s="161" t="inlineStr"/>
     </row>
     <row r="71" ht="42.75" customHeight="1">
       <c r="A71" s="20" t="inlineStr">
@@ -6195,11 +5995,7 @@
 4. Соответствие фактически предоставленных типов доступа установленным правилам не проверяется на регулярной основе.</t>
         </is>
       </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H71" s="161" t="inlineStr"/>
     </row>
     <row r="72" ht="57" customHeight="1">
       <c r="A72" s="20" t="inlineStr">
@@ -6300,11 +6096,7 @@
 4. Запрет не доведён до сведения эксплуатационного персонала.</t>
         </is>
       </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H72" s="161" t="inlineStr"/>
     </row>
     <row r="73" ht="57" customHeight="1">
       <c r="A73" s="20" t="inlineStr">
@@ -6376,11 +6168,7 @@
 4. Выявленные случаи наличия у пользователя прав локального администратора не устраняются в разумный срок.</t>
         </is>
       </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H73" s="161" t="inlineStr"/>
     </row>
     <row r="74" ht="225" customHeight="1">
       <c r="A74" s="20" t="inlineStr">
@@ -6448,11 +6236,7 @@
 4. Пользователи не проинформированы о значении данного уведомления и о необходимых действиях в случае обнаружения несоответствия.</t>
         </is>
       </c>
-      <c r="H74" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H74" s="161" t="inlineStr"/>
     </row>
     <row r="75" ht="171" customHeight="1">
       <c r="A75" s="20" t="inlineStr">
@@ -6518,11 +6302,7 @@
 3. Тестирование состава действий, доступных до аутентификации, не проводится на регулярной основе.</t>
         </is>
       </c>
-      <c r="H75" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H75" s="161" t="inlineStr"/>
     </row>
     <row r="76" ht="28.5" customHeight="1">
       <c r="A76" s="20" t="inlineStr">
@@ -6676,11 +6456,7 @@
 4. Отсутствуют настроенные оповещения о превышении порогового числа неуспешных попыток аутентификации в единицу времени.</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H78" s="161" t="inlineStr"/>
     </row>
     <row r="79" ht="156.75" customHeight="1">
       <c r="A79" s="20" t="inlineStr">
@@ -6754,11 +6530,7 @@
 4. Журналы хранятся менее установленного срока, что не позволяет предоставить свидетельства за требуемый период.</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H79" s="161" t="inlineStr"/>
     </row>
     <row r="80" ht="171" customHeight="1">
       <c r="A80" s="20" t="inlineStr">
@@ -6829,11 +6601,7 @@
 4. Журналы событий сессий разных систем не собираются централизованно.</t>
         </is>
       </c>
-      <c r="H80" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H80" s="161" t="inlineStr"/>
     </row>
     <row r="81" ht="142.5" customHeight="1">
       <c r="A81" s="20" t="inlineStr">
@@ -6904,11 +6672,7 @@
 4. Журналы запуска программных сервисов хранятся менее установленного срока.</t>
         </is>
       </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H81" s="161" t="inlineStr"/>
     </row>
     <row r="82" ht="185.25" customHeight="1">
       <c r="A82" s="20" t="inlineStr">
@@ -6982,11 +6746,7 @@
 4. Журналы событий изменения аутентификационных данных хранятся менее установленного срока.</t>
         </is>
       </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H82" s="161" t="inlineStr"/>
     </row>
     <row r="83" ht="42.75" customHeight="1">
       <c r="A83" s="20" t="inlineStr">
@@ -7021,7 +6781,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Мера реализуется исключительно организационными методами и предполагает:
+Мера не предусматривает технической составляющей и целиком опирается на организационные меры:
 1. Фиксацию в журнале (реестре) инцидентов, связанных с компрометацией аутентификационных данных (см. также меру РД.29), не только факта самой компрометации, но и перечня конкретных действий, выполненных субъектом и вовлечёнными сотрудниками в связи с этим случаем;
 2. Указание в такой записи даты и времени выполнения каждого действия (сообщение о компрометации, смена аутентификационных данных, иные реагирующие мероприятия) и ответственного за его выполнение;
 3. Периодический контроль подразделением информационной безопасности полноты и своевременности регистрации предусмотренных действий по зафиксированным случаям компрометации.</t>
@@ -7051,11 +6811,7 @@
 3. Периодический контроль полноты и своевременности регистрации таких действий не проводится.</t>
         </is>
       </c>
-      <c r="H83" s="7" t="inlineStr">
-        <is>
-          <t>Нет недостатков.</t>
-        </is>
-      </c>
+      <c r="H83" s="161" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
@@ -7269,7 +7025,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает:
+Со стороны организационных мер требуется:
 1. Определение во внутреннем нормативном документе порядка допуска лиц, не являющихся работниками организации (представителей контролирующих органов, аудиторов, курьеров, сотрудников подрядных и клининговых организаций), к самостоятельному физическому доступу в помещения;
 2. Ведение журнала учёта таких лиц с фиксацией даты, времени, цели визита и лица, санкционировавшего доступ;
 3. Установление ограниченного срока действия временного пропуска, выдаваемого таким лицам, и порядка его возврата (аннулирования) по окончании визита или работ.</t>
@@ -7368,7 +7124,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает:
+На организационном уровне необходимо:
 1. Определение во внутреннем нормативном документе порядка допуска технического (вспомогательного) персонала (обслуживающего инженерные системы, кондиционирование, электропитание и т. п.) к самостоятельному физическому доступу в помещения;
 2. Ведение учёта выдачи и возврата ключей или карт доступа техническому персоналу;
 3. Периодический пересмотр состава помещений и зон, доступных техническому персоналу, на предмет соответствия фактически выполняемым работам.</t>
@@ -7492,12 +7248,11 @@
           </r>
         </is>
       </c>
-      <c r="G89" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Отсутствует документ регламентирующий правила предоставления физического доступа;
+      <c r="G89" s="153" t="inlineStr">
+        <is>
+          <t>1. Отсутствует документ, регламентирующий правила предоставления физического доступа;
 2. Нарушение процедуры сопровождения, когда контролируемое лицо на короткое время остаётся без присмотра;
-3.  Отсутствие чёткого определения уполномоченных сотрудников, имеющих право осуществлять сопровождение.                           
-</t>
+3. Отсутствие чёткого определения уполномоченных сотрудников, имеющих право осуществлять сопровождение.</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7700,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Мера реализуется исключительно организационными методами и предполагает:
+Ввиду организационного характера меры необходимо:
 1. Определение требования об обязательном размещении серверного и сетевого оборудования в запираемых стоечных шкафах при проектировании и вводе в эксплуатацию серверных и технических помещений;
 2. Проведение инвентаризации существующего оборудования на предмет соответствия данному требованию с составлением плана устранения выявленных несоответствий;
 3. Контроль соблюдения требования при вводе в эксплуатацию нового оборудования.</t>
@@ -8010,7 +7765,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает:
+В организационном плане мера сводится к:
 1. Определение перечня лиц, имеющих право доступа к запираемым серверным стоечным шкафам (ключи, коды доступа);
 2. Ведение учёта выдачи ключей (кодов доступа) к шкафам и фактов открытия шкафов;
 3. Периодический контроль соответствия фактического круга лиц, имеющих доступ к шкафам, установленному перечню.</t>
@@ -8075,7 +7830,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+Учитывая сугубо технический характер меры, необходимо:
 1. Настройку сервера (базы данных) СКУД на хранение архива событий физического доступа в течение срока не менее трёх лет;
 2. Обеспечение достаточной ёмкости системы хранения данных с учётом фактического объёма событий, генерируемых СКУД, и выбранного срока хранения;
 3. Организацию резервного копирования архива событий СКУД для защиты от утраты данных вследствие сбоя оборудования.
@@ -8440,7 +8195,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Мера реализуется исключительно организационными методами и предполагает:
+Организационно мера реализуется через:
 1. Разработку и утверждение регламента периодического контроля состояния общедоступных объектов доступа (банкоматов, платёжных терминалов, общедоступных рабочих мест) на предмет несанкционированных изменений в аппаратном обеспечении (скиммеры, посторонние устройства) и программном обеспечении;
 2. Проведение контрольных мероприятий (визуальный осмотр, проверку целостности пломб, сверку версий ПО) с определённой периодичностью, охватывающей все общедоступные объекты доступа;
 3. Оформление результатов каждой проверки актом с фиксацией выявленных отклонений;
@@ -8472,11 +8227,7 @@
 3. Результаты контроля не фиксируются, что делает невозможным подтверждение выполнения меры при проверке.</t>
         </is>
       </c>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>Не полные свидетельства.</t>
-        </is>
-      </c>
+      <c r="H104" s="161" t="inlineStr"/>
     </row>
     <row r="105" ht="142.5" customHeight="1">
       <c r="A105" s="20" t="inlineStr">
@@ -8594,7 +8345,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+Будучи технической по своей природе, мера предполагает:
 1. Оснащение входных дверей помещений, в которых расположены объекты доступа, системой контроля и управления доступом (СКУД), автоматически регистрирующей каждый факт входа и выхода;
 2. Настройку СКУД на фиксацию как минимум даты, времени, идентификатора субъекта и точки доступа для каждого события входа (выхода);
 3. Централизованный сбор и хранение указанных событий для последующего анализа, расследования инцидентов и предоставления свидетельств проверяющим.
@@ -8777,7 +8528,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает:
+С организационной точки зрения предполагается:
 1. Ведение реестра (описи) объектов доступа с указанием типа объекта, инвентарного номера, места размещения (сегмента сети), ответственного подразделения и статуса эксплуатации;
 2. Установление обязанности подразделений, вводящих в эксплуатацию новые объекты доступа, регистрировать их в реестре до подключения к вычислительной сети организации;
 3. Периодическую сверку реестра с фактическим составом объектов доступа и актуализацию записей при выводе объектов из эксплуатации.</t>
@@ -9179,7 +8930,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Организационная реализация предполагает:
+Организационные шаги включают:
 1. Разработку и утверждение регламента проведения контроля фактического состава эксплуатируемых объектов доступа и их размещения в сегментах вычислительных сетей, с указанием периодичности контроля, перечня проверяемых типов объектов и ответственных лиц;
 2. Проведение периодических проверок фактического состава объектов доступа и их размещения с установленной периодичностью;
 3. Оформление результатов каждой проверки актом с фиксацией выявленных расхождений и принятых мер по их устранению.</t>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -818,6 +818,9 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -10888,14 +10891,61 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D144" s="34" t="inlineStr">
-        <is>
-          <t>Между разными контурами безопасности (например, контуром обработки платежей и контуром обычной офисной сети) не должно быть незаметного сетевого взаимодействия — должен как минимум выявляться сам факт такой активности. В ином случае это может привести к возникновению скомпрометированного хоста в офисной сети, который  установит канал связи с системами платёжного контура в обход политики сегментации или туннелирование через разрешённый протокол для скрытого перемещения между контурами.</t>
-        </is>
-      </c>
-      <c r="E144" s="31" t="n"/>
-      <c r="F144" s="31" t="n"/>
-      <c r="G144" s="31" t="n"/>
+      <c r="D144" s="144" t="inlineStr">
+        <is>
+          <t>Между разными контурами безопасности (например, контуром обработки платежей и контуром обычной офисной сети) не должно быть незаметного сетевого взаимодействия — как минимум должен выявляться сам факт такой активности, поскольку в противном случае скомпрометированный хост в офисной сети способен установить канал связи с системами платёжного контура в обход политики сегментации либо организовать туннелирование через разрешённый протокол для скрытого перемещения между контурами.
+Главная цель меры — обнаруживать попытки обхода сетевой сегментации (мер СМЭ.1—СМЭ.13) на раннем этапе, поскольку сама по себе сегментация не гарантирует полной непроницаемости границ между контурами: часть каналов обхода (туннелирование, использование разрешённых протоколов не по назначению) не блокируется межсетевым экраном и выявляется только поведенческим анализом трафика.</t>
+        </is>
+      </c>
+      <c r="E144" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Развёртывание средств анализа сетевого трафика (NTA, Network Traffic Analysis) или систем обнаружения вторжений (IDS) на границах между сегментами разных контуров безопасности;
+2. Формирование профиля типового («нормального») сетевого взаимодействия между контурами на основе утверждённой матрицы сетевого взаимодействия (мера СМЭ.4) для последующего выявления отклонений от него;
+3. Настройку правил и сигнатур выявления аномалий — нехарактерных протоколов, туннелирования, обращений к нетипичным портам, всплесков объёма трафика между контурами;
+4. Централизованный сбор выявленных событий в SIEM-системе с настройкой оповещения подразделения информационной безопасности.
+Класс используемых средств — системы анализа сетевого трафика (NTA), системы обнаружения вторжений (IDS).
+Иностранные: Cisco Stealthwatch, Darktrace, Vectra AI и пр.
+Российские сертифицированные (ФСТЭК): PT NAD, Kaspersky KATA/KUMA, «Гарда NDR» и др.
+Открытый код: Zeek, Suricata и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F144" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек средств анализа трафика (NTA/IDS), подтверждающие контроль трафика между сегментами разных контуров безопасности;
+3. Журналы (отчёты) о выявленных аномалиях межконтурного сетевого взаимодействия за проверяемый период;
+4. Результаты тестирования (имитация нетипичного межконтурного взаимодействия), подтверждающие срабатывание средств выявления аномалий.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G144" s="151" t="inlineStr">
+        <is>
+          <t>1. Средства анализа трафика между контурами безопасности не развёрнуты либо развёрнуты не на всех границах контуров;
+2. Профиль типового межконтурного взаимодействия не сформирован, что не позволяет достоверно отличить аномалию от штатного трафика;
+3. Выявленные аномалии не анализируются оперативно, оповещения по ним не настроены;
+4. Правила выявления аномалий не пересматриваются при изменении состава систем и характера межконтурного взаимодействия.</t>
+        </is>
+      </c>
       <c r="H144" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -10919,14 +10969,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D145" s="34" t="inlineStr">
-        <is>
-          <t>Требуется выявлять аномалии именно на границе с интернетом — отдельно от внутренней межконтурной активности (ВСА.1), во избежание на контуре command-and-control трафика скомпрометированного хоста к внешнему серверу управления, который остаётся незамеченным при отсутствии анализа поведения на границе с интернетом, и чтобы не допустить эксфильтрацию данных наружу через нетипичный канал (например, DNS-туннель).</t>
-        </is>
-      </c>
-      <c r="E145" s="31" t="n"/>
-      <c r="F145" s="31" t="n"/>
-      <c r="G145" s="31" t="n"/>
+      <c r="D145" s="144" t="inlineStr">
+        <is>
+          <t>Требуется выявлять аномалии именно на границе с сетью Интернет — отдельно от анализа внутренней межконтурной активности (мера ВСА.1), чтобы не допустить, что command-and-control трафик скомпрометированного хоста к внешнему серверу управления останется незамеченным при отсутствии анализа поведения на границе с Интернетом, а также чтобы исключить эксфильтрацию данных наружу через нетипичный канал (например, DNS-туннелирование).
+Главная цель меры — обеспечить поведенческий контроль трафика на самой рискованной границе сети — с публичным Интернетом, поскольку межсетевое экранирование (меры СМЭ.15—СМЭ.19) фильтрует взаимодействие по формальным признакам (адрес, порт, протокол), но не способно самостоятельно распознать вредоносную активность, замаскированную под разрешённый, легитимно выглядящий трафик.</t>
+        </is>
+      </c>
+      <c r="E145" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими средствами, необходимо:
+1. Развёртывание средств анализа сетевого трафика (NTA) или систем обнаружения вторжений (IDS) на границе внутренних вычислительных сетей организации с сетью Интернет;
+2. Настройку правил и сигнатур выявления аномального исходящего и входящего трафика — обращений к известным command-and-control серверам, нетипичных объёмов передачи данных, использования протоколов туннелирования (DNS-туннели, HTTP-туннели) для скрытой передачи данных;
+3. Централизованный сбор выявленных событий в SIEM-системе с настройкой оповещения подразделения информационной безопасности о выявленных аномалиях.
+Класс используемых средств — системы анализа сетевого трафика (NTA), системы обнаружения вторжений (IDS).
+Иностранные: Darktrace, Vectra AI, Cisco Stealthwatch и пр.
+Российские сертифицированные (ФСТЭК): PT NAD, Kaspersky KATA/KUMA и др.
+Открытый код: Zeek, Suricata и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F145" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек средств анализа трафика на границе с сетью Интернет;
+3. Журналы (отчёты) о выявленных аномалиях трафика с сетью Интернет за проверяемый период;
+4. Результаты тестирования (имитация обращения к типовому индикатору компрометации — тестовому C2-домену), подтверждающие срабатывание средств выявления.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G145" s="151" t="inlineStr">
+        <is>
+          <t>1. Средства анализа трафика с сетью Интернет развёрнуты не на всех точках подключения (см. также меру СМЭ.19);
+2. Сигнатуры и правила выявления аномального трафика не обновляются на регулярной основе;
+3. Выявленные аномалии не анализируются оперативно, реагирование затягивается;
+4. Анализ ограничивается только объёмом трафика, без учёта его характера (типа протокола, признаков туннелирования).</t>
+        </is>
+      </c>
       <c r="H145" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -10950,14 +11046,61 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D146" s="34" t="inlineStr">
-        <is>
-          <t>Банкоматы и платёжные терминалы физически доступны неограниченному кругу лиц и представляют собой отдельный, особо чувствительный сегмент — их взаимодействие с интернетом должно контролироваться отдельно от общего периметра во избежание компрометации банкомата/терминала, которая может использоваться для установления канала с внешним сервером атакующего.</t>
-        </is>
-      </c>
-      <c r="E146" s="31" t="n"/>
-      <c r="F146" s="31" t="n"/>
-      <c r="G146" s="31" t="n"/>
+      <c r="D146" s="144" t="inlineStr">
+        <is>
+          <t>Банкоматы и платёжные терминалы физически доступны неограниченному кругу лиц и представляют собой отдельный, особо чувствительный сегмент (см. меру СМЭ.11) — их взаимодействие с сетью Интернет должно контролироваться отдельно от общего периметра, чтобы не допустить, что компрометация банкомата (терминала) будет использована для установления канала связи с внешним сервером атакующего.
+Главная цель меры — учесть специфику общедоступных объектов доступа при выявлении сетевых аномалий: типовой («нормальный») профиль их сетевого взаимодействия существенно уже, чем у обычных пользовательских или серверных сегментов (как правило, ограничивается обменом с процессинговым центром), что позволяет выявлять отклонения точнее и быстрее, чем при общем анализе интернет-трафика организации.</t>
+        </is>
+      </c>
+      <c r="E146" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввиду того, что мера реализуется только технически, необходимо:
+1. Развёртывание средств анализа сетевого трафика (NTA) или систем обнаружения вторжений (IDS) на границе сегмента общедоступных объектов доступа (мера СМЭ.11) с сетью Интернет;
+2. Формирование узкого («эталонного») профиля разрешённого сетевого взаимодействия общедоступных объектов доступа (как правило, ограниченного обменом с процессинговым центром) для точного выявления отклонений;
+3. Настройку правил выявления аномалий — обращений к посторонним (не входящим в эталонный профиль) адресам, нетипичных протоколов, попыток установления исходящих соединений, не связанных с процессингом операций;
+4. Централизованный сбор выявленных событий в SIEM-системе с настройкой приоритетного оповещения ввиду критичности данного сегмента.
+Класс используемых средств — системы анализа сетевого трафика (NTA), системы обнаружения вторжений (IDS).
+Иностранные: Darktrace, Vectra AI и пр.
+Российские сертифицированные (ФСТЭК): PT NAD, Kaspersky KATA/KUMA и др.
+Открытый код: Zeek, Suricata и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F146" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек средств анализа трафика на границе сегмента общедоступных объектов доступа;
+3. Эталонный профиль разрешённого сетевого взаимодействия общедоступных объектов доступа;
+4. Журналы (отчёты) о выявленных аномалиях за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G146" s="151" t="inlineStr">
+        <is>
+          <t>1. Средства анализа трафика на границе сегмента общедоступных объектов доступа не развёрнуты либо развёрнуты частично;
+2. Эталонный профиль разрешённого взаимодействия не сформирован, анализ ведётся по общим (менее точным) правилам, единым для всей сети;
+3. Оповещение о выявленных аномалиях в данном сегменте не имеет приоритета, несмотря на критичность общедоступных объектов доступа;
+4. Средства анализа не пересматриваются при вводе новых банкоматов или терминалов, а также при изменении их сетевой конфигурации.</t>
+        </is>
+      </c>
       <c r="H146" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -10981,14 +11124,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D147" s="34" t="inlineStr">
-        <is>
-          <t>Мера ВСА.4 предписывает контролировать отсутствие (выявлять) аномальную сетевую активность, которая может свидетельствовать о попытках несанкционированного логического доступа к ресурсам, размещённым в вычислительных сетях финансовой организации, подключенных к сети Интернет (DMZ).</t>
-        </is>
-      </c>
-      <c r="E147" s="31" t="n"/>
-      <c r="F147" s="31" t="n"/>
-      <c r="G147" s="31" t="n"/>
+      <c r="D147" s="144" t="inlineStr">
+        <is>
+          <t>Мера предписывает контролировать отсутствие (выявлять) аномальную сетевую активность, которая может свидетельствовать о попытках несанкционированного логического доступа к ресурсам, размещённым в вычислительных сетях финансовой организации, подключённых к сети Интернет (в демилитаризованной зоне, DMZ).
+Главная цель меры — обнаруживать попытки несанкционированного доступа именно к тем ресурсам, которые по своей природе доступны из сети Интернет (веб-серверам, почтовым шлюзам, API-интерфейсам), поскольку эти ресурсы подвергаются направленным попыткам эксплуатации существенно чаще, чем внутренние, и нуждаются в отдельном, более чувствительном контроле, учитывающем специфику именно этой категории атак (перебор параметров, эксплуатация уязвимостей веб-приложений, попытки обхода аутентификации).</t>
+        </is>
+      </c>
+      <c r="E147" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера не имеет организационной составляющей — её выполнение обеспечивается техническими средствами:
+1. Развёртывание средств обнаружения вторжений (IDS/IPS) и, для веб-ориентированных ресурсов, межсетевых экранов уровня веб-приложений (WAF) на границе сегмента, подключённого к сети Интернет (DMZ);
+2. Настройку правил и сигнатур выявления типовых атак на логический доступ — перебора учётных данных, попыток эксплуатации известных уязвимостей, аномального числа запросов с одного источника, попыток обхода механизмов аутентификации;
+3. Централизованный сбор выявленных событий в SIEM-системе с корреляцией событий IDS/IPS/WAF с журналами самих интернет-доступных ресурсов для повышения точности выявления.
+Класс используемых средств — системы обнаружения и предотвращения вторжений (IDS/IPS), межсетевые экраны уровня веб-приложений (WAF).
+Иностранные: Palo Alto Networks Threat Prevention, Imperva WAF и пр.
+Российские сертифицированные (ФСТЭК): PT Application Firewall, «Гарда WAF», «Континент 4» (IPS) и др.
+Открытый код: Suricata, Snort, ModSecurity (WAF) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F147" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек IDS/IPS и WAF на границе DMZ;
+3. Журналы (отчёты) о выявленных попытках несанкционированного логического доступа к интернет-доступным ресурсам за проверяемый период;
+4. Результаты тестирования (имитация типовой атаки — перебора параметров, попытки эксплуатации уязвимости), подтверждающие срабатывание средств обнаружения.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G147" s="151" t="inlineStr">
+        <is>
+          <t>1. Средства обнаружения вторжений (IDS/IPS) или WAF развёрнуты не для всех интернет-доступных ресурсов;
+2. Сигнатурные базы и правила выявления атак не обновляются на регулярной основе;
+3. События IDS/IPS/WAF не сопоставляются (не коррелируются) с журналами самих ресурсов, что снижает точность выявления;
+4. Выявленные попытки несанкционированного доступа не анализируются оперативно.</t>
+        </is>
+      </c>
       <c r="H147" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -11012,14 +11201,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D148" s="34" t="inlineStr">
-        <is>
-          <t>Отдельно контролируется аномальная активность именно в каналах удалённого доступа (VPN, RDP, терминальные шлюзы) — эта точка входа имеет свою специфику атак, отличную от обычного интернет-трафика. Это требование направлено на обнаружение подозрительных действий, которые могут указывать на попытку злоумышленника получить доступ к системам организации через удаленные подключения. Аномалией может считаться, например, подключение в нерабочее время, с подозрительных IP-адресов, множественные неудачные попытки аутентификации, подбор паролей, нехарактерные для нормального трафика подключения к критичным ресурсам и т.п.</t>
-        </is>
-      </c>
-      <c r="E148" s="31" t="n"/>
-      <c r="F148" s="31" t="n"/>
-      <c r="G148" s="31" t="n"/>
+      <c r="D148" s="144" t="inlineStr">
+        <is>
+          <t>Отдельно контролируется аномальная активность именно в каналах удалённого доступа (VPN, RDP, терминальные шлюзы) — эта точка входа имеет свою специфику атак, отличную от обычного интернет-трафика (мера ВСА.2). К признакам аномалии относятся, в частности: подключение в нерабочее время, подключение с подозрительных (нетипичных для организации) IP-адресов или из нехарактерных географических регионов, множественные неудачные попытки аутентификации, подбор паролей, а также нехарактерные для нормального поведения обращения к критичным ресурсам сразу после подключения.
+Главная цель меры — своевременно обнаруживать попытки злоумышленника получить доступ к системам организации через каналы удалённого доступа, поскольку именно эти каналы наиболее часто используются для первичного проникновения — как в результате компрометации учётных данных легитимного сотрудника, так и в результате прямого подбора или эксплуатации уязвимостей самих средств удалённого доступа.</t>
+        </is>
+      </c>
+      <c r="E148" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация носит чисто технический характер и включает:
+1. Настройку расширенного журналирования на средствах удалённого доступа (VPN-шлюзах, серверах терминального доступа) с фиксацией источника подключения, времени, длительности сессии и учётной записи;
+2. Настройку правил выявления аномалий подключений — по времени (нерабочие часы), по географии и репутации источника, по числу неуспешных попыток аутентификации, по нетипичному для конкретного пользователя поведению после подключения;
+3. Централизованный сбор событий удалённого доступа в SIEM-системе с корреляцией с иными источниками (например, с журналами идентификации и аутентификации, мера РД.39—РД.40) для повышения точности выявления.
+Класс используемых средств — системы анализа поведения пользователей и сущностей (UEBA), системы управления событиями информационной безопасности (SIEM).
+Иностранные: Exabeam, Microsoft Defender for Identity и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM (с модулем поведенческого анализа), Kaspersky KUMA и др.
+Открытый код: Wazuh (с правилами корреляции) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F148" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами средств удалённого доступа;
+2. Скриншоты (выгрузки) настроек журналирования и правил выявления аномалий на средствах удалённого доступа;
+3. Журналы (отчёты) о выявленных аномалиях удалённого доступа за проверяемый период;
+4. Результаты тестирования (имитация подключения в нерабочее время либо серии неуспешных попыток аутентификации), подтверждающие срабатывание правил выявления.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G148" s="151" t="inlineStr">
+        <is>
+          <t>1. Журналирование подключений удалённого доступа ведётся не в полном объёме (например, не фиксируется источник или длительность сессии);
+2. Правила выявления аномалий удалённого доступа не учитывают все признаки (например, не анализируется география подключений);
+3. События удалённого доступа не сопоставляются с журналами идентификации и аутентификации, что снижает точность выявления;
+4. Выявленные аномалии не анализируются оперативно, реагирование на подозрительные подключения затягивается.</t>
+        </is>
+      </c>
       <c r="H148" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -11043,14 +11278,61 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D149" s="34" t="inlineStr">
-        <is>
-          <t>Если ресурс доступа подключён ко внутренней вычислительной сети организации, то должны контролироваться именно попытки логического доступа к внутренним серверам/сервисам со стороны внутренних же хостов на случай скомпрометированного внутреннего хоста, пытающегося подобрать доступ ко внутренним файловым хранилищам/базам данных, и когда легитимный пользователь пытается получить доступ к ресурсу за пределами своих полномочий (excessive access attempts).</t>
-        </is>
-      </c>
-      <c r="E149" s="31" t="n"/>
-      <c r="F149" s="31" t="n"/>
-      <c r="G149" s="31" t="n"/>
+      <c r="D149" s="144" t="inlineStr">
+        <is>
+          <t>Если ресурс доступа подключён к внутренней вычислительной сети организации, должны контролироваться попытки логического доступа к внутренним серверам и сервисам со стороны внутренних же хостов — как в случае скомпрометированного внутреннего хоста, пытающегося подобрать доступ к внутренним файловым хранилищам или базам данных, так и в случае, когда легитимный пользователь пытается получить доступ к ресурсу за пределами своих полномочий (избыточные попытки доступа).
+Главная цель меры — распространить контроль аномальной активности не только на границы сети (интернет, межконтурные границы — меры ВСА.1—ВСА.2), но и на взаимодействие внутри самой внутренней сети, поскольку значительная часть реальных атак после первичного проникновения развивается именно за счёт горизонтального перемещения (lateral movement) между внутренними ресурсами, которое не пересекает ни одну из контролируемых сетевых границ.</t>
+        </is>
+      </c>
+      <c r="E149" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как речь идёт о чисто технической мере, реализация включает:
+1. Развёртывание средств анализа сетевого трафика (NTA) внутри внутренней вычислительной сети организации, а не только на её периметре;
+2. Настройку правил выявления аномального логического доступа — обращений к ресурсам, нехарактерных для конкретного хоста или учётной записи, множественных неуспешных попыток доступа, попыток доступа за пределами предоставленных прав;
+3. Корреляцию событий сетевого уровня с событиями логического доступа (мера УЗП.9, РД.30) для повышения точности отличия штатного поведения от аномального;
+4. Централизованный сбор выявленных событий в SIEM-системе с настройкой оповещения подразделения информационной безопасности.
+Класс используемых средств — системы анализа сетевого трафика (NTA), системы обнаружения сетевых атак.
+Иностранные: Darktrace, Vectra AI, Cisco Stealthwatch и пр.
+Российские сертифицированные (ФСТЭК): PT NAD, «Гарда NDR» и др.
+Открытый код: Zeek, Suricata и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F149" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек средств анализа внутреннего сетевого трафика;
+3. Журналы (отчёты) о выявленных аномалиях внутреннего логического доступа за проверяемый период;
+4. Результаты тестирования (имитация попытки доступа к ресурсу за пределами предоставленных прав), подтверждающие срабатывание правил выявления.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G149" s="151" t="inlineStr">
+        <is>
+          <t>1. Анализ трафика ограничивается периметром сети, внутреннее (межхостовое) взаимодействие не контролируется;
+2. Правила выявления аномального доступа не сопоставляются с данными о фактически предоставленных правах доступа;
+3. Выявленные аномалии внутреннего доступа не анализируются оперативно;
+4. Средства анализа развёрнуты не во всех внутренних сегментах, содержащих критичные ресурсы доступа.</t>
+        </is>
+      </c>
       <c r="H149" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -11074,14 +11356,60 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D150" s="34" t="inlineStr">
-        <is>
-          <t>Требуется отдельно контролировать активность, направленная на кражу или перехват учётных данных именно легитимных пользователей. Эта мера крайне необходима для защиты от перехвата хэшей учётных данных в сети (например, атаки типа Pass-the-Hash, LLMNR/NBT-NS poisoning), сетевого сниффинга или ARP-спуфинга, которые перехватывают передаваемые аутентификационные данные.</t>
-        </is>
-      </c>
-      <c r="E150" s="31" t="n"/>
-      <c r="F150" s="31" t="n"/>
-      <c r="G150" s="31" t="n"/>
+      <c r="D150" s="144" t="inlineStr">
+        <is>
+          <t>Требуется отдельно контролировать активность, направленную на кражу или перехват аутентификационных данных именно легитимных субъектов доступа. Эта мера необходима для защиты от перехвата хешей учётных данных в сети (например, атак типа Pass-the-Hash, LLMNR/NBT-NS poisoning), сетевого сниффинга или ARP-спуфинга, которые позволяют перехватывать передаваемые по сети аутентификационные данные.
+Главная цель меры — выявлять техники получения чужих аутентификационных данных, которые не всегда сопровождаются явным нарушением правил межсетевого экранирования или очевидным всплеском объёма трафика, — то есть атаки, направленные не на сами ресурсы доступа, а на компрометацию средства идентификации субъекта, после чего злоумышленник получает возможность действовать от имени легитимного пользователя, оставаясь неотличимым от него для большинства иных средств контроля.</t>
+        </is>
+      </c>
+      <c r="E150" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера подразумевает исключительно технические меры защиты, а именно:
+1. Развёртывание средств анализа сетевого трафика (NTA) с сигнатурами и поведенческими моделями, специфичными для выявления перехвата аутентификационных данных (ARP-спуфинг, LLMNR/NBT-NS poisoning, Pass-the-Hash);
+2. Настройку встроенных механизмов защиты служб идентификации и аутентификации (отключение устаревших, уязвимых протоколов разрешения имён при отсутствии производственной необходимости в них);
+3. Настройку корреляции сетевых индикаторов с событиями идентификации и аутентификации (мера РД.39—РД.40) для выявления случаев, когда аутентификационные данные используются нетипичным для их владельца образом сразу после признаков перехвата.
+Класс используемых средств — системы анализа сетевого трафика (NTA) с поведенческим анализом.
+Иностранные: Darktrace, Vectra AI и пр.
+Российские сертифицированные (ФСТЭК): PT NAD, Kaspersky KATA/KUMA и др.
+Открытый код: Zeek и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F150" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек средств анализа трафика, подтверждающие наличие сигнатур выявления перехвата аутентификационных данных;
+3. Журналы (отчёты) о выявленных попытках перехвата аутентификационных данных за проверяемый период;
+4. Результаты тестирования (контролируемая имитация атаки перехвата — в рамках согласованного анализа защищённости), подтверждающие срабатывание средств выявления.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G150" s="151" t="inlineStr">
+        <is>
+          <t>1. Средства анализа трафика не содержат сигнатур (поведенческих моделей), специфичных для выявления перехвата аутентификационных данных;
+2. Устаревшие протоколы разрешения имён, уязвимые к перехвату (LLMNR, NBT-NS), не отключены при отсутствии производственной необходимости;
+3. Корреляция сетевых индикаторов перехвата с последующим нетипичным использованием аутентификационных данных не настроена;
+4. Тестирование защищённости от подобных атак (в рамках анализа защищённости) не проводится.</t>
+        </is>
+      </c>
       <c r="H150" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -11105,14 +11433,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D151" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует выявлять DoS/DDoS-активность в отношении интернет-доступных ресурсов. Реализация меры позволит замечать DDoS-атаки, которые перегружают канал/ресурс и остаются незамеченными в ином случае, это всё относится к атаке на уровне приложения (L7 DoS — множество легитимных на вид запросов), которые маскируются под обычную нагрузку.</t>
-        </is>
-      </c>
-      <c r="E151" s="31" t="n"/>
-      <c r="F151" s="31" t="n"/>
-      <c r="G151" s="31" t="n"/>
+      <c r="D151" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует выявлять активность, характерную для атак типа «отказ в обслуживании» (DoS/DDoS), в отношении ресурсов доступа, доступных из сети Интернет. Помимо объёмных атак, перегружающих канал связи или ресурс, отдельного внимания требуют атаки на уровне приложений (L7 DoS) — большое количество внешне легитимных запросов, которые маскируются под обычную нагрузку и не всегда выявляются простым контролем объёма трафика.
+Главная цель меры — обнаруживать признаки развивающейся DoS/DDoS-атаки до того, как она приведёт к фактическому отказу в обслуживании интернет-доступных ресурсов, поскольку раннее выявление даёт время на принятие мер противодействия (в том числе автоматическое блокирование, предусмотренное мерой ВСА.9) до наступления реального ущерба для доступности сервисов.</t>
+        </is>
+      </c>
+      <c r="E151" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Реализация меры лежит полностью в технической плоскости и включает:
+1. Развёртывание средств обнаружения DoS/DDoS-активности — как на уровне анализа объёма и характера сетевого трафика (Netflow-анализ, специализированные средства защиты от DDoS-атак), так и на прикладном уровне (WAF, средства анализа поведения запросов к веб-приложениям);
+2. Настройку базовых («нормальных») профилей нагрузки на интернет-доступные ресурсы для выявления отклонений — как резких всплесков объёма, так и аномального, но формально легитимного роста числа запросов, характерного для атак уровня приложения;
+3. Централизованный сбор выявленных событий в SIEM-системе с настройкой оперативного оповещения подразделения информационной безопасности и (при наличии) взаимодействия с оператором связи или сервисом защиты от DDoS.
+Класс используемых средств — специализированные средства обнаружения и защиты от DDoS-атак, межсетевые экраны уровня веб-приложений (WAF).
+Иностранные: Cloudflare, Akamai, Radware DefensePro и пр.
+Российские сертифицированные (ФСТЭК): «Гарда Anti-DDoS», StormWall, «Курс — Анти-DDoS» и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F151" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек средств обнаружения DoS/DDoS-активности;
+3. Журналы (отчёты) о выявленных признаках DoS/DDoS-активности за проверяемый период;
+4. Результаты тестирования (нагрузочное тестирование в контролируемых условиях либо анализ отчётов провайдера защиты от DDoS), подтверждающие фактическую способность выявления.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G151" s="151" t="inlineStr">
+        <is>
+          <t>1. Средства обнаружения DoS/DDoS-активности не охватывают все интернет-доступные ресурсы организации;
+2. Контроль ограничивается только объёмными показателями, без учёта атак на уровне приложений (L7 DoS);
+3. Базовые профили нагрузки не сформированы или не актуализируются при изменении характера использования сервисов;
+4. Взаимодействие с оператором связи или внешним сервисом защиты от DDoS не регламентировано.</t>
+        </is>
+      </c>
       <c r="H151" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -11136,14 +11510,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D152" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует реализовать автоматическую блокировку DoS/DDoS-трафика практически в реальном времени, без ручного вмешательства оператора, что идёт совместно с детектированием такой активности, которая, если не заблокирована как атака, приводит к исчерпыванию ресурсов до момента ручного реагирования, что в свою очередь приводит к простою сервиса, и задержка ручной блокировки при массированной атаке может вовсе не успеть предотвратить отказ в обслуживании.</t>
-        </is>
-      </c>
-      <c r="E152" s="31" t="n"/>
-      <c r="F152" s="31" t="n"/>
-      <c r="G152" s="31" t="n"/>
+      <c r="D152" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы блокирование DoS/DDoS-трафика, выявленного в рамках меры ВСА.8, выполнялось автоматически и практически в реальном времени, без ожидания ручного вмешательства оператора.
+Главная цель меры — не допустить исчерпания ресурсов атакуемой системы до момента ручного реагирования: при массированной атаке задержка даже в несколько минут на ручное принятие решения способна привести к простою сервиса, тогда как автоматическое блокирование позволяет пресечь атаку практически сразу после её обнаружения, минимизируя фактическое время недоступности сервиса для легитимных пользователей.</t>
+        </is>
+      </c>
+      <c r="E152" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как данная мера — целиком техническая, для её выполнения необходимо:
+1. Настройку автоматического (без подтверждения оператора) применения средствами защиты от DDoS-атак (мера ВСА.8) мер противодействия при выявлении признаков атаки — ограничения скорости (rate limiting), блокирования источников с аномальным поведением, перенаправления трафика через центр очистки (scrubbing center);
+2. Настройку эскалации на ручное реагирование только для случаев, требующих экспертной оценки (например, при риске ложного срабатывания в отношении легитимного всплеска нагрузки);
+3. Регистрацию всех фактов автоматического блокирования для последующего анализа корректности срабатывания и дальнейшей настройки правил.
+Класс используемых средств — специализированные средства обнаружения и защиты от DDoS-атак.
+Иностранные: Cloudflare, Akamai, Radware DefensePro и пр.
+Российские сертифицированные (ФСТЭК): «Гарда Anti-DDoS», StormWall, «Курс — Анти-DDoS» и др.
+Открытый код: специализированных открытых решений данного класса, как правило, не применяется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F152" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Скриншоты (выгрузки) настроек автоматического блокирования DoS/DDoS-трафика;
+3. Журналы (отчёты) о фактах автоматического блокирования за проверяемый период с указанием времени реакции;
+4. Результаты тестирования (контролируемая имитация атаки), подтверждающие фактическое время срабатывания автоматической блокировки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G152" s="151" t="inlineStr">
+        <is>
+          <t>1. Блокирование DoS/DDoS-трафика требует подтверждения оператора и не выполняется автоматически;
+2. Время автоматического реагирования не измеряется и не подтверждается тестированием;
+3. Автоматическое блокирование настроено не для всех интернет-доступных ресурсов;
+4. Факты автоматического блокирования не анализируются на предмет ложных срабатываний, влияющих на доступность для легитимных пользователей.</t>
+        </is>
+      </c>
       <c r="H152" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -11167,14 +11587,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D153" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует не только определять спам-сообщения, но и иметь техническую возможность блокировать их до попадания к получателю, чтобы избежать фишинговых писем, которые доходят до пользователей и становятся точкой входа для компрометации (вложение с вредоносным кодом, ссылка на фишинговый сайт) и прочих массовых спам-рассылок, которые перегружают почтовую инфраструктуру и маскируют целевые фишинговые письма в общем потоке.</t>
-        </is>
-      </c>
-      <c r="E153" s="31" t="n"/>
-      <c r="F153" s="31" t="n"/>
-      <c r="G153" s="31" t="n"/>
+      <c r="D153" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует не только определять спам-сообщения, но и иметь техническую возможность блокировать их до попадания к получателю — это необходимо, чтобы избежать ситуации, при которой фишинговые письма доходят до пользователей и становятся точкой входа для компрометации (вложение с вредоносным кодом, ссылка на фишинговый сайт), а также чтобы массовые спам-рассылки не перегружали почтовую инфраструктуру и не маскировали целевые фишинговые письма в общем потоке корреспонденции.
+Главная цель меры — снизить вероятность того, что вредоносное или мошенническое письмо будет открыто сотрудником, поскольку электронная почта остаётся одним из самых массовых и результативных каналов первичной компрометации, а полагаться исключительно на бдительность пользователей (без технической фильтрации) недостаточно.</t>
+        </is>
+      </c>
+      <c r="E153" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Развёртывание на почтовом шлюзе (мера СМЭ.20) средств антиспам-фильтрации, анализирующих входящие сообщения по совокупности признаков — репутации отправителя, содержимому, вложениям, соответствию SPF/DKIM/DMARC;
+2. Настройку технической возможности автоматической блокировки (карантина, удаления) сообщений, классифицированных как спам, до их доставки в почтовый ящик получателя;
+3. Регулярное обновление баз репутации отправителей и сигнатур спам-фильтра для поддержания эффективности фильтрации против новых видов рассылок.
+Класс используемых средств — средства антиспам-фильтрации (Anti-Spam), почтовые шлюзы с функцией фильтрации.
+Иностранные: Proofpoint Email Protection, Cisco Secure Email и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для почтовых серверов, Dr.Web Mail Security Suite и др.
+Открытый код: SpamAssassin, Rspamd и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F153" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами почтовой инфраструктуры;
+2. Скриншоты (выгрузки) настроек антиспам-фильтрации на почтовом шлюзе;
+3. Статистика (отчёты) о заблокированных спам-сообщениях за проверяемый период;
+4. Результаты тестирования (отправка тестового сообщения с признаками спама), подтверждающие фактическое срабатывание блокировки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G153" s="151" t="inlineStr">
+        <is>
+          <t>1. Антиспам-фильтрация настроена не на всех почтовых потоках (например, отсутствует для внутренней почты, поступающей извне через отдельный шлюз);
+2. Классифицированные как спам сообщения помещаются в карантин, но техническая блокировка их доставки отсутствует;
+3. Базы репутации отправителей и сигнатуры спам-фильтра не обновляются на регулярной основе;
+4. Эффективность фильтрации (доля пропущенного спама) не контролируется и не анализируется.</t>
+        </is>
+      </c>
       <c r="H153" s="26" t="inlineStr">
         <is>
           <t>Нет недостатков. 
@@ -11198,59 +11664,33 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D154" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Мера конкретизирует требование именно </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">способа </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>выявления аномальной активности (пока ВСА.1-ВСА.9 определяют виды аномалий)  — путём анализа трафика именно на стыке между группами сегментов, относящихся к разным контурам безопасности, чтобы не допустить атаку, распространяющуюся из одного контура безопасности в другой через межконтурный трафик, что может оставаться незамеченным без такого выделенного анализа внутренней границы, а не только периметра с Интернетом.</t>
-          </r>
-        </is>
-      </c>
-      <c r="E154" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D154" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует именно способ выявления аномальной активности (пока меры ВСА.1—ВСА.9 определяют её виды) — путём анализа трафика на стыке между группами сегментов, относящихся к разным контурам безопасности, чтобы не допустить, что атака, распространяющаяся из одного контура безопасности в другой через межконтурный трафик, останется незамеченной без такого выделенного анализа внутренней границы, а не только периметра с сетью Интернет.
+Главная цель меры — задать конкретный технический способ реализации контроля, предусмотренного мерой ВСА.1: не просто зафиксировать требование выявлять межконтурные аномалии, а прямо указать, что это достигается сканированием и анализом трафика именно на границах между группами сегментов разных контуров.</t>
+        </is>
+      </c>
+      <c r="E154" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Мера предполагает использование специализированных программно-аппаратных средств для сканирования и анализа сетевого трафика между контурами безопасности.
+            <t xml:space="preserve">
+Мера предполагает использование специализированных программно-аппаратных средств для сканирования и анализа сетевого трафика на границах между группами сегментов, относящихся к разным контурам безопасности.
 Основные направления технической реализации:
 1. Использование систем обнаружения и предотвращения вторжений (IDS/IPS);
 2. Использование систем анализа сетевого трафика (NTA);
-3. Настройка межсетевых экранов (МЭ): фильтрация трафика между группами сегментов разных контуров безопасности должна быть настроена в соответствии с утверждёнными правилами; настройка разрешений только необходимых сетевых протоколов и портов; реализация принципа «запрещено всё, что не разрешено» для трафика между контурами;
-4. Сбор зарегистрированных событий в SIEM.</t>
+3. Настройка межсетевых экранов (МЭ): фильтрация трафика между группами сегментов разных контуров безопасности в соответствии с утверждёнными правилами, разрешение только необходимых сетевых протоколов и портов, реализация принципа «запрещено всё, что не разрешено» для трафика между контурами;
+4. Сбор зарегистрированных событий в SIEM.
+Класс используемых средств — системы обнаружения и предотвращения вторжений (IDS/IPS), системы анализа сетевого трафика (NTA).
+Иностранные: Cisco Stealthwatch, Darktrace, Vectra AI и пр.
+Российские сертифицированные (ФСТЭК): PT NAD, Kaspersky KATA/KUMA, «Гарда NDR» и др.
+Открытый код: Zeek, Suricata и др.</t>
           </r>
         </is>
       </c>
@@ -11279,9 +11719,9 @@
           </r>
         </is>
       </c>
-      <c r="G154" s="36" t="inlineStr">
-        <is>
-          <t>1. Отсутствие средств анализа трафика между контурами безопасности — контроль не организован.
+      <c r="G154" s="151" t="inlineStr">
+        <is>
+          <t>1. Отсутствие средств анализа трафика между контурами безопасности — контроль не организован;
 2. Анализ трафика осуществляется не для всех групп сегментов, входящих в разные контуры безопасности;
 3. Ошибки в правилах, допускающие неразрешённое взаимодействие между контурами.</t>
         </is>
@@ -11303,187 +11743,131 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D155" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует контроля аномальной активности (которые определяют ВСА.1–ВСА.9) именно внутри сегмента — между хостами одной зоны доверия. Так мера закрывает скрытое перемещение атакующего между хостами внутри сегмента (lateral movement) после компрометации одного узла, внутреннее сканирование и распространение вредоносного кода, невидимое периметровыми IDS/IPS.</t>
-        </is>
-      </c>
-      <c r="E155" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D155" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует контроля аномальной активности, виды которой определяют меры ВСА.1—ВСА.9, именно внутри сегмента — между хостами одной зоны доверия. Так закрывается скрытое перемещение атакующего между хостами внутри сегмента (lateral movement) после компрометации одного узла, внутреннее сканирование сети и распространение вредоносного кода — активность, невидимая для периметровых средств обнаружения (IDS/IPS), контролирующих только границы сети.
+Главная цель меры — распространить технический контроль аномалий не только на границы сегментов (мера ВСА.11) и внешний периметр (мера ВСА.13), но и на трафик внутри самого сегмента, поскольку значительная часть атак после первичного проникновения развивается именно за счёт горизонтального перемещения между хостами одной зоны доверия.</t>
+        </is>
+      </c>
+      <c r="E155" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Мера предполагает использование специализированных программно-аппаратных средств для сканирования и анализа сетевого трафика между контурами безопасности.
+            <t xml:space="preserve">
+Мера предполагает использование специализированных программно-аппаратных средств для сканирования и анализа сетевого трафика внутри сегмента контура безопасности — то есть между хостами одной зоны доверия, а не на его внешних границах (см. меры ВСА.11, ВСА.13).
+Основные направления технической реализации:
+1. Использование систем обнаружения сетевых атак (NAD, Network Attack Detection);
+2. Настройка фильтрации трафика внутри сегмента: в рамках анализа может осуществляться фильтрация между отдельными зонами внутри сегмента на межсетевом экране (микросегментация) с разрешением только необходимых сетевых протоколов и портов;
+3. Сбор зарегистрированных событий в SIEM.
+Класс используемых средств — системы обнаружения сетевых атак (NAD, NTA).
+Иностранные: Cisco Stealthwatch, Darktrace, Vectra AI и пр.
+Российские сертифицированные (ФСТЭК): PT NAD, Kaspersky KATA/KUMA, «Гарда NDR» и др.
+Открытый код: Zeek, Suricata и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F155" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Демонстрация (скриншоты) настроек используемых систем анализа сетевого трафика (например, PT NAD, Kaspersky KATA), подтверждающая, что анализ трафика в пределах сегментов контура безопасности организован и настроен;
+2. Логи сетевого оборудования и средств анализа трафика — записи, подтверждающие факт мониторинга и анализа трафика внутри сегментов;
+3. Логи SIEM-системы (при использовании).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G155" s="151" t="inlineStr">
+        <is>
+          <t>1. Анализ трафика осуществляется не для всех сегментов, входящих в контуры безопасности;
+2. Не внедрены специализированные системы для сканирования и анализа внутреннего трафика;
+3. Профиль штатного («нормального») внутрисегментного взаимодействия не сформирован, что затрудняет отличие аномалии от обычного трафика;
+4. Выявленные внутрисегментные аномалии не передаются оперативно подразделению информационной безопасности.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="315" customHeight="1">
+      <c r="A156" s="20" t="inlineStr">
+        <is>
+          <t>ВСА.13</t>
+        </is>
+      </c>
+      <c r="B156" s="21" t="inlineStr">
+        <is>
+          <t>Реализация контроля, предусмотренного мерами ВСА.1 - ВСА.9 настоящей таблицы, путем сканирования и анализа сетевого трафика между вычислительными сетями финансовой организации и сетью Интернет</t>
+        </is>
+      </c>
+      <c r="C156" s="22" t="inlineStr">
+        <is>
+          <t>Н-Т-Т</t>
+        </is>
+      </c>
+      <c r="D156" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует контроля аномальной активности, виды которой определяют меры ВСА.1—ВСА.9, на границе с сетью Интернет — весь трафик, пересекающий периметр между внутренними сетями и Интернетом, должен сканироваться и анализироваться отдельно. Это закрывает риски необнаруженной эксфильтрации данных или command-and-control трафика скомпрометированного хоста через интернет-канал, а также атак извне (сканирования, попыток эксплуатации), остающихся незамеченными при отсутствии анализа именно на границе с Интернетом.
+Главная цель меры — задать конкретный технический способ реализации контроля, предусмотренного мерой ВСА.2, применительно именно к трафику, пересекающему внешний периметр организации, — так же, как мера ВСА.11 задаёт способ реализации для межконтурных границ, а мера ВСА.12 — для трафика внутри сегмента.</t>
+        </is>
+      </c>
+      <c r="E156" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера предполагает использование специализированных программно-аппаратных средств для сканирования и анализа сетевого трафика на границе внутренних вычислительных сетей организации с сетью Интернет.
 Основные направления технической реализации:
 1. Использование систем обнаружения сетевых атак (NAD);
-2. Настройка фильтрации трафика. В рамках анализа трафика может осуществляться фильтрация между зонами сети на межсетевом экране с настройкой разрешений только необходимых сетевых протоколов и портов;
-3. Сбор зарегистрированных событий в SIEM.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco Stealthwatch, Darktrace, Vectra AI и пр.
-- Российские сертифицированные: PT NAD, Kaspersky KATA/KUMA, Гарда NDR и пр.
-- Открытый код: Zeek, Suricata и пр.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F155" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+2. Использование систем обнаружения и предотвращения вторжений (IDS/IPS) для выявления аномалий на границе с сетью Интернет;
+3. Настройка межсетевых экранов на границе с сетью Интернет: фильтрация трафика в соответствии с утверждённой матрицей сетевого взаимодействия (мера СМЭ.17), разрешение только необходимых сетевых протоколов и портов, реализация принципа «запрещено всё, что не разрешено»;
+4. Сбор зарегистрированных событий в SIEM.
+Класс используемых средств — системы обнаружения сетевых атак (NAD), системы обнаружения и предотвращения вторжений (IDS/IPS).
+Иностранные: Palo Alto Networks Threat Prevention, Cisco Firepower IPS, Fortinet FortiGate IPS и пр.
+Российские сертифицированные (ФСТЭК): UserGate NGFW (модуль IPS), «Континент 4» (IPS), PT NAD и др.
+Открытый код: Suricata, Snort и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F156" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Проверочные процедуры (свидетельства) - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-1. Демонстрация (скриншоты) настроек используемых систем анализа сетевого трафика (SolarWinds, PT NAD и др.) — подтверждение того, что анализ трафика в пределах сегментов контура безопасности организован и настроен;
-2. Логи сетевого оборудования и средств анализа трафика — записи, подтверждающие факт мониторинга и анализа трафика внутри сегментов;
-3. Логи SIEM-системы (при использовании).</t>
-          </r>
-        </is>
-      </c>
-      <c r="G155" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Анализ трафика осуществляется не для всех сегментов, входящих в контуры безопасности;
-2. Не внедрены специализированные системы для сканирования и анализа внутреннего трафика. </t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="315" customHeight="1">
-      <c r="A156" s="20" t="inlineStr">
-        <is>
-          <t>ВСА.13</t>
-        </is>
-      </c>
-      <c r="B156" s="21" t="inlineStr">
-        <is>
-          <t>Реализация контроля, предусмотренного мерами ВСА.1 - ВСА.9 настоящей таблицы, путем сканирования и анализа сетевого трафика между вычислительными сетями финансовой организации и сетью Интернет</t>
-        </is>
-      </c>
-      <c r="C156" s="22" t="inlineStr">
-        <is>
-          <t>Н-Т-Т</t>
-        </is>
-      </c>
-      <c r="D156" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует контроля аномальной активности (которые определяют ВСА.1–ВСА.9) для границы с интернетом — весь трафик, пересекающий периметр между внутренними сетями и интернетом, должен сканироваться и анализироваться отдельно. Это закрывает риски необнаруженной эксфильтрации данных или command-and-control трафика скомпрометированного хоста через интернет-канал, а также атак извне (сканирование, попытки эксплуатации), не замеченные при отсутствии анализа именно на границе с интернетом.</t>
-        </is>
-      </c>
-      <c r="E156" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Реализация - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Мера предполагает использование специализированных программно-аппаратных средств для сканирования и анализа сетевого трафика между контурами безопасности.
-Основные направления технической реализации:
-1. Использование систем обнаружения сетевых атак (NAD);
-2. Для выявления аномалий на границе с Интернетом могут применяться системы IDS/IPS;
-3. Настройка межсетевых экранов (МЭ): фильтрация трафика между группами сегментов разных контуров безопасности должна быть настроена в соответствии с утверждёнными правилами; настройка разрешений только необходимых сетевых протоколов и портов; реализация принципа «запрещено всё, что не разрешено» для трафика между контурами;
-4. Сбор зарегистрированных событий в SIEM.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Palo Alto Networks Threat Prevention, Cisco Firepower IPS, Fortinet FortiGate IPS и пр.
-- Российские сертифицированные: UserGate NGFW (модуль IPS), Континент 4 (IPS), PT NAD и пр.
-- Открытый код: Suricata, Snort и пр.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F156" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Проверочные процедуры (свидетельства) - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-1. Демонстрация (скриншоты) настроек используемых систем анализа сетевого трафика (SolarWinds, PT NAD и др.) — подтверждение того, что анализ трафика между внутренними сетями и Интернетом организован и настроен;
-2. Демонстрация (скриншоты) настроек межсетевого экрана и PTAF — подтверждение фильтрации трафика на границе с Интернетом;
+            <t xml:space="preserve">
+1. Демонстрация (скриншоты) настроек используемых систем анализа сетевого трафика (например, PT NAD), подтверждающая, что анализ трафика между внутренними сетями и Интернетом организован и настроен;
+2. Демонстрация (скриншоты) настроек межсетевого экрана и системы обнаружения вторжений на границе с сетью Интернет, подтверждающая фильтрацию и контроль трафика;
 3. Логи сетевого оборудования и средств анализа трафика — записи, подтверждающие факт мониторинга и анализа трафика между внутренними сетями и Интернетом;
 4. Логи SIEM-системы (при использовании).</t>
           </r>
         </is>
       </c>
-      <c r="G156" s="36" t="inlineStr">
-        <is>
-          <t>1.  Анализ трафика осуществляется не для всех каналов связи с Интернетом;
-2. Ошибки в правилах, допускающие неразрешённое взаимодействие с внешней сетью.</t>
+      <c r="G156" s="151" t="inlineStr">
+        <is>
+          <t>1. Анализ трафика осуществляется не для всех каналов связи с сетью Интернет;
+2. Ошибки в правилах, допускающие неразрешённое взаимодействие с внешней сетью;
+3. Сигнатурные базы систем обнаружения вторжений на границе с Интернетом не обновляются на регулярной основе;
+4. Выявленные аномалии на границе с Интернетом не сопоставляются с событиями внутреннего сегмента (мера ВСА.12) для оценки масштаба возможного проникновения.</t>
         </is>
       </c>
     </row>
@@ -11516,55 +11900,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D158" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы каждый факт обнаружения аномальной сетевой активности фиксировался как событие защиты информации, а не просто отображался на экране оператора и терялся.  Это закрывает уязвимости, когда инцидент не расследуется постфактум из-за отсутствия истории срабатываний, или атака продолжает оставаться незамеченной, если предыдущее срабатывание не было зафиксировано и проанализировано.</t>
-        </is>
-      </c>
-      <c r="E158" s="67" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="12"/>
+      <c r="D158" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы каждый факт обнаружения аномальной сетевой активности фиксировался как событие защиты информации, а не просто отображался на экране оператора и терялся. Это закрывает ситуацию, когда инцидент невозможно расследовать постфактум из-за отсутствия истории срабатываний, либо атака продолжает оставаться незамеченной, если предыдущее срабатывание не было зафиксировано и проанализировано.
+Главная цель меры — превратить разрозненные срабатывания средств выявления аномалий (мер ВСА.1—ВСА.8) в единую, пригодную для анализа доказательную базу, поскольку ценность самого факта обнаружения аномалии резко снижается, если он не сохраняется и не может быть впоследствии сопоставлен с другими событиями при расследовании инцидента.</t>
+        </is>
+      </c>
+      <c r="E158" s="165" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Times New Roman"/>
-              <sz val="12"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">Все срабатывания средств обнаружения аномалий (ВСА.1–ВСА.8) настраиваются на обязательную генерацию события: время, источник/назначение, тип аномалии, сработавшее правило. События передаются в SIEM с сохранением на срок, достаточный для расследования и выполнения требований регулятора.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="12"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Splunk, IBM QRadar и пр.
-- Российские сертифицированные: MaxPatrol SIEM, Kaspersky KUMA и пр.
-- Открытый код: Wazuh, Elastic SIEM и пр.</t>
+            <t xml:space="preserve">
+Все срабатывания средств обнаружения аномалий (мер ВСА.1—ВСА.8) настраиваются на обязательную генерацию события с указанием как минимум времени, источника и назначения, типа аномалии и сработавшего правила. События передаются в SIEM-систему с хранением на срок, достаточный для расследования и выполнения требований регулятора.
+Класс используемых средств — системы управления событиями информационной безопасности (SIEM).
+Иностранные: Splunk, IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, Kaspersky KUMA и др.
+Открытый код: Wazuh, Elastic SIEM и др.</t>
           </r>
         </is>
       </c>
@@ -11629,10 +11986,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D160" s="21" t="n"/>
-      <c r="E160" s="31" t="n"/>
-      <c r="F160" s="31" t="n"/>
-      <c r="G160" s="31" t="n"/>
+      <c r="D160" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует применения сетевых протоколов, которые технически обеспечивают три взаимосвязанных свойства защищённого сетевого соединения: подлинность самого соединения (уверенность, что оно установлено именно с ожидаемым узлом, а не с подменённым), контроль целостности передаваемых данных (обнаружение любого искажения в процессе передачи) и двустороннюю аутентификацию сторон — при осуществлении логического доступа по телекоммуникационным каналам и линиям связи, не контролируемым финансовой организацией.
+Главная цель меры — исключить угрозы, характерные именно для незащищённых или недостаточно защищённых сетевых соединений через неконтролируемые каналы связи: подмену одной из сторон соединения (man-in-the-middle), скрытое искажение передаваемых данных и одностороннюю аутентификацию, при которой только одна из сторон подтверждает свою подлинность, оставляя вторую сторону уязвимой для атаки подмены.</t>
+        </is>
+      </c>
+      <c r="E160" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Применение криптографических сетевых протоколов, обеспечивающих одновременно шифрование (либо, как минимум, контроль целостности) передаваемых данных и взаимную аутентификацию сторон соединения — TLS с двусторонней (mutual) аутентификацией по сертификатам, IPsec с аутентификацией на основе сертификатов или предустановленных ключей, SSH с аутентификацией по ключам;
+2. Технический запрет на установление соединений по неконтролируемым каналам связи с использованием протоколов, не обеспечивающих контроль целостности и (или) двустороннюю аутентификацию (например, устаревших версий TLS, протоколов без проверки сертификата сервера и клиента);
+3. Периодический технический контроль (сканирование, анализ конфигураций) фактически применяемых версий протоколов и параметров аутентификации на предмет соответствия установленным требованиям.
+Класс используемых средств — средства криптографической защиты каналов связи (VPN-шлюзы, TLS-терминаторы), инфраструктура открытых ключей (PKI).
+Иностранные: Cisco AnyConnect, Palo Alto GlobalProtect и пр.
+Российские сертифицированные (ФСТЭК): «С-Терра Шлюз», ViPNet Coordinator, «Континент» (VPN) и др.
+Открытый код: OpenVPN, WireGuard (с внешним PKI) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F160" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры;
+2. Скриншоты (выгрузки) настроек используемых протоколов и параметров аутентификации на средствах защищённого сетевого взаимодействия;
+3. Результаты сканирования (аудита) конфигураций на предмет использования устаревших или не обеспечивающих взаимную аутентификацию протоколов;
+4. Результаты тестирования (попытка установления соединения без прохождения взаимной аутентификации), подтверждающие блокирование такой попытки.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G160" s="151" t="inlineStr">
+        <is>
+          <t>1. На части каналов связи, не контролируемых организацией, применяются протоколы, не обеспечивающие взаимную (двустороннюю) аутентификацию сторон;
+2. Используются устаревшие версии криптографических протоколов с известными уязвимостями;
+3. Проверка сертификата (иного признака подлинности) удалённой стороны технически возможна, но не является обязательной для установления соединения;
+4. Периодический контроль фактически применяемых версий протоколов не проводится.</t>
+        </is>
+      </c>
       <c r="H160" s="7" t="inlineStr">
         <is>
           <t>Нет недостатков.</t>
@@ -11661,7 +12068,7 @@
 Главная цель меры — обеспечить безопасность информационного обмена при удаленном доступе по неконтролируемым каналам связи, гарантируя, что данные не будут перехвачены, изменены, а также что обе стороны обмена являются именно теми, за кого себя выдают.</t>
         </is>
       </c>
-      <c r="E161" s="36" t="inlineStr">
+      <c r="E161" s="151" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11690,25 +12097,11 @@
 </t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
- Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco AnyConnect, Palo Alto GlobalProtect и пр.
-- Российские сертифицированные: КриптоПро CSP/NGate, ViPNet Coordinator, Континент 4 (VPN) и пр.
-- Открытый код: OpenVPN, WireGuard (с внешним PKI) и пр.</t>
+            <t xml:space="preserve">
+Класс используемых средств — средства криптографической защиты каналов связи (VPN-шлюзы), инфраструктура открытых ключей (PKI).
+Иностранные: Cisco AnyConnect, Palo Alto GlobalProtect и пр.
+Российские сертифицированные (ФСТЭК): ViPNet Coordinator, «Континент 4» (VPN) и др.
+Открытый код: OpenVPN, WireGuard (с внешним PKI) и др.</t>
           </r>
         </is>
       </c>
@@ -11742,6 +12135,11 @@
           <t>1. Реализована только односторонняя аутентификация (клиент проверяет сервер, обратной проверки нет).
 2. Не все неконтролируемые каналы (в т. ч. резервные) защищены — часть трафика идёт в открытом виде.
 3. Используются устаревшие/слабые криптографические протоколы (не соответствующие текущим требованиям).</t>
+        </is>
+      </c>
+      <c r="H161" s="156" t="inlineStr">
+        <is>
+          <t>СКЗИ (в т. ч. КриптоПро CSP, упоминавшийся в исходном тексте) в РФ сертифицируются преимущественно ФСБ России, а не ФСТЭК России, поэтому исключён из списка «российские сертифицированные (ФСТЭК)» — при выборе конкретного СКЗИ дополнительно сверяться с реестром сертифицированных ФСБ России средств.</t>
         </is>
       </c>
     </row>
@@ -26632,8 +27030,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -12172,51 +12172,28 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D163" s="34" t="inlineStr">
-        <is>
-          <t>Точка доступа Wi-Fi должна проверять подлинность подключающегося устройства, а не пускать любое устройство, знающее пароль сети. Мера закрывает возможность подключения постороннего устройства к корпоративной беспроводной сети при компрометации общего пароля и обязует привязывать доступ к конкретному устройству/пользователю.</t>
-        </is>
-      </c>
-      <c r="E163" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D163" s="144" t="inlineStr">
+        <is>
+          <t>Точка доступа Wi-Fi должна проверять подлинность подключающегося устройства, а не пускать любое устройство, знающее пароль сети. Мера закрывает возможность подключения постороннего устройства к корпоративной беспроводной сети при компрометации общего пароля и обязует привязывать доступ к конкретному устройству/пользователю.
+Главная цель меры — исключить возможность подключения к корпоративной беспроводной сети любого устройства, знающего лишь общий пароль, не связывая доступ с конкретным устройством или пользователем, поскольку общий предварительный ключ (PSK) в случае утечки компрометирует сеть целиком, тогда как индивидуальная аутентификация позволяет отозвать доступ точечно.</t>
+        </is>
+      </c>
+      <c r="E163" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-На точках доступа настраивается аутентификация устройств по протоколу 802.1X с проверкой через RADIUS/сертификаты устройства, либо (как минимум) индивидуальные учётные данные вместо общего PSK-пароля. Не аутентифицированные устройства к сети не допускаются.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>- Иностранные: Cisco ISE + WLC, Aruba ClearPass и пр.
-- Российские сертифицированные: Ideco NGFW (RADIUS-модуль), «Атликс» Wi-Fi (сертифицированные точки доступа с 802.1X) и пр.
-- Открытый код: FreeRADIUS + hostapd и пр.</t>
+            <t xml:space="preserve">
+На точках доступа настраивается аутентификация устройств по протоколу 802.1X с проверкой через RADIUS/сертификаты устройства, либо (как минимум) индивидуальные учётные данные вместо общего PSK-пароля. Неаутентифицированные устройства к сети не допускаются.
+Класс используемых средств — RADIUS-серверы и контроллеры точек доступа с поддержкой 802.1X.
+Иностранные: Cisco ISE + WLC, Aruba ClearPass и пр.
+Российские сертифицированные (ФСТЭК): Ideco NGFW (RADIUS-модуль), точки доступа «Атликс» с поддержкой 802.1X и др.
+Открытый код: FreeRADIUS + hostapd и др.</t>
           </r>
         </is>
       </c>
@@ -12268,51 +12245,28 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D164" s="34" t="inlineStr">
-        <is>
-          <t>Трафик между устройством и точкой доступа должен быть зашифрован и защищён от подмены, чтобы защититься от перехвата передаваемых данных при слабом или устаревшем шифровании (например, WEP, WPA) и от внедрения поддельных пакетов в сессию при отсутствии контроля целостности.</t>
-        </is>
-      </c>
-      <c r="E164" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D164" s="144" t="inlineStr">
+        <is>
+          <t>Трафик между устройством и точкой доступа должен быть зашифрован и защищён от подмены, чтобы защититься от перехвата передаваемых данных при слабом или устаревшем шифровании (например, WEP, WPA) и от внедрения поддельных пакетов в сессию при отсутствии контроля целостности.
+Главная цель меры — защититься от перехвата передаваемых данных при слабом или устаревшем шифровании (например, WEP, WPA) и от внедрения поддельных пакетов в сессию при отсутствии контроля целостности, поскольку беспроводная среда передачи в принципе доступна для прослушивания любому находящемуся в зоне действия сигнала, и только стойкое шифрование делает перехваченный трафик бесполезным для злоумышленника.</t>
+        </is>
+      </c>
+      <c r="E164" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
             <t xml:space="preserve">
 На точках доступа и клиентских устройствах настраивается современный протокол шифрования беспроводного канала (WPA2-Enterprise/WPA3) с индивидуальными ключами сессии для каждого устройства. Устаревшие протоколы (WEP, WPA-PSK с общим ключом) отключаются.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco WLC (WPA3-Enterprise), Aruba (WPA3) и пр.
-- Российские сертифицированные: точки доступа «Атликс» с поддержкой WPA2/WPA3-Enterprise и пр.
-- Открытый код: hostapd (WPA2/WPA3-Enterprise) и пр.</t>
+Класс используемых средств — точки доступа и контроллеры беспроводных сетей с поддержкой WPA2/WPA3-Enterprise.
+Иностранные: Cisco WLC (WPA3-Enterprise), Aruba (WPA3) и пр.
+Российские сертифицированные (ФСТЭК): точки доступа «Атликс» с поддержкой WPA2/WPA3-Enterprise и др.
+Открытый код: hostapd (WPA2/WPA3-Enterprise) и др.</t>
           </r>
         </is>
       </c>
@@ -12364,51 +12318,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D165" s="34" t="inlineStr">
-        <is>
-          <t>Точки доступа Wi-Fi и связанное с ними оборудование должны находиться в отдельном сетевом сегменте, а не подключаться напрямую во внутреннюю сеть наравне с другими устройствами, что сразу исключает компрометацию точки доступа (физическую или удалённую) и не даёт прямого доступа во внутреннюю сеть.</t>
-        </is>
-      </c>
-      <c r="E165" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D165" s="144" t="inlineStr">
+        <is>
+          <t>Точки доступа Wi-Fi и связанное с ними оборудование должны находиться в отдельном сетевом сегменте, а не подключаться напрямую во внутреннюю сеть наравне с другими устройствами, что сразу исключает компрометацию точки доступа (физическую или удалённую) и не даёт прямого доступа во внутреннюю сеть.
+Главная цель меры — исключить прямой доступ во внутреннюю сеть в случае компрометации точки доступа (физической или удалённой), поскольку выделенный сегмент ограничивает последствия такой компрометации периметром самого беспроводного сегмента, а не всей внутренней инфраструктурой.</t>
+        </is>
+      </c>
+      <c r="E165" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Точки доступа и их управляющие контроллеры выносятся в отдельный VLAN/сегмент, изолированный от прочих внутренних сетей на сетевом уровне (L3). Все дальнейшие требования по изоляции и МЭ (ЗБС.4–ЗБС.7) применяются именно к этому сегменту.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>- Иностранные: Cisco WLC + dedicated VLAN, Aruba Mobility Controller и пр.
-- Российские сертифицированные: PT NGFW, UserGate NGFW (сегментация VLAN), Континент 4 и пр.
-- Открытый код: VLAN-конфигурация на управляемых коммутаторах (например, через OpenWRT-инфраструктуру) и пр.</t>
+            <t xml:space="preserve">
+Точки доступа и их управляющие контроллеры выносятся в отдельный VLAN/сегмент, изолированный от прочих внутренних сетей на сетевом уровне (L3). Все дальнейшие требования по изоляции и межсетевому экранированию (меры ЗБС.4—ЗБС.7) применяются именно к этому сегменту.
+Класс используемых средств — активное сетевое оборудование с поддержкой сегментации сети (VLAN).
+Иностранные: Cisco WLC (выделенный VLAN), Aruba Mobility Controller и пр.
+Российские сертифицированные (ФСТЭК): PT NGFW, UserGate NGFW (сегментация VLAN), «Континент 4» и др.
+Открытый код: управляемые коммутаторы с поддержкой VLAN (например, на базе OpenWRT) и др.</t>
           </r>
         </is>
       </c>
@@ -12436,10 +12367,12 @@
           </r>
         </is>
       </c>
-      <c r="G165" s="36" t="inlineStr">
-        <is>
-          <t>1. Часть точек доступа подключена в общий сегмент с пользовательскими устройствами.
-2. Управляющий трафик контроллера точек доступа не изолирован от пользовательского Wi-Fi-трафика.</t>
+      <c r="G165" s="151" t="inlineStr">
+        <is>
+          <t>1. Часть точек доступа подключена в общий сегмент с пользовательскими устройствами;
+2. Управляющий трафик контроллера точек доступа не изолирован от пользовательского Wi-Fi-трафика;
+3. Выделенный сегмент не документирован в общей схеме сегментации сети (см. также меру СМЭ.1);
+4. Состав сегмента не пересматривается при подключении новых точек доступа.</t>
         </is>
       </c>
     </row>
@@ -12459,52 +12392,28 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D166" s="34" t="inlineStr">
-        <is>
-          <t>Требуется строгая изоляция беспроводного сегмента (ЗБС.3) от остальной внутренней сети на канальном уровне (L2) — без общего broadcast-домена и ARP-видимости, чтобы не происходила компрометация беспроводной инфраструктуры и нельзя было получить прямой L2-доступ к остальной внутренней сети (ARP-спуфинг, сниффинг широковещательного трафика).</t>
-        </is>
-      </c>
-      <c r="E166" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D166" s="144" t="inlineStr">
+        <is>
+          <t>Требуется строгая изоляция беспроводного сегмента (ЗБС.3) от остальной внутренней сети на канальном уровне (L2) — без общего broadcast-домена и ARP-видимости, чтобы не происходила компрометация беспроводной инфраструктуры и нельзя было получить прямой L2-доступ к остальной внутренней сети (ARP-спуфинг, сниффинг широковещательного трафика).
+Главная цель меры — не допустить компрометацию беспроводной инфраструктуры с получением прямого канального (L2) доступа к остальной внутренней сети, поскольку на канальном уровне возможны атаки (ARP-спуфинг, прослушивание широковещательного трафика), не блокируемые обычной маршрутизацией и фильтрацией на более высоких уровнях.</t>
+        </is>
+      </c>
+      <c r="E166" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
             <t xml:space="preserve">
 Беспроводной сегмент выносится в отдельный L2-домен без прямой канальной связности с прочими сетями, взаимодействие с остальной инфраструктурой строится только через контролируемый L3-шлюз с фильтрацией.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco Catalyst (private VLAN, L2 isolation) и пр.
-- Российские сертифицированные: PT NGFW, UserGate NGFW и пр.
-- Открытый код: управляемые коммутаторы с private VLAN и пр.</t>
+Класс используемых средств — активное сетевое оборудование с поддержкой изоляции на канальном уровне (private VLAN).
+Иностранные: Cisco Catalyst (private VLAN, L2 isolation) и пр.
+Российские сертифицированные (ФСТЭК): PT NGFW, UserGate NGFW и др.
+Открытый код: управляемые коммутаторы с поддержкой private VLAN и др.</t>
           </r>
         </is>
       </c>
@@ -12532,10 +12441,12 @@
           </r>
         </is>
       </c>
-      <c r="G166" s="36" t="inlineStr">
-        <is>
-          <t>1. Обнаружена остаточная L2-связность (общий broadcast-домен) с внутренней сетью.
-2. Изоляция реализована только на сетевом уровне (L3), что не соответствует требованию УЗ1.</t>
+      <c r="G166" s="151" t="inlineStr">
+        <is>
+          <t>1. Обнаружена остаточная L2-связность (общий широковещательный домен) с внутренней сетью;
+2. Изоляция реализована только на сетевом уровне (L3), что не соответствует требованию для уровня защиты 1 (УЗ1);
+3. Контроллер точек доступа имеет канальную связность с сегментами, не относящимися к беспроводной инфраструктуре;
+4. Отсутствие L2-связности не подтверждается периодическим тестированием.</t>
         </is>
       </c>
     </row>
@@ -12555,51 +12466,28 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D167" s="34" t="inlineStr">
-        <is>
-          <t>Требуется изоляция беспроводного сегмента (ЗБС.3) от остальной внутренней сети на сетевом уровне (L3) — маршрутизация и списки управления доступом (ACL) между сегментами, без обязательной канальной изоляции. Это защищает от случаев, когда скомпрометированное Wi-Fi-устройство может свободно маршрутизировать трафик во внутреннюю сеть.</t>
-        </is>
-      </c>
-      <c r="E167" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D167" s="144" t="inlineStr">
+        <is>
+          <t>Требуется изоляция беспроводного сегмента (ЗБС.3) от остальной внутренней сети на сетевом уровне (L3) — маршрутизация и списки управления доступом (ACL) между сегментами, без обязательной канальной изоляции. Это защищает от случаев, когда скомпрометированное Wi-Fi-устройство может свободно маршрутизировать трафик во внутреннюю сеть.
+Главная цель меры — задать менее строгий (по сравнению с мерой ЗБС.4), но обязательный минимум изоляции беспроводного сегмента для уровней защиты, где полная канальная изоляция не требуется: маршрутизация и списки контроля доступа на сетевом уровне всё равно не позволяют скомпрометированному Wi-Fi-устройству свободно взаимодействовать с внутренней сетью в обход установленных правил.</t>
+        </is>
+      </c>
+      <c r="E167" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Между беспроводным сегментом и прочими внутренними сетями настраивается маршрутизация с контролем доступа (ACL/МЭ) на сетевом уровне, прямая L2-связность не обязательна к исключению.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco Catalyst/WLC (L3 ACL) и пр.
-- Российские сертифицированные: PT NGFW, UserGate NGFW и пр.
-- Открытый код: iptables/nftables на пограничном маршрутизаторе сегмента и пр.</t>
+            <t xml:space="preserve">
+Между беспроводным сегментом и прочими внутренними сетями настраивается маршрутизация с контролем доступа (списками контроля доступа, межсетевым экраном) на сетевом уровне; прямая канальная (L2) изоляция при этом не обязательна.
+Класс используемых средств — маршрутизаторы и межсетевые экраны с поддержкой списков контроля доступа (ACL).
+Иностранные: Cisco Catalyst/WLC (ACL на сетевом уровне) и пр.
+Российские сертифицированные (ФСТЭК): PT NGFW, UserGate NGFW и др.
+Открытый код: iptables/nftables на пограничном маршрутизаторе сегмента и др.</t>
           </r>
         </is>
       </c>
@@ -12627,10 +12515,12 @@
           </r>
         </is>
       </c>
-      <c r="G167" s="36" t="inlineStr">
-        <is>
-          <t>1. ACL между сегментами не покрывают все направления трафика (например, только исходящий, без входящего контроля).
-2. Правила маршрутизации/ACL не пересматривались при изменении состава сегмента.</t>
+      <c r="G167" s="151" t="inlineStr">
+        <is>
+          <t>1. Списки контроля доступа между сегментами не покрывают все направления трафика (например, только исходящий, без входящего контроля);
+2. Правила маршрутизации и ACL не пересматривались при изменении состава сегмента;
+3. Часть трафика между беспроводным сегментом и внутренней сетью проходит в обход настроенной маршрутизации;
+4. Тестирование фактической изоляции (попытка недопустимого маршрута) не проводится.</t>
         </is>
       </c>
     </row>
@@ -12650,51 +12540,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D168" s="34" t="inlineStr">
-        <is>
-          <t>Между беспроводным сегментом (ЗБС.3) и остальной внутренней сетью должен стоять межсетевой экран, фильтрующий трафик не только по адресам/портам (сетевой уровень), но и по содержимому/приложениям (прикладной уровень). Это позволяет исключать случаи, когда вредоносный трафик или туннелирование внутри разрешённого протокола проходят через фильтр, ограниченный только сетевым уровнем, а также когда происходит обход политики доступа через разрешённые порты с нелегитимным содержимым.</t>
-        </is>
-      </c>
-      <c r="E168" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">На стыке беспроводного сегмента с остальной сетью устанавливается межсетевой экран нового поколения (NGFW) с включённой фильтрацией на прикладном уровне (App-ID/DPI), а не только классический stateful-МЭ. Политики фильтрации формируются по принципу минимально необходимого доступа.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Palo Alto NGFW, Fortinet FortiGate и прочие.
-- Российские сертифицированные: PT NGFW (Positive Technologies, фильтрация на сетевом и прикладном уровнях, DPI), UserGate NGFW и прочие.
-- Открытый код: pfSense + Suricata (в режиме inline) и прочие.</t>
+      <c r="D168" s="144" t="inlineStr">
+        <is>
+          <t>Между беспроводным сегментом (ЗБС.3) и остальной внутренней сетью должен стоять межсетевой экран, фильтрующий трафик не только по адресам/портам (сетевой уровень), но и по содержимому/приложениям (прикладной уровень). Это позволяет исключать случаи, когда вредоносный трафик или туннелирование внутри разрешённого протокола проходят через фильтр, ограниченный только сетевым уровнем, а также когда происходит обход политики доступа через разрешённые порты с нелегитимным содержимым.
+Главная цель меры — исключить обход политики доступа, при котором вредоносный трафик или туннелирование маскируется под разрешённый протокол: фильтрация только по адресам и портам не способна выявить такую маскировку, тогда как анализ на прикладном уровне позволяет распознать несоответствие фактического содержимого заявленному протоколу.</t>
+        </is>
+      </c>
+      <c r="E168" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+На стыке беспроводного сегмента с остальной сетью устанавливается межсетевой экран нового поколения (NGFW) с включённой фильтрацией на прикладном уровне (App-ID/DPI), а не только классический stateful-межсетевой экран. Политики фильтрации формируются по принципу минимально необходимого доступа.
+Класс используемых средств — межсетевые экраны следующего поколения (NGFW) с функцией глубокого анализа пакетов (DPI).
+Иностранные: Palo Alto NGFW, Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): PT NGFW, UserGate NGFW и др.
+Открытый код: pfSense совместно с Suricata (в режиме inline) и др.</t>
           </r>
         </is>
       </c>
@@ -12722,10 +12589,12 @@
           </r>
         </is>
       </c>
-      <c r="G168" s="36" t="inlineStr">
-        <is>
-          <t>1. Фильтрация настроена только на сетевом уровне (адреса/порты), прикладной уровень не задействован.
-2. Политики МЭ избыточно широкие (правила «разрешить всё» вместо точечных правил).</t>
+      <c r="G168" s="151" t="inlineStr">
+        <is>
+          <t>1. Фильтрация настроена только на сетевом уровне (по адресам и портам), прикладной уровень не задействован;
+2. Политики межсетевого экрана избыточно широкие (правила «разрешить всё» вместо точечных правил);
+3. Сигнатурные базы и правила анализа прикладного уровня не обновляются на регулярной основе;
+4. Эффективность фильтрации на прикладном уровне не проверяется тестированием.</t>
         </is>
       </c>
     </row>
@@ -12745,52 +12614,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D169" s="34" t="inlineStr">
-        <is>
-          <t>Взаимодействие беспроводного сегмента с остальной сетью должно происходить строго по заранее определённым правилам и протоколам, а не произвольным образом. Это соответствие нужно постоянно контролировать, а не только настроить один раз, чтобы не возникал постепенный «дрейф» правил межсетевого экранирования (накопление избыточных разрешений со временем) и было запрещено использование нештатных протоколов или портов в обход утверждённой схемы взаимодействия.</t>
-        </is>
-      </c>
-      <c r="E169" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D169" s="144" t="inlineStr">
+        <is>
+          <t>Взаимодействие беспроводного сегмента с остальной сетью должно происходить строго по заранее определённым правилам и протоколам, а не произвольным образом. Это соответствие нужно постоянно контролировать, а не только настроить один раз, чтобы не возникал постепенный «дрейф» правил межсетевого экранирования (накопление избыточных разрешений со временем) и было запрещено использование нештатных протоколов или портов в обход утверждённой схемы взаимодействия.
+Главная цель меры — не допустить постепенного «дрейфа» правил межсетевого экранирования (накопления избыточных, никем не пересматриваемых разрешений с течением времени) и использования нештатных протоколов или портов в обход утверждённой схемы взаимодействия, поскольку однократной настройки правил недостаточно — соответствие фактической конфигурации утверждённым правилам нужно подтверждать регулярно.</t>
+        </is>
+      </c>
+      <c r="E169" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Реализация правил взаимодействия (матрица допустимых протоколов и направлений трафика между сегментом ЗБС.3 и остальной сетью) на межсетевое экранирование (МЭ) и периодическая сверка задокументированных правил с фактической конфигурацией — вручную или средствами анализа конфигураций.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco Firepower Management Center (аудит правил) и прочие.
-- Российские сертифицированные: PT NGFW (журналирование и анализ применяемых правил), UserGate NGFW и прочие.
-- Открытый код: nftables + скрипты сверки конфигурации с эталоном и прочие.</t>
+            <t xml:space="preserve">
+Правила взаимодействия (матрица допустимых протоколов и направлений трафика между сегментом ЗБС.3 и остальной сетью) реализуются на межсетевом экране, а соответствие задокументированных правил фактической конфигурации периодически сверяется — вручную либо средствами анализа конфигураций.
+Класс используемых средств — межсетевые экраны, средства анализа и контроля соответствия конфигураций сетевой политике.
+Иностранные: Cisco Firepower Management Center (аудит правил) и пр.
+Российские сертифицированные (ФСТЭК): PT NGFW (журналирование и анализ применяемых правил), UserGate NGFW и др.
+Открытый код: nftables совместно со скриптами сверки конфигурации с эталоном и др.</t>
           </r>
         </is>
       </c>
@@ -12818,10 +12663,12 @@
           </r>
         </is>
       </c>
-      <c r="G169" s="36" t="inlineStr">
-        <is>
-          <t>1. Матрица допустимого взаимодействия устарела или не работает.
-2. Фактическая конфигурация МЭ расходится с утверждённой матрицей (избыточные правила не удаляются).</t>
+      <c r="G169" s="151" t="inlineStr">
+        <is>
+          <t>1. Матрица допустимого взаимодействия устарела и не отражает фактически используемые протоколы и направления;
+2. Фактическая конфигурация межсетевого экрана расходится с утверждённой матрицей (избыточные правила не удаляются);
+3. Периодическая сверка фактической конфигурации с матрицей не проводится или проводится формально;
+4. Ответственный за актуальность матрицы и её сверку с конфигурацией не определён.</t>
         </is>
       </c>
     </row>
@@ -12841,51 +12688,28 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D170" s="34" t="inlineStr">
-        <is>
-          <t>Точки доступа должны отклонять подключение любых устройств, не внесённых в реестр разрешённых, включая попытки подключения снаружи здания (с парковки, соседних помещений). Реализация меры не допустит подключение постороннего устройства к корпоративному Wi-Fi при перехвате или подборе учётных данных и предотвратит атаку с территориально удалённой точки (через направленную антенну) без физического проникновения в здание.</t>
-        </is>
-      </c>
-      <c r="E170" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D170" s="144" t="inlineStr">
+        <is>
+          <t>Точки доступа должны отклонять подключение любых устройств, не внесённых в реестр разрешённых, включая попытки подключения снаружи здания (с парковки, соседних помещений). Реализация меры не допустит подключение постороннего устройства к корпоративному Wi-Fi при перехвате или подборе учётных данных и предотвратит атаку с территориально удалённой точки (через направленную антенну) без физического проникновения в здание.
+Главная цель меры — не допустить подключения постороннего устройства к корпоративной беспроводной сети при перехвате или подборе учётных данных, а также предотвратить атаку с территориально удалённой точки (например, через направленную антенну с парковки или соседнего помещения) без физического проникновения в контролируемые здания и сооружения организации.</t>
+        </is>
+      </c>
+      <c r="E170" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-На точках доступа включается whitelist-контроль по MAC-адресу/сертификату устройства в дополнение к аутентификации устройств по 802.1X (ЗБС.1). Мощность сигнала точек доступа настраивается так, чтобы минимизировать покрытие за пределами контролируемой территории. Опционально — WIPS (беспроводная система предотвращения вторжений) для активного обнаружения и блокировки rogue-подключений через дополнительный анализ политик безопасности и классификацию устройств.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco WLC (rogue containment), Aruba WIPS и прочие.
-- Российские сертифицированные: точки доступа «Атликс» с whitelist-фильтрацией и прочие.
-- Открытый код: hostapd (MAC ACL) и прочие.</t>
+            <t xml:space="preserve">
+На точках доступа включается контроль по списку разрешённых устройств (whitelist) по MAC-адресу или сертификату устройства в дополнение к аутентификации по протоколу 802.1X (мера ЗБС.1). Мощность сигнала точек доступа настраивается так, чтобы минимизировать покрытие за пределами контролируемой территории. Дополнительно может применяться беспроводная система предотвращения вторжений (WIPS) для активного обнаружения и блокирования несанкционированных (rogue) точек доступа и подключений.
+Класс используемых средств — точки доступа с функцией контроля устройств по списку разрешённых, беспроводные системы предотвращения вторжений (WIPS).
+Иностранные: Cisco WLC (rogue containment), Aruba WIPS и пр.
+Российские сертифицированные (ФСТЭК): точки доступа «Атликс» с контролем по списку разрешённых устройств и др.
+Открытый код: hostapd (контроль по MAC-адресам) и др.</t>
           </r>
         </is>
       </c>
@@ -12913,10 +12737,12 @@
           </r>
         </is>
       </c>
-      <c r="G170" s="36" t="inlineStr">
-        <is>
-          <t>1. Блокировка реализована только через 802.1X без дополнительного контроля по устройству (whitelist).
-2. Мощность сигнала не оптимизирована — сеть уверенно принимается за пределами здания.</t>
+      <c r="G170" s="151" t="inlineStr">
+        <is>
+          <t>1. Блокировка реализована только через 802.1X без дополнительного контроля по списку разрешённых устройств;
+2. Мощность сигнала не оптимизирована — сеть уверенно принимается за пределами здания;
+3. Система предотвращения вторжений (WIPS), выявляющая несанкционированные точки доступа, не развёрнута;
+4. Список разрешённых устройств не актуализируется при выводе устройств из эксплуатации.</t>
         </is>
       </c>
     </row>
@@ -12949,51 +12775,28 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D172" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует, что каждая отклонённая попытка подключения незарегистрированного устройства (следуя ЗБС.8) должна фиксироваться как событие, а не просто блокироваться молча. Такой подход позволит предотвратить серию попыток подбора доступа, которая обычно остаётся незамеченной при отсутствии регистрации. Также без этой меры невозможно расследовать инцидент постфактум без истории попыток подключения.</t>
-        </is>
-      </c>
-      <c r="E172" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D172" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, что каждая отклонённая попытка подключения незарегистрированного устройства (следуя ЗБС.8) должна фиксироваться как событие, а не просто блокироваться молча. Такой подход позволит предотвратить серию попыток подбора доступа, которая обычно остаётся незамеченной при отсутствии регистрации. Также без этой меры невозможно расследовать инцидент постфактум без истории попыток подключения.
+Главная цель меры — обеспечить возможность выявления серии попыток подбора доступа к беспроводной сети, которая обычно остаётся незамеченной при отсутствии регистрации, а также сформировать историю попыток подключения, без которой невозможно расследовать инцидент постфактум.</t>
+        </is>
+      </c>
+      <c r="E172" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Точки доступа настраиваются на генерацию события при каждой отклонённой попытке подключения (MAC-адрес устройства, время, точка доступа), дополнительно события могут передаваться в SIEM для корреляции и алертинга при аномальной частоте попыток.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>- Иностранные: Cisco WLC + Splunk и прочие.
-- Российские сертифицированные: PT MaxPatrol SIEM, Kaspersky KUMA — приём и корреляция событий с точек доступа и прочие
-- Открытый код: Wazuh и прочие.</t>
+            <t xml:space="preserve">
+Точки доступа настраиваются на генерацию события при каждой отклонённой попытке подключения (с фиксацией MAC-адреса устройства, времени и точки доступа); дополнительно события могут передаваться в SIEM-систему для корреляции и оповещения при аномальной частоте попыток.
+Класс используемых средств — точки доступа со встроенным журналированием, системы управления событиями информационной безопасности (SIEM).
+Иностранные: Cisco WLC совместно со Splunk и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, Kaspersky KUMA (приём и корреляция событий с точек доступа) и др.
+Открытый код: Wazuh и др.</t>
           </r>
         </is>
       </c>
@@ -13021,10 +12824,12 @@
           </r>
         </is>
       </c>
-      <c r="G172" s="36" t="inlineStr">
-        <is>
-          <t>1. События регистрируются локально на точке доступа, но отдельно не выделяются попытки подключения за пределами периметра.
-2. Отсутствует алертинг при массовых или повторяющихся попытках подключения (событие фиксируется, но не анализируется).</t>
+      <c r="G172" s="151" t="inlineStr">
+        <is>
+          <t>1. События регистрируются локально на точке доступа, но отдельно не выделяются попытки подключения из-за пределов контролируемой территории;
+2. Оповещение при массовых или повторяющихся попытках подключения не настроено (событие фиксируется, но не анализируется);
+3. События отклонённых подключений не передаются в централизованную систему (SIEM), что затрудняет корреляцию с иными событиями;
+4. Журналы отклонённых подключений хранятся менее срока, необходимого для расследования.</t>
         </is>
       </c>
     </row>
@@ -13044,52 +12849,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D173" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы любое изменение настроек межсетевого экранирования (МЭ) или сегментации, защищающих беспроводной сегмент (ЗБС.4–ЗБС.7), фиксировалось как полноценное событие — кто, когда и что изменил. Именно так можно вовремя предотвратить несанкционированное или ошибочное изменение правил (например, добавление избыточного разрешения), которое иначе осталось бы незамеченным без журнала изменений, и когда невозможно установить причину появления такой «дыры» в правилах при расследовании.</t>
-        </is>
-      </c>
-      <c r="E173" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D173" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы любое изменение настроек межсетевого экранирования (МЭ) или сегментации, защищающих беспроводной сегмент (ЗБС.4–ЗБС.7), фиксировалось как полноценное событие — кто, когда и что изменил. Именно так можно вовремя предотвратить несанкционированное или ошибочное изменение правил (например, добавление избыточного разрешения), которое иначе осталось бы незамеченным без журнала изменений, и когда невозможно установить причину появления такой «дыры» в правилах при расследовании.
+Главная цель меры — своевременно выявлять несанкционированное или ошибочное изменение правил защиты беспроводного сегмента (например, добавление избыточного разрешения), которое иначе осталось бы незамеченным, и обеспечить возможность установить причину появления такой «дыры» в правилах при расследовании.</t>
+        </is>
+      </c>
+      <c r="E173" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-На МЭ/системах сегментации включается журналирование изменений конфигурации (аудит-лог) с фиксацией учётной записи администратора, времени и содержания. События по изменениям дополнительно могут передаваться в SIEM/систему управления изменениями.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Cisco Firepower (change audit log) и прочие.
-- Российские сертифицированные: PT NGFW для журнал изменений конфигурации сети, PT MaxPatrol SIEM / Kaspersky KUMA для централизованного сбора и прочие.
-- Открытый код: Git-репозиторий конфигураций (config-as-code) + аудит коммитов и прочие.</t>
+            <t xml:space="preserve">
+На межсетевых экранах и системах сегментации включается журналирование изменений конфигурации (аудит-лог) с фиксацией учётной записи администратора, времени и содержания изменения. События об изменениях дополнительно могут передаваться в SIEM-систему или систему управления изменениями.
+Класс используемых средств — межсетевые экраны и системы сегментации со встроенным аудитом изменений, системы управления событиями информационной безопасности (SIEM).
+Иностранные: Cisco Firepower (журнал изменений конфигурации) и пр.
+Российские сертифицированные (ФСТЭК): PT NGFW (журнал изменений конфигурации сети), MaxPatrol SIEM, Kaspersky KUMA (централизованный сбор) и др.
+Открытый код: Git-репозиторий конфигураций (config-as-code) совместно с аудитом коммитов и др.</t>
           </r>
         </is>
       </c>
@@ -13117,10 +12898,12 @@
           </r>
         </is>
       </c>
-      <c r="G173" s="36" t="inlineStr">
-        <is>
-          <t>1. Изменения конфигурации фиксируются не на всех устройствах сегментации.
-2. Журнал изменений не содержит привязки к конкретным учётным записям (используется общая административная учётная запись).</t>
+      <c r="G173" s="151" t="inlineStr">
+        <is>
+          <t>1. Изменения конфигурации фиксируются не на всех устройствах сегментации;
+2. Журнал изменений не содержит привязки к конкретным учётным записям (используется общая административная учётная запись);
+3. События изменения конфигурации не передаются в централизованную систему (SIEM);
+4. Журнал изменений не анализируется на предмет выявления несанкционированных или ошибочных изменений.</t>
         </is>
       </c>
     </row>
@@ -27030,8 +26813,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -12949,10 +12949,61 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D176" s="21" t="n"/>
-      <c r="E176" s="31" t="n"/>
-      <c r="F176" s="31" t="n"/>
-      <c r="G176" s="31" t="n"/>
+      <c r="D176" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регулярно проверять оборудование и программное обеспечение, обеспечивающие сегментацию и изоляцию контуров безопасности (меры СМЭ.1—СМЭ.13), на предмет известных (описанных в общедоступных базах данных) уязвимостей, использование которых потенциально позволяет обойти установленную сетевую изоляцию, а выявленные уязвимости — устранять в оперативном порядке.
+Главная цель меры — не допустить, чтобы средства, отвечающие за разграничение контуров безопасности, сами становились точкой обхода этого разграничения: известная, но не устранённая уязвимость в межсетевом экране или ином сегментирующем оборудовании способна свести на нет всю эффективность сетевой сегментации, реализованной мерами СМЭ.1—СМЭ.13.</t>
+        </is>
+      </c>
+      <c r="E176" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Проведение регулярного сканирования на наличие уязвимостей (vulnerability scanning) оборудования и ПО, обеспечивающих сегментацию и межсетевое экранирование между контурами безопасности;
+2. Сопоставление выявленных версий ПО и конфигураций с общедоступными базами данных уязвимостей (например, банком данных угроз ФСТЭК России, CVE) для определения применимости известных уязвимостей;
+3. Установление и соблюдение регламентированных сроков устранения выявленных уязвимостей в зависимости от степени их критичности (установка обновлений, применение компенсирующих мер);
+4. Повторную проверку (регрессионное сканирование) после устранения уязвимости для подтверждения фактического закрытия.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей), системы управления уязвимостями (Vulnerability Management).
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F176" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами сетевой инфраструктуры и подразделением информационной безопасности;
+2. Отчёты сканирования на наличие уязвимостей оборудования и ПО, обеспечивающих сегментацию контуров безопасности, за проверяемый период;
+3. Регламент, устанавливающий сроки устранения уязвимостей в зависимости от степени критичности;
+4. Акты (свидетельства) устранения выявленных уязвимостей и результаты повторного сканирования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G176" s="151" t="inlineStr">
+        <is>
+          <t>1. Сканирование на наличие уязвимостей охватывает не всё оборудование, обеспечивающее сегментацию контуров безопасности;
+2. Установленные сроки устранения уязвимостей систематически не соблюдаются;
+3. Повторное сканирование после устранения уязвимости не проводится, фактическое закрытие не подтверждается;
+4. Критичные уязвимости устраняются с той же приоритетностью, что и низкокритичные, без учёта степени риска.</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="85.5" customHeight="1">
       <c r="A177" s="20" t="inlineStr">
@@ -12970,10 +13021,86 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D177" s="21" t="n"/>
-      <c r="E177" s="31" t="n"/>
-      <c r="F177" s="31" t="n"/>
-      <c r="G177" s="31" t="n"/>
+      <c r="D177" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к границе с сетью Интернет: оборудование и ПО, обеспечивающие изоляцию внутренних сетей от Интернета (меры СМЭ.14—СМЭ.19), должны регулярно проверяться на известные уязвимости, а выявленные — оперативно устраняться.
+Главная цель меры — исключить ситуацию, при которой периметр организации защищён формально (межсетевые экраны и иные средства установлены), но фактически уязвим из-за неустранённых известных недостатков в самих защитных средствах, поскольку граница с публичным Интернетом — наиболее вероятная точка приложения усилий внешнего злоумышленника.</t>
+        </is>
+      </c>
+      <c r="E177" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная составляющая предполагает:
+1. Разработку и утверждение регламента управления уязвимостями (vulnerability management), определяющего периодичность сканирования, источники данных об уязвимостях, сроки устранения по степени критичности и ответственных лиц;
+2. Ведение перечня оборудования и ПО, обеспечивающего изоляцию с сетью Интернет, подлежащего первоочередному контролю уязвимостей ввиду повышенной критичности этой границы.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль дополняется:
+1. Проведением регулярного сканирования на наличие уязвимостей оборудования и ПО на границе с сетью Интернет с повышенной (по сравнению с внутренними сегментами) периодичностью ввиду критичности этой границы;
+2. Сопоставлением выявленных версий и конфигураций с общедоступными базами данных уязвимостей (банк данных угроз ФСТЭК России, CVE);
+3. Приоритетным устранением выявленных уязвимостей на периметре с последующим регрессионным сканированием.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей).
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F177" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент управления уязвимостями с указанием периодичности сканирования и сроков устранения по степени критичности;
+2. Перечень оборудования и ПО на границе с сетью Интернет, подлежащего первоочередному контролю.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Отчёты сканирования на наличие уязвимостей оборудования и ПО на границе с сетью Интернет за проверяемый период;
+2. Акты (свидетельства) устранения выявленных уязвимостей и результаты повторного сканирования;
+3. Итоги интервью с администраторами сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G177" s="151" t="inlineStr">
+        <is>
+          <t>1. Периодичность сканирования оборудования на границе с сетью Интернет не выше, чем для внутренних сегментов, несмотря на повышенную критичность этой границы;
+2. Установленные сроки устранения критичных уязвимостей на периметре не соблюдаются;
+3. Часть оборудования на границе с сетью Интернет исключена из регулярного сканирования (например, оборудование операторов связи или подрядчиков);
+4. Повторное сканирование после устранения уязвимости не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="99.75" customHeight="1">
       <c r="A178" s="20" t="inlineStr">
@@ -12991,10 +13118,86 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D178" s="21" t="n"/>
-      <c r="E178" s="31" t="n"/>
-      <c r="F178" s="31" t="n"/>
-      <c r="G178" s="31" t="n"/>
+      <c r="D178" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к сегменту общедоступных объектов доступа (банкоматов, платёжных терминалов): оборудование и ПО, обеспечивающее изоляцию этого сегмента от сети Интернет (мера СМЭ.11), должны регулярно проверяться на известные уязвимости, а выявленные — оперативно устраняться.
+Главная цель меры — учесть повышенную критичность этой границы: общедоступные объекты доступа физически находятся вне контролируемой территории организации, и известная, но не устранённая уязвимость на границе этого сегмента существенно упрощает злоумышленнику получение контроля над устройствами, напрямую связанными с проведением финансовых операций.</t>
+        </is>
+      </c>
+      <c r="E178" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная составляющая предполагает:
+1. Включение оборудования на границе сегмента общедоступных объектов доступа в перечень объектов первоочередного контроля уязвимостей;
+2. Установление сокращённых (по сравнению с общим регламентом) сроков устранения выявленных на этой границе уязвимостей ввиду критичности сегмента.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль дополняется:
+1. Проведением регулярного сканирования на наличие уязвимостей оборудования и ПО на границе сегмента общедоступных объектов доступа с сетью Интернет;
+2. Сопоставлением выявленных версий и конфигураций с общедоступными базами данных уязвимостей (банк данных угроз ФСТЭК России, CVE);
+3. Приоритетным устранением выявленных уязвимостей с последующим регрессионным сканированием.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей).
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F178" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень оборудования на границе сегмента общедоступных объектов доступа, подлежащего первоочередному контролю уязвимостей;
+2. Регламент, устанавливающий сокращённые сроки устранения уязвимостей для данного сегмента.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Отчёты сканирования на наличие уязвимостей оборудования на границе сегмента общедоступных объектов доступа за проверяемый период;
+2. Акты (свидетельства) устранения выявленных уязвимостей и результаты повторного сканирования;
+3. Итоги интервью с администраторами сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G178" s="151" t="inlineStr">
+        <is>
+          <t>1. Оборудование на границе сегмента общедоступных объектов доступа сканируется по общему графику, без учёта повышенной критичности сегмента;
+2. Сокращённые сроки устранения уязвимостей для данного сегмента не установлены или не соблюдаются;
+3. Часть общедоступных объектов доступа (например, территориально удалённые) исключена из регулярного сканирования;
+4. Повторное сканирование после устранения уязвимости не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="85.5" customHeight="1">
       <c r="A179" s="20" t="inlineStr">
@@ -13012,10 +13215,86 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D179" s="21" t="n"/>
-      <c r="E179" s="31" t="n"/>
-      <c r="F179" s="31" t="n"/>
-      <c r="G179" s="31" t="n"/>
+      <c r="D179" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к самим ресурсам доступа, размещённым в сегменте, подключённом к сети Интернет (DMZ), — веб-серверам, почтовым шлюзам, API-интерфейсам: эти ресурсы должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный логический доступ, а выявленные уязвимости — оперативно устраняться.
+Главная цель меры — защитить непосредственно интернет-доступные ресурсы (в отличие от меры ЦЗИ.2, которая контролирует уязвимости сетевого оборудования на границе), поскольку именно уязвимости прикладного уровня самих ресурсов (устаревшие версии веб-приложений, известные уязвимости CMS, библиотек) наиболее часто используются для получения несанкционированного доступа.</t>
+        </is>
+      </c>
+      <c r="E179" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная составляющая предполагает:
+1. Ведение перечня ресурсов доступа, размещённых в сегменте, подключённом к сети Интернет, подлежащих регулярному контролю уязвимостей;
+2. Установление требования об обязательном сканировании ресурса на уязвимости перед вводом в эксплуатацию и после каждого существенного изменения (обновления версии, добавления функциональности).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль дополняется:
+1. Проведением регулярного сканирования на наличие уязвимостей интернет-доступных ресурсов, включая сканирование на уровне веб-приложений (поиск известных уязвимостей CMS, библиотек, компонентов);
+2. Сопоставлением выявленных версий компонентов с общедоступными базами данных уязвимостей (банк данных угроз ФСТЭК России, CVE);
+3. Приоритетным устранением выявленных уязвимостей интернет-доступных ресурсов с последующим регрессионным сканированием.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей, в том числе веб-приложений).
+Иностранные: Tenable Nessus, Qualys WAS (для веб-приложений) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, PT Application Inspector (анализ защищённости приложений) и др.
+Открытый код: OpenVAS, OWASP ZAP и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F179" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень интернет-доступных ресурсов, подлежащих регулярному контролю уязвимостей;
+2. Свидетельства сканирования ресурса на уязвимости перед вводом в эксплуатацию (акты, отчёты).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Отчёты сканирования на наличие уязвимостей интернет-доступных ресурсов за проверяемый период;
+2. Акты (свидетельства) устранения выявленных уязвимостей и результаты повторного сканирования;
+3. Итоги интервью с администраторами интернет-доступных ресурсов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G179" s="151" t="inlineStr">
+        <is>
+          <t>1. Сканирование на уязвимости не охватывает уровень веб-приложений, ограничивается сетевым уровнем;
+2. Новые интернет-доступные ресурсы вводятся в эксплуатацию без предварительного сканирования на уязвимости;
+3. Выявленные уязвимости прикладного уровня устраняются со значительной задержкой относительно установленных сроков;
+4. Повторное сканирование после устранения уязвимости не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="57" customHeight="1">
       <c r="A180" s="20" t="inlineStr">
@@ -13033,10 +13312,86 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D180" s="21" t="n"/>
-      <c r="E180" s="31" t="n"/>
-      <c r="F180" s="31" t="n"/>
-      <c r="G180" s="31" t="n"/>
+      <c r="D180" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к средствам удалённого доступа (VPN-шлюзам, серверам терминального доступа): эти средства должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный удалённый доступ, а выявленные уязвимости — оперативно устраняться.
+Главная цель меры — защитить каналы удалённого доступа, которые являются одной из наиболее часто эксплуатируемых точек входа злоумышленника: известная, но не устранённая уязвимость VPN-шлюза или сервера терминального доступа зачастую позволяет обойти даже корректно настроенные меры аутентификации (меры РД.1—РД.29).</t>
+        </is>
+      </c>
+      <c r="E180" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная составляющая предполагает:
+1. Ведение перечня средств удалённого доступа, подлежащих регулярному контролю уязвимостей;
+2. Установление требования о приоритетном (внеплановом) сканировании средств удалённого доступа при публикации критичных уязвимостей соответствующих продуктов.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль дополняется:
+1. Проведением регулярного сканирования на наличие уязвимостей средств удалённого доступа (VPN-шлюзов, серверов терминального доступа);
+2. Оперативным отслеживанием бюллетеней безопасности производителей используемых средств удалённого доступа и банка данных угроз ФСТЭК России на предмет публикации новых критичных уязвимостей;
+3. Приоритетным устранением выявленных уязвимостей средств удалённого доступа с последующим регрессионным сканированием.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей).
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F180" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень средств удалённого доступа, подлежащих регулярному контролю уязвимостей;
+2. Регламент, устанавливающий порядок внепланового сканирования при публикации критичных уязвимостей.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Отчёты сканирования на наличие уязвимостей средств удалённого доступа за проверяемый период;
+2. Акты (свидетельства) устранения выявленных уязвимостей и результаты повторного сканирования;
+3. Итоги интервью с администраторами средств удалённого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G180" s="151" t="inlineStr">
+        <is>
+          <t>1. Средства удалённого доступа сканируются по общему графику, без учёта критичности этого канала;
+2. Внеплановое сканирование при публикации критичных уязвимостей продукта не проводится;
+3. Бюллетени безопасности производителей используемых средств удалённого доступа не отслеживаются на регулярной основе;
+4. Устранение выявленных уязвимостей средств удалённого доступа затягивается сверх установленных сроков.</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="85.5" customHeight="1">
       <c r="A181" s="20" t="inlineStr">
@@ -13054,10 +13409,61 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D181" s="21" t="n"/>
-      <c r="E181" s="31" t="n"/>
-      <c r="F181" s="31" t="n"/>
-      <c r="G181" s="31" t="n"/>
+      <c r="D181" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к ресурсам доступа, размещённым во внутренней вычислительной сети организации (не подключённой напрямую к сети Интернет): такие ресурсы также должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный логический доступ.
+Главная цель меры — не допустить ложного ощущения защищённости внутренних ресурсов на основании одной лишь их сетевой изолированности от Интернета: значительная часть реальных атак развивается уже после первичного проникновения за счёт эксплуатации известных, но не устранённых уязвимостей внутренних систем при горизонтальном перемещении злоумышленника (lateral movement).</t>
+        </is>
+      </c>
+      <c r="E181" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Проведение регулярного сканирования на наличие уязвимостей ресурсов доступа, размещённых во внутренней вычислительной сети организации;
+2. Сопоставление выявленных версий ПО и конфигураций с общедоступными базами данных уязвимостей (банк данных угроз ФСТЭК России, CVE);
+3. Установление и соблюдение регламентированных сроков устранения выявленных уязвимостей в зависимости от критичности ресурса и степени риска;
+4. Повторное (регрессионное) сканирование после устранения уязвимости для подтверждения фактического закрытия.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей).
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F181" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами внутренней сетевой инфраструктуры;
+2. Отчёты сканирования на наличие уязвимостей внутренних ресурсов доступа за проверяемый период;
+3. Регламент, устанавливающий сроки устранения уязвимостей внутренних ресурсов по степени критичности;
+4. Акты (свидетельства) устранения выявленных уязвимостей и результаты повторного сканирования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G181" s="151" t="inlineStr">
+        <is>
+          <t>1. Сканирование на наличие уязвимостей охватывает не все внутренние ресурсы доступа (например, забыли про унаследованные системы);
+2. Устранение уязвимостей внутренних ресурсов откладывается на более поздний срок по сравнению с интернет-доступными ресурсами без документированного обоснования;
+3. Повторное сканирование после устранения уязвимости не проводится;
+4. Критичность выявленных уязвимостей не оценивается применительно к конкретному ресурсу (используется только общая оценка производителя сканера).</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="57" customHeight="1">
       <c r="A182" s="20" t="inlineStr">
@@ -13075,10 +13481,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D182" s="21" t="n"/>
-      <c r="E182" s="31" t="n"/>
-      <c r="F182" s="31" t="n"/>
-      <c r="G182" s="31" t="n"/>
+      <c r="D182" s="144" t="inlineStr">
+        <is>
+          <t>Мера задаёт конкретный технический способ реализации контроля, предусмотренного мерами ЦЗИ.1—ЦЗИ.6: применительно к серверному и сетевому оборудованию контроль отсутствия известных уязвимостей выполняется путём сканирования и анализа параметров настроек (конфигураций) этого оборудования.
+Главная цель меры — обеспечить, чтобы уязвимости, связанные не с версией установленного ПО, а именно с некорректной или небезопасной конфигурацией серверного и сетевого оборудования (открытые неиспользуемые порты, небезопасные параметры протоколов, оставленные тестовые учётные записи), также выявлялись в рамках регулярного контроля, а не оставались вне поля зрения сканирования, ориентированного только на версии ПО.</t>
+        </is>
+      </c>
+      <c r="E182" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Проведение регулярного сканирования параметров настроек серверного и сетевого оборудования на соответствие эталонным (безопасным) профилям конфигурации;
+2. Использование банков данных типовых недостатков конфигурации (например, CIS Benchmarks, рекомендаций производителей) для формирования критериев проверки;
+3. Формирование отчётов о выявленных отклонениях от безопасной конфигурации с указанием конкретного параметра и рекомендуемого значения.
+Класс используемых средств — средства анализа защищённости с функцией контроля конфигураций (Configuration Assessment).
+Иностранные: Tenable Nessus (Compliance Checks), Qualys Policy Compliance и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenSCAP и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F182" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами серверного и сетевого оборудования;
+2. Эталонные профили безопасной конфигурации серверного и сетевого оборудования;
+3. Отчёты сканирования параметров настроек за проверяемый период с перечнем выявленных отклонений;
+4. Акты устранения выявленных отклонений от эталонной конфигурации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G182" s="151" t="inlineStr">
+        <is>
+          <t>1. Эталонные профили безопасной конфигурации не разработаны или не утверждены;
+2. Сканирование параметров настроек охватывает не всё серверное и сетевое оборудование;
+3. Выявленные отклонения от эталонной конфигурации не устраняются в установленный срок;
+4. Эталонные профили конфигурации не пересматриваются при появлении новых рекомендаций производителей или регуляторов.</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="114" customHeight="1">
       <c r="A183" s="20" t="inlineStr">
@@ -13096,10 +13552,61 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D183" s="21" t="n"/>
-      <c r="E183" s="53" t="n"/>
-      <c r="F183" s="53" t="n"/>
-      <c r="G183" s="53" t="n"/>
+      <c r="D183" s="144" t="inlineStr">
+        <is>
+          <t>Мера задаёт способ реализации контроля, предусмотренного мерами ЦЗИ.1—ЦЗИ.6, применительно к прикладному ПО, ПО автоматизированных систем (АС) и системному ПО, установленному на серверном и сетевом оборудовании: контроль осуществляется путём сканирования и анализа состава, версий и параметров настроек такого ПО.
+Главная цель меры — распространить контроль уязвимостей не только на само серверное и сетевое оборудование (мера ЦЗИ.7), но и на программное обеспечение, функционирующее на этом оборудовании, поскольку значительная часть известных уязвимостей относится именно к прикладному, системному ПО и ПО АС, а не к аппаратной платформе или сетевой конфигурации.</t>
+        </is>
+      </c>
+      <c r="E183" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Проведение регулярного сканирования серверного и сетевого оборудования для инвентаризации фактически установленного прикладного ПО, ПО АС и системного ПО с указанием версий;
+2. Сопоставление выявленного состава и версий ПО с общедоступными базами данных уязвимостей (банк данных угроз ФСТЭК России, CVE) для определения применимых уязвимостей;
+3. Анализ параметров настроек указанного ПО на соответствие эталонным (безопасным) профилям конфигурации;
+4. Формирование отчётов о выявленных уязвимостях и отклонениях конфигурации с последующим контролем их устранения.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей) с функцией инвентаризации ПО.
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F183" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами серверного и сетевого оборудования;
+2. Отчёты инвентаризации состава и версий прикладного, системного ПО и ПО АС на серверном и сетевом оборудовании;
+3. Отчёты сканирования на наличие уязвимостей выявленного ПО за проверяемый период;
+4. Акты (свидетельства) устранения выявленных уязвимостей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G183" s="157" t="inlineStr">
+        <is>
+          <t>1. Инвентаризация состава ПО охватывает не все серверы и сетевое оборудование;
+2. Сканирование не выявляет уязвимости отдельных категорий ПО (например, специализированного ПО АС собственной разработки, отсутствующего в базах данных уязвимостей);
+3. Выявленные уязвимости прикладного и системного ПО устраняются с нарушением установленных сроков;
+4. Результаты сканирования не сопоставляются с реестром ПО (меры ИУ.1—ИУ.2), что не позволяет выявить неучтённое ПО.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="85.5" customHeight="1">
       <c r="A184" s="20" t="inlineStr">
@@ -13117,10 +13624,61 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D184" s="21" t="n"/>
-      <c r="E184" s="53" t="n"/>
-      <c r="F184" s="53" t="n"/>
-      <c r="G184" s="53" t="n"/>
+      <c r="D184" s="144" t="inlineStr">
+        <is>
+          <t>Мера задаёт способ реализации контроля, предусмотренного мерами ЦЗИ.1—ЦЗИ.6, применительно к прикладному, системному ПО и ПО АС, установленному на автоматизированных рабочих местах (АРМ) пользователей и эксплуатационного персонала.
+Главная цель меры — распространить контроль известных уязвимостей на рабочие станции, которые, в отличие от серверов, эксплуатируются большим количеством пользователей, чаще подвергаются внешним воздействиям (электронная почта, веб-браузинг, съёмные носители) и в силу многочисленности парка сложнее поддаются единообразному контролю обновлений вручную.</t>
+        </is>
+      </c>
+      <c r="E184" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+1. Проведение регулярного сканирования АРМ пользователей и эксплуатационного персонала для инвентаризации фактически установленного прикладного, системного ПО и ПО АС с указанием версий;
+2. Сопоставление выявленного состава и версий ПО с общедоступными базами данных уязвимостей (банк данных угроз ФСТЭК России, CVE);
+3. Анализ параметров настроек ПО АРМ на соответствие эталонным (безопасным) профилям конфигурации;
+4. Формирование отчётов о выявленных уязвимостях и отклонениях с последующим контролем их устранения, в том числе с учётом территориально распределённого и многочисленного парка АРМ.
+Класс используемых средств — средства анализа защищённости с функцией инвентаризации ПО на конечных точках.
+Иностранные: Tenable Nessus (Agent-based scanning), Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F184" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами АРМ;
+2. Отчёты инвентаризации состава и версий ПО на выборке АРМ;
+3. Отчёты сканирования на наличие уязвимостей АРМ за проверяемый период;
+4. Акты (свидетельства) устранения выявленных уязвимостей на парке АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G184" s="157" t="inlineStr">
+        <is>
+          <t>1. Сканирование охватывает не весь парк АРМ (например, исключены удалённые или редко подключаемые рабочие места);
+2. Инвентаризация ПО на АРМ проводится нерегулярно, данные о версиях устаревают;
+3. Устранение выявленных уязвимостей на АРМ систематически затягивается сверх установленных сроков;
+4. Результаты сканирования не сопоставляются с перечнем разрешённого ПО (мера ЦЗИ.20).</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="71.25" customHeight="1">
       <c r="A185" s="20" t="inlineStr">
@@ -13138,10 +13696,61 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D185" s="21" t="n"/>
-      <c r="E185" s="53" t="n"/>
-      <c r="F185" s="53" t="n"/>
-      <c r="G185" s="53" t="n"/>
+      <c r="D185" s="144" t="inlineStr">
+        <is>
+          <t>Мера задаёт способ реализации контроля, предусмотренного мерами ЦЗИ.1—ЦЗИ.6, применительно к самим средствам и системам защиты информации: их состав, версии и параметры настроек также подлежат регулярному сканированию и анализу на предмет известных уязвимостей.
+Главная цель меры — исключить ситуацию, при которой контроль уязвимостей распространяется на всю инфраструктуру, кроме самих средств защиты информации, поскольку уязвимость в СЗИ способна не просто открыть отдельный канал атаки, а полностью обесценить защитную функцию, которую данное средство должно было обеспечивать.</t>
+        </is>
+      </c>
+      <c r="E185" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввиду того, что мера реализуется только технически, необходимо:
+1. Проведение регулярного сканирования средств и систем защиты информации для инвентаризации фактически установленных версий и параметров настроек;
+2. Сопоставление выявленных версий СЗИ с общедоступными базами данных уязвимостей (банк данных угроз ФСТЭК России, CVE) и бюллетенями безопасности производителей СЗИ;
+3. Анализ параметров настроек СЗИ на соответствие эталонным (безопасным) профилям конфигурации;
+4. Приоритетное устранение выявленных уязвимостей СЗИ с последующим регрессионным сканированием, учитывая критичность этих средств для общей системы защиты информации.
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей).
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F185" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Итоги интервью с администраторами средств и систем защиты информации;
+2. Отчёты инвентаризации состава и версий СЗИ за проверяемый период;
+3. Отчёты сканирования на наличие уязвимостей СЗИ;
+4. Акты (свидетельства) устранения выявленных уязвимостей СЗИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G185" s="157" t="inlineStr">
+        <is>
+          <t>1. Средства и системы защиты информации исключены из общего периметра сканирования уязвимостей (ошибочно считаются заведомо доверенными);
+2. Бюллетени безопасности производителей используемых СЗИ не отслеживаются на регулярной основе;
+3. Устранение выявленных уязвимостей СЗИ откладывается из опасения нарушить их работоспособность, без формального анализа риска;
+4. Повторное сканирование после устранения уязвимости СЗИ не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="57" customHeight="1">
       <c r="A186" s="20" t="inlineStr">
@@ -13159,10 +13768,55 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D186" s="21" t="n"/>
-      <c r="E186" s="31" t="n"/>
-      <c r="F186" s="31" t="n"/>
-      <c r="G186" s="31" t="n"/>
+      <c r="D186" s="144" t="inlineStr">
+        <is>
+          <t>Мера запрещает использование на рабочих (боевых) АРМ пользователей и эксплуатационного персонала, задействованных в выполнении бизнес-процессов, программного обеспечения, предназначенного для разработки, отладки и (или) тестирования ПО (компиляторов, отладчиков, сред разработки, инструментов дизассемблирования).
+Главная цель меры — исключить наличие на рабочих станциях инструментария, который в руках злоумышленника (в том числе получившего контроль над АРМ) может быть использован для разработки, адаптации или отладки вредоносного кода непосредственно в атакуемой инфраструктуре, а также для анализа и обхода установленных средств защиты.</t>
+        </is>
+      </c>
+      <c r="E186" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе прямого запрета на установку и использование на рабочих АРМ пользователей и эксплуатационного персонала ПО для разработки, отладки и тестирования, за исключением АРМ, специально выделенных для этих целей (в сегменте разработки и тестирования, мера СМЭ.6);
+2. Проведение периодической инвентаризации ПО, установленного на рабочих АРМ, на предмет выявления запрещённого инструментария разработки;
+3. При выявлении нарушений — инициирование удаления запрещённого ПО и, при необходимости, служебного разбирательства.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F186" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, содержащий запрет на использование ПО для разработки, отладки и тестирования на рабочих АРМ;
+2. Акты (отчёты) инвентаризации ПО, установленного на рабочих АРМ, на предмет выявления запрещённого инструментария;
+3. Свидетельства устранения выявленных нарушений.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G186" s="151" t="inlineStr">
+        <is>
+          <t>1. Запрет не распространяется на эксплуатационный персонал, обосновывающий необходимость такого ПО служебными задачами, без формального выделения отдельного АРМ;
+2. Инвентаризация ПО на рабочих АРМ на предмет выявления инструментов разработки не проводится или проводится нерегулярно;
+3. Средства разработки (например, встроенные интерпретаторы скриптовых языков в составе офисных пакетов, средства удалённого администрирования с возможностью выполнения кода) не учитываются при определении состава запрещённого ПО;
+4. Выявленные нарушения (наличие запрещённого ПО) не устраняются в разумный срок.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
@@ -26813,8 +27467,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -821,6 +821,12 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -13847,73 +13853,75 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D188" s="21" t="n"/>
-      <c r="E188" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Реализация - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Мера широкая, закрывается несколькими подходами, дополняющими друг друга технически:
-1. Патч/vulnerability-менеджмент — автоматическая инвентаризация версий ПО на серверном/сетевом оборудовании, сопоставление с базами уязвимостей, применение обновлений по расписанию с контролем результата.
-2. Централизованное управление серверами (платформа класса endpoint/server management) — единая консоль развёртывания и контроля обновлений ПО и сигнатурных баз СЗИ на всём парке серверов.
-3. Контроль целостности и соответствия конфигураций — фиксация эталонных версий ПО серверного/сетевого оборудования, автоматическое выявление отклонений (устаревшая версия, несанкционированный откат обновления).
-4. С помощью регистрации и сверки через SIEM, когда события установки/обновления ПО собираются в SIEM и сверяются с плановым графиком обновлений.
-Здесь важно учесть, что встроенных средств (например, WSUS, apt/yum) не всегда может быть достаточно - рекомендуется обеспечить централизованный охват и подтверждение результата по всей инфраструктуре, чего штатные средства дать не могут.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Патч/VM — Иностранные: Ivanti Patch Management · РФ сертифицированные: PT MaxPatrol VM · Открытый код: Ansible-плейбуки инвентаризации/обновления пакетов
-- Централизованное управление серверами — Иностранные: Microsoft SCCM · РФ сертифицированные: Kaspersky Security Center (модуль управления обновлениями)
-- Контроль целостности конфигураций — Иностранные: Tripwire Enterprise · РФ сертифицированные: Efros Config Inspector
-- SIEM (регистрация и сверка) — РФ сертифицированные: PT MaxPatrol SIEM, Kaspersky KUMA · Открытый код: Wazuh</t>
-          </r>
-        </is>
-      </c>
-      <c r="F188" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Проверочные процедуры (свидетельства) - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
+      <c r="D188" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует контролировать, что программное обеспечение (средств защиты информации, прикладное, ПО АС, системное) и сигнатурные базы средств защиты информации на серверном и сетевом оборудовании фактически развёрнуты в соответствии с эталонным составом и своевременно обновляются, в том числе для устранения выявленных в рамках мер ЦЗИ.1—ЦЗИ.10 уязвимостей.
+Главная цель меры — не допустить разрыва между выявлением уязвимости (мерами ЦЗИ.1—ЦЗИ.10) и её фактическим устранением: обнаружение уязвимости само по себе не защищает организацию, если процесс размещения и применения обновлений не отлажен, не контролируется централизованно и не подтверждается фактическим результатом на всём парке серверного и сетевого оборудования.</t>
+        </is>
+      </c>
+      <c r="E188" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Разработку и утверждение регламента управления обновлениями (patch management), определяющего источники обновлений, порядок тестирования (см. также меру ЦЗИ.14), сроки установки в зависимости от критичности и ответственных лиц;
+2. Ведение эталонного перечня версий ПО и сигнатурных баз, подлежащих поддержанию в актуальном состоянии на серверном и сетевом оборудовании;
+3. Периодический контроль фактического соответствия установленных версий эталонному перечню с оформлением результатов актом.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера широкая и закрывается несколькими дополняющими друг друга техническими подходами:
+1. Патч-менеджмент — автоматизированная инвентаризация версий ПО на серверном и сетевом оборудовании, сопоставление с базами уязвимостей, применение обновлений по расписанию с контролем результата;
+2. Централизованное управление серверами (платформа класса endpoint/server management) — единая консоль развёртывания и контроля обновлений ПО и сигнатурных баз СЗИ на всём парке серверов;
+3. Контроль целостности и соответствия конфигураций — фиксация эталонных версий ПО серверного и сетевого оборудования, автоматическое выявление отклонений (устаревшая версия, несанкционированный откат обновления);
+4. Регистрация и сверка через SIEM-систему — события установки и обновления ПО собираются в SIEM и сверяются с плановым графиком обновлений.
+Встроенных средств отдельных операционных систем (например, WSUS, apt/yum) не всегда достаточно — рекомендуется обеспечить централизованный охват и подтверждение результата по всей инфраструктуре, чего разрозненные штатные средства обеспечить не могут.
+Класс используемых средств — системы управления обновлениями и уязвимостями (Patch/Vulnerability Management), платформы централизованного управления серверами, средства контроля целостности конфигураций.
+Иностранные: Ivanti Patch Management, Microsoft SCCM, Tripwire Enterprise и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, Kaspersky Security Center (модуль управления обновлениями), «Efros Config Inspector» и др.
+Открытый код: Ansible (плейбуки инвентаризации и обновления пакетов), Wazuh (регистрация и сверка событий) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F188" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент управления обновлениями (patch management);
+2. Эталонный перечень версий ПО и сигнатурных баз, подлежащих поддержанию в актуальном состоянии;
+3. Акты периодического контроля соответствия установленных версий эталонному перечню.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
             <t xml:space="preserve">
 1. Конфигурация системы патч-менеджмента.
 2. Выгрузка инвентаризации версий ПО и истории обновлений серверного/сетевого оборудования.
@@ -13922,7 +13930,14 @@
           </r>
         </is>
       </c>
-      <c r="G188" s="31" t="n"/>
+      <c r="G188" s="151" t="inlineStr">
+        <is>
+          <t>1. Регламент управления обновлениями не охватывает все категории ПО (например, забыли про сигнатурные базы или сетевое оборудование);
+2. Обновления устанавливаются нерегулярно, без контроля фактического охвата всего парка серверного и сетевого оборудования;
+3. Централизованный контроль версий и сигнатурных баз отсутствует, полагаются только на разрозненные штатные средства отдельных систем;
+4. Фактическое устранение уязвимости после установки обновления не подтверждается повторной проверкой.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="401.25" customHeight="1">
       <c r="A189" s="20" t="inlineStr">
@@ -13940,73 +13955,73 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D189" s="71" t="n"/>
-      <c r="E189" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Реализация - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Мера широкая, закрывается несколькими подходами, дополняющими друг друга технически:
-1. Через патч-менеджмент АРМ с централизованным развёртыванием обновлений на пользовательские рабочие станции по расписанию и с контролем охвата.
-2. С применением централизованного управление конечными точками (EPP/платформа управления АРМ), где используется единая консоль обновления ПО — один из модулей общей платформы защиты рабочих станций.
-3. С использованием контроля целостности/состава ПО АРМ для фиксации эталонного набора версий ПО на образе АРМ и выявления отклонений (устаревшая версия, самовольный откат).
-4. С помощью регистрации и сверки через SIEM, где  события установки/обновления ПО на АРМ (прямо связано с мерой ЦЗИ.29) собираются в SIEM и сверяются с плановым графиком.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Патч/VM — Иностранные: Ivanti Patch Management · РФ сертифицированные: PT MaxPatrol VM · Открытый код: Ansible-плейбуки инвентаризации/обновления пакетов
-- Централизованное управление серверами — Иностранные: Microsoft SCCM · РФ сертифицированные: Kaspersky Security Center (модуль управления обновлениями)
-- Контроль целостности конфигураций — Иностранные: Tripwire Enterprise · РФ сертифицированные: Efros Config Inspector
-- SIEM (регистрация и сверка) — РФ сертифицированные: PT MaxPatrol SIEM, Kaspersky KUMA · Открытый код: Wazuh</t>
-          </r>
-        </is>
-      </c>
-      <c r="F189" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Проверочные процедуры (свидетельства) - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
+      <c r="D189" s="166" t="inlineStr">
+        <is>
+          <t>Мера аналогична ЦЗИ.12, но распространяется на автоматизированные рабочие места (АРМ) пользователей и эксплуатационного персонала: их программное обеспечение (средства защиты информации, прикладное, ПО АС, системное) должно контролироваться на предмет размещения в соответствии с эталонным составом и своевременно обновляться, в том числе для устранения выявленных уязвимостей.
+Главная цель меры — обеспечить актуальность и защищённость ПО именно на рабочих станциях, парк которых, как правило, существенно многочисленнее серверного оборудования, а обновление зависит не только от централизованных процессов, но и от фактического подключения конкретного АРМ к сети в момент распространения обновления.</t>
+        </is>
+      </c>
+      <c r="E189" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Распространение регламента управления обновлениями (мера ЦЗИ.12) на парк АРМ пользователей и эксплуатационного персонала с учётом его специфики (территориальной распределённости, непостоянного подключения к сети);
+2. Установление предельного срока, в течение которого АРМ, не получившее критичное обновление, подлежит принудительному изолированию от сети до устранения отставания;
+3. Периодический контроль фактического охвата парка АРМ актуальными обновлениями с оформлением результатов актом.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера широкая и закрывается несколькими дополняющими друг друга техническими подходами:
+1. Патч-менеджмент АРМ — централизованное развёртывание обновлений на пользовательские рабочие станции по расписанию, с контролем фактического охвата парка;
+2. Централизованное управление конечными точками (EPP-платформа или платформа управления АРМ) — единая консоль обновления ПО как один из модулей общей платформы защиты рабочих станций;
+3. Контроль целостности и состава ПО АРМ — фиксация эталонного набора версий ПО на образе АРМ и выявление отклонений (устаревшая версия, самовольный откат);
+4. Регистрация и сверка через SIEM-систему — события установки и обновления ПО на АРМ (см. также меру ЦЗИ.29) собираются в SIEM и сверяются с плановым графиком.
+Класс используемых средств — системы управления обновлениями и уязвимостями (Patch/Vulnerability Management), платформы централизованного управления конечными точками (EPP).
+Иностранные: Ivanti Patch Management, Microsoft SCCM и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, Kaspersky Security Center (модуль управления обновлениями) и др.
+Открытый код: Ansible (плейбуки инвентаризации и обновления пакетов) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F189" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент управления обновлениями, распространённый на парк АРМ, с учётом его специфики;
+2. Свидетельства принудительной изоляции от сети АРМ, не получивших критичные обновления в установленный срок (при наличии таких случаев).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
             <t xml:space="preserve">
 1. Конфигурация централизованной системы управления обновлениями.
 2. Отчёт о статусе последних обновлений по парку АРМ за проверяемый период.
@@ -14015,7 +14030,14 @@
           </r>
         </is>
       </c>
-      <c r="G189" s="32" t="n"/>
+      <c r="G189" s="152" t="inlineStr">
+        <is>
+          <t>1. Значительная часть парка АРМ не подключается к сети регулярно, из-за чего обновления на них не устанавливаются длительное время;
+2. Централизованный контроль фактического охвата парка АРМ актуальными обновлениями не ведётся;
+3. Критичные обновления АРМ устанавливаются с той же приоритетностью, что и некритичные;
+4. Отклонения от эталонного состава ПО на образе АРМ (самовольный откат обновлений пользователем) не выявляются.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="157.5" customHeight="1">
       <c r="A190" s="20" t="inlineStr">
@@ -14033,36 +14055,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D190" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы обновления (по ЦЗИ.12 и ЦЗИ.13) в продуктивной среде проверялись в отдельном тестовом сегменте, чтобы АС могла по-прежнему работать корректно после установки обновления. Это спасёт от случаев, когда обновление ломает функциональность или защитные механизмы АС, ведь зачастую из-за отсутствия предварительной проверки такое "слепое" применение патчей приводит к простою критичных систем.</t>
-        </is>
-      </c>
-      <c r="E190" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D190" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы обновления, устанавливаемые в рамках мер ЦЗИ.12 и ЦЗИ.13, предварительно проверялись в отдельном сегменте разработки и тестирования (мера СМЭ.6) на предмет работоспособности и корректности функционирования автоматизированной системы (АС), прежде чем применяться в продуктивной среде.
+Главная цель меры — не допустить ситуации, когда установка обновления нарушает функциональность или защитные механизмы АС: без предварительной проверки в тестовом сегменте «слепое» применение обновлений в продуктивной среде способно привести к простою критичных систем, что зачастую наносит больший ущерб, чем сама уязвимость, которую обновление устраняет.</t>
+        </is>
+      </c>
+      <c r="E190" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - О</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Регламентируется обязательный этап тестирования обновлений в сегменте разработки/тестирования перед продакшеном: тест-кейсы на ключевые функции АС, фиксация результатов, формальное согласование выкатки обновления, и это регламентируется в Политике/Положении обеспечения информационной безопасности на стадиях жизненного цикла автоматизированных банковских систем. 
-Зачастую реализуется базовыми средствами (staging-окружение, ручное тестирование по чек-листу) без выделенного СЗИ, но для большей зрелости процесса рекомендуется формализованный CI/CD-пайплайн с автотестами.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F190" s="31" t="n"/>
-      <c r="G190" s="31" t="n"/>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Регламентацию обязательного этапа тестирования обновлений в сегменте разработки и тестирования перед их применением в продуктивной среде — во внутреннем нормативном документе (положении об обеспечении защиты информации на стадиях жизненного цикла автоматизированных систем);
+2. Формирование набора тест-кейсов, покрывающих ключевые функции АС, для проверки её работоспособности после установки обновления;
+3. Документальную фиксацию результатов тестирования и формальное согласование выкатки обновления в продуктивную среду ответственным лицом.
+На практике мера, как правило, реализуется базовыми средствами (staging-окружением, ручным тестированием по чек-листу) без выделенного средства защиты информации; для повышения зрелости процесса рекомендуется формализованный CI/CD-пайплайн с автоматизированными тестами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F190" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий обязательность тестирования обновлений перед применением в продуктивной среде;
+2. Набор тест-кейсов для проверки работоспособности АС после установки обновления;
+3. Протоколы (акты) тестирования обновлений с результатами и согласованием выкатки в продуктивную среду.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G190" s="151" t="inlineStr">
+        <is>
+          <t>1. Тестирование обновлений в сегменте разработки и тестирования проводится не для всех обновлений, а выборочно;
+2. Тест-кейсы не охватывают ключевые функции АС, ограничиваются поверхностной проверкой запуска;
+3. Согласование выкатки обновления в продуктивную среду носит формальный характер, без анализа результатов тестирования;
+4. Результаты тестирования не фиксируются документально, что не позволяет подтвердить факт его проведения.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="57" customHeight="1">
       <c r="A191" s="20" t="inlineStr">
@@ -14080,10 +14122,86 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D191" s="21" t="n"/>
-      <c r="E191" s="31" t="n"/>
-      <c r="F191" s="31" t="n"/>
-      <c r="G191" s="31" t="n"/>
+      <c r="D191" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы после установки обновлений ПО на серверном и сетевом оборудовании (мера ЦЗИ.12) проводилась повторная проверка на отсутствие известных уязвимостей — как для подтверждения того, что устраняемая обновлением уязвимость действительно закрыта, так и для выявления новых уязвимостей, которые могло привнести само обновление.
+Главная цель меры — не полагаться на предположение, что установка обновления автоматически означает устранение уязвимости: некорректно применённое обновление, конфликт версий или ошибка в самом обновлении способны оставить уязвимость открытой или создать новую, и только повторная проверка подтверждает фактический результат.</t>
+        </is>
+      </c>
+      <c r="E191" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Установление обязательного этапа повторной проверки (регрессионного сканирования) в регламенте управления обновлениями (мера ЦЗИ.12) как неотъемлемой части процесса устранения уязвимости, а не отдельной по желанию процедуры;
+2. Определение критериев, при которых устранение уязвимости считается подтверждённым (отсутствие уязвимости по результатам не менее одного повторного сканирования).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль дополняется:
+1. Проведением повторного (регрессионного) сканирования на уязвимости серверного и сетевого оборудования непосредственно после установки обновлений;
+2. Сопоставлением результатов повторного сканирования с перечнем уязвимостей, выявленных до обновления, для подтверждения их устранения;
+3. Дополнительным сканированием на предмет новых уязвимостей, которые могло привнести само обновление (например, из-за изменения конфигурации по умолчанию).
+Класс используемых средств — средства анализа защищённости (сканеры уязвимостей).
+Иностранные: Tenable Nessus, Qualys VMDR и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, «Сканер-ВС» и др.
+Открытый код: OpenVAS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F191" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент управления обновлениями с указанием обязательного этапа повторной проверки после обновления;
+2. Критерии подтверждения фактического устранения уязвимости.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Отчёты повторного (регрессионного) сканирования после установки обновлений за проверяемый период;
+2. Сопоставление перечня уязвимостей до и после обновления, подтверждающее их устранение;
+3. Итоги интервью с администраторами серверного и сетевого оборудования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G191" s="151" t="inlineStr">
+        <is>
+          <t>1. Повторное сканирование после установки обновлений проводится не всегда, а выборочно;
+2. Устранение уязвимости считается подтверждённым по факту установки обновления, без фактической повторной проверки;
+3. Новые уязвимости, привнесённые самим обновлением, не выявляются, так как сканирование ориентировано только на ранее известный перечень;
+4. Результаты повторного сканирования не сопоставляются с исходным перечнем уязвимостей.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="42.75" customHeight="1">
       <c r="A192" s="20" t="inlineStr">
@@ -14101,10 +14219,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D192" s="21" t="n"/>
-      <c r="E192" s="31" t="n"/>
-      <c r="F192" s="31" t="n"/>
-      <c r="G192" s="31" t="n"/>
+      <c r="D192" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует создания и хранения эталонных (заведомо корректных, актуальных) копий программного обеспечения автоматизированных систем (АС), средств и систем защиты информации и системного ПО, а также обеспечения технической возможности восстановления из этих копий в случае нештатной ситуации — сбоя, отказа оборудования, повреждения данных, компрометации системы.
+Главная цель меры — минимизировать время простоя и объём потерь при нештатной ситуации: наличие заведомо корректной эталонной копии позволяет оперативно восстановить работоспособность системы, не полагаясь на реконструкцию ПО «с нуля» или на потенциально скомпрометированные текущие версии.</t>
+        </is>
+      </c>
+      <c r="E192" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Определение перечня ПО (АС, СЗИ, системного), для которого создание и хранение эталонных копий является обязательным, исходя из критичности систем;
+2. Установление порядка и периодичности создания эталонных копий, а также требований к месту и условиям их хранения (изолированно от систем-источников, с защитой от несанкционированного доступа);
+3. Регламентацию порядка тестового восстановления из эталонных копий на периодической основе для подтверждения их фактической пригодности;
+4. Определение ответственных за создание, хранение и восстановление эталонных копий.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F192" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) создания, хранения и восстановления эталонных копий ПО;
+2. Перечень ПО, для которого созданы эталонные копии, с указанием актуальности (даты последнего обновления копии);
+3. Акты (протоколы) тестового восстановления из эталонных копий.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G192" s="151" t="inlineStr">
+        <is>
+          <t>1. Эталонные копии созданы не для всего критичного ПО, определённого в перечне;
+2. Эталонные копии хранятся вместе с системами-источниками, без изоляции, что не защищает их от того же инцидента, что и оригинал;
+3. Тестовое восстановление из эталонных копий не проводится, фактическая пригодность копий не подтверждается;
+4. Эталонные копии не обновляются при выходе новых версий ПО, восстановление привело бы к устаревшей и уязвимой версии.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="47.25" customHeight="1">
       <c r="A193" s="20" t="inlineStr">
@@ -14123,10 +14287,61 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D193" s="21" t="n"/>
-      <c r="E193" s="31" t="n"/>
-      <c r="F193" s="31" t="n"/>
-      <c r="G193" s="31" t="n"/>
+      <c r="D193" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует ведения учёта эталонных копий ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО, созданных в рамках меры ЦЗИ.16, а также контроля их целостности — то есть подтверждения того, что хранимая копия не была изменена (случайно повреждена или преднамеренно скомпрометирована) с момента её создания.
+Главная цель меры — исключить ситуацию, когда организация полагается на эталонную копию для восстановления после нештатной ситуации, а фактически копия непригодна: изменена, повреждена или подменена, и это обнаруживается только в момент восстановления, когда времени на альтернативные действия уже нет.</t>
+        </is>
+      </c>
+      <c r="E193" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Контроль целостности эталонных копий обеспечивается:
+1. Вычислением контрольных сумм (хеш-значений) эталонных копий ПО в момент их создания и фиксацией эталонных значений отдельно от самих копий;
+2. Периодическим автоматическим пересчётом контрольных сумм хранимых копий и их сопоставлением с зафиксированными эталонными значениями;
+3. Автоматическим оповещением ответственных лиц при выявлении несоответствия — как признака повреждения или несанкционированного изменения копии;
+4. Ведением учёта (реестра) эталонных копий с указанием версии, даты создания и результатов последней проверки целостности.
+Класс используемых средств — средства контроля целостности файлов (file integrity monitoring), в том числе входящие в состав системы резервного копирования или системы контроля конфигураций.
+Иностранные: Tripwire Enterprise, Veeam Backup &amp; Replication (встроенная проверка целостности резервных копий) и пр.
+Российские сертифицированные (ФСТЭК): Efros Config Inspector, «Кибер Бэкап» (встроенная проверка целостности) и др.
+Открытый код: AIDE, OSSEC (модуль контроля целостности файлов) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F193" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Реестр (учёт) эталонных копий ПО с указанием версий и дат создания.
+2. Конфигурация средства контроля целостности эталонных копий.
+3. Журнал (отчёт) результатов периодической проверки целостности эталонных копий за проверяемый период.
+4. Итоги интервью с ответственным за хранение эталонных копий.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G193" s="151" t="inlineStr">
+        <is>
+          <t>1. Контрольные суммы эталонных копий фиксируются в момент создания, но их периодический пересчёт и сверка в дальнейшем не проводятся;
+2. Эталонные значения контрольных сумм хранятся вместе с самими копиями, без изоляции, что не защищает от согласованной подмены и копии, и эталона;
+3. Учёт (реестр) эталонных копий ведётся не по всему перечню ПО, для которого копии должны создаваться согласно мере ЦЗИ.16;
+4. Оповещение об обнаруженном несоответствии контрольной суммы не настроено, нарушение целостности выявляется только при попытке восстановления.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="252" customHeight="1">
       <c r="A194" s="20" t="inlineStr">
@@ -14144,84 +14359,70 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D194" s="21" t="n"/>
-      <c r="E194" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Применяется система класса Configuration Management, автоматически хранящая эталонные конфигурации, выявляющая отклонения (drift detection) и позволяющая откатить настройки к эталону. При технической реализации недостаточно просто хранить конфигурации "как код" через Ansible-плейбуки/GPO-экспорт без выделенного СЗИ - здесь нужен именн</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>о автоматический контро</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">ль дрейфа.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>- Иностранные: Tripwire Enterprise, Ansible + AWX (drift detection) и пр.
-- Российские сертифицированные: Efros Config Inspector (Газинформсервис) — класс контроля конфигураций и целостности настроек и прочие
-- Открытый код: Ansible + git (конфигурация как код с историей изменений) и пр.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F194" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Проверочные процедуры (свидетельства) - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
+      <c r="D194" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует ведения учёта эталонных значений параметров настроек (конфигураций) ПО автоматизированных систем (АС), системного ПО, средств и систем защиты информации, контроля их целостности (соответствия фактических настроек эталонным) и обеспечения технической возможности восстановления эталонных настроек в случае нештатной ситуации.
+Главная цель меры — обеспечить, что защитные и функциональные свойства системы определяются не только установленной версией ПО (меры ЦЗИ.16/ЦЗИ.17), но и его настройками: несанкционированное или ошибочное изменение конфигурации способно снизить защищённость системы так же существенно, как отсутствие обновления, а без эталона и контроля отклонений такое изменение останется незамеченным.</t>
+        </is>
+      </c>
+      <c r="E194" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Определение перечня ПО (АС, системного, СЗИ), для которого фиксация эталонных значений параметров настройки является обязательной, исходя из критичности систем;
+2. Регламентацию порядка фиксации, пересмотра и хранения эталонных значений настроек, включая ответственных лиц и порядок согласования изменений эталона;
+3. Регламентацию порядка восстановления эталонных настроек в случае нештатной ситуации (сбоя, несанкционированного изменения) с указанием допустимых сроков восстановления.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технический контроль реализуется применением системы класса Configuration Management, которая автоматически хранит эталонные конфигурации, выявляет отклонения (drift detection) от них и позволяет откатить настройки к эталону. Хранения конфигураций «как код» (например, набором Ansible-плейбуков или экспортом групповых политик) без выделенного средства защиты для этого недостаточно — необходим именно автоматический контроль дрейфа настроек и оповещение об отклонениях.
+Класс используемых средств — системы управления конфигурациями (Configuration Management) с функцией контроля дрейфа настроек (drift detection).
+Иностранные: Tripwire Enterprise, Ansible + AWX (drift detection) и пр.
+Российские сертифицированные (ФСТЭК): Efros Config Inspector и др.
+Открытый код: Ansible совместно с git (конфигурация как код с историей изменений) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F194" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень ПО, для которого зафиксированы эталонные значения параметров настройки;
+2. Регламент фиксации, пересмотра и восстановления эталонных настроек;
+3. Акты (протоколы) восстановления эталонных настроек при нештатных ситуациях (при наличии таких случаев).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
             <t xml:space="preserve">
 1. Конфигурация системы контроля конфигураций.
 2. Отчёт о выявленных отклонениях от эталона за проверяемый период.
@@ -14229,7 +14430,14 @@
           </r>
         </is>
       </c>
-      <c r="G194" s="31" t="n"/>
+      <c r="G194" s="151" t="inlineStr">
+        <is>
+          <t>1. Эталонные значения настроек зафиксированы не для всего ПО, определённого в перечне, в частности упускается системное ПО и сетевое оборудование;
+2. Автоматический контроль дрейфа настроек не применяется, конфигурации хранятся «как код», но фактическое отклонение выявляется только вручную и нерегулярно;
+3. Возможность восстановления эталонных настроек не проверялась тестово, фактическая работоспособность процедуры отката не подтверждена;
+4. Изменения эталонных значений настроек вносятся без согласования и документальной фиксации причины изменения.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="47.25" customHeight="1">
       <c r="A195" s="39" t="inlineStr">
@@ -14247,10 +14455,89 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D195" s="40" t="n"/>
-      <c r="E195" s="73" t="n"/>
-      <c r="F195" s="73" t="n"/>
-      <c r="G195" s="73" t="n"/>
+      <c r="D195" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует контроля целостности и достоверности источников получения ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО при его распространении и (или) обновлении — то есть подтверждения того, что дистрибутив или обновление получены именно от легитимного производителя (разработчика) и не были подменены или модифицированы на этапе доставки.
+Главная цель меры — противодействовать угрозам цепочки поставок (supply chain): без контроля достоверности источника и целостности получаемого ПО организация рискует установить компонент, скомпрометированный ещё до попадания в её инфраструктуру, — такая подмена не выявляется мерами ЦЗИ.12—ЦЗИ.18, ориентированными на уже установленное ПО.</t>
+        </is>
+      </c>
+      <c r="E195" s="167" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Регламентацию перечня доверенных источников получения ПО (официальные сайты и репозитории производителей, авторизованные дистрибьюторы) для каждой категории используемого ПО;
+2. Запрет на получение ПО из непроверенных источников (сторонние файлообменники, неофициальные зеркала) во внутреннем нормативном документе;
+3. Регламентацию обязательной проверки целостности и подлинности получаемого ПО перед его применением, включая порядок действий при выявлении несоответствия.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технически контроль реализуется:
+1. Проверкой цифровой подписи дистрибутивов и обновлений производителя перед их применением;
+2. Сверкой контрольных сумм (хеш-значений) полученного ПО со значениями, опубликованными производителем по доверенному каналу;
+3. Использованием доверенных (официальных) репозиториев и зеркал с контролем целостности на уровне менеджера пакетов;
+4. Регистрацией и сверкой через SIEM-систему фактов получения и применения обновлений из внешних источников.
+Класс используемых средств — встроенные механизмы проверки цифровой подписи и контрольных сумм пакетов (менеджеры пакетов, средства патч-менеджмента), дополняемые средствами централизованного контроля доверенных источников.
+Иностранные: встроенная проверка подписи пакетов Microsoft SCCM/WSUS, Ivanti Patch Management и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM (контроль источников обновлений в рамках патч-менеджмента) и др.
+Открытый код: встроенная проверка GPG-подписи пакетов в apt/yum/dnf, sigstore/cosign (проверка подписи контейнерных образов) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F195" s="167" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень доверенных источников получения ПО по категориям;
+2. Внутренний нормативный документ, запрещающий получение ПО из непроверенных источников;
+3. Регламент проверки целостности и подлинности получаемого ПО.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства проверки цифровой подписи и контрольных сумм получаемого ПО.
+2. Журнал (отчёт) о результатах проверки подлинности и целостности обновлений за проверяемый период, включая выявленные несоответствия (при наличии).
+3. Итоги интервью с ответственным за получение и распространение обновлений ПО.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G195" s="167" t="inlineStr">
+        <is>
+          <t>1. Проверка цифровой подписи и контрольных сумм получаемого ПО настроена не для всех категорий ПО, а выборочно (например, только для ОС, но не для прикладного ПО и СЗИ);
+2. Перечень доверенных источников не формализован, фактический источник получения ПО определяется на усмотрение конкретного администратора;
+3. При выявлении несоответствия контрольной суммы или подписи полученное ПО всё равно применяется без разбирательства причины;
+4. Обновления сторонних (не входящих в состав ОС) компонентов получаются из непроверенных репозиториев, не входящих в утверждённый перечень.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="74" t="inlineStr">
@@ -27467,8 +27754,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -14568,10 +14568,87 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D197" s="21" t="n"/>
-      <c r="E197" s="53" t="n"/>
-      <c r="F197" s="53" t="n"/>
-      <c r="G197" s="53" t="n"/>
+      <c r="D197" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует ведения перечня разрешённого к использованию программного обеспечения (ПО) на АРМ пользователей и эксплуатационного персонала и периодического контроля фактического состава установленного ПО на предмет соответствия этому перечню. В отличие от меры ЦЗИ.23 (контроль состава ПО, запускаемого именно на этапе загрузки ОС), здесь контролируется полный состав ПО АРМ на протяжении всей работы системы, а не только момент старта.
+Главная цель меры — обеспечить видимость фактического состава ПО на рабочих станциях: без регулярного сопоставления с эталонным перечнем неразрешённое ПО (самовольно установленное пользователем, оставшееся после ранее санкционированной задачи, или внедрённое злоумышленником) может присутствовать на АРМ длительное время незамеченным.</t>
+        </is>
+      </c>
+      <c r="E197" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Формирование и утверждение перечня разрешённого к использованию на АРМ ПО, дифференцированного по категориям пользователей и решаемым задачам;
+2. Регламентацию порядка пересмотра перечня при возникновении обоснованной потребности в новом ПО;
+3. Установление периодичности контроля фактического состава ПО АРМ и порядка действий при выявлении несоответствия эталонному перечню.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технический контроль реализуется:
+1. Автоматизированной инвентаризацией фактически установленного и запущенного ПО на АРМ;
+2. Автоматическим сопоставлением результатов инвентаризации с перечнем разрешённого ПО и формированием отчёта об отклонениях;
+3. Оповещением ответственных лиц при выявлении неразрешённого ПО.
+Класс используемых средств — системы инвентаризации программного обеспечения (Software Asset Management), также реализуемые как модуль EDR/EPP-платформы или платформы централизованного управления АРМ.
+Иностранные: Microsoft SCCM (инвентаризация ПО), Flexera (Software Asset Management) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center (инвентаризация ПО), Secret Net Studio (модуль контроля состава ПО) и др.
+Открытый код: Wazuh (модуль инвентаризации ПО, syscollector) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F197" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень разрешённого к использованию ПО АРМ по категориям пользователей;
+2. Регламент пересмотра перечня и контроля фактического состава ПО АРМ.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства инвентаризации ПО.
+2. Отчёт сопоставления фактического состава ПО с эталонным перечнем за проверяемый период.
+3. Итоги интервью с ответственным за администрирование АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G197" s="157" t="inlineStr">
+        <is>
+          <t>1. Перечень разрешённого ПО не актуализирован, не отражает реально используемое в работе ПО, из-за чего фиксируется массовое «несоответствие»;
+2. Инвентаризация фактического состава ПО проводится не по всему парку АРМ, а выборочно;
+3. Выявленные отклонения от эталонного перечня не анализируются и не приводят к каким-либо действиям;
+4. Контроль охватывает только ПО, установленное штатным образом, но не переносимые (portable) версии приложений, не требующие установки.</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="47.25" customHeight="1">
       <c r="A198" s="20" t="inlineStr">
@@ -14589,10 +14666,84 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D198" s="21" t="n"/>
-      <c r="E198" s="53" t="n"/>
-      <c r="F198" s="53" t="n"/>
-      <c r="G198" s="53" t="n"/>
+      <c r="D198" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует не только выявления неразрешённого ПО на АРМ (мера ЦЗИ.20), но и технического исключения самой возможности его установки и (или) запуска — то есть перехода от детективного контроля к превентивному блокированию.
+Главная цель меры — не допустить исполнения неразрешённого (в том числе вредоносного) кода на АРМ в принципе: при исключительно детективном контроле (мера ЦЗИ.20) неразрешённое ПО успевает выполниться до момента обнаружения, тогда как превентивная блокировка устраняет саму возможность запуска.</t>
+        </is>
+      </c>
+      <c r="E198" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Определение режима контроля (whitelisting — разрешено только явно перечисленное ПО, либо blacklisting — запрещено только явно перечисленное) исходя из категории АРМ и критичности решаемых на них задач;
+2. Регламентацию порядка оперативного согласования запуска нового ПО, требующегося пользователю для решения рабочей задачи, без длительного простоя;
+3. Определение перечня АРМ, для которых применение технологии контроля запуска ПО невозможно по производственным причинам, с компенсирующими мерами.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением технологии контроля запуска приложений (application control / whitelisting), блокирующей установку и (или) запуск ПО, не входящего в перечень разрешённого. Контроль может осуществляться по признакам пути размещения файла, издателя (цифровой подписи) или хеш-суммы конкретной версии — предпочтительным является контроль по цифровой подписи или хешу как более устойчивый к обходу простым переименованием или перемещением файла.
+Класс используемых средств — средства контроля запуска приложений (application control), как правило, входящие в состав EDR/EPP-платформы или отдельного решения класса Host Intrusion Prevention System (HIPS).
+Иностранные: Carbon Black App Control, Microsoft AppLocker (встроенный компонент Windows) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль контроля запуска приложений), Secret Net Studio (замкнутая программная среда) и др.
+Открытый код: встроенный модуль AppArmor/SELinux (Linux) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F198" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент, определяющий режим контроля запуска ПО (whitelisting/blacklisting) и порядок согласования запуска нового ПО;
+2. Перечень АРМ, исключённых из технического контроля запуска ПО, с указанием компенсирующих мер (при наличии).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства контроля запуска приложений на образце АРМ.
+2. Журнал событий блокировки запуска неразрешённого ПО за проверяемый период.
+3. Итоги интервью с ответственным за администрирование АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G198" s="157" t="inlineStr">
+        <is>
+          <t>1. Технология контроля запуска приложений применяется не на всех АРМ, а выборочно, без формального обоснования исключений;
+2. Контроль настроен по пути размещения файла, что позволяет обойти блокировку простым копированием разрешённого файла поверх запрещённого;
+3. Режим работы фактически переведён в «только уведомление» без реальной блокировки, чтобы избежать обращений пользователей;
+4. Правила контроля не пересматриваются при изменении перечня разрешённого ПО (мера ЦЗИ.20), из-за чего накапливается рассинхронизация.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="15.75" customFormat="1" customHeight="1" s="76">
       <c r="A199" s="20" t="inlineStr">
@@ -14610,10 +14761,84 @@
           <t>Н-О-Т</t>
         </is>
       </c>
-      <c r="D199" s="21" t="n"/>
-      <c r="E199" s="21" t="n"/>
-      <c r="F199" s="21" t="n"/>
-      <c r="G199" s="21" t="n"/>
+      <c r="D199" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична ЦЗИ.20, но распространяется на серверное оборудование: требует ведения перечня разрешённого к использованию ПО серверов и периодического контроля фактического состава установленного ПО на соответствие этому перечню.
+Главная цель меры — ограничить состав ПО серверов исключительно тем, что необходимо для выполнения ими своих функций: избыточное ПО (неиспользуемые службы, средства удалённого администрирования сомнительного происхождения, оставленный инструментарий разработки) на сервере расширяет поверхность атаки в существенно более критичном сегменте инфраструктуры, чем рабочая станция.</t>
+        </is>
+      </c>
+      <c r="E199" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Формирование и утверждение перечня разрешённого к использованию ПО для каждого класса (роли) серверов исходя из выполняемых функций;
+2. Регламентацию порядка согласования установки дополнительного ПО на сервер и порядка периодического пересмотра эталонного перечня;
+3. Установление периодичности контроля фактического состава ПО серверов и порядка действий при выявлении несоответствия.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технический контроль реализуется автоматизированной инвентаризацией фактически установленного ПО на серверах и его сопоставлением с эталонным перечнем для соответствующего класса (роли) сервера, с оповещением ответственных лиц при выявлении отклонений.
+Класс используемых средств — системы инвентаризации программного обеспечения (Software Asset Management), также реализуемые как модуль централизованной платформы управления серверами или средства контроля конфигураций.
+Иностранные: Microsoft SCCM, Tanium (инвентаризация активов) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, Efros Config Inspector и др.
+Открытый код: Ansible (инвентаризационные плейбуки), Wazuh (syscollector) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F199" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень разрешённого к использованию ПО по классам (ролям) серверов;
+2. Регламент согласования установки дополнительного ПО и контроля фактического состава ПО серверов.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства инвентаризации ПО серверного оборудования.
+2. Отчёт сопоставления фактического состава ПО серверов с эталонным перечнем за проверяемый период.
+3. Итоги интервью с ответственным за администрирование серверной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G199" s="144" t="inlineStr">
+        <is>
+          <t>1. Эталонный перечень разрешённого ПО единый для всех серверов без дифференциации по классам (ролям), что делает контроль формальным;
+2. Инвентаризация фактического состава ПО серверов проводится нерегулярно или не охватывает весь парк;
+3. Установка дополнительного ПО на сервер в рамках оперативных задач (например, при расследовании инцидента) не документируется и не удаляется впоследствии;
+4. Выявленные отклонения от эталонного перечня не приводят к удалению избыточного ПО в разумный срок.</t>
+        </is>
+      </c>
       <c r="H199" s="7" t="n"/>
     </row>
     <row r="200" ht="346.5" customHeight="1">
@@ -14632,51 +14857,27 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D200" s="78" t="inlineStr">
-        <is>
-          <t>Мера направлена на контроль состава программного обеспечения (ПО), инициализируемого на этапе загрузки операционной системы (ОС): автозапускаемые драйверы, службы, компоненты инициализации — то есть до завершения полной загрузки ОС и начала пользовательской сессии. Это отдельный объект контроля по отношению к мерам ЦЗИ.20/21 (здесь не контроль состава ПО АРМ в целом в любой момент работы системы, а именно перед запуском ОС). Без контроля состава на этапе загрузки вредоносный или неразрешённый компонент, встроенный в автозагрузку, может получить управление раньше, чем инициализируются пользовательские механизмы защиты, и скрыть своё присутствие от последующего контроля, закрепиться в системе с высокими привилегиями, обойти контроль состава ПО, реализуемый мерами ЦЗИ.20/21/32.</t>
-        </is>
-      </c>
-      <c r="E200" s="80" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D200" s="144" t="inlineStr">
+        <is>
+          <t>Мера направлена на контроль состава программного обеспечения (ПО), инициализируемого на этапе загрузки операционной системы (ОС): автозапускаемые драйверы, службы, компоненты инициализации — то есть до завершения полной загрузки ОС и начала пользовательской сессии. Это отдельный объект контроля по отношению к мерам ЦЗИ.20/21 (здесь не контроль состава ПО АРМ в целом в любой момент работы системы, а именно перед запуском ОС). Без контроля состава на этапе загрузки вредоносный или неразрешённый компонент, встроенный в автозагрузку, может получить управление раньше, чем инициализируются пользовательские механизмы защиты, и скрыть своё присутствие от последующего контроля, закрепиться в системе с высокими привилегиями, обойти контроль состава ПО, реализуемый мерами ЦЗИ.20/21/32.
+Главная цель меры — не допустить получения управления системой вредоносным или неразрешённым компонентом до момента, когда становятся доступны штатные средства защиты уровня ОС: контроль состава ПО на этапе загрузки закрывает разрыв, который не покрывают меры ЦЗИ.20/21/32, ориентированные на состав ПО уже работающей ОС.</t>
+        </is>
+      </c>
+      <c r="E200" s="164" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
             <t xml:space="preserve">
 Мера требует реализацию контроля состава ПО, запускаемого при загрузке ОС, что достигается средствами доверенной загрузки (СДЗ) — как правило, отдельным аппаратно-программным модулем доверенной загрузки (АПМДЗ). Такие средства инициализируются до полной загрузки ОС и формируют независимую от неё проверку состава компонентов, участвующих в загрузке.
 При выборе инструмента реализации необходимо запрашивать у производителя техническую документацию (руководство администратора), явно подтверждающую работу заявленного механизма на этапе, предшествующем полной загрузке ОС, и уточнять, требуется ли для этого отдельный сертифицированный модуль, не входящий в базовую поставку продукта (см. выявленные коллизии).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Российские сертифицированные: ПАК «Соболь» (Код Безопасности), «Аккорд-АМДЗ» (ОКБ САПР) и др.</t>
+Класс используемых средств — аппаратно-программные модули доверенной загрузки (АПМДЗ) / средства доверенной загрузки (СДЗ).
+Российские сертифицированные (ФСТЭК/ФСБ): ПАК «Соболь» (Код Безопасности), «Аккорд-АМДЗ» (ОКБ САПР) и др. Зарубежные и открытые аналоги данного класса в РФ не применяются в силу требований ФСТЭК/ФСБ к доверенной загрузке.</t>
           </r>
         </is>
       </c>
@@ -14752,56 +14953,57 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D201" s="34" t="inlineStr">
-        <is>
-          <t>При каждом запуске компонента прикладного ПО АС на рабочей станции нужно проверять, что этот файл не был изменён с момента последней проверенной версии. Так можно избежать подмены легитимного компонента АС вредоносным аналогом (троянизация, DLL hijacking) и случая, когда запуск скомпрометированного клиентского модуля АС остаётся незамеченным, если целостность не проверяется на старте.</t>
-        </is>
-      </c>
-      <c r="E201" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">На АРМ устанавливается средство контроля целостности (класс FIM/Application Control в составе EDR/HIPS), которое при запуске компонента ПО АС сверяет его контрольную сумму или цифровую подпись с эталоном, а при несовпадении — блокирует запуск и генерирует событие защиты информации.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Carbon Black App Control, Tripwire for Servers
-- Российские сертифицированные: Kaspersky Endpoint Security для бизнеса (модуль контроля целостности/Application Control), Dallas Lock 8.0 — СЗИ от НСД с функцией контроля целостности и прочие
-- Открытый код: Wazuh (модуль FIM — File Integrity Monitoring)</t>
-          </r>
-        </is>
-      </c>
-      <c r="F201" s="31" t="n"/>
-      <c r="G201" s="31" t="n"/>
+      <c r="D201" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы при каждом запуске компонента прикладного ПО автоматизированной системы (АС) на АРМ пользователя или эксплуатационного персонала проверялось, что запускаемый файл не был изменён с момента последней проверенной (эталонной) версии.
+Главная цель меры — исключить возможность подмены легитимного компонента АС вредоносным аналогом (троянизация, DLL hijacking) непосредственно на рабочей станции: без контроля целостности на старте запуск скомпрометированного клиентского модуля АС остаётся незамеченным, а подменённый компонент получает доступ ко всем данным и полномочиям, которыми обладает легитимное ПО АС.</t>
+        </is>
+      </c>
+      <c r="E201" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+На АРМ устанавливается средство контроля целостности (класс File Integrity Monitoring / Application Control в составе EDR/HIPS), которое при запуске компонента ПО АС сверяет его контрольную сумму или цифровую подпись с эталонным значением, а при несовпадении — блокирует запуск и генерирует событие защиты информации (см. также меру ЦЗИ.34 в части регистрации результатов).
+Класс используемых средств — средства контроля целостности запускаемых файлов (File Integrity Monitoring), в том числе в составе EDR/HIPS-платформы.
+Иностранные: Carbon Black App Control, Tripwire for Servers и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль контроля целостности/Application Control), Dallas Lock 8.0 (СЗИ от НСД с функцией контроля целостности) и др.
+Открытый код: Wazuh (модуль FIM — File Integrity Monitoring) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F201" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства контроля целостности запускаемых файлов ПО АС на образце АРМ.
+2. Эталонный перечень контрольных сумм (цифровых подписей) компонентов ПО АС.
+3. Журнал событий блокировки запуска компонентов ПО АС с нарушенной целостностью за проверяемый период.
+4. Итоги интервью с ответственным за администрирование АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G201" s="151" t="inlineStr">
+        <is>
+          <t>1. Контроль целостности настроен не для всех компонентов ПО АС, а только для основного исполняемого файла, без учёта подключаемых библиотек (DLL);
+2. Эталонные значения контрольных сумм не обновляются согласованно с выпуском новых версий ПО АС, что приводит к массовым ложным блокировкам и последующему отключению контроля;
+3. При выявлении нарушения целостности запуск блокируется, но событие не передаётся в SIEM-систему для централизованного анализа;
+4. Контроль целостности реализован только детективно (уведомление), без фактической блокировки запуска изменённого компонента.</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="220.5" customHeight="1">
       <c r="A202" s="20" t="inlineStr">
@@ -14819,82 +15021,52 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D202" s="34" t="inlineStr">
-        <is>
-          <t>Загрузка ОС на АРМ должна проверяться на подлинность и неизменность ещё до старта самой операционной системы, чтобы избежать загрузку АРМ с постороннего носителя (USB/LiveCD), когда буткит/руткит модифицирует загрузчик до старта ОС и остаётся невидимым для средств защиты уровня ОС.</t>
-        </is>
-      </c>
-      <c r="E202" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D202" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы загрузка операционной системы (ОС) на АРМ пользователей и эксплуатационного персонала проверялась на подлинность и неизменность ещё до старта самой ОС.
+Главная цель меры — исключить загрузку АРМ с постороннего носителя (USB, LiveCD) или с модифицированным загрузчиком: буткит или руткит, внедрённый на этом этапе, начинает работу раньше средств защиты уровня ОС и остаётся для них невидимым, получая контроль над системой до того, как штатные механизмы защиты успевают инициализироваться.</t>
+        </is>
+      </c>
+      <c r="E202" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-На АРМ применяется аппаратно-программный модуль доверенной загрузки (АПМДЗ), проверяющий целостность загрузчика и BIOS/UEFI и блокирующий загрузку с посторонних носителей до входа в доверенную ОС. Встроенный UEFI Secure Boot без выделенного СЗИ окажется недостаточным, поэтому требуется отдельный аппаратный модуль.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">- Зарубежные АПМДЗ в РФ не применяются по требованиям ФСТЭК/ФСБ.
-- Российские сертифицированные: ПАК «Соболь» (Код Безопасности), «Аккорд-АМДЗ» (ОКБ САПР) и прочие.
-</t>
-          </r>
-        </is>
-      </c>
-      <c r="F202" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+            <t xml:space="preserve">
+На АРМ применяется аппаратно-программный модуль доверенной загрузки (АПМДЗ), проверяющий целостность загрузчика и BIOS/UEFI и блокирующий загрузку с посторонних носителей до входа в доверенную ОС. Встроенного UEFI Secure Boot без выделенного сертифицированного модуля недостаточно для закрытия меры — требуется отдельный аппаратный модуль доверенной загрузки.
+Класс используемых средств — аппаратно-программные модули доверенной загрузки (АПМДЗ).
+Российские сертифицированные (ФСТЭК/ФСБ): ПАК «Соболь» (Код Безопасности), «Аккорд-АМДЗ» (ОКБ САПР) и др. Зарубежные АПМДЗ в РФ не применяются в силу требований ФСТЭК/ФСБ к доверенной загрузке.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F202" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Проверочные процедуры (свидетельства) - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
             <t xml:space="preserve">
 1. Конфигурация АПМДЗ и Secure Boot на образце АРМ.
-2. Акт установки и активации модуля доверенной загрузки по парку АРМ - важно по требованию ФСБ.
+2. Акт установки и активации модуля доверенной загрузки по парку АРМ (значим с точки зрения требований ФСБ).
 3. Итоги интервью с ответственным за защиту АРМ.</t>
           </r>
         </is>
       </c>
-      <c r="G202" s="36" t="inlineStr">
-        <is>
-          <t>1. АПМДЗ установлен не на всех АРМ пользователей и эксплуатационного персонала.
-2. Используется только программный Secure Boot без сертифицированного аппаратного модуля там, где требуется более строгий контроль.</t>
+      <c r="G202" s="151" t="inlineStr">
+        <is>
+          <t>1. АПМДЗ установлен не на всех АРМ пользователей и эксплуатационного персонала, включая АРМ с повышенными полномочиями;
+2. Используется только программный UEFI Secure Boot без сертифицированного аппаратного модуля там, где требуется более строгий контроль;
+3. Пароль (ПИН-код) администратора АПМДЗ не меняется со значения по умолчанию, установленного при внедрении;
+4. Факт срабатывания блокировки АПМДЗ (попытка загрузки с постороннего носителя) не передаётся для централизованного анализа.</t>
         </is>
       </c>
     </row>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -15086,10 +15086,59 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D203" s="21" t="n"/>
-      <c r="E203" s="31" t="n"/>
-      <c r="F203" s="31" t="n"/>
-      <c r="G203" s="31" t="n"/>
+      <c r="D203" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует контроля (выявления) фактов использования в автоматизированной системе (АС) технологии мобильного кода — программного кода, который передаётся по сети и исполняется на стороне получателя без предварительной установки (сценарии в составе веб-страниц, макросы офисных документов, объекты ActiveX, сценарии PowerShell/командных интерпретаторов, загружаемые Java-апплеты и подобные механизмы).
+Главная цель меры — обеспечить видимость применения технологии, которая по своей природе способна исполнять произвольные инструкции без явного действия пользователя по «установке» и потому нередко выпадает из поля зрения традиционного контроля состава ПО (меры ЦЗИ.20/22): без выявления фактов использования мобильного кода организация не может оценить связанный с этим риск и целенаправленно ограничить его применение только оправданными случаями.</t>
+        </is>
+      </c>
+      <c r="E203" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технический контроль реализуется:
+1. Анализом сетевого и почтового трафика на предмет передачи объектов, содержащих технологию мобильного кода (сценарии, макросы, ActiveX-объекты, вложения с активным содержимым);
+2. Контролем на стороне АРМ и серверов фактов запуска интерпретаторов сценариев (командных оболочек, PowerShell, WSH) и активации макросов офисных документов;
+3. Регистрацией и централизованным анализом выявленных фактов использования мобильного кода для последующей оценки их правомерности (см. также меру ЦЗИ.35 в части регистрации).
+Класс используемых средств — средства анализа сетевого трафика и содержимого (Content Filtering / Sandbox), функциональность выявления сценариев в составе EDR/EPP-платформы.
+Иностранные: Symantec Content Analysis (песочница), Palo Alto Networks (WildFire, анализ содержимого) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (контроль макросов и сценариев), PT Sandbox и др.
+Открытый код: встроенное журналирование PowerShell (Script Block Logging), Sysmon (события создания процессов интерпретаторов) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F203" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства выявления использования технологии мобильного кода.
+2. Журнал (отчёт) выявленных фактов использования мобильного кода за проверяемый период.
+3. Итоги интервью с ответственным за мониторинг ИБ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G203" s="151" t="inlineStr">
+        <is>
+          <t>1. Контроль охватывает только один канал (например, только почтовые вложения), тогда как мобильный код может поступать и через веб-трафик, съёмные носители или уже присутствовать во внутренних документах;
+2. Выявленные факты использования мобильного кода не анализируются на предмет правомерности, а лишь накапливаются в журнале без дальнейших действий;
+3. Контроль настроен только для распространённых форматов (макросы Office), но не охватывает менее очевидные механизмы (сценарии PowerShell, встроенный JavaScript в PDF);
+4. Пороговые значения (правила выявления) не пересматриваются при появлении новых техник использования мобильного кода злоумышленниками.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="13" t="inlineStr">
@@ -15120,10 +15169,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D205" s="21" t="n"/>
-      <c r="E205" s="31" t="n"/>
-      <c r="F205" s="31" t="n"/>
-      <c r="G205" s="31" t="n"/>
+      <c r="D205" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта выявления уязвимости в рамках процессов сканирования и анализа защищённости (меры ЦЗИ.1—ЦЗИ.11), а не только формирования итогового отчёта по результатам сканирования.
+Главная цель меры — обеспечить полную и достоверную историю выявленных уязвимостей для последующего анализа (в том числе повторного выявления той же уязвимости, признака регресса или несвоевременного устранения), а не полагаться на единственный «плоский» отчёт сканирования, который не позволяет отследить динамику и не защищён от случайной потери или замены более поздним отчётом.</t>
+        </is>
+      </c>
+      <c r="E205" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства анализа защищённости (сканера уязвимостей) на автоматическое формирование события защиты информации при каждом факте выявления уязвимости, с фиксацией её идентификатора (CVE), уровня критичности, затронутого актива и времени обнаружения, и последующей передачей этих событий в SIEM-систему для централизованного хранения и корреляции.
+Класс используемых средств — встроенный механизм журналирования средства анализа защищённости (сканера уязвимостей), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Tenable Nessus (журнал сканирования), Splunk (централизованный сбор событий) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM (журнал выявленных уязвимостей), MaxPatrol SIEM, KUMA и др.
+Открытый код: OpenVAS (журнал сканирования), Wazuh (сбор и корреляция событий) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F205" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования событий выявления уязвимостей в средстве анализа защищённости.
+2. Выгрузка зарегистрированных событий выявления уязвимостей за проверяемый период.
+3. Итоги интервью с ответственным за управление уязвимостями.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G205" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируется только итоговый отчёт по завершении сканирования, а не отдельное событие по каждому факту выявления уязвимости;
+2. События выявления уязвимостей не передаются в SIEM-систему, доступны только в интерфейсе самого сканера с ограниченным сроком хранения;
+3. При повторном выявлении ранее известной уязвимости отдельное событие не формируется, что не позволяет отследить длительность её существования;
+4. Уровень критичности уязвимости не фиксируется в событии, что не позволяет приоритизировать реагирование по журналу событий.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="47.25" customHeight="1">
       <c r="A206" s="20" t="inlineStr">
@@ -15141,10 +15236,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D206" s="21" t="n"/>
-      <c r="E206" s="31" t="n"/>
-      <c r="F206" s="31" t="n"/>
-      <c r="G206" s="31" t="n"/>
+      <c r="D206" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта установки, обновления и (или) удаления ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО на серверном и сетевом оборудовании — то есть регистрации результата операций, выполняемых в рамках меры ЦЗИ.12.
+Главная цель меры — обеспечить возможность ретроспективно подтвердить, какое ПО, когда и кем было установлено, обновлено или удалено на конкретном сервере или сетевом устройстве: без такой регистрации расследование инцидента, связанного с несанкционированным изменением состава ПО, невозможно, а факт применения планового обновления невозможно формально подтвердить.</t>
+        </is>
+      </c>
+      <c r="E206" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой системы патч-менеджмента, платформы централизованного управления серверами и штатных средств журналирования операционных систем на фиксацию событий установки, обновления и удаления пакетов (ПО), с указанием инициатора операции, времени и результата, и последующей передачей таких событий в SIEM-систему.
+Класс используемых средств — встроенные журналы операционных систем и систем управления пакетами, системы управления обновлениями (Patch Management), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Microsoft SCCM (журнал развёртывания ПО), Splunk и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, MaxPatrol SIEM, KUMA и др.
+Открытый код: журнал пакетного менеджера (apt/yum history), Wazuh (сбор и корреляция событий) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F206" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования операций установки/обновления/удаления ПО на серверном и сетевом оборудовании.
+2. Выгрузка зарегистрированных событий за проверяемый период с сопоставлением с плановым графиком обновлений (мера ЦЗИ.12).
+3. Итоги интервью с ответственным за эксплуатацию серверной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G206" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация событий охватывает серверное оборудование, но не распространяется на сетевое (маршрутизаторы, коммутаторы, межсетевые экраны);
+2. Инициатор операции (учётная запись, от имени которой выполнено изменение) не фиксируется в событии, что не позволяет установить ответственного;
+3. События установки/обновления/удаления ПО не передаются в SIEM-систему, доступны только в локальных журналах отдельных серверов с ограниченным сроком хранения;
+4. Неуспешные (прерванные) операции установки/обновления не регистрируются, фиксируются только успешно завершённые.</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="47.25" customHeight="1">
       <c r="A207" s="20" t="inlineStr">
@@ -15162,10 +15303,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D207" s="21" t="n"/>
-      <c r="E207" s="31" t="n"/>
-      <c r="F207" s="31" t="n"/>
-      <c r="G207" s="31" t="n"/>
+      <c r="D207" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична ЦЗИ.28, но распространяется на АРМ пользователей и эксплуатационного персонала: требует регистрации в качестве события защиты информации каждого факта установки, обновления и (или) удаления прикладного ПО, ПО АС, средств и систем защиты информации, системного ПО на рабочих станциях.
+Главная цель меры — обеспечить ту же возможность ретроспективного подтверждения состава изменений ПО, что и на серверах, но применительно к существенно более многочисленному и территориально распределённому парку АРМ, где несанкционированная установка ПО пользователем — значимо более вероятный сценарий, чем на серверном оборудовании.</t>
+        </is>
+      </c>
+      <c r="E207" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой системы патч-менеджмента, платформы централизованного управления АРМ (EPP-платформы) и штатных средств журналирования операционной системы на фиксацию событий установки, обновления и удаления ПО на АРМ, с указанием инициатора операции, времени и результата, и последующей передачей таких событий в SIEM-систему.
+Класс используемых средств — встроенные журналы операционных систем, платформы централизованного управления конечными точками (EPP), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Microsoft SCCM, Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор и корреляция событий, включая инвентаризацию ПО) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F207" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования операций установки/обновления/удаления ПО на образце АРМ.
+2. Выгрузка зарегистрированных событий по парку АРМ за проверяемый период.
+3. Итоги интервью с ответственным за поддержку пользователей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G207" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация событий установлена только на части парка АРМ, для АРМ, длительное время не подключающихся к сети, история изменений не собирается вовсе;
+2. Событие фиксирует факт изменения, но не различает санкционированную (в рамках патч-менеджмента) и несанкционированную (самовольную) установку ПО пользователем;
+3. Установка ПО в обход централизованной системы управления (например, с правами локального администратора) не регистрируется;
+4. События не передаются в SIEM-систему, доступны только локально на АРМ и утрачиваются при переустановке или выходе из строя рабочей станции.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="78.75" customHeight="1">
       <c r="A208" s="20" t="inlineStr">
@@ -15183,14 +15370,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D208" s="34" t="inlineStr">
-        <is>
-          <t>Каждый запуск службы/демона должен фиксироваться как событие ИБ, чтобы не допустить незамеченный запуск постороннего сервиса закрепления в системе (persistence) и чтобы дать возможность восстановить хронологию при расследовании истории запусков.</t>
-        </is>
-      </c>
-      <c r="E208" s="31" t="n"/>
-      <c r="F208" s="31" t="n"/>
-      <c r="G208" s="31" t="n"/>
+      <c r="D208" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы каждый запуск программного сервиса (службы, демона) на серверном оборудовании и АРМ регистрировался как событие защиты информации.
+Главная цель меры — не допустить незамеченного запуска постороннего сервиса, используемого для закрепления в системе (persistence): вредоносный код и злоумышленник, получивший контроль над системой, нередко регистрируют собственную службу для автоматического восстановления присутствия после перезагрузки, и без регистрации фактов запуска сервисов такая активность останется без возможности ретроспективного расследования.</t>
+        </is>
+      </c>
+      <c r="E208" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой штатного журнала операционной системы (журнал служб) на фиксацию событий запуска, остановки и изменения параметров запуска (автозапуск) программных сервисов, с последующей передачей таких событий в SIEM-систему для централизованного анализа и выявления аномальных (ранее не наблюдавшихся) сервисов.
+Класс используемых средств — встроенные средства журналирования операционной системы, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Splunk (сбор и анализ журналов служб), Microsoft Sysmon (детальное журналирование создания процессов и служб) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh, встроенный журнал systemd/Event Log и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F208" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования запуска программных сервисов на образце сервера и АРМ.
+2. Выгрузка зарегистрированных событий запуска сервисов за проверяемый период.
+3. Итоги интервью с ответственным за мониторинг ИБ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G208" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация запуска сервисов настроена только на серверном оборудовании, но не на АРМ, где риск несанкционированной установки службы выше;
+2. События запуска сервисов собираются локально, но не передаются в SIEM-систему для централизованного анализа и выявления аномалий;
+3. Выявление ранее не наблюдавшихся (новых) сервисов не автоматизировано, анализ журнала проводится только по факту уже случившегося инцидента;
+4. Регистрируется факт запуска, но не факт изменения параметров автозапуска сервиса, что не позволяет выявить закрепление в системе до перезагрузки.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="78.75" customHeight="1">
       <c r="A209" s="20" t="inlineStr">
@@ -15208,14 +15437,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D209" s="34" t="inlineStr">
-        <is>
-          <t>Результаты проверок состава ПО (по мерам ЦЗИ.20 для АРМ и ЦЗИ.22 для серверов) должны фиксироваться как событие с итогом проверки, а не просто выполняться. Чтобы избежать проблем с контролем реального состава ПО и с отсутствием истории таких проверок.</t>
-        </is>
-      </c>
-      <c r="E209" s="31" t="n"/>
-      <c r="F209" s="31" t="n"/>
-      <c r="G209" s="31" t="n"/>
+      <c r="D209" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы результаты каждой проверки состава ПО серверного оборудования (мера ЦЗИ.22) фиксировались как событие защиты информации с итогом проверки, а не просто выполнялись без регистрации.
+Главная цель меры — обеспечить возможность подтвердить сам факт и результат контроля состава ПО серверов за конкретный период: без регистрации результатов проверок невозможно отличить ситуацию, когда контроль реально выполнялся и не выявил отклонений, от ситуации, когда контроль не выполнялся вовсе, что критично при расследовании инцидента или проверке соответствия.</t>
+        </is>
+      </c>
+      <c r="E209" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства инвентаризации ПО серверного оборудования (мера ЦЗИ.22) на автоматическое формирование события по завершении каждого цикла проверки, с фиксацией результата (соответствие/несоответствие эталонному перечню, перечень выявленных отклонений) и передачей события в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования средства инвентаризации ПО / системы управления конфигурациями, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Microsoft SCCM (журнал инвентаризации), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, Efros Config Inspector, MaxPatrol SIEM и др.
+Открытый код: Wazuh (события syscollector), Ansible (журнал выполнения плейбуков инвентаризации) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F209" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования результатов проверок состава ПО серверного оборудования.
+2. Выгрузка зарегистрированных результатов проверок за проверяемый период.
+3. Итоги интервью с ответственным за администрирование серверной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G209" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируется только факт выявленного отклонения, а не каждый цикл проверки, что не позволяет подтвердить регулярность контроля;
+2. Периодичность формирования события не соответствует установленной регламентом (мера ЦЗИ.22) периодичности самой проверки;
+3. Событие не содержит перечня выявленных отклонений, только общий признак «соответствие/несоответствие», что затрудняет последующий анализ;
+4. Результаты проверок не передаются в SIEM-систему, доступны только в локальном журнале средства инвентаризации.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="31.5" customHeight="1">
       <c r="A210" s="20" t="inlineStr">
@@ -15233,10 +15504,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D210" s="21" t="n"/>
-      <c r="E210" s="31" t="n"/>
-      <c r="F210" s="31" t="n"/>
-      <c r="G210" s="31" t="n"/>
+      <c r="D210" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична ЦЗИ.31, но требует регистрации результатов выполнения операций по контролю состава ПО АРМ пользователей и эксплуатационного персонала (мера ЦЗИ.20) в качестве события защиты информации.
+Главная цель меры — обеспечить ту же возможность подтверждения факта и результата контроля, что и для серверного оборудования (мера ЦЗИ.31), применительно к парку АРМ, для которого регулярность и полнота охвата проверками особенно значимы ввиду его многочисленности и территориальной распределённости.</t>
+        </is>
+      </c>
+      <c r="E210" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства инвентаризации ПО АРМ (мера ЦЗИ.20) на автоматическое формирование события по завершении каждого цикла проверки, с фиксацией результата (соответствие/несоответствие эталонному перечню, перечень выявленных отклонений) и передачей события в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования системы инвентаризации ПО (Software Asset Management) / EPP-платформы, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Microsoft SCCM, Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (события syscollector) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F210" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования результатов проверок состава ПО АРМ.
+2. Выгрузка зарегистрированных результатов проверок по парку АРМ за проверяемый период.
+3. Итоги интервью с ответственным за администрирование АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G210" s="151" t="inlineStr">
+        <is>
+          <t>1. Событие формируется только для АРМ, фактически подключённых к сети в момент проверки, без учёта длительно отсутствующих;
+2. Регистрируется только факт выявленного отклонения, а не каждый цикл проверки по всему парку АРМ;
+3. Результаты проверок не сопоставляются с данными меры ЦЗИ.20 о фактическом составе разрешённого ПО за тот же период;
+4. Результаты проверок не передаются в SIEM-систему, доступны только в локальной консоли средства инвентаризации.</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="378" customHeight="1">
       <c r="A211" s="77" t="inlineStr">
@@ -15254,51 +15571,27 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D211" s="78" t="inlineStr">
-        <is>
-          <t>Мера является производной от ЦЗИ.23  и требует регистрации результатов каждого выполнения контроля состава программного обеспечения (ПО) именно на этапе инициализации операционной системы (ОС), а не факта запуска отдельных приложений пользователем. В отличие от меры ЦЗИ.32 здесь контролируется и регистрируется состав ПО именно на уровне начальной инициализации ОС и запуска компонентов в ходе её старта, в том числе тех, что завершают работу сразу после окончания загрузки. Без такой регистрации невозможно ретроспективно подтвердить факт и результат контроля на этапе загрузки при расследовании инцидента, связанного с компрометацией автозагружаемых компонентов, либо при проверке соответствия.</t>
-        </is>
-      </c>
-      <c r="E211" s="80" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Регистрация результатов контроля состава ПО, запускаемого при загрузке ОС, должна осуществляется средствами журналирования аппаратно-программного модуля доверенной загрузки (АПМДЗ).
+      <c r="D211" s="144" t="inlineStr">
+        <is>
+          <t>Мера является производной от ЦЗИ.23 и требует регистрации результатов каждого выполнения контроля состава программного обеспечения (ПО) именно на этапе инициализации операционной системы (ОС), а не факта запуска отдельных приложений пользователем. В отличие от меры ЦЗИ.32 здесь контролируется и регистрируется состав ПО именно на уровне начальной инициализации ОС и запуска компонентов в ходе её старта, в том числе тех, что завершают работу сразу после окончания загрузки.
+Главная цель меры — обеспечить возможность ретроспективно подтвердить факт и результат контроля именно на этапе загрузки при расследовании инцидента, связанного с компрометацией автозагружаемых компонентов, либо при проверке соответствия: без такой регистрации невозможно отличить ситуацию, когда контроль на этапе загрузки реально выполнялся и не выявил отклонений, от ситуации, когда он не выполнялся вовсе.</t>
+        </is>
+      </c>
+      <c r="E211" s="164" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация результатов контроля состава ПО, запускаемого при загрузке ОС, должна осуществляться средствами журналирования аппаратно-программного модуля доверенной загрузки (АПМДЗ).
 Журналы событий программных средств защиты информации (СЗИ) общего назначения (контроль приложений EDR/EPP-агентов, антивирусов, централизованных консолей управления, например Kaspersky Security Center) фиксируют запуск процессов, инициированный пользователем или системой уже после старта ОС, и не являются регистрацией результатов контроля на этапе загрузки — такие журналы можно использовать только как дополнительное свидетельство к основному, полученному от АПМДЗ/СДЗ, но не как самостоятельное закрытие меры (см. выявленные коллизии).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Российские сертифицированные: ПАК «Соболь» (Код Безопасности), «Аккорд-АМДЗ» (ОКБ САПР) и др.</t>
+Класс используемых средств — журнал аппаратно-программного модуля доверенной загрузки (АПМДЗ) / средства доверенной загрузки (СДЗ).
+Российские сертифицированные (ФСТЭК/ФСБ): ПАК «Соболь» (Код Безопасности), «Аккорд-АМДЗ» (ОКБ САПР) и др. Зарубежные и открытые аналоги данного класса в РФ не применяются в силу требований ФСТЭК/ФСБ к доверенной загрузке.</t>
           </r>
         </is>
       </c>
@@ -15325,10 +15618,12 @@
           </r>
         </is>
       </c>
-      <c r="G211" s="80" t="inlineStr">
-        <is>
-          <t>1. Регистрируются только случаи выявленных отклонений, а не каждый цикл проверки.
-2. Отсутствует связь между событием регистрации и конкретной версией эталонного перечня, на соответствие которому проводилась проверка.</t>
+      <c r="G211" s="164" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только случаи выявленных отклонений, а не каждый цикл проверки, что не позволяет подтвердить регулярность контроля;
+2. Отсутствует связь между событием регистрации и конкретной версией эталонного перечня, на соответствие которому проводилась проверка;
+3. События регистрации результатов контроля автозагрузки не передаются в SIEM-систему, доступны только в локальном журнале АПМДЗ;
+4. Периодичность формирования события не соответствует фактической периодичности проверок автозагрузки на образцах АРМ.</t>
         </is>
       </c>
       <c r="H211" s="82" t="inlineStr">
@@ -15372,14 +15667,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D212" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует, что каждая проверка целостности компонентов ПО АС фиксировалась как событие с результатом — не только сама блокировка при нарушении, но и факт штатной успешной проверки. Это позволяет подтвердить, что контроль целостности реально выполнялся в конкретный период и что доступна история проверок для расследования инцидента с подменой компонента АС.</t>
-        </is>
-      </c>
-      <c r="E212" s="31" t="n"/>
-      <c r="F212" s="31" t="n"/>
-      <c r="G212" s="31" t="n"/>
+      <c r="D212" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы каждая проверка целостности запускаемых компонентов ПО автоматизированных систем (АС) на АРМ (мера ЦЗИ.24) фиксировалась как событие защиты информации с результатом — не только сама блокировка при выявленном нарушении, но и факт штатной успешной проверки.
+Главная цель меры — подтвердить, что контроль целостности реально выполнялся в конкретный период, а не только зафиксировать случаи его срабатывания: доступность полной истории проверок (включая штатные, без нарушений) необходима как для расследования инцидента, связанного с подменой компонента АС, так и для подтверждения непрерывности работы самого механизма контроля.</t>
+        </is>
+      </c>
+      <c r="E212" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства контроля целостности запускаемых файлов (мера ЦЗИ.24) на формирование события при каждой проведённой проверке — как при успешном подтверждении целостности, так и при выявленном нарушении, с последующей передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования средства контроля целостности запускаемых файлов (File Integrity Monitoring) в составе EDR/HIPS-платформы, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Tripwire for Servers, Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (модуль FIM) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F212" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования результатов проверок целостности запускаемых компонентов ПО АС на образце АРМ.
+2. Выгрузка зарегистрированных результатов проверок за проверяемый период, включая штатные (без нарушений).
+3. Итоги интервью с ответственным за администрирование АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G212" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только случаи выявленного нарушения целостности (блокировки), штатные успешные проверки не фиксируются, что не позволяет подтвердить непрерывность контроля;
+2. Событие не содержит идентификатор проверенного компонента ПО АС и его контрольную сумму, что затрудняет последующий анализ;
+3. События проверок целостности не передаются в SIEM-систему, доступны только в локальном журнале средства защиты на АРМ;
+4. Регистрация результатов настроена не для всех компонентов ПО АС, подлежащих контролю целостности по мере ЦЗИ.24, а только для основного исполняемого файла.</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="20" t="inlineStr">
@@ -15397,10 +15734,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D213" s="21" t="n"/>
-      <c r="E213" s="31" t="n"/>
-      <c r="F213" s="31" t="n"/>
-      <c r="G213" s="31" t="n"/>
+      <c r="D213" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта выявления использования технологии мобильного кода (мера ЦЗИ.26).
+Главная цель меры — обеспечить полную и доступную для последующего анализа историю применения мобильного кода в инфраструктуре: без регистрации таких фактов как отдельных событий защиты информации оценка масштаба и правомерности использования этой технологии сводится к разрозненным наблюдениям, не пригодным для расследования инцидента или периодического анализа тенденций.</t>
+        </is>
+      </c>
+      <c r="E213" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства выявления использования технологии мобильного кода (мера ЦЗИ.26) на автоматическое формирование события при каждом выявленном факте, с фиксацией источника, типа мобильного кода и затронутого актива, и последующей передачей событий в SIEM-систему для централизованного анализа.
+Класс используемых средств — встроенный механизм журналирования средства анализа сетевого трафика и содержимого / EDR-платформы, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Symantec Content Analysis, Palo Alto Networks (WildFire) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса, PT Sandbox, MaxPatrol SIEM и др.
+Открытый код: Sysmon (события создания процессов интерпретаторов), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F213" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования фактов выявления использования технологии мобильного кода.
+2. Выгрузка зарегистрированных событий за проверяемый период.
+3. Итоги интервью с ответственным за мониторинг ИБ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G213" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация событий охватывает не все каналы, по которым выявляется мобильный код (мера ЦЗИ.26), а только часть из них;
+2. События не содержат сведений о типе мобильного кода и затронутом активе, что не позволяет провести содержательный анализ;
+3. События не передаются в SIEM-систему, доступны только в локальном журнале средства выявления;
+4. Повторяющиеся факты использования одного и того же типа мобильного кода не агрегируются, что затрудняет выявление тенденций.</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="78.75" customHeight="1">
       <c r="A214" s="20" t="inlineStr">
@@ -15420,10 +15803,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D214" s="21" t="n"/>
-      <c r="E214" s="31" t="n"/>
-      <c r="F214" s="31" t="n"/>
-      <c r="G214" s="31" t="n"/>
+      <c r="D214" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого результата выполнения операций по контролю целостности и достоверности источников получения при распространении и (или) обновлении ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО (мера ЦЗИ.19).
+Главная цель меры — обеспечить возможность подтвердить, что контроль подлинности источника и целостности каждого полученного обновления фактически выполнялся, а не только зафиксировать случаи выявленного несоответствия: полная история проверок необходима для расследования инцидента, связанного с компрометацией цепочки поставок ПО, и для подтверждения соответствия установленному регламенту.</t>
+        </is>
+      </c>
+      <c r="E214" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства проверки цифровой подписи и контрольных сумм получаемого ПО (мера ЦЗИ.19) на формирование события при каждой выполненной проверке — как при успешном подтверждении подлинности и целостности источника, так и при выявленном несоответствии, с последующей передачей событий в SIEM-систему.
+Класс используемых средств — встроенные механизмы журналирования систем патч-менеджмента и менеджеров пакетов, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Microsoft SCCM/WSUS (журнал проверки подписи обновлений), Splunk и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol VM, MaxPatrol SIEM, KUMA и др.
+Открытый код: журнал GPG-проверки пакетного менеджера (apt/yum), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F214" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования результатов проверок подлинности источника и целостности получаемого ПО.
+2. Выгрузка зарегистрированных результатов проверок за проверяемый период, включая выявленные несоответствия (при наличии).
+3. Итоги интервью с ответственным за получение и распространение обновлений ПО.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G214" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только случаи выявленного несоответствия подписи или контрольной суммы, а не каждая выполненная проверка;
+2. Регистрация настроена не для всех категорий ПО, подлежащих контролю по мере ЦЗИ.19, а только для обновлений операционной системы;
+3. События не содержат сведения об источнике получения ПО, что не позволяет впоследствии подтвердить его доверенность;
+4. Результаты проверок не передаются в SIEM-систему, доступны только в локальном журнале средства патч-менеджмента.</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="13" t="inlineStr">

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -827,6 +827,9 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -15896,10 +15899,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D217" s="21" t="n"/>
-      <c r="E217" s="31" t="n"/>
-      <c r="F217" s="31" t="n"/>
-      <c r="G217" s="31" t="n"/>
+      <c r="D217" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует развёртывания средств защиты от вредоносного кода непосредственно на физических АРМ пользователей и эксплуатационного персонала — как одном из самостоятельных уровней эшелонированной защиты, наряду с уровнями серверов, сетевого трафика и других объектов (меры ЗВК.2—ЗВК.7).
+Главная цель меры — закрыть тот уровень заражения, который остаётся вне зоны действия сетевых и серверных средств защиты: рабочая станция взаимодействует с внешними носителями, почтой и веб-ресурсами непосредственно, и именно она чаще всего оказывается точкой первичного проникновения вредоносного кода в инфраструктуру.</t>
+        </is>
+      </c>
+      <c r="E217" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается установкой на каждый физический АРМ агента защиты от вредоносного кода (антивирус / EPP-платформа), обеспечивающего постоянное сканирование файловой системы, оперативной памяти и запускаемых процессов, с автоматическим получением обновлений сигнатурных баз и обновлений самого движка.
+Класс используемых средств — средства защиты от вредоносного кода (антивирусы) уровня конечных точек (Endpoint Protection Platform, EPP).
+Иностранные: ESET Endpoint Antivirus, Bitdefender GravityZone и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса, Dr.Web Enterprise Security Suite и др.
+Открытый код: ClamAV (ограниченно применим как основное средство защиты на Windows-АРМ) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F217" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства защиты от вредоносного кода на образце АРМ.
+2. Выгрузка из консоли централизованного управления со статусом установки агента по парку АРМ за проверяемый период.
+3. Итоги интервью с ответственным за защиту АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G217" s="151" t="inlineStr">
+        <is>
+          <t>1. Средство защиты от вредоносного кода установлено не на всех АРМ, в частности отсутствует на АРМ подрядчиков и временных сотрудников;
+2. Актуальность сигнатурных баз и версии самого агента на части парка АРМ не отслеживается централизованно;
+3. Возможность локального отключения или деинсталляции агента пользователем не ограничена правами доступа;
+4. Проверка охвата АРМ средством защиты не входит в регулярный цикл контроля, проводится только по факту инцидента.</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="31.5" customHeight="1">
       <c r="A218" s="20" t="inlineStr">
@@ -15917,10 +15966,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D218" s="21" t="n"/>
-      <c r="E218" s="31" t="n"/>
-      <c r="F218" s="31" t="n"/>
-      <c r="G218" s="31" t="n"/>
+      <c r="D218" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует развёртывания защиты от вредоносного кода на уровне виртуальной информационной инфраструктуры (гипервизоры, виртуальные машины, VDI-инфраструктура) как отдельного уровня эшелонированной защиты, отличного от защиты физических АРМ и серверов (меры ЗВК.1, ЗВК.3).
+Главная цель меры — учесть специфику виртуальной среды, где классический агентный антивирус на каждой виртуальной машине создаёт избыточную нагрузку на общие вычислительные ресурсы хоста (так называемый «antivirus storm» при одновременном сканировании множества ВМ) и не защищает сам гипервизор как отдельный объект атаки.</t>
+        </is>
+      </c>
+      <c r="E218" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением средств защиты, адаптированных для виртуальной инфраструктуры, — безагентных (agentless) решений, интегрированных с гипервизором на уровне API, либо облегчённых агентов с централизованным вынесением сигнатурного анализа на выделенный сервер сканирования (light agent), что снижает нагрузку на ресурсы хостовой системы по сравнению с классическим агентом на каждой ВМ.
+Класс используемых средств — средства защиты виртуальной инфраструктуры от вредоносного кода (безагентные или light agent решения для VMware/Hyper-V/отечественных гипервизоров).
+Иностранные: Trend Micro Deep Security (агентное/безагентное решение для виртуализации) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для виртуальных сред (Light Agent), Dr.Web Enterprise Security Suite (модуль для виртуальных сред) и др.
+Открытый код: полноценных специализированных решений для виртуализации в открытом доступе практически нет, применяется ClamAV в составе гостевой ОС ВМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F218" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства защиты виртуальной инфраструктуры от вредоносного кода.
+2. Выгрузка из консоли управления со статусом защиты по парку виртуальных машин за проверяемый период.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G218" s="151" t="inlineStr">
+        <is>
+          <t>1. Защитой охвачены не все виртуальные машины, в частности новые ВМ, создаваемые из шаблона без предустановленного агента;
+2. Защита не распространяется на сам гипервизор как отдельный объект (управляющая консоль, гипервизорный слой);
+3. При миграции виртуальной машины между хостами защита не переносится автоматически и требует ручной донастройки;
+4. Нагрузка на общие ресурсы хоста при одновременном сканировании множества ВМ не контролируется, что приводит к отключению сканирования администраторами.</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="31.5" customHeight="1">
       <c r="A219" s="20" t="inlineStr">
@@ -15938,10 +16033,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D219" s="21" t="n"/>
-      <c r="E219" s="31" t="n"/>
-      <c r="F219" s="31" t="n"/>
-      <c r="G219" s="31" t="n"/>
+      <c r="D219" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует развёртывания защиты от вредоносного кода на уровне серверного оборудования как отдельного уровня эшелонированной защиты, наряду с защитой АРМ (мера ЗВК.1) и виртуальной инфраструктуры (мера ЗВК.2).
+Главная цель меры — защитить критичный сегмент инфраструктуры, компрометация которого влечёт более тяжёлые последствия, чем заражение отдельной рабочей станции: сервер, как правило, обрабатывает данные многих пользователей одновременно и обладает более широкими сетевыми правами доступа, что делает его привлекательной целью для распространения вредоносного кода по инфраструктуре.</t>
+        </is>
+      </c>
+      <c r="E219" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается установкой на серверное оборудование серверной редакции средства защиты от вредоносного кода, учитывающей особенности серверных операционных систем и минимизирующей влияние на производительность выполняемых на сервере сервисов (например, за счёт исключения из полного сканирования каталогов баз данных по регламентированным правилам).
+Класс используемых средств — средства защиты от вредоносного кода серверного класса (Server Security).
+Иностранные: Trend Micro Deep Security, Bitdefender GravityZone (серверная редакция) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для серверов, Dr.Web Enterprise Security Suite (серверная редакция) и др.
+Открытый код: ClamAV (для серверов на базе Linux) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F219" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства защиты от вредоносного кода на образце сервера.
+2. Выгрузка из консоли централизованного управления со статусом установки агента по серверному парку за проверяемый период.
+3. Итоги интервью с ответственным за администрирование серверной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G219" s="151" t="inlineStr">
+        <is>
+          <t>1. Серверная защита от вредоносного кода развёрнута не на всех серверах, отдельные категории (например, серверы СУБД) исключены без формального обоснования;
+2. Исключения из области сканирования (каталоги, процессы) не документированы и не пересматриваются на предмет обоснованности;
+3. Полное (глубокое) сканирование серверов не проводится из опасения снижения производительности, ограничиваются только резидентным мониторингом;
+4. Обновление сигнатурных баз на серверах, изолированных от общей сети (например, в контуре безопасности), не организовано отдельным каналом.</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="31.5" customHeight="1">
       <c r="A220" s="20" t="inlineStr">
@@ -15959,10 +16100,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D220" s="21" t="n"/>
-      <c r="E220" s="31" t="n"/>
-      <c r="F220" s="31" t="n"/>
-      <c r="G220" s="31" t="n"/>
+      <c r="D220" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует реализации защиты от вредоносного кода на уровне контроля межсетевого трафика — то есть выявления и блокирования вредоносного кода непосредственно в потоке данных, пересекающем границы контролируемых сегментов сети, вне зависимости от того, установлена ли конечная защита (меры ЗВК.1—ЗВК.3) на узле-получателе.
+Главная цель меры — сформировать дополнительный, независимый от конечных узлов рубеж обороны: сетевой уровень контроля способен выявить вредоносный код до момента его получения конечным устройством, а также обнаружить заражение узла, на котором конечная защита была отключена, обойдена или не установлена.</t>
+        </is>
+      </c>
+      <c r="E220" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на периметре и (или) границах внутренних сегментов сети средства сетевой защиты от вредоносного кода (модуль антивирусной проверки трафика в составе межсетевого экрана нового поколения, NGFW, либо системы предотвращения вторжений, IPS), выполняющего разбор и проверку сигнатур передаваемых файлов и потоков без участия конечного узла.
+Класс используемых средств — модуль антивирусной проверки сетевого трафика в составе межсетевого экрана нового поколения (NGFW) или системы предотвращения вторжений (IPS).
+Иностранные: Palo Alto Networks (модуль Threat Prevention), Fortinet FortiGate (антивирусный модуль) и пр.
+Российские сертифицированные (ФСТЭК): «Континент» (Код Безопасности, модуль антивирусной проверки), UserGate (модуль антивируса) и др.
+Открытый код: Suricata (сигнатурный анализ трафика на базе открытых баз правил) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F220" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля антивирусной проверки сетевого трафика.
+2. Схема расположения точек контроля межсетевого трафика в топологии сети.
+3. Журнал (отчёт) о выявленных и заблокированных фактах передачи вредоносного кода за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G220" s="151" t="inlineStr">
+        <is>
+          <t>1. Контроль межсетевого трафика на предмет вредоносного кода реализован только на внешнем периметре, но не на границах внутренних сегментов сети;
+2. Зашифрованный трафик (TLS) не подвергается расшифровке для антивирусной проверки, что оставляет значимую часть трафика вне контроля;
+3. Обновление сигнатурных баз модуля антивирусной проверки трафика выполняется реже, чем предусмотрено регламентом;
+4. Выявленные факты передачи вредоносного кода фиксируются, но не сопоставляются с конечным узлом-получателем для дальнейшего реагирования.</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="31.5" customHeight="1">
       <c r="A221" s="20" t="inlineStr">
@@ -15980,10 +16167,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D221" s="21" t="n"/>
-      <c r="E221" s="31" t="n"/>
-      <c r="F221" s="31" t="n"/>
-      <c r="G221" s="31" t="n"/>
+      <c r="D221" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует реализации защиты от вредоносного кода на уровне контроля почтового трафика — проверки вложений и содержимого электронных сообщений на почтовом шлюзе до их доставки получателю.
+Главная цель меры — перекрыть один из наиболее массовых и результативных каналов первичного заражения: электронная почта остаётся основным способом доставки вредоносных вложений и фишинговых ссылок, а проверка на почтовом шлюзе позволяет блокировать вредоносный код до его попадания на АРМ пользователя, вне зависимости от того, откроет ли пользователь вложение.</t>
+        </is>
+      </c>
+      <c r="E221" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на почтовом шлюзе (Secure Email Gateway) средства антивирусной проверки входящих и исходящих сообщений, выполняющего сигнатурный и эвристический анализ вложений и содержимого писем, с автоматическим карантином или удалением выявленных вредоносных сообщений до их доставки получателю.
+Класс используемых средств — средства защиты почтового трафика от вредоносного кода (Secure Email Gateway с модулем антивирусной проверки).
+Иностранные: Proofpoint Email Protection, Cisco Secure Email и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для почтовых серверов, «Континент» (модуль почтовой безопасности) и др.
+Открытый код: ClamAV (модуль почтовой проверки, например в связке с Postfix/MIMEDefang) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F221" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация почтового шлюза в части антивирусной проверки вложений и содержимого.
+2. Журнал (отчёт) о выявленных и заблокированных вредоносных сообщениях за проверяемый период.
+3. Итоги интервью с ответственным за администрирование почтовой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G221" s="151" t="inlineStr">
+        <is>
+          <t>1. Антивирусная проверка почтового трафика реализована только для входящих сообщений, исходящие не проверяются, что не позволяет выявить рассылку с уже заражённого АРМ;
+2. Вложения в защищённых паролем архивах не подвергаются проверке и пропускаются без анализа;
+3. Обновление сигнатурных баз почтового шлюза выполняется с той же периодичностью, что и на конечных точках, без учёта повышенной критичности данного канала;
+4. Карантин выявленных вредоносных сообщений не анализируется на предмет целенаправленных атак, письма удаляются без дальнейшего разбора.</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="47.25" customHeight="1">
       <c r="A222" s="20" t="inlineStr">
@@ -16001,10 +16234,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D222" s="21" t="n"/>
-      <c r="E222" s="31" t="n"/>
-      <c r="F222" s="31" t="n"/>
-      <c r="G222" s="31" t="n"/>
+      <c r="D222" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует реализации защиты от вредоносного кода на уровне входного контроля устройств и переносных (отчуждаемых) носителей информации — то есть проверки съёмных носителей (флеш-накопителей, внешних дисков) и подключаемых устройств до их использования в вычислительных сетях организации (детальные технические требования к процедуре установлены мерами ЗВК.18/ЗВК.19).
+Главная цель меры — закрыть канал заражения, не зависящий от периметровой и почтовой защиты (меры ЗВК.4, ЗВК.5): съёмный носитель, заражённый вне контролируемой инфраструктуры (например, на личном компьютере сотрудника), способен внести вредоносный код напрямую на АРМ или сервер в обход сетевого контроля.</t>
+        </is>
+      </c>
+      <c r="E222" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается развёртыванием выделенного узла (станции) входного контроля, на котором каждый съёмный носитель или устройство проверяется средством защиты от вредоносного кода перед первым подключением к рабочей сети организации, при этом само подключение непроверенных носителей к рабочим АРМ и серверам технически ограничивается (см. также меру УЗП.29 в части контроля портов ввода-вывода).
+Класс используемых средств — выделенные станции (киоски) входного контроля съёмных носителей на базе средства защиты от вредоносного кода, средства контроля подключаемых устройств (Device Control).
+Иностранные: Kingston IronKey (аппаратный шифрованный носитель с встроенной проверкой), DeviceLock DLP (модуль Device Control) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль Device Control), Secret Net Studio (контроль устройств) и др.
+Открытый код: ClamAV (сканирование содержимого носителя на выделенной станции) в сочетании со штатными средствами блокировки USB-портов ОС.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F222" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) входного контроля устройств и переносных носителей информации.
+2. Конфигурация выделенной станции (киоска) входного контроля.
+3. Журнал проверок съёмных носителей и подключаемых устройств за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G222" s="151" t="inlineStr">
+        <is>
+          <t>1. Входной контроль организован не для всех категорий носителей, в частности не распространяется на внешние диски и мобильные устройства с функцией накопителя;
+2. Технический запрет на подключение непроверенных носителей к рабочим АРМ отсутствует, входной контроль носит рекомендательный (не принудительный) характер;
+3. Станция входного контроля не изолирована от рабочей сети, что не исключает риск заражения самой станции контроля;
+4. Проверенный носитель повторно не досматривается при последующих использованиях, хотя мог быть подключён к непроверенному узлу в промежутке.</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="47.25" customHeight="1">
       <c r="A223" s="20" t="inlineStr">
@@ -16022,10 +16301,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D223" s="21" t="n"/>
-      <c r="E223" s="31" t="n"/>
-      <c r="F223" s="31" t="n"/>
-      <c r="G223" s="31" t="n"/>
+      <c r="D223" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует реализации защиты от вредоносного кода на уровне контроля общедоступных объектов доступа — устройств, физически доступных неограниченному кругу лиц (банкоматов, платёжных терминалов, инфокиосков), с учётом их специфики: как правило, встроенной (embedded) операционной системы и невозможности установки классического антивирусного агента с полным функционалом.
+Главная цель меры — защитить категорию устройств с повышенным риском физического доступа злоумышленника (в отличие от АРМ и серверов, расположенных в контролируемых помещениях): общедоступность банкоматов и терминалов делает их удобной целью для установки вредоносного кода через физическое подключение или через уязвимости встроенного ПО, что подтверждается известными случаями атак типа «black box» и джекпоттинга.</t>
+        </is>
+      </c>
+      <c r="E223" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением специализированного средства защиты от вредоносного кода для встроенных систем (Embedded/ATM Security), реализующего преимущественно технологию замкнутой программной среды (whitelisting) — запуск разрешён только для явно перечисленного эталонного набора процессов устройства, что минимизирует нагрузку на ограниченные ресурсы встроенной ОС по сравнению с классическим сигнатурным сканированием.
+Класс используемых средств — специализированные средства защиты встраиваемых систем и банкоматов/терминалов (Embedded/ATM Security) с функцией замкнутой программной среды.
+Иностранные: McAfee (Trellix) Embedded Control, Symantec (Broadcom) Embedded Security и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Embedded Systems Security и др.
+Открытый код: специализированных открытых решений данного класса на практике не применяется в силу узкой embedded-специфики.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F223" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства защиты встроенных систем на образце банкомата (терминала).
+2. Эталонный перечень разрешённых к запуску процессов, применяемый в режиме замкнутой программной среды.
+3. Итоги интервью с ответственным за эксплуатацию банкоматной (терминальной) сети.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G223" s="151" t="inlineStr">
+        <is>
+          <t>1. Защита от вредоносного кода развёрнута не на всех устройствах общедоступного доступа, часть банкоматов эксплуатируется без неё;
+2. Режим замкнутой программной среды не активирован, средство защиты работает только в режиме мониторинга без фактической блокировки;
+3. Эталонный перечень разрешённых процессов не пересматривается при обновлении прикладного ПО банкомата (терминала), что приводит к массовым сбоям или к отключению контроля;
+4. Физический доступ к системному блоку банкомата (терминала) не контролируется отдельно, что позволяет обойти защиту прямым подключением к аппаратной части.</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="13" t="inlineStr">
@@ -16056,10 +16381,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D225" s="21" t="n"/>
-      <c r="E225" s="31" t="n"/>
-      <c r="F225" s="31" t="n"/>
-      <c r="G225" s="31" t="n"/>
+      <c r="D225" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы средства защиты от вредоносного кода, развёрнутые на всех уровнях эшелонированной защиты (меры ЗВК.1—ЗВК.7), функционировали в постоянном автоматическом режиме, включая автоматическую (без ручного вмешательства) установку обновлений программных компонентов и сигнатурных баз данных.
+Главная цель меры — исключить зависимость эффективности защиты от вредоносного кода от человеческого фактора и ручных операций: средство защиты с устаревшей сигнатурной базой или временно отключенное вручную не способно выявлять актуальные угрозы, а ручное управление обновлениями на большом парке объектов защиты неизбежно приводит к отставанию хотя бы части из них.</t>
+        </is>
+      </c>
+      <c r="E225" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается централизованной настройкой всех развёрнутых средств защиты от вредоносного кода на автоматическое (по расписанию, без запроса подтверждения оператора) получение обновлений программных компонентов и сигнатурных баз данных с сервера обновлений производителя или локального сервера-ретранслятора, а также централизованным контролем фактической актуальности версий по всему парку объектов защиты.
+Класс используемых средств — консоли централизованного управления средствами защиты от вредоносного кода (Security Management Console) со встроенным модулем управления обновлениями.
+Иностранные: ESET PROTECT, Bitdefender GravityZone Console и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, Dr.Web Enterprise Security Suite (централизованная консоль) и др.
+Открытый код: freshclam (автоматизированное обновление баз ClamAV) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F225" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация автоматического обновления в консоли централизованного управления средствами защиты от вредоносного кода.
+2. Отчёт консоли управления об актуальности версий сигнатурных баз и программных компонентов по всем объектам защиты за проверяемый период.
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G225" s="151" t="inlineStr">
+        <is>
+          <t>1. Автоматическое обновление настроено не для всех уровней защиты (меры ЗВК.1—ЗВК.7), часть объектов (например, банкоматы) обновляется вручную по отдельному графику без единого контроля;
+2. Объекты, длительное время не подключающиеся к сети (изолированные АРМ, объекты в удалённых подразделениях), не имеют альтернативного канала получения обновлений;
+3. Централизованный контроль фактической актуальности версий не ведётся, отсутствие обновления на конкретном объекте выявляется только по факту инцидента;
+4. При сбое автоматического обновления средство защиты продолжает функционировать с устаревшей базой без оповещения ответственных лиц.</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="261.75" customHeight="1">
       <c r="A226" s="20" t="inlineStr">
@@ -16077,51 +16448,28 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D226" s="34" t="inlineStr">
-        <is>
-          <t>Антивирусная защита на рабочих станциях должна работать постоянно в фоновом режиме как системная служба, подниматься автоматически при каждой загрузке ОС, а не запускаться вручную пользователем от случая к случаю. Что предотвратит случаи, когда пользователь намеренно или случайно завершает процесс антивируса, и заражение остаётся незамеченным до следующего ручного запуска, или когда при перезагрузке АРМ защита не поднимается автоматически и станция какое-то время работает, будучи полностью незащищённой.</t>
-        </is>
-      </c>
-      <c r="E226" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D226" s="144" t="inlineStr">
+        <is>
+          <t>Антивирусная защита на рабочих станциях должна работать постоянно в фоновом режиме как системная служба, подниматься автоматически при каждой загрузке ОС, а не запускаться вручную пользователем от случая к случаю.
+Главная цель меры — предотвратить ситуацию, когда пользователь намеренно или случайно завершает процесс антивируса и заражение остаётся незамеченным до следующего ручного запуска, а также случай, когда при перезагрузке АРМ защита не поднимается автоматически и станция какое-то время работает, будучи полностью незащищённой.</t>
+        </is>
+      </c>
+      <c r="E226" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Антивирусный агент устанавливается на АРМ как системная служба (Windows Service) или демон (Unix daemon), запуск которой прописан в автозагрузке ОС и не зависит от входа пользователя в систему, при этом, уровень привилегий службы должен не позволить обычному пользователю остановить службу без прав администратора.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>- Иностранные: ESET Endpoint Antivirus, Bitdefender GravityZone
-- Российские сертифицированные: Kaspersky Endpoint Security для бизнеса, Dr.Web Enterprise Security Suite
-- Открытый код: ClamAV (демон clamd) — покрывает Unix-контур, для Windows-АРМ как основное СЗИ практически не применяется</t>
+            <t xml:space="preserve">
+Антивирусный агент устанавливается на АРМ как системная служба (Windows Service) или демон (Unix daemon), запуск которой прописан в автозагрузке ОС и не зависит от входа пользователя в систему, при этом уровень привилегий службы должен не позволять обычному пользователю остановить службу без прав администратора.
+Класс используемых средств — средства защиты от вредоносного кода (антивирусы) уровня конечных точек, функционирующие в резидентном режиме системной службы.
+Иностранные: ESET Endpoint Antivirus, Bitdefender GravityZone и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса, Dr.Web Enterprise Security Suite и др.
+Открытый код: ClamAV (демон clamd) — покрывает Unix-контур, для Windows-АРМ как основное средство защиты практически не применяется.</t>
           </r>
         </is>
       </c>
@@ -16156,11 +16504,7 @@
 3. Автозапуск службы не проверяется после переустановки ОС на АРМ.</t>
         </is>
       </c>
-      <c r="H226" s="26" t="inlineStr">
-        <is>
-          <t>В разделе "пояснения" написано "не выявлены" и "Уровень защиты информации 3-Т, 2-Т, 1-Т."</t>
-        </is>
-      </c>
+      <c r="H226" s="168" t="n"/>
     </row>
     <row r="227" ht="31.5" customHeight="1">
       <c r="A227" s="20" t="inlineStr">
@@ -16178,10 +16522,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D227" s="21" t="n"/>
-      <c r="E227" s="53" t="n"/>
-      <c r="F227" s="53" t="n"/>
-      <c r="G227" s="53" t="n"/>
+      <c r="D227" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует применения средств защиты от вредоносного кода, которые сами реализуют функцию контроля целостности собственных программных компонентов.
+Главная цель меры — противодействовать атакам, направленным непосредственно на само средство защиты: вредоносный код нередко в первую очередь пытается отключить, модифицировать или подменить компоненты антивирусного агента, чтобы затем действовать незамеченным, и без самоконтроля целостности такая модификация останется невыявленной.</t>
+        </is>
+      </c>
+      <c r="E227" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается выбором средства защиты от вредоносного кода, декларирующего и фактически реализующего встроенный механизм самозащиты (self-protection), включающий контроль целостности собственных исполняемых файлов, драйверов и параметров конфигурации, с автоматическим восстановлением или блокировкой запуска при выявлении несанкционированного изменения.
+Класс используемых средств — средства защиты от вредоносного кода со встроенным модулем самозащиты (self-protection, tamper protection).
+Иностранные: ESET Endpoint Antivirus (модуль самозащиты), Bitdefender GravityZone и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль самозащиты AVP Self-Defense), Dr.Web Enterprise Security Suite (SelfPROtect) и др.
+Открытый код: реализация встроенной самозащиты в открытых решениях (ClamAV) практически отсутствует.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F227" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Техническая документация (руководство администратора) средства защиты от вредоносного кода, подтверждающая наличие модуля самозащиты.
+2. Конфигурация модуля самозащиты на образце АРМ/сервера.
+3. Результат попытки несанкционированного изменения компонента средства защиты в контролируемых условиях с фиксацией реакции (при проведении такой проверки).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G227" s="157" t="inlineStr">
+        <is>
+          <t>1. Средство защиты от вредоносного кода не декларирует и не реализует функцию самоконтроля целостности собственных компонентов;
+2. Модуль самозащиты присутствует в составе продукта, но фактически отключён в конфигурации по умолчанию;
+3. Самозащита распространяется только на исполняемые файлы, но не на параметры конфигурации и сигнатурные базы, которые можно подменить без обнаружения;
+4. Реакция на выявленное нарушение целостности ограничивается локальным событием без передачи оповещения в SIEM-систему.</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="31.5" customHeight="1">
       <c r="A228" s="20" t="inlineStr">
@@ -16199,10 +16589,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D228" s="21" t="n"/>
-      <c r="E228" s="31" t="n"/>
-      <c r="F228" s="31" t="n"/>
-      <c r="G228" s="31" t="n"/>
+      <c r="D228" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует контроля фактов отключения средств защиты от вредоносного кода и своевременности установки их обновлений на всём парке защищаемых объектов.
+Главная цель меры — не допустить длительного существования незащищённого или устаревшего узла: сам факт установки средства защиты (меры ЗВК.1—ЗВК.3) не гарантирует его непрерывной работы, а без централизованного контроля отключение или отставание в обновлениях на отдельных объектах может оставаться незамеченным продолжительное время.</t>
+        </is>
+      </c>
+      <c r="E228" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается централизованным мониторингом консоли управления средствами защиты от вредоносного кода на предмет статуса каждого объекта защиты (включён/отключён, актуальность версии и сигнатурной базы), с автоматическим оповещением ответственных лиц при выявлении отклонения и передачей соответствующих событий в SIEM-систему.
+Класс используемых средств — консоли централизованного управления средствами защиты от вредоносного кода (Security Management Console) с функцией мониторинга статуса.
+Иностранные: ESET PROTECT, Bitdefender GravityZone Console и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, Dr.Web Enterprise Security Suite (централизованная консоль) и др.
+Открытый код: Wazuh (сбор событий статуса агентов защиты) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F228" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация мониторинга статуса средств защиты от вредоносного кода в консоли централизованного управления.
+2. Отчёт об отключениях и об отставании в обновлениях по парку объектов защиты за проверяемый период.
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G228" s="151" t="inlineStr">
+        <is>
+          <t>1. Мониторинг статуса средств защиты охватывает только часть парка объектов, объекты, длительное время не подключающиеся к сети, выпадают из контроля;
+2. Оповещение об отключении средства защиты формируется, но не имеет установленного срока реагирования, из-за чего простаивает без действий продолжительное время;
+3. Отставание в обновлениях сигнатурных баз не рассматривается как повод для оповещения, отслеживается только полное отключение средства защиты;
+4. События об отключении и отставании в обновлениях не передаются в SIEM-систему, доступны только в локальной консоли управления.</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="31.5" customHeight="1">
       <c r="A229" s="20" t="inlineStr">
@@ -16220,10 +16656,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D229" s="21" t="n"/>
-      <c r="E229" s="31" t="n"/>
-      <c r="F229" s="31" t="n"/>
-      <c r="G229" s="31" t="n"/>
+      <c r="D229" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует выполнения не реже одного раза в неделю полной проверки объектов защиты (АРМ, серверов) на отсутствие вредоносного кода, дополняющей постоянное резидентное сканирование (меры ЗВК.1, ЗВК.9).
+Главная цель меры — выявить вредоносный код, который мог остаться необнаруженным резидентным (фоновым) сканированием — например, файлы, к которым не было обращения с момента заражения, либо код, чья сигнатура добавлена в базу уже после первичного заражения объекта; регулярная полная проверка ретроспективно перепроверяет весь массив данных по актуальным на текущий момент сигнатурам.</t>
+        </is>
+      </c>
+      <c r="E229" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой средства защиты от вредоносного кода на автоматическое выполнение полной проверки файловой системы объекта защиты по расписанию с периодичностью не реже одного раза в неделю, с централизованным контролем фактического выполнения таких проверок по всему парку объектов и оповещением при пропуске планового цикла.
+Класс используемых средств — встроенный планировщик полных проверок в составе средства защиты от вредоносного кода, консоль централизованного управления с контролем выполнения задач сканирования.
+Иностранные: ESET PROTECT (планировщик задач сканирования), Bitdefender GravityZone и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center (задачи полной проверки по расписанию), Dr.Web Enterprise Security Suite и др.
+Открытый код: cron-задание для запуска clamscan по расписанию и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F229" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация задачи еженедельной полной проверки в средстве защиты от вредоносного кода.
+2. Отчёт о фактическом выполнении еженедельных проверок по парку объектов защиты за проверяемый период.
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G229" s="151" t="inlineStr">
+        <is>
+          <t>1. Расписание полной проверки настроено реже, чем раз в неделю, либо смещается администраторами без формального обоснования при жалобах на снижение производительности;
+2. Полная проверка не завершается за отведённое время на объектах с большим объёмом данных, что фактически означает неполный охват файловой системы;
+3. Централизованный контроль фактического выполнения еженедельных проверок не ведётся, пропуски выявляются только по факту инцидента;
+4. Проверка не распространяется на объекты, выключенные или находящиеся в спящем режиме в плановое время её выполнения, без последующего донаверстывания.</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="94.5" customHeight="1">
       <c r="A230" s="20" t="inlineStr">
@@ -16243,10 +16725,56 @@
           <t>Т-Н-Н</t>
         </is>
       </c>
-      <c r="D230" s="21" t="n"/>
-      <c r="E230" s="31" t="n"/>
-      <c r="F230" s="31" t="n"/>
-      <c r="G230" s="31" t="n"/>
+      <c r="D230" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует применения средств защиты от вредоносного кода различных производителей как минимум для двух уровней — физических АРМ пользователей и эксплуатационного персонала и серверного оборудования, то есть исключения ситуации, когда оба уровня защищены продуктом одного и того же вендора.
+Главная цель меры — снизить риск одновременного обхода защиты на всех объектах инфраструктуры за счёт уязвимости или технологии обхода, специфичной для конкретного производителя: применение решений разных производителей на разных уровнях защиты создаёт «эшелонированную» гетерогенность, при которой пробел в детектировании одного продукта с высокой вероятностью компенсируется другим.</t>
+        </is>
+      </c>
+      <c r="E230" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается выбором и внедрением для уровня АРМ и уровня серверного оборудования средств защиты от вредоносного кода различных производителей (с различными сигнатурными базами и детектирующими движками), при этом оба решения централизованно администрируются и их совместное функционирование (в первую очередь на терминальных серверах и серверах, взаимодействующих с АРМ) заранее проверяется на отсутствие конфликтов.
+Класс используемых средств — средства защиты от вредоносного кода (антивирусы) двух и более независимых производителей для разных уровней защиты.
+Иностранные: сочетание, например, ESET (уровень АРМ) и Bitdefender (уровень серверов) и пр.
+Российские сертифицированные (ФСТЭК): сочетание, например, Kaspersky Endpoint Security для бизнеса (уровень АРМ) и Dr.Web Enterprise Security Suite (уровень серверов) и др.
+Открытый код: сочетание коммерческого решения на одном уровне с ClamAV на другом (как правило, на серверах с ОС Linux) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F230" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень производителей средств защиты от вредоносного кода, применяемых по уровням защиты (АРМ / серверное оборудование).
+2. Конфигурация обоих средств защиты, подтверждающая различие производителей.
+3. Результат проверки совместимости (отсутствия конфликтов) применяемых решений на объектах совместного взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G230" s="151" t="inlineStr">
+        <is>
+          <t>1. На уровне АРМ и уровне серверов фактически используется продукт одного и того же производителя, требование мультивендорности не выполняется;
+2. Второй производитель применяется формально на ограниченном числе объектов, недостаточном для реального снижения риска;
+3. Совместимость решений двух производителей не проверялась, что создаёт риск конфликтов при их одновременном функционировании на смежных объектах;
+4. Выбор второго производителя не пересматривается при смене основного вендора, из-за чего оба решения со временем оказываются связаны общими партнёрскими технологиями детектирования.</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="94.5" customHeight="1">
       <c r="A231" s="20" t="inlineStr">
@@ -16267,10 +16795,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D231" s="50" t="n"/>
-      <c r="E231" s="31" t="n"/>
-      <c r="F231" s="51" t="n"/>
-      <c r="G231" s="51" t="n"/>
+      <c r="D231" s="155" t="inlineStr">
+        <is>
+          <t>Мера аналогична ЗВК.13, но расширяет требование мультивендорности с двух до трёх уровней защиты — физических АРМ, серверного оборудования и контроля межсетевого трафика (мера ЗВК.4).
+Главная цель меры — распространить гетерогенность средств защиты и на сетевой уровень: без учёта уровня контроля межсетевого трафика вредоносный код, обходящий детектирование конкретного производителя, мог бы беспрепятственно проходить сетевой периметр тем же продуктом, что установлен на конечных точках, если бы производитель совпадал.</t>
+        </is>
+      </c>
+      <c r="E231" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается дополнением мультивендорной схемы, применяемой для уровней АРМ и серверов (мера ЗВК.13), третьим независимым производителем на уровне контроля межсетевого трафика (модуль антивирусной проверки в составе NGFW/IPS), с проверкой отсутствия конфликтов совместного функционирования всех трёх применяемых решений.
+Класс используемых средств — средства защиты от вредоносного кода трёх и более независимых производителей для уровней АРМ, серверов и контроля межсетевого трафика.
+Иностранные: сочетание производителей уровня конечных точек (ESET, Bitdefender) с модулем антивирусной проверки Palo Alto Networks/Fortinet на сетевом уровне и пр.
+Российские сертифицированные (ФСТЭК): сочетание Kaspersky Endpoint Security для бизнеса и Dr.Web Enterprise Security Suite на уровне АРМ/серверов с модулем антивирусной проверки «Континент» на сетевом уровне и др.
+Открытый код: дополнение мультивендорной схемы модулем Suricata на сетевом уровне и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F231" s="145" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень производителей средств защиты от вредоносного кода по трём уровням (АРМ / серверное оборудование / контроль межсетевого трафика).
+2. Конфигурация всех трёх средств защиты, подтверждающая различие производителей.
+3. Результат проверки совместимости применяемых решений на объектах совместного взаимодействия.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G231" s="145" t="inlineStr">
+        <is>
+          <t>1. Третий (сетевой) уровень мультивендорной схемы формально присутствует, но модуль антивирусной проверки трафика на нём фактически отключён или не обновляется;
+2. Производитель на сетевом уровне совпадает с одним из производителей, применяемых на уровне АРМ или серверов;
+3. Мультивендорность обеспечена на момент внедрения, но не пересматривается при смене или поглощении одного из производителей другим;
+4. Совместимость всех трёх решений при их одновременном функционировании не проверялась.</t>
+        </is>
+      </c>
       <c r="H231" s="10" t="n"/>
     </row>
     <row r="232" ht="63" customHeight="1">
@@ -16289,10 +16863,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D232" s="21" t="n"/>
-      <c r="E232" s="31" t="n"/>
-      <c r="F232" s="31" t="n"/>
-      <c r="G232" s="31" t="n"/>
+      <c r="D232" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует выполнения проверок на отсутствие вредоносного кода путём анализа информационных потоков, передаваемых между сегментами контуров безопасности и иными внутренними вычислительными сетями финансовой организации.
+Главная цель меры — контролировать внутреннее перемещение вредоносного кода между сегментами сети с разным уровнем критичности: заражение, проникшее в менее критичный сегмент, способно распространиться во внутренний контур безопасности через легитимные информационные потоки между сегментами, если эти потоки не проверяются отдельно от периметрового контроля (мера ЗВК.4).</t>
+        </is>
+      </c>
+      <c r="E232" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается размещением средства антивирусной проверки трафика на границе сегментов контуров безопасности (мера СМЭ.1 в части сегментирования) с иными внутренними вычислительными сетями организации, выполняющего анализ информационных потоков, пересекающих эту границу, независимо от периметровой защиты.
+Класс используемых средств — модуль антивирусной проверки сетевого трафика в составе межсетевого экрана нового поколения (NGFW) или системы предотвращения вторжений (IPS), размещаемый на внутренних границах сегментов.
+Иностранные: Palo Alto Networks (Threat Prevention), Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): «Континент» (модуль антивирусной проверки), UserGate и др.
+Открытый код: Suricata (сигнатурный анализ трафика на внутренних границах сегментов) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F232" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Схема расположения точек антивирусного контроля на границах сегментов контуров безопасности.
+2. Конфигурация модуля антивирусной проверки трафика на границе сегмента.
+3. Журнал (отчёт) о выявленных фактах передачи вредоносного кода между сегментами за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G232" s="151" t="inlineStr">
+        <is>
+          <t>1. Антивирусная проверка внутренних информационных потоков реализована не на всех границах сегментов контуров безопасности, а только на отдельных, признанных критичными;
+2. Зашифрованный внутренний трафик между сегментами не подвергается расшифровке для проверки;
+3. Правила и сигнатурные базы средства проверки внутреннего трафика обновляются реже, чем на периметровом уровне (мера ЗВК.4);
+4. Выявленные факты передачи вредоносного кода между сегментами не расследуются на предмет источника заражения в сегменте-отправителе.</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="47.25" customHeight="1">
       <c r="A233" s="20" t="inlineStr">
@@ -16310,10 +16930,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D233" s="21" t="n"/>
-      <c r="E233" s="31" t="n"/>
-      <c r="F233" s="31" t="n"/>
-      <c r="G233" s="31" t="n"/>
+      <c r="D233" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична ЗВК.15, но требует выполнения проверок на отсутствие вредоносного кода путём анализа информационных потоков между внутренними вычислительными сетями финансовой организации и сетью Интернет.
+Главная цель меры — обеспечить дополнительный, не зависящий от конечных точек и почтового шлюза (меры ЗВК.1, ЗВК.5) контроль всего массива интернет-трафика на границе с внешней сетью, включая протоколы и каналы (веб-трафик, файлообменные и облачные сервисы), не покрываемые специализированной почтовой защитой.</t>
+        </is>
+      </c>
+      <c r="E233" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается размещением на границе внутренних вычислительных сетей организации с сетью Интернет средства антивирусной проверки трафика (модуль в составе NGFW/прокси-сервера), выполняющего анализ передаваемых по всем протоколам объектов (веб-трафик, файловый обмен) с расшифровкой TLS-сессий в объёме, установленном внутренними регламентами.
+Класс используемых средств — модуль антивирусной проверки веб- и интернет-трафика в составе межсетевого экрана нового поколения (NGFW) или прокси-сервера (Secure Web Gateway).
+Иностранные: Zscaler Internet Access, Palo Alto Networks (URL Filtering + Threat Prevention) и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate (модуль веб-безопасности) и др.
+Открытый код: Squid (прокси-сервер) в связке с ClamAV (модуль антивирусной проверки, например c-icap) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F233" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства антивирусной проверки трафика на границе с сетью Интернет.
+2. Регламент расшифровки TLS-трафика для антивирусной проверки.
+3. Журнал (отчёт) о выявленных и заблокированных фактах передачи вредоносного кода из сети Интернет за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G233" s="151" t="inlineStr">
+        <is>
+          <t>1. Проверке подвергается только веб-трафик по протоколу HTTP, тогда как значимая часть трафика проходит по HTTPS без расшифровки и остаётся непроверенной;
+2. Отдельные категории интернет-ресурсов (например, облачные хранилища, используемые для бизнес-задач) исключены из проверки без анализа связанного с этим риска;
+3. Контроль информационных потоков с сетью Интернет не охватывает нестандартные порты и протоколы, используемые отдельными приложениями;
+4. Выявленные факты передачи вредоносного кода из сети Интернет не сопоставляются с внутренним узлом-инициатором обращения для дальнейшего реагирования.</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="63" customHeight="1">
       <c r="A234" s="20" t="inlineStr">
@@ -16331,10 +16997,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D234" s="21" t="n"/>
-      <c r="E234" s="31" t="n"/>
-      <c r="F234" s="31" t="n"/>
-      <c r="G234" s="31" t="n"/>
+      <c r="D234" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует выполнения проверок на отсутствие вредоносного кода путём анализа информационных потоков между сегментами, предназначенными для размещения общедоступных объектов доступа (в том числе банкоматов, платёжных терминалов), и сетью Интернет.
+Главная цель меры — обеспечить сетевой контроль трафика именно для сегмента повышенного риска (мера ЗВК.7): общедоступные объекты доступа физически доступны неограниченному кругу лиц, а их взаимодействие с сетью Интернет (обновления, передача транзакционных данных) представляет отдельный канал, который должен контролироваться независимо от встроенной в сами устройства защиты.</t>
+        </is>
+      </c>
+      <c r="E234" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается размещением на границе сегмента, предназначенного для общедоступных объектов доступа, с сетью Интернет отдельного средства антивирусной проверки трафика, учитывающего специфику протоколов взаимодействия банкоматов и терминалов (в частности, ограниченный и заранее известный перечень адресов и протоколов, к которым устройства обращаются легитимно).
+Класс используемых средств — модуль антивирусной проверки сетевого трафика в составе межсетевого экрана нового поколения (NGFW), размещаемого на границе сегмента общедоступных объектов доступа.
+Иностранные: Palo Alto Networks (Threat Prevention), Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: Suricata с профилем правил, ограниченным легитимным перечнем адресов и протоколов банкоматной (терминальной) сети.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F234" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Схема расположения точки контроля на границе сегмента общедоступных объектов доступа с сетью Интернет.
+2. Конфигурация средства антивирусной проверки трафика данного сегмента.
+3. Журнал (отчёт) о выявленных фактах передачи вредоносного кода за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G234" s="151" t="inlineStr">
+        <is>
+          <t>1. Сегмент общедоступных объектов доступа не выделен отдельно, антивирусная проверка его трафика с сетью Интернет ведётся в общем потоке без отдельного контроля;
+2. Перечень легитимных адресов и протоколов, к которым обращаются банкоматы (терминалы), не формализован, что не позволяет выявлять аномальные обращения как признак компрометации;
+3. Обновление правил и сигнатурных баз средства проверки данного сегмента не синхронизировано с обновлением прикладного ПО самих устройств;
+4. Выявленные факты передачи вредоносного кода в данном сегменте не эскалируются с повышенным приоритетом, обрабатываются наравне с прочим трафиком.</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="110.25" customHeight="1">
       <c r="A235" s="20" t="inlineStr">
@@ -16352,14 +17064,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D235" s="34" t="inlineStr">
-        <is>
-          <t>Любое устройство и съёмный носитель (флеш-накопитель, внешний диск, ноутбук сотрудника или подрядчика) должны быть проверены на отсутствие вредоносного кода до того, как получат доступ к вычислительной сети организации, что поможет избежать заноса вредоносного кода через заражённый USB-носитель в обход периметровой защиты и избежать подключение неучтённого устройства.</t>
-        </is>
-      </c>
-      <c r="E235" s="31" t="n"/>
-      <c r="F235" s="31" t="n"/>
-      <c r="G235" s="31" t="n"/>
+      <c r="D235" s="144" t="inlineStr">
+        <is>
+          <t>Любое устройство и съёмный носитель информации (флеш-накопитель, внешний диск, мобильный компьютер сотрудника или подрядчика) должны быть проверены на отсутствие вредоносного кода до того, как получат доступ к вычислительной сети организации.
+Главная цель меры — избежать заноса вредоносного кода через заражённый носитель в обход периметровой и почтовой защиты (меры ЗВК.4, ЗВК.5), а также исключить подключение неучтённого устройства, состав и происхождение которого организации неизвестны.</t>
+        </is>
+      </c>
+      <c r="E235" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается организацией выделенного узла (станции) входного контроля, на котором каждое устройство и съёмный носитель проверяются средством защиты от вредоносного кода перед первым подключением к рабочей сети, в сочетании с техническим ограничением возможности подключения непроверенных устройств непосредственно к рабочим АРМ и серверам (контроль портов ввода-вывода).
+Класс используемых средств — выделенные станции (киоски) входного контроля на базе средства защиты от вредоносного кода, средства контроля подключаемых устройств (Device Control).
+Иностранные: DeviceLock DLP (модуль Device Control) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль Device Control), Secret Net Studio (контроль устройств) и др.
+Открытый код: ClamAV на выделенной станции контроля в сочетании со штатной блокировкой USB-портов ОС.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F235" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) входного контроля устройств и переносных носителей информации.
+2. Конфигурация выделенной станции (киоска) входного контроля и средства ограничения подключения непроверенных устройств.
+3. Журнал проверок устройств и носителей за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G235" s="151" t="inlineStr">
+        <is>
+          <t>1. Входной контроль не распространяется на мобильные компьютеры (ноутбуки) сотрудников и подрядчиков, ограничиваясь только флеш-накопителями;
+2. Техническое ограничение подключения непроверенных устройств к рабочим АРМ отсутствует, входной контроль носит рекомендательный характер;
+3. Устройства и носители организации, уже прошедшие проверку, повторно не досматриваются после использования вне контролируемой инфраструктуры;
+4. Станция входного контроля физически не изолирована от рабочей сети, что создаёт риск заражения самой станции.</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="110.25" customHeight="1">
       <c r="A236" s="20" t="inlineStr">
@@ -16377,10 +17131,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D236" s="21" t="n"/>
-      <c r="E236" s="31" t="n"/>
-      <c r="F236" s="31" t="n"/>
-      <c r="G236" s="31" t="n"/>
+      <c r="D236" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает усиленный вариант входного контроля (мера ЗВК.18) для устройств и переносных носителей информации: проверка выполняется в выделенном сегменте вычислительной сети, из которого исключена возможность информационного взаимодействия с иными сегментами сети организации, кроме управляющего взаимодействия по установленным правилам и протоколам.
+Главная цель меры — гарантированно исключить прямой сетевой доступ проверяемого (потенциально заражённого) устройства к рабочей инфраструктуре организации на весь период проверки: в отличие от меры ЗВК.18, где риск ограничивается физическим подключением к станции контроля, здесь дополнительно устраняется риск сетевого распространения через саму станцию входного контроля, если бы она имела прямой доступ к другим сегментам.</t>
+        </is>
+      </c>
+      <c r="E236" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается выделением для входного контроля устройств и носителей отдельного сегмента вычислительной сети, изолированного от иных сегментов организации на сетевом уровне (мера СМЭ.1) с исключением любого информационного взаимодействия, кроме строго определённого управляющего трафика (передача результатов проверки, обновление сигнатурных баз станции контроля), реализуемого по установленным правилам и протоколам через контролируемый шлюз.
+Класс используемых средств — средства сегментации сети (межсетевые экраны, VLAN) в сочетании со средством защиты от вредоносного кода на станции входного контроля, размещённой в выделенном сегменте.
+Иностранные: Cisco (сегментация на базе VLAN/ACL) в сочетании с DeviceLock DLP и пр.
+Российские сертифицированные (ФСТЭК): «Континент» (сегментация) в сочетании с Kaspersky Endpoint Security для бизнеса и др.
+Открытый код: iptables/nftables (сегментация) в сочетании с ClamAV на станции контроля.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F236" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Схема сегментации сети, подтверждающая изоляцию выделенного сегмента входного контроля.
+2. Конфигурация правил межсетевого взаимодействия, ограничивающих трафик выделенного сегмента только управляющим информационным взаимодействием.
+3. Итоги интервью с ответственным за администрирование сети и станции входного контроля.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G236" s="151" t="inlineStr">
+        <is>
+          <t>1. Выделенный сегмент входного контроля фактически имеет более широкий доступ к иным сегментам сети, чем предусмотрено для управляющего взаимодействия;
+2. Правила межсетевого взаимодействия выделенного сегмента не пересматривались с момента внедрения и не приведены в соответствие с изменившейся топологией сети;
+3. Изоляция сегмента реализована логически (VLAN) без дополнительного контроля межсетевым экраном, что не исключает риск неавторизованного перенастройки сетевого оборудования;
+4. Управляющее информационное взаимодействие выделенного сегмента не регистрируется как событие защиты информации.</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="47.25" customHeight="1">
       <c r="A237" s="20" t="inlineStr">
@@ -16398,10 +17198,56 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D237" s="21" t="n"/>
-      <c r="E237" s="31" t="n"/>
-      <c r="F237" s="31" t="n"/>
-      <c r="G237" s="31" t="n"/>
+      <c r="D237" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует выполнения предварительных проверок на отсутствие вредоносного кода устанавливаемого или изменяемого программного обеспечения (ПО) до его установки или изменения, а также повторных проверок после установки и (или) изменения ПО.
+Главная цель меры — контролировать канал заражения через сам процесс установки и обновления ПО (меры ЦЗИ.12, ЦЗИ.13): проверка только уже установленного и работающего ПО (резидентная защита, мера ЗВК.1) не позволяет выявить вредоносный код, внедрённый непосредственно в дистрибутив или в процесс его установки, а повторная проверка после установки дополнительно подтверждает, что сам процесс установки не привнёс постороннего кода.</t>
+        </is>
+      </c>
+      <c r="E237" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется организационными методами и предполагает:
+1. Регламентацию обязательного этапа проверки на отсутствие вредоносного кода дистрибутива устанавливаемого или изменяемого ПО до начала его установки, как неотъемлемой части регламента управления обновлениями (мера ЦЗИ.12);
+2. Регламентацию обязательного этапа повторной проверки объекта установки (сервера, АРМ) на отсутствие вредоносного кода непосредственно после завершения установки или изменения ПО;
+3. Определение порядка действий при выявлении вредоносного кода на любом из этапов проверки, включая отмену установки и информирование ответственных за ИБ.
+На практике данная организационная мера, как правило, опирается на уже развёрнутые средства защиты от вредоносного кода (меры ЗВК.1, ЗВК.3, ЗВК.12) без отдельного специализированного средства — их применение регламентируется как обязательный этап процесса установки и обновления ПО.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F237" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент управления обновлениями с указанием обязательных этапов предварительной и последующей проверки на отсутствие вредоносного кода;
+2. Акты (свидетельства) выполнения предварительной и последующей проверки по конкретным случаям установки/изменения ПО за проверяемый период;
+3. Свидетельства действий при выявлении вредоносного кода на этапе проверки (при наличии таких случаев).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G237" s="151" t="inlineStr">
+        <is>
+          <t>1. Предварительная проверка дистрибутива на отсутствие вредоносного кода выполняется не для всех категорий ПО, а выборочно, для наиболее критичных систем;
+2. Повторная проверка после установки/изменения ПО не выполняется как самостоятельный этап, ограничиваются только предварительной проверкой дистрибутива;
+3. Результаты выполненных проверок документально не фиксируются, что не позволяет подтвердить факт их проведения при аудите;
+4. Требование о проверке не распространяется на изменения, вносимые в экстренном (внеплановом) порядке при устранении инцидента.</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="31.5" customHeight="1">
       <c r="A238" s="20" t="inlineStr">
@@ -16419,10 +17265,84 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D238" s="21" t="n"/>
-      <c r="E238" s="31" t="n"/>
-      <c r="F238" s="31" t="n"/>
-      <c r="G238" s="31" t="n"/>
+      <c r="D238" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует запрета неконтролируемого открытия самораспаковывающихся архивов и исполняемых файлов, полученных из сети Интернет.
+Главная цель меры — противодействовать распространённой технике социальной инженерии, при которой вредоносный код маскируется под самораспаковывающийся архив или обычный исполняемый файл (в том числе с двойным расширением), а пользователь запускает его самостоятельно, минуя тем самым необходимость эксплуатации уязвимости: без контроля такого запуска техническая защита на уровне трафика и резидентного сканирования (меры ЗВК.4, ЗВК.1) может быть обойдена самим пользователем, действующим по указанию злоумышленника.</t>
+        </is>
+      </c>
+      <c r="E238" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Закрепление во внутреннем нормативном документе прямого запрета на самостоятельное открытие пользователем самораспаковывающихся архивов и исполняемых файлов, полученных из внешних источников (сеть Интернет, вложения электронной почты), без предварительной проверки;
+2. Регламентацию порядка обращения пользователя к ответственным за ИБ при необходимости открытия такого файла в рамках рабочей задачи;
+3. Проведение регулярного обучения пользователей распознаванию признаков вредоносных вложений, замаскированных под самораспаковывающиеся архивы и исполняемые файлы (мера ОРД в части повышения осведомлённости).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Технический контроль дополняется применением на АРМ технологии контроля запуска приложений (мера ЦЗИ.21) и правил почтового/веб-шлюза (меры ЗВК.4, ЗВК.5), блокирующих автоматический запуск и (или) открытие самораспаковывающихся архивов и исполняемых файлов, полученных из сети Интернет, без явного разрешения со стороны средства защиты.
+Класс используемых средств — средства контроля запуска приложений (application control) на АРМ, правила фильтрации содержимого на почтовом/веб-шлюзе.
+Иностранные: Microsoft AppLocker (правила блокировки запуска по типу источника), Proofpoint Email Protection (блокировка вложений-исполняемых файлов) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (контроль запуска приложений), «Континент» (модуль почтовой безопасности) и др.
+Открытый код: правила фильтрации по расширению файла на почтовом шлюзе (например, в связке Postfix/MIMEDefang) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F238" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, содержащий запрет на неконтролируемое открытие самораспаковывающихся архивов и исполняемых файлов из сети Интернет;
+2. Свидетельства проведения обучения пользователей распознаванию признаков вредоносных вложений.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация правил блокировки запуска/открытия таких файлов на образце АРМ и на почтовом/веб-шлюзе.
+2. Журнал (отчёт) о заблокированных попытках открытия самораспаковывающихся архивов и исполняемых файлов за проверяемый период.
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G238" s="151" t="inlineStr">
+        <is>
+          <t>1. Запрет закреплён во внутреннем нормативном документе, но технический контроль его соблюдения отсутствует, полагаются только на осведомлённость пользователя;
+2. Правила блокировки распространяются на почтовые вложения, но не охватывают файлы, загруженные напрямую из сети Интернет (веб-трафик, файлообменные сервисы);
+3. Пользователи с повышенными правами (локальный администратор АРМ) могут обходить установленные технические ограничения;
+4. Обучение пользователей распознаванию признаков вредоносных вложений проводится нерегулярно, без контроля усвоения материала.</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="13" t="inlineStr">
@@ -16453,10 +17373,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D240" s="21" t="n"/>
-      <c r="E240" s="31" t="n"/>
-      <c r="F240" s="31" t="n"/>
-      <c r="G240" s="31" t="n"/>
+      <c r="D240" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой выполненной операции по проведению проверки на отсутствие вредоносного кода — как резидентного сканирования (мера ЗВК.1), так и еженедельных полных проверок (мера ЗВК.12) и проверок при установке/изменении ПО (мера ЗВК.20).
+Главная цель меры — обеспечить возможность подтвердить сам факт и охват выполненных проверок за конкретный период, а не полагаться на предположение, что раз средство защиты установлено, то проверки выполняются в соответствии с регламентом: без регистрации результатов невозможно отличить регулярно проверяемый объект от объекта, на котором проверки фактически не выполнялись.</t>
+        </is>
+      </c>
+      <c r="E240" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства защиты от вредоносного кода на автоматическое формирование события по завершении каждой проверки (резидентной, полной по расписанию, при установке/изменении ПО), с фиксацией типа проверки, охвата и результата, и последующей передачей событий в SIEM-систему для централизованного хранения и анализа.
+Класс используемых средств — встроенный механизм журналирования средства защиты от вредоносного кода, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: ESET PROTECT (журнал выполненных задач сканирования), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор событий clamscan/clamd) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F240" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования операций проверки на отсутствие вредоносного кода в средстве защиты.
+2. Выгрузка зарегистрированных событий проверок за проверяемый период с сопоставлением по типам (резидентная/полная/при установке ПО).
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G240" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только результаты полных проверок по расписанию, резидентное сканирование не формирует отдельных событий за каждый цикл;
+2. События проверок не передаются в SIEM-систему, доступны только в локальной консоли управления средством защиты;
+3. Событие не содержит сведений об охвате проверки (объём проверенных файлов), что не позволяет подтвердить её полноту;
+4. Пропуски плановых проверок (например, на выключенных в плановое время объектах) не регистрируются как отдельное событие.</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="20" t="inlineStr">
@@ -16474,10 +17440,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D241" s="21" t="n"/>
-      <c r="E241" s="31" t="n"/>
-      <c r="F241" s="31" t="n"/>
-      <c r="G241" s="31" t="n"/>
+      <c r="D241" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта выявления вредоносного кода на любом из уровней эшелонированной защиты (меры ЗВК.1—ЗВК.7).
+Главная цель меры — обеспечить полную и достоверную историю фактов заражения для последующего анализа: без регистрации каждого отдельного факта как события защиты информации невозможно оценить реальную интенсивность попыток заражения инфраструктуры, выявить целенаправленную атаку по совокупности отдельных фактов и подтвердить своевременность реагирования на каждый из них.</t>
+        </is>
+      </c>
+      <c r="E241" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой всех развёрнутых средств защиты от вредоносного кода на всех уровнях (АРМ, серверы, сетевой и почтовый трафик) на автоматическое формирование события при каждом факте выявления вредоносного кода, с фиксацией идентификатора обнаруженного объекта, затронутого актива, времени и предпринятого действия (блокировка, карантин, удаление), и передачей событий в SIEM-систему для централизованной корреляции.
+Класс используемых средств — встроенный механизм журналирования средств защиты от вредоносного кода на всех уровнях защиты, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: ESET PROTECT, Palo Alto Networks (журнал Threat Prevention), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, «Континент», MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh, Suricata (события выявления вредоносного кода в трафике) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F241" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования фактов выявления вредоносного кода на всех уровнях защиты.
+2. Выгрузка зарегистрированных фактов выявления вредоносного кода за проверяемый период, сведённая по всем уровням.
+3. Итоги интервью с ответственным за мониторинг ИБ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G241" s="151" t="inlineStr">
+        <is>
+          <t>1. События выявления вредоносного кода собираются не со всех уровней защиты, отдельные уровни (например, банкоматы и терминалы) не подключены к централизованному сбору событий;
+2. Событие не содержит сведений о предпринятом действии (успешно ли заблокирован вредоносный код), что не позволяет оценить фактический результат реагирования;
+3. Повторяющиеся факты выявления одного и того же вредоносного объекта на одном узле не агрегируются, что затрудняет выявление хронического заражения;
+4. Факты выявления вредоносного кода не сопоставляются между уровнями защиты для выявления единой цепочки атаки.</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="31.5" customHeight="1">
       <c r="A242" s="20" t="inlineStr">
@@ -16495,10 +17507,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D242" s="21" t="n"/>
-      <c r="E242" s="31" t="n"/>
-      <c r="F242" s="31" t="n"/>
-      <c r="G242" s="31" t="n"/>
+      <c r="D242" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта неконтролируемого использования технологии мобильного кода — то есть случая, когда контроль (выявление) использования такой технологии (мера ЦЗИ.26) фиксирует применение мобильного кода в обход установленных ограничений.
+Главная цель меры — обеспечить возможность ретроспективно подтвердить факты применения потенциально опасной технологии в тех случаях, когда её использование не было заранее санкционировано: без такой регистрации риск, связанный с исполнением произвольного кода на стороне получателя без явной установки, остаётся неучтённым при последующем анализе инцидентов.</t>
+        </is>
+      </c>
+      <c r="E242" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средств выявления использования технологии мобильного кода (мера ЦЗИ.26) — анализа сетевого/почтового трафика и контроля запуска интерпретаторов сценариев на АРМ и серверах — на формирование события защиты информации при каждом выявленном факте неконтролируемого (не входящего в перечень разрешённых) применения мобильного кода, с передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования средств анализа содержимого и контроля запуска сценариев (EDR/EPP-платформа), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Palo Alto Networks (WildFire), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса, PT Sandbox, MaxPatrol SIEM, KUMA и др.
+Открытый код: Sysmon (Script Block Logging PowerShell), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F242" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования фактов неконтролируемого использования технологии мобильного кода.
+2. Выгрузка зарегистрированных событий за проверяемый период.
+3. Итоги интервью с ответственным за мониторинг ИБ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G242" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация событий охватывает не все каналы использования мобильного кода (мера ЦЗИ.26), в частности не распространяется на макросы офисных документов;
+2. Разграничение между санкционированным и неконтролируемым использованием мобильного кода не формализовано, регистрируются все факты без различия;
+3. События не передаются в SIEM-систему, доступны только в локальном журнале средства выявления;
+4. Периодический анализ зарегистрированных фактов на предмет тенденций и целенаправленных атак не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="31.5" customHeight="1">
       <c r="A243" s="20" t="inlineStr">
@@ -16516,10 +17574,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D243" s="21" t="n"/>
-      <c r="E243" s="31" t="n"/>
-      <c r="F243" s="31" t="n"/>
-      <c r="G243" s="31" t="n"/>
+      <c r="D243" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого сбоя в функционировании средств защиты от вредоносного кода — то есть случаев некорректной работы, аварийного завершения процесса или иной технической неисправности средства защиты, отличных от его намеренного отключения (мера ЗВК.27).
+Главная цель меры — обеспечить видимость случаев, когда объект фактически остаётся без защиты не вследствие чьих-либо действий, а вследствие технической неисправности самого средства защиты: без регистрации таких сбоев отсутствие защиты может долгое время оставаться незамеченным, будучи неотличимым от штатной работы средства защиты в фоновом режиме.</t>
+        </is>
+      </c>
+      <c r="E243" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства защиты от вредоносного кода и (или) агента мониторинга операционной системы на автоматическое формирование события при выявлении сбоя в работе средства защиты (аварийное завершение процесса, отказ модуля сканирования, недоступность службы обновлений), с передачей событий в SIEM-систему и автоматическим оповещением ответственных лиц.
+Класс используемых средств — встроенный механизм журналирования средства защиты от вредоносного кода, средства мониторинга состояния служб операционной системы, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: ESET PROTECT (мониторинг статуса агентов), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (мониторинг статуса процессов/служб) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F243" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования сбоев в функционировании средств защиты от вредоносного кода.
+2. Выгрузка зарегистрированных фактов сбоев за проверяемый период с указанием времени восстановления работоспособности.
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G243" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация сбоев ограничивается только полным отказом службы, частичные сбои (например, недоступность модуля обновления при работающем сканере) не выявляются;
+2. Оповещение о сбое не имеет установленного срока реагирования, инцидент простаивает без действий продолжительное время;
+3. Отличие сбоя от намеренного отключения средства защиты (мера ЗВК.27) не разделяется в журнале событий, что затрудняет последующее расследование;
+4. События о сбоях не передаются в SIEM-систему, доступны только в локальной консоли управления.</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="31.5" customHeight="1">
       <c r="A244" s="20" t="inlineStr">
@@ -16537,10 +17641,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D244" s="21" t="n"/>
-      <c r="E244" s="31" t="n"/>
-      <c r="F244" s="31" t="n"/>
-      <c r="G244" s="31" t="n"/>
+      <c r="D244" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого сбоя в выполнении контроля (проверок) на отсутствие вредоносного кода — то есть случая, когда запланированная проверка (резидентная, еженедельная полная, при установке/изменении ПО) не была выполнена или была прервана до завершения.
+Главная цель меры — отличать зафиксированный факт «проверка не выполнена» от простого отсутствия события о её выполнении (мера ЗВК.22): без явной регистрации сбоя пропуск проверки, вызванный, например, отключением объекта в плановое время или технической ошибкой планировщика, останется незамеченным до следующего аудита.</t>
+        </is>
+      </c>
+      <c r="E244" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается сопоставлением планового графика проверок (мера ЗВК.12) с фактически зарегистрированными событиями их выполнения (мера ЗВК.22) и автоматическим формированием отдельного события «сбой выполнения проверки» при выявлении пропуска или незавершения плановой проверки, с передачей события в SIEM-систему.
+Класс используемых средств — консоль централизованного управления средством защиты от вредоносного кода с функцией контроля выполнения задач по расписанию, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: ESET PROTECT (отчёт о невыполненных задачах), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center (отчёт о статусе задач проверки), MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh в сочетании со скриптом сверки планового и фактического расписания cron-заданий сканирования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F244" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация контроля выполнения плановых проверок на отсутствие вредоносного кода.
+2. Выгрузка зарегистрированных сбоев выполнения проверок за проверяемый период.
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G244" s="151" t="inlineStr">
+        <is>
+          <t>1. Сопоставление планового графика проверок с фактически выполненными не автоматизировано, пропуски выявляются только вручную и нерегулярно;
+2. Сбой выполнения проверки не приводит к автоматическому оповещению ответственных лиц, фиксируется только в отчёте, просматриваемом периодически;
+3. Прерванная (незавершённая) проверка засчитывается как выполненная, если она была начата, без контроля фактического завершения;
+4. Регистрация сбоев не охватывает проверки, выполняемые при установке/изменении ПО (мера ЗВК.20), только резидентные и полные проверки по расписанию.</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="20" t="inlineStr">
@@ -16558,10 +17708,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D245" s="21" t="n"/>
-      <c r="E245" s="31" t="n"/>
-      <c r="F245" s="31" t="n"/>
-      <c r="G245" s="31" t="n"/>
+      <c r="D245" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта отключения средства защиты от вредоносного кода — как штатного (санкционированного, например, для проведения регламентных работ), так и несанкционированного.
+Главная цель меры — обеспечить возможность отличить факт намеренного (в том числе несанкционированного) отключения от технического сбоя (мера ЗВК.25) и подтвердить, что каждое отключение было санкционировано и ограничено по времени: период, в течение которого объект остаётся без защиты по чьей-либо инициативе, представляет отдельный, управляемый организацией риск, требующий отдельного контроля.</t>
+        </is>
+      </c>
+      <c r="E245" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средства защиты от вредоносного кода на автоматическое формирование события при каждом отключении (остановке службы/агента, выходе из режима резидентной защиты) с фиксацией инициатора и времени, а также события о последующем включении, с передачей обоих событий в SIEM-систему и сопоставлением с перечнем санкционированных регламентных работ.
+Класс используемых средств — встроенный механизм журналирования средства защиты от вредоносного кода, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: ESET PROTECT (события статуса агента), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security Center, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (мониторинг статуса процессов/служб) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F245" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования фактов отключения и последующего включения средств защиты от вредоносного кода.
+2. Выгрузка зарегистрированных фактов отключения за проверяемый период с сопоставлением перечню санкционированных регламентных работ.
+3. Итоги интервью с ответственным за администрирование средств защиты от вредоносного кода.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G245" s="151" t="inlineStr">
+        <is>
+          <t>1. Событие фиксирует факт отключения, но не содержит сведений об инициаторе (учётной записи), что не позволяет установить ответственного;
+2. Отключение, произведённое пользователем с правами локального администратора в обход централизованной консоли, не регистрируется;
+3. Сопоставление зарегистрированных отключений с перечнем санкционированных регламентных работ не проводится, любое отключение считается допустимым без разбора;
+4. Продолжительность нахождения объекта в отключённом состоянии не контролируется на предмет превышения установленного лимита.</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="31.5" customHeight="1">
       <c r="A246" s="20" t="inlineStr">
@@ -16579,10 +17775,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D246" s="21" t="n"/>
-      <c r="E246" s="31" t="n"/>
-      <c r="F246" s="31" t="n"/>
-      <c r="G246" s="31" t="n"/>
+      <c r="D246" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта нарушения целостности программных компонентов средств защиты от вредоносного кода, выявленного встроенным механизмом самозащиты (мера ЗВК.10).
+Главная цель меры — обеспечить возможность ретроспективно подтвердить факт и время попытки компрометации самого средства защиты: обнаружение нарушения целостности его компонентов (мера ЗВК.10) без регистрации соответствующего события фиксируется только локально и рискует остаться без внимания ответственных за ИБ лиц, тогда как именно такая попытка нередко служит индикатором целенаправленной атаки на инфраструктуру.</t>
+        </is>
+      </c>
+      <c r="E246" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой встроенного модуля самозащиты средства защиты от вредоносного кода (мера ЗВК.10) на автоматическое формирование события защиты информации при каждом выявленном нарушении целостности собственных программных компонентов, с фиксацией затронутого компонента, времени и предпринятого действия (блокировка, восстановление), и передачей события в SIEM-систему с повышенным приоритетом обработки.
+Класс используемых средств — встроенный механизм журналирования модуля самозащиты (self-protection, tamper protection) средства защиты от вредоносного кода, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: ESET Endpoint Antivirus (журнал модуля самозащиты), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (журнал AVP Self-Defense), Dr.Web Enterprise Security Suite (SelfPROtect), MaxPatrol SIEM, KUMA и др.
+Открытый код: встроенная самозащита в открытых решениях практически отсутствует, полноценная регистрация данного типа события средствами ClamAV не реализуется.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F246" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования нарушений целостности программных компонентов средств защиты от вредоносного кода.
+2. Выгрузка зарегистрированных фактов нарушения целостности за проверяемый период (при наличии).
+3. Итоги интервью с ответственным за мониторинг ИБ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G246" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация нарушений целостности компонентов средства защиты не настроена как отдельный класс событий, смешивается с общими событиями сбоев (мера ЗВК.25);
+2. Событие не передаётся с повышенным приоритетом, обрабатывается наравне с рядовыми событиями, хотя является индикатором потенциальной целенаправленной атаки;
+3. События не передаются в SIEM-систему, доступны только в локальном журнале средства защиты на конкретном объекте;
+4. Реакция на выявленное нарушение целостности ограничивается его регистрацией без последующего расследования на предмет масштаба компрометации.</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="13" t="inlineStr">

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -17876,9 +17876,50 @@
 Главная цель меры — предотвратить несанкционированную передачу конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) за пределы организации через электронную почту.</t>
         </is>
       </c>
-      <c r="E249" s="31" t="n"/>
-      <c r="F249" s="31" t="n"/>
-      <c r="G249" s="31" t="n"/>
+      <c r="E249" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на почтовом шлюзе средства защиты от утечек информации (DLP), контролирующего адрес получателя каждого исходящего письма: сообщения на адреса, не входящие в перечень разрешённых (белый список контрагентов, личные почтовые сервисы), блокируются автоматически, а для разрешённых адресов выполняется контентный анализ вложений и текста письма.
+Класс используемых средств — системы предотвращения утечек информации (Data Loss Prevention, DLP) с модулем контроля почтового канала.
+Иностранные: Forcepoint DLP, Symantec (Broadcom) DLP и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor (РТК-Солар) и др.
+Открытый код: полноценных DLP-решений данного класса в открытом коде практически не представлено, применяются частичные решения на базе правил почтового шлюза (например, Postfix с проверкой адресата по спискам).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F249" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация DLP-системы в части контроля адресов получателей исходящей почты и перечня разрешённых внешних адресов.
+2. Журнал (отчёт) о заблокированных попытках отправки конфиденциальной информации на внешние адреса за проверяемый период.
+3. Итоги интервью с ответственным за администрирование DLP-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G249" s="151" t="inlineStr">
+        <is>
+          <t>1. Перечень разрешённых внешних адресов (белый список) не актуализируется при увольнении сотрудников контрагентов или расторжении договоров;
+2. Контентный анализ для разрешённых сценариев отправки фактически не выполняется, разрешённые адреса полностью исключены из контроля;
+3. Блокировка настроена только для явных признаков конфиденциальной информации (маркировка грифом), но не срабатывает при отправке данных без формальной маркировки;
+4. Попытки блокированной отправки не эскалируются с достаточной срочностью для оперативного реагирования на возможную попытку утечки.</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="236.25" customHeight="1">
       <c r="A250" s="20" t="inlineStr">
@@ -17904,9 +17945,50 @@
 Главная цель меры — предотвратить несанкционированную передачу конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) за пределы организации через все возможные интернет-каналы.</t>
         </is>
       </c>
-      <c r="E250" s="31" t="n"/>
-      <c r="F250" s="31" t="n"/>
-      <c r="G250" s="31" t="n"/>
+      <c r="E250" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на веб-прокси (шлюзе доступа в Интернет) средства защиты от утечек информации, контролирующего передачу данных по протоколам HTTP/HTTPS, мессенджерам и облачным сервисам: неразрешённые каналы передачи (личные облачные хранилища, файлообменники, не входящие в перечень разрешённых) блокируются, а для разрешённых сервисов выполняется контентный анализ передаваемых данных с расшифровкой TLS-сессий в объёме, установленном внутренними регламентами.
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контроля веб-канала (Web DLP), интегрируемым с прокси-сервером или NGFW.
+Иностранные: Forcepoint DLP (Web), Zscaler (модуль DLP) и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor и др.
+Открытый код: Squid (прокси-сервер) в сочетании с правилами контентной фильтрации, без полноценного контентного анализа DLP-класса.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F250" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация DLP-системы в части контроля веб-канала и перечня разрешённых интернет-сервисов.
+2. Регламент расшифровки TLS-трафика для контентного анализа.
+3. Журнал (отчёт) о заблокированных попытках передачи конфиденциальной информации в сеть Интернет за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G250" s="151" t="inlineStr">
+        <is>
+          <t>1. Зашифрованный трафик (HTTPS) части разрешённых интернет-сервисов не расшифровывается для контентного анализа, что фактически выводит их из-под контроля;
+2. Перечень заблокированных каналов передачи ограничивается только явными файлообменниками, не охватывая мессенджеры и облачные сервисы синхронизации;
+3. Контентный анализ разрешённых сценариев передачи не настроен на выявление структурированных данных (номера карт, СНИЛС), ограничивается ключевыми словами;
+4. Правила блокировки не пересматриваются при появлении новых популярных интернет-сервисов, используемых сотрудниками в обход контроля.</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="220.5" customHeight="1">
       <c r="A251" s="20" t="inlineStr">
@@ -17932,9 +18014,50 @@
 Главная цель меры — предотвратить несанкционированное выведение конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) на бумажные носители.</t>
         </is>
       </c>
-      <c r="E251" s="21" t="n"/>
-      <c r="F251" s="21" t="n"/>
-      <c r="G251" s="21" t="n"/>
+      <c r="E251" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на серверах и АРМ агента контроля печати в составе DLP-системы, перехватывающего задание на печать до его передачи на принтер: печать документов, содержащих признаки конфиденциальной информации без соответствующего разрешения, блокируется, а для разрешённых сценариев выполняется контентный анализ документа и протоколирование факта печати (см. также меру ПУИ.30 в части регистрации).
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контроля печати (Print Control).
+Иностранные: Forcepoint DLP (Discovery/Print), Symantec (Broadcom) DLP и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor и др.
+Открытый код: полноценных DLP-модулей контроля печати в открытом коде практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F251" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля контроля печати DLP-системы на образце АРМ.
+2. Журнал (отчёт) о заблокированных попытках печати конфиденциальной информации за проверяемый период.
+3. Итоги интервью с ответственным за администрирование DLP-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G251" s="144" t="inlineStr">
+        <is>
+          <t>1. Контроль печати развёрнут не на всех АРМ, часть рабочих станций исключена из-под контроля;
+2. Контентный анализ печатаемых документов ограничивается форматом .docx/.pdf, документы иных форматов пропускаются без проверки;
+3. Печать через сетевые принтеры без предустановленного драйвера с агентом контроля обходит установленную блокировку;
+4. Разрешённые сценарии печати (например, для конкретного подразделения) не пересматриваются при изменении должностных обязанностей сотрудников.</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="236.25" customHeight="1">
       <c r="A252" s="20" t="inlineStr">
@@ -17960,9 +18083,50 @@
 Главная цель меры — предотвратить несанкционированное копирование конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) на внешние носители, которые могут быть вынесены за пределы организации.</t>
         </is>
       </c>
-      <c r="E252" s="21" t="n"/>
-      <c r="F252" s="21" t="n"/>
-      <c r="G252" s="21" t="n"/>
+      <c r="E252" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на АРМ агента контроля устройств и каналов копирования в составе DLP-системы, перехватывающего операцию записи файла на съёмный носитель: копирование документов, содержащих признаки конфиденциальной информации без соответствующего разрешения, блокируется, а для разрешённых сценариев выполняется контентный анализ копируемых данных (см. также меру ПУИ.17).
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контроля устройств и каналов копирования (Device Control / Endpoint DLP).
+Иностранные: Forcepoint DLP (Endpoint), DeviceLock DLP и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Kaspersky Endpoint Security для бизнеса (модуль Device Control) и др.
+Открытый код: полноценных Endpoint DLP-решений данного класса в открытом коде практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F252" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля контроля устройств и каналов копирования DLP-системы на образце АРМ.
+2. Журнал (отчёт) о заблокированных попытках копирования конфиденциальной информации на съёмные носители за проверяемый период.
+3. Итоги интервью с ответственным за администрирование DLP-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G252" s="144" t="inlineStr">
+        <is>
+          <t>1. Контроль копирования развёрнут не на всех АРМ, что позволяет обойти блокировку, используя незащищённую рабочую станцию;
+2. Контентный анализ копируемых данных не настроен, блокировка выполняется только по признаку типа устройства (съёмный носитель), без анализа содержимого;
+3. Копирование через промежуточные каналы (например, во временную папку с последующей ручной архивацией) не отслеживается как единая цепочка действий;
+4. Разрешённые сценарии копирования не документируются и не пересматриваются на предмет актуальности.</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="13" t="inlineStr">
@@ -17993,38 +18157,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D254" s="34" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Исходящая почта проверяется не по факту адресата и письма (как в ПУИ.1), а по содержимому протокола</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t> </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>почтового обмена — анализируется текст и вложения всех исходящих писем на предмет конфиденциальной информации, независимо от того, куда они направлены. Это защищает от обхода сотрудником блокировки по внешним адресам (ПУИ.1) и от утечки конфиденциальных данных на внутренние адреса-пересыльщики с автоматической переадресацией во внешний ящик, когда само письмо во вложении имеет нейтральное именем файла и тему, не вызывающих подозрений при поверхностной проверке.</t>
-          </r>
-        </is>
-      </c>
-      <c r="E254" s="21" t="n"/>
-      <c r="F254" s="21" t="n"/>
-      <c r="G254" s="21" t="n"/>
+      <c r="D254" s="144" t="inlineStr">
+        <is>
+          <t>Исходящая почта проверяется не по факту адресата и письма (как в мере ПУИ.1), а по содержимому протокола почтового обмена — анализируется текст и вложения всех исходящих писем на предмет конфиденциальной информации, независимо от того, куда они направлены.
+Главная цель меры — защитить от обхода блокировки по внешним адресам (мера ПУИ.1) и от утечки конфиденциальных данных через внутренние адреса-пересыльщики с автоматической переадресацией во внешний ящик, когда само письмо во вложении имеет нейтральные имя файла и тему, не вызывающие подозрений при поверхностной проверке.</t>
+        </is>
+      </c>
+      <c r="E254" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на почтовом шлюзе модуля контентного анализа DLP-системы, выполняющего разбор текста и вложений всех исходящих сообщений (лингвистический, статистический анализ, поиск по цифровым отпечаткам конфиденциальных документов) вне зависимости от адреса получателя, с автоматическим карантином сообщений, содержащих признаки утечки.
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контентного анализа почтового трафика.
+Иностранные: Forcepoint DLP, Symantec (Broadcom) DLP и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor и др.
+Открытый код: полноценных DLP-решений данного класса в открытом коде практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F254" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля контентного анализа исходящей почты DLP-системы.
+2. Отчёт о выявленных фактах конфиденциальной информации в исходящих письмах за проверяемый период, включая переадресованные сообщения.
+3. Итоги интервью с ответственным за администрирование DLP-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G254" s="144" t="inlineStr">
+        <is>
+          <t>1. Контентный анализ настроен только на явные ключевые слова и грифы, не выявляет данные, замаскированные (перефразированные, отсканированные как изображение) под неструктурированный текст;
+2. Автоматическая переадресация писем на внешние ящики не отслеживается отдельно от прочих сценариев отправки;
+3. Вложения в защищённых паролем архивах не подвергаются контентному анализу и пропускаются без проверки;
+4. Правила выявления конфиденциальной информации (цифровые отпечатки, шаблоны) не актуализируются при появлении новых типов защищаемых документов.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="94.5" customHeight="1">
       <c r="A255" s="20" t="inlineStr">
@@ -18042,14 +18224,56 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D255" s="34" t="inlineStr">
-        <is>
-          <t>Все отправленные и полученные электронные письма должны сохраняться в едином архиве: не менее 1 месяца в режиме оперативного доступа (быстрый поиск) и не менее 6 месяцев в архивном доступе. Благодаря этому при расследовании утечки или инцидента с почтой легко восстановить содержимое переписки за нужный ближайший период.</t>
-        </is>
-      </c>
-      <c r="E255" s="21" t="n"/>
-      <c r="F255" s="21" t="n"/>
-      <c r="G255" s="21" t="n"/>
+      <c r="D255" s="144" t="inlineStr">
+        <is>
+          <t>Все отправленные и полученные электронные письма должны сохраняться в едином архиве: не менее одного месяца в режиме оперативного доступа (быстрый поиск) и не менее 6 месяцев в режиме архивного доступа.
+Главная цель меры — обеспечить возможность оперативно восстановить содержимое переписки за ближайший период при расследовании утечки или инцидента, связанного с электронной почтой, не полагаясь на индивидуальные почтовые ящики пользователей, которые могут быть очищены или недоступны.</t>
+        </is>
+      </c>
+      <c r="E255" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается развёртыванием системы архивирования электронной почты, автоматически копирующей каждое отправленное и полученное сообщение в единый архив с раздельным хранением: последние (не менее одного месяца) сообщения — в режиме оперативного (быстрого) доступа, а весь период (не менее 6 месяцев) — в режиме архивного доступа с более длительным временем поиска.
+Класс используемых средств — системы архивирования электронной почты (Email Archiving), часто интегрируемые с DLP-системой как единая платформа хранения.
+Иностранные: Proofpoint Enterprise Archive, Mimecast Email Archiving и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor (модуль архивирования), Solar Dozor (архив коммуникаций) и др.
+Открытый код: MailArchiva (Community Edition) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F255" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация системы архивирования электронной почты с указанием сроков оперативного и архивного хранения.
+2. Результат тестового поиска и восстановления письма из архива за оперативный и за архивный период.
+3. Итоги интервью с ответственным за администрирование почтовой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G255" s="144" t="inlineStr">
+        <is>
+          <t>1. Фактический срок хранения в архиве меньше установленного регламентом минимума из-за ограниченного объёма выделенного хранилища;
+2. Архивируются только входящие и исходящие внешние письма, внутренняя переписка сотрудников в архив не попадает;
+3. Поиск по архиву за пределами оперативного периода занимает существенно больше времени, чем предполагает практическая применимость при расследовании;
+4. Целостность архивных данных не контролируется, отсутствует защита от несанкционированного удаления отдельных писем из архива.</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="94.5" customHeight="1">
       <c r="A256" s="20" t="inlineStr">
@@ -18067,15 +18291,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D256" s="34" t="inlineStr">
-        <is>
-          <t>Все отправленные и полученные электронные письма должны
-сохраняться в едином архиве: не менее 3 месяца в режиме оперативного доступа (быстрый поиск) и не менее 1 года в архивном доступе. Благодаря этому при расследовании утечки или инцидента с почтой легко восстановить содержимое переписки за нужный период.</t>
-        </is>
-      </c>
-      <c r="E256" s="53" t="n"/>
-      <c r="F256" s="53" t="n"/>
-      <c r="G256" s="53" t="n"/>
+      <c r="D256" s="144" t="inlineStr">
+        <is>
+          <t>Все отправленные и полученные электронные письма должны сохраняться в едином архиве: не менее 3 месяцев в режиме оперативного доступа (быстрый поиск) и не менее одного года в режиме архивного доступа.
+Главная цель меры — обеспечить, для более критичных (в сравнении с мерой ПИУ.6) уровней защиты, доступность содержимого переписки за более длительный период при расследовании утечки или инцидента, связанного с электронной почтой, компенсируя тем самым более отложенное во времени обнаружение отдельных инцидентов.</t>
+        </is>
+      </c>
+      <c r="E256" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация аналогична мере ПИУ.6 и обеспечивается той же системой архивирования электронной почты, настроенной на увеличенные сроки хранения: не менее 3 месяцев в режиме оперативного доступа и не менее одного года — в режиме архивного доступа.
+Класс используемых средств — системы архивирования электронной почты (Email Archiving).
+Иностранные: Proofpoint Enterprise Archive, Mimecast Email Archiving и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor (модуль архивирования), Solar Dozor и др.
+Открытый код: MailArchiva (Community Edition) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F256" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация системы архивирования электронной почты с увеличенными сроками оперативного и архивного хранения.
+2. Результат тестового поиска и восстановления письма из архива за оперативный и за архивный период.
+3. Итоги интервью с ответственным за администрирование почтовой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G256" s="157" t="inlineStr">
+        <is>
+          <t>1. Увеличенный срок хранения применяется не для всех категорий объектов, требующих данного уровня защиты, часть систем архивирует почту по сокращённому сроку (мера ПИУ.6);
+2. Объём выделенного хранилища не рассчитан на фактическую нагрузку при увеличенном сроке хранения, что создаёт риск переполнения и досрочной ротации архива;
+3. Раздельность режимов оперативного и архивного доступа не подтверждена практически — поиск за пределами трёх месяцев занимает неприемлемо долгое время;
+4. Целостность и доступность архивных данных за длительный период не проверяются периодическим тестовым восстановлением.</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="114" customHeight="1">
       <c r="A257" s="20" t="inlineStr">
@@ -18093,14 +18358,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D257" s="34" t="inlineStr">
-        <is>
-          <t>Для передачи почты должен использоваться строго ограниченный перечень сетевых протоколов (например, только SMTP/IMAP через корпоративный почтовый шлюз), а не произвольные протоколы, позволяющие обойти контроль содержимого, иначе туннелирование почтового трафика через нестандартные протоколы скрывает факт передачи данных от систем мониторинга и позволяет сотруднику тихо компрометировать  данные.</t>
-        </is>
-      </c>
-      <c r="E257" s="31" t="n"/>
-      <c r="F257" s="31" t="n"/>
-      <c r="G257" s="31" t="n"/>
+      <c r="D257" s="144" t="inlineStr">
+        <is>
+          <t>Для передачи почты должен использоваться строго ограниченный перечень сетевых протоколов (например, только SMTP/IMAP через корпоративный почтовый шлюз), а не произвольные протоколы, позволяющие обойти контроль содержимого.
+Главная цель меры — исключить туннелирование почтового трафика через нестандартные протоколы: в обход разрешённого перечня оно скрывает факт передачи данных от систем мониторинга и контентного анализа (мера ПУИ.5), позволяя сотруднику тайно передавать конфиденциальную информацию за пределы организации.</t>
+        </is>
+      </c>
+      <c r="E257" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой межсетевого экрана на разрешение исходящего почтового трафика только по установленному перечню протоколов и портов (SMTP, IMAP через корпоративный почтовый шлюз) с блокированием прямого исходящего SMTP-соединения с АРМ и серверов, минующего шлюз, а также контролем (Deep Packet Inspection) на предмет несоответствия фактического протокола заявленному порту.
+Класс используемых средств — межсетевой экран нового поколения (NGFW) с функцией контроля приложений и протоколов (Application Control, Deep Packet Inspection).
+Иностранные: Palo Alto Networks (App-ID), Fortinet FortiGate (Application Control) и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: iptables/nftables в сочетании с Suricata (выявление протокола, не соответствующего порту).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F257" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация межсетевого экрана в части ограничения перечня разрешённых протоколов и портов для почтового трафика.
+2. Журнал (отчёт) о заблокированных попытках использования непредусмотренных протоколов для почтового обмена за проверяемый период.
+3. Итоги интервью с ответственным за администрирование сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G257" s="151" t="inlineStr">
+        <is>
+          <t>1. Ограничение установлено только на уровне номера порта, без контроля фактического протокола, что позволяет туннелировать иной трафик через разрешённый порт;
+2. Правило блокирования прямого исходящего SMTP-соединения не распространяется на серверы, взаимодействующие с внешними почтовыми сервисами по служебной необходимости, без отдельного анализа обоснованности исключения;
+3. Попытки использования непредусмотренных протоколов для почтового обмена фиксируются, но не анализируются на предмет системности (повторяющиеся попытки с одного узла);
+4. Перечень разрешённых протоколов не пересматривался с момента внедрения меры, несмотря на изменение состава используемых почтовых сервисов.</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="114" customHeight="1">
       <c r="A258" s="20" t="inlineStr">
@@ -18118,14 +18425,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D258" s="34" t="inlineStr">
-        <is>
-          <t>В качестве вложений к письмам должны быть разрешены только определённые форматы файлов (например, документы .docx, PDF), а потенциально опасные или неконтролируемые форматы (архивы с паролем, исполняемые файлы, нестандартные контейнеры) должны блокироваться. Это позволит защитить конфиденциальные данные от упаковывания в запароленные архивы, которые системы контентного анализа (ПУИ.5) не смогут проверить изнутри.</t>
-        </is>
-      </c>
-      <c r="E258" s="31" t="n"/>
-      <c r="F258" s="31" t="n"/>
-      <c r="G258" s="31" t="n"/>
+      <c r="D258" s="144" t="inlineStr">
+        <is>
+          <t>В качестве вложений к письмам должны быть разрешены только определённые форматы файлов (например, документы .docx, PDF), а потенциально опасные или неконтролируемые форматы (архивы с паролем, исполняемые файлы, нестандартные контейнеры) должны блокироваться.
+Главная цель меры — защитить конфиденциальные данные от упаковки в запароленные архивы или нестандартные контейнеры, содержимое которых системы контентного анализа (мера ПУИ.5) не в состоянии проверить изнутри, тем самым исключая обход контентного контроля через простое изменение формата вложения.</t>
+        </is>
+      </c>
+      <c r="E258" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой почтового шлюза на автоматическое определение фактического формата (типа содержимого) каждого вложения по его сигнатуре (а не только по расширению файла) и блокирование вложений, формат которых не входит в перечень разрешённых, с отдельной обработкой архивов, защищённых паролем, как заведомо неразрешённого формата.
+Класс используемых средств — средства фильтрации содержимого почтового шлюза (Secure Email Gateway) с функцией определения типа файла по сигнатуре.
+Иностранные: Proofpoint Email Protection, Cisco Secure Email и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для почтовых серверов, «Континент» (модуль почтовой безопасности) и др.
+Открытый код: правила фильтрации вложений по MIME-типу и сигнатуре в связке Postfix/MIMEDefang.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F258" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень разрешённых форматов файлов данных для вложений в электронные сообщения.
+2. Конфигурация почтового шлюза в части определения и блокирования запрещённых форматов вложений.
+3. Журнал (отчёт) о заблокированных вложениях неразрешённого формата за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G258" s="151" t="inlineStr">
+        <is>
+          <t>1. Определение формата вложения выполняется только по расширению файла, что позволяет обойти блокировку простым переименованием запрещённого файла;
+2. Архивы, защищённые паролем, блокируются не полностью — пропускаются, если пароль отсутствует в самом архиве, но передан отдельным письмом;
+3. Перечень разрешённых форматов не пересматривается при появлении новых рабочих задач, требующих иных типов вложений, что приводит к массовым обращениям за исключениями;
+4. Вложенные в разрешённый формат (например, .docx) объекты — активное содержимое, встроенные архивы — не проверяются на предмет запрещённого содержимого внутри.</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="85.5" customHeight="1">
       <c r="A259" s="20" t="inlineStr">
@@ -18143,14 +18492,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D259" s="34" t="inlineStr">
-        <is>
-          <t>Должны устанавливаться предельные (конечные) размеры файлов, которые можно передать вложением в письме, чтобы превышение лимита вложения вызывало блокировку передачи. В таком случае почта не сможет быть использована как канал массовой утечки конфиденциальных данных (выгрузка базы, дамп) одним вложением.</t>
-        </is>
-      </c>
-      <c r="E259" s="31" t="n"/>
-      <c r="F259" s="31" t="n"/>
-      <c r="G259" s="31" t="n"/>
+      <c r="D259" s="144" t="inlineStr">
+        <is>
+          <t>Должны устанавливаться предельные (максимальные) размеры файлов, которые можно передать вложением в письме, при превышении которых передача блокируется.
+Главная цель меры — исключить использование почты как канала массовой утечки конфиденциальных данных: выгрузка базы данных или иного объёмного дампа информации, как правило, существенно превышает размер типового рабочего вложения, и ограничение размера технически отсекает такой сценарий, не требуя предварительного контентного анализа.</t>
+        </is>
+      </c>
+      <c r="E259" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой почтового шлюза на автоматическое блокирование исходящих сообщений, суммарный размер вложений которых превышает установленный лимит, с дифференциацией лимита по категориям пользователей при производственной необходимости.
+Класс используемых средств — средства фильтрации содержимого почтового шлюза (Secure Email Gateway) с функцией ограничения размера сообщений и вложений.
+Иностранные: Proofpoint Email Protection, Cisco Secure Email и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для почтовых серверов, «Континент» (модуль почтовой безопасности) и др.
+Открытый код: встроенные ограничения размера сообщений в Postfix/Exim.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F259" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация почтового шлюза в части ограничения размера вложений исходящих сообщений.
+2. Журнал (отчёт) о заблокированных попытках отправки вложений сверх установленного лимита за проверяемый период.
+3. Итоги интервью с ответственным за администрирование почтовой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G259" s="151" t="inlineStr">
+        <is>
+          <t>1. Установленный лимит размера вложений завышен относительно объёма типового рабочего документа, что не создаёт реального препятствия для выгрузки значимого объёма данных;
+2. Для отдельных категорий пользователей лимит отключён полностью по производственной необходимости, без компенсирующего контентного контроля;
+3. Ограничение обходится дроблением объёмного файла на несколько сообщений меньшего размера, что не отслеживается как единая цепочка передачи;
+4. Лимит применяется только к вложениям, но не к объёму текста самого письма, допускающему вставку больших массивов данных непосредственно в тело сообщения.</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="128.25" customHeight="1">
       <c r="A260" s="55" t="inlineStr">
@@ -18168,14 +18559,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D260" s="34" t="inlineStr">
-        <is>
-          <t>Содержимое данных, передаваемых пользователем в Интернет через браузер и другие приложения, должно анализироваться по содержанию на наличие конфиденциальной информации, что необходимо для избежания утечки конфиденциальных данных через веб-форму, чат или иную загрузку на сайт без контроля содержимого запроса, когда сотрудник использует облачные сервисы синхронизации файлов (не файлообменники, а именно веб-интерфейсы) для передачи данных без точечной блокировки конкретных ресурсов.</t>
-        </is>
-      </c>
-      <c r="E260" s="31" t="n"/>
-      <c r="F260" s="31" t="n"/>
-      <c r="G260" s="31" t="n"/>
+      <c r="D260" s="144" t="inlineStr">
+        <is>
+          <t>Содержимое данных, передаваемых пользователем в Интернет через браузер и другие приложения, должно анализироваться на наличие конфиденциальной информации.
+Главная цель меры — исключить утечку конфиденциальных данных через веб-форму, чат или иную загрузку на сайт без контроля содержимого запроса, в том числе через легитимные облачные сервисы синхронизации файлов, точечная блокировка которых по адресу ресурса (мера ПУИ.12) недостаточна, поскольку сами эти сервисы используются организацией в рабочих целях.</t>
+        </is>
+      </c>
+      <c r="E260" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на веб-прокси модуля контентного анализа DLP-системы, выполняющего разбор передаваемых пользователем данных (формы, файлы, чаты, загрузки в облачные сервисы) вне зависимости от того, заблокирован ли сам ресурс, с расшифровкой TLS-сессий в объёме, установленном внутренними регламентами, и автоматической блокировкой при выявлении признаков конфиденциальной информации.
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контентного анализа веб-канала (Web DLP).
+Иностранные: Forcepoint DLP (Web), Zscaler (модуль DLP) и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor и др.
+Открытый код: полноценных Web DLP-решений данного класса в открытом коде практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F260" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля контентного анализа веб-трафика DLP-системы.
+2. Регламент расшифровки TLS-трафика для контентного анализа веб-канала.
+3. Журнал (отчёт) о заблокированных попытках передачи конфиденциальной информации в сеть Интернет через веб-канал за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G260" s="151" t="inlineStr">
+        <is>
+          <t>1. Контентный анализ веб-трафика не распространяется на разрешённые (используемые в рабочих целях) облачные сервисы, что оставляет значимый канал утечки вне контроля;
+2. Расшифровка TLS-трафика реализована выборочно, значимая часть веб-трафика проходит проверку только по метаданным (адрес, объём), без анализа содержимого;
+3. Контентный анализ не распознаёт данные, вставленные в изображение (скриншот таблицы) или переданные через API мобильных приложений в обход браузера;
+4. Правила выявления конфиденциальной информации не адаптированы к специфике организации, ограничиваются общими шаблонами (номера карт, СНИЛС) без учёта внутренних форматов документов.</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="128.25" customHeight="1">
       <c r="A261" s="20" t="inlineStr">
@@ -18193,14 +18626,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D261" s="34" t="inlineStr">
-        <is>
-          <t>Ресурсы сети Интернет должны классифицироваться по категориям (файлообменники, облачные хранилища, личная почта, соцсети и т.д.), и доступ к запрещённым категориям должен блокироваться на уровне веб-фильтра, а не по каждому отдельному сайту вручную. В таком случае, если сотрудник использует новый ещё не занесённый в чёрный список файлообменник для выгрузки данных, то с этой категоризацией ресурс уже будет недоступен (заблокирован превентивно, а не постфактум).</t>
-        </is>
-      </c>
-      <c r="E261" s="31" t="n"/>
-      <c r="F261" s="31" t="n"/>
-      <c r="G261" s="31" t="n"/>
+      <c r="D261" s="144" t="inlineStr">
+        <is>
+          <t>Ресурсы сети Интернет должны классифицироваться по категориям (файлообменники, облачные хранилища, личная почта, социальные сети и т. д.), а доступ к запрещённым категориям должен блокироваться на уровне веб-фильтра, а не по каждому отдельному сайту вручную.
+Главная цель меры — обеспечить превентивную, а не постфактумную блокировку: при таком подходе, если сотрудник начинает использовать новый, ещё не занесённый в чёрный список файлообменник для выгрузки данных, ресурс уже недоступен благодаря принадлежности к заблокированной категории, а не только по факту явного добавления его отдельного адреса в список запрещённых.</t>
+        </is>
+      </c>
+      <c r="E261" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на веб-прокси или NGFW модуля категоризации веб-ресурсов (URL Filtering), использующего регулярно обновляемую производителем базу категорий сайтов, с блокировкой доступа к категориям, запрещённым внутренними правилами (файлообменники, анонимайзеры, личная почта и подобные), а не только к отдельным адресам.
+Класс используемых средств — средства категоризации и фильтрации веб-ресурсов (URL Filtering / Web Content Filtering) в составе NGFW или прокси-сервера.
+Иностранные: Palo Alto Networks (URL Filtering), Zscaler и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate (модуль веб-фильтрации) и др.
+Открытый код: Squid с подключаемой базой категорий (например, Shalla's Blacklists) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F261" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля категоризации веб-ресурсов с перечнем заблокированных категорий.
+2. Отчёт о частоте и дате обновления базы категорий веб-ресурсов.
+3. Журнал (отчёт) о заблокированных попытках доступа к запрещённым категориям сайтов за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G261" s="151" t="inlineStr">
+        <is>
+          <t>1. База категорий веб-ресурсов обновляется реже, чем предусмотрено регламентом производителя, что снижает актуальность классификации новых ресурсов;
+2. Перечень заблокированных категорий не охватывает все категории повышенного риска утечки (например, доступны анонимайзеры, позволяющие обходить прочую фильтрацию);
+3. Классификация ресурса ошибочно относит используемый в рабочих целях сервис к разрешённой категории, хотя фактически он относится к файлообменникам;
+4. Правила категоризации не применяются к зашифрованному трафику при отсутствии расшифровки TLS, доступ определяется только по домену без учёта фактического содержимого.</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="128.25" customHeight="1">
       <c r="A262" s="20" t="inlineStr">
@@ -18218,14 +18693,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D262" s="34" t="inlineStr">
-        <is>
-          <t>Взаимодействие с сетью Интернет должно осуществляться только по строго определённому перечню протоколов и портов, а не по любым доступным. Это предотвращает использование сотрудником нестандартного порта или протокола (например, туннелирование через DNS или ICMP) для обхода периметровых средств контроля и контентного анализа,  а также исключает наличие лишних открытых портов, которые могут создавать неучтённые каналы связи с внешними ресурсами в обход политики безопасности.</t>
-        </is>
-      </c>
-      <c r="E262" s="31" t="n"/>
-      <c r="F262" s="31" t="n"/>
-      <c r="G262" s="31" t="n"/>
+      <c r="D262" s="144" t="inlineStr">
+        <is>
+          <t>Взаимодействие с сетью Интернет должно осуществляться только по строго определённому перечню протоколов и портов, а не по любым доступным.
+Главная цель меры — исключить использование сотрудником нестандартного порта или протокола (например, туннелирование через DNS или ICMP) для обхода периметровых средств контроля и контентного анализа (меры ПУИ.2, ПУИ.11), а также устранить неучтённые каналы связи с внешними ресурсами, создаваемые лишними открытыми портами в обход установленной политики безопасности.</t>
+        </is>
+      </c>
+      <c r="E262" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой межсетевого экрана на разрешение исходящего трафика в сеть Интернет только по установленному перечню протоколов и портов, с блокированием прочих протоколов по умолчанию и дополнительным контролем (Deep Packet Inspection) на предмет несоответствия фактического протокола заявленному порту, включая выявление туннелирования через DNS/ICMP.
+Класс используемых средств — межсетевой экран нового поколения (NGFW) с функцией контроля приложений и протоколов (Application Control, Deep Packet Inspection).
+Иностранные: Palo Alto Networks (App-ID), Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: iptables/nftables в сочетании с Suricata (выявление аномального DNS/ICMP-трафика).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F262" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация межсетевого экрана в части ограничения перечня разрешённых протоколов и портов для взаимодействия с сетью Интернет.
+2. Журнал (отчёт) о заблокированных попытках использования непредусмотренных протоколов и портов за проверяемый период.
+3. Итоги интервью с ответственным за администрирование сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G262" s="151" t="inlineStr">
+        <is>
+          <t>1. Выявление туннелирования через разрешённые по умолчанию протоколы (DNS, ICMP) не настроено, ограничиваются только контролем номеров портов;
+2. Перечень разрешённых протоколов и портов избыточно широк, включает неиспользуемые фактически сервисы, оставленные «на всякий случай»;
+3. Правило блокировки распространяется не на все сегменты сети, отдельные сегменты (например, тестовый) исключены без формального обоснования;
+4. Попытки использования непредусмотренных протоколов фиксируются, но не анализируются на предмет системности и признаков целенаправленного обхода контроля.</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="185.25" customHeight="1">
       <c r="A263" s="20" t="inlineStr">
@@ -18249,9 +18766,50 @@
 Главная цель меры — минимизировать риски компрометации и утечки конфиденциальной информации через наименее защищённый сегмент сети, который является основной мишенью для внешних атак.</t>
         </is>
       </c>
-      <c r="E263" s="31" t="n"/>
-      <c r="F263" s="31" t="n"/>
-      <c r="G263" s="31" t="n"/>
+      <c r="E263" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе прямого запрета на хранение и обработку информации конфиденциального характера на объектах доступа, размещённых в сегментах вычислительных сетей, подключённых к сети Интернет (в первую очередь в DMZ);
+2. Классификацию (мера ИУ) объектов доступа, размещённых в таких сегментах, с явным указанием отсутствия у них полномочий на обработку конфиденциальной информации;
+3. Периодический контроль (инвентаризацию данных) на предмет фактического отсутствия конфиденциальной информации на объектах доступа в DMZ-сегменте и иных сегментах, подключённых к сети Интернет.
+На практике данная организационная мера технически подкрепляется архитектурным принципом «тонкого» DMZ-сегмента, где объекты доступа выполняют роль прокси/шлюза к внутренним системам, не сохраняя данные локально.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F263" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, содержащий запрет на хранение и обработку конфиденциальной информации на объектах доступа в сегментах, подключённых к сети Интернет;
+2. Результаты классификации объектов доступа, подтверждающие отсутствие у них полномочий на обработку конфиденциальной информации;
+3. Акты (отчёты) периодического контроля на предмет фактического отсутствия конфиденциальной информации на объектах доступа в DMZ-сегменте.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G263" s="151" t="inlineStr">
+        <is>
+          <t>1. Запрет закреплён во внутреннем нормативном документе, но периодический контроль его фактического соблюдения не проводится;
+2. На объектах доступа в DMZ-сегменте временно размещаются конфиденциальные данные в рамках отладки или тестирования, без последующего гарантированного удаления;
+3. Архитектура DMZ-сегмента не исключает локальное кеширование конфиденциальных данных промежуточными сервисами (например, кеш веб-сервера);
+4. Классификация новых объектов доступа, размещаемых в сегментах, подключённых к сети Интернет, не проводится на регулярной основе.</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="99.75" customHeight="1">
       <c r="A264" s="20" t="inlineStr">
@@ -18275,9 +18833,50 @@
 Главная цель меры — предотвратить несанкционированное выведение конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) на бумажные носители.</t>
         </is>
       </c>
-      <c r="E264" s="21" t="n"/>
-      <c r="F264" s="21" t="n"/>
-      <c r="G264" s="21" t="n"/>
+      <c r="E264" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация дополняет контроль печати по типу документа и сотруднику (мера ПУИ.3) модулем контентного анализа DLP-системы, выполняющим разбор содержимого документа, отправляемого на печать, независимо от того, кем и с какого устройства инициировано задание, с автоматической блокировкой при выявлении признаков конфиденциальной информации, выходящей за пределы разрешённого сценария.
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контентного анализа печати (Print Control).
+Иностранные: Forcepoint DLP (Discovery/Print) и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor и др.
+Открытый код: полноценных DLP-модулей контентного анализа печати в открытом коде практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F264" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля контентного анализа печати DLP-системы.
+2. Журнал (отчёт) о заблокированных попытках печати конфиденциальной информации, выявленных контентным анализом, за проверяемый период.
+3. Итоги интервью с ответственным за администрирование DLP-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G264" s="144" t="inlineStr">
+        <is>
+          <t>1. Контентный анализ печати не распознаёт конфиденциальную информацию в отсканированных изображениях документа (без распознавания текста, OCR);
+2. Анализ ограничивается текстовым содержимым, не учитывает табличные и графические данные (диаграммы, схемы), содержащие защищаемую информацию;
+3. Разрешённые исключения из контентного анализа (например, для типовых форм) не пересматриваются при изменении формы документа;
+4. Результаты контентного анализа печати не сопоставляются с результатами анализа иных каналов (почта, копирование) для выявления попыток обхода через смену канала.</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="128.25" customHeight="1">
       <c r="A265" s="20" t="inlineStr">
@@ -18295,14 +18894,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D265" s="34" t="inlineStr">
-        <is>
-          <t>Должно быть реализовано использование «печати по запросу» (pull printing) для МФУ — когда задание уходит на сервер печати и физически распечатывается только после того, как пользователь подтвердит себя на устройстве паролем или картой доступа. Благодаря этому документ, отправленный на печать, не лежит в открытом лотке принтера неограниченное время и его не может забрать постороннее, также это позволяет вести учёт отпечатанных документов с привязкой к лицу, которое его физически получило.</t>
-        </is>
-      </c>
-      <c r="E265" s="21" t="n"/>
-      <c r="F265" s="21" t="n"/>
-      <c r="G265" s="21" t="n"/>
+      <c r="D265" s="144" t="inlineStr">
+        <is>
+          <t>Должно быть реализовано использование «печати по запросу» (pull printing) для многофункциональных устройств — когда задание уходит на сервер печати и физически распечатывается только после того, как пользователь подтвердит себя на устройстве паролем или картой доступа.
+Главная цель меры — исключить нахождение распечатанного документа в открытом лотке принтера неограниченное время, откуда его может забрать постороннее лицо, а также обеспечить учёт отпечатанных документов с привязкой к конкретному лицу, физически получившему их.</t>
+        </is>
+      </c>
+      <c r="E265" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается развёртыванием сервера очереди печати с функцией «печати по запросу», удерживающего задание в очереди до момента аутентификации пользователя непосредственно на многофункциональном устройстве по паролю, PIN-коду или персональной карте доступа, после чего документ немедленно распечатывается.
+Класс используемых средств — системы управления печатью (Print Management) с функцией печати по запросу (pull printing / follow-me printing).
+Иностранные: PaperCut MF, Ysoft SafeQ и пр.
+Российские сертифицированные (ФСТЭК): специализированных сертифицированных решений данного узкого класса на практике немного, применяется встроенный функционал pull printing многофункциональных устройств отечественных и локализованных производителей в сочетании с СКУД организации.
+Открытый код: CUPS в сочетании со сторонними скриптами аутентификации по карте (ограниченно применимо как основное решение).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F265" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация сервера печати с указанием режима «печати по запросу» и способа аутентификации на устройстве.
+2. Выгрузка журнала печати с сопоставлением задания конкретному лицу, подтвердившему получение документа на устройстве.
+3. Итоги интервью с ответственным за администрирование печатной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G265" s="144" t="inlineStr">
+        <is>
+          <t>1. Режим печати по запросу настроен не для всех многофункциональных устройств, часть принтеров работает в обычном режиме прямой печати;
+2. Аутентификация на устройстве осуществляется общим (гостевым) кодом доступа, не позволяющим достоверно установить конкретное лицо, получившее документ;
+3. Задания, не востребованные пользователем в установленный срок, автоматически не удаляются из очереди печати, накапливаясь на сервере;
+4. Печать со сторонних (личных) устройств в обход сервера очереди технически не заблокирована.</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="128.25" customHeight="1">
       <c r="A266" s="39" t="inlineStr">
@@ -18326,9 +18967,50 @@
 Главная цель меры — предотвратить несанкционированное копирование персональных данных, банковской тайны, коммерческой тайны и иной защищаемой информации на внешние носители, которые могут быть вынесены за пределы организации.</t>
         </is>
       </c>
-      <c r="E266" s="21" t="n"/>
-      <c r="F266" s="21" t="n"/>
-      <c r="G266" s="21" t="n"/>
+      <c r="E266" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация дополняет блокировку по факту разрешения/запрета копирования (мера ПУИ.4) модулем контентного анализа DLP-системы, выполняющим разбор содержимого файла в момент операции копирования на съёмный носитель, вне зависимости от того, разрешена ли такая операция в принципе, с автоматической блокировкой при выявлении конфиденциальной информации, выходящей за пределы разрешённого сценария.
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контентного анализа канала копирования на съёмные носители (Endpoint DLP).
+Иностранные: Forcepoint DLP (Endpoint), DeviceLock DLP и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Kaspersky Endpoint Security для бизнеса (модуль контентной фильтрации Device Control) и др.
+Открытый код: полноценных Endpoint DLP-решений данного класса в открытом коде практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F266" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля контентного анализа копирования на съёмные носители DLP-системы.
+2. Журнал (отчёт) о заблокированных попытках копирования конфиденциальной информации, выявленных контентным анализом, за проверяемый период.
+3. Итоги интервью с ответственным за администрирование DLP-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G266" s="144" t="inlineStr">
+        <is>
+          <t>1. Контентный анализ копирования не распознаёт данные в архивированном или переименованном файле, ограничивается проверкой типовых форматов документов;
+2. Контроль охватывает только копирование на съёмные USB-носители, не распространяясь на копирование по локальной сети на неучтённый ресурс;
+3. Правила выявления конфиденциальной информации не синхронизированы с аналогичными правилами почтового и веб-каналов, что даёт неравномерное покрытие;
+4. Разрешённые сценарии копирования (для выделенных подразделений) исключены из контентного анализа полностью, без выборочной проверки.</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="128.25" customHeight="1">
       <c r="A267" s="20" t="inlineStr">
@@ -18346,14 +19028,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D267" s="34" t="inlineStr">
-        <is>
-          <t>Физические порты ввода-вывода средств вычислительной техники (СВТ) (USB, LPT, Bluetooth, инфракрасный порт и т. п.), не используемые в рабочих целях, должны быть заблокированы на уровне АРМ, и по умолчанию должны быть доступны только разрешённые интерфейсы. Тогда не будет происходить подключение постороннего устройства через незаблокированный неиспользуемый порт (например, Bluetooth-адаптер) для передачи данных в обход контролируемых USB-накопителей.</t>
-        </is>
-      </c>
-      <c r="E267" s="31" t="n"/>
-      <c r="F267" s="31" t="n"/>
-      <c r="G267" s="31" t="n"/>
+      <c r="D267" s="144" t="inlineStr">
+        <is>
+          <t>Физические порты ввода-вывода средств вычислительной техники (USB, LPT, Bluetooth, инфракрасный порт и т. п.), не используемые в рабочих целях, должны быть заблокированы на уровне АРМ, при этом по умолчанию должны быть доступны только явно разрешённые интерфейсы.
+Главная цель меры — исключить подключение постороннего устройства через незаблокированный неиспользуемый порт (например, Bluetooth-адаптер) для передачи данных в обход контролируемых каналов, таких как USB-накопители, для которых уже действуют меры контентного анализа и блокировки (меры ПУИ.4, ПУИ.17).</t>
+        </is>
+      </c>
+      <c r="E267" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой средства контроля устройств (Device Control) на АРМ по принципу «запрещено всё, что явно не разрешено»: все физические порты ввода-вывода блокируются по умолчанию, а разрешение предоставляется только для портов и типов устройств, необходимых для решения рабочих задач конкретной категории пользователей.
+Класс используемых средств — средства контроля подключаемых устройств и портов ввода-вывода (Device Control), как правило, в составе EPP-платформы или DLP-системы.
+Иностранные: DeviceLock DLP, Forcepoint DLP (Endpoint) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль Device Control), Secret Net Studio (контроль устройств) и др.
+Открытый код: штатные средства ограничения устройств ОС (например, групповые политики Windows) без централизованного управления полноценного класса Device Control.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F267" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства контроля устройств и портов ввода-вывода на образце АРМ.
+2. Перечень разрешённых портов и типов устройств по категориям пользователей.
+3. Журнал (отчёт) о заблокированных попытках подключения устройств к незаблокированным ранее портам за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G267" s="151" t="inlineStr">
+        <is>
+          <t>1. Контроль портов настроен не на всех АРМ, часть рабочих станций (в частности, АРМ подрядчиков) исключена из-под контроля;
+2. Разрешение для отдельных категорий пользователей предоставлено избыточно широко («на все случаи»), без привязки к конкретной рабочей задаче;
+3. Виртуальные (эмулируемые в составе иного устройства) интерфейсы, например USB-модем в составе смартфона, не распознаются средством контроля как отдельный тип устройства и остаются разрешёнными;
+4. Перечень разрешённых портов и устройств не пересматривается при изменении должностных обязанностей сотрудника.</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="128.25" customHeight="1">
       <c r="A268" s="20" t="inlineStr">
@@ -18377,9 +19101,50 @@
 Главная цель меры — предотвратить несанкционированное копирование конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) на внешние носители, которые могут быть вынесены за пределы организации, а также исключить риск заражения вредоносным ПО через непроверенные съемные носители.</t>
         </is>
       </c>
-      <c r="E268" s="31" t="n"/>
-      <c r="F268" s="31" t="n"/>
-      <c r="G268" s="31" t="n"/>
+      <c r="E268" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой средства контроля устройств (Device Control) на АРМ по принципу «белого списка»: подключение переносного носителя информации разрешается только при условии, что его уникальный идентификатор (серийный номер) входит в перечень зарегистрированных (учтённых) устройств, для прочих — подключение блокируется автоматически.
+Класс используемых средств — средства контроля подключаемых устройств (Device Control) с функцией «белого списка» по серийному номеру устройства.
+Иностранные: DeviceLock DLP, Forcepoint DLP (Endpoint) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль Device Control), Secret Net Studio и др.
+Открытый код: полноценной реализации «белого списка» по серийному номеру устройства в открытых решениях практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F268" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства контроля устройств в части «белого списка» зарегистрированных переносных носителей.
+2. Перечень (реестр) зарегистрированных (учтённых) переносных носителей информации.
+3. Журнал (отчёт) о заблокированных попытках подключения незарегистрированных носителей за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G268" s="151" t="inlineStr">
+        <is>
+          <t>1. Реестр зарегистрированных носителей не актуализируется при выводе носителя из эксплуатации, заблокированный физически носитель остаётся в «белом списке»;
+2. Идентификация носителя по серийному номеру технически обходится устройствами, эмулирующими серийный номер уже зарегистрированного носителя;
+3. Регистрация нового носителя в перечне выполняется без предварительной проверки его на отсутствие вредоносного кода (см. также меру ЗВК.18);
+4. Контроль настроен не на всех АРМ, что позволяет подключить незарегистрированный носитель к рабочей станции, исключённой из-под контроля.</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="13" t="inlineStr">
@@ -18410,10 +19175,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D270" s="21" t="n"/>
-      <c r="E270" s="31" t="n"/>
-      <c r="F270" s="31" t="n"/>
-      <c r="G270" s="31" t="n"/>
+      <c r="D270" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует ведения учёта машинных носителей информации (МНИ), предназначенных для хранения информации конфиденциального характера, и контроля их фактического использования на протяжении всего жизненного цикла — от постановки на учёт до вывода из эксплуатации.
+Главная цель меры — обеспечить полную видимость того, где и на каких носителях фактически хранится конфиденциальная информация: без формального учёта организация не в состоянии подтвердить местонахождение и статус каждого носителя, что делает невозможным контроль их использования (мера ПУИ.21), маркирование (мера ПУИ.22) и гарантированное уничтожение данных при выводе из эксплуатации (меры ПУИ.23/24).</t>
+        </is>
+      </c>
+      <c r="E270" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Ведение реестра (перечня) МНИ, предназначенных для хранения информации конфиденциального характера, с указанием типа носителя, ответственного держателя и текущего статуса;
+2. Регламентацию порядка постановки на учёт нового носителя и снятия с учёта выводимого из эксплуатации;
+3. Проведение периодической инвентаризации фактического наличия и местонахождения учтённых носителей с сверкой с данными реестра.
+На практике мера, как правило, реализуется базовыми средствами (реестром в форме таблицы или специализированного модуля системы управления ИТ-активами) без отдельного выделенного средства защиты информации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F270" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Реестр (перечень) учтённых МНИ, предназначенных для хранения информации конфиденциального характера;
+2. Регламент постановки на учёт и снятия с учёта МНИ;
+3. Акты (отчёты) периодической инвентаризации МНИ с результатами сверки с реестром.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G270" s="151" t="inlineStr">
+        <is>
+          <t>1. Реестр учтённых МНИ не актуализируется своевременно при передаче носителя другому сотруднику или выводе из эксплуатации;
+2. Инвентаризация фактического наличия носителей проводится нерегулярно или не по полному перечню учтённых МНИ;
+3. Учёту подлежат только съёмные носители (флеш-накопители, диски), тогда как встроенные накопители АРМ и серверов, также содержащие конфиденциальную информацию, из реестра исключены;
+4. Ответственный держатель носителя не определён однозначно, при инвентаризации отдельные носители не удаётся сопоставить с конкретным сотрудником.</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="42.75" customHeight="1">
       <c r="A271" s="20" t="inlineStr">
@@ -18431,10 +19242,55 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D271" s="21" t="n"/>
-      <c r="E271" s="31" t="n"/>
-      <c r="F271" s="31" t="n"/>
-      <c r="G271" s="31" t="n"/>
+      <c r="D271" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует документарного определения порядка использования и доступа к машинным носителям информации (МНИ), предназначенным для хранения информации конфиденциального характера.
+Главная цель меры — исключить произвольное (не регламентированное) обращение с носителями конфиденциальной информации: без формально установленного порядка использования и доступа сотрудники руководствуются собственными представлениями о допустимом обращении с носителем, что создаёт неконтролируемый разброс практик и повышает риск утраты или неконтролируемого распространения содержащихся на нём данных.</t>
+        </is>
+      </c>
+      <c r="E271" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Разработку и утверждение внутреннего нормативного документа, устанавливающего порядок использования учтённых МНИ (условия выдачи, хранения, транспортировки, возврата) и порядок предоставления доступа к содержащейся на них информации;
+2. Определение перечня должностей (ролей), которым разрешено получать в пользование МНИ, предназначенные для хранения конфиденциальной информации, исходя из служебной необходимости;
+3. Ознакомление сотрудников, работающих с такими носителями, с установленным порядком под подпись.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F271" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, определяющий порядок использования и доступа к МНИ, предназначенным для хранения информации конфиденциального характера;
+2. Перечень должностей (ролей), которым разрешено получать в пользование такие носители;
+3. Листы ознакомления сотрудников с установленным порядком.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G271" s="151" t="inlineStr">
+        <is>
+          <t>1. Установленный порядок не охватывает этап транспортировки носителя за пределы контролируемой зоны (командировки, курьерская доставка);
+2. Перечень должностей, которым разрешено получать носители в пользование, не пересматривается при изменении организационной структуры;
+3. Ознакомление сотрудников с порядком проводится формально, без подтверждения фактического усвоения требований;
+4. Порядок не устанавливает предельный срок нахождения носителя у конкретного сотрудника, что затрудняет контроль его своевременного возврата.</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="20" t="inlineStr">
@@ -18452,10 +19308,55 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D272" s="21" t="n"/>
-      <c r="E272" s="31" t="n"/>
-      <c r="F272" s="31" t="n"/>
-      <c r="G272" s="31" t="n"/>
+      <c r="D272" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует маркирования учтённых машинных носителей информации (МНИ), предназначенных для хранения информации конфиденциального характера, — то есть их физического обозначения, позволяющего однозначно идентифицировать конкретный носитель и сопоставить его с записью в реестре учёта (мера ПУИ.20).
+Главная цель меры — обеспечить возможность визуально и однозначно отличить учтённый носитель конфиденциальной информации от личного или неучтённого носителя, а также исключить путаницу между учтёнными носителями при их одновременном использовании несколькими сотрудниками.</t>
+        </is>
+      </c>
+      <c r="E272" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Регламентацию способа маркирования учтённых МНИ (уникальный идентификационный номер, соответствующий записи в реестре, нанесённый на корпус носителя способом, устойчивым к повреждению при эксплуатации);
+2. Обязательное маркирование каждого носителя непосредственно при постановке на учёт (мера ПУИ.20), до его выдачи в пользование;
+3. Периодический контроль соответствия маркировки фактически используемых носителей записям реестра.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F272" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) маркирования учтённых МНИ;
+2. Выборочный осмотр учтённых носителей на предмет наличия читаемой маркировки, соответствующей записи в реестре;
+3. Акты периодического контроля соответствия маркировки носителей данным реестра.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G272" s="151" t="inlineStr">
+        <is>
+          <t>1. Маркировка носителя выполнена способом, не устойчивым к повреждению (наклейка, стираемая надпись), и утрачивается в процессе эксплуатации;
+2. Часть учтённых носителей выдана в пользование до маркирования, что не позволяет однозначно идентифицировать их как учтённые;
+3. Периодический контроль соответствия маркировки данным реестра не проводится;
+4. Формат маркировки не унифицирован, разные подразделения используют собственные обозначения, что затрудняет централизованный учёт.</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="128.25" customHeight="1">
       <c r="A273" s="20" t="inlineStr">
@@ -18473,14 +19374,56 @@
           <t>Т-Н-Н</t>
         </is>
       </c>
-      <c r="D273" s="34" t="inlineStr">
-        <is>
-          <t>При выводе машинного носителя информации из эксплуатации (или его передаче в стороннюю организацию) информация должна стираться средствами, обеспечивающими полную (не просто по заголовкам) перезапись данных во избежание случаев, когда списанный или переданный в ремонт носитель с остаточными данными восстанавливается сторонним лицом стандартными средствами восстановления файлов. То же касается случаев, когда списываются и сами средства вычислительной техники.</t>
-        </is>
-      </c>
-      <c r="E273" s="31" t="n"/>
-      <c r="F273" s="31" t="n"/>
-      <c r="G273" s="31" t="n"/>
+      <c r="D273" s="144" t="inlineStr">
+        <is>
+          <t>При выводе машинного носителя информации из эксплуатации (или его передаче в стороннюю организацию) содержащаяся на нём информация должна стираться средствами, обеспечивающими полную (а не только по заголовкам файловой таблицы) перезапись данных; то же требование распространяется на случаи, когда списывается сама единица средства вычислительной техники (СВТ), в состав которой входит носитель.
+Главная цель меры — исключить восстановление стандартными средствами восстановления файлов остаточных данных со списанного или переданного в ремонт (стороннюю организацию) носителя: удаление файла или форматирование раздела средствами операционной системы, как правило, лишь помечает место на носителе как свободное, не уничтожая физически записанные данные.</t>
+        </is>
+      </c>
+      <c r="E273" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением специализированного средства гарантированного удаления (стирания) данных, выполняющего многократную перезапись всего адресного пространства носителя случайными или заданными шаблонами данных в соответствии с одним из признанных алгоритмов (например, по ГОСТ Р 50739 или аналогичным методикам), с формированием протокола (сертификата) о выполненном стирании.
+Класс используемых средств — средства гарантированного уничтожения (стирания) информации на машинных носителях.
+Иностранные: Blancco Drive Eraser и пр.
+Российские сертифицированные (ФСТЭК): «Терьер» (гарантированное уничтожение информации), «Кольчуга-К» и др.
+Открытый код: DBAN (Darik's Boot and Nuke) — ограниченно применим как основное средство ввиду отсутствия сертификации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F273" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства гарантированного удаления данных, применяемого при выводе МНИ из эксплуатации.
+2. Протоколы (сертификаты) стирания по конкретным носителям, выведенным из эксплуатации или переданным в стороннюю организацию, за проверяемый период.
+3. Итоги интервью с ответственным за вывод из эксплуатации СВТ и МНИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G273" s="151" t="inlineStr">
+        <is>
+          <t>1. Процедура гарантированного стирания применяется не ко всем выводимым из эксплуатации носителям, часть списывается без предварительной обработки;
+2. Протокол (сертификат) стирания не формируется или не сохраняется, что не позволяет впоследствии подтвердить факт выполненной перезаписи по конкретному носителю;
+3. Неисправные носители, не поддающиеся программному стиранию, выводятся из эксплуатации без физического уничтожения, компенсирующего невозможность перезаписи;
+4. Стирание не распространяется на встроенные накопители периферийных устройств (многофункциональных устройств печати, копиров), также содержащих остаточные данные.</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="114" customHeight="1">
       <c r="A274" s="20" t="inlineStr">
@@ -18498,14 +19441,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D274" s="34" t="inlineStr">
-        <is>
-          <t>При выводе машинного носителя информации из эксплуатации (или его передаче в стороннюю организацию)  информация стирается средствами гарантированного удаления информации для максимально полного исключения восстановления данных с носителя, а не просто методом перезаписи. Это поможет не допустить восстановление и последующую утечку данных с носителя при его списании или при списании привязанного средства вычислительной техники.</t>
-        </is>
-      </c>
-      <c r="E274" s="31" t="n"/>
-      <c r="F274" s="31" t="n"/>
-      <c r="G274" s="31" t="n"/>
+      <c r="D274" s="144" t="inlineStr">
+        <is>
+          <t>При выводе машинного носителя информации из эксплуатации (или его передаче в стороннюю организацию) информация стирается средствами гарантированного удаления информации, обеспечивающими более высокий, в сравнении с мерой ПУИ.23, уровень исключения возможности восстановления данных.
+Главная цель меры — не допустить восстановление и последующую утечку данных с носителя повышенной критичности при его списании (или списании привязанного средства вычислительной техники), применяя для таких носителей методы уничтожения, устойчивые не только к стандартным программным средствам восстановления, но и к специализированным методам криминалистического анализа.</t>
+        </is>
+      </c>
+      <c r="E274" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением средства гарантированного стирания, дополненного при необходимости методом физического уничтожения носителя (размагничивание, механическое разрушение) для носителей повышенной критичности, для которых программная перезапись не признаётся достаточной, с формированием акта уничтожения, фиксирующего использованный метод.
+Класс используемых средств — средства гарантированного уничтожения информации на машинных носителях, включая устройства физического уничтожения (шредеры для носителей информации, размагничиватели).
+Иностранные: Blancco Drive Eraser (программное гарантированное стирание) и пр.
+Российские сертифицированные (ФСТЭК): «Терьер», «Кольчуга-К» (программное стирание); устройства физического уничтожения носителей отечественного производства (шредеры, размагничиватели) для носителей повышенной критичности.
+Открытый код: DBAN — ограниченно применим как основное средство ввиду отсутствия сертификации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F274" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства гарантированного удаления данных и (или) документация на устройство физического уничтожения носителей.
+2. Акты уничтожения по конкретным носителям повышенной критичности за проверяемый период с указанием применённого метода.
+3. Итоги интервью с ответственным за вывод из эксплуатации СВТ и МНИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G274" s="151" t="inlineStr">
+        <is>
+          <t>1. Критерии отнесения носителя к категории, требующей физического уничтожения, а не только программного стирания, не формализованы;
+2. Акт уничтожения не содержит достаточных сведений для идентификации конкретного уничтоженного носителя (серийный номер, инвентарный номер);
+3. Физическое уничтожение носителей выполняется силами сторонней организации без контроля со стороны организации-заказчика за фактическим уничтожением конкретного носителя;
+4. Носители, признанные неисправными и не поддающимися программной перезаписи, не всегда направляются на физическое уничтожение, а иногда просто утилизируются как отходы.</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="85.5" customHeight="1">
       <c r="A275" s="20" t="inlineStr">
@@ -18523,14 +19508,56 @@
           <t>Т-Н-Н</t>
         </is>
       </c>
-      <c r="D275" s="34" t="inlineStr">
-        <is>
-          <t>При передаче (перезакреплении) машинного носителя информации между работниками или подразделениями внутри организации, информация стирается средствами полной перезаписи данных, чтобы сотрудник, получивший носитель «по наследству» от коллеги, не имел доступа к остаточным данным прежнего владельца, не относящимся к его задачам.</t>
-        </is>
-      </c>
-      <c r="E275" s="31" t="n"/>
-      <c r="F275" s="31" t="n"/>
-      <c r="G275" s="31" t="n"/>
+      <c r="D275" s="144" t="inlineStr">
+        <is>
+          <t>При передаче (перезакреплении) машинного носителя информации между работниками или структурными подразделениями внутри организации информация стирается средствами полной перезаписи данных.
+Главная цель меры — исключить доступ сотрудника, получившего носитель «по наследству» от коллеги или другого подразделения, к остаточным данным прежнего владельца, не относящимся к его текущим служебным задачам, тем самым не допуская избыточного доступа к конфиденциальной информации по формальному признаку обладания носителем.</t>
+        </is>
+      </c>
+      <c r="E275" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается тем же классом средств гарантированного удаления данных, что и при выводе носителя из эксплуатации (мера ПУИ.23), применяемым в рамках регламентированной процедуры перезакрепления носителя между сотрудниками или подразделениями, с обязательным стиранием до фактической передачи носителя новому держателю.
+Класс используемых средств — средства гарантированного уничтожения (стирания) информации на машинных носителях.
+Иностранные: Blancco Drive Eraser и пр.
+Российские сертифицированные (ФСТЭК): «Терьер», «Кольчуга-К» и др.
+Открытый код: DBAN — ограниченно применим как основное средство ввиду отсутствия сертификации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F275" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) стирания данных при перезакреплении МНИ между работниками и (или) подразделениями.
+2. Протоколы стирания по конкретным случаям перезакрепления носителей за проверяемый период.
+3. Итоги интервью с ответственным за учёт и выдачу МНИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G275" s="151" t="inlineStr">
+        <is>
+          <t>1. Стирание данных при перезакреплении носителя выполняется не всегда, а только по инициативе прежнего владельца, без обязательного контроля со стороны ответственного за учёт МНИ;
+2. Перезакрепление носителя внутри одного подразделения (между сотрудниками одной рабочей группы) исключается из процедуры обязательного стирания;
+3. Протокол стирания при перезакреплении не оформляется, что не позволяет подтвердить факт выполненной перезаписи;
+4. Носитель передаётся новому держателю до завершения процедуры стирания, с расчётом на «добровольное» удаление данных новым владельцем.</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="99.75" customHeight="1">
       <c r="A276" s="20" t="inlineStr">
@@ -18548,14 +19575,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D276" s="34" t="inlineStr">
-        <is>
-          <t>При передаче (перезакреплении) машинного носителя информации между работниками или подразделениями стирание выполняется средствами гарантированного  удаления информации для исключения восстановления данных, чтобы сотрудник, получивший носитель «по наследству» от коллеги, не имел доступа к остаточным данным прежнего владельца, не относящимся к его задачам.</t>
-        </is>
-      </c>
-      <c r="E276" s="31" t="n"/>
-      <c r="F276" s="31" t="n"/>
-      <c r="G276" s="31" t="n"/>
+      <c r="D276" s="144" t="inlineStr">
+        <is>
+          <t>При передаче (перезакреплении) машинного носителя информации между работниками или подразделениями стирание данных выполняется средствами гарантированного удаления информации — для носителей повышенной критичности, для которых полной перезаписи (мера ПУИ.25) недостаточно.
+Главная цель меры — обеспечить тот же результат исключения доступа к остаточным данным прежнего владельца, что и мера ПУИ.25, но применительно к носителям с повышенным уровнем защищаемой информации, для которых требуется более строгий метод удаления, устойчивый к специализированным методам восстановления.</t>
+        </is>
+      </c>
+      <c r="E276" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением средства гарантированного стирания к носителям повышенной критичности при их перезакреплении между работниками или подразделениями, с формированием протокола, фиксирующего использованный метод удаления и подтверждающего его выполнение до фактической передачи носителя новому держателю.
+Класс используемых средств — средства гарантированного уничтожения (стирания) информации на машинных носителях.
+Иностранные: Blancco Drive Eraser и пр.
+Российские сертифицированные (ФСТЭК): «Терьер», «Кольчуга-К» и др.
+Открытый код: DBAN — ограниченно применим как основное средство ввиду отсутствия сертификации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F276" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок) гарантированного стирания данных при перезакреплении носителей повышенной критичности.
+2. Протоколы стирания по конкретным случаям перезакрепления таких носителей за проверяемый период.
+3. Итоги интервью с ответственным за учёт и выдачу МНИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G276" s="151" t="inlineStr">
+        <is>
+          <t>1. Критерии отнесения носителя к категории, требующей гарантированного (а не обычного) стирания при перезакреплении, не формализованы;
+2. Протокол стирания оформляется формально, без фактической проверки результата выполненной перезаписи;
+3. Перезакрепление носителей повышенной критичности между сотрудниками одного подразделения выполняется в упрощённом порядке, без обязательного стирания;
+4. Ответственность за инициирование процедуры гарантированного стирания при перезакреплении носителя не закреплена за конкретной ролью.</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="85.5" customHeight="1">
       <c r="A277" s="20" t="inlineStr">
@@ -18573,14 +19642,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D277" s="34" t="inlineStr">
-        <is>
-          <t>Информация конфиденциального характера, хранящаяся на машинных носителях информации, которые физически выносятся за пределы организации (командировки, курьерская доставка, работа вне офиса), должна шифроваться во избежание утечки в случае утери или кражи такого носителя за пределами контролируемой зоны организации.</t>
-        </is>
-      </c>
-      <c r="E277" s="31" t="n"/>
-      <c r="F277" s="31" t="n"/>
-      <c r="G277" s="31" t="n"/>
+      <c r="D277" s="144" t="inlineStr">
+        <is>
+          <t>Информация конфиденциального характера, хранящаяся на машинных носителях информации, которые физически выносятся за пределы организации (командировки, курьерская доставка, работа вне офиса), должна шифроваться.
+Главная цель меры — исключить утечку конфиденциальных данных в случае утери или кражи носителя за пределами контролируемой зоны организации: физический вынос носителя за периметр лишает организацию возможности контролировать его физическую сохранность, и только криптографическая защита содержимого гарантирует, что данные останутся недоступны при утрате контроля над самим носителем.</t>
+        </is>
+      </c>
+      <c r="E277" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением средства криптографической защиты информации, шифрующего содержимое носителя (полнодисковое шифрование съёмного накопителя либо шифрование контейнера/раздела) с использованием стойкого алгоритма и аутентификацией пользователя при каждом обращении к зашифрованным данным, исключающей доступ к содержимому носителя без знания ключа (пароля) шифрования.
+Класс используемых средств — средства криптографической защиты информации (СКЗИ) для шифрования съёмных машинных носителей информации.
+Иностранные: BitLocker To Go (для носителей, используемых вне контура повышенных требований к криптографии), Kingston IronKey (аппаратно шифруемые носители) и пр.
+Российские сертифицированные (ФСБ): КриптоПро CSP (шифрование съёмных носителей), СКЗИ «Соболь»/«Верба-OW» и аналогичные сертифицированные средства криптографической защиты.
+Открытый код: VeraCrypt — применим ограниченно, требует отдельной оценки соответствия требованиям к криптографической защите.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F277" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация средства криптографической защиты, применяемого для шифрования МНИ, выносимых за пределы организации.
+2. Перечень (реестр) носителей, для которых применяется шифрование при выносе за пределы контролируемой зоны.
+3. Итоги интервью с ответственным за учёт и выдачу МНИ, выносимых за пределы организации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G277" s="151" t="inlineStr">
+        <is>
+          <t>1. Требование о шифровании распространяется не на все категории носителей, выносимых за пределы организации, в частности исключены личные устройства сотрудников с корпоративными данными;
+2. Ключ (пароль) шифрования передаётся вместе с носителем или хранится в легкодоступном месте, что нивелирует защитный эффект шифрования;
+3. Контроль фактического включения шифрования перед выносом носителя за пределы организации не проводится, полагаются на добросовестность сотрудника;
+4. Применяемое средство криптографической защиты не соответствует требованиям к используемым алгоритмам и классу криптографической защиты для обрабатываемой категории информации.</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
@@ -18611,14 +19722,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D279" s="34" t="inlineStr">
-        <is>
-          <t>Должно фиксироваться отдельным событием защиты информации использование ранее заблокированных портов ввода-вывода средств вычислительной техники, чтобы можно было заметить его дальнейшее использование в случае временной разблокировки порта для служебных целей.</t>
-        </is>
-      </c>
-      <c r="E279" s="31" t="n"/>
-      <c r="F279" s="31" t="n"/>
-      <c r="G279" s="31" t="n"/>
+      <c r="D279" s="144" t="inlineStr">
+        <is>
+          <t>Должно фиксироваться отдельным событием защиты информации использование ранее заблокированных портов ввода-вывода средств вычислительной техники (мера ПУИ.18).
+Главная цель меры — обеспечить видимость случаев временной разблокировки порта для служебных целей и последующего его использования: сам факт разблокировки порта создаёт временное окно повышенного риска, и без регистрации фактического использования разблокированного порта невозможно подтвердить, что оно ограничилось заявленной служебной задачей.</t>
+        </is>
+      </c>
+      <c r="E279" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой средства контроля устройств и портов ввода-вывода (мера ПУИ.18) на автоматическое формирование события защиты информации при каждом факте подключения устройства к порту, временно переведённому в разрешённый режим, с фиксацией типа подключённого устройства, времени и инициатора разблокировки, и передачей события в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования средства контроля устройств (Device Control), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: DeviceLock DLP (журнал использования портов), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль Device Control), MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор событий подключения устройств) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F279" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования использования разблокированных портов ввода-вывода.
+2. Выгрузка зарегистрированных фактов использования разблокированных портов за проверяемый период с сопоставлением заявленной служебной задаче.
+3. Итоги интервью с ответственным за администрирование средств контроля устройств.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G279" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируется только факт разблокировки порта, но не факт последующего фактического подключения устройства к нему;
+2. Событие не содержит сведений об инициаторе разблокировки, что не позволяет установить ответственного за принятое решение;
+3. Использование порта после истечения заявленного срока служебной необходимости не приводит к автоматической повторной блокировке и отдельному событию;
+4. События не передаются в SIEM-систему, доступны только в локальном журнале средства контроля устройств.</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="71.25" customHeight="1">
       <c r="A280" s="20" t="inlineStr">
@@ -18636,14 +19789,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D280" s="34" t="inlineStr">
-        <is>
-          <t>Каждое обращение работника к ресурсам сети Интернет должно фиксироваться как событие защиты информации. Это позволяет иметь историю обращений и установить, кто и когда посещал конкретный ресурс, и выявить причастного, если утечка данных произошла через веб-канал.</t>
-        </is>
-      </c>
-      <c r="E280" s="31" t="n"/>
-      <c r="F280" s="31" t="n"/>
-      <c r="G280" s="31" t="n"/>
+      <c r="D280" s="144" t="inlineStr">
+        <is>
+          <t>Каждое обращение работника к ресурсам сети Интернет должно фиксироваться как событие защиты информации.
+Главная цель меры — обеспечить историю обращений, позволяющую установить, кто и когда посещал конкретный ресурс, и оперативно выявить причастного сотрудника при расследовании утечки данных, произошедшей через веб-канал (меры ПУИ.2, ПУИ.11, ПУИ.12).</t>
+        </is>
+      </c>
+      <c r="E280" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой веб-прокси (шлюза доступа в Интернет) на журналирование каждого обращения пользователя к ресурсам сети Интернет с фиксацией учётной записи (или сетевого адреса, сопоставляемого с учётной записью), адреса ресурса, времени и результата (разрешено/заблокировано), и последующей передачей событий в SIEM-систему для централизованного хранения и анализа.
+Класс используемых средств — встроенный механизм журналирования веб-прокси (Secure Web Gateway) или NGFW, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Zscaler Internet Access (журнал обращений), Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate (журнал веб-фильтрации), MaxPatrol SIEM, KUMA и др.
+Открытый код: Squid (access log) в сочетании с Wazuh (централизованный сбор и анализ) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F280" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования обращений работников к ресурсам сети Интернет на веб-прокси.
+2. Выгрузка зарегистрированных обращений к ресурсам сети Интернет за проверяемый период.
+3. Итоги интервью с ответственным за администрирование сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G280" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация обращений выполняется по сетевому адресу устройства, без сопоставления с конкретной учётной записью пользователя, что затрудняет установление причастного лица;
+2. Регистрируются только заблокированные обращения, разрешённые (успешные) посещения ресурсов не фиксируются;
+3. Журнал обращений хранится с недостаточным для расследования сроком (менее срока, установленного мерами МАС.15/16 для данных регистрации);
+4. Обращения по зашифрованному (HTTPS) трафику фиксируются только по домену без детализации конкретного адреса страницы.</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="71.25" customHeight="1">
       <c r="A281" s="20" t="inlineStr">
@@ -18661,14 +19856,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D281" s="34" t="inlineStr">
-        <is>
-          <t>Каждый факт вывода информации на печать должен фиксироваться как отдельное событие защиты информации. Благодаря этому можно установить постфактум, кто, что и когда распечатал, при расследовании утечки через бумажный носитель.</t>
-        </is>
-      </c>
-      <c r="E281" s="31" t="n"/>
-      <c r="F281" s="31" t="n"/>
-      <c r="G281" s="31" t="n"/>
+      <c r="D281" s="144" t="inlineStr">
+        <is>
+          <t>Каждый факт вывода информации на печать должен фиксироваться как отдельное событие защиты информации.
+Главная цель меры — обеспечить возможность постфактум установить, кто, что и когда распечатал, при расследовании утечки конфиденциальной информации через бумажный носитель, дополняя техническую защиту, реализуемую мерами ПУИ.3, ПУИ.15, ПУИ.16.</t>
+        </is>
+      </c>
+      <c r="E281" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой сервера печати и (или) модуля контроля печати DLP-системы на журналирование каждого задания печати с фиксацией учётной записи пользователя, наименования документа, количества страниц, устройства печати и времени, и последующей передачей событий в SIEM-систему.
+Класс используемых средств — системы управления печатью (Print Management) и (или) встроенный механизм журналирования модуля контроля печати DLP-системы, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: PaperCut MF (журнал заданий печати), Forcepoint DLP и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor, MaxPatrol SIEM, KUMA и др.
+Открытый код: CUPS (журнал печати) в сочетании с Wazuh (централизованный сбор) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F281" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования фактов вывода информации на печать.
+2. Выгрузка зарегистрированных фактов печати за проверяемый период с сопоставлением конкретному пользователю и документу.
+3. Итоги интервью с ответственным за администрирование печатной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G281" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация фактов печати охватывает не все многофункциональные устройства организации, часть локальных (не сетевых) принтеров исключена из-под контроля;
+2. Событие фиксирует только факт печати и наименование документа, без сохранения содержимого или его цифрового отпечатка, что не позволяет впоследствии восстановить, что именно было напечатано;
+3. События печати не передаются в SIEM-систему, доступны только в локальной консоли сервера печати;
+4. Журнал печати не сопоставляется с результатами контентного анализа (мера ПУИ.15) для выявления случаев печати конфиденциальной информации.</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="71.25" customHeight="1">
       <c r="A282" s="20" t="inlineStr">
@@ -18686,14 +19923,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D282" s="34" t="inlineStr">
-        <is>
-          <t>Результаты контентного анализа, выполняемого мерами ПУИ.5 (почта), ПУИ.11 (веб), ПУИ.15 (печать) и ПУИ.17 (копирование на носители), должны фиксироваться как отдельные события защиты информации, включая как случаи блокировки, так и разрешённые прохождения проверки.</t>
-        </is>
-      </c>
-      <c r="E282" s="31" t="n"/>
-      <c r="F282" s="31" t="n"/>
-      <c r="G282" s="31" t="n"/>
+      <c r="D282" s="144" t="inlineStr">
+        <is>
+          <t>Результаты контентного анализа, выполняемого мерами ПУИ.5 (почта), ПУИ.11 (веб), ПУИ.15 (печать) и ПУИ.17 (копирование на носители), должны фиксироваться как отдельные события защиты информации, включая как случаи блокировки, так и разрешённые прохождения проверки.
+Главная цель меры — обеспечить единую, сводную по всем каналам утечки историю результатов контентного анализа: без такой регистрации результаты разрозненно остаются в локальных журналах каждого канала, что не позволяет проследить попытку передачи одной и той же конфиденциальной информации разными каналами (например, сначала через почту, затем через печать) как единую цепочку событий.</t>
+        </is>
+      </c>
+      <c r="E282" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой DLP-системы на формирование единого события по каждому результату контентного анализа независимо от канала (почта, веб, печать, копирование), с фиксацией канала, результата (заблокировано/разрешено), сработавшего правила и учётной записи пользователя, и передачей всех событий в единое хранилище (SIEM или собственный инцидент-модуль DLP-системы) для сквозной корреляции по всем каналам.
+Класс используемых средств — системы предотвращения утечек информации (DLP) с единым модулем инцидент-менеджмента, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Forcepoint DLP (Incident Manager), Symantec (Broadcom) DLP и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor (единая консоль инцидентов), Solar Dozor и др.
+Открытый код: полноценной единой консоли инцидент-менеджмента DLP-класса в открытых решениях практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F282" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация единого инцидент-модуля (консоли) DLP-системы, объединяющего результаты контентного анализа по всем каналам.
+2. Выгрузка зарегистрированных результатов контентного анализа за проверяемый период по каждому из каналов (почта, веб, печать, копирование).
+3. Итоги интервью с ответственным за администрирование DLP-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G282" s="151" t="inlineStr">
+        <is>
+          <t>1. Результаты контентного анализа разных каналов фиксируются в разрозненных журналах соответствующих подсистем, единая сводная регистрация не реализована;
+2. Регистрируются только заблокированные события, разрешённые прохождения контентной проверки не фиксируются, что не позволяет оценить полную картину применения меры;
+3. Сопоставление событий по разным каналам для выявления единой цепочки попыток утечки одной и той же информации не проводится;
+4. Срок хранения зарегистрированных результатов контентного анализа не соответствует установленному для данных регистрации событий защиты информации (меры МАС.15/16).</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="42.75" customHeight="1">
       <c r="A283" s="20" t="inlineStr">
@@ -18711,10 +19990,52 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D283" s="16" t="n"/>
-      <c r="E283" s="31" t="n"/>
-      <c r="F283" s="31" t="n"/>
-      <c r="G283" s="31" t="n"/>
+      <c r="D283" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого действия по учёту и снятию с учёта машинных носителей информации (МНИ), предназначенных для хранения информации конфиденциального характера (мера ПУИ.20).
+Главная цель меры — обеспечить ретроспективную прослеживаемость изменений реестра учтённых носителей: без регистрации самих действий по учёту и снятию с учёта невозможно достоверно установить, когда конкретный носитель был поставлен на учёт, кем, и когда и по чьей инициативе снят с учёта, что необходимо при расследовании инцидента, связанного с носителем.</t>
+        </is>
+      </c>
+      <c r="E283" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает регистрацию каждого действия по постановке на учёт и снятию с учёта МНИ непосредственно в реестре учтённых носителей (мера ПУИ.20) с фиксацией даты, инициатора действия и основания (приказ, служебная записка), а не только актуального статуса носителя без истории его изменений.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F283" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Реестр учтённых МНИ с историей действий по постановке на учёт и снятию с учёта (не только актуальным статусом);
+2. Выгрузка зарегистрированных действий по учёту и снятию с учёта носителей за проверяемый период;
+3. Итоги интервью с ответственным за учёт МНИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G283" s="151" t="inlineStr">
+        <is>
+          <t>1. Реестр хранит только актуальный статус носителя, история предыдущих действий по учёту и снятию с учёта не сохраняется при обновлении записи;
+2. Основание для снятия носителя с учёта (приказ, служебная записка) не фиксируется, отражается только сам факт снятия;
+3. Действия по учёту и снятию с учёта, выполненные в устной или неформальной форме, не находят отражения в реестре;
+4. Регистрация действий по учёту не защищена от последующего редактирования задним числом ответственным за ведение реестра.</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="20" t="inlineStr">
@@ -18732,10 +20053,52 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D284" s="16" t="n"/>
-      <c r="E284" s="31" t="n"/>
-      <c r="F284" s="31" t="n"/>
-      <c r="G284" s="31" t="n"/>
+      <c r="D284" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта стирания информации с машинных носителей информации (МНИ), выполненного в рамках мер ПУИ.23—ПУИ.26.
+Главная цель меры — зафиксировать отдельным событием сам факт и результат выполненного стирания, дополняя формируемый техническими средствами протокол (мера ПУИ.23) организационной регистрацией: это позволяет впоследствии подтвердить, что стирание было выполнено в отношении конкретного носителя, в установленный срок и уполномоченным лицом, а не только предъявить сам факт наличия протокола без привязки к организационному контролю.</t>
+        </is>
+      </c>
+      <c r="E284" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает регистрацию каждого факта стирания информации с МНИ в журнале (реестре) учёта носителей (мера ПУИ.20) с указанием даты стирания, применённого метода (мера ПУИ.23/24/25/26), ответственного лица и ссылки на технический протокол (сертификат) стирания как подтверждающий документ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F284" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Журнал (реестр) регистрации фактов стирания информации с МНИ со ссылкой на технические протоколы стирания;
+2. Выгрузка зарегистрированных фактов стирания за проверяемый период с сопоставлением конкретному носителю и ответственному лицу;
+3. Итоги интервью с ответственным за вывод из эксплуатации и перезакрепление МНИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G284" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрация фактов стирания в организационном журнале ведётся не по всем случаям, для части носителей имеется только технический протокол без организационной записи;
+2. Ссылка на технический протокол стирания в журнале регистрации отсутствует, что не позволяет быстро сопоставить организационную запись с техническим подтверждением;
+3. Ответственное за выполнение стирания лицо не фиксируется как отдельное поле записи;
+4. Журнал регистрации фактов стирания не защищён от редактирования задним числом.</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="13" t="inlineStr">

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -830,6 +830,9 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -20142,10 +20145,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D287" s="21" t="n"/>
-      <c r="E287" s="31" t="n"/>
-      <c r="F287" s="31" t="n"/>
-      <c r="G287" s="31" t="n"/>
+      <c r="D287" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых техническими мерами, входящими в состав системы защиты информации (СЗИ от НСД, средствами криптографической защиты, средствами защиты от вредоносного кода, DLP-системой и иными применяемыми техническими средствами защиты).
+Главная цель меры — обеспечить непрерывное наблюдение именно за тем массивом событий, который формируют сами средства защиты, поскольку он в первую очередь содержит прямые индикаторы срабатывания защитных механизмов, попыток их обхода или нарушения их штатной работы, и без организованного мониторинга такие индикаторы остаются недоступными для своевременного реагирования.</t>
+        </is>
+      </c>
+      <c r="E287" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой централизованного сбора событий, формируемых всеми техническими средствами защиты информации, в систему мониторинга (SIEM) с определением правил корреляции и приоритизации, специфичных именно для событий от СЗИ, и организацией круглосуточного наблюдения (силами собственного или привлечённого SOC) за формируемыми оповещениями.
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM), центр мониторинга и реагирования на инциденты (SOC).
+Иностранные: Splunk, IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA (Kaspersky Unified Monitoring and Analysis) и др.
+Открытый код: Wazuh, Elastic (ELK Stack) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F287" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация SIEM-системы в части сбора событий от технических средств защиты информации.
+2. Регламент мониторинга событий защиты информации, формируемых СЗИ.
+3. Итоги интервью с ответственным за мониторинг (SOC).</t>
+          </r>
+        </is>
+      </c>
+      <c r="G287" s="151" t="inlineStr">
+        <is>
+          <t>1. Мониторингом охвачены не все технические средства защиты информации, отдельные СЗИ (например, DLP-система) не подключены к централизованному сбору;
+2. Правила корреляции и приоритизации событий от СЗИ не адаптированы к специфике конкретных средств защиты, используются только общие шаблоны;
+3. Мониторинг событий организован не в круглосуточном режиме, что создаёт временные окна без наблюдения;
+4. Оповещения о срабатывании СЗИ формируются, но не имеют установленного регламентом срока и порядка реагирования.</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="85.5" customHeight="1">
       <c r="A288" s="20" t="inlineStr">
@@ -20163,14 +20212,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D288" s="34" t="inlineStr">
-        <is>
-          <t>Мониторинг должен охватывать данные регистрации, формируемые активным сетевым оборудованием — маршрутизаторами и коммутаторами. Таким образом, возможно вовремя обнаружить несанкционированное изменение конфигурации коммутатора или маршрутизатора (создание скрытого VLAN, изменение маршрутизации).</t>
-        </is>
-      </c>
-      <c r="E288" s="31" t="n"/>
-      <c r="F288" s="31" t="n"/>
-      <c r="G288" s="31" t="n"/>
+      <c r="D288" s="144" t="inlineStr">
+        <is>
+          <t>Мониторинг должен охватывать данные регистрации, формируемые активным сетевым оборудованием — маршрутизаторами и коммутаторами.
+Главная цель меры — своевременно обнаружить несанкционированное изменение конфигурации коммутатора или маршрутизатора (создание скрытого VLAN, изменение маршрутизации), которое иначе способно долгое время оставаться незамеченным на уровне вышестоящих систем мониторинга, ориентированных на иные источники событий.</t>
+        </is>
+      </c>
+      <c r="E288" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой активного сетевого оборудования (маршрутизаторов, коммутаторов) на журналирование событий, связанных с изменением конфигурации, доступом к устройству и работой протоколов маршрутизации, с последующей передачей событий по протоколу syslog в систему централизованного сбора и корреляции (SIEM).
+Класс используемых средств — встроенные средства журналирования сетевого оборудования (syslog), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Cisco (syslog, NetFlow), Splunk и пр.
+Российские сертифицированные (ФСТЭК): «Континент» (журнал управления конфигурацией), MaxPatrol SIEM, KUMA и др.
+Открытый код: rsyslog/syslog-ng (сбор с сетевого оборудования), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F288" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования и передачи событий (syslog) на образце сетевого оборудования.
+2. Выгрузка зарегистрированных событий изменения конфигурации сетевого оборудования за проверяемый период.
+3. Итоги интервью с ответственным за администрирование сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G288" s="151" t="inlineStr">
+        <is>
+          <t>1. Журналирование настроено не на всём активном сетевом оборудовании, часть устройств (в удалённых подразделениях) исключена из мониторинга;
+2. События изменения конфигурации собираются, но не сопоставляются с перечнем санкционированных изменений (регламентом управления изменениями);
+3. Локальный буфер журнала на самом сетевом устройстве ограничен по объёму и перезаписывается быстрее, чем события успевают передаваться в SIEM при временном разрыве канала;
+4. Мониторинг не выявляет факты отключения или изменения самой передачи журнала (syslog) со стороны скомпрометированного устройства.</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="71.25" customHeight="1">
       <c r="A289" s="20" t="inlineStr">
@@ -20188,20 +20279,57 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D289" s="34" t="inlineStr">
-        <is>
-          <t>Мониторинг должен охватывать данные регистрации, формируемые сетевыми приложениями и сервисами — веб-серверами, почтовыми серверами, прокси, DNS и другими сервисами инфраструктуры, чтобы вовремя обнаруживать случаи компрометации этих сервисов и приложений.</t>
-        </is>
-      </c>
-      <c r="E289" s="31" t="n"/>
-      <c r="F289" s="31" t="n"/>
-      <c r="G289" s="31" t="n"/>
-      <c r="H289" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D289" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых сетевыми приложениями и сервисами — веб-серверами, почтовыми серверами, прокси, DNS и другими сервисами инфраструктуры.
+Главная цель меры — своевременно обнаруживать случаи компрометации сетевых приложений и сервисов: именно эти компоненты, как правило, непосредственно доступны из внешней или менее доверенной сети и чаще других становятся точкой первичного проникновения, а их собственные журналы содержат специфичные для конкретного протокола или приложения индикаторы атаки, недоступные на уровне сетевого оборудования (мера МАС.2).</t>
+        </is>
+      </c>
+      <c r="E289" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой сетевых приложений и сервисов (веб-серверов, почтовых серверов, прокси, DNS-серверов) на журналирование событий доступа, ошибок и административных действий с последующей передачей событий в систему централизованного сбора и корреляции (SIEM) с правилами выявления аномалий, специфичных для каждого типа сервиса (например, признаков SQL-инъекции в журнале веб-сервера).
+Класс используемых средств — встроенные средства журналирования сетевых приложений и сервисов, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: журналы Nginx/Apache/Postfix, Splunk и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор и правила корреляции для типовых сервисов), ELK Stack и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F289" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования на образцах сетевых приложений и сервисов.
+2. Выгрузка зарегистрированных событий по сетевым приложениям и сервисам за проверяемый период.
+3. Итоги интервью с ответственным за администрирование сетевых сервисов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G289" s="151" t="inlineStr">
+        <is>
+          <t>1. Мониторингом охвачены не все сетевые приложения и сервисы, отдельные вспомогательные сервисы (внутренний DNS, прокси для тестового контура) исключены;
+2. Правила выявления аномалий не адаптированы к специфике конкретного приложения, применяются только общие сигнатуры;
+3. Уровень детализации журналирования на сервисах установлен ниже необходимого для выявления признаков компрометации (например, не фиксируются полные параметры запроса);
+4. Журналы сетевых приложений хранятся локально дольше, чем передаются в SIEM, что создаёт риск их утраты при компрометации самого сервиса.</t>
+        </is>
+      </c>
+      <c r="H289" s="168" t="n"/>
     </row>
     <row r="290" ht="99.75" customHeight="1">
       <c r="A290" s="20" t="inlineStr">
@@ -20219,20 +20347,57 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D290" s="34" t="inlineStr">
-        <is>
-          <t>Мониторинг должен охватывать события, формируемые системным ПО — операционными системами и СУБД (аутентификация, изменение прав, запуск процессов, операции с данными), чтобы вовремя обнаруживать случаи повышения привилегий или несанкционированного изменения данных в СУБД, компрометации учётной записи администратора базы данных (БД) и т.д.</t>
-        </is>
-      </c>
-      <c r="E290" s="53" t="n"/>
-      <c r="F290" s="53" t="n"/>
-      <c r="G290" s="53" t="n"/>
-      <c r="H290" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D290" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых системным ПО — операционными системами и системами управления базами данных (СУБД).
+Главная цель меры — своевременно обнаруживать случаи повышения привилегий, несанкционированного изменения данных или компрометации учётной записи администратора на уровне, максимально приближённом к самим защищаемым данным: события аутентификации, изменения прав и операций с данными на уровне ОС и СУБД зачастую являются первым (а иногда единственным) индикатором инцидента, не проявляющимся на сетевом уровне.</t>
+        </is>
+      </c>
+      <c r="E290" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой аудита операционных систем и СУБД на журналирование событий аутентификации, изменения прав доступа, запуска процессов и операций с данными, с последующей передачей событий в систему централизованного сбора и корреляции (SIEM) и правилами выявления признаков повышения привилегий и аномальных операций с данными.
+Класс используемых средств — встроенные средства аудита операционных систем и СУБД, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Windows Event Log/Sysmon, аудит Oracle/PostgreSQL, Splunk и пр.
+Российские сертифицированные (ФСТЭК): аудит отечественных ОС (Astra Linux, «РЕД ОС»), MaxPatrol SIEM, KUMA и др.
+Открытый код: auditd (Linux), Wazuh (сбор и корреляция) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F290" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация аудита на образцах операционных систем и СУБД.
+2. Выгрузка зарегистрированных событий аутентификации, изменения прав и операций с данными за проверяемый период.
+3. Итоги интервью с ответственным за администрирование ОС и СУБД.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G290" s="157" t="inlineStr">
+        <is>
+          <t>1. Аудит СУБД настроен только на уровне подключения, детальные операции с данными (SELECT/UPDATE/DELETE над критичными таблицами) не журналируются;
+2. Мониторингом охвачены не все серверы с системным ПО, тестовые и вспомогательные серверы исключены без формального обоснования;
+3. Учётные записи с максимальными привилегиями (встроенный администратор ОС/СУБД) исключены из аудита как «доверенные», что оставляет наиболее критичные действия вне контроля;
+4. Правила выявления повышения привилегий не пересматриваются при изменении ролевой модели ОС/СУБД.</t>
+        </is>
+      </c>
+      <c r="H290" s="168" t="n"/>
     </row>
     <row r="291" ht="30" customHeight="1">
       <c r="A291" s="39" t="inlineStr">
@@ -20250,16 +20415,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D291" s="84" t="n"/>
-      <c r="E291" s="40" t="n"/>
-      <c r="F291" s="40" t="n"/>
-      <c r="G291" s="40" t="n"/>
-      <c r="H291" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D291" s="169" t="inlineStr">
+        <is>
+          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых автоматизированными системами (АС) и прикладными приложениями организации.
+Главная цель меры — обеспечить видимость событий на уровне бизнес-логики самих АС (например, финансовых транзакций, изменений клиентских данных), которые не отражаются ни в журналах сетевого оборудования (мера МАС.2), ни в журналах ОС/СУБД (мера МАС.4): именно на этом уровне выявляются мошеннические операции и нарушения бизнес-процессов, невидимые на инфраструктурном уровне.</t>
+        </is>
+      </c>
+      <c r="E291" s="153" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой АС и прикладных приложений на формирование событий защиты информации, связанных с выполнением значимых бизнес-операций (аутентификация в АС, изменение критичных данных, выполнение транзакций), с последующей передачей событий в систему централизованного сбора и корреляции (SIEM) и правилами выявления признаков мошеннических операций и нарушений бизнес-логики.
+Класс используемых средств — встроенные механизмы аудита автоматизированных систем и прикладных приложений, система централизованного сбора и корреляции событий (SIEM), в отдельных случаях — специализированные антифрод-платформы.
+Иностранные: Splunk (сбор прикладных логов), SAS Fraud Management и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор прикладных логов), ELK Stack и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F291" s="153" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования событий защиты информации в АС и прикладных приложениях.
+2. Выгрузка зарегистрированных прикладных событий за проверяемый период.
+3. Итоги интервью с ответственным за эксплуатацию АС.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G291" s="153" t="inlineStr">
+        <is>
+          <t>1. Мониторингом охвачены не все АС организации, унаследованные (легаси) системы формируют события в формате, не интегрированном с SIEM;
+2. Регистрируются только технические события (вход/выход из АС), но не события уровня бизнес-логики (изменение суммы транзакции, реквизитов получателя);
+3. Правила выявления мошеннических операций и нарушений бизнес-логики не актуализируются при изменении бизнес-процессов АС;
+4. Разработчики АС не привлекаются к определению перечня событий, подлежащих регистрации, что приводит к формальному, а не содержательному покрытию.</t>
+        </is>
+      </c>
+      <c r="H291" s="168" t="n"/>
     </row>
     <row r="292" ht="30" customHeight="1">
       <c r="A292" s="20" t="inlineStr">
@@ -20277,16 +20483,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D292" s="21" t="n"/>
-      <c r="E292" s="31" t="n"/>
-      <c r="F292" s="31" t="n"/>
-      <c r="G292" s="31" t="n"/>
-      <c r="H292" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D292" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых контроллерами доменов.
+Главная цель меры — обеспечить приоритетное наблюдение за наиболее критичным компонентом инфраструктуры аутентификации и авторизации: компрометация контроллера домена предоставляет злоумышленнику контроль над учётными записями и правами доступа в масштабе всей инфраструктуры, что делает своевременное выявление признаков такой компрометации (например, необычной активности встроенных привилегированных групп) задачей повышенного приоритета по сравнению с мониторингом рядового сервера.</t>
+        </is>
+      </c>
+      <c r="E292" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой расширенного аудита безопасности на контроллерах доменов (события аутентификации, изменения групповых политик, членства в привилегированных группах, репликации каталога) с последующей передачей событий в систему централизованного сбора и корреляции (SIEM) и правилами выявления известных техник атак на инфраструктуру Active Directory (например, Kerberoasting, DCSync).
+Класс используемых средств — встроенные средства аудита службы каталогов (Active Directory и аналогичные), система централизованного сбора и корреляции событий (SIEM), специализированные средства обнаружения атак на инфраструктуру каталогов.
+Иностранные: Microsoft Defender for Identity, Splunk и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA (в том числе с готовыми правилами выявления атак на AD) и др.
+Открытый код: Wazuh (сбор событий контроллера домена), BloodHound (анализ путей эскалации привилегий, для аудита конфигурации) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F292" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация расширенного аудита безопасности на контроллерах доменов.
+2. Выгрузка зарегистрированных событий контроллеров доменов за проверяемый период, включая события изменения привилегированных групп.
+3. Итоги интервью с ответственным за администрирование службы каталогов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G292" s="151" t="inlineStr">
+        <is>
+          <t>1. Расширенный аудит безопасности настроен не на всех контроллерах доменов, часть резервных контроллеров исключена;
+2. Правила выявления известных техник атак на инфраструктуру каталогов не применяются, мониторинг ограничивается только базовыми событиями входа/выхода;
+3. Изменения членства в критичных привилегированных группах (Domain Admins и аналогичных) не выделены в отдельную категорию событий повышенного приоритета;
+4. Мониторинг событий контроллеров доменов не организован в круглосуточном режиме, несмотря на критичность данного компонента инфраструктуры.</t>
+        </is>
+      </c>
+      <c r="H292" s="168" t="n"/>
     </row>
     <row r="293" ht="57" customHeight="1">
       <c r="A293" s="20" t="inlineStr">
@@ -20305,16 +20552,57 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D293" s="21" t="n"/>
-      <c r="E293" s="31" t="n"/>
-      <c r="F293" s="31" t="n"/>
-      <c r="G293" s="31" t="n"/>
-      <c r="H293" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D293" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых средствами (системами) контроля и управления доступом (СКУД).
+Главная цель меры — распространить мониторинг событий защиты информации на физический уровень доступа: события СКУД (проход через контролируемую точку доступа, попытки прохода вне графика, срабатывание тревожных датчиков) необходимы для сопоставления с событиями логического доступа (например, для выявления входа в АС с рабочего места сотрудника, физически не присутствующего в контролируемой зоне в это время).</t>
+        </is>
+      </c>
+      <c r="E293" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы контроля и управления доступом на журналирование событий прохода через контролируемые точки доступа, попыток несанкционированного прохода и срабатывания тревожных датчиков, с последующей передачей событий в систему централизованного сбора и корреляции (SIEM) и правилами сопоставления с событиями логического доступа к информационным ресурсам.
+Класс используемых средств — встроенные средства журналирования систем контроля и управления доступом (СКУД), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: HID Global (журнал событий СКУД), Splunk и пр.
+Российские сертифицированные (ФСТЭК/аттестация физической защиты): «Sigur», Bolid («Орион») и др.
+Открытый код: полноценных СКУД-платформ данного класса в открытом коде практически не представлено, интеграция с SIEM выполняется через экспорт событий СКУД в Wazuh/ELK.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F293" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования событий системы контроля и управления доступом.
+2. Выгрузка зарегистрированных событий СКУД за проверяемый период, включая попытки несанкционированного прохода.
+3. Итоги интервью с ответственным за физическую защиту и администрирование СКУД.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G293" s="151" t="inlineStr">
+        <is>
+          <t>1. События СКУД собираются локально в собственной консоли системы, но не передаются в SIEM для сопоставления с событиями логического доступа;
+2. Мониторингом охвачены не все контролируемые точки доступа, часть второстепенных помещений исключена из системы регистрации;
+3. Правила сопоставления физического и логического доступа (выявление входа в систему при отсутствии сотрудника в контролируемой зоне) не настроены;
+4. Срабатывания тревожных датчиков и попытки несанкционированного прохода не имеют установленного регламентом порядка и срока реагирования.</t>
+        </is>
+      </c>
+      <c r="H293" s="168" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
@@ -20345,14 +20633,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D295" s="34" t="inlineStr">
-        <is>
-          <t>Данные регистрации со всех источников, определённых мерами МАС.1–МАС.7 (СЗИ, сетевое оборудование, сервисы, ОС/СУБД, АС, контроллеры доменов, средства контроля доступа), должны собираться в единую централизованную систему, а не оставаться разрозненно на каждом источнике. Тогда при расследовании инцидента, затрагивающего несколько систем, будет возможно сопоставить события из разных источников в единой точке сбора, где локальные логи реплицируются централизованно.</t>
-        </is>
-      </c>
-      <c r="E295" s="31" t="n"/>
-      <c r="F295" s="31" t="n"/>
-      <c r="G295" s="31" t="n"/>
+      <c r="D295" s="144" t="inlineStr">
+        <is>
+          <t>Данные регистрации со всех источников, определённых мерами МАС.1—МАС.7 (СЗИ, сетевое оборудование, сервисы, ОС/СУБД, АС, контроллеры доменов, средства контроля доступа), должны собираться в единую централизованную систему, а не оставаться разрозненно на каждом источнике.
+Главная цель меры — обеспечить возможность сопоставления событий из разных источников в единой точке сбора при расследовании инцидента, затрагивающего несколько систем: без централизации локальные журналы разных источников недоступны для сквозного анализа и, как правило, имеют существенно более короткий срок хранения на самом источнике, чем требуется для полноценного расследования.</t>
+        </is>
+      </c>
+      <c r="E295" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается развёртыванием системы централизованного сбора событий (SIEM), к которой подключаются все источники, определённые мерами МАС.1—МАС.7, с настройкой транспорта передачи событий (агенты сбора, syslog, API) для каждого типа источника и контролем фактического подключения каждого из них (см. также меру МАС.10 в части контроля формирования событий).
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Splunk, IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh, ELK Stack (Elasticsearch, Logstash, Kibana) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F295" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация SIEM-системы с перечнем подключённых источников, соответствующим мерам МАС.1—МАС.7.
+2. Схема транспорта передачи событий по типам источников.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G295" s="151" t="inlineStr">
+        <is>
+          <t>1. Централизованный сбор охватывает не все источники, определённые мерами МАС.1—МАС.7, отдельные категории источников передают события только в локальный журнал;
+2. Транспорт передачи событий не защищён (незашифрованный syslog по UDP), что создаёт риск потери или подмены событий в пути;
+3. Подключение нового источника инфраструктуры к централизованному сбору не является обязательным этапом процесса ввода его в эксплуатацию;
+4. Централизованная система сбора имеет единую точку отказа без резервирования, что при её недоступности прекращает сбор событий со всех источников одновременно.</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="57" customHeight="1">
       <c r="A296" s="20" t="inlineStr">
@@ -20370,10 +20700,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D296" s="21" t="n"/>
-      <c r="E296" s="31" t="n"/>
-      <c r="F296" s="31" t="n"/>
-      <c r="G296" s="31" t="n"/>
+      <c r="D296" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует генерации временных меток для данных регистрации о событиях защиты информации и синхронизации системного времени всех объектов информатизации, используемых для формирования, сбора и анализа данных регистрации, с единым источником точного времени.
+Главная цель меры — обеспечить возможность достоверно восстановить хронологическую последовательность событий, зафиксированных разными источниками: без единой синхронизации времени временные метки событий от разных систем несопоставимы между собой, что делает невозможным построение единой временной шкалы инцидента, растянутого по нескольким компонентам инфраструктуры.</t>
+        </is>
+      </c>
+      <c r="E296" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается развёртыванием службы синхронизации времени (протокол NTP) с использованием доверенного (в том числе аппаратного, например ГЛОНАСС/GPS-приёмника) источника точного времени, к которому подключаются все объекты информатизации, формирующие данные регистрации, с периодическим контролем расхождения системного времени каждого источника с эталонным.
+Класс используемых средств — серверы точного времени (NTP-серверы), в том числе с аппаратным источником синхронизации (ГЛОНАСС/GPS).
+Иностранные: встроенные NTP-клиенты операционных систем, синхронизация с публичными пулами NTP (ограниченно применимо для контура повышенных требований к доверенности источника) и пр.
+Российские сертифицированные: сертифицированные серверы точного времени с приёмником ГЛОНАСС отечественного производства и др.
+Открытый код: chrony/ntpd (клиент и сервер NTP) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F296" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация службы синхронизации времени и перечень источников точного времени.
+2. Отчёт о расхождении системного времени объектов информатизации с эталонным источником за проверяемый период.
+3. Итоги интервью с ответственным за администрирование инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G296" s="151" t="inlineStr">
+        <is>
+          <t>1. Синхронизация времени настроена не для всех объектов информатизации, формирующих данные регистрации, отдельные изолированные сегменты синхронизируются с локальным, а не единым источником;
+2. Источник точного времени, с которым синхронизируются объекты внутреннего контура, сам не проверяется на доверенность (публичный интернет-сервер без резервирования);
+3. Контроль фактического расхождения времени между объектами информатизации не автоматизирован, отклонение выявляется только по факту затруднений при расследовании инцидента;
+4. Допустимое расхождение системного времени не регламентировано, что не позволяет объективно оценить, укладывается ли фактическое отклонение в приемлемые пределы.</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="273.75" customHeight="1">
       <c r="A297" s="20" t="inlineStr">
@@ -20391,71 +20767,40 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D297" s="34" t="inlineStr">
-        <is>
-          <t>Недостаточно один раз настроить регистрацию событий на источниках (МАС.1–МАС.7) — нужно постоянно проверять, что она продолжает фактически формироваться, а не работает из-за сбоя, отключения аудита или изменения конфигурации. Мера позволяет обнаружить случаи отключения аудита администратором или злоумышленником на конкретном источнике (сервисе, ОС, сетевом устройстве).</t>
-        </is>
-      </c>
-      <c r="E297" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D297" s="144" t="inlineStr">
+        <is>
+          <t>Недостаточно один раз настроить регистрацию событий на источниках (меры МАС.1—МАС.7) — нужно постоянно проверять, что она продолжает фактически формироваться, а не прекратилась из-за сбоя, отключения аудита или изменения конфигурации.
+Главная цель меры — обнаружить случаи отключения аудита администратором или злоумышленником на конкретном источнике (сервисе, ОС, сетевом устройстве): без отдельного контроля формирования событий отсутствие данных регистрации от источника неотличимо от штатной ситуации, когда на источнике попросту не происходило значимых событий.</t>
+        </is>
+      </c>
+      <c r="E297" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - О</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Регламентация периодической ручной или полуавтоматической сверки: ответственный за ИБ по графику проверяет, что каждый источник из перечня МАС.1–МАС.7 продолжает формировать события, и фиксирует результат реализованного контроля.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Реализация - Т</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Автоматический технический контроль: система централизованного сбора (SIEM) отслеживает поток событий от каждого зарегистрированного источника и генерирует алерт при отсутствии событий дольше установленного интервала (dead source detection / health check).
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: Splunk (health check источников), Elastic Security и пр.
-- Российские сертифицированные: MaxPatrol SIEM (Positive Technologies) — контроль состояния источников событий, KUMA (Kaspersky Unified Monitoring and Analysis) и пр.
-- Открытый код: Wazuh и пр.</t>
+            <t xml:space="preserve">
+Регламентация периодической ручной или полуавтоматической сверки: ответственный за ИБ по установленному графику проверяет, что каждый источник из перечня МАС.1—МАС.7 продолжает формировать события, и документально фиксирует результат выполненной проверки.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Автоматический технический контроль обеспечивается настройкой системы централизованного сбора (SIEM) на отслеживание потока событий от каждого зарегистрированного источника и формирование оповещения при отсутствии событий дольше установленного интервала (dead source detection / health check).
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM) с функцией контроля состояния источников (health check).
+Иностранные: Splunk (health check источников), Elastic Security и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM (контроль состояния источников событий), KUMA и др.
+Открытый код: Wazuh и др.</t>
           </r>
         </is>
       </c>
@@ -20527,14 +20872,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D298" s="34" t="inlineStr">
-        <is>
-          <t>При передаче данных регистрации через сеть Интернет (например, между филиалом и центральной SIEM) должна обеспечиваться защита от раскрытия и модификации, а также двухсторонняя аутентификация сторон канала — аналогично требованию ЗВС.2, но применительно именно к потоку событий ИБ. Это необходимо для защиты от перехвата или подмены событий защиты информации, когда в пути маскируются следы атаки ещё до попадания данных в центральное хранилище, а отсутствие взаимной аутентификации не позволяет постороннему узлу выдать себя за легитимный источник и внедрить поддельные события (или заблокировать передачу настоящих).</t>
-        </is>
-      </c>
-      <c r="E298" s="31" t="n"/>
-      <c r="F298" s="31" t="n"/>
-      <c r="G298" s="31" t="n"/>
+      <c r="D298" s="144" t="inlineStr">
+        <is>
+          <t>При передаче данных регистрации через сеть Интернет (например, между филиалом и центральной SIEM) должна обеспечиваться защита от раскрытия и модификации, а также двухсторонняя аутентификация сторон канала — аналогично требованию ЗВС.2, но применительно именно к потоку событий защиты информации.
+Главная цель меры — исключить перехват или подмену событий защиты информации в пути следования, ещё до их попадания в центральное хранилище: без взаимной аутентификации сторон посторонний узел способен выдать себя за легитимный источник и внедрить поддельные события либо заблокировать (перехватить) передачу настоящих, тем самым маскируя следы атаки до того, как они станут доступны для анализа.</t>
+        </is>
+      </c>
+      <c r="E298" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением криптографического протокола защищённой передачи данных (TLS с взаимной аутентификацией сторон по сертификатам, либо VPN-туннель) для канала передачи данных регистрации через сеть Интернет, с контролем целостности передаваемых событий и отказом в приёме данных от узла, не прошедшего взаимную аутентификацию.
+Класс используемых средств — средства криптографической защиты канала передачи данных (TLS/VPN) с функцией взаимной (двухсторонней) аутентификации сторон.
+Иностранные: встроенная поддержка mTLS в транспортных агентах SIEM (Splunk Forwarder over TLS) и пр.
+Российские сертифицированные (ФСБ): КриптоПро CSP/TLS, «Континент» (VPN-модуль) и др.
+Открытый код: OpenVPN/WireGuard (VPN-туннель) в сочетании с mTLS транспортных агентов сбора событий (Wazuh, rsyslog over TLS).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F298" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация криптографической защиты и взаимной аутентификации канала передачи данных регистрации через сеть Интернет.
+2. Схема канала передачи данных регистрации между удалённым источником и центральной SIEM-системой.
+3. Итоги интервью с ответственным за администрирование канала передачи данных регистрации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G298" s="151" t="inlineStr">
+        <is>
+          <t>1. Взаимная аутентификация сторон канала не реализована, применяется только односторонняя аутентификация сервера (стандартный TLS без mTLS);
+2. Защита канала передачи распространяется не на все удалённые источники, часть филиалов передаёт события по незащищённому каналу;
+3. Сертификаты (ключи), используемые для взаимной аутентификации, не имеют установленного регламентом срока действия и порядка замены;
+4. Целостность передаваемых данных регистрации не контролируется отдельно от факта успешного установления защищённого соединения.</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="99.75" customHeight="1">
       <c r="A299" s="20" t="inlineStr">
@@ -20552,14 +20939,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D299" s="34" t="inlineStr">
-        <is>
-          <t>При централизованном сборе данных регистрация должна обеспечиваться гарантированной доставкой, чтобы события не терялись при сбоях канала связи или перегрузке системы сбора, а буферизовались и досылались повторно. Это позволяет избежать задержек и безвозвратных утечек событий безопасности, сформированных в момент кратковременного разрыва канала между источником и центральной системой.</t>
-        </is>
-      </c>
-      <c r="E299" s="53" t="n"/>
-      <c r="F299" s="53" t="n"/>
-      <c r="G299" s="53" t="n"/>
+      <c r="D299" s="144" t="inlineStr">
+        <is>
+          <t>При централизованном сборе данных регистрации должна обеспечиваться гарантированная доставка, чтобы события не терялись при сбоях канала связи или перегрузке системы сбора, а буферизовались и досылались повторно.
+Главная цель меры — избежать безвозвратной утраты событий защиты информации, сформированных в момент кратковременного разрыва канала между источником и центральной системой: без механизма гарантированной доставки именно тот интервал, когда канал связи временно недоступен, зачастую совпадает с активной фазой атаки, в течение которой злоумышленник намеренно нарушает связность инфраструктуры.</t>
+        </is>
+      </c>
+      <c r="E299" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на источниках событий (агентах сбора) локальной буферизации данных регистрации на время недоступности канала связи или перегрузки центральной системы сбора, с автоматической повторной отправкой накопленных событий после восстановления связности и подтверждением их фактического приёма центральной системой (доставка с подтверждением, at-least-once delivery).
+Класс используемых средств — агенты (форвардеры) сбора событий с функцией локальной буферизации и гарантированной доставки, промежуточные брокеры сообщений.
+Иностранные: Splunk Universal Forwarder (буферизация и повторная отправка), Kafka (промежуточный брокер) и пр.
+Российские сертифицированные (ФСТЭК): агенты сбора MaxPatrol SIEM/KUMA с функцией буферизации и др.
+Открытый код: Wazuh agent (буферизация на источнике), Filebeat + Kafka и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F299" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация агентов (форвардеров) сбора событий в части буферизации и гарантированной доставки.
+2. Результат тестового моделирования разрыва канала связи с подтверждением последующей доставки накопленных событий.
+3. Итоги интервью с ответственным за администрирование системы централизованного сбора.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G299" s="157" t="inlineStr">
+        <is>
+          <t>1. Объём локального буфера на источнике недостаточен для покрытия типичной продолжительности разрыва канала связи, что приводит к частичной потере событий при длительных сбоях;
+2. Подтверждение фактического приёма события центральной системой не контролируется, форвардер считает событие доставленным сразу после отправки;
+3. Гарантированная доставка настроена не для всех источников, критичные с точки зрения объёма событий источники (например, DLP-система) исключены из механизма буферизации;
+4. Факты срабатывания буферизации (временной недоступности канала) не регистрируются как отдельное событие (см. также меру МАС.21).</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="99.75" customHeight="1">
       <c r="A300" s="20" t="inlineStr">
@@ -20577,14 +21006,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D300" s="34" t="inlineStr">
-        <is>
-          <t>Должен быть зарезервирован объём памяти под хранение данных регистрации (которые финансовая организация выбрала к регистрации), достаточный для хранения событий в течение установленного срока без риска переполнения хранилища. В ином случае переполнение хранилища приводит к перезаписи старых событий раньше установленного срока хранения, и данные, нужные для расследования, оказываются утрачены.</t>
-        </is>
-      </c>
-      <c r="E300" s="31" t="n"/>
-      <c r="F300" s="31" t="n"/>
-      <c r="G300" s="31" t="n"/>
+      <c r="D300" s="144" t="inlineStr">
+        <is>
+          <t>Должен быть зарезервирован объём памяти под хранение данных регистрации (которые финансовая организация выбрала к регистрации), достаточный для хранения событий в течение установленного срока без риска переполнения хранилища.
+Главная цель меры — предотвратить преждевременную (до истечения установленного срока хранения) перезапись старых событий вследствие переполнения хранилища: без заблаговременного расчёта и резервирования необходимого объёма памяти данные, необходимые для расследования инцидента, могут оказаться безвозвратно утрачены задолго до истечения формально установленного срока их хранения (меры МАС.15/16).</t>
+        </is>
+      </c>
+      <c r="E300" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается расчётом необходимого объёма хранилища данных регистрации исходя из фактической интенсивности потока событий от всех подключённых источников (мера МАС.8) и установленного срока хранения, с заблаговременным резервированием этого объёма и настройкой автоматического оповещения при приближении фактической заполненности хранилища к пороговому значению, требующему расширения.
+Класс используемых средств — система хранения данных (СХД), масштабируемая подсистема хранения событий в составе SIEM-платформы.
+Иностранные: масштабируемые индексные кластеры Splunk, IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): подсистема хранения MaxPatrol SIEM/KUMA и др.
+Открытый код: масштабируемый кластер Elasticsearch (в составе ELK Stack) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F300" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Расчёт необходимого объёма хранилища данных регистрации исходя из интенсивности потока событий и установленного срока хранения.
+2. Конфигурация системы хранения с указанием фактически зарезервированного объёма и настроенных пороговых оповещений о заполненности.
+3. Отчёт о фактической динамике заполнения хранилища данных регистрации за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G300" s="151" t="inlineStr">
+        <is>
+          <t>1. Расчёт необходимого объёма хранилища выполнен без учёта роста интенсивности потока событий при подключении новых источников;
+2. Пороговое оповещение о приближении к заполненности хранилища не настроено, переполнение выявляется только по факту начавшейся перезаписи данных;
+3. Резервирование объёма выполнено формально (по факту закупки оборудования), без периодического пересчёта фактической достаточности;
+4. При достижении предела хранилища происходит автоматическая перезапись данных без предварительной архивации в более дешёвое (холодное) хранилище с более длительным сроком.</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="128.25" customHeight="1">
       <c r="A301" s="20" t="inlineStr">
@@ -20602,14 +21073,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D301" s="34" t="inlineStr">
-        <is>
-          <t>Хранимые данные регистрации о событий защиты информации должны быть защищены от НСД, а их целостность и доступность — обеспечены (хеширование, резервное копирование, разграничение доступа). Мера не позволит злоумышленнику, получившему доступ к хранилищу логов, изменять или удалять записи о своих действиях, скрывая следы атаки, а наличие резервного копирования спасёт от безвозвратной потери всей истории событий в случае сбоя хранилища.</t>
-        </is>
-      </c>
-      <c r="E301" s="31" t="n"/>
-      <c r="F301" s="31" t="n"/>
-      <c r="G301" s="31" t="n"/>
+      <c r="D301" s="144" t="inlineStr">
+        <is>
+          <t>Хранимые данные регистрации о событиях защиты информации должны быть защищены от несанкционированного доступа, а их целостность и доступность — обеспечены (хеширование, резервное копирование, разграничение доступа).
+Главная цель меры — не допустить, чтобы злоумышленник, получивший доступ к хранилищу журналов (в том числе администратор с расширенными правами), мог изменять или удалять записи о собственных действиях, тем самым скрывая следы атаки; наличие резервного копирования дополнительно защищает от безвозвратной потери всей истории событий при сбое самого хранилища.</t>
+        </is>
+      </c>
+      <c r="E301" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается разграничением доступа к хранилищу данных регистрации по принципу минимально необходимых полномочий (с исключением возможности удаления или модификации записей даже для администраторов SIEM-системы в штатном режиме работы), применением средств контроля целостности хранимых данных (хеш-цепочки записей, WORM-хранилище — write once, read many) и регулярным резервным копированием.
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM) с функцией разграничения доступа и контроля целостности хранимых данных, средства резервного копирования.
+Иностранные: Splunk (ролевая модель доступа, индексная целостность), Veeam Backup &amp; Replication и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM/KUMA (разграничение доступа к архиву событий), «Кибер Бэкап» и др.
+Открытый код: Elasticsearch (ролевая модель X-Pack Security), immutable-хранилище на базе объектного хранилища с политикой WORM.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F301" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация разграничения доступа к хранилищу данных регистрации с указанием полномочий отдельных ролей.
+2. Конфигурация средства контроля целостности хранимых данных регистрации.
+3. Отчёт о выполненном резервном копировании данных регистрации за проверяемый период и результат тестового восстановления.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G301" s="151" t="inlineStr">
+        <is>
+          <t>1. Учётные записи администраторов SIEM-системы фактически обладают полномочиями на удаление и модификацию хранимых записей в штатном режиме работы;
+2. Контроль целостности хранимых данных регистрации не реализован, изменение отдельной записи в хранилище технически не выявляется;
+3. Резервное копирование данных регистрации выполняется, но тестовое восстановление из резервной копии не проводится, фактическая пригодность копий не подтверждена;
+4. Резервные копии данных регистрации хранятся в той же зоне доступа, что и основное хранилище, без изоляции от единой точки компрометации.</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="28.5" customHeight="1">
       <c r="A302" s="20" t="inlineStr">
@@ -20627,10 +21140,56 @@
           <t>Т-Т-Н</t>
         </is>
       </c>
-      <c r="D302" s="21" t="n"/>
-      <c r="E302" s="31" t="n"/>
-      <c r="F302" s="31" t="n"/>
-      <c r="G302" s="31" t="n"/>
+      <c r="D302" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует обеспечения возможности доступа к данным регистрации о событиях защиты информации в течение трёх лет с момента их формирования.
+Главная цель меры — установить минимальный срок доступности данных регистрации, достаточный для расследования инцидентов, факт которых был обнаружен со значительной задержкой относительно момента их совершения: многие целенаправленные атаки и мошеннические схемы выявляются далеко не сразу, и без установленного минимального срока доступности исходные данные регистрации к моменту обнаружения могут быть уже безвозвратно утрачены.</t>
+        </is>
+      </c>
+      <c r="E302" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается организацией многоуровневого хранения данных регистрации: оперативное (быстрый поиск) хранение на индексном хранилище SIEM-системы на протяжении ближайшего периода и последующая архивация в более дешёвое (холодное) хранилище с сохранением возможности поиска и восстановления данных на протяжении не менее трёх лет с момента их формирования.
+Класс используемых средств — система хранения данных (СХД) с многоуровневой архитектурой (оперативное/архивное хранилище) в составе или в сочетании с SIEM-платформой.
+Иностранные: Splunk (SmartStore, архивные индексы), объектное хранилище класса Amazon S3 Glacier (для архивного уровня) и пр.
+Российские сертифицированные (ФСТЭК): архивная подсистема MaxPatrol SIEM/KUMA, отечественные объектные хранилища для архивного уровня.
+Открытый код: Elasticsearch (архивные индексы с холодным/замороженным уровнем хранения, ILM) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F302" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация многоуровневого хранения данных регистрации с указанием фактического срока хранения на архивном уровне.
+2. Результат тестового поиска и восстановления данных регистрации за период, приближающийся к трёхлетнему сроку.
+3. Итоги интервью с ответственным за администрирование системы хранения данных регистрации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G302" s="151" t="inlineStr">
+        <is>
+          <t>1. Фактический срок хранения данных регистрации на архивном уровне меньше установленного мерой трёхлетнего минимума из-за ограниченного объёма архивного хранилища;
+2. Доступ к данным регистрации, перенесённым в архивное хранилище, требует ручного восстановления администратором и не может быть выполнен оперативно при расследовании;
+3. Требование о трёхлетнем сроке доступности распространяется не на все источники данных регистрации, определённые мерами МАС.1—МАС.7;
+4. Целостность архивных данных регистрации за длительный период не контролируется отдельно от контроля целостности оперативного хранилища (мера МАС.14).</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="42.75" customHeight="1">
       <c r="A303" s="20" t="inlineStr">
@@ -20649,10 +21208,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D303" s="21" t="n"/>
-      <c r="E303" s="53" t="n"/>
-      <c r="F303" s="53" t="n"/>
-      <c r="G303" s="53" t="n"/>
+      <c r="D303" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична МАС.15, но устанавливает повышенный, пятилетний минимальный срок обеспечения доступа к данным регистрации о событиях защиты информации — для уровня защиты, требующего более длительной ретроспективной доступности.
+Главная цель меры — обеспечить тот же результат доступности данных регистрации для расследования инцидентов с длительным периодом обнаружения, что и мера МАС.15, но применительно к объектам защиты повышенной критичности, для которых регуляторные и договорные требования предполагают более продолжительный период ретроспективного анализа.</t>
+        </is>
+      </c>
+      <c r="E303" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация аналогична мере МАС.15 и обеспечивается той же многоуровневой архитектурой хранения данных регистрации, рассчитанной на увеличенный, не менее пятилетний срок доступности данных на архивном уровне хранения.
+Класс используемых средств — система хранения данных (СХД) с многоуровневой архитектурой (оперативное/архивное хранилище) в составе или в сочетании с SIEM-платформой.
+Иностранные: Splunk (SmartStore, архивные индексы), объектное хранилище класса Amazon S3 Glacier Deep Archive и пр.
+Российские сертифицированные (ФСТЭК): архивная подсистема MaxPatrol SIEM/KUMA, отечественные объектные хранилища для архивного уровня.
+Открытый код: Elasticsearch (замороженный уровень хранения, ILM с длительным сроком) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F303" s="157" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация многоуровневого хранения данных регистрации с указанием фактического пятилетнего срока хранения на архивном уровне.
+2. Расчёт необходимого объёма архивного хранилища исходя из пятилетнего срока и интенсивности потока событий.
+3. Результат тестового поиска и восстановления данных регистрации за период, приближающийся к пятилетнему сроку.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G303" s="157" t="inlineStr">
+        <is>
+          <t>1. Пятилетний срок хранения применяется не для всех объектов защиты, требующих данного уровня, часть систем архивирует данные регистрации по сокращённому (трёхлетнему) сроку меры МАС.15;
+2. Объём архивного хранилища не рассчитан на фактическую нагрузку при увеличенном до пяти лет сроке хранения, что создаёт риск переполнения задолго до истечения срока;
+3. Носители архивного хранилища (например, ленточные накопители) не проходят периодическую проверку читаемости на протяжении длительного срока хранения;
+4. Доступ к данным пятилетней давности требует привлечения стороннего подрядчика (поставщика архивного решения), что не позволяет уложиться в разумные сроки при реальном расследовании.</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
@@ -20683,14 +21288,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D305" s="34" t="inlineStr">
-        <is>
-          <t>Система обработки данных регистрации должна уметь приводить события от разных источников к единому формату (нормализация), а также фильтровать, агрегировать и классифицировать их — без этого разнородные логи невозможно анализировать вместе, ведь события от разных источников могут храниться в несовместимых форматах и могут не сопоставляться по умолчанию при расследовании инцидента.</t>
-        </is>
-      </c>
-      <c r="E305" s="31" t="n"/>
-      <c r="F305" s="31" t="n"/>
-      <c r="G305" s="31" t="n"/>
+      <c r="D305" s="144" t="inlineStr">
+        <is>
+          <t>Система обработки данных регистрации должна уметь приводить события от разных источников к единому формату (нормализация), а также фильтровать, агрегировать и классифицировать их.
+Главная цель меры — сделать разнородные журналы разных источников пригодными для совместного анализа: события от различных систем, как правило, хранятся в несовместимых форматах и не сопоставляются между собой без предварительной обработки, что без нормализации, фильтрации и агрегации делает невозможным сквозной анализ данных регистрации при расследовании инцидента.</t>
+        </is>
+      </c>
+      <c r="E305" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой в системе централизованного сбора событий (SIEM) парсеров (правил разбора), приводящих события от каждого типа источника к единой внутренней модели данных (нормализация), а также правил фильтрации незначимых событий, агрегации повторяющихся событий и классификации по типу и категории защиты информации.
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM) с модулем нормализации, фильтрации и классификации данных регистрации.
+Иностранные: Splunk (Common Information Model), IBM QRadar (DSM-парсеры) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM/KUMA (готовые и настраиваемые правила нормализации) и др.
+Открытый код: Logstash/Elastic Common Schema (нормализация в составе ELK Stack) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F305" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация правил нормализации, фильтрации, агрегации и классификации данных регистрации в SIEM-системе.
+2. Перечень источников, для которых настроены и фактически применяются правила нормализации.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G305" s="151" t="inlineStr">
+        <is>
+          <t>1. Правила нормализации настроены не для всех подключённых источников (мера МАС.8), события части источников поступают в необработанном (сыром) виде;
+2. Правила фильтрации настроены избыточно широко и отсеивают события, впоследствии оказывающиеся значимыми для расследования;
+3. Классификация событий по категориям защиты информации не актуализируется при появлении новых типов источников;
+4. Новые парсеры (правила нормализации) для нетиповых источников разрабатываются со значительной задержкой после фактического подключения источника.</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="99.75" customHeight="1">
       <c r="A306" s="20" t="inlineStr">
@@ -20708,14 +21355,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D306" s="34" t="inlineStr">
-        <is>
-          <t>Система обработки данных регистрации должна обеспечивать автоматическое выявление и анализ событий, потенциально связанных с инцидентами защиты информации, включая НСД — например, через корреляционные правила, а не просто хранить сырые логи. Этот механизм выявления связанных событий позволяет сложить в единую картину атаку, растянувшуюся во времени и по разным источникам.</t>
-        </is>
-      </c>
-      <c r="E306" s="31" t="n"/>
-      <c r="F306" s="31" t="n"/>
-      <c r="G306" s="31" t="n"/>
+      <c r="D306" s="144" t="inlineStr">
+        <is>
+          <t>Система обработки данных регистрации должна обеспечивать автоматическое выявление и анализ событий, потенциально связанных с инцидентами защиты информации, включая несанкционированный доступ, — например, через корреляционные правила, а не простое хранение сырых журналов.
+Главная цель меры — сложить в единую картину атаку, растянутую во времени и по разным источникам: отдельное событие, зафиксированное на одном источнике, зачастую не выглядит подозрительным само по себе, и только автоматизированная корреляция цепочки связанных событий разных источников позволяет своевременно выявить признаки развивающегося инцидента.</t>
+        </is>
+      </c>
+      <c r="E306" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой в системе централизованного сбора событий (SIEM) корреляционных правил и (или) моделей поведенческого анализа (UEBA), автоматически сопоставляющих связанные по времени, субъекту или ресурсу события разных источников и формирующих инцидент при выявлении цепочки, соответствующей известному сценарию атаки или аномальному поведению.
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM) с модулем корреляционных правил, средства поведенческого анализа пользователей и сущностей (User and Entity Behavior Analytics, UEBA).
+Иностранные: Splunk Enterprise Security, IBM QRadar (корреляционные правила) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM/KUMA (встроенные и настраиваемые корреляционные правила) и др.
+Открытый код: Wazuh (правила корреляции), Sigma (открытый формат описания правил обнаружения) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F306" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень (база) корреляционных правил, применяемых в SIEM-системе.
+2. Выгрузка сформированных инцидентов защиты информации по результатам автоматического выявления за проверяемый период.
+3. Итоги интервью с ответственным за мониторинг (SOC) и анализ данных регистрации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G306" s="151" t="inlineStr">
+        <is>
+          <t>1. База корреляционных правил не пересматривается и не пополняется при появлении новых известных техник атак (например, по матрице MITRE ATT&amp;CK);
+2. Корреляционные правила покрывают не все источники, подключённые к централизованному сбору, часть источников фактически исключена из автоматического анализа;
+3. Результаты срабатывания корреляционных правил (потенциальные инциденты) не имеют установленного регламентом порядка и срока первичного разбора;
+4. Эффективность корреляционных правил (доля ложных срабатываний, случаи пропуска реальных инцидентов) не оценивается на регулярной основе.</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="99.75" customHeight="1">
       <c r="A307" s="20" t="inlineStr">
@@ -20733,14 +21422,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D307" s="34" t="inlineStr">
-        <is>
-          <t>Система обработки данных регистрации должна позволять получить полный перечень действий и операций конкретного субъекта доступа за заданный период — то есть строить историю «что делал конкретный пользователь». Это необходимо для расследования активности пользователя при подозрении на инсайдерскую деятельность или компрометацию учётной записи.</t>
-        </is>
-      </c>
-      <c r="E307" s="31" t="n"/>
-      <c r="F307" s="31" t="n"/>
-      <c r="G307" s="31" t="n"/>
+      <c r="D307" s="144" t="inlineStr">
+        <is>
+          <t>Система обработки данных регистрации должна позволять получить полный перечень действий и операций конкретного субъекта доступа за заданный период — то есть строить историю «что делал конкретный пользователь».
+Главная цель меры — обеспечить возможность расследования активности конкретного пользователя при подозрении на инсайдерскую деятельность или компрометацию его учётной записи: без возможности выборки по субъекту доступа аналитик вынужден вручную просматривать разрозненные события множества источников, что делает подобное расследование практически неосуществимым в разумные сроки.</t>
+        </is>
+      </c>
+      <c r="E307" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой в системе централизованного сбора событий (SIEM) сквозной идентификации субъекта доступа во всех нормализованных событиях (единый идентификатор учётной записи, сопоставляемый между разными источниками, в том числе при использовании разных логинов в разных системах) и функции построения выборки (таймлайна) всех действий конкретного субъекта за заданный период по всем подключённым источникам.
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM) с функцией построения выборки действий по субъекту доступа (user activity timeline).
+Иностранные: Splunk (User Activity dashboard), IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM/KUMA (карточка пользователя с историей действий) и др.
+Открытый код: Wazuh/ELK Stack (построение выборки по полю пользователя средствами поискового запроса) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F307" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация SIEM-системы в части сквозной идентификации субъекта доступа между источниками.
+2. Результат тестового построения выборки всех действий конкретного субъекта доступа за заданный период.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G307" s="151" t="inlineStr">
+        <is>
+          <t>1. Сквозная идентификация субъекта доступа не реализована для всех источников, при использовании разных учётных записей в разных системах действия одного и того же сотрудника не сопоставляются автоматически;
+2. Построение выборки действий субъекта доступа возможно только в пределах оперативного (быстрого) хранилища, но не по данным, перенесённым в архив (меры МАС.15/16);
+3. Выборка по субъекту доступа не включает события систем, для которых не настроена нормализация (мера МАС.17), такие источники приходится анализировать отдельно вручную;
+4. Время построения выборки по субъекту доступа за длительный период существенно превышает практически приемлемое для оперативного расследования.</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="128.25" customHeight="1">
       <c r="A308" s="20" t="inlineStr">
@@ -20758,14 +21489,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D308" s="34" t="inlineStr">
-        <is>
-          <t>Система обработки данных регистрации должна позволять получить полный перечень действий субъектов доступа применительно к конкретному ресурсу доступа — то есть строить историю «кто обращался к конкретному ресурсу», в отличие от МАС.19, где выборка идёт от субъекта. В данном случае выборка именно по ресурсу. Мера помогает при инциденте, связанном с компрометацией или утечкой конкретного ресурса (базы данных, файла, сервера), быстро установить круг лиц, обращавшихся к нему.</t>
-        </is>
-      </c>
-      <c r="E308" s="31" t="n"/>
-      <c r="F308" s="31" t="n"/>
-      <c r="G308" s="31" t="n"/>
+      <c r="D308" s="144" t="inlineStr">
+        <is>
+          <t>Система обработки данных регистрации должна позволять получить полный перечень действий субъектов доступа применительно к конкретному ресурсу доступа — то есть строить историю «кто обращался к конкретному ресурсу», в отличие от меры МАС.19, где выборка строится от субъекта, а здесь — от ресурса.
+Главная цель меры — при инциденте, связанном с компрометацией или утечкой конкретного ресурса (базы данных, файла, сервера), быстро установить полный круг лиц, обращавшихся к нему за интересующий период, что невозможно, если система обработки данных регистрации позволяет строить выборки только по субъекту, но не по объекту доступа.</t>
+        </is>
+      </c>
+      <c r="E308" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой в системе централизованного сбора событий (SIEM) сквозной идентификации ресурса доступа во всех нормализованных событиях (единый идентификатор ресурса, сопоставляемый между разными источниками при обращении к нему разными способами) и функции построения выборки всех действий субъектов доступа применительно к конкретному ресурсу за заданный период.
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM) с функцией построения выборки действий по объекту (ресурсу) доступа.
+Иностранные: Splunk (Asset and Identity framework), IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM/KUMA (карточка актива с историей обращений) и др.
+Открытый код: Wazuh/ELK Stack (построение выборки по полю ресурса средствами поискового запроса) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F308" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация SIEM-системы в части сквозной идентификации ресурса доступа между источниками.
+2. Результат тестового построения выборки всех действий субъектов доступа применительно к конкретному ресурсу за заданный период.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G308" s="151" t="inlineStr">
+        <is>
+          <t>1. Сквозная идентификация ресурса не реализована для всех источников, при обращении к ресурсу через разные точки доступа (например, напрямую к серверу и через прикладной интерфейс АС) события не сопоставляются автоматически;
+2. Перечень ресурсов, для которых обеспечена возможность построения выборки по объекту доступа, не пересматривается при вводе в эксплуатацию новых информационных ресурсов;
+3. Построение выборки по ресурсу возможно только в пределах оперативного хранилища, но не по данным, перенесённым в архив (меры МАС.15/16);
+4. Выборка по ресурсу не позволяет отдельно выделить обращения с использованием привилегированных учётных записей, значимые с точки зрения приоритета расследования.</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="13" t="inlineStr">
@@ -20796,14 +21569,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D310" s="34" t="inlineStr">
-        <is>
-          <t>Любые нарушения и сбои в самом процессе формирования и сбора данных регистрации должны фиксироваться как отдельные события защиты информации — это дополняет контроль формирования, обеспечивая фактическую историю таких сбоев для анализа, чтобы в случае повторяющихся сбоев сбора событий с конкретного источника выявлять следы злоумышленника, вызывающего отказ агента сбора логов на скомпрометированном узле.</t>
-        </is>
-      </c>
-      <c r="E310" s="31" t="n"/>
-      <c r="F310" s="31" t="n"/>
-      <c r="G310" s="31" t="n"/>
+      <c r="D310" s="144" t="inlineStr">
+        <is>
+          <t>Любые нарушения и сбои в самом процессе формирования и сбора данных регистрации должны фиксироваться как отдельные события защиты информации, дополняя контроль формирования (мера МАС.10) фактической историей таких сбоев для последующего анализа.
+Главная цель меры — выявлять повторяющиеся сбои сбора событий с конкретного источника как возможный след злоумышленника, намеренно вызывающего отказ агента сбора журналов на скомпрометированном узле: единичный сбой, как правило, является технической случайностью, тогда как системность сбоев по конкретному источнику — значимый индикатор для расследования.</t>
+        </is>
+      </c>
+      <c r="E310" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы централизованного сбора событий (SIEM) на автоматическое формирование отдельного события при выявлении нарушения или сбоя в процессе формирования и сбора данных регистрации (отказ агента сбора, ошибка парсинга/нормализации, разрыв канала передачи) с фиксацией источника, времени и характера сбоя, и последующим анализом истории сбоев на предмет системности по конкретному источнику.
+Класс используемых средств — встроенный механизм журналирования системы централизованного сбора событий (SIEM), функция контроля состояния источников и агентов сбора (health check).
+Иностранные: Splunk (внутренние логи Forwarder/Indexer), IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM/KUMA (журнал состояния источников и агентов сбора) и др.
+Открытый код: Wazuh (журнал состояния агентов), Elastic Stack Monitoring и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F310" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования нарушений и сбоев в формировании и сборе данных регистрации.
+2. Выгрузка зарегистрированных нарушений и сбоев за проверяемый период с анализом системности по источникам.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G310" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только полные отказы агента сбора, частичные сбои (ошибки нормализации отдельных событий) не фиксируются как отдельная категория;
+2. Анализ системности повторяющихся сбоев по конкретному источнику на предмет признаков компрометации не проводится, каждый сбой рассматривается изолированно;
+3. Оповещение о сбое сбора данных регистрации не имеет установленного регламентом срока реагирования;
+4. Сбои, вызванные плановыми регламентными работами на источнике, не отделяются от внеплановых сбоев, что затрудняет выявление действительно значимых случаев.</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="85.5" customHeight="1">
       <c r="A311" s="20" t="inlineStr">
@@ -20821,14 +21636,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D311" s="34" t="inlineStr">
-        <is>
-          <t>Каждое обращение к хранимым данным регистрации событий защиты информации должно фиксироваться отдельным событием — кто, когда и к каким именно данным обращался. Это необходимо для расследования случаев, когда администратор или злоумышленник просматривает или экспортирует чувствительные логи.</t>
-        </is>
-      </c>
-      <c r="E311" s="31" t="n"/>
-      <c r="F311" s="31" t="n"/>
-      <c r="G311" s="31" t="n"/>
+      <c r="D311" s="144" t="inlineStr">
+        <is>
+          <t>Каждое обращение к хранимым данным регистрации событий защиты информации должно фиксироваться отдельным событием — кто, когда и к каким именно данным обращался.
+Главная цель меры — обеспечить возможность расследования случаев, когда администратор или злоумышленник, получивший доступ к хранилищу событий, просматривает или экспортирует чувствительные данные регистрации: само хранилище содержит сведения обо всей активности инфраструктуры, и доступ к нему без отдельного контроля способен использоваться для разведки перед атакой или для сокрытия следов уже совершённых действий.</t>
+        </is>
+      </c>
+      <c r="E311" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы централизованного сбора событий (SIEM) на аудит собственных операций доступа к хранимым данным регистрации (поисковые запросы, экспорт данных, административные действия) с фиксацией учётной записи, времени и объёма затронутых данных, и передачей таких событий в отдельный, изолированный от общего потока журнал.
+Класс используемых средств — встроенный механизм аудита действий пользователей SIEM-системы (audit trail).
+Иностранные: Splunk (внутренний индекс _audit), IBM QRadar (журнал аудита) и пр.
+Российские сертифицированные (ФСТЭК): встроенный аудит действий пользователей MaxPatrol SIEM/KUMA и др.
+Открытый код: Elasticsearch/Kibana (журнал аудита X-Pack Security) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F311" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация аудита доступа к хранимым данным регистрации в SIEM-системе.
+2. Выгрузка зарегистрированных фактов доступа к хранимым данным регистрации за проверяемый период.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G311" s="151" t="inlineStr">
+        <is>
+          <t>1. Аудит доступа к хранимым данным регистрации охватывает только административные действия (изменение конфигурации), но не сами поисковые запросы и просмотр данных аналитиками;
+2. Журнал аудита доступа к данным регистрации хранится в общем индексе вместе с прочими событиями, а не изолированно, что не защищает его от модификации тем же администратором;
+3. Экспорт (выгрузка) данных регистрации за пределы SIEM-системы не фиксируется как отдельное событие повышенной значимости;
+4. Аудит доступа не распространяется на данные регистрации, перенесённые в архивное хранилище (меры МАС.15/16).</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="85.5" customHeight="1">
       <c r="A312" s="20" t="inlineStr">
@@ -20846,14 +21703,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D312" s="34" t="inlineStr">
-        <is>
-          <t>Изменения правил нормализации, фильтрации, агрегации и классификации данных регистрации должны фиксироваться отдельным событием защиты информации — кто, когда и что именно изменил в логике обработки событий. Это необходимо для расследования подмены правил фильтрации злоумышленником или администратором.</t>
-        </is>
-      </c>
-      <c r="E312" s="31" t="n"/>
-      <c r="F312" s="31" t="n"/>
-      <c r="G312" s="31" t="n"/>
+      <c r="D312" s="144" t="inlineStr">
+        <is>
+          <t>Изменения правил нормализации, фильтрации, агрегации и классификации данных регистрации (мера МАС.17) должны фиксироваться отдельным событием защиты информации — кто, когда и что именно изменил в логике обработки событий.
+Главная цель меры — исключить возможность скрытого искажения логики обработки данных регистрации: изменение правила фильтрации или нормализации способно избирательно «ослепить» систему мониторинга в отношении определённого типа событий (например, исключить из анализа события конкретной учётной записи), и без регистрации самого факта такого изменения подобное искажение может долго оставаться незамеченным.</t>
+        </is>
+      </c>
+      <c r="E312" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы централизованного сбора событий (SIEM) на аудит изменений собственной конфигурации в части правил нормализации, фильтрации, агрегации и классификации данных регистрации, с фиксацией учётной записи, времени изменения и содержания внесённой правки (сравнение версии правила до и после изменения), и передачей таких событий в изолированный журнал аудита конфигурации.
+Класс используемых средств — встроенный механизм аудита изменения конфигурации SIEM-системы (audit trail, контроль версий правил).
+Иностранные: Splunk (журнал изменений конфигурации, версионирование), IBM QRadar и пр.
+Российские сертифицированные (ФСТЭК): встроенный аудит изменения правил обработки MaxPatrol SIEM/KUMA и др.
+Открытый код: контроль версий правил через git-репозиторий конфигурации (например, для Logstash/Sigma-правил) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F312" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация аудита изменения правил нормализации, фильтрации, агрегации и классификации данных регистрации в SIEM-системе.
+2. Выгрузка зарегистрированных изменений правил обработки данных регистрации за проверяемый период с сопоставлением регламенту внесения изменений.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G312" s="151" t="inlineStr">
+        <is>
+          <t>1. Аудит изменений правил обработки данных регистрации не выявляет изменения, внесённые в обход штатного интерфейса управления (например, прямым редактированием конфигурационного файла);
+2. Зарегистрированные изменения правил не сопоставляются с регламентом внесения изменений (мерой управления изменениями), любое изменение считается допустимым без проверки согласования;
+3. Содержание внесённой правки (что именно изменилось в правиле) не фиксируется, регистрируется только факт изменения без деталей;
+4. Журнал аудита изменения конфигурации не изолирован от общего потока данных регистрации и потенциально доступен для модификации тем же кругом лиц, чьи действия он призван контролировать.</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="13" t="n"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -21779,20 +21779,84 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D314" s="34" t="inlineStr">
-        <is>
-          <t>События, выявленные в ходе мониторинга и анализа и потенциально указывающие на инцидент ИБ, включая НСД, должны регистрироваться отдельно — как алерты, требующие дальнейшей обработки, а не растворяться в общем потоке логов. Это позволяет не терять конкретные критические события и потенциальные инциденты среди тысяч рядовых событий.</t>
-        </is>
-      </c>
-      <c r="E314" s="31" t="n"/>
-      <c r="F314" s="31" t="n"/>
-      <c r="G314" s="31" t="n"/>
-      <c r="H314" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D314" s="144" t="inlineStr">
+        <is>
+          <t>События, выявленные в ходе мониторинга и анализа (меры МАС.17—МАС.20) и потенциально указывающие на инцидент защиты информации, включая НСД, должны регистрироваться отдельно — как алерты, требующие дальнейшей обработки, а не растворяться в общем потоке рядовых событий.
+Главная цель меры — не допустить, чтобы конкретное критическое событие или потенциальный инцидент оказались потеряны среди тысяч рядовых событий: без выделенной регистрации таких событий их обработка целиком зависит от того, заметит ли их аналитик вручную, что при большом объёме потока событий защиты информации практически неосуществимо.</t>
+        </is>
+      </c>
+      <c r="E314" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Регламентацию критериев, по которым событие защиты информации признаётся потенциально связанным с инцидентом (в том числе с НСД) и подлежит отдельной регистрации;
+2. Определение порядка передачи зарегистрированного потенциального инцидента от системы мониторинга к группе реагирования на инциденты защиты информации (ГРИЗИ, меры РИ.7—РИ.9).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы централизованного сбора и корреляции событий (SIEM) на автоматическое формирование отдельной карточки (тикета) при срабатывании корреляционного правила или иного признака потенциального инцидента (мера МАС.18), с выделением такой карточки в отдельную очередь обработки, не пересекающуюся с общим потоком сырых событий.
+Класс используемых средств — система централизованного сбора и корреляции событий (SIEM) с модулем управления инцидентами (Incident Response / Case Management), нередко реализуемым в виде отдельной SOAR-платформы.
+Иностранные: Splunk (Notable Events), IBM QRadar (Offenses) и пр.
+Российские сертифицированные (ФСТЭК): MaxPatrol SIEM/KUMA (карточки инцидентов), R-Vision SOAR и др.
+Открытый код: TheHive (платформа управления инцидентами) в сочетании с Wazuh/ELK Stack.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F314" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Регламент (порядок), определяющий критерии отнесения события к потенциальному инциденту и порядок его передачи в ГРИЗИ.
+2. Итоги интервью с ответственным за организацию реагирования на инциденты.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация SIEM-системы в части выделения потенциальных инцидентов в отдельную очередь обработки.
+2. Выгрузка зарегистрированных карточек потенциальных инцидентов за проверяемый период.
+3. Итоги интервью с ответственным за администрирование SIEM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G314" s="151" t="inlineStr">
+        <is>
+          <t>1. Критерии отнесения события к потенциальному инциденту не формализованы, решение принимается аналитиком по своему усмотрению в каждом отдельном случае;
+2. Отдельная очередь обработки потенциальных инцидентов не выделена, аналитик вынужден вручную выискивать значимые события в общем потоке;
+3. Не все источники, охваченные мониторингом (мера МАС.1—МАС.7), подключены к формированию потенциальных инцидентов, часть источников фактически не порождает алертов;
+4. Передача зарегистрированного потенциального инцидента группе реагирования (ГРИЗИ) происходит с задержкой, не соответствующей критичности выявленного события.</t>
+        </is>
+      </c>
+      <c r="H314" s="168" t="n"/>
     </row>
     <row r="315" ht="156.75" customHeight="1">
       <c r="A315" s="20" t="inlineStr">
@@ -21810,20 +21874,86 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D315" s="34" t="inlineStr">
-        <is>
-          <t>Информация о потенциальных инцидентах ИБ, поступающая не из технических средств мониторинга, а от людей — работников, клиентов, контрагентов (например, жалоба клиента на подозрительную операцию, сообщение сотрудника о фишинговом письме), должна фиксироваться с указанием источника и характера обращения. Мера призвана помочь не упустить сигналы о потенциальном мошенничестве от клиентов и доводить до группы реагирования на инциденты защиты информации (ГРИЗИ) устные сообщения сотрудников о замеченной подозрительной активности, что может быть использовано при последующем расследовании.</t>
-        </is>
-      </c>
-      <c r="E315" s="31" t="n"/>
-      <c r="F315" s="31" t="n"/>
-      <c r="G315" s="31" t="n"/>
-      <c r="H315" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D315" s="144" t="inlineStr">
+        <is>
+          <t>Информация о потенциальных инцидентах защиты информации, поступающая не из технических средств мониторинга, а от людей — работников, клиентов, контрагентов финансовой организации (например, жалоба клиента на подозрительную операцию, сообщение сотрудника о фишинговом письме), должна фиксироваться с указанием источника и характера обращения.
+Главная цель меры — не упустить сигналы о потенциальном инциденте, поступающие по каналам, не охваченным автоматизированным мониторингом (меры МАС.1—МАС.7): сообщение клиента о подозрительной операции или устное сообщение сотрудника о замеченной подозрительной активности нередко становится первым и единственным индикатором инцидента, который затем может быть использован при последующем расследовании, если он был своевременно зафиксирован.</t>
+        </is>
+      </c>
+      <c r="E315" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Определение перечня каналов получения информации о потенциальных инцидентах от работников, клиентов и контрагентов (телефон горячей линии, форма обратной связи, электронная почта, личное обращение);
+2. Регламентацию обязанности работников незамедлительно сообщать о замеченных признаках инцидента защиты информации (мера РИ.4 в части единых правил получения такой информации);
+3. Обучение работников, взаимодействующих с клиентами, распознаванию признаков потенциального инцидента в обращениях клиентов.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация дополняет организационные каналы регистрацией поступивших сообщений в той же системе управления инцидентами (мера РИ.1), что и события, выявленные автоматизированным мониторингом, с фиксацией источника обращения (работник/клиент/контрагент), канала поступления и содержания сообщения.
+Класс используемых средств — система управления инцидентами (Incident Response / Case Management), интегрированная с каналами приёма обращений (форма на портале, интеграция с CRM/контакт-центром).
+Иностранные: ServiceNow (Case Management) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR, MaxPatrol SIEM/KUMA (регистрация ручных обращений) и др.
+Открытый код: TheHive (ручное создание карточки инцидента по обращению) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F315" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, регламентирующий обязанность и порядок сообщения работниками о признаках инцидента защиты информации;
+2. Свидетельства проведения обучения работников, взаимодействующих с клиентами, распознаванию признаков потенциального инцидента;
+3. Перечень каналов получения информации о потенциальных инцидентах от клиентов и контрагентов.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация системы управления инцидентами в части регистрации обращений от работников, клиентов и контрагентов.
+2. Выгрузка зарегистрированных обращений о потенциальных инцидентах за проверяемый период с указанием источника.
+3. Итоги интервью с ответственным за приём обращений о потенциальных инцидентах.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G315" s="151" t="inlineStr">
+        <is>
+          <t>1. Обращения клиентов о подозрительных операциях фиксируются в системе контакт-центра, но не передаются в систему управления инцидентами защиты информации;
+2. Работники не осведомлены об обязанности и порядке сообщения о замеченных признаках инцидента, обращения происходят стихийно, без единого канала;
+3. Устные сообщения сотрудников о подозрительной активности не документируются, фиксируются только письменные обращения;
+4. Обучение работников, взаимодействующих с клиентами, распознаванию признаков инцидента проводится нерегулярно, без контроля усвоения материала.</t>
+        </is>
+      </c>
+      <c r="H315" s="168" t="n"/>
     </row>
     <row r="316" ht="85.5" customHeight="1">
       <c r="A316" s="20" t="inlineStr">
@@ -21841,20 +21971,84 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D316" s="34" t="inlineStr">
-        <is>
-          <t>Инциденты ИБ должны классифицироваться по степени критичности — с учётом их влияния на бизнес-процессы организации, а не обрабатываться по единому шаблону независимо от масштаба последствий. Такое требование позволяет учитывать критичность инцидентов и не терять их среди рядовых событий.</t>
-        </is>
-      </c>
-      <c r="E316" s="31" t="n"/>
-      <c r="F316" s="31" t="n"/>
-      <c r="G316" s="31" t="n"/>
-      <c r="H316" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D316" s="144" t="inlineStr">
+        <is>
+          <t>Инциденты защиты информации должны классифицироваться по степени критичности — с учётом их влияния на предоставление финансовых услуг, реализацию бизнес-процессов и (или) технологических процессов организации, а не обрабатываться по единому шаблону независимо от масштаба последствий.
+Главная цель меры — обеспечить приоритизацию реагирования соразмерно фактической критичности инцидента: без формализованной классификации инцидент с существенным влиянием на предоставление финансовых услуг рискует быть обработан с той же очерёдностью, что и рядовое малозначимое событие, что приводит к неоправданной задержке реагирования именно там, где скорость реакции наиболее важна.</t>
+        </is>
+      </c>
+      <c r="E316" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Разработку и утверждение шкалы критичности инцидентов защиты информации с чёткими критериями отнесения инцидента к каждому уровню исходя из его влияния на предоставление финансовых услуг, бизнес-процессы и технологические процессы;
+2. Определение для каждого уровня критичности соответствующих сроков и порядка реагирования (мера РИ.6);
+3. Закрепление ответственности за первичную классификацию инцидента непосредственно на этапе его регистрации (роль оператора-диспетчера ГРИЗИ, мера РИ.9).</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы управления инцидентами на автоматическое или полуавтоматическое присвоение уровня критичности карточке инцидента исходя из типа затронутого события, критичности актива (см. классификацию ресурсов доступа) и заданных правил, с возможностью последующей ручной корректировки аналитиком.
+Класс используемых средств — система управления инцидентами (Incident Response / Case Management) с функцией автоматической приоритизации по критичности.
+Иностранные: ServiceNow (правила приоритизации инцидентов) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR, MaxPatrol SIEM/KUMA (правила присвоения критичности) и др.
+Открытый код: TheHive (ручная/полуавтоматическая классификация по степени тяжести) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F316" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ (шкала критичности) с критериями классификации инцидентов защиты информации по степени влияния.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация системы управления инцидентами в части автоматической приоритизации по критичности.
+2. Выгрузка карточек инцидентов за проверяемый период с указанием присвоенного уровня критичности и сопоставлением критериям.
+3. Итоги интервью с ответственным за администрирование системы управления инцидентами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G316" s="151" t="inlineStr">
+        <is>
+          <t>1. Шкала критичности инцидентов не увязана с реальным влиянием на предоставление финансовых услуг, критерии сформулированы абстрактно и допускают произвольную трактовку;
+2. Присвоенный уровень критичности не пересматривается при получении новой информации в ходе расследования инцидента, хотя фактическое влияние может измениться;
+3. Классификация инцидента выполняется формально, без учёта фактической критичности затронутого актива;
+4. Инциденты с изначально заниженной критичностью не подлежат последующему контролю (аудиту) правильности присвоенного уровня.</t>
+        </is>
+      </c>
+      <c r="H316" s="168" t="n"/>
     </row>
     <row r="317" ht="57" customHeight="1">
       <c r="A317" s="20" t="inlineStr">
@@ -21872,16 +22066,55 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D317" s="21" t="n"/>
-      <c r="E317" s="31" t="n"/>
-      <c r="F317" s="31" t="n"/>
-      <c r="G317" s="31" t="n"/>
-      <c r="H317" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D317" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует установления и применения единых правил получения от работников, клиентов и (или) контрагентов финансовой организации информации, потенциально связанной с инцидентами защиты информации.
+Главная цель меры — формализовать процесс, лежащий в основе меры РИ.2: без единых, документально закреплённых правил получения такой информации сам факт наличия канала для обращений (телефон, форма обратной связи) не гарантирует, что поступившее сообщение будет обработано единообразно и своевременно доведено до группы реагирования, вне зависимости от того, кто из сотрудников его принял.</t>
+        </is>
+      </c>
+      <c r="E317" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Разработку и утверждение внутреннего нормативного документа, устанавливающего единые правила приёма, первичной обработки и передачи в ГРИЗИ информации, потенциально связанной с инцидентами защиты информации, поступающей от работников, клиентов и контрагентов;
+2. Определение обязательного минимального состава сведений, фиксируемых при приёме такого обращения (дата, источник, канал, содержание, контактные данные обратившегося);
+3. Установление предельного срока передачи зарегистрированного обращения от лица, принявшего его, в ГРИЗИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F317" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий единые правила получения информации, потенциально связанной с инцидентами, от работников, клиентов и контрагентов;
+2. Выборочная проверка зарегистрированных обращений на предмет соответствия установленному составу фиксируемых сведений и срокам передачи в ГРИЗИ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G317" s="151" t="inlineStr">
+        <is>
+          <t>1. Единые правила приёма обращений установлены только для одного канала (например, для контакт-центра), тогда как обращения по иным каналам обрабатываются без формализованного порядка;
+2. Обязательный минимальный состав фиксируемых сведений об обращении соблюдается не в полном объёме, отдельные обращения регистрируются без указания источника или содержания;
+3. Предельный срок передачи обращения в ГРИЗИ не соблюдается на практике, фактическая передача происходит с существенной задержкой;
+4. Работники, непосредственно принимающие обращения от клиентов и контрагентов, не ознакомлены с установленными правилами под подпись.</t>
+        </is>
+      </c>
+      <c r="H317" s="168" t="n"/>
     </row>
     <row r="318" ht="114" customHeight="1">
       <c r="A318" s="20" t="inlineStr">
@@ -21899,20 +22132,83 @@
           <t>О-Т-Т</t>
         </is>
       </c>
-      <c r="D318" s="34" t="inlineStr">
-        <is>
-          <t>Для регистрации и классификации инцидентов должен применяться единый, заранее определённый состав атрибутов (идентификатор, дата и время, тип, источник, степень критичности, статус) с закреплёнными допустимыми значениями каждого атрибута, а не произвольное описание в свободной форме, чтобы разные операторы заполняли карточки инцидентов одинаково и поддерживали отчётность и автоматический поиск по типу или критичности инцидентов.</t>
-        </is>
-      </c>
-      <c r="E318" s="31" t="n"/>
-      <c r="F318" s="31" t="n"/>
-      <c r="G318" s="31" t="n"/>
-      <c r="H318" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D318" s="144" t="inlineStr">
+        <is>
+          <t>Для регистрации и классификации инцидентов должен применяться единый, заранее определённый состав атрибутов (идентификатор, дата и время, тип, источник, степень критичности, статус) с закреплёнными допустимыми значениями каждого атрибута, а не произвольное описание инцидента в свободной форме.
+Главная цель меры — обеспечить, чтобы разные операторы заполняли карточки инцидентов единообразно: без единого справочника атрибутов и их допустимых значений накапливающиеся записи об инцидентах становятся несопоставимыми между собой, что не позволяет вести содержательную отчётность и выполнять автоматический поиск инцидентов по типу или уровню критичности.</t>
+        </is>
+      </c>
+      <c r="E318" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Организационная реализация предполагает:
+1. Разработку и утверждение внутреннего нормативного документа, устанавливающего состав обязательных атрибутов карточки инцидента защиты информации и справочник допустимых значений для каждого атрибута;
+2. Регламентацию порядка пересмотра и пополнения справочника допустимых значений атрибутов при появлении новых типов инцидентов.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы управления инцидентами на использование структурированной формы (карточки) инцидента со справочными (выпадающими) полями атрибутов, исключающей ввод значений, не входящих в утверждённый справочник, и не допускающей регистрацию инцидента с незаполненными обязательными атрибутами.
+Класс используемых средств — система управления инцидентами (Incident Response / Case Management) со структурированной (справочной) моделью карточки инцидента.
+Иностранные: ServiceNow (структурированные поля Case) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR, MaxPatrol SIEM/KUMA (структурированная карточка инцидента) и др.
+Открытый код: TheHive (настраиваемая структура карточки инцидента) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F318" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий состав атрибутов карточки инцидента и справочник их допустимых значений.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t xml:space="preserve">
+Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация системы управления инцидентами в части структурированных полей карточки инцидента.
+2. Выборочная проверка карточек зарегистрированных инцидентов на предмет заполнения всех обязательных атрибутов допустимыми значениями.
+3. Итоги интервью с ответственным за администрирование системы управления инцидентами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G318" s="151" t="inlineStr">
+        <is>
+          <t>1. Справочник допустимых значений атрибутов не пересматривался длительное время, что вынуждает операторов подбирать неточно соответствующее значение из устаревшего перечня;
+2. Отдельные атрибуты карточки инцидента допускают ввод произвольного текста вместо выбора из справочника, что снижает единообразие данных;
+3. Обязательность заполнения всех атрибутов технически не контролируется, часть карточек инцидентов сохраняется с неполным составом сведений;
+4. Состав атрибутов карточки инцидента не пересматривался при появлении новых типов инцидентов, характерных для организации.</t>
+        </is>
+      </c>
+      <c r="H318" s="168" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="13" t="inlineStr">
@@ -21943,20 +22239,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D320" s="34" t="inlineStr">
-        <is>
-          <t>В организации должны быть установлены и закреплены в ВНД единые правила реагирования на инциденты ИБ — последовательность действий, сроки и ответственные для инцидентов разных типов, а не ситуативное реагирование по усмотрению конкретного сотрудника. Наличие такого единого регламента позволяет не откладывать обработку различных инцидентов и не затягивать реагирование на критические из них.</t>
-        </is>
-      </c>
-      <c r="E320" s="31" t="n"/>
-      <c r="F320" s="31" t="n"/>
-      <c r="G320" s="31" t="n"/>
-      <c r="H320" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D320" s="144" t="inlineStr">
+        <is>
+          <t>В организации должны быть установлены и закреплены во внутреннем нормативном документе единые правила реагирования на инциденты защиты информации — последовательность действий, сроки и ответственные для инцидентов разных типов, а не ситуативное реагирование по усмотрению конкретного сотрудника.
+Главная цель меры — не допустить, чтобы обработка инцидента откладывалась или затягивалась из-за отсутствия заранее определённого порядка действий: наличие единого регламента реагирования исключает ситуацию, когда конкретный исполнитель тратит время на выработку последовательности действий уже в процессе реагирования на критический инцидент, вместо того чтобы следовать заранее отработанному алгоритму.</t>
+        </is>
+      </c>
+      <c r="E320" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Разработку и утверждение внутреннего нормативного документа, устанавливающего единый порядок реагирования на инциденты защиты информации в зависимости от их типа и уровня критичности (мера РИ.3);
+2. Определение для каждого типа (сценария) инцидента типового алгоритма (плейбука) реагирования с указанием последовательности действий, контрольных сроков и ответственных исполнителей на каждом этапе;
+3. Периодический пересмотр установленных правил реагирования по результатам фактически произошедших инцидентов и учений (тренировок).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F320" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий единые правила реагирования на инциденты защиты информации;
+2. Типовые алгоритмы (плейбуки) реагирования по основным сценариям инцидентов;
+3. Свидетельства пересмотра правил реагирования по результатам произошедших инцидентов или проведённых учений.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G320" s="151" t="inlineStr">
+        <is>
+          <t>1. Установленные правила реагирования охватывают не все типы инцидентов, для нетиповых сценариев отдельный алгоритм действий отсутствует;
+2. Контрольные сроки этапов реагирования не отслеживаются на практике, регламент носит декларативный характер;
+3. Правила реагирования не пересматривались длительное время, несмотря на изменения в составе инфраструктуры и появление новых типов угроз;
+4. Ответственные исполнители на разных этапах реагирования не ознакомлены с установленным порядком под подпись.</t>
+        </is>
+      </c>
+      <c r="H320" s="168" t="n"/>
     </row>
     <row r="321" ht="71.25" customHeight="1">
       <c r="A321" s="20" t="inlineStr">
@@ -21974,20 +22306,56 @@
           <t>О-Н-Н</t>
         </is>
       </c>
-      <c r="D321" s="34" t="inlineStr">
-        <is>
-          <t>В организации должны быть определены и назначены роли, связанные с реагированием на инциденты ИБ в целом (кто вовлекается в процесс реагирования и какие у него обязанности). Мера избавляет от неопределённости ответственности и задач при реагировании на инциденты.</t>
-        </is>
-      </c>
-      <c r="E321" s="31" t="n"/>
-      <c r="F321" s="31" t="n"/>
-      <c r="G321" s="31" t="n"/>
-      <c r="H321" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D321" s="144" t="inlineStr">
+        <is>
+          <t>В организации должны быть определены и назначены роли, связанные с реагированием на инциденты защиты информации в целом — то есть закреплено, кто вовлекается в процесс реагирования и какие обязанности за ним закрепляются.
+Главная цель меры — устранить неопределённость ответственности и состава задач при реагировании на инцидент: без заранее определённых и назначенных ролей состав участников и распределение обязанностей формируются стихийно уже в момент возникновения инцидента, что неизбежно замедляет реагирование именно тогда, когда скорость реакции наиболее критична.</t>
+        </is>
+      </c>
+      <c r="E321" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Определение перечня ролей, участвующих в процессе реагирования на инциденты защиты информации, и закрепление за каждой ролью зоны ответственности и полномочий;
+2. Назначение конкретных сотрудников (или подразделений) на определённые роли соответствующим организационно-распорядительным документом (приказом);
+3. Регламентацию порядка замещения на случай отсутствия сотрудника, назначенного на конкретную роль (резервирование ролей).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F321" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, определяющий перечень ролей, связанных с реагированием на инциденты защиты информации, и зону ответственности каждой роли;
+2. Приказ (распорядительный документ) о назначении конкретных сотрудников на определённые роли;
+3. Регламент замещения ролей на случай отсутствия основного исполнителя.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G321" s="151" t="inlineStr">
+        <is>
+          <t>1. Перечень ролей определён формально, но фактическое назначение конкретных сотрудников на роли не оформлено распорядительным документом;
+2. Резервирование (замещение) ролей на случай отсутствия основного исполнителя не предусмотрено, что создаёт риск задержки реагирования в его отсутствие;
+3. Один и тот же сотрудник совмещает роли, совмещение которых создаёт конфликт интересов (например, аналитик и лицо, утверждающее закрытие инцидента);
+4. Назначенные на роли сотрудники не осведомлены о своих обязанностях в рамках процесса реагирования на инциденты.</t>
+        </is>
+      </c>
+      <c r="H321" s="168" t="n"/>
     </row>
     <row r="322" ht="42.75" customHeight="1">
       <c r="A322" s="20" t="inlineStr">
@@ -22005,16 +22373,55 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D322" s="21" t="n"/>
-      <c r="E322" s="31" t="n"/>
-      <c r="F322" s="31" t="n"/>
-      <c r="G322" s="31" t="n"/>
-      <c r="H322" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D322" s="144" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует РИ.7 применительно к специализированной группе реагирования на инциденты защиты информации (ГРИЗИ): требует определения и назначения ролей именно в её составе, а не только ролей, связанных с реагированием на инциденты в целом.
+Главная цель меры — сформировать выделенную, специализированную структуру реагирования вместо распределения обязанностей по реагированию между сотрудниками, для которых это не является основной функцией: наличие именно ГРИЗИ с чётко определёнными внутренними ролями обеспечивает предсказуемость и повторяемость процесса реагирования на каждый очередной инцидент.</t>
+        </is>
+      </c>
+      <c r="E322" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Формирование группы реагирования на инциденты защиты информации (ГРИЗИ) как выделенной организационной структуры (штатного подразделения либо матричной рабочей группы) и определение ролей в её составе (мера РИ.9);
+2. Закрепление состава ГРИЗИ и распределения ролей внутри неё соответствующим организационно-распорядительным документом;
+3. Определение порядка взаимодействия ГРИЗИ с иными подразделениями организации (ИТ, юридическая служба, служба безопасности, пресс-служба) при реагировании на инцидент.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F322" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ (положение о ГРИЗИ), определяющий её состав, роли и порядок взаимодействия с иными подразделениями;
+2. Приказ (распорядительный документ) о создании ГРИЗИ и назначении сотрудников на роли в её составе.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G322" s="151" t="inlineStr">
+        <is>
+          <t>1. ГРИЗИ формально создана распорядительным документом, но фактически не функционирует как выделенная структура, реагирование выполняется силами ИТ-подразделения без чёткого разделения ролей;
+2. Порядок взаимодействия ГРИЗИ с иными подразделениями (юридической службой, пресс-службой) не регламентирован, что замедляет комплексное реагирование на значимые инциденты;
+3. Состав ГРИЗИ не пересматривался при изменении организационной структуры организации;
+4. Полномочия ГРИЗИ на межподразделенческое взаимодействие не признаются иными подразделениями как обязательные к исполнению.</t>
+        </is>
+      </c>
+      <c r="H322" s="168" t="n"/>
     </row>
     <row r="323" ht="213.75" customHeight="1">
       <c r="A323" s="20" t="inlineStr">
@@ -22036,16 +22443,56 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D323" s="50" t="n"/>
-      <c r="E323" s="31" t="n"/>
-      <c r="F323" s="51" t="n"/>
-      <c r="G323" s="51" t="n"/>
-      <c r="H323" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D323" s="155" t="inlineStr">
+        <is>
+          <t>Мера конкретизирует состав ГРИЗИ (мера РИ.8), требуя выделения в её составе не менее четырёх основных ролей: руководителя ГРИЗИ (оперативное руководство реагированием), оператора-диспетчера (сбор и регистрация информации об инцидентах), аналитика (непосредственные действия по реагированию) и секретаря (документирование результатов, формирование аналитических отчётов).
+Главная цель меры — обеспечить разделение функций внутри ГРИЗИ, исключающее совмещение несовместимых ролей одним лицом: раздельное выполнение функций руководства, приёма информации, содержательного анализа и документирования снижает риск как перегрузки одного сотрудника на критическом этапе реагирования, так и предвзятого документирования результатов лицом, самим же принимавшим решения по инциденту.</t>
+        </is>
+      </c>
+      <c r="E323" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление в положении о ГРИЗИ (мера РИ.8) четырёх основных ролей — руководителя, оператора-диспетчера, аналитика и секретаря — с детальным описанием функциональных обязанностей каждой роли;
+2. Назначение конкретных сотрудников на каждую из указанных ролей, с исключением совмещения ролей, создающих конфликт интересов (в частности, роли аналитика и секретаря, документирующего результаты его же действий);
+3. Определение порядка взаимодействия между ролями в рамках единого процесса реагирования на конкретный инцидент.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F323" s="145" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Положение о ГРИЗИ с описанием функциональных обязанностей ролей руководителя, оператора-диспетчера, аналитика и секретаря;
+2. Приказ (распорядительный документ) о назначении конкретных сотрудников на каждую из четырёх ролей;
+3. Выборочная проверка карточек инцидентов на предмет фактического распределения действий между ролями в соответствии с их обязанностями.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G323" s="145" t="inlineStr">
+        <is>
+          <t>1. Одна из четырёх основных ролей ГРИЗИ (чаще всего секретаря) не назначена отдельно, её функции выполняет аналитик по факту без формального закрепления;
+2. Функциональные обязанности ролей описаны формально и не соответствуют фактическому распределению действий при реагировании на реальные инциденты;
+3. Роль оператора-диспетчера фактически не задействована, приём и первичная регистрация информации об инциденте выполняется сразу аналитиком, минуя предусмотренный процесс;
+4. При отсутствии сотрудника, назначенного на одну из ролей, инцидент обрабатывается с нарушением предусмотренного распределения функций, без предусмотренного замещения (мера РИ.7).</t>
+        </is>
+      </c>
+      <c r="H323" s="168" t="n"/>
     </row>
     <row r="324" ht="99.75" customHeight="1">
       <c r="A324" s="20" t="inlineStr">
@@ -22063,20 +22510,57 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D324" s="34" t="inlineStr">
-        <is>
-          <t>Члены группы реагирования на инциденты защиты информации (ГРИЗИ) должны получать оповещения о выявленных инцидентах ИБ оперативно и автоматически, без задержек, то есть так, чтобы критичный инцидент выявлялся системой мониторинга и информация о нём сразу доходила до ответственных лиц, что не даст злоумышленнику дополнительного времени на развитие атаки.</t>
-        </is>
-      </c>
-      <c r="E324" s="31" t="n"/>
-      <c r="F324" s="31" t="n"/>
-      <c r="G324" s="31" t="n"/>
-      <c r="H324" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D324" s="144" t="inlineStr">
+        <is>
+          <t>Члены группы реагирования на инциденты защиты информации (ГРИЗИ) должны получать оповещения о выявленных инцидентах защиты информации оперативно и автоматически, без задержек.
+Главная цель меры — не дать злоумышленнику дополнительного времени на развитие атаки: критичный инцидент должен выявляться системой мониторинга и информация о нём должна незамедлительно доходить до ответственных лиц, поскольку промежуток между фактическим выявлением инцидента и его доведением до ГРИЗИ — это время, в течение которого атака продолжает развиваться без противодействия.</t>
+        </is>
+      </c>
+      <c r="E324" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы управления инцидентами и (или) SIEM-системы на автоматическую рассылку оповещений членам ГРИЗИ (с распределением по ролям и уровню критичности инцидента) при регистрации новой карточки инцидента, с использованием нескольких независимых каналов оповещения (электронная почта, СМС, мессенджер, автодозвон) для критичных инцидентов, обеспечивающих доставку оповещения даже при недоступности одного из каналов.
+Класс используемых средств — модуль оповещения (нотификации) в составе системы управления инцидентами (Incident Response / Case Management) или SIEM/SOAR-платформы.
+Иностранные: ServiceNow (модуль оповещений), PagerDuty (эскалация и дежурства) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR (модуль оповещения), MaxPatrol SIEM/KUMA и др.
+Открытый код: TheHive в сочетании с внешними каналами оповещения (интеграция с мессенджерами по API) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F324" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация модуля автоматического оповещения членов ГРИЗИ при регистрации инцидента, с указанием используемых каналов.
+2. Отчёт о фактическом времени доставки оповещений членам ГРИЗИ по зарегистрированным инцидентам за проверяемый период.
+3. Итоги интервью с ответственным за администрирование системы управления инцидентами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G324" s="151" t="inlineStr">
+        <is>
+          <t>1. Оповещение членов ГРИЗИ настроено только по одному каналу (например, электронной почте), что не гарантирует доставку при его недоступности для критичных инцидентов;
+2. Оповещение рассылается без учёта распределения ролей, все члены ГРИЗИ получают одинаковое уведомление независимо от их зоны ответственности;
+3. Фактическое время доставки и прочтения оповещения не отслеживается, что не позволяет подтвердить оперативность оповещения на практике;
+4. Оповещение о критичных инцидентах, выявленных в нерабочее время, не предусматривает эскалацию на случай отсутствия реакции дежурного в установленный срок.</t>
+        </is>
+      </c>
+      <c r="H324" s="168" t="n"/>
     </row>
     <row r="325" ht="42.75" customHeight="1">
       <c r="A325" s="20" t="inlineStr">
@@ -22094,16 +22578,56 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D325" s="21" t="n"/>
-      <c r="E325" s="31" t="n"/>
-      <c r="F325" s="31" t="n"/>
-      <c r="G325" s="31" t="n"/>
-      <c r="H325" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D325" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует предоставления членам ГРИЗИ прав логического и физического доступа, а также административных полномочий, необходимых для проведения реагирования на инциденты защиты информации.
+Главная цель меры — исключить ситуацию, при которой реагирование на инцидент задерживается из-за отсутствия у аналитика ГРИЗИ достаточных прав доступа к затронутой инцидентом системе: без заранее предоставленных (или оперативно предоставляемых по установленной процедуре) полномочий проведение анализа, локализации и устранения последствий инцидента невозможно осуществить своевременно.</t>
+        </is>
+      </c>
+      <c r="E325" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Определение перечня прав логического и физического доступа, а также административных полномочий, необходимых членам ГРИЗИ (в первую очередь аналитикам) для выполнения задач реагирования, применительно к различным категориям систем;
+2. Регламентацию порядка предоставления таких прав — на постоянной основе для системных ресурсов реагирования (SIEM, система управления инцидентами) либо оперативно, по факту возникновения конкретного инцидента, для доступа к затронутой системе, с последующим отзывом по завершении реагирования;
+3. Ведение учёта фактически предоставленных членам ГРИЗИ прав доступа с периодическим пересмотром на предмет актуальности.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F325" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень прав логического и физического доступа и административных полномочий, необходимых членам ГРИЗИ для проведения реагирования;
+2. Регламент порядка предоставления и отзыва таких прав, в том числе в оперативном порядке при возникновении инцидента;
+3. Выгрузка фактически предоставленных членам ГРИЗИ прав доступа и полномочий за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G325" s="151" t="inlineStr">
+        <is>
+          <t>1. Оперативное предоставление прав доступа членам ГРИЗИ на время реагирования на конкретный инцидент не формализовано, права запрашиваются по общей процедуре, не учитывающей срочность реагирования;
+2. Предоставленные на время реагирования расширенные права доступа не отзываются своевременно по завершении обработки инцидента;
+3. Перечень необходимых членам ГРИЗИ прав определён не для всех категорий систем, для новых типов активов (например, облачной инфраструктуры) порядок предоставления доступа не установлен;
+4. Административные полномочия, предоставленные аналитику ГРИЗИ, не журналируются отдельно от обычных административных действий персонала эксплуатации.</t>
+        </is>
+      </c>
+      <c r="H325" s="168" t="n"/>
     </row>
     <row r="326" ht="156.75" customHeight="1">
       <c r="A326" s="20" t="inlineStr">
@@ -22126,16 +22650,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D326" s="50" t="n"/>
-      <c r="E326" s="31" t="n"/>
-      <c r="F326" s="51" t="n"/>
-      <c r="G326" s="51" t="n"/>
-      <c r="H326" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D326" s="155" t="inlineStr">
+        <is>
+          <t>Мера требует проведения реагирования на каждый обнаруженный инцидент защиты информации, включающего: анализ инцидента, определение источников и причин его возникновения, оценку последствий для предоставления финансовых услуг и реализации бизнес-процессов (технологических процессов), принятие мер по устранению последствий и планирование мер по предотвращению повторного возникновения.
+Главная цель меры — обеспечить полноту реагирования на каждый инцидент, а не ограничиться только устранением его непосредственных симптомов: инцидент, реагирование на который свелось к восстановлению работоспособности без анализа первопричины и оценки последствий, с высокой вероятностью повторится в силу того, что породившая его уязвимость или недостаток процесса остаются неустранёнными.</t>
+        </is>
+      </c>
+      <c r="E326" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе (мера РИ.6) обязательного состава этапов реагирования на каждый инцидент — анализа, определения источников и причин, оценки последствий, устранения последствий и планирования мер по предотвращению повторного возникновения;
+2. Определение критериев, при которых допускается сокращённый порядок реагирования для инцидентов минимальной критичности, без исключения ни одного из пяти этапов по существу;
+3. Контроль (со стороны руководителя ГРИЗИ или иного уполномоченного лица) фактического выполнения всех предусмотренных этапов реагирования по каждому инциденту перед его закрытием (мера РИ.14).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F326" s="145" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий обязательный состав этапов реагирования на инцидент;
+2. Выборочная проверка карточек закрытых инцидентов на предмет фактического выполнения всех предусмотренных этапов реагирования (анализ, определение причин, оценка последствий, устранение, планирование мер предотвращения);
+3. Итоги интервью с членами ГРИЗИ по порядку фактического реагирования на инциденты.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G326" s="145" t="inlineStr">
+        <is>
+          <t>1. Реагирование на инциденты низкой критичности фактически ограничивается устранением симптомов без анализа источников и причин возникновения;
+2. Планирование мер по предотвращению повторного возникновения инцидента формулируется формально, без последующего контроля их фактической реализации;
+3. Оценка последствий инцидента для предоставления финансовых услуг и реализации бизнес-процессов не документируется как отдельный результат анализа;
+4. Контроль полноты выполнения всех этапов реагирования перед закрытием инцидента не проводится, решение о закрытии принимается исполнителем без верификации.</t>
+        </is>
+      </c>
+      <c r="H326" s="168" t="n"/>
     </row>
     <row r="327" ht="30" customHeight="1">
       <c r="A327" s="20" t="inlineStr">
@@ -22153,16 +22717,55 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D327" s="21" t="n"/>
-      <c r="E327" s="31" t="n"/>
-      <c r="F327" s="31" t="n"/>
-      <c r="G327" s="31" t="n"/>
-      <c r="H327" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D327" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует установления и применения единых правил сбора, фиксации и распространения информации об инцидентах защиты информации.
+Главная цель меры — обеспечить единообразие процесса накопления и передачи сведений об инциденте на всех этапах его обработки и всем заинтересованным сторонам: без единых правил информация об одном и том же инциденте может фиксироваться по-разному разными участниками ГРИЗИ и распространяться в неполном или искажённом виде за пределы группы реагирования — руководству, регулятору, иным заинтересованным подразделениям.</t>
+        </is>
+      </c>
+      <c r="E327" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Регламентацию единого порядка и формы сбора и фиксации информации об инциденте на каждом этапе реагирования, обеспечивающего согласованность с составом атрибутов карточки инцидента (мера РИ.5);
+2. Определение перечня адресатов (руководство организации, регулятор, иные подразделения) и условий, при которых информация об инциденте подлежит распространению за пределы ГРИЗИ, с указанием состава сведений, подлежащих раскрытию каждому адресату;
+3. Установление сроков информирования каждого из адресатов в зависимости от критичности инцидента (мера РИ.3).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F327" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий единые правила сбора, фиксации и распространения информации об инцидентах защиты информации;
+2. Свидетельства фактического информирования установленных адресатов по зарегистрированным инцидентам за проверяемый период, с сопоставлением требуемым срокам.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G327" s="151" t="inlineStr">
+        <is>
+          <t>1. Правила распространения информации об инциденте не определяют однозначно состав сведений, подлежащих раскрытию конкретному адресату, что приводит к избыточному или недостаточному информированию;
+2. Установленные сроки информирования регулятора или руководства организации по критичным инцидентам не соблюдаются на практике;
+3. Информация об инциденте, зафиксированная на разных этапах реагирования разными членами ГРИЗИ, содержит противоречия, не выявляемые при последующем распространении;
+4. Правила сбора и фиксации информации не учитывают необходимость сохранения информации, пригодной для последующего использования правоохранительными органами при обращении в них.</t>
+        </is>
+      </c>
+      <c r="H327" s="168" t="n"/>
     </row>
     <row r="328" ht="99.75" customHeight="1">
       <c r="A328" s="20" t="inlineStr">
@@ -22180,20 +22783,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D328" s="34" t="inlineStr">
-        <is>
-          <t>В организации должны быть установлены и закреплены в ВНД единые правила закрытия инцидентов ИБ — определены критерии, при которых инцидент можно считать закрытым, и порядок подтверждения этого факта, а не произвольное решение исполнителя. Мера решает вопрос закрытия инцидента с документальным подтверждением устранения его причины и создаёт налаженные процессы по устранению инцидентов.</t>
-        </is>
-      </c>
-      <c r="E328" s="31" t="n"/>
-      <c r="F328" s="31" t="n"/>
-      <c r="G328" s="31" t="n"/>
-      <c r="H328" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D328" s="144" t="inlineStr">
+        <is>
+          <t>В организации должны быть установлены и закреплены во внутреннем нормативном документе единые правила закрытия инцидентов защиты информации — определены критерии, при которых инцидент может считаться закрытым, и порядок подтверждения этого факта, а не произвольное решение исполнителя.
+Главная цель меры — обеспечить документальное подтверждение того, что причина инцидента действительно устранена, прежде чем он будет признан закрытым: без формализованных критериев и порядка подтверждения инцидент рискует быть закрыт преждевременно, по факту восстановления работоспособности системы, тогда как его первопричина остаётся неустранённой и способна привести к повторному возникновению.</t>
+        </is>
+      </c>
+      <c r="E328" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Определение критериев, при выполнении которых инцидент признаётся закрытым (устранение последствий, подтверждённое отсутствие признаков продолжающейся активности, реализация запланированных мер по предотвращению повторного возникновения);
+2. Регламентацию порядка подтверждения закрытия инцидента уполномоченным лицом (как правило, руководителем ГРИЗИ), отличным от непосредственного исполнителя реагирования;
+3. Определение перечня документов и сведений, обязательных для приложения к карточке инцидента при его закрытии.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F328" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, устанавливающий единые правила и критерии закрытия инцидентов защиты информации;
+2. Выборочная проверка карточек закрытых инцидентов на предмет соответствия установленным критериям закрытия и наличия подтверждения уполномоченным лицом;
+3. Итоги интервью с руководителем ГРИЗИ по порядку подтверждения закрытия инцидентов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G328" s="151" t="inlineStr">
+        <is>
+          <t>1. Закрытие инцидента подтверждается тем же лицом, которое выполняло реагирование, без независимой проверки уполномоченным лицом;
+2. Критерии закрытия инцидента сформулированы абстрактно («инцидент устранён») без конкретных проверяемых условий;
+3. Инциденты закрываются по истечении установленного внутреннего срока независимо от фактического выполнения всех критериев закрытия;
+4. Обязательный перечень документов, прилагаемых к карточке при закрытии инцидента, соблюдается не в полном объёме.</t>
+        </is>
+      </c>
+      <c r="H328" s="168" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="13" t="inlineStr">
@@ -22224,14 +22863,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D330" s="34" t="inlineStr">
-        <is>
-          <t>Информация об инцидентах ИБ (карточки, логи, вложения расследования) сама по себе является чувствительными данными и должна быть защищена от НСД, а её целостность и доступность должны быть обеспечены. Мера позволяет не допустить злоумышленника к хранилищу информации об инцидентах и не дать ему узнать, какие его действия уже обнаружены, чтобы он не мог корректировать тактику атаки.</t>
-        </is>
-      </c>
-      <c r="E330" s="31" t="n"/>
-      <c r="F330" s="31" t="n"/>
-      <c r="G330" s="31" t="n"/>
+      <c r="D330" s="144" t="inlineStr">
+        <is>
+          <t>Информация об инцидентах защиты информации (карточки, логи, вложения расследования) сама по себе является чувствительными данными и должна быть защищена от НСД, а её целостность и доступность должны быть обеспечены.
+Главная цель меры — не допустить злоумышленника к хранилищу информации об инцидентах и не дать ему узнать, какие его действия уже обнаружены: осведомлённость атакующего о ходе расследования позволяет ему скорректировать тактику атаки и уйти от дальнейшего обнаружения.</t>
+        </is>
+      </c>
+      <c r="E330" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается размещением информации об инцидентах защиты информации (карточек, приложенных материалов расследования) в системе управления инцидентами с разграничением доступа по ролям (мера РИ.16), контролем целостности хранимых записей (защита от несанкционированного изменения или удаления карточки инцидента) и регулярным резервным копированием.
+Класс используемых средств — система управления инцидентами (Incident Response / Case Management) с функцией разграничения доступа и контроля целостности хранимых записей, средства резервного копирования.
+Иностранные: ServiceNow (ролевая модель, аудит изменений) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR, MaxPatrol SIEM/KUMA (разграничение доступа к карточкам инцидентов) и др.
+Открытый код: TheHive (ролевая модель доступа) в сочетании со средствами резервного копирования.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F330" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация системы управления инцидентами в части разграничения доступа и контроля целостности хранимой информации об инцидентах.
+2. Отчёт о выполненном резервном копировании информации об инцидентах за проверяемый период и результат тестового восстановления.
+3. Итоги интервью с ответственным за администрирование системы управления инцидентами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G330" s="151" t="inlineStr">
+        <is>
+          <t>1. Учётные записи администраторов системы управления инцидентами фактически обладают полномочиями на удаление или изменение карточек инцидентов без ограничений;
+2. Контроль целостности хранимой информации об инцидентах не реализован, факт изменения ранее закрытой карточки технически не выявляется;
+3. Резервное копирование информации об инцидентах выполняется, но тестовое восстановление не проводится, фактическая пригодность копий не подтверждена;
+4. Приложенные к карточке инцидента материалы расследования (файлы, дампы) хранятся отдельно от самой карточки без единого контроля доступа и целостности.</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="114" customHeight="1">
       <c r="A331" s="20" t="inlineStr">
@@ -22249,14 +22930,56 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D331" s="34" t="inlineStr">
-        <is>
-          <t>Доступ членов группы реагирования на инциденты защиты информации (ГРИЗИ) к информации об инцидентах должен быть разграничен в соответствии с их ролью (оператор-диспетчер, аналитик, секретарь, руководитель) — каждый видит, только то, что соответствует его функциям, а не весь массив данных. Благодаря этой мере разграничение по ролям сужает круг лиц, способных случайно или намеренно исказить данные об инциденте, не входящем в их зону ответственности.</t>
-        </is>
-      </c>
-      <c r="E331" s="21" t="n"/>
-      <c r="F331" s="21" t="n"/>
-      <c r="G331" s="21" t="n"/>
+      <c r="D331" s="144" t="inlineStr">
+        <is>
+          <t>Доступ членов группы реагирования на инциденты защиты информации (ГРИЗИ) к информации об инцидентах должен быть разграничен в соответствии с их ролью (оператор-диспетчер, аналитик, секретарь, руководитель) — каждый видит только то, что соответствует его функциям, а не весь массив данных.
+Главная цель меры — сузить круг лиц, способных случайно или намеренно исказить данные об инциденте, не входящем в их зону ответственности: разграничение доступа по ролям снижает риск как непреднамеренной порчи чужих данных расследования, так и намеренного искажения хода реагирования лицом, для которого доступ к конкретному инциденту не является служебной необходимостью.</t>
+        </is>
+      </c>
+      <c r="E331" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой в системе управления инцидентами ролевой модели доступа, при которой видимость и доступный набор действий над карточкой инцидента и приложенными материалами определяются ролью пользователя в составе ГРИЗИ (руководитель, оператор-диспетчер, аналитик, секретарь), закреплённой мерой РИ.9.
+Класс используемых средств — система управления инцидентами (Incident Response / Case Management) с ролевой моделью разграничения доступа (Role-Based Access Control).
+Иностранные: ServiceNow (ролевая модель ACL) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR, MaxPatrol SIEM/KUMA (ролевое разграничение доступа к карточкам инцидентов) и др.
+Открытый код: TheHive (ролевая модель доступа) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F331" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация ролевой модели доступа к информации об инцидентах в системе управления инцидентами, сопоставленная распределению ролей ГРИЗИ (мера РИ.9).
+2. Результат тестовой проверки доступности карточки инцидента и приложенных материалов для пользователей с разными ролями.
+3. Итоги интервью с ответственным за администрирование системы управления инцидентами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G331" s="144" t="inlineStr">
+        <is>
+          <t>1. Ролевая модель доступа настроена не для всех ролей ГРИЗИ, часть пользователей имеет более широкий доступ, чем предусмотрено их функциональными обязанностями;
+2. Разграничение доступа применяется только к самой карточке инцидента, но не к приложенным материалам расследования (файлам, дампам), доступным всем членам ГРИЗИ без ограничений;
+3. Права доступа, предоставленные пользователю при временном исполнении чужой роли (замещение по мере РИ.7), не отзываются по окончании замещения;
+4. Фактическое соответствие настроенных прав доступа утверждённому распределению ролей не проверяется на периодической основе.</t>
+        </is>
+      </c>
     </row>
     <row r="332" ht="28.5" customHeight="1">
       <c r="A332" s="20" t="inlineStr">
@@ -22274,10 +22997,56 @@
           <t>Т-Т-Н</t>
         </is>
       </c>
-      <c r="D332" s="21" t="n"/>
-      <c r="E332" s="21" t="n"/>
-      <c r="F332" s="21" t="n"/>
-      <c r="G332" s="21" t="n"/>
+      <c r="D332" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует обеспечения возможности доступа к информации об инцидентах защиты информации в течение трёх лет с момента их регистрации.
+Главная цель меры — установить минимальный срок доступности сведений об инциденте, достаточный для проведения ретроспективного анализа при повторном возникновении сходного инцидента, для расследования по запросу регулятора или правоохранительных органов, а также для оценки эффективности реализованных мер по предотвращению повторного возникновения (мера РИ.12): без установленного минимального срока информация об инциденте может быть удалена или архивирована так, что станет фактически недоступной задолго до истечения практически значимого периода.</t>
+        </is>
+      </c>
+      <c r="E332" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается организацией многоуровневого хранения информации об инцидентах защиты информации в системе управления инцидентами: оперативное хранение на протяжении ближайшего периода и последующая архивация с сохранением возможности поиска и восстановления карточек инцидентов и приложенных материалов на протяжении не менее трёх лет с момента их регистрации.
+Класс используемых средств — система управления инцидентами (Incident Response / Case Management) с многоуровневой архитектурой хранения (оперативное/архивное хранилище).
+Иностранные: ServiceNow (архивные таблицы Case Management) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR, MaxPatrol SIEM/KUMA (архивное хранение карточек инцидентов) и др.
+Открытый код: TheHive в сочетании с архивным хранилищем (объектное хранилище для приложенных материалов).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F332" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация многоуровневого хранения информации об инцидентах с указанием фактического срока хранения на архивном уровне.
+2. Результат тестового поиска и восстановления карточки инцидента и приложенных материалов за период, приближающийся к трёхлетнему сроку.
+3. Итоги интервью с ответственным за администрирование системы управления инцидентами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G332" s="144" t="inlineStr">
+        <is>
+          <t>1. Фактический срок хранения информации об инцидентах на архивном уровне меньше установленного мерой трёхлетнего минимума из-за ограниченного объёма архивного хранилища;
+2. Приложенные к карточке материалы расследования (файлы, дампы) хранятся с меньшим сроком, чем сама карточка инцидента, и удаляются раньше установленного срока;
+3. Доступ к архивной информации об инцидентах требует ручного восстановления администратором и не может быть выполнен оперативно при повторном обращении к инциденту;
+4. Целостность архивной информации об инцидентах за длительный период не контролируется отдельно от контроля целостности оперативного хранилища (мера РИ.15).</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="28.5" customHeight="1">
       <c r="A333" s="20" t="inlineStr">
@@ -22295,10 +23064,56 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D333" s="21" t="n"/>
-      <c r="E333" s="21" t="n"/>
-      <c r="F333" s="21" t="n"/>
-      <c r="G333" s="21" t="n"/>
+      <c r="D333" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична РИ.17, но устанавливает повышенный, пятилетний минимальный срок обеспечения доступа к информации об инцидентах защиты информации — для уровня защиты, требующего более длительной ретроспективной доступности.
+Главная цель меры — обеспечить тот же результат доступности информации об инцидентах для длительного ретроспективного анализа, что и мера РИ.17, но применительно к объектам защиты повышенной критичности, для которых регуляторные и договорные требования предполагают более продолжительный период хранения сведений об инцидентах.</t>
+        </is>
+      </c>
+      <c r="E333" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация аналогична мере РИ.17 и обеспечивается той же многоуровневой архитектурой хранения информации об инцидентах, рассчитанной на увеличенный, не менее пятилетний срок доступности данных на архивном уровне хранения.
+Класс используемых средств — система управления инцидентами (Incident Response / Case Management) с многоуровневой архитектурой хранения (оперативное/архивное хранилище).
+Иностранные: ServiceNow (архивные таблицы Case Management) и пр.
+Российские сертифицированные (ФСТЭК): R-Vision SOAR, MaxPatrol SIEM/KUMA и др.
+Открытый код: TheHive в сочетании с архивным хранилищем с длительным сроком хранения.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F333" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация многоуровневого хранения информации об инцидентах с указанием фактического пятилетнего срока хранения на архивном уровне.
+2. Расчёт необходимого объёма архивного хранилища исходя из пятилетнего срока и фактического количества регистрируемых инцидентов.
+3. Результат тестового поиска и восстановления информации об инциденте за период, приближающийся к пятилетнему сроку.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G333" s="144" t="inlineStr">
+        <is>
+          <t>1. Пятилетний срок хранения применяется не для всех объектов защиты, требующих данного уровня, часть инцидентов хранится по сокращённому (трёхлетнему) сроку меры РИ.17;
+2. Объём архивного хранилища не рассчитан на фактическую нагрузку при увеличенном до пяти лет сроке хранения материалов расследования (файлов, дампов значительного объёма);
+3. Носители архивного хранилища не проходят периодическую проверку читаемости на протяжении длительного срока хранения;
+4. Доступ к информации об инцидентах пятилетней давности требует привлечения стороннего подрядчика (поставщика системы управления инцидентами), что не позволяет уложиться в разумные сроки при реальном обращении к архиву.</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
@@ -22329,10 +23144,56 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D335" s="21" t="n"/>
-      <c r="E335" s="21" t="n"/>
-      <c r="F335" s="21" t="n"/>
-      <c r="G335" s="21" t="n"/>
+      <c r="D335" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждого факта доступа к информации об инцидентах защиты информации.
+Главная цель меры — обеспечить возможность расследования случаев, когда сотрудник (в том числе не входящий в состав ГРИЗИ) обращается к чувствительной информации об инцидентах: сведения об инциденте содержат данные о выявленных уязвимостях, скомпрометированных учётных записях и предпринятых мерах реагирования, и доступ к ним без отдельного контроля способен использоваться для разведки перед повторной атакой или для сокрытия следов уже совершённых действий.</t>
+        </is>
+      </c>
+      <c r="E335" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой системы управления инцидентами на аудит собственных операций доступа к информации об инцидентах (просмотр карточки, экспорт приложенных материалов, административные действия) с фиксацией учётной записи, времени и объёма затронутых данных, и передачей таких событий в систему централизованного сбора и корреляции (SIEM).
+Класс используемых средств — встроенный механизм аудита действий пользователей системы управления инцидентами (audit trail), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: ServiceNow (журнал аудита Case Management) и пр.
+Российские сертифицированные (ФСТЭК): встроенный аудит R-Vision SOAR/MaxPatrol SIEM/KUMA, доступ к карточкам инцидентов и др.
+Открытый код: TheHive (журнал действий пользователей) в сочетании с Wazuh (централизованный сбор) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F335" s="144" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация аудита доступа к информации об инцидентах в системе управления инцидентами.
+2. Выгрузка зарегистрированных фактов доступа к информации об инцидентах за проверяемый период, сопоставленная составу ГРИЗИ и распределению ролей (мера РИ.16).
+3. Итоги интервью с ответственным за администрирование системы управления инцидентами.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G335" s="144" t="inlineStr">
+        <is>
+          <t>1. Регистрация доступа охватывает только просмотр карточки инцидента, но не экспорт или скачивание приложенных материалов расследования;
+2. Обращения к информации об инцидентах со стороны пользователей, не входящих в состав ГРИЗИ (например, привилегированных администраторов системы), не выделяются как события повышенного внимания;
+3. События доступа к информации об инцидентах не передаются в SIEM-систему, доступны только в локальном журнале аудита системы управления инцидентами;
+4. Периодический анализ журнала доступа к информации об инцидентах на предмет аномальной активности не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="13" t="inlineStr">

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -13035,7 +13035,7 @@
       </c>
       <c r="D177" s="144" t="inlineStr">
         <is>
-          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к границе с сетью Интернет: оборудование и ПО, обеспечивающие изоляцию внутренних сетей от Интернета (меры СМЭ.14—СМЭ.19), должны регулярно проверяться на известные уязвимости, а выявленные — оперативно устраняться.
+          <t>Применительно к границе с сетью Интернет требование меры ЦЗИ.1 звучит конкретнее: оборудование и ПО, обеспечивающие изоляцию внутренних сетей от Интернета (меры СМЭ.14—СМЭ.19), должны регулярно проверяться на известные уязвимости, а выявленные — оперативно устраняться.
 Главная цель меры — исключить ситуацию, при которой периметр организации защищён формально (межсетевые экраны и иные средства установлены), но фактически уязвим из-за неустранённых известных недостатков в самих защитных средствах, поскольку граница с публичным Интернетом — наиболее вероятная точка приложения усилий внешнего злоумышленника.</t>
         </is>
       </c>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="D178" s="144" t="inlineStr">
         <is>
-          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к сегменту общедоступных объектов доступа (банкоматов, платёжных терминалов): оборудование и ПО, обеспечивающее изоляцию этого сегмента от сети Интернет (мера СМЭ.11), должны регулярно проверяться на известные уязвимости, а выявленные — оперативно устраняться.
+          <t>То же требование меры ЦЗИ.1 распространяется и на сегмент общедоступных объектов доступа (банкоматов, платёжных терминалов): оборудование и ПО, обеспечивающее изоляцию этого сегмента от сети Интернет (мера СМЭ.11), должны регулярно проверяться на известные уязвимости, а выявленные — оперативно устраняться.
 Главная цель меры — учесть повышенную критичность этой границы: общедоступные объекты доступа физически находятся вне контролируемой территории организации, и известная, но не устранённая уязвимость на границе этого сегмента существенно упрощает злоумышленнику получение контроля над устройствами, напрямую связанными с проведением финансовых операций.</t>
         </is>
       </c>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="D179" s="144" t="inlineStr">
         <is>
-          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к самим ресурсам доступа, размещённым в сегменте, подключённом к сети Интернет (DMZ), — веб-серверам, почтовым шлюзам, API-интерфейсам: эти ресурсы должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный логический доступ, а выявленные уязвимости — оперативно устраняться.
+          <t>Требование меры ЦЗИ.1 находит применение и в отношении самих ресурсов доступа, размещённых в сегменте, подключённом к сети Интернет (DMZ), — веб-серверов, почтовых шлюзов, API-интерфейсов: эти ресурсы должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный логический доступ, а выявленные уязвимости — оперативно устраняться.
 Главная цель меры — защитить непосредственно интернет-доступные ресурсы (в отличие от меры ЦЗИ.2, которая контролирует уязвимости сетевого оборудования на границе), поскольку именно уязвимости прикладного уровня самих ресурсов (устаревшие версии веб-приложений, известные уязвимости CMS, библиотек) наиболее часто используются для получения несанкционированного доступа.</t>
         </is>
       </c>
@@ -13326,7 +13326,7 @@
       </c>
       <c r="D180" s="144" t="inlineStr">
         <is>
-          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к средствам удалённого доступа (VPN-шлюзам, серверам терминального доступа): эти средства должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный удалённый доступ, а выявленные уязвимости — оперативно устраняться.
+          <t>Аналогичное требование меры ЦЗИ.1 предъявляется к средствам удалённого доступа (VPN-шлюзам, серверам терминального доступа): эти средства должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный удалённый доступ, а выявленные уязвимости — оперативно устраняться.
 Главная цель меры — защитить каналы удалённого доступа, которые являются одной из наиболее часто эксплуатируемых точек входа злоумышленника: известная, но не устранённая уязвимость VPN-шлюза или сервера терминального доступа зачастую позволяет обойти даже корректно настроенные меры аутентификации (меры РД.1—РД.29).</t>
         </is>
       </c>
@@ -13423,7 +13423,7 @@
       </c>
       <c r="D181" s="144" t="inlineStr">
         <is>
-          <t>Мера конкретизирует требование меры ЦЗИ.1 применительно к ресурсам доступа, размещённым во внутренней вычислительной сети организации (не подключённой напрямую к сети Интернет): такие ресурсы также должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный логический доступ.
+          <t>Тот же принцип, заданный мерой ЦЗИ.1, распространяется на ресурсы доступа, размещённые во внутренней вычислительной сети организации (не подключённой напрямую к сети Интернет): такие ресурсы также должны регулярно проверяться на известные уязвимости, использование которых может позволить несанкционированный логический доступ.
 Главная цель меры — не допустить ложного ощущения защищённости внутренних ресурсов на основании одной лишь их сетевой изолированности от Интернета: значительная часть реальных атак развивается уже после первичного проникновения за счёт эксплуатации известных, но не устранённых уязвимостей внутренних систем при горизонтальном перемещении злоумышленника (lateral movement).</t>
         </is>
       </c>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="D183" s="144" t="inlineStr">
         <is>
-          <t>Мера задаёт способ реализации контроля, предусмотренного мерами ЦЗИ.1—ЦЗИ.6, применительно к прикладному ПО, ПО автоматизированных систем (АС) и системному ПО, установленному на серверном и сетевом оборудовании: контроль осуществляется путём сканирования и анализа состава, версий и параметров настроек такого ПО.
+          <t>Применительно к прикладному ПО, ПО автоматизированных систем (АС) и системному ПО, установленному на серверном и сетевом оборудовании, контроль, предусмотренный мерами ЦЗИ.1—ЦЗИ.6, приобретает следующий вид: он осуществляется путём сканирования и анализа состава, версий и параметров настроек такого ПО.
 Главная цель меры — распространить контроль уязвимостей не только на само серверное и сетевое оборудование (мера ЦЗИ.7), но и на программное обеспечение, функционирующее на этом оборудовании, поскольку значительная часть известных уязвимостей относится именно к прикладному, системному ПО и ПО АС, а не к аппаратной платформе или сетевой конфигурации.</t>
         </is>
       </c>
@@ -13638,7 +13638,7 @@
       </c>
       <c r="D184" s="144" t="inlineStr">
         <is>
-          <t>Мера задаёт способ реализации контроля, предусмотренного мерами ЦЗИ.1—ЦЗИ.6, применительно к прикладному, системному ПО и ПО АС, установленному на автоматизированных рабочих местах (АРМ) пользователей и эксплуатационного персонала.
+          <t>Тот же контроль, что предусмотрен мерами ЦЗИ.1—ЦЗИ.6, распространяется на прикладное, системное ПО и ПО АС, установленное на автоматизированных рабочих местах (АРМ) пользователей и эксплуатационного персонала.
 Главная цель меры — распространить контроль известных уязвимостей на рабочие станции, которые, в отличие от серверов, эксплуатируются большим количеством пользователей, чаще подвергаются внешним воздействиям (электронная почта, веб-браузинг, съёмные носители) и в силу многочисленности парка сложнее поддаются единообразному контролю обновлений вручную.</t>
         </is>
       </c>
@@ -13710,7 +13710,7 @@
       </c>
       <c r="D185" s="144" t="inlineStr">
         <is>
-          <t>Мера задаёт способ реализации контроля, предусмотренного мерами ЦЗИ.1—ЦЗИ.6, применительно к самим средствам и системам защиты информации: их состав, версии и параметры настроек также подлежат регулярному сканированию и анализу на предмет известных уязвимостей.
+          <t>Контроль, предусмотренный мерами ЦЗИ.1—ЦЗИ.6, распространяется и на сами средства и системы защиты информации: их состав, версии и параметры настроек также подлежат регулярному сканированию и анализу на предмет известных уязвимостей.
 Главная цель меры — исключить ситуацию, при которой контроль уязвимостей распространяется на всю инфраструктуру, кроме самих средств защиты информации, поскольку уязвимость в СЗИ способна не просто открыть отдельный канал атаки, а полностью обесценить защитную функцию, которую данное средство должно было обеспечивать.</t>
         </is>
       </c>
@@ -14367,7 +14367,7 @@
       </c>
       <c r="D194" s="144" t="inlineStr">
         <is>
-          <t>Мера требует ведения учёта эталонных значений параметров настроек (конфигураций) ПО автоматизированных систем (АС), системного ПО, средств и систем защиты информации, контроля их целостности (соответствия фактических настроек эталонным) и обеспечения технической возможности восстановления эталонных настроек в случае нештатной ситуации.
+          <t>Эталонные значения параметров настроек (конфигураций) ПО автоматизированных систем (АС), системного ПО, средств и систем защиты информации подлежат учёту и контролю целостности (соответствия фактических настроек эталонным), а сама возможность восстановления эталонных настроек в случае нештатной ситуации должна быть технически обеспечена.
 Главная цель меры — обеспечить, что защитные и функциональные свойства системы определяются не только установленной версией ПО (меры ЦЗИ.16/ЦЗИ.17), но и его настройками: несанкционированное или ошибочное изменение конфигурации способно снизить защищённость системы так же существенно, как отсутствие обновления, а без эталона и контроля отклонений такое изменение останется незамеченным.</t>
         </is>
       </c>
@@ -15244,7 +15244,7 @@
       </c>
       <c r="D206" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого факта установки, обновления и (или) удаления ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО на серверном и сетевом оборудовании — то есть регистрации результата операций, выполняемых в рамках меры ЦЗИ.12.
+          <t>Отдельной регистрации в качестве события защиты информации подлежит каждый факт установки, обновления и (или) удаления ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО на серверном и сетевом оборудовании — то есть результат операций, выполняемых в рамках меры ЦЗИ.12.
 Главная цель меры — обеспечить возможность ретроспективно подтвердить, какое ПО, когда и кем было установлено, обновлено или удалено на конкретном сервере или сетевом устройстве: без такой регистрации расследование инцидента, связанного с несанкционированным изменением состава ПО, невозможно, а факт применения планового обновления невозможно формально подтвердить.</t>
         </is>
       </c>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="D214" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого результата выполнения операций по контролю целостности и достоверности источников получения при распространении и (или) обновлении ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО (мера ЦЗИ.19).
+          <t>Каждый результат выполнения операций по контролю целостности и достоверности источников получения при распространении и (или) обновлении ПО автоматизированных систем (АС), средств и систем защиты информации, системного ПО (мера ЦЗИ.19) должен регистрироваться в качестве события защиты информации.
 Главная цель меры — обеспечить возможность подтвердить, что контроль подлинности источника и целостности каждого полученного обновления фактически выполнялся, а не только зафиксировать случаи выявленного несоответствия: полная история проверок необходима для расследования инцидента, связанного с компрометацией цепочки поставок ПО, и для подтверждения соответствия установленному регламенту.</t>
         </is>
       </c>
@@ -16038,7 +16038,7 @@
       </c>
       <c r="D219" s="144" t="inlineStr">
         <is>
-          <t>Мера требует развёртывания защиты от вредоносного кода на уровне серверного оборудования как отдельного уровня эшелонированной защиты, наряду с защитой АРМ (мера ЗВК.1) и виртуальной инфраструктуры (мера ЗВК.2).
+          <t>Отдельным уровнем эшелонированной защиты, наряду с защитой АРМ (мера ЗВК.1) и виртуальной инфраструктуры (мера ЗВК.2), мера устанавливает развёртывание защиты от вредоносного кода на уровне серверного оборудования.
 Главная цель меры — защитить критичный сегмент инфраструктуры, компрометация которого влечёт более тяжёлые последствия, чем заражение отдельной рабочей станции: сервер, как правило, обрабатывает данные многих пользователей одновременно и обладает более широкими сетевыми правами доступа, что делает его привлекательной целью для распространения вредоносного кода по инфраструктуре.</t>
         </is>
       </c>
@@ -16105,7 +16105,7 @@
       </c>
       <c r="D220" s="144" t="inlineStr">
         <is>
-          <t>Мера требует реализации защиты от вредоносного кода на уровне контроля межсетевого трафика — то есть выявления и блокирования вредоносного кода непосредственно в потоке данных, пересекающем границы контролируемых сегментов сети, вне зависимости от того, установлена ли конечная защита (меры ЗВК.1—ЗВК.3) на узле-получателе.
+          <t>На уровне контроля межсетевого трафика мера требует реализации защиты от вредоносного кода — то есть выявления и блокирования вредоносного кода непосредственно в потоке данных, пересекающем границы контролируемых сегментов сети, вне зависимости от того, установлена ли конечная защита (меры ЗВК.1—ЗВК.3) на узле-получателе.
 Главная цель меры — сформировать дополнительный, независимый от конечных узлов рубеж обороны: сетевой уровень контроля способен выявить вредоносный код до момента его получения конечным устройством, а также обнаружить заражение узла, на котором конечная защита была отключена, обойдена или не установлена.</t>
         </is>
       </c>
@@ -16172,7 +16172,7 @@
       </c>
       <c r="D221" s="144" t="inlineStr">
         <is>
-          <t>Мера требует реализации защиты от вредоносного кода на уровне контроля почтового трафика — проверки вложений и содержимого электронных сообщений на почтовом шлюзе до их доставки получателю.
+          <t>Применительно к уровню контроля почтового трафика мера требует реализации защиты от вредоносного кода — проверки вложений и содержимого электронных сообщений на почтовом шлюзе до их доставки получателю.
 Главная цель меры — перекрыть один из наиболее массовых и результативных каналов первичного заражения: электронная почта остаётся основным способом доставки вредоносных вложений и фишинговых ссылок, а проверка на почтовом шлюзе позволяет блокировать вредоносный код до его попадания на АРМ пользователя, вне зависимости от того, откроет ли пользователь вложение.</t>
         </is>
       </c>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="D222" s="144" t="inlineStr">
         <is>
-          <t>Мера требует реализации защиты от вредоносного кода на уровне входного контроля устройств и переносных (отчуждаемых) носителей информации — то есть проверки съёмных носителей (флеш-накопителей, внешних дисков) и подключаемых устройств до их использования в вычислительных сетях организации (детальные технические требования к процедуре установлены мерами ЗВК.18/ЗВК.19).
+          <t>Ещё один самостоятельный уровень эшелонированной защиты от вредоносного кода, которого требует мера, — входной контроль устройств и переносных (отчуждаемых) носителей информации: то есть проверка съёмных носителей (флеш-накопителей, внешних дисков) и подключаемых устройств до их использования в вычислительных сетях организации (детальные технические требования к процедуре установлены мерами ЗВК.18/ЗВК.19).
 Главная цель меры — закрыть канал заражения, не зависящий от периметровой и почтовой защиты (меры ЗВК.4, ЗВК.5): съёмный носитель, заражённый вне контролируемой инфраструктуры (например, на личном компьютере сотрудника), способен внести вредоносный код напрямую на АРМ или сервер в обход сетевого контроля.</t>
         </is>
       </c>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="D223" s="144" t="inlineStr">
         <is>
-          <t>Мера требует реализации защиты от вредоносного кода на уровне контроля общедоступных объектов доступа — устройств, физически доступных неограниченному кругу лиц (банкоматов, платёжных терминалов, инфокиосков), с учётом их специфики: как правило, встроенной (embedded) операционной системы и невозможности установки классического антивирусного агента с полным функционалом.
+          <t>Отдельный уровень защиты от вредоносного кода, предусмотренный мерой, — контроль общедоступных объектов доступа: устройств, физически доступных неограниченному кругу лиц (банкоматов, платёжных терминалов, инфокиосков), с учётом их специфики — как правило, встроенной (embedded) операционной системы и невозможности установки классического антивирусного агента с полным функционалом.
 Главная цель меры — защитить категорию устройств с повышенным риском физического доступа злоумышленника (в отличие от АРМ и серверов, расположенных в контролируемых помещениях): общедоступность банкоматов и терминалов делает их удобной целью для установки вредоносного кода через физическое подключение или через уязвимости встроенного ПО, что подтверждается известными случаями атак типа «black box» и джекпоттинга.</t>
         </is>
       </c>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="D240" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждой выполненной операции по проведению проверки на отсутствие вредоносного кода — как резидентного сканирования (мера ЗВК.1), так и еженедельных полных проверок (мера ЗВК.12) и проверок при установке/изменении ПО (мера ЗВК.20).
+          <t>Каждая выполненная операция по проведению проверки на отсутствие вредоносного кода — резидентное сканирование (мера ЗВК.1), еженедельная полная проверка (мера ЗВК.12) или проверка при установке/изменении ПО (мера ЗВК.20) — должна регистрироваться в качестве события защиты информации.
 Главная цель меры — обеспечить возможность подтвердить сам факт и охват выполненных проверок за конкретный период, а не полагаться на предположение, что раз средство защиты установлено, то проверки выполняются в соответствии с регламентом: без регистрации результатов невозможно отличить регулярно проверяемый объект от объекта, на котором проверки фактически не выполнялись.</t>
         </is>
       </c>
@@ -17445,7 +17445,7 @@
       </c>
       <c r="D241" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого факта выявления вредоносного кода на любом из уровней эшелонированной защиты (меры ЗВК.1—ЗВК.7).
+          <t>Каждый факт выявления вредоносного кода на любом из уровней эшелонированной защиты (меры ЗВК.1—ЗВК.7) должен регистрироваться в качестве события защиты информации.
 Главная цель меры — обеспечить полную и достоверную историю фактов заражения для последующего анализа: без регистрации каждого отдельного факта как события защиты информации невозможно оценить реальную интенсивность попыток заражения инфраструктуры, выявить целенаправленную атаку по совокупности отдельных фактов и подтвердить своевременность реагирования на каждый из них.</t>
         </is>
       </c>
@@ -17512,7 +17512,7 @@
       </c>
       <c r="D242" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого факта неконтролируемого использования технологии мобильного кода — то есть случая, когда контроль (выявление) использования такой технологии (мера ЦЗИ.26) фиксирует применение мобильного кода в обход установленных ограничений.
+          <t>Регистрации в качестве события защиты информации подлежит каждый факт неконтролируемого использования технологии мобильного кода — то есть ситуация, при которой контроль (выявление) использования такой технологии (мера ЦЗИ.26) фиксирует применение мобильного кода в обход установленных ограничений.
 Главная цель меры — обеспечить возможность ретроспективно подтвердить факты применения потенциально опасной технологии в тех случаях, когда её использование не было заранее санкционировано: без такой регистрации риск, связанный с исполнением произвольного кода на стороне получателя без явной установки, остаётся неучтённым при последующем анализе инцидентов.</t>
         </is>
       </c>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="D243" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого сбоя в функционировании средств защиты от вредоносного кода — то есть случаев некорректной работы, аварийного завершения процесса или иной технической неисправности средства защиты, отличных от его намеренного отключения (мера ЗВК.27).
+          <t>Каждый сбой в функционировании средств защиты от вредоносного кода — некорректная работа, аварийное завершение процесса или иная техническая неисправность средства защиты, отличная от его намеренного отключения (мера ЗВК.27), — должен регистрироваться в качестве события защиты информации.
 Главная цель меры — обеспечить видимость случаев, когда объект фактически остаётся без защиты не вследствие чьих-либо действий, а вследствие технической неисправности самого средства защиты: без регистрации таких сбоев отсутствие защиты может долгое время оставаться незамеченным, будучи неотличимым от штатной работы средства защиты в фоновом режиме.</t>
         </is>
       </c>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="D244" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого сбоя в выполнении контроля (проверок) на отсутствие вредоносного кода — то есть случая, когда запланированная проверка (резидентная, еженедельная полная, при установке/изменении ПО) не была выполнена или была прервана до завершения.
+          <t>Отдельной регистрации в качестве события защиты информации подлежит каждый сбой в выполнении контроля (проверок) на отсутствие вредоносного кода — случай, когда запланированная проверка (резидентная, еженедельная полная, при установке/изменении ПО) не была выполнена или была прервана до завершения.
 Главная цель меры — отличать зафиксированный факт «проверка не выполнена» от простого отсутствия события о её выполнении (мера ЗВК.22): без явной регистрации сбоя пропуск проверки, вызванный, например, отключением объекта в плановое время или технической ошибкой планировщика, останется незамеченным до следующего аудита.</t>
         </is>
       </c>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="D245" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого факта отключения средства защиты от вредоносного кода — как штатного (санкционированного, например, для проведения регламентных работ), так и несанкционированного.
+          <t>Каждый факт отключения средства защиты от вредоносного кода — как штатного (санкционированного, например, для проведения регламентных работ), так и несанкционированного — подлежит регистрации в качестве события защиты информации.
 Главная цель меры — обеспечить возможность отличить факт намеренного (в том числе несанкционированного) отключения от технического сбоя (мера ЗВК.25) и подтвердить, что каждое отключение было санкционировано и ограничено по времени: период, в течение которого объект остаётся без защиты по чьей-либо инициативе, представляет отдельный, управляемый организацией риск, требующий отдельного контроля.</t>
         </is>
       </c>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="D246" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого факта нарушения целостности программных компонентов средств защиты от вредоносного кода, выявленного встроенным механизмом самозащиты (мера ЗВК.10).
+          <t>Выявленный встроенным механизмом самозащиты (мера ЗВК.10) факт нарушения целостности программных компонентов средств защиты от вредоносного кода должен регистрироваться в качестве события защиты информации.
 Главная цель меры — обеспечить возможность ретроспективно подтвердить факт и время попытки компрометации самого средства защиты: обнаружение нарушения целостности его компонентов (мера ЗВК.10) без регистрации соответствующего события фиксируется только локально и рискует остаться без внимания ответственных за ИБ лиц, тогда как именно такая попытка нередко служит индикатором целенаправленной атаки на инфраструктуру.</t>
         </is>
       </c>
@@ -17871,9 +17871,9 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D249" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует организовать блокирование неразрешенной и контроль (анализ) разрешенной передачи информации конфиденциального характера на внешние адреса электронной почты.
+      <c r="D249" s="144" t="inlineStr">
+        <is>
+          <t>На внешние адреса электронной почты должны распространяться блокирование неразрешённой и контроль (анализ) разрешённой передачи информации конфиденциального характера.
 Блокирование — запрет на отправку конфиденциальной информации на внешние почтовые адреса (например, на личную почту сотрудника или адрес контрагента, не включенный в «белый список»).
 Контроль (анализ) — для разрешенных сценариев отправки (например, контрагентам по договору) организуется анализ содержимого писем и вложений, чтобы убедиться, что передается именно та информация и в том объеме, который разрешен.
 Главная цель меры — предотвратить несанкционированную передачу конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) за пределы организации через электронную почту.</t>
@@ -17940,9 +17940,9 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D250" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует организовать блокирование неразрешенной и контроль (анализ) разрешенной передачи информации конфиденциального характера в сеть Интернет с использованием информационной инфраструктуры финансовой организации.
+      <c r="D250" s="144" t="inlineStr">
+        <is>
+          <t>Аналогичное требование — блокирование неразрешённой и контроль (анализ) разрешённой передачи информации конфиденциального характера — распространяется на передачу в сеть Интернет с использованием информационной инфраструктуры финансовой организации.
 Блокирование — запрет на передачу конфиденциальной информации в Интернет (например, через веб-браузеры, облачные сервисы, мессенджеры, файловые хостинги и другие протоколы).
 Контроль (анализ) — для разрешенных сценариев передачи организуется анализ содержимого трафика (контентный анализ), чтобы убедиться, что передается именно та информация и в том объеме, который разрешен.
 Главная цель меры — предотвратить несанкционированную передачу конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) за пределы организации через все возможные интернет-каналы.</t>
@@ -18009,9 +18009,9 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D251" s="65" t="inlineStr">
-        <is>
-          <t>Мера требует организовать блокирование неразрешенной и контроль (анализ) разрешенной печати информации конфиденциального характера.
+      <c r="D251" s="163" t="inlineStr">
+        <is>
+          <t>Печать информации конфиденциального характера также подлежит блокированию в неразрешённых случаях и контролю (анализу) в разрешённых.
 Блокирование — запрет на печать документов, содержащих конфиденциальную информацию, если это не разрешено политиками безопасности.
 Контроль (анализ) — для разрешенных сценариев печати организуется анализ содержимого документов, чтобы убедиться, что печатается именно та информация и в том объеме, который разрешен.
 Главная цель меры — предотвратить несанкционированное выведение конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) на бумажные носители.</t>
@@ -18078,9 +18078,9 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D252" s="34" t="inlineStr">
-        <is>
-          <t>Мера ПУИ.4 требует организовать блокирование неразрешенного и контроль (анализ) разрешенного копирования информации конфиденциального характера на переносные (отчуждаемые) носители информации.
+      <c r="D252" s="144" t="inlineStr">
+        <is>
+          <t>Копирование информации конфиденциального характера на переносные (отчуждаемые) носители информации должно быть заблокировано в неразрешённых случаях и подконтрольно (проанализировано) в разрешённых.
 Блокирование — запрет на копирование документов, содержащих конфиденциальную информацию, на съемные носители, если это не разрешено политиками безопасности.
 Контроль (анализ) — для разрешенных сценариев копирования организуется анализ содержимого документов, чтобы убедиться, что копируется именно та информация и в том объеме, который разрешен.
 Главная цель меры — предотвратить несанкционированное копирование конфиденциальных данных (персональных данных, банковской тайны, коммерческой тайны и т.п.) на внешние носители, которые могут быть вынесены за пределы организации.</t>
@@ -18296,8 +18296,8 @@
       </c>
       <c r="D256" s="144" t="inlineStr">
         <is>
-          <t>Все отправленные и полученные электронные письма должны сохраняться в едином архиве: не менее 3 месяцев в режиме оперативного доступа (быстрый поиск) и не менее одного года в режиме архивного доступа.
-Главная цель меры — обеспечить, для более критичных (в сравнении с мерой ПИУ.6) уровней защиты, доступность содержимого переписки за более длительный период при расследовании утечки или инцидента, связанного с электронной почтой, компенсируя тем самым более отложенное во времени обнаружение отдельных инцидентов.</t>
+          <t>Электронные письма — как отправленные, так и полученные — должны сохраняться в едином архиве и для более критичного (в сравнении с мерой ПИУ.6) уровня защиты: не менее 3 месяцев в режиме оперативного доступа (быстрый поиск) и не менее одного года в режиме архивного доступа.
+Главная цель меры — обеспечить, для более критичных уровней защиты, доступность содержимого переписки за более длительный период при расследовании утечки или инцидента, связанного с электронной почтой, компенсируя тем самым более отложенное во времени обнаружение отдельных инцидентов.</t>
         </is>
       </c>
       <c r="E256" s="157" t="inlineStr">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="D274" s="144" t="inlineStr">
         <is>
-          <t>При выводе машинного носителя информации из эксплуатации (или его передаче в стороннюю организацию) информация стирается средствами гарантированного удаления информации, обеспечивающими более высокий, в сравнении с мерой ПУИ.23, уровень исключения возможности восстановления данных.
+          <t>Для носителей повышенной критичности вывод машинного носителя информации из эксплуатации (или его передача в стороннюю организацию) требует стирания информации средствами гарантированного удаления, обеспечивающими более высокий, в сравнении с мерой ПУИ.23, уровень исключения возможности восстановления данных.
 Главная цель меры — не допустить восстановление и последующую утечку данных с носителя повышенной критичности при его списании (или списании привязанного средства вычислительной техники), применяя для таких носителей методы уничтожения, устойчивые не только к стандартным программным средствам восстановления, но и к специализированным методам криминалистического анализа.</t>
         </is>
       </c>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="D276" s="144" t="inlineStr">
         <is>
-          <t>При передаче (перезакреплении) машинного носителя информации между работниками или подразделениями стирание данных выполняется средствами гарантированного удаления информации — для носителей повышенной критичности, для которых полной перезаписи (мера ПУИ.25) недостаточно.
+          <t>Для носителей повышенной критичности, для которых полной перезаписи (мера ПУИ.25) недостаточно, при передаче (перезакреплении) между работниками или подразделениями стирание данных выполняется средствами гарантированного удаления информации.
 Главная цель меры — обеспечить тот же результат исключения доступа к остаточным данным прежнего владельца, что и мера ПУИ.25, но применительно к носителям с повышенным уровнем защищаемой информации, для которых требуется более строгий метод удаления, устойчивый к специализированным методам восстановления.</t>
         </is>
       </c>
@@ -20058,7 +20058,7 @@
       </c>
       <c r="D284" s="144" t="inlineStr">
         <is>
-          <t>Мера требует регистрации в качестве события защиты информации каждого факта стирания информации с машинных носителей информации (МНИ), выполненного в рамках мер ПУИ.23—ПУИ.26.
+          <t>Каждый факт стирания информации с машинных носителей информации (МНИ), выполненного в рамках мер ПУИ.23—ПУИ.26, подлежит регистрации в качестве события защиты информации.
 Главная цель меры — зафиксировать отдельным событием сам факт и результат выполненного стирания, дополняя формируемый техническими средствами протокол (мера ПУИ.23) организационной регистрацией: это позволяет впоследствии подтвердить, что стирание было выполнено в отношении конкретного носителя, в установленный срок и уполномоченным лицом, а не только предъявить сам факт наличия протокола без привязки к организационному контролю.</t>
         </is>
       </c>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="D287" s="144" t="inlineStr">
         <is>
-          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых техническими мерами, входящими в состав системы защиты информации (СЗИ от НСД, средствами криптографической защиты, средствами защиты от вредоносного кода, DLP-системой и иными применяемыми техническими средствами защиты).
+          <t>Отдельного мониторинга требуют данные регистрации о событиях защиты информации, формируемые техническими мерами, входящими в состав системы защиты информации (СЗИ от НСД, средствами криптографической защиты, средствами защиты от вредоносного кода, DLP-системой и иными применяемыми техническими средствами защиты).
 Главная цель меры — обеспечить непрерывное наблюдение именно за тем массивом событий, который формируют сами средства защиты, поскольку он в первую очередь содержит прямые индикаторы срабатывания защитных механизмов, попыток их обхода или нарушения их штатной работы, и без организованного мониторинга такие индикаторы остаются недоступными для своевременного реагирования.</t>
         </is>
       </c>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="D289" s="144" t="inlineStr">
         <is>
-          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых сетевыми приложениями и сервисами — веб-серверами, почтовыми серверами, прокси, DNS и другими сервисами инфраструктуры.
+          <t>Мониторингом должны быть охвачены и данные регистрации о событиях защиты информации, формируемые сетевыми приложениями и сервисами — веб-серверами, почтовыми серверами, прокси, DNS и другими сервисами инфраструктуры.
 Главная цель меры — своевременно обнаруживать случаи компрометации сетевых приложений и сервисов: именно эти компоненты, как правило, непосредственно доступны из внешней или менее доверенной сети и чаще других становятся точкой первичного проникновения, а их собственные журналы содержат специфичные для конкретного протокола или приложения индикаторы атаки, недоступные на уровне сетевого оборудования (мера МАС.2).</t>
         </is>
       </c>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="D290" s="144" t="inlineStr">
         <is>
-          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых системным ПО — операционными системами и системами управления базами данных (СУБД).
+          <t>Отдельный объект мониторинга — данные регистрации о событиях защиты информации, формируемые системным ПО: операционными системами и системами управления базами данных (СУБД).
 Главная цель меры — своевременно обнаруживать случаи повышения привилегий, несанкционированного изменения данных или компрометации учётной записи администратора на уровне, максимально приближённом к самим защищаемым данным: события аутентификации, изменения прав и операций с данными на уровне ОС и СУБД зачастую являются первым (а иногда единственным) индикатором инцидента, не проявляющимся на сетевом уровне.</t>
         </is>
       </c>
@@ -20417,7 +20417,7 @@
       </c>
       <c r="D291" s="169" t="inlineStr">
         <is>
-          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых автоматизированными системами (АС) и прикладными приложениями организации.
+          <t>Мониторинг должен распространяться и на данные регистрации о событиях защиты информации, формируемые автоматизированными системами (АС) и прикладными приложениями организации.
 Главная цель меры — обеспечить видимость событий на уровне бизнес-логики самих АС (например, финансовых транзакций, изменений клиентских данных), которые не отражаются ни в журналах сетевого оборудования (мера МАС.2), ни в журналах ОС/СУБД (мера МАС.4): именно на этом уровне выявляются мошеннические операции и нарушения бизнес-процессов, невидимые на инфраструктурном уровне.</t>
         </is>
       </c>
@@ -20485,7 +20485,7 @@
       </c>
       <c r="D292" s="144" t="inlineStr">
         <is>
-          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых контроллерами доменов.
+          <t>Приоритетным объектом мониторинга данных регистрации о событиях защиты информации мера определяет контроллеры доменов.
 Главная цель меры — обеспечить приоритетное наблюдение за наиболее критичным компонентом инфраструктуры аутентификации и авторизации: компрометация контроллера домена предоставляет злоумышленнику контроль над учётными записями и правами доступа в масштабе всей инфраструктуры, что делает своевременное выявление признаков такой компрометации (например, необычной активности встроенных привилегированных групп) задачей повышенного приоритета по сравнению с мониторингом рядового сервера.</t>
         </is>
       </c>
@@ -20554,7 +20554,7 @@
       </c>
       <c r="D293" s="144" t="inlineStr">
         <is>
-          <t>Мера требует организации мониторинга данных регистрации о событиях защиты информации, формируемых средствами (системами) контроля и управления доступом (СКУД).
+          <t>Мониторинг событий защиты информации должен охватывать и данные регистрации, формируемые средствами (системами) контроля и управления доступом (СКУД).
 Главная цель меры — распространить мониторинг событий защиты информации на физический уровень доступа: события СКУД (проход через контролируемую точку доступа, попытки прохода вне графика, срабатывание тревожных датчиков) необходимы для сопоставления с событиями логического доступа (например, для выявления входа в АС с рабочего места сотрудника, физически не присутствующего в контролируемой зоне в это время).</t>
         </is>
       </c>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="D305" s="144" t="inlineStr">
         <is>
-          <t>Система обработки данных регистрации должна уметь приводить события от разных источников к единому формату (нормализация), а также фильтровать, агрегировать и классифицировать их.
+          <t>Обработка данных регистрации должна включать приведение событий от разных источников к единому формату (нормализация), а также их фильтрацию, агрегацию и классификацию.
 Главная цель меры — сделать разнородные журналы разных источников пригодными для совместного анализа: события от различных систем, как правило, хранятся в несовместимых форматах и не сопоставляются между собой без предварительной обработки, что без нормализации, фильтрации и агрегации делает невозможным сквозной анализ данных регистрации при расследовании инцидента.</t>
         </is>
       </c>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="D306" s="144" t="inlineStr">
         <is>
-          <t>Система обработки данных регистрации должна обеспечивать автоматическое выявление и анализ событий, потенциально связанных с инцидентами защиты информации, включая несанкционированный доступ, — например, через корреляционные правила, а не простое хранение сырых журналов.
+          <t>Возможность автоматического выявления и анализа событий, потенциально связанных с инцидентами защиты информации, включая несанкционированный доступ, — например, посредством корреляционных правил, а не простого хранения сырых журналов, — должна обеспечивать система обработки данных регистрации.
 Главная цель меры — сложить в единую картину атаку, растянутую во времени и по разным источникам: отдельное событие, зафиксированное на одном источнике, зачастую не выглядит подозрительным само по себе, и только автоматизированная корреляция цепочки связанных событий разных источников позволяет своевременно выявить признаки развивающегося инцидента.</t>
         </is>
       </c>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="D307" s="144" t="inlineStr">
         <is>
-          <t>Система обработки данных регистрации должна позволять получить полный перечень действий и операций конкретного субъекта доступа за заданный период — то есть строить историю «что делал конкретный пользователь».
+          <t>Получение полного перечня действий и операций конкретного субъекта доступа за заданный период — то есть построение истории «что делал конкретный пользователь» — также должно быть доступно в системе обработки данных регистрации.
 Главная цель меры — обеспечить возможность расследования активности конкретного пользователя при подозрении на инсайдерскую деятельность или компрометацию его учётной записи: без возможности выборки по субъекту доступа аналитик вынужден вручную просматривать разрозненные события множества источников, что делает подобное расследование практически неосуществимым в разумные сроки.</t>
         </is>
       </c>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="D308" s="144" t="inlineStr">
         <is>
-          <t>Система обработки данных регистрации должна позволять получить полный перечень действий субъектов доступа применительно к конкретному ресурсу доступа — то есть строить историю «кто обращался к конкретному ресурсу», в отличие от меры МАС.19, где выборка строится от субъекта, а здесь — от ресурса.
+          <t>В дополнение к мере МАС.19 система обработки данных регистрации должна позволять получить полный перечень действий субъектов доступа применительно к конкретному ресурсу доступа — то есть строить историю «кто обращался к конкретному ресурсу», где, в отличие от МАС.19, выборка строится не от субъекта, а от ресурса.
 Главная цель меры — при инциденте, связанном с компрометацией или утечкой конкретного ресурса (базы данных, файла, сервера), быстро установить полный круг лиц, обращавшихся к нему за интересующий период, что невозможно, если система обработки данных регистрации позволяет строить выборки только по субъекту, но не по объекту доступа.</t>
         </is>
       </c>
@@ -22308,7 +22308,7 @@
       </c>
       <c r="D321" s="144" t="inlineStr">
         <is>
-          <t>В организации должны быть определены и назначены роли, связанные с реагированием на инциденты защиты информации в целом — то есть закреплено, кто вовлекается в процесс реагирования и какие обязанности за ним закрепляются.
+          <t>Кто именно вовлекается в процесс реагирования на инциденты защиты информации и какие обязанности за ним закреплены, должно быть определено и зафиксировано отдельными назначенными ролями — в дополнение к самому порядку реагирования, установленному мерой РИ.6.
 Главная цель меры — устранить неопределённость ответственности и состава задач при реагировании на инцидент: без заранее определённых и назначенных ролей состав участников и распределение обязанностей формируются стихийно уже в момент возникновения инцидента, что неизбежно замедляет реагирование именно тогда, когда скорость реакции наиболее критична.</t>
         </is>
       </c>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -3088,11 +3088,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Реализация носит сугубо технический характер и охватывает настройку регистрации и контроля действий привилегированных пользователей. Основные направления технической реализации:
+Реализация носит сугубо технический характер и охватывает настройку регистрации и контроля действий привилегированных пользователей. Штатный аудит на уровне операционных систем, СУБД, сетевого оборудования и прикладного ПО закрывает саму регистрацию таких действий без отдельного приобретения средства защиты информации, но не решает задачу контроля — записи сессий привилегированного доступа, оперативного оповещения о деструктивных операциях и сквозной корреляции между разнородными источниками, для чего и нужны специализированные PAM и SIEM. Основные направления технической реализации:
 1. Настройка расширенного аудита действий привилегированных учётных записей на уровне операционных систем, СУБД, сетевого оборудования и прикладного ПО, охватывающая операции, способные привести к деструктивному воздействию (остановка сервисов, изменение критичных конфигураций, удаление данных, отключение средств защиты);
 2. Применение специализированных систем контроля действий привилегированных пользователей (PAM, Privileged Access Management), обеспечивающих запись сессий привилегированного доступа и журналирование выполненных команд;
 3. Централизованный сбор событий, связанных с действиями эксплуатационного персонала, в SIEM-системе с настройкой правил корреляции для выявления потенциально деструктивных операций.
-Класс используемых средств — системы контроля действий привилегированных пользователей (PAM), системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — встроенные средства аудита ОС/СУБД/сетевого оборудования (штатная регистрация); системы контроля действий привилегированных пользователей (PAM) и системы управления событиями информационной безопасности (SIEM) — для записи сессий и централизованной корреляции.
 Иностранные: CyberArk PAM, BeyondTrust Privileged Remote Access и пр.
 Российские сертифицированные (ФСТЭК): «Система контроля привилегированных пользователей SafeInspect», Indeed Privileged Access Manager, MaxPatrol SIEM и др.
 Открытый код: Teleport, Wazuh и др.</t>
@@ -4059,11 +4059,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Так как организационных мер здесь не предусмотрено, всё сводится к техническим настройкам:
+Так как организационных мер здесь не предусмотрено, всё сводится к техническим настройкам. Выпуск и проверка сертификата устройства через внутренний удостоверяющий центр (Active Directory Certificate Services) и доменное членство АРМ — штатная возможность инфраструктуры Windows-домена, не требующая отдельного средства защиты информации, и для доступа из доверенной внутренней сети её, как правило, достаточно. Выделенное средство контроля доступа к сети (NAC) или VPN-шлюз с проверкой сертификата устройства становится необходимым, когда административный доступ осуществляется за пределами доменной сети — через VPN, беспроводные сети или сегменты с недоверенными коммутаторами, где штатные доменные политики не действуют:
 1. Использование сертификатов устройств (машинных сертификатов, выпущенных внутренним удостоверяющим центром) или иных технических признаков (например, привязки по MAC-адресу совместно с сертификатом, доменного членства АРМ), подтверждающих легитимность АРМ эксплуатационного персонала;
 2. Настройка средств сетевого доступа (VPN-шлюзов, систем контроля доступа к сети — NAC) таким образом, чтобы административный доступ предоставлялся только с АРМ, прошедших аутентификацию устройства;
 3. Технический запрет административного доступа с устройств, не прошедших аутентификацию (в том числе с личных и неучтённых устройств).
-Класс используемых средств — средства контроля доступа к сети (NAC), инфраструктура открытых ключей (PKI) для аутентификации устройств, VPN-шлюзы с проверкой сертификата устройства.
+Класс используемых средств — инфраструктура открытых ключей (PKI) и служба каталогов для аутентификации устройств по доменному членству (штатные возможности); средства контроля доступа к сети (NAC) и VPN-шлюзы с проверкой сертификата устройства — для доступа за пределами доменной сети.
 Иностранные: Cisco ISE, Palo Alto GlobalProtect и пр.
 Российские сертифицированные (ФСТЭК): «С-Терра Шлюз», ViPNet Coordinator и др.
 Открытый код: FreeRADIUS (совместно с PKI) и др.</t>
@@ -4130,11 +4130,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Здесь требуются только технические решения:
+Здесь требуются только технические решения. Как и в мере РД.6 (для эксплуатационного персонала), проверка сертификата устройства или доменного членства АРМ — штатная возможность инфраструктуры Windows-домена, не требующая отдельного средства защиты информации, и для доступа из доверенной внутренней сети её обычно достаточно:
 1. Использование сертификатов устройств или доменного членства АРМ пользователей как условия для предоставления логического доступа к информационным ресурсам;
-2. Настройка средств контроля доступа к сети (NAC) или VPN-шлюзов таким образом, чтобы доступ предоставлялся только с АРМ, прошедших проверку принадлежности к корпоративному парку устройств;
+2. Настройка средств контроля доступа к сети (NAC) или VPN-шлюзов таким образом, чтобы доступ предоставлялся только с АРМ, прошедших проверку принадлежности к корпоративному парку устройств — там, где доступ осуществляется за пределами доменной сети (VPN, беспроводные сети, недоверенные сегменты);
 3. Технический запрет доступа с личных, неучтённых или не прошедших проверку устройств.
-Класс используемых средств — средства контроля доступа к сети (NAC), инфраструктура открытых ключей (PKI) для аутентификации устройств, службы каталогов с привязкой устройств к домену.
+Класс используемых средств — инфраструктура открытых ключей (PKI) и служба каталогов с привязкой устройств к домену (штатные возможности); средства контроля доступа к сети (NAC) и VPN-шлюзы — для доступа за пределами доменной сети.
 Иностранные: Microsoft Active Directory (доменное членство), Cisco ISE и пр.
 Российские сертифицированные (ФСТЭК): Secret Net Studio, ViPNet Coordinator и др.
 Открытый код: FreeRADIUS, FreeIPA и др.</t>
@@ -4477,10 +4477,10 @@
           <r>
             <t xml:space="preserve">
 Так как мера реализуется только техническими средствами, необходимо:
-1. Настройку информационных систем и служб каталогов таким образом, чтобы при попытке открытия новой сессии под учётной записью, уже имеющей активную сессию с другого АРМ, происходил отказ в доступе либо принудительное завершение предыдущей сессии;
-2. Централизованный контроль активных сессий (Single Session Enforcement) через систему управления доступом или средства терминального доступа;
+1. Настройку информационных систем и служб каталогов таким образом, чтобы при попытке открытия новой сессии под учётной записью, уже имеющей активную сессию с другого АРМ, происходил отказ в доступе либо принудительное завершение предыдущей сессии — для систем на базе Active Directory и терминальных служб данная настройка штатная и не требует отдельного средства защиты информации;
+2. Централизованный контроль активных сессий (Single Session Enforcement) через систему управления доступом или специализированные средства терминального доступа — там, где парк систем неоднороден и штатных доменных политик недостаточно для единой точки контроля;
 3. Регистрацию попыток открытия параллельных сессий под одной учётной записью для последующего анализа на предмет возможной компрометации.
-Класс используемых средств — средства терминального доступа и виртуализации рабочих столов (VDI), системы контроля сессий, службы каталогов с политикой ограничения одновременных сеансов.
+Класс используемых средств — служба каталогов с политикой ограничения одновременных сеансов (штатная возможность для доменных систем); при неоднородном парке систем — специализированные средства терминального доступа и виртуализации рабочих столов (VDI), системы контроля сессий.
 Иностранные: Citrix Virtual Apps and Desktops, Microsoft Remote Desktop Services (ограничение сессий) и пр.
 Российские сертифицированные (ФСТЭК): «Термидеск», Astra Linux (совместно со средствами разграничения сессий) и др.
 Открытый код: FreeRDP (с ограничениями на стороне сервера) и др.</t>
@@ -5053,12 +5053,12 @@
           <r>
             <t xml:space="preserve">
 Так как речь идёт о чисто технической мере, реализация включает:
-1. Настройку в системах управления привилегированным доступом, службах каталогов и на управляемом оборудовании политики максимального срока действия пароля эксплуатационного персонала, не превышающего 90 дней;
+1. Настройку раздельной (более строгой) политики максимального срока действия пароля эксплуатационного персонала, не превышающего 90 дней, — для доменных систем это штатная возможность (например, Fine-Grained Password Policy в Active Directory), не требующая отдельного средства защиты информации; для неоднородного парка систем и оборудования, где такой штатной политики нет, применяются системы управления привилегированным доступом (PAM);
 2. Применение более строгого контроля соблюдения данной политики по сравнению с учётными записями рядовых пользователей — с учётом повышенной критичности привилегированных прав доступа;
 3. Технический запрет на продолжение административной работы под учётной записью с истёкшим сроком действия пароля;
 4. Технический запрет на повторное использование ранее применявшихся паролей (история паролей) для привилегированных учётных записей.
-Класс используемых средств — системы управления привилегированным доступом (PAM), службы каталогов с политикой паролей.
-Иностранные: CyberArk PAM, Microsoft Active Directory (Fine-Grained Password Policy) и пр.
+Класс используемых средств — служба каталогов с раздельной политикой паролей для привилегированных учётных записей (штатная возможность, например Fine-Grained Password Policy); для централизованного контроля неоднородного парка систем — системы управления привилегированным доступом (PAM).
+Иностранные: Microsoft Active Directory (Fine-Grained Password Policy), CyberArk PAM и пр.
 Российские сертифицированные (ФСТЭК): Indeed Privileged Access Manager, «Система контроля привилегированных пользователей SafeInspect» и др.
 Открытый код: Teleport и др.</t>
           </r>
@@ -5194,11 +5194,11 @@
           <r>
             <t xml:space="preserve">
 Организационные меры для данного требования не предусмотрены — реализация строится на технических решениях:
-1. Настройку отдельной (более строгой) политики паролей для привилегированных (административных) учётных записей — минимальная длина пароля не менее шестнадцати символов;
+1. Настройку отдельной (более строгой) политики паролей для привилегированных (административных) учётных записей — минимальная длина пароля не менее шестнадцати символов; для доменных систем это штатная возможность (Fine-Grained Password Policy в Active Directory), не требующая отдельного средства защиты информации;
 2. Технический запрет на установку эксплуатационным персоналом пароля короче установленного минимума;
-3. Распространение данной настройки на все административные интерфейсы и системы, к которым эксплуатационный персонал осуществляет логический доступ, включая сетевое оборудование и средства защиты информации.
-Класс используемых средств — системы управления привилегированным доступом (PAM), службы каталогов с раздельными политиками паролей (Fine-Grained Password Policy).
-Иностранные: CyberArk PAM, Microsoft Active Directory (Fine-Grained Password Policy) и пр.
+3. Распространение данной настройки на все административные интерфейсы и системы, к которым эксплуатационный персонал осуществляет логический доступ, включая сетевое оборудование и средства защиты информации — там, где штатной политики службы каталогов недостаточно (оборудование и системы, не интегрированные с доменом), применяются системы управления привилегированным доступом (PAM).
+Класс используемых средств — служба каталогов с раздельными политиками паролей (Fine-Grained Password Policy — штатная возможность); для оборудования и систем вне домена — системы управления привилегированным доступом (PAM).
+Иностранные: Microsoft Active Directory (Fine-Grained Password Policy), CyberArk PAM и пр.
 Российские сертифицированные (ФСТЭК): Indeed Privileged Access Manager, Secret Net Studio и др.
 Открытый код: Teleport и др.</t>
           </r>
@@ -6060,11 +6060,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Технически права логического доступа разграничиваются так:
+Базовое разделение учётных записей и техническое ограничение состава ролей, доступных привилегированной учётной записи (пункты 1–2), реализуются штатными средствами разграничения доступа (ролевой моделью АС, группами Active Directory) без отдельного средства защиты информации. Для автоматизированного анализа и оповещения о фактах использования привилегированной учётной записи не по назначению (пункт 3) штатных средств недостаточно — нужны PAM и SIEM:
 1. Предоставление эксплуатационному персоналу двух раздельных учётных записей — привилегированной (административной) для задач эксплуатации и обычной пользовательской для выполнения непроизводственных операций (при их наличии у данного сотрудника);
 2. Технический запрет использования привилегированных учётных записей для входа в АС и выполнения в них функций, относящихся к бизнес-процессам и технологическим процессам (например, ограничение состава ролей, доступных привилегированной учётной записи, только административными функциями);
 3. Регистрацию и автоматизированный анализ фактов выполнения под привилегированными учётными записями операций, типичных для бизнес-процессов, с оповещением подразделения информационной безопасности при выявлении таких фактов.
-Класс используемых средств — системы управления привилегированным доступом (PAM), системы управления событиями информационной безопасности (SIEM).
+Класс используемых средств — ролевая модель доступа АС и служба каталогов (штатное разграничение ролей); системы управления привилегированным доступом (PAM) и системы управления событиями информационной безопасности (SIEM) — для автоматизированного анализа и оповещения.
 Иностранные: CyberArk PAM, Splunk (для анализа журналов) и пр.
 Российские сертифицированные (ФСТЭК): Indeed Privileged Access Manager, MaxPatrol SIEM и др.
 Открытый код: Teleport, Wazuh и др.</t>
@@ -6651,14 +6651,14 @@
           </r>
           <r>
             <t xml:space="preserve">
-Так как организационных мер здесь не предусмотрено, всё сводится к техническим настройкам:
+Так как организационных мер здесь не предусмотрено, всё сводится к техническим настройкам. Сама регистрация факта запуска сервиса — штатная возможность журнала операционной системы (Windows Event Log, systemd journal), не требующая отдельного средства защиты информации; для централизованного сбора и анализа таких событий по всему парку серверов и АРМ штатного локального журналирования недостаточно, требуется система управления событиями информационной безопасности (SIEM):
 1. Настройку регистрации события запуска каждого программного сервиса (службы, приложения, скрипта автоматизации), осуществляющего логический доступ к информационным ресурсам от имени технической учётной записи;
 2. Фиксацию в журнале как минимум даты и времени запуска, идентификатора сервиса и технической учётной записи, от имени которой он запущен;
 3. Централизованный сбор данных о запуске программных сервисов для последующего анализа на предмет выявления несанкционированного или аномального запуска.
-Класс используемых средств — системы управления событиями информационной безопасности (SIEM), средства мониторинга процессов и служб операционных систем.
-Иностранные: Splunk, Microsoft Sysmon (мониторинг запуска процессов) и пр.
+Класс используемых средств — встроенные средства журналирования операционных систем (штатная регистрация запуска сервисов); системы управления событиями информационной безопасности (SIEM) и средства мониторинга процессов — для централизованного сбора и анализа.
+Иностранные: Microsoft Sysmon (мониторинг запуска процессов), Splunk и пр.
 Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, RuSIEM и др.
-Открытый код: Wazuh, osquery и др.</t>
+Открытый код: osquery, Wazuh и др.</t>
           </r>
         </is>
       </c>
@@ -6725,13 +6725,13 @@
           </r>
           <r>
             <t xml:space="preserve">
-Мера реализуется исключительно техническими средствами:
+Мера реализуется исключительно техническими средствами. Сама регистрация факта изменения аутентификационных данных — штатная возможность операционных систем, служб каталогов, СУБД и прикладных информационных систем, не требующая отдельного средства защиты информации; для централизованного сбора и анализа таких событий на предмет аномалий по всей инфраструктуре штатного локального журналирования недостаточно, требуется система управления событиями информационной безопасности (SIEM):
 1. Настройку операционных систем, каталогов, СУБД и прикладных информационных систем на регистрацию каждого факта изменения аутентификационных данных субъекта (смены пароля, перевыпуска сертификата, привязки/отвязки фактора МФА);
 2. Фиксацию в журнале как минимум даты и времени изменения, идентификатора субъекта, инициатора изменения (сам субъект или администратор) и результата операции;
 3. Централизованный сбор данных об изменениях аутентификационных данных для последующего анализа на предмет аномалий.
-Класс используемых средств — системы управления событиями информационной безопасности (SIEM), службы каталогов и системы управления учётными записями (IdM) со встроенным аудитом.
-Иностранные: Splunk, Microsoft Active Directory (Audit Credential Validation) и пр.
-Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, Avanpost IDM и др.
+Класс используемых средств — встроенные средства аудита операционных систем, служб каталогов, СУБД и систем управления учётными записями (IdM) — штатная регистрация; системы управления событиями информационной безопасности (SIEM) — для централизованного сбора и анализа.
+Иностранные: Microsoft Active Directory (Audit Credential Validation), Splunk и пр.
+Российские сертифицированные (ФСТЭК): Avanpost IDM, MaxPatrol SIEM и др.
 Открытый код: Wazuh, ELK Stack и др.</t>
           </r>
         </is>
@@ -9132,11 +9132,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Реализация меры предполагает настройку журналирования событий на всех компонентах сетевой инфраструктуры, где происходит подключение объектов доступа:
-1. Настройку средств контроля сетевого доступа (NAC — Network Access Control) или систем обнаружения сетевых устройств, обеспечивающих автоматическую регистрацию появления новых объектов доступа в вычислительных сетях организации;
-2. Настройку регистрации событий подключения объектов доступа (серверов, рабочих станций, сетевого оборудования, банкоматов и платёжных терминалов) в журналах безопасности сетевых устройств (коммутаторов с поддержкой SNMP, систем управления IP-адресами — IPAM) и системах NAC (например, Cisco ISE, ForeScout, PacketFence);
-3. Настройку протоколирования фактов установления сетевого соединения с фиксацией MAC-адреса и IP-адреса подключаемого объекта, временной метки и порта коммутатора, к которому выполнено подключение.
-Класс используемых средств — средства контроля сетевого доступа (NAC), активное сетевое оборудование со встроенным журналированием.
+Реализация меры предполагает настройку журналирования событий на всех компонентах сетевой инфраструктуры, где происходит подключение объектов доступа. Базовая фиксация факта подключения (MAC-адрес, IP-адрес, время, порт коммутатора) достигается штатными средствами уже имеющегося управляемого сетевого оборудования (журналы коммутаторов с поддержкой SNMP, системы управления IP-адресами — IPAM) без отдельного приобретения; выделенное средство контроля сетевого доступа (NAC) становится необходимым для автоматической классификации подключаемых устройств, профилирования и активного реагирования (карантина) на неизвестные объекты доступа, чего штатное журналирование коммутаторов не обеспечивает:
+1. Настройку регистрации событий подключения объектов доступа (серверов, рабочих станций, сетевого оборудования, банкоматов и платёжных терминалов) в журналах безопасности сетевых устройств (коммутаторов с поддержкой SNMP, систем управления IP-адресами — IPAM);
+2. Настройку протоколирования фактов установления сетевого соединения с фиксацией MAC-адреса и IP-адреса подключаемого объекта, временной метки и порта коммутатора, к которому выполнено подключение;
+3. Настройку средств контроля сетевого доступа (NAC) или систем обнаружения сетевых устройств для автоматической классификации, профилирования и (при необходимости) карантина неизвестных объектов доступа.
+Класс используемых средств — активное сетевое оборудование со встроенным журналированием и системы управления IP-адресами (IPAM) — штатные возможности; средства контроля сетевого доступа (NAC) — для автоматической классификации и активного реагирования.
 Иностранные: Cisco ISE, ForeScout CounterACT, Aruba ClearPass и пр.
 Российские сертифицированные (ФСТЭК): Ideco NAC, «Solar inCode» и др.
 Открытый код: PacketFence, OpenNAC и др.</t>
@@ -12015,11 +12015,12 @@
           </r>
           <r>
             <t xml:space="preserve">
-Поскольку мера реализуется только техническими методами, её внедрение предполагает:
+Поскольку мера реализуется только техническими методами, её внедрение предполагает применение криптографических протоколов, многие из которых штатно встроены в операционные системы и прикладное ПО без отдельного приобретения (TLS — в браузеры, СУБД, веб-серверы; SSH — в серверные операционные системы) и не требуют выделенного средства защиты информации, если для аутентификации сторон используется собственная (внутренняя) инфраструктура открытых ключей организации:
 1. Применение криптографических сетевых протоколов, обеспечивающих одновременно шифрование (либо, как минимум, контроль целостности) передаваемых данных и взаимную аутентификацию сторон соединения — TLS с двусторонней (mutual) аутентификацией по сертификатам, IPsec с аутентификацией на основе сертификатов или предустановленных ключей, SSH с аутентификацией по ключам;
 2. Технический запрет на установление соединений по неконтролируемым каналам связи с использованием протоколов, не обеспечивающих контроль целостности и (или) двустороннюю аутентификацию (например, устаревших версий TLS, протоколов без проверки сертификата сервера и клиента);
 3. Периодический технический контроль (сканирование, анализ конфигураций) фактически применяемых версий протоколов и параметров аутентификации на предмет соответствия установленным требованиям.
-Класс используемых средств — средства криптографической защиты каналов связи (VPN-шлюзы, TLS-терминаторы), инфраструктура открытых ключей (PKI).
+Выделенный VPN-шлюз становится необходим не для защиты отдельного протокола прикладного уровня, а для организации туннелируемого сетевого доступа (площадка-площадка, удалённый доступ), где требуется единая точка управления политиками и централизованный контроль подключений.
+Класс используемых средств — штатные криптографические протоколы (TLS, SSH, IPsec) операционных систем и прикладного ПО с использованием внутренней инфраструктуры открытых ключей (PKI); для организации туннелируемого доступа — выделенные VPN-шлюзы.
 Иностранные: Cisco AnyConnect, Palo Alto GlobalProtect и пр.
 Российские сертифицированные (ФСТЭК): «С-Терра Шлюз», ViPNet Coordinator, «Континент» (VPN) и др.
 Открытый код: OpenVPN, WireGuard (с внешним PKI) и др.</t>
@@ -13993,12 +13994,12 @@
           </r>
           <r>
             <t xml:space="preserve">
-Мера широкая и закрывается несколькими дополняющими друг друга техническими подходами:
+Штатным (не требующим отдельного приобретения) базовым каналом распространения обновлений служат встроенные механизмы самой операционной системы — служба WSUS (роль Windows Server) для домена Windows или unattended-upgrades/apt-mirror для Linux, — способные централизованно распространять обновления по расписанию без выделенного средства защиты информации. Однако штатных средств недостаточно для явно требуемого мерой контроля фактического охвата парка АРМ, автоматического выявления отставших устройств и их принудительной изоляции — для этого мера широкая и закрывается несколькими дополняющими друг друга техническими подходами:
 1. Патч-менеджмент АРМ — централизованное развёртывание обновлений на пользовательские рабочие станции по расписанию, с контролем фактического охвата парка;
 2. Централизованное управление конечными точками (EPP-платформа или платформа управления АРМ) — единая консоль обновления ПО как один из модулей общей платформы защиты рабочих станций;
 3. Контроль целостности и состава ПО АРМ — фиксация эталонного набора версий ПО на образе АРМ и выявление отклонений (устаревшая версия, самовольный откат);
 4. Регистрация и сверка через SIEM-систему — события установки и обновления ПО на АРМ (см. также меру ЦЗИ.29) собираются в SIEM и сверяются с плановым графиком.
-Класс используемых средств — системы управления обновлениями и уязвимостями (Patch/Vulnerability Management), платформы централизованного управления конечными точками (EPP).
+Класс используемых средств — штатная служба обновлений ОС (WSUS, apt) для базового распространения обновлений; системы управления обновлениями и уязвимостями (Patch/Vulnerability Management) и платформы централизованного управления конечными точками (EPP) — для контроля охвата парка, отчётности и выявления отклонений.
 Иностранные: Ivanti Patch Management, Microsoft SCCM и пр.
 Российские сертифицированные (ФСТЭК): MaxPatrol VM, Kaspersky Security Center (модуль управления обновлениями) и др.
 Открытый код: Ansible (плейбуки инвентаризации и обновления пакетов) и др.</t>
@@ -14606,11 +14607,11 @@
           </r>
           <r>
             <t xml:space="preserve">
-Технический контроль реализуется:
+Базовую инвентаризацию установленного ПО можно получить штатными средствами (диспетчер пакетов операционной системы, PowerShell/WMI-запросы, скрипты) без отдельного приобретения. Однако штатных средств недостаточно для требуемого мерой автоматического сопоставления фактического состава ПО с эталонным перечнем и оповещения ответственных лиц по всему парку АРМ — для этого технический контроль реализуется:
 1. Автоматизированной инвентаризацией фактически установленного и запущенного ПО на АРМ;
 2. Автоматическим сопоставлением результатов инвентаризации с перечнем разрешённого ПО и формированием отчёта об отклонениях;
 3. Оповещением ответственных лиц при выявлении неразрешённого ПО.
-Класс используемых средств — системы инвентаризации программного обеспечения (Software Asset Management), также реализуемые как модуль EDR/EPP-платформы или платформы централизованного управления АРМ.
+Класс используемых средств — штатный диспетчер пакетов ОС и сценарии инвентаризации (базовый уровень); системы инвентаризации программного обеспечения (Software Asset Management), также реализуемые как модуль EDR/EPP-платформы или платформы централизованного управления АРМ — для автоматического сопоставления и оповещения по всему парку.
 Иностранные: Microsoft SCCM (инвентаризация ПО), Flexera (Software Asset Management) и пр.
 Российские сертифицированные (ФСТЭК): Kaspersky Security Center (инвентаризация ПО), Secret Net Studio (модуль контроля состава ПО) и др.
 Открытый код: Wazuh (модуль инвентаризации ПО, syscollector) и др.</t>
@@ -14880,7 +14881,7 @@
           </r>
           <r>
             <t xml:space="preserve">
-Мера требует реализацию контроля состава ПО, запускаемого при загрузке ОС, что достигается средствами доверенной загрузки (СДЗ) — как правило, отдельным аппаратно-программным модулем доверенной загрузки (АПМДЗ). Такие средства инициализируются до полной загрузки ОС и формируют независимую от неё проверку состава компонентов, участвующих в загрузке.
+Мера требует реализацию контроля состава ПО, запускаемого при загрузке ОС, что достигается средствами доверенной загрузки (СДЗ) — как правило, отдельным аппаратно-программным модулем доверенной загрузки (АПМДЗ). Такие средства инициализируются до полной загрузки ОС и формируют независимую от неё проверку состава компонентов, участвующих в загрузке. Встроенного в большинство современных АРМ механизма UEFI Secure Boot самого по себе недостаточно для закрытия меры: он не является сертифицированным средством доверенной загрузки, не формирует независимого от ОС журнала событий контроля (см. также меру ЦЗИ.33) и не удовлетворяет требованиям ФСТЭК/ФСБ к доверенной загрузке — поэтому необходим именно отдельный сертифицированный аппаратно-программный модуль.
 При выборе инструмента реализации необходимо запрашивать у производителя техническую документацию (руководство администратора), явно подтверждающую работу заявленного механизма на этапе, предшествующем полной загрузке ОС, и уточнять, требуется ли для этого отдельный сертифицированный модуль, не входящий в базовую поставку продукта (см. выявленные коллизии).
 Класс используемых средств — аппаратно-программные модули доверенной загрузки (АПМДЗ) / средства доверенной загрузки (СДЗ).
 Российские сертифицированные (ФСТЭК/ФСБ): ПАК «Соболь» (Код Безопасности), «Аккорд-АМДЗ» (ОКБ САПР) и др. Зарубежные и открытые аналоги данного класса в РФ не применяются в силу требований ФСТЭК/ФСБ к доверенной загрузке.</t>
@@ -14976,8 +14977,8 @@
           </r>
           <r>
             <t xml:space="preserve">
-На АРМ устанавливается средство контроля целостности (класс File Integrity Monitoring / Application Control в составе EDR/HIPS), которое при запуске компонента ПО АС сверяет его контрольную сумму или цифровую подпись с эталонным значением, а при несовпадении — блокирует запуск и генерирует событие защиты информации (см. также меру ЦЗИ.34 в части регистрации результатов).
-Класс используемых средств — средства контроля целостности запускаемых файлов (File Integrity Monitoring), в том числе в составе EDR/HIPS-платформы.
+На АРМ устанавливается средство контроля целостности (класс File Integrity Monitoring / Application Control в составе EDR/HIPS), которое при запуске компонента ПО АС сверяет его контрольную сумму или цифровую подпись с эталонным значением, а при несовпадении — блокирует запуск и генерирует событие защиты информации (см. также меру ЦЗИ.34 в части регистрации результатов). Для АРМ на базе Windows частично штатным вариантом (без отдельного приобретения EDR/HIPS) выступают встроенные компоненты AppLocker или Windows Defender Application Control (WDAC), поддерживающие проверку цифровой подписи (хеша) файла перед запуском; однако для полноценного покрытия требования меры — централизованного управления эталонными значениями по всему парку АРМ и передачи событий блокировки в общий контур регистрации (мера ЦЗИ.34) — штатных возможностей, как правило, недостаточно, и используется специализированное средство защиты.
+Класс используемых средств — встроенные компоненты контроля запуска приложений операционной системы (AppLocker, WDAC — штатная, частичная возможность); средства контроля целостности запускаемых файлов (File Integrity Monitoring) в составе EDR/HIPS-платформы — для централизованного управления и регистрации по всему парку.
 Иностранные: Carbon Black App Control, Tripwire for Servers и пр.
 Российские сертифицированные (ФСТЭК): Kaspersky Endpoint Security для бизнеса (модуль контроля целостности/Application Control), Dallas Lock 8.0 (СЗИ от НСД с функцией контроля целостности) и др.
 Открытый код: Wazuh (модуль FIM — File Integrity Monitoring) и др.</t>
@@ -18244,8 +18245,8 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация обеспечивается развёртыванием системы архивирования электронной почты, автоматически копирующей каждое отправленное и полученное сообщение в единый архив с раздельным хранением: последние (не менее одного месяца) сообщения — в режиме оперативного (быстрого) доступа, а весь период (не менее 6 месяцев) — в режиме архивного доступа с более длительным временем поиска.
-Класс используемых средств — системы архивирования электронной почты (Email Archiving), часто интегрируемые с DLP-системой как единая платформа хранения.
+Техническая реализация обеспечивается развёртыванием системы архивирования электронной почты, автоматически копирующей каждое отправленное и полученное сообщение в единый архив с раздельным хранением: последние (не менее одного месяца) сообщения — в режиме оперативного (быстрого) доступа, а весь период (не менее 6 месяцев) — в режиме архивного доступа с более длительным временем поиска. Для организаций на базе Microsoft Exchange/Exchange Online частично штатным вариантом (без отдельного приобретения) выступают встроенные политики хранения (Retention Policies) и функция In-Place Archive; однако штатных возможностей почтового сервера, как правило, недостаточно для единого архива, охватывающего несколько почтовых систем, гарантированной неизменяемости архива и удобного полнотекстового поиска при расследовании инцидента — для этого используется специализированная система архивирования.
+Класс используемых средств — встроенные политики хранения и архив почтового сервера (Retention Policies, In-Place Archive — штатная, частичная возможность); системы архивирования электронной почты (Email Archiving), часто интегрируемые с DLP-системой как единая платформа хранения.
 Иностранные: Proofpoint Enterprise Archive, Mimecast Email Archiving и пр.
 Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor (модуль архивирования), Solar Dozor (архив коммуникаций) и др.
 Открытый код: MailArchiva (Community Edition) и др.</t>
@@ -18311,8 +18312,8 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация аналогична мере ПИУ.6 и обеспечивается той же системой архивирования электронной почты, настроенной на увеличенные сроки хранения: не менее 3 месяцев в режиме оперативного доступа и не менее одного года — в режиме архивного доступа.
-Класс используемых средств — системы архивирования электронной почты (Email Archiving).
+Техническая реализация аналогична мере ПИУ.6 и обеспечивается той же системой архивирования электронной почты, настроенной на увеличенные сроки хранения: не менее 3 месяцев в режиме оперативного доступа и не менее одного года — в режиме архивного доступа. Как и в мере ПИУ.6, штатных политик хранения почтового сервера (Retention Policies, In-Place Archive) может быть достаточно для базового варианта, но для гарантированной неизменяемости архива, охватывающего несколько почтовых систем, требуется специализированная система архивирования.
+Класс используемых средств — встроенные политики хранения и архив почтового сервера (штатная, частичная возможность); системы архивирования электронной почты (Email Archiving).
 Иностранные: Proofpoint Enterprise Archive, Mimecast Email Archiving и пр.
 Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor (модуль архивирования), Solar Dozor и др.
 Открытый код: MailArchiva (Community Edition) и др.</t>
@@ -18378,8 +18379,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация обеспечивается настройкой межсетевого экрана на разрешение исходящего почтового трафика только по установленному перечню протоколов и портов (SMTP, IMAP через корпоративный почтовый шлюз) с блокированием прямого исходящего SMTP-соединения с АРМ и серверов, минующего шлюз, а также контролем (Deep Packet Inspection) на предмет несоответствия фактического протокола заявленному порту.
-Класс используемых средств — межсетевой экран нового поколения (NGFW) с функцией контроля приложений и протоколов (Application Control, Deep Packet Inspection).
+Базовое ограничение перечня протоколов и портов, используемых для передачи почты, достигается штатными правилами практически любого межсетевого экрана — в том числе уже развёрнутого на периметре в рамках мер сегментации сети (СМЭ) — без отдельного приобретения. Дополнительный контроль (Deep Packet Inspection) на предмет несоответствия фактического протокола заявленному порту — то есть защита от туннелирования постороннего трафика под видом разрешённого порта — штатными правилами базового межсетевого экрана не обеспечивается и требует межсетевого экрана нового поколения (NGFW) с соответствующим функционалом:
+1. Настройка межсетевого экрана на разрешение исходящего почтового трафика только по установленному перечню протоколов и портов (SMTP, IMAP через корпоративный почтовый шлюз) с блокированием прямого исходящего SMTP-соединения с АРМ и серверов, минующего шлюз;
+2. Контроль (Deep Packet Inspection) на предмет несоответствия фактического протокола заявленному порту.
+Класс используемых средств — межсетевой экран с базовыми правилами ограничения протоколов и портов (штатная возможность имеющегося периметрового оборудования); межсетевой экран нового поколения (NGFW) с функцией контроля приложений и протоколов (Application Control, Deep Packet Inspection) — для защиты от туннелирования.
 Иностранные: Palo Alto Networks (App-ID), Fortinet FortiGate (Application Control) и пр.
 Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
 Открытый код: iptables/nftables в сочетании с Suricata (выявление протокола, не соответствующего порту).</t>
@@ -18445,8 +18448,10 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация обеспечивается настройкой почтового шлюза на автоматическое определение фактического формата (типа содержимого) каждого вложения по его сигнатуре (а не только по расширению файла) и блокирование вложений, формат которых не входит в перечень разрешённых, с отдельной обработкой архивов, защищённых паролем, как заведомо неразрешённого формата.
-Класс используемых средств — средства фильтрации содержимого почтового шлюза (Secure Email Gateway) с функцией определения типа файла по сигнатуре.
+Базовая фильтрация вложений по расширению файла в большинстве почтовых систем (например, транспортные правила Exchange/Exchange Online) реализуется штатными средствами без отдельного приобретения. Однако штатных транспортных правил недостаточно для определения формата именно по сигнатуре содержимого (а не по расширению) и для отдельной обработки вложений в защищённых паролем архивах — это требует специализированного шлюза с функцией определения типа файла по сигнатуре:
+1. Настройка почтового шлюза на автоматическое определение фактического формата (типа содержимого) каждого вложения по его сигнатуре (а не только по расширению файла);
+2. Блокирование вложений, формат которых не входит в перечень разрешённых, с отдельной обработкой архивов, защищённых паролем, как заведомо неразрешённого формата.
+Класс используемых средств — штатные транспортные правила почтового сервера (фильтрация по расширению — базовый уровень); средства фильтрации содержимого почтового шлюза (Secure Email Gateway) с функцией определения типа файла по сигнатуре — для защиты от обхода переименованием файла.
 Иностранные: Proofpoint Email Protection, Cisco Secure Email и пр.
 Российские сертифицированные (ФСТЭК): Kaspersky Security для почтовых серверов, «Континент» (модуль почтовой безопасности) и др.
 Открытый код: правила фильтрации вложений по MIME-типу и сигнатуре в связке Postfix/MIMEDefang.</t>
@@ -20162,8 +20167,8 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация обеспечивается настройкой централизованного сбора событий, формируемых всеми техническими средствами защиты информации, в систему мониторинга (SIEM) с определением правил корреляции и приоритизации, специфичных именно для событий от СЗИ, и организацией круглосуточного наблюдения (силами собственного или привлечённого SOC) за формируемыми оповещениями.
-Класс используемых средств — система централизованного сбора и корреляции событий (SIEM), центр мониторинга и реагирования на инциденты (SOC).
+Техническая реализация обеспечивается настройкой централизованного сбора событий, формируемых всеми техническими средствами защиты информации, в систему мониторинга (SIEM) с определением правил корреляции и приоритизации, специфичных именно для событий от СЗИ, и организацией круглосуточного наблюдения (силами собственного или привлечённого SOC) за формируемыми оповещениями. Штатная пересылка событий (например, встроенная функция Windows Event Forwarding, syslog-переадресация в Linux) способна централизованно собирать события от отдельных СЗИ без отдельного приобретения; однако для выполнения самой цели меры — корреляции, приоритизации и круглосуточного наблюдения за потоком событий от разнородных средств защиты — штатной пересылки недостаточно, требуется система централизованного сбора и корреляции событий (SIEM).
+Класс используемых средств — штатная пересылка событий операционной системы (Windows Event Forwarding, syslog) для базового сбора; система централизованного сбора и корреляции событий (SIEM) и центр мониторинга и реагирования на инциденты (SOC) — для корреляции, приоритизации и круглосуточного наблюдения.
 Иностранные: Splunk, IBM QRadar и пр.
 Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA (Kaspersky Unified Monitoring and Analysis) и др.
 Открытый код: Wazuh, Elastic (ELK Stack) и др.</t>
@@ -20650,8 +20655,8 @@
           </r>
           <r>
             <t xml:space="preserve">
-Техническая реализация обеспечивается развёртыванием системы централизованного сбора событий (SIEM), к которой подключаются все источники, определённые мерами МАС.1—МАС.7, с настройкой транспорта передачи событий (агенты сбора, syslog, API) для каждого типа источника и контролем фактического подключения каждого из них (см. также меру МАС.10 в части контроля формирования событий).
-Класс используемых средств — система централизованного сбора и корреляции событий (SIEM).
+Техническая реализация обеспечивается развёртыванием системы централизованного сбора событий (SIEM), к которой подключаются все источники, определённые мерами МАС.1—МАС.7, с настройкой транспорта передачи событий (агенты сбора, syslog, API) для каждого типа источника и контролем фактического подключения каждого из них (см. также меру МАС.10 в части контроля формирования событий). Базовый транспорт передачи событий от большинства источников может строиться на штатных механизмах — syslog (сетевое оборудование, сетевые сервисы, серверы на базе Linux) и Windows Event Forwarding (для операционных систем Windows) — без отдельного приобретения. Однако штатных механизмов передачи недостаточно для выполнения самой цели меры: они не обеспечивают ни единой точки хранения и корреляции событий от всех типов источников одновременно, ни гарантированной доставки (мера МАС.12), ни нормализации разнородных форматов (мера МАС.17) — для этого используется система централизованного сбора и корреляции событий (SIEM).
+Класс используемых средств — штатные механизмы пересылки событий (syslog, Windows Event Forwarding) для базового транспорта; система централизованного сбора и корреляции событий (SIEM) — для единой точки хранения, гарантированной доставки и нормализации.
 Иностранные: Splunk, IBM QRadar и пр.
 Российские сертифицированные (ФСТЭК): MaxPatrol SIEM, KUMA и др.
 Открытый код: Wazuh, ELK Stack (Elasticsearch, Logstash, Kibana) и др.</t>
@@ -32720,8 +32725,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -833,6 +833,9 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -23242,10 +23245,64 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D338" s="21" t="n"/>
-      <c r="E338" s="31" t="n"/>
-      <c r="F338" s="31" t="n"/>
-      <c r="G338" s="31" t="n"/>
+      <c r="D338" s="144" t="inlineStr">
+        <is>
+          <t>Мера устанавливает базовое (рамочное) требование идентификации, аутентификации и авторизации (разграничения доступа) при осуществлении логического доступа к виртуальным машинам и серверным компонентам виртуализации — то есть распространяет общие принципы, уже применяемые к обычной информационной инфраструктуре (меры УЗП.1, РД.1), на среду виртуализации как на отдельный объект защиты.
+Главная цель меры — не допустить, чтобы виртуальная инфраструктура (гипервизоры, консоли управления, виртуальные машины) осталась вне периметра контроля доступа, применяемого к остальной инфраструктуре: без базовой идентификации и разграничения прав доступ к среде виртуализации мог бы предоставляться без персонализации и достаточного контроля, что для управляющего уровня, способного повлиять сразу на множество систем, представляет повышенный риск.</t>
+        </is>
+      </c>
+      <c r="E338" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Поскольку мера реализуется только техническими методами, её внедрение предполагает настройку идентификации, аутентификации и разграничения прав доступа непосредственно на уровне серверных компонентов виртуализации (гипервизора, консоли управления) и виртуальных машин, аналогично тому, как это делается для физической инфраструктуры (меры УЗП.1, РД.1):
+1. Настройку гипервизора и консоли управления виртуализацией (vCenter/ESXi, Hyper-V/SCVMM, OpenStack, Proxmox) таким образом, чтобы вход и выполнение любых операций были возможны только после успешной идентификации и аутентификации под персональной учётной записью;
+2. Настройку разграничения прав логического доступа (ролевой модели) к виртуальным машинам и серверным компонентам виртуализации в соответствии с принципом минимально необходимых полномочий;
+3. Запрет использования встроенных общих (root/administrator) учётных записей для повседневной эксплуатации.
+Класс используемых средств — встроенные механизмы идентификации, аутентификации и разграничения доступа платформы виртуализации (штатная возможность); специализированные средства защиты информации для виртуальной инфраструктуры — для расширенного контроля и соответствия сертификационным требованиям.
+Иностранные: VMware vCenter/ESXi (встроенный RBAC), Microsoft Hyper-V/SCVMM, OpenStack Keystone и пр.
+Российские сертифицированные (ФСТЭК): vGate (Код Безопасности), СЗИ ВИ Dallas Lock и др.
+Открытый код: Proxmox VE (встроенный RBAC), OpenStack Keystone и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F338" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация идентификации, аутентификации и разграничения прав доступа на образце гипервизора/консоли управления виртуализацией.
+2. Перечень учётных записей с доступом к серверным компонентам виртуализации и назначенных им ролей.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G338" s="151" t="inlineStr">
+        <is>
+          <t>1. Доступ к гипервизору или консоли управления осуществляется под общей (встроенной) учётной записью без персонализации;
+2. Ролевая модель не выстроена, большинству учётных записей назначены максимальные привилегии независимо от фактических задач;
+3. Настройки идентификации и аутентификации для среды виртуализации не пересматриваются при изменении состава эксплуатационного персонала;
+4. Между разными платформами виртуализации (гипервизор, СХД, консоль резервного копирования) используются несогласованные, независимо администрируемые учётные записи.</t>
+        </is>
+      </c>
+      <c r="H338" s="156" t="inlineStr">
+        <is>
+          <t>Текст меры в столбце B рабочего файла дословно совпадает с заголовком раздела «Базовый состав мер по организации идентификации, аутентификации, авторизации (разграничения доступа)...» и, по всей видимости, не содержит собственной формулировки ЗСВ.1 — похоже на техническую ошибку переноса данных при создании файла. Заполнение выше выполнено по интерпретации ЗСВ.1 как рамочной (базовой) меры идентификации/аутентификации/авторизации для виртуальных машин и серверных компонентов виртуализации, аналогичной вводным мерам УЗП.1/РД.1. Рекомендуется сверить точную формулировку меры с печатным текстом ГОСТ Р 57580.1.</t>
+        </is>
+      </c>
     </row>
     <row r="339" ht="114" customHeight="1">
       <c r="A339" s="20" t="inlineStr">
@@ -23267,10 +23324,59 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D339" s="21" t="n"/>
-      <c r="E339" s="31" t="n"/>
-      <c r="F339" s="31" t="n"/>
-      <c r="G339" s="31" t="n"/>
+      <c r="D339" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы одновременный доступ к виртуальным машинам с АРМ пользователей и эксплуатационного персонала разграничивался и контролировался в пределах только одного контура безопасности, причём сама эта изоляция должна обеспечиваться на уровне не выше третьего (сетевого) по семиуровневой модели ГОСТ Р ИСО/МЭК 7498-1 — то есть средствами сетевой адресации и маршрутизации, а не полагаться исключительно на прикладной уровень (например, только на разграничение прав в интерфейсе консоли управления).
+Главная цель меры — исключить одновременный доступ одного АРМ к виртуальным машинам разных контуров безопасности на сетевом уровне: без такого ограничения рабочая станция, подключённая одновременно к нескольким контурам, способна стать «мостом», через который информация или вредоносное воздействие перемещаются между контурами в обход прикладных средств контроля.</t>
+        </is>
+      </c>
+      <c r="E339" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается сетевой сегментацией (VLAN, отдельные подсети) на уровне не выше третьего по модели ГОСТ Р ИСО/МЭК 7498-1, ограничивающей одновременное сетевое взаимодействие одного АРМ с виртуальными машинами более чем одного контура безопасности, а также запретом маршрутизации между сегментами разных контуров с АРМ конечного пользователя:
+1. Выделение отдельных сетевых сегментов (VLAN, подсетей) для доступа к виртуальным машинам каждого контура безопасности;
+2. Настройку правил маршрутизации и списков доступа (ACL), исключающих возможность одновременного сетевого подключения одного АРМ к сегментам разных контуров;
+3. Технический запрет на использование одного АРМ или jump-host для параллельного доступа к виртуальным машинам разных контуров (см. также меру ЗСВ.20).
+Класс используемых средств — средства сетевой сегментации (VLAN, ACL на маршрутизаторах и коммутаторах), межсетевые экраны.
+Иностранные: Cisco (VLAN, ACL), Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: iptables/nftables, Open vSwitch и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F339" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Схема сетевой сегментации, подтверждающая разделение доступа к виртуальным машинам разных контуров безопасности на уровне не выше третьего.
+2. Конфигурация правил маршрутизации и списков доступа (ACL), ограничивающих одновременное подключение АРМ к сегментам разных контуров.
+3. Итоги интервью с ответственным за администрирование сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G339" s="151" t="inlineStr">
+        <is>
+          <t>1. Сетевая сегментация обеспечивает изоляцию контуров номинально, но фактически один физический или виртуальный сетевой интерфейс АРМ имеет одновременный маршрут к сегментам обоих контуров;
+2. Ограничение реализовано только на прикладном уровне (в консоли управления виртуализацией), без подкрепления сетевой сегментацией;
+3. Правила маршрутизации и ACL не пересматриваются при изменении топологии сети;
+4. Контроль одновременного доступа не распространяется на резервные (аварийные) каналы подключения АРМ.</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="114" customHeight="1">
       <c r="A340" s="20" t="inlineStr">
@@ -23288,14 +23394,59 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D340" s="34" t="inlineStr">
-        <is>
-          <t>ВМ не должна иметь одновременный доступ к СХД за пределами своего контура безопасности — доступ к СХД разграничивается так же строго, как и доступ к самим ВМ (аналогично ЗСВ.1, но применительно к хранилищу, а не к АРМ). Это позволяет в случае компрометации ВМ одного контура безопасности изолировать доступ к datastore/LUN другого контура, чтобы не допустить чтения и изменения чужих данных напрямую через уровень хранения.</t>
-        </is>
-      </c>
-      <c r="E340" s="31" t="n"/>
-      <c r="F340" s="31" t="n"/>
-      <c r="G340" s="31" t="n"/>
+      <c r="D340" s="144" t="inlineStr">
+        <is>
+          <t>Виртуальная машина не должна иметь одновременный доступ к системе хранения данных (СХД) за пределами своего контура безопасности — доступ к СХД разграничивается так же строго, как и доступ к самим виртуальным машинам (аналогично мере ЗСВ.1, но применительно к хранилищу, а не к АРМ).
+Главная цель меры — в случае компрометации виртуальной машины одного контура безопасности изолировать доступ к datastore/LUN другого контура, чтобы не допустить чтения и изменения чужих данных напрямую через уровень хранения, в обход контроля доступа, реализуемого на уровне самих виртуальных машин.</t>
+        </is>
+      </c>
+      <c r="E340" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается разграничением доступа виртуальных машин к системе хранения данных на уровне самой СХД, не зависящем от контроля доступа на уровне гипервизора или консоли управления:
+1. Выделение отдельных логических разделов (LUN, datastore, volume) системы хранения данных для каждого контура безопасности (см. также меру ЗСВ.21);
+2. Настройку зонирования (zoning) и маскирования (masking) на уровне SAN/NAS, ограничивающих видимость и доступность разделов только хостам виртуализации своего контура;
+3. Технический запрет на подключение диска, снапшота или резервной копии виртуальной машины одного контура к виртуальной машине другого контура без контролируемой процедуры.
+Класс используемых средств — встроенные средства разграничения доступа систем хранения данных (зонирование, маскирование, ACL).
+Иностранные: VMware vSphere/VMFS (Storage Policies), Dell EMC/NetApp SAN (zoning, masking) и пр.
+Российские сертифицированные (ФСТЭК): vGate (контроль доступа к СХД), СЗИ ВИ Dallas Lock и др.
+Открытый код: Ceph (пулы и права доступа), GlusterFS и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F340" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация зонирования и маскирования (или эквивалентных правил разграничения) на системе хранения данных.
+2. Сопоставление фактического распределения логических разделов СХД по контурам безопасности утверждённой схеме.
+3. Итоги интервью с ответственным за администрирование системы хранения данных.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G340" s="151" t="inlineStr">
+        <is>
+          <t>1. Виртуальные машины разных контуров безопасности используют общий логический раздел (LUN, datastore) системы хранения данных;
+2. Зонирование или маскирование настроено не на всех хостах виртуализации, часть хостов видит разделы «чужого» контура;
+3. Подключение диска или снапшота виртуальной машины одного контура к машине другого контура технически не заблокировано;
+4. Распределение логических разделов СХД по контурам не пересматривается при изменении состава виртуальных машин.</t>
+        </is>
+      </c>
     </row>
     <row r="341" ht="99.75" customHeight="1">
       <c r="A341" s="20" t="inlineStr">
@@ -23317,10 +23468,59 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D341" s="21" t="n"/>
-      <c r="E341" s="31" t="n"/>
-      <c r="F341" s="31" t="n"/>
-      <c r="G341" s="31" t="n"/>
+      <c r="D341" s="144" t="inlineStr">
+        <is>
+          <t>Мера дополняет требование ЗСВ.3, устанавливая, что разграничение и контроль одновременного доступа виртуальных машин к системе хранения данных в пределах контура безопасности должны обеспечиваться на уровне не выше третьего (сетевого) по семиуровневой модели ГОСТ Р ИСО/МЭК 7498-1.
+Главная цель меры — обеспечить, что изоляция доступа виртуальных машин к системе хранения данных (мера ЗСВ.3) опирается на сетевой уровень (адресацию, маршрутизацию, зонирование сети хранения), а не только на прикладные настройки консоли управления виртуализацией, которые можно обойти при компрометации самой консоли.</t>
+        </is>
+      </c>
+      <c r="E341" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается сетевой изоляцией сети хранения данных (SAN/iSCSI/NFS) на уровне не выше третьего по модели ГОСТ Р ИСО/МЭК 7498-1, разделяющей трафик к СХД разных контуров безопасности:
+1. Выделение отдельных сетей хранения данных (VLAN, VSAN-зонирование для Fibre Channel, отдельные подсети для iSCSI/NFS) для каждого контура безопасности;
+2. Настройку правил маршрутизации и зонирования сети хранения, исключающих сетевую доступность разделов СХД одного контура из сети другого контура;
+3. Технический запрет на маршрутизацию трафика системы хранения данных между сетями разных контуров.
+Класс используемых средств — средства сетевой сегментации сети хранения данных (VLAN, VSAN-зонирование Fibre Channel), средства сетевой сегментации (маршрутизаторы, коммутаторы с ACL).
+Иностранные: Cisco MDS (VSAN-зонирование Fibre Channel), Brocade и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: Open vSwitch, iptables/nftables и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F341" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Схема сетевой сегментации сети хранения данных, подтверждающая разделение по контурам безопасности на уровне не выше третьего.
+2. Конфигурация зонирования (VSAN) и правил маршрутизации сети хранения данных.
+3. Итоги интервью с ответственным за администрирование сети хранения данных.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G341" s="151" t="inlineStr">
+        <is>
+          <t>1. Сеть хранения данных общая для всех контуров безопасности, разграничение обеспечивается только настройками СХД (мера ЗСВ.3), без сетевой изоляции;
+2. VSAN-зонирование или сегментация сети хранения настроены не на всех коммутаторах сети хранения данных;
+3. Маршрутизация между сетями хранения данных разных контуров технически возможна, хотя фактически не используется;
+4. Схема сетевой сегментации сети хранения данных не пересматривается при подключении нового оборудования.</t>
+        </is>
+      </c>
     </row>
     <row r="342" ht="57" customHeight="1">
       <c r="A342" s="20" t="inlineStr">
@@ -23338,10 +23538,59 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D342" s="21" t="n"/>
-      <c r="E342" s="31" t="n"/>
-      <c r="F342" s="31" t="n"/>
-      <c r="G342" s="31" t="n"/>
+      <c r="D342" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует идентификации и аутентификации пользователей серверными компонентами виртуализации и (или) средствами централизованных сервисов аутентификации при предоставлении доступа к виртуальным машинам — то есть подтверждения личности пользователя не только на уровне самой виртуальной машины (гостевой ОС), но и на уровне платформы виртуализации, через которую этот доступ предоставляется.
+Главная цель меры — исключить ситуацию, при которой доступ к виртуальной машине предоставляется анонимно или под общей учётной записью на уровне платформы виртуализации, даже если внутри самой виртуальной машины (гостевой ОС) действует корректная идентификация: без аутентификации на уровне платформы виртуализации невозможно достоверно установить, кто именно инициировал сеанс подключения к виртуальной машине.</t>
+        </is>
+      </c>
+      <c r="E342" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Настройку серверных компонентов виртуализации (гипервизора, брокера подключений VDI) на обязательную идентификацию и аутентификацию пользователя перед предоставлением доступа к виртуальной машине, независимо от последующей аутентификации внутри гостевой ОС;
+2. Интеграцию платформы виртуализации с централизованным сервисом аутентификации (службой каталогов) для использования единой учётной записи пользователя;
+3. Запрет предоставления доступа к виртуальной машине по прямому сетевому адресу в обход брокера подключений или консоли управления виртуализацией.
+Класс используемых средств — встроенные механизмы идентификации и аутентификации платформы виртуализации (брокер подключений VDI, гипервизор), интегрированные со службой каталогов.
+Иностранные: VMware Horizon (брокер подключений), Microsoft RDS/Hyper-V с интеграцией AD и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», vGate и др.
+Открытый код: Apache Guacamole (с интеграцией LDAP), oVirt и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F342" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация идентификации и аутентификации на образце серверного компонента виртуализации (брокера подключений, гипервизора).
+2. Результат тестового подключения к виртуальной машине в обход брокера/консоли управления, подтверждающий блокировку такого подключения.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G342" s="151" t="inlineStr">
+        <is>
+          <t>1. Аутентификация пользователя на уровне платформы виртуализации не настроена, доступ к виртуальной машине предоставляется по прямому сетевому адресу без прохождения через брокер подключений;
+2. Платформа виртуализации не интегрирована со службой каталогов, используются локальные учётные записи, не персонализированные для конечных пользователей;
+3. Аутентификация на уровне платформы виртуализации ограничивается частью виртуальных машин, для остальных доступ предоставляется без предварительной проверки;
+4. Отключение (обход) обязательной аутентификации технически возможно с использованием альтернативных протоколов подключения.</t>
+        </is>
+      </c>
     </row>
     <row r="343" ht="99.75" customHeight="1">
       <c r="A343" s="20" t="inlineStr">
@@ -23359,14 +23608,59 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D343" s="34" t="inlineStr">
-        <is>
-          <t>Технология предоставления доступа к ВМ должна исключать возможность одновременного входа с одними и теми же аутентификационными данными сразу в несколько ВМ — набор учётных данных субъекта доступа должен быть привязан ровно к одной ВМ, чтобы избежать компрометации одной пары логин/пароль (или сертификата), способной дать злоумышленнику доступ сразу к нескольким ВМ.</t>
-        </is>
-      </c>
-      <c r="E343" s="31" t="n"/>
-      <c r="F343" s="31" t="n"/>
-      <c r="G343" s="31" t="n"/>
+      <c r="D343" s="144" t="inlineStr">
+        <is>
+          <t>Технология предоставления доступа к виртуальным машинам должна исключать возможность одновременного входа с одними и теми же аутентификационными данными сразу в несколько виртуальных машин — набор учётных данных субъекта доступа должен быть привязан ровно к одной виртуальной машине.
+Главная цель меры — избежать ситуации, когда компрометация одной пары логин/пароль (или сертификата) даёт злоумышленнику доступ сразу к нескольким виртуальным машинам: жёсткая привязка учётных данных к единственной машине ограничивает последствия компрометации одного набора аутентификационных данных периметром только одной виртуальной машины.</t>
+        </is>
+      </c>
+      <c r="E343" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой брокера подключений или гипервизора на однозначное сопоставление набора аутентификационных данных ровно одной виртуальной машине, с технической блокировкой попытки использования тех же данных для подключения к другой машине:
+1. Настройку персональной (закреплённой) виртуальной машины за конкретной учётной записью пользователя в пуле VDI (dedicated/persistent desktop) вместо общего пула с произвольным назначением;
+2. Технический запрет использования одной учётной записи для одновременного подключения к разным виртуальным машинам;
+3. Регистрацию попыток использования учётных данных для подключения к виртуальной машине, за которой они не закреплены.
+Класс используемых средств — брокер подключений VDI с функцией закрепления персональной виртуальной машины за учётной записью (dedicated/persistent desktop assignment).
+Иностранные: VMware Horizon (Dedicated Assignment), Microsoft RDS (личные виртуальные рабочие столы) и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», vGate и др.
+Открытый код: oVirt (закрепление виртуальных машин за пользователем) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F343" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация брокера подключений в части закрепления виртуальных машин за учётными записями пользователей.
+2. Результат тестовой попытки подключения к «чужой» виртуальной машине под учётными данными, закреплёнными за другой машиной, подтверждающий блокировку.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G343" s="151" t="inlineStr">
+        <is>
+          <t>1. Используется пул виртуальных машин с произвольным (не персональным) назначением, одна учётная запись способна получить доступ к разным машинам пула в разные сеансы;
+2. Технический запрет на параллельное подключение одной учётной записи к нескольким виртуальным машинам не настроен;
+3. Попытки использования «чужих» учётных данных для подключения не регистрируются как отдельное событие;
+4. Закрепление виртуальной машины за учётной записью не пересматривается при увольнении или смене должности сотрудника.</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="114" customHeight="1">
       <c r="A344" s="20" t="inlineStr">
@@ -23384,14 +23678,59 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D344" s="34" t="inlineStr">
-        <is>
-          <t>Доступ с использованием одних аутентификационных данных должен быть возможен не просто к одной ВМ, а к одной ВМ только с одного конкретного АРМ пользователя или эксплуатационного персонала: жёсткая привязка «учётные данные ВМ — АРМ». Данная мера защищает от компрометации учётных данных, способных позволить злоумышленнику подключиться к ВМ с произвольного устройства, а не только с легитимного рабочего места пользователя.</t>
-        </is>
-      </c>
-      <c r="E344" s="31" t="n"/>
-      <c r="F344" s="31" t="n"/>
-      <c r="G344" s="31" t="n"/>
+      <c r="D344" s="144" t="inlineStr">
+        <is>
+          <t>Доступ с использованием одних аутентификационных данных должен быть возможен не просто к одной виртуальной машине, а к одной виртуальной машине только с одного конкретного АРМ пользователя или эксплуатационного персонала — то есть мера дополняет ЗСВ.6 жёсткой привязкой «учётные данные — виртуальная машина — АРМ».
+Главная цель меры — защититься от компрометации учётных данных, позволяющей злоумышленнику подключиться к виртуальной машине с произвольного устройства: привязка не только к конкретной машине, но и к конкретному АРМ существенно ограничивает возможность использования украденных или подобранных аутентификационных данных за пределами легитимного рабочего места пользователя.</t>
+        </is>
+      </c>
+      <c r="E344" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается дополнением привязки «учётные данные — виртуальная машина» (мера ЗСВ.6) привязкой к конкретному АРМ, с которого разрешено подключение:
+1. Настройку брокера подключений или гипервизора на проверку соответствия инициирующего АРМ (по сетевому адресу, сертификату устройства или иному техническому признаку) разрешённому для данной учётной записи и виртуальной машины;
+2. Технический запрет подключения к закреплённой виртуальной машине с АРМ, не входящего в перечень разрешённых для данной учётной записи;
+3. Регистрацию попыток подключения к виртуальной машине с неразрешённого АРМ.
+Класс используемых средств — брокер подключений VDI с функцией привязки клиентского устройства (client device binding), средства аутентификации устройств (сертификаты, доменное членство АРМ — см. также меру РД.7).
+Иностранные: VMware Horizon (True SSO с привязкой устройства), Microsoft RDS и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», vGate и др.
+Открытый код: oVirt (в сочетании с сетевыми ограничениями доступа) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F344" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация брокера подключений в части привязки виртуальной машины к конкретному разрешённому АРМ.
+2. Результат тестовой попытки подключения к виртуальной машине с неразрешённого АРМ, подтверждающий блокировку.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G344" s="151" t="inlineStr">
+        <is>
+          <t>1. Привязка виртуальной машины к конкретному АРМ не настроена, подключение возможно с любого устройства при наличии верных учётных данных;
+2. Проверка соответствия АРМ выполняется только по сетевому адресу, который легко подменяется (спуфинг), без привязки к аппаратному или сертификатному признаку устройства;
+3. Попытки подключения с неразрешённого АРМ не регистрируются как отдельное событие;
+4. Перечень разрешённых АРМ для конкретной учётной записи не пересматривается при замене рабочей станции сотрудника.</t>
+        </is>
+      </c>
     </row>
     <row r="345" ht="99.75" customHeight="1">
       <c r="A345" s="20" t="inlineStr">
@@ -23409,14 +23748,59 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D345" s="34" t="inlineStr">
-        <is>
-          <t>Должна быть техническая возможность принудительно завершить (заблокировать/выключить) уже установленную сессию работы пользователя с ВМ — независимо от желания самого пользователя, чтобы скомпрометированная или подозрительная сессия работы с ВМ могла быть оперативно прервана эксплуатационным персоналом во избежание действий злоумышленника на ВМ.</t>
-        </is>
-      </c>
-      <c r="E345" s="31" t="n"/>
-      <c r="F345" s="31" t="n"/>
-      <c r="G345" s="31" t="n"/>
+      <c r="D345" s="144" t="inlineStr">
+        <is>
+          <t>Должна быть техническая возможность принудительно завершить (заблокировать/выключить) уже установленную сессию работы пользователя с виртуальной машиной — независимо от желания самого пользователя.
+Главная цель меры — дать эксплуатационному персоналу возможность оперативно прервать скомпрометированную или подозрительную сессию работы с виртуальной машиной: без технической возможности принудительного завершения сессии реагирование на выявленный инцидент ограничивается более медленными и менее надёжными мерами (например, изоляцией сети), пока сама сессия продолжает действовать.</t>
+        </is>
+      </c>
+      <c r="E345" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно техническими средствами:
+1. Настройку консоли управления виртуализацией (гипервизора, брокера подключений) на предоставление эксплуатационному персоналу функции принудительного завершения (отключения) активной сессии работы пользователя с виртуальной машиной;
+2. Разграничение прав на выполнение принудительного завершения сессии в соответствии с ролевой моделью (мера ЗСВ.11), исключающее использование данной функции неуполномоченными лицами;
+3. Регистрацию каждого факта принудительного завершения сессии с указанием инициатора и причины (см. также меру ЗСВ.30).
+Класс используемых средств — встроенная функция консоли управления виртуализацией (гипервизора, брокера подключений VDI) по принудительному завершению сессии.
+Иностранные: VMware vCenter/Horizon (Disconnect/Log Off Session), Microsoft SCVMM/RDS и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», vGate и др.
+Открытый код: oVirt, Proxmox VE и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F345" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация консоли управления виртуализацией, подтверждающая наличие функции принудительного завершения сессии.
+2. Результат тестового принудительного завершения сессии с фиксацией времени выполнения.
+3. Журнал событий принудительного завершения сессий за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G345" s="151" t="inlineStr">
+        <is>
+          <t>1. Функция принудительного завершения сессии технически доступна, но право её использования не ограничено ролевой моделью;
+2. Принудительное завершение сессии не приводит к полному сбросу состояния виртуальной машины, пользователь способен восстановить сессию;
+3. Факты принудительного завершения сессии не регистрируются с указанием инициатора и причины;
+4. Функция принудительного завершения сессии недоступна для части виртуальных машин (например, размещённых на отдельном, нестандартном гипервизоре).</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="243.75" customHeight="1">
       <c r="A346" s="20" t="inlineStr">
@@ -23434,50 +23818,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D346" s="47" t="inlineStr">
-        <is>
-          <t>Мера реализуется с помощью контроля и протоколирования доступа администраторов, операторов и другого эксплуатационного персонала к гипервизорам, СХД и консолям управления с реализацией двухфакторной аутентификации. Мера напрямую снижает  возможности компрометации учетной записи администратора виртуализации и не позволяет атакующему создавать и удалять ВМ, подключать диски, изменять сеть, отключать защиту и т.д..</t>
-        </is>
-      </c>
-      <c r="E346" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Доступ эксплуатационного персонала к vCenter/ESXi/NSX Manager, Hyper-V/SCVMM, OpenStack/Proxmox и СХД выполняется только через централизованную учетную запись, MFA/2FA и, для админских сессий, через PAM/bastion с записью действий. Журналы входов, отказов, изменений прав, операций с виртуальной машиной (ВМ) и обращений к системе хранения данных (СХД) хранятся на локальных встроенных журналах платформы, но здесь же рекомендуется использовать передачу журналов в SIEM для независимого хранения и корреляции.                                                                                                                      </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств реализации:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware vSphere/vCenter + ESXi syslog/Aria Operations for Logs - RBAC, Microsoft Hyper-V + SCVMM/Windows Admin Center + AD/MFA/Windows Event Forwarding и пр.
-Российские сертифицированные средства (ФСТЭК): vGate (Код Безопасности), СЗИ ВИ Dallas Lock и пр. 
-Открытый код: FreeIPA, Keycloak (с RADIUS и TOTP), OpenSSH и пр.                                                                                  </t>
+      <c r="D346" s="170" t="inlineStr">
+        <is>
+          <t>Мера реализуется с помощью контроля и протоколирования доступа администраторов, операторов и другого эксплуатационного персонала к гипервизорам, системе хранения данных (СХД) и консолям управления с реализацией двухфакторной аутентификации.
+Главная цель меры — напрямую снизить риск компрометации учётной записи администратора виртуализации: без двухфакторной аутентификации и протоколирования компрометация одного лишь пароля позволила бы атакующему создавать и удалять виртуальные машины, подключать диски, изменять сеть, отключать средства защиты и совершать иные действия, затрагивающие сразу множество систем.</t>
+        </is>
+      </c>
+      <c r="E346" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Доступ эксплуатационного персонала к vCenter/ESXi/NSX Manager, Hyper-V/SCVMM, OpenStack/Proxmox и системе хранения данных выполняется только через централизованную учётную запись, двухфакторную аутентификацию (MFA/2FA) и, для административных сессий, через PAM/bastion-узел с записью действий. Журналы входов, отказов, изменений прав и операций с виртуальной машиной (ВМ) и обращений к СХД хранятся во встроенных журналах платформы виртуализации, но рекомендуется также передавать их в SIEM-систему для независимого хранения и корреляции.
+Класс используемых средств — платформа виртуализации со встроенным контролем доступа и MFA, дополняемая системами контроля действий привилегированных пользователей (PAM) для записи административных сессий.
+Иностранные: VMware vSphere/vCenter + ESXi syslog/Aria Operations for Logs (RBAC), Microsoft Hyper-V + SCVMM/Windows Admin Center + AD/MFA/Windows Event Forwarding и пр.
+Российские сертифицированные (ФСТЭК): vGate (Код Безопасности), СЗИ ВИ Dallas Lock и др.
+Открытый код: FreeIPA, Keycloak (с RADIUS и TOTP), OpenSSH и др.</t>
           </r>
         </is>
       </c>
@@ -23535,14 +23897,59 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D347" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы программные и программно-аппаратные средства защиты информации (СЗИ), обеспечивающие контроль и регистрацию доступа администраторов к гипервизорам и системам хранения данных, были установлены непосредственно на физических средствах вычислительной техники (СВТ), а не внутри виртуальных машин. Это исключает возможность обхода или отключения средств контроля со стороны эксплуатационного персонала через управление виртуальной средой.</t>
-        </is>
-      </c>
-      <c r="E347" s="31" t="n"/>
-      <c r="F347" s="31" t="n"/>
-      <c r="G347" s="31" t="n"/>
+      <c r="D347" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы программные и программно-аппаратные средства защиты информации, обеспечивающие контроль и регистрацию доступа администраторов к гипервизорам и системе хранения данных (мера ЗСВ.9), были установлены непосредственно на физических средствах вычислительной техники, а не внутри виртуальных машин.
+Главная цель меры — исключить возможность обхода или отключения средств контроля доступа со стороны эксплуатационного персонала через управление виртуальной средой: если бы средство контроля само функционировало как виртуальная машина, администратор гипервизора мог бы приостановить, удалить или изменить его наравне с любой другой виртуальной машиной, тем самым отключив контроль над собственными действиями.</t>
+        </is>
+      </c>
+      <c r="E347" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается размещением программно-аппаратных и программных средств защиты, реализующих контроль и регистрацию доступа к гипервизору и системе хранения данных, непосредственно на физических серверах виртуализации (СВТ), вне зависимости и вне управления самой виртуальной средой, которую они контролируют:
+1. Установку агентов средств контроля доступа (vGate, аналогичных СЗИ виртуальной инфраструктуры) непосредственно на физический гипервизор (bare-metal), а не в виде отдельной виртуальной машины внутри контролируемой среды;
+2. Размещение центральной консоли управления средством контроля на выделенном физическом сервере или в отдельном, изолированном от контролируемой инфраструктуры управляющем сегменте (см. также меру ЗСВ.22);
+3. Технический запрет на приостановку, изменение конфигурации или удаление компонентов средства контроля доступа средствами самой платформы виртуализации.
+Класс используемых средств — программно-аппаратные и программные средства защиты информации для виртуальной инфраструктуры, устанавливаемые на физическом уровне (bare-metal agent).
+Иностранные: специализированных зарубежных решений данного класса, устанавливаемых именно на физический уровень гипервизора, на практике немного ввиду архитектурных особенностей.
+Российские сертифицированные (ФСТЭК): vGate (Код Безопасности, устанавливается на физический сервер виртуализации), СЗИ ВИ Dallas Lock и др.
+Открытый код: агенты аудита уровня операционной системы гипервизора (auditd для KVM/Proxmox) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F347" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Техническая документация (архитектура развёртывания) средства контроля доступа, подтверждающая его размещение на физическом уровне.
+2. Результат проверки невозможности приостановки или удаления компонентов средства контроля средствами консоли управления виртуализацией.
+3. Итоги интервью с ответственным за администрирование средств защиты виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G347" s="151" t="inlineStr">
+        <is>
+          <t>1. Средство контроля доступа фактически развёрнуто как виртуальная машина внутри контролируемой среды, что позволяет администратору гипервизора приостановить или удалить его;
+2. Центральная консоль управления средством контроля размещена в общем управляемом сегменте вместе с контролируемыми объектами;
+3. Часть физических серверов виртуализации (например, недавно введённые в эксплуатацию) не охвачена средством контроля доступа, установленным на физическом уровне;
+4. Целостность и работоспособность агента средства контроля на физическом уровне не проверяется на периодической основе.</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="229.5" customHeight="1">
       <c r="A348" s="20" t="inlineStr">
@@ -23570,47 +23977,28 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D348" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует реализацию разделения правил управления правами логического доступа субъектом с целью не допустить  у одного субъекта сочетание функций на создание ВМ, управление образами, предоставление доступа, управление СХД, гипервизорами и виртуальными сетями - необходимо разделять эти функции на несколько субъектов, чтобы исключить компрометацию одной учетной записи атакующим с получением полного технологического цикла действий</t>
-        </is>
-      </c>
-      <c r="E348" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Ввод ролевой модели с чётким запретом совмещения критичных функций: администратор гипервизора, администратор виртуальных сетей, администратор систем хранения данных (СХД), администратор образов, администратор средств защиты информации (СЗИ) и аудитор. Права выдаются по принципу least privilege и по заявкам, запрещаются универсальные роли типа full administrator для повседневной эксплуатации, действия по изменению ролей должны журналироваться.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware vCenter, OpenStack Keystone/RBAC, Microsoft SCVMM и пр.
-Российские сертифицированные средства (ФСТЭК): vGate, СЗИ ВИ Dallas Lock и пр.
-Открытый код: OpenStack Keystone, Proxmox VE и пр.                        </t>
+      <c r="D348" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует разделения правил управления правами логического доступа между субъектами с целью не допустить у одного субъекта сочетания функций на создание виртуальных машин, управление их образами, предоставление доступа, управление системой хранения данных (СХД), гипервизорами и виртуальными сетями.
+Главная цель меры — исключить возможность компрометации одной учётной записи атакующим с получением полного технологического цикла действий: если одному субъекту доступны сразу все критичные функции виртуальной инфраструктуры, компрометация единственной учётной записи предоставляет злоумышленнику контроль над всей средой виртуализации целиком, тогда как разделение функций требует компрометации нескольких независимых учётных записей одновременно.</t>
+        </is>
+      </c>
+      <c r="E348" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Ввод ролевой модели с чётким запретом совмещения критичных функций: администратор гипервизора, администратор виртуальных сетей, администратор систем хранения данных (СХД), администратор образов, администратор средств защиты информации (СЗИ) и аудитор. Права выдаются по принципу минимально необходимых полномочий и по заявкам; запрещаются универсальные роли (full administrator) для повседневной эксплуатации; действия по изменению ролей должны журналироваться.
+Класс используемых средств — встроенная ролевая модель платформы виртуализации (RBAC), дополняемая специализированными средствами защиты виртуальной инфраструктуры для контроля совмещения ролей.
+Иностранные: VMware vCenter, OpenStack Keystone/RBAC, Microsoft SCVMM и пр.
+Российские сертифицированные (ФСТЭК): vGate, СЗИ ВИ Dallas Lock и др.
+Открытый код: OpenStack Keystone, Proxmox VE и др.</t>
           </r>
         </is>
       </c>
@@ -23644,25 +24032,12 @@
           </r>
         </is>
       </c>
-      <c r="G348" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve"> 1) одному или нескольким субъектам логического доступа назначены права, охватывающие две или более критических функций;
-2) нет настройки протоколирования изменений прав доступа.                               </t>
-          </r>
+      <c r="G348" s="154" t="inlineStr">
+        <is>
+          <t>1. Одному или нескольким субъектам логического доступа назначены права, охватывающие две или более критических функций (например, администратор гипервизора одновременно управляет и образами виртуальных машин);
+2. Изменения прав доступа и назначения ролей не протоколируются;
+3. Универсальная роль (full administrator) используется для повседневной эксплуатации вместо назначения по заявкам в рамках отдельных ролей;
+4. Фактическое распределение ролей не пересматривается при изменении должностных обязанностей эксплуатационного персонала.</t>
         </is>
       </c>
     </row>
@@ -23682,10 +24057,55 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D349" s="21" t="n"/>
-      <c r="E349" s="31" t="n"/>
-      <c r="F349" s="31" t="n"/>
-      <c r="G349" s="31" t="n"/>
+      <c r="D349" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует размещать серверные и пользовательские компоненты автоматизированной системы (АС) на разных виртуальных машинах — то есть не совмещать в рамках одной виртуальной машины, например, серверную часть АС (СУБД, прикладной сервер) и клиентские/пользовательские компоненты доступа.
+Главная цель меры — ограничить последствия компрометации: если серверные и пользовательские компоненты размещены на одной виртуальной машине, компрометация пользовательской части (более подверженной атакам через взаимодействие с конечными пользователями) немедленно предоставляет злоумышленнику доступ и к серверной части той же АС, тогда как разделение по разным виртуальным машинам требует дополнительного шага для развития атаки.</t>
+        </is>
+      </c>
+      <c r="E349" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе (архитектурных требованиях к развёртыванию АС) требования о размещении серверных и пользовательских компонентов автоматизированной системы на разных виртуальных машинах;
+2. Проверку соблюдения данного требования на этапе проектирования и ввода в эксплуатацию новой автоматизированной системы или её компонента;
+3. Периодическую инвентаризацию фактического распределения компонентов действующих автоматизированных систем по виртуальным машинам на предмет соответствия установленному требованию.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F349" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ (архитектурные требования), устанавливающий раздельное размещение серверных и пользовательских компонентов АС;
+2. Схема распределения компонентов автоматизированных систем по виртуальным машинам;
+3. Акты (отчёты) периодической инвентаризации фактического распределения компонентов АС по виртуальным машинам.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G349" s="151" t="inlineStr">
+        <is>
+          <t>1. Для унаследованных (легаси) автоматизированных систем серверные и пользовательские компоненты исторически размещены на одной виртуальной машине без плана миграции к раздельному размещению;
+2. Проверка соблюдения требования на этапе проектирования новой АС носит формальный характер, без фактического контроля архитектуры развёртывания;
+3. Периодическая инвентаризация фактического распределения компонентов по виртуальным машинам не проводится;
+4. Требование о раздельном размещении не распространяется на вспомогательные (тестовые, отладочные) экземпляры автоматизированных систем.</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
@@ -23716,78 +24136,55 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D351" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует создать изолированные сегменты сети (включая виртуальные) для размещения ВМ с серверными компонентами автоматизированных систем, относящихся к разным контурам безопасности. Это предотвращает распространение угроз между ними.</t>
-        </is>
-      </c>
-      <c r="E351" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">1. Настройка виртуальной сетевой инфраструктуры на выделение отдельных сегментов (VLAN, VXLAN, виртуальных подсетей) для размещения совокупности виртуальных машин, предназначенных для серверных компонентов АС каждого контура безопасности с созданием отдельных виртуальных коммутаторов или порт-групп с назначением уникальных VLAN ID для каждой группы ВМ разных контуров.
+      <c r="D351" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует создать изолированные сегменты сети (включая виртуальные) для размещения виртуальных машин с серверными компонентами автоматизированных систем, относящихся к разным контурам безопасности.
+Главная цель меры — предотвратить распространение угроз между контурами безопасности: без изоляции на уровне сетевых сегментов компрометация одной виртуальной машины создаёт риск беспрепятственного распространения на серверные компоненты автоматизированных систем других контуров, размещённые в общем сетевом пространстве.</t>
+        </is>
+      </c>
+      <c r="E351" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Настройка виртуальной сетевой инфраструктуры на выделение отдельных сегментов (VLAN, VXLAN, виртуальных подсетей) для размещения совокупности виртуальных машин, предназначенных для серверных компонентов АС каждого контура безопасности, с созданием отдельных виртуальных коммутаторов или порт-групп с назначением уникальных VLAN ID для каждой группы виртуальных машин разных контуров;
 2. Настройка правил межсетевого экранирования на уровне гипервизора (например, с использованием распределённого межсетевого экрана) для ограничения информационного взаимодействия между сегментами разных контуров в соответствии с утверждённой матрицей доступа.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware NSX, Microsoft Azure Virtual Network, Cisco ACI и пр.
+Класс используемых средств — средства виртуальной сетевой сегментации гипервизора (виртуальные коммутаторы, VLAN/VXLAN), распределённый межсетевой экран на уровне гипервизора.
+Иностранные: VMware NSX, Microsoft Azure Virtual Network, Cisco ACI и пр.
 Российские сертифицированные (ФСТЭК): ViPNet Coordinator, Secret Net Studio, Dallas Lock 8.0 и пр.
-Открытый код: Open vSwitch, KVM с libvirt и пр.                             </t>
-          </r>
-        </is>
-      </c>
-      <c r="F351" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Проверочные процедуры (свидетельства) - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>1) конфигурация виртуальных сегментов на гипервизоре;
-2) подтверждение (карта) соответствия ВМ серверных АРМ и контуров безопасности;
-3) конфигурация сетевых интерфейсов/гипервизора.</t>
-          </r>
-        </is>
-      </c>
-      <c r="G351" s="61" t="inlineStr">
-        <is>
-          <t>1) ВМ разных контуров находятся в общей виртуальной сети или едином широковещательном домене;
-2) на уровне гипервизора не настроены правила межсетевого экранирования;
-3) распределение ВМ по сегментам не соответствует актуальному расположению АС.</t>
+Открытый код: Open vSwitch, KVM с libvirt и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F351" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация виртуальных сегментов на гипервизоре;
+2. Подтверждение (карта) соответствия виртуальных машин серверных компонентов АС и контуров безопасности;
+3. Конфигурация сетевых интерфейсов/гипервизора.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G351" s="160" t="inlineStr">
+        <is>
+          <t>1. Виртуальные машины разных контуров находятся в общей виртуальной сети или едином широковещательном домене;
+2. На уровне гипервизора не настроены правила межсетевого экранирования;
+3. Распределение виртуальных машин по сегментам не соответствует актуальному расположению автоматизированных систем;
+4. Новые виртуальные машины по умолчанию создаются в общем сегменте без явного назначения контура безопасности.</t>
         </is>
       </c>
     </row>
@@ -23807,77 +24204,54 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D352" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует создать изолированные сетевые сегменты (включая виртуальные) для размещения виртуальных машин, на которых развернуты АРМ пользователей и эксплуатационного персонала, относящиеся к разным контурам безопасности. Это предотвращает несанкционированный доступ между контурами безопасности..</t>
-        </is>
-      </c>
-      <c r="E352" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
+      <c r="D352" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует создать изолированные сетевые сегменты (включая виртуальные) для размещения виртуальных машин, на которых развёрнуты АРМ пользователей и эксплуатационного персонала, относящиеся к разным контурам безопасности.
+Главная цель меры — предотвратить несанкционированный доступ между контурами безопасности на уровне рабочих станций: мера дополняет ЗСВ.13 (сегментация серверных компонентов) применительно к виртуализированным АРМ, поскольку без раздельной сегментации виртуальный АРМ одного контура способен получить сетевой доступ к ресурсам другого контура наравне с серверными компонентами.</t>
+        </is>
+      </c>
+      <c r="E352" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-На уровне гипервизора/SDN создаются отдельные виртуальные сегменты под VDI-рабочие места для каждого контура безопасности, распределяя виртуальные АРМ и синхронизируя их с пользователями на конкретном контуре безопасности.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Иностранные: VMware NSX + Horizon, Microsoft Azure Virtual Network, Cisco ACI и пр.
-Российские сертифицированные (ФСТЭК): ViPNet Coordinator VA (ИнфоТеКС), zVirt Max (Orion soft)и пр.
-Открытый код: Open vSwitch, KVM с libvirt и пр.</t>
-          </r>
-        </is>
-      </c>
-      <c r="F352" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Проверочные процедуры (свидетельства) - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>1) конфигурация виртуальных сегментов VDI-пулов с распределением по контурам безопасности;
-2) карта соответствия пользователей виртуальных АРМ и контуров безопасности;
-3) итоги интервью с администратором виртуализации.</t>
-          </r>
-        </is>
-      </c>
-      <c r="G352" s="61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1) ВМ разных контуров находятся в общей виртуальной сети 
-2) назначение пользователей на VDI-пул не проверяется на соответствие его контуру безопасности.
-</t>
+            <t xml:space="preserve">
+На уровне гипервизора/SDN создаются отдельные виртуальные сегменты под VDI-рабочие места для каждого контура безопасности, с распределением виртуальных АРМ и синхронизацией их назначения с фактическим контуром конкретного пользователя.
+Класс используемых средств — средства виртуальной сетевой сегментации гипервизора/SDN для VDI-инфраструктуры.
+Иностранные: VMware NSX + Horizon, Microsoft Azure Virtual Network, Cisco ACI и пр.
+Российские сертифицированные (ФСТЭК): ViPNet Coordinator VA (ИнфоТеКС), zVirt Max (Orion soft) и пр.
+Открытый код: Open vSwitch, KVM с libvirt и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F352" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация виртуальных сегментов VDI-пулов с распределением по контурам безопасности;
+2. Карта соответствия пользователей, виртуальных АРМ и контуров безопасности;
+3. Итоги интервью с администратором виртуализации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G352" s="160" t="inlineStr">
+        <is>
+          <t>1. Виртуальные машины разных контуров находятся в общей виртуальной сети;
+2. Назначение пользователей на VDI-пул не проверяется на соответствие его контуру безопасности;
+3. Пул виртуальных АРМ не разделён по контурам безопасности, все виртуальные рабочие столы создаются из единого общего пула;
+4. Перенос пользователя в другой VDI-пул при смене контура безопасности не сопровождается пересозданием виртуального АРМ.</t>
         </is>
       </c>
     </row>
@@ -23901,84 +24275,54 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D353" s="44" t="inlineStr">
-        <is>
-          <t>Мера реализуется в случае, если создается межсегментный обмен управляемым между сегментами вычислительных сетей через физическое оборудование/ПАК и (или) программные средства межсетевого экранирования, функционирующие на уровне гипервизора: трафик между контурами не идет напрямую, а проходит через контролируемые точки фильтрации.  Фильтрация ВМ разных контуров должна находиться там, где реально проходит east-west трафик между ВМ и сегментами, что помешает злоумышленнику обойти межсетевое экранирование.</t>
-        </is>
-      </c>
-      <c r="E353" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
+      <c r="D353" s="153" t="inlineStr">
+        <is>
+          <t>Мера реализуется в случае, если создаётся межсегментный обмен между сегментами вычислительных сетей, определёнными мерами ЗСВ.13 и ЗСВ.14, через физическое оборудование (программно-аппаратный комплекс) и (или) программные средства межсетевого экранирования, функционирующие на уровне гипервизора: трафик между контурами не идёт напрямую, а проходит через контролируемые точки фильтрации.
+Главная цель меры — обеспечить, чтобы фильтрация трафика между виртуальными машинами разных контуров находилась там, где реально проходит east-west трафик между виртуальными машинами и сегментами: точка фильтрации, вынесенная только на внешний периметр, не способна перехватить трафик, циркулирующий между виртуальными машинами внутри одного и того же физического хоста, что позволило бы злоумышленнику обойти межсетевое экранирование.</t>
+        </is>
+      </c>
+      <c r="E353" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Создать информационный обмен между сегментами и контурами через контролируемые точки фильтрации: физические средства межсетевого экранирования нового поколения (NGFW), виртуальные межсетевые экраны, распределенный firewall на гипервизоре или security groups. Прямой L2/L3 обмен между контурами запрещается, все разрешения оформляются в матрице сетевых потоков и реализуются как allow-list.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств реализации:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware NSX Distributed Firewall/Edge - фильтрация на уровне гипервизора и микросегментация; OpenStack Neutron Security Groups/FWaaS или Proxmox VE Firewall и пр.
-Российские сертифицированные средства (ФСТЭК): vGate, UserGate NGFW, Континент 4 и пр.
-Открытый код: Open vSwitch, pfSense и пр.  </t>
-          </r>
-        </is>
-      </c>
-      <c r="F353" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Проверочные процедуры (свидетельства) - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">1) выгрузка журналов событий и конфигурации распределённого межсетевого экрана на гипервизоре за проверяемый период (разрешённые и заблокированные соединения между сегментами);
-2) демонстрация отсутствия прямого взаимодействия ВМ из разных сегментов в обход фильтрации.
-3) итоги интервью с администратором виртуализации.        </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>                     </t>
-          </r>
-        </is>
-      </c>
-      <c r="G353" s="46" t="inlineStr">
-        <is>
-          <t>1) информационный обмен между сегментами серверных компонентов АС и АРМ пользователей и эксплуатационного персонала осуществляется напрямую (мостом или маршрутизацией на уровне ОС), без прохождения через межсетевой экран на гипервизоре;
-2) точка фильтрации присутствует, но покрывает не все хосты виртуализации (настроена только на части сегментов).</t>
+            <t xml:space="preserve">
+Информационный обмен между сегментами и контурами организуется через контролируемые точки фильтрации: физические средства межсетевого экранирования нового поколения (NGFW), виртуальные межсетевые экраны, распределённый firewall на гипервизоре или security groups. Прямой L2/L3 обмен между контурами запрещается, все разрешения оформляются в матрице сетевых потоков и реализуются как allow-list.
+Класс используемых средств — распределённый межсетевой экран на уровне гипервизора (микросегментация), дополняемый физическим межсетевым экраном нового поколения (NGFW) на границах, где трафик выходит за пределы гипервизора.
+Иностранные: VMware NSX Distributed Firewall/Edge (фильтрация на уровне гипервизора и микросегментация), OpenStack Neutron Security Groups/FWaaS, Proxmox VE Firewall и пр.
+Российские сертифицированные (ФСТЭК): vGate, UserGate NGFW, «Континент» 4 и др.
+Открытый код: Open vSwitch, pfSense и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F353" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Выгрузка журналов событий и конфигурации распределённого межсетевого экрана на гипервизоре за проверяемый период (разрешённые и заблокированные соединения между сегментами);
+2. Демонстрация отсутствия прямого взаимодействия виртуальных машин из разных сегментов в обход фильтрации;
+3. Итоги интервью с администратором виртуализации.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G353" s="154" t="inlineStr">
+        <is>
+          <t>1. Информационный обмен между сегментами серверных компонентов АС и АРМ пользователей и эксплуатационного персонала осуществляется напрямую (мостом или маршрутизацией на уровне ОС), без прохождения через межсетевой экран на гипервизоре;
+2. Точка фильтрации присутствует, но покрывает не все хосты виртуализации (настроена только на части сегментов);
+3. Матрица разрешённых сетевых потоков не пересматривается при изменении состава виртуальных машин;
+4. Правила распределённого межсетевого экрана разрешают избыточно широкий трафик («любой-любой») вместо явного allow-list.</t>
         </is>
       </c>
     </row>
@@ -23998,10 +24342,59 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D354" s="21" t="n"/>
-      <c r="E354" s="31" t="n"/>
-      <c r="F354" s="31" t="n"/>
-      <c r="G354" s="31" t="n"/>
+      <c r="D354" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует межсетевого экранирования сегментов (групп сегментов) вычислительных сетей, определённых мерами ЗСВ.13 и ЗСВ.14, включая фильтрацию данных не только на сетевом, но и на прикладном уровне семиуровневой модели ГОСТ Р ИСО/МЭК 7498-1.
+Главная цель меры — обеспечить более глубокий уровень контроля межсегментного трафика, чем простая фильтрация по адресам и портам (сетевой уровень): анализ на прикладном уровне позволяет выявлять попытки использования разрешённого порта не по назначению (туннелирование постороннего протокола, эксплуатация уязвимости конкретного приложения) и тем самым закрывает канал обхода, доступный при фильтрации только по сетевым реквизитам.</t>
+        </is>
+      </c>
+      <c r="E354" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением межсетевого экрана нового поколения (NGFW) или распределённого межсетевого экрана на уровне гипервизора, поддерживающего фильтрацию на прикладном уровне (Application Control, Deep Packet Inspection), для сегментов, определённых мерами ЗСВ.13/ЗСВ.14:
+1. Настройка правил межсетевого экранирования, фильтрующих трафик между сегментами не только по сетевым адресам и портам, но и по типу приложения/протокола прикладного уровня;
+2. Ведение и регулярный пересмотр матрицы разрешённого прикладного трафика между сегментами разных контуров безопасности;
+3. Блокирование трафика, не соответствующего заявленному протоколу прикладного уровня для используемого порта.
+Класс используемых средств — межсетевой экран нового поколения (NGFW) с функцией контроля приложений (Application Control, Deep Packet Inspection), в том числе в исполнении распределённого межсетевого экрана на уровне гипервизора.
+Иностранные: VMware NSX (Distributed Firewall с Layer 7 Application ID), Palo Alto Networks, Fortinet FortiGate и пр.
+Российские сертифицированные (ФСТЭК): UserGate NGFW, «Континент» 4, vGate и др.
+Открытый код: Suricata (в связке с Open vSwitch) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F354" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация правил межсетевого экранирования с фильтрацией на прикладном уровне между сегментами, определёнными мерами ЗСВ.13/ЗСВ.14;
+2. Матрица разрешённого прикладного трафика между сегментами разных контуров безопасности;
+3. Журнал (отчёт) о заблокированных фактах несоответствия трафика заявленному протоколу за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G354" s="151" t="inlineStr">
+        <is>
+          <t>1. Межсетевое экранирование между сегментами реализовано только на сетевом уровне (по адресам и портам), фильтрация на прикладном уровне не настроена;
+2. Матрица разрешённого прикладного трафика не пересматривается при изменении состава размещённых в сегментах приложений;
+3. Фильтрация на прикладном уровне применяется не ко всем сегментам, определённым мерами ЗСВ.13/ЗСВ.14, а выборочно;
+4. Правила межсетевого экранирования не пересматриваются при изменении топологии виртуальной сети.</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="71.25" customHeight="1">
       <c r="A355" s="20" t="inlineStr">
@@ -24019,10 +24412,59 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D355" s="21" t="n"/>
-      <c r="E355" s="31" t="n"/>
-      <c r="F355" s="31" t="n"/>
-      <c r="G355" s="31" t="n"/>
+      <c r="D355" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы информационное взаимодействие между сегментами (группами сегментов) вычислительных сетей, определёнными мерами ЗСВ.13 и ЗСВ.14, осуществлялось и контролировалось в соответствии с установленными правилами и протоколами сетевого взаимодействия, а не по произвольному, неконтролируемому набору протоколов.
+Главная цель меры — исключить неконтролируемое расширение состава протоколов и правил взаимодействия между сегментами разных контуров безопасности: без ограничения перечня разрешённых протоколов и контроля его соблюдения межсегментное взаимодействие способно постепенно «обрасти» неучтёнными, нерегламентированными каналами связи, каждый из которых представляет потенциальный путь распространения угрозы между контурами.</t>
+        </is>
+      </c>
+      <c r="E355" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается ограничением информационного взаимодействия между сегментами, определёнными мерами ЗСВ.13/ЗСВ.14, строго установленным перечнем протоколов и правил, реализуемых на распределённом межсетевом экране гипервизора или физическом межсетевом экране:
+1. Документальное закрепление перечня разрешённых протоколов и направлений сетевого взаимодействия между сегментами разных контуров безопасности (матрица сетевых потоков);
+2. Настройка правил межсетевого экранирования в строгом соответствии с утверждённой матрицей, с запретом (deny by default) всего трафика, явно не включённого в перечень разрешённого;
+3. Периодическая сверка фактической конфигурации правил межсетевого экранирования с утверждённой матрицей сетевых потоков.
+Класс используемых средств — распределённый межсетевой экран на уровне гипервизора и (или) физический межсетевой экран, средства анализа и контроля соответствия конфигураций сетевой политике.
+Иностранные: VMware NSX Distributed Firewall, Cisco ACI и пр.
+Российские сертифицированные (ФСТЭК): vGate, UserGate NGFW, «Континент» 4 и др.
+Открытый код: Open vSwitch, nftables совместно со скриптами сверки конфигурации с эталоном.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F355" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Матрица разрешённых протоколов и направлений сетевого взаимодействия между сегментами, определёнными мерами ЗСВ.13/ЗСВ.14;
+2. Конфигурация правил межсетевого экранирования между указанными сегментами;
+3. Акты (отчёты) периодической сверки фактической конфигурации правил с утверждённой матрицей сетевых потоков.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G355" s="151" t="inlineStr">
+        <is>
+          <t>1. Матрица разрешённых протоколов и направлений сетевого взаимодействия не формализована, правила межсетевого экранирования настроены на усмотрение администратора;
+2. Правила межсетевого экранирования допускают трафик, явно не включённый в утверждённую матрицу («любой-любой» вместо allow-list);
+3. Периодическая сверка фактической конфигурации с утверждённой матрицей не проводится;
+4. Изменения правил межсетевого экранирования вносятся без предварительного согласования с утверждённой матрицей сетевых потоков.</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="85.5" customHeight="1">
       <c r="A356" s="20" t="inlineStr">
@@ -24043,10 +24485,59 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D356" s="21" t="n"/>
-      <c r="E356" s="31" t="n"/>
-      <c r="F356" s="31" t="n"/>
-      <c r="G356" s="31" t="n"/>
+      <c r="D356" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы меры защиты информации ЗСВ.15—ЗСВ.17 (организация межсегментного обмена через контролируемые точки фильтрации, межсетевое экранирование на прикладном уровне, взаимодействие по установленным правилам и протоколам) реализовывались физическим оборудованием (программно-аппаратным комплексом) и (или) программными средствами межсетевого экранирования, функционирующими именно на уровне гипервизора среды виртуализации.
+Главная цель меры — конкретизировать, где именно должна физически находиться точка фильтрации, введённая мерами ЗСВ.15—ЗСВ.17: если функции межсетевого экранирования вынесены только на внешний физический периметр, они не способны контролировать трафик, циркулирующий между виртуальными машинами внутри одного физического хоста виртуализации (так называемый east-west трафик), что позволило бы злоумышленнику обойти контроль, действуя исключительно внутри среды виртуализации.</t>
+        </is>
+      </c>
+      <c r="E356" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается тем, что функции межсетевого экранирования, предусмотренные мерами ЗСВ.15—ЗСВ.17, выполняются именно распределённым межсетевым экраном (или программно-аппаратным комплексом), интегрированным на уровне гипервизора, а не только внешним физическим устройством на периметре сети:
+1. Развёртывание распределённого межсетевого экрана или его виртуального модуля непосредственно на каждом хосте гипервизора, обслуживающем виртуальные машины контролируемых сегментов;
+2. Обеспечение применения правил фильтрации ко всему трафику между виртуальными машинами, включая трафик внутри одного физического хоста (east-west), не выходящий за пределы гипервизора;
+3. Технический контроль (тестирование) фактического перехвата и фильтрации трафика между виртуальными машинами, расположенными на одном физическом хосте.
+Класс используемых средств — распределённый межсетевой экран на уровне гипервизора (программный модуль или программно-аппаратный комплекс, интегрированный со средой виртуализации).
+Иностранные: VMware NSX Distributed Firewall, Cisco ACI (Virtual Edge) и пр.
+Российские сертифицированные (ФСТЭК): vGate, «Континент» 4 (виртуальный модуль) и др.
+Открытый код: Open vSwitch (с правилами фильтрации на уровне порт-групп) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F356" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Техническая документация (архитектура развёртывания) распределённого межсетевого экрана, подтверждающая его функционирование на уровне гипервизора;
+2. Результат тестовой проверки фильтрации east-west трафика между виртуальными машинами одного физического хоста;
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G356" s="151" t="inlineStr">
+        <is>
+          <t>1. Функции межсетевого экранирования реализованы только внешним физическим устройством на периметре, east-west трафик между виртуальными машинами одного хоста не фильтруется;
+2. Распределённый межсетевой экран развёрнут не на всех хостах гипервизора, обслуживающих контролируемые сегменты;
+3. Правила распределённого межсетевого экрана не синхронизированы с правилами внешнего физического межсетевого экрана, что создаёт рассогласование политик;
+4. Тестовая проверка фактической фильтрации east-west трафика не проводится на периодической основе.</t>
+        </is>
+      </c>
     </row>
     <row r="357" ht="57" customHeight="1">
       <c r="A357" s="20" t="inlineStr">
@@ -24066,14 +24557,59 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D357" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует организовать сетевое взаимодействие между ВМ разных АС строго в соответствии с заранее определёнными правилами и протоколами. Это предотвращает несанкционированный доступ между ВМ различных систем.</t>
-        </is>
-      </c>
-      <c r="E357" s="31" t="n"/>
-      <c r="F357" s="31" t="n"/>
-      <c r="G357" s="31" t="n"/>
+      <c r="D357" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует организовать сетевое взаимодействие между виртуальными машинами разных автоматизированных систем (АС) строго в соответствии с заранее определёнными правилами и протоколами.
+Главная цель меры — предотвратить несанкционированный доступ между виртуальными машинами различных систем: в отличие от мер ЗСВ.13—ЗСВ.18, регулирующих взаимодействие между сегментами разных контуров безопасности, данная мера охватывает и взаимодействие между виртуальными машинами разных АС внутри одного контура, где без формализованных правил также возможно избыточное, неконтролируемое сетевое взаимодействие между системами, не связанными общей бизнес-логикой.</t>
+        </is>
+      </c>
+      <c r="E357" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой правил сетевого взаимодействия (security groups, микросегментация на уровне гипервизора) между виртуальными машинами разных автоматизированных систем в соответствии с документально закреплённой матрицей разрешённых потоков:
+1. Определение и документальное закрепление перечня разрешённых протоколов и направлений сетевого взаимодействия между виртуальными машинами разных автоматизированных систем;
+2. Настройку правил микросегментации (security groups, распределённого межсетевого экрана) на уровне гипервизора, ограничивающих взаимодействие между виртуальными машинами разных АС строго установленным перечнем;
+3. Периодическую сверку фактически настроенных правил с утверждённой матрицей сетевых потоков между автоматизированными системами.
+Класс используемых средств — средства микросегментации на уровне гипервизора (security groups, распределённый межсетевой экран).
+Иностранные: VMware NSX (Distributed Firewall, микросегментация), OpenStack Neutron Security Groups и пр.
+Российские сертифицированные (ФСТЭК): vGate, «Континент» 4 и др.
+Открытый код: Open vSwitch, Proxmox VE Firewall и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F357" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Матрица разрешённых протоколов и направлений сетевого взаимодействия между виртуальными машинами разных автоматизированных систем;
+2. Конфигурация правил микросегментации (security groups) на образце гипервизора;
+3. Акты (отчёты) периодической сверки фактической конфигурации правил с утверждённой матрицей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G357" s="151" t="inlineStr">
+        <is>
+          <t>1. Виртуальные машины разных автоматизированных систем взаимодействуют без ограничения по протоколам и направлениям, правила микросегментации не настроены;
+2. Матрица разрешённых сетевых потоков между автоматизированными системами не формализована документально;
+3. Правила микросегментации не пересматриваются при выводе автоматизированной системы из эксплуатации или изменении её состава;
+4. Периодическая сверка фактических правил с утверждённой матрицей не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="358" ht="229.5" customHeight="1">
       <c r="A358" s="20" t="inlineStr">
@@ -24091,47 +24627,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D358" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мера считается реализованной, если исключается возможность информационного взаимодействия и переноса информации между сегментами разных контуров безопасности через АРМ пользователей и эксплуатационного персонала, используемые для доступа к ВМ разных контуров. Мера позволяет не допустить ситуации, когда АРМ администратора может стать «ручным мостом» между контурами безопасности через буфер обмена, подключенные диски, USB, общие папки или последовательные подключения к разным зонам. </t>
-        </is>
-      </c>
-      <c r="E358" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Запрещается использование одного АРМ или jump host для одновременного доступа к ВМ разных контуров безопасности. Для каждого контура должны применяться отдельные админские АРМ, отдельные bastion/PAM-точки и отдельные сетевые маршруты; запрещаются dual-homing, shared clipboard, drive redirection, shared folders, drag-and-drop, USB passthrough и неконтролируемый файловый обмен в RDP/VMRC/SPICE/VNC.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Иностранные: VMware Horizon/vSphere VMRC policy + vCenter permissions, Microsoft RDP/Group Policy/Hyper-V Enhanced Session policy или Citrix policies - отключение clipboard, drive redirection и USB redirection и пр.
-Российские сертифицированные средств (ФСТЭК): vGate, Dallas Lock 8.0 / СЗИ ВИ Dallas Lock и пр.
-Открытый код: Apache Guacamole, oVirt и пр.</t>
+      <c r="D358" s="153" t="inlineStr">
+        <is>
+          <t>Мера считается реализованной, если исключается возможность информационного взаимодействия и переноса информации между сегментами разных контуров безопасности через АРМ пользователей и эксплуатационного персонала, используемые для доступа к виртуальным машинам разных контуров безопасности.
+Главная цель меры — не допустить ситуации, когда АРМ администратора становится «ручным мостом» между контурами безопасности через буфер обмена, подключённые диски, USB, общие папки или последовательные подключения к разным зонам: без технического исключения таких каналов переноса информации сама по себе сетевая изоляция контуров (меры ЗСВ.13—ЗСВ.19) может быть обойдена через рабочее место человека, обладающего легитимным доступом сразу к нескольким контурам.</t>
+        </is>
+      </c>
+      <c r="E358" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Запрещается использование одного АРМ или jump-host для одновременного доступа к виртуальным машинам разных контуров безопасности. Для каждого контура должны применяться отдельные административные АРМ, отдельные bastion/PAM-точки и отдельные сетевые маршруты; запрещаются dual-homing, общий буфер обмена (shared clipboard), перенаправление дисков (drive redirection), общие папки (shared folders), drag-and-drop, перенаправление USB (USB passthrough) и неконтролируемый файловый обмен в RDP/VMRC/SPICE/VNC.
+Класс используемых средств — политики клиента удалённого доступа (RDP/VMRC/SPICE/VNC) и групповые политики операционной системы, ограничивающие перенос данных между сеансами; средства защиты виртуальной инфраструктуры для контроля назначения АРМ по контурам.
+Иностранные: VMware Horizon/vSphere VMRC policy + vCenter permissions, Microsoft RDP/Group Policy/Hyper-V Enhanced Session policy, Citrix policies (отключение clipboard, drive redirection и USB redirection) и пр.
+Российские сертифицированные (ФСТЭК): vGate, Dallas Lock 8.0/СЗИ ВИ Dallas Lock и др.
+Открытый код: Apache Guacamole, oVirt и др.</t>
           </r>
         </is>
       </c>
@@ -24191,46 +24708,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D359" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мера требует на уровне хранилища разделять сети общей СХД с логической изоляцией разных контуров, что исключает ошибочное подключение LUN/datastore и несанкционированный доступ к дискам ВМ. </t>
-        </is>
-      </c>
-      <c r="E359" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
+      <c r="D359" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует на уровне хранилища разделять сети общей системы хранения данных (СХД) с логической изоляцией разных контуров безопасности.
+Главная цель меры — исключить ошибочное подключение LUN/datastore и несанкционированный доступ к дискам виртуальных машин: без логического разделения хранилища по контурам администратор способен по ошибке (или злоумышленник — намеренно) подключить том хранения одного контура к виртуальной машине другого контура, минуя сетевой уровень изоляции (меры ЗСВ.3, ЗСВ.4).</t>
+        </is>
+      </c>
+      <c r="E359" s="154" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Для каждого контура безопасности создаются отдельные datastore/LUN/volume/storage pool, на SAN/NAS настраиваются zoning, masking, ACL и отдельные политики резервного копирования. В vCenter/Proxmox/OpenStack Cinder права к хранилищам назначаются по ролям и контурам, запрещается подключение дисков, снапшотов и backup-реплик между контурами без контролируемой процедуры.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">                                                                        Иностранные: VMware vSphere/vSAN/VMFS datastore permissions + Storage Policies, OpenStack Cinder/Proxmox storage pools или Microsoft Hyper-V/SCVMM + SMB/SAN permissions и пр.
-Российские сертифицированные средства (ФСТЭК): vGate, СЗИ ВИ Dallas Lock и пр.
-Открытый код: Ceph , GlusterFS и пр.                                                                      </t>
+            <t xml:space="preserve">
+Для каждого контура безопасности создаются отдельные datastore/LUN/volume/storage pool, на SAN/NAS настраиваются zoning, masking, ACL и отдельные политики резервного копирования. В vCenter/Proxmox/OpenStack Cinder права к хранилищам назначаются по ролям и контурам; запрещается подключение дисков, снапшотов и backup-реплик между контурами без контролируемой процедуры.
+Класс используемых средств — встроенные средства разграничения доступа систем хранения данных (Storage Policies, зонирование, маскирование, ACL).
+Иностранные: VMware vSphere/vSAN/VMFS datastore permissions + Storage Policies, OpenStack Cinder/Proxmox storage pools, Microsoft Hyper-V/SCVMM + SMB/SAN permissions и пр.
+Российские сертифицированные (ФСТЭК): vGate, СЗИ ВИ Dallas Lock и др.
+Открытый код: Ceph, GlusterFS и др.</t>
           </r>
         </is>
       </c>
@@ -24293,47 +24792,28 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D360" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует выделять отдельные сегменты управления, в которых располагаются АРМ эксплуатационного персонала (администраторов, операторов) для администрирования серверных компонентов виртуализации и системы хранения данных, что снижает вероятность компрометации управляющего контура, которая в ином случае может дать возможность менять сети, диски, снапшоты, шаблоны, роли, настройки СЗИ и состояние ВМ, поэтому management plane (управляющий контур) должен быть изолирован от рабочих нагрузок.</t>
-        </is>
-      </c>
-      <c r="E360" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
+      <c r="D360" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует выделять отдельные сегменты управления, в которых располагаются АРМ эксплуатационного персонала (администраторов, операторов), используемые для администрирования серверных компонентов виртуализации и системы хранения данных.
+Главная цель меры — снизить вероятность компрометации управляющего контура (management plane): без изоляции от рабочих нагрузок компрометация сегмента, где размещены обычные пользовательские или серверные виртуальные машины, создаёт риск получения доступа и к управляющему уровню, который позволяет менять сети, диски, снапшоты, шаблоны, роли, настройки средств защиты информации и состояние виртуальных машин.</t>
+        </is>
+      </c>
+      <c r="E360" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Создается отдельный management-сегмент/VLAN/VRF для vCenter, ESXi management interface, NSX Manager, Proxmox VE management, OpenStack management/API, СХД, backup-систем и СЗИ. Доступ в сегмент управления разрешается только с выделенных админских АРМ или через PAM/bastion, с MFA, журналированием, запретом маршрутизации из пользовательских и серверных сегментов и отдельными правилами межсетевого экранирования.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware vSphere/NSX, Microsoft Hyper-V/SCVMM, OpenStack control plane и пр.
-Российские сертифицированные средства (ФСТЭК): vGate, Континент 4, UserGate NGFW и пр.
-Открытый код: Open vSwitch, pfSense и пр.                                   </t>
+            <t xml:space="preserve">
+Создаётся отдельный management-сегмент/VLAN/VRF для vCenter, ESXi management interface, NSX Manager, Proxmox VE management, OpenStack management/API, системы хранения данных, систем резервного копирования и средств защиты информации. Доступ в сегмент управления разрешается только с выделенных административных АРМ или через PAM/bastion, с многофакторной аутентификацией (MFA), журналированием, запретом маршрутизации из пользовательских и серверных сегментов и отдельными правилами межсетевого экранирования.
+Класс используемых средств — средства сетевой сегментации управляющего контура (VLAN/VRF), межсетевые экраны, дополняемые системами контроля привилегированного доступа (PAM/bastion) для доступа в сегмент управления.
+Иностранные: VMware vSphere/NSX, Microsoft Hyper-V/SCVMM, OpenStack control plane и пр.
+Российские сертифицированные (ФСТЭК): vGate, «Континент» 4, UserGate NGFW и др.
+Открытый код: Open vSwitch, pfSense и др.</t>
           </r>
         </is>
       </c>
@@ -32725,8 +33205,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -836,6 +836,9 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -24895,16 +24898,57 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D362" s="50" t="n"/>
-      <c r="E362" s="31" t="n"/>
-      <c r="F362" s="51" t="n"/>
-      <c r="G362" s="51" t="n"/>
-      <c r="H362" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">НЕТ РАЗДЕЛЕНИЯ НА ОТДЕЛЬНЫЙ БЛОК 23-31
-</t>
-        </is>
-      </c>
+      <c r="D362" s="155" t="inlineStr">
+        <is>
+          <t>Мера требует регламентации и контроля выполнения операций в рамках жизненного цикла базовых образов виртуальных машин, а также операций по копированию образов виртуальных машин.
+Главная цель меры — обеспечить управляемость и прослеживаемость всего жизненного цикла базового образа — от создания и обновления до вывода из эксплуатации, а также любых операций копирования: без формализованного регламента образы виртуальных машин способны изменяться и распространяться бесконтрольно, что подрывает доверие к базовому образу как к эталону (см. также меру ЗСВ.26 в части контроля целостности при запуске).</t>
+        </is>
+      </c>
+      <c r="E362" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Разработку и утверждение внутреннего нормативного документа, регламентирующего порядок создания, обновления, тестирования, утверждения и вывода из эксплуатации базовых образов виртуальных машин;
+2. Регламентацию порядка и условий, при которых допускается копирование образов виртуальных машин (в том числе для целей резервного копирования или тиражирования), с определением ответственных и порядка согласования;
+3. Ведение реестра утверждённых базовых образов с указанием версии, назначения и даты последнего пересмотра;
+4. Периодический контроль соответствия фактически используемых образов утверждённому реестру.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F362" s="145" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, регламентирующий жизненный цикл базовых образов виртуальных машин и порядок их копирования;
+2. Реестр утверждённых базовых образов виртуальных машин;
+3. Акты (отчёты) периодического контроля соответствия фактически используемых образов утверждённому реестру.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G362" s="145" t="inlineStr">
+        <is>
+          <t>1. Регламент жизненного цикла образов не охватывает все этапы (например, отсутствует порядок вывода устаревшего образа из эксплуатации);
+2. Копирование образов виртуальных машин выполняется без согласования и вне зафиксированного в регламенте порядка;
+3. Реестр утверждённых базовых образов не актуализируется при выпуске новой версии образа;
+4. Периодический контроль соответствия фактически используемых образов реестру не проводится.</t>
+        </is>
+      </c>
+      <c r="H362" s="171" t="n"/>
     </row>
     <row r="363" ht="85.5" customHeight="1">
       <c r="A363" s="20" t="inlineStr">
@@ -24924,10 +24968,55 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D363" s="50" t="n"/>
-      <c r="E363" s="31" t="n"/>
-      <c r="F363" s="51" t="n"/>
-      <c r="G363" s="51" t="n"/>
+      <c r="D363" s="155" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы в базовые образы виртуальных машин включалось только программное обеспечение (ПО) технических мер защиты информации, применяемых в пределах виртуальных машин, и ПО автоматизированной системы (АС), — то есть исключает включение в базовый образ любого иного, избыточного ПО.
+Главная цель меры — минимизировать состав программного обеспечения базового образа исключительно необходимым минимумом: избыточное ПО (средства разработки, административные утилиты общего назначения, неиспользуемые сервисы), однажды попавшее в базовый образ, автоматически тиражируется на все виртуальные машины, созданные из этого образа, расширяя поверхность атаки каждой из них без функциональной необходимости.</t>
+        </is>
+      </c>
+      <c r="E363" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Регламентацию перечня категорий ПО, допустимых к включению в базовый образ виртуальной машины, — ограниченного программным обеспечением технических мер защиты информации и программным обеспечением автоматизированной системы;
+2. Проведение контроля состава ПО на этапе формирования и утверждения нового базового образа (мера ЗСВ.23), исключающего включение в него ПО, не входящего в утверждённый перечень;
+3. Периодический контроль фактического состава ПО утверждённых базовых образов на предмет соответствия установленному ограничению.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F363" s="145" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, ограничивающий перечень ПО, допустимого к включению в базовый образ виртуальной машины;
+2. Акт контроля состава ПО на этапе утверждения нового базового образа;
+3. Акты (отчёты) периодического контроля фактического состава ПО утверждённых базовых образов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G363" s="145" t="inlineStr">
+        <is>
+          <t>1. В базовый образ включено ПО, не относящееся ни к средствам защиты информации, ни к ПО автоматизированной системы (например, средства разработки или административные утилиты общего назначения);
+2. Контроль состава ПО при формировании нового базового образа не документируется, полагаются на добросовестность инженера, готовившего образ;
+3. Периодический контроль фактического состава ПО утверждённых базовых образов не проводится;
+4. Программное обеспечение, добавленное в образ временно для целей отладки, не удаляется перед утверждением образа как базового.</t>
+        </is>
+      </c>
       <c r="H363" s="10" t="n"/>
     </row>
     <row r="364" ht="28.5" customHeight="1">
@@ -24946,10 +25035,56 @@
           <t>Н-О-О</t>
         </is>
       </c>
-      <c r="D364" s="21" t="n"/>
-      <c r="E364" s="31" t="n"/>
-      <c r="F364" s="31" t="n"/>
-      <c r="G364" s="31" t="n"/>
+      <c r="D364" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы каждая виртуальная машина была отнесена только к одному из контуров безопасности, — то есть исключает ситуацию, при которой одна и та же виртуальная машина одновременно считается принадлежащей нескольким контурам.
+Главная цель меры — обеспечить однозначность применения мер сегментации и изоляции (меры ЗСВ.13—ЗСВ.19): если бы виртуальная машина могла относиться сразу к нескольким контурам безопасности, к ней пришлось бы применять противоречащие друг другу правила сетевой изоляции и разграничения доступа, а сама попытка отнесения к нескольким контурам фактически создавала бы легитимный мост между ними, для предотвращения которого и вводятся меры сегментации.</t>
+        </is>
+      </c>
+      <c r="E364" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Регламентацию порядка однозначного отнесения каждой создаваемой виртуальной машины к одному, и только одному, контуру безопасности на этапе её создания;
+2. Ведение реестра (карты) соответствия виртуальных машин контурам безопасности, синхронизированного с фактическим распределением по сегментам (меры ЗСВ.13/ЗСВ.14);
+3. Регламентацию порядка изменения принадлежности виртуальной машины контуру безопасности (при обоснованной необходимости) с обязательным пересозданием или полной проверкой машины, а не простым переносом действующей;
+4. Периодический контроль соответствия фактического распределения виртуальных машин по сегментам утверждённому реестру.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F364" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, регламентирующий порядок отнесения виртуальных машин к контурам безопасности;
+2. Реестр (карта) соответствия виртуальных машин контурам безопасности;
+3. Акты (отчёты) периодического контроля соответствия фактического распределения виртуальных машин реестру.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G364" s="151" t="inlineStr">
+        <is>
+          <t>1. Реестр соответствия виртуальных машин контурам безопасности не актуализируется при создании новых виртуальных машин;
+2. Отдельные виртуальные машины (как правило, вспомогательные или тестовые) фактически используются для задач нескольких контуров безопасности без формального переотнесения;
+3. Изменение принадлежности виртуальной машины контуру безопасности выполняется простым переносом действующей машины без пересоздания или полной проверки;
+4. Периодический контроль соответствия фактического распределения виртуальных машин утверждённому реестру не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="365" ht="229.5" customHeight="1">
       <c r="A365" s="20" t="inlineStr">
@@ -24972,47 +25107,28 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D365" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует перед каждым запуском ВМ автоматически проверять целостность её базового образа, установленного программного обеспечения и конфигураций встроенных средств защиты (например, антивируса или межсетевого экрана), что исключает заражение базового образа ВМ, ведущее к массовому развертыванию заражённой машины.</t>
-        </is>
-      </c>
-      <c r="E365" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Хранить базовые образы ВМ в доверенном репозитории; для шаблонов, ISO, cloud images и профилей проверять хэши/цифровые подписи, состояние агентов СЗИ/EDR/AV/HIDS и параметры защитных политик. Перед запуском или вводом ВМ в эксплуатацию выполнять контроль целостности; неподписанные, измененные или неутвержденные образы нужно блокировать. Для поддерживаемых платформ включать Secure Boot, vTPM и контроль конфигураций.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware vSphere Content Library/VM Encryption/Secure Boot/vTPM, Microsoft Hyper-V Generation 2/Secure Boot/vTPM/Shielded VM или OpenStack Glance image signature verification и пр.
-Российские сертифицированные средства (ФСТЭК): vGate, Secret Net  / СДЗ Secret Net и пр.
-Открытый код: AIDE (Advanced Intrusion Detection Environment), Osquery и пр.                                                                           </t>
+      <c r="D365" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует перед каждым запуском виртуальной машины автоматически проверять целостность её базового образа, установленного программного обеспечения и конфигураций встроенных средств защиты (например, антивируса или межсетевого экрана).
+Главная цель меры — исключить заражение базового образа виртуальной машины, способное привести к массовому развёртыванию заражённых машин: поскольку базовый образ тиражируется на множество виртуальных машин (мера ЗСВ.24), незамеченная компрометация одного образа распространяется на весь парк машин, созданных из него, если целостность образа не проверяется перед каждым запуском.</t>
+        </is>
+      </c>
+      <c r="E365" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Базовые образы виртуальных машин хранятся в доверенном репозитории; для шаблонов, ISO, cloud-образов и профилей проверяются хеш-суммы/цифровые подписи, состояние агентов средств защиты информации (СЗИ)/EDR/AV/HIDS и параметры защитных политик. Перед запуском или вводом виртуальной машины в эксплуатацию выполняется контроль целостности; неподписанные, изменённые или неутверждённые образы блокируются. Для поддерживаемых платформ включаются Secure Boot, vTPM и контроль конфигураций.
+Класс используемых средств — доверенный репозиторий образов с проверкой цифровой подписи/хеш-суммы, встроенные механизмы доверенной загрузки виртуальной машины (Secure Boot, vTPM), средства контроля целостности файлов.
+Иностранные: VMware vSphere Content Library/VM Encryption/Secure Boot/vTPM, Microsoft Hyper-V Generation 2/Secure Boot/vTPM/Shielded VM, OpenStack Glance (проверка подписи образов) и пр.
+Российские сертифицированные (ФСТЭК): vGate, Secret Net/СДЗ Secret Net и др.
+Открытый код: AIDE (Advanced Intrusion Detection Environment), Osquery и др.</t>
           </r>
         </is>
       </c>
@@ -25073,10 +25189,55 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D366" s="21" t="n"/>
-      <c r="E366" s="31" t="n"/>
-      <c r="F366" s="31" t="n"/>
-      <c r="G366" s="31" t="n"/>
+      <c r="D366" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует запрета на копирование текущих образов виртуальных машин, использующих средства криптографической защиты информации (СКЗИ), с загруженными криптографическими ключами.
+Главная цель меры — не допустить неконтролируемого тиражирования криптографических ключей вместе с копией образа виртуальной машины: снимок (снапшот) или полная копия работающей виртуальной машины с загруженным в память ключом фактически создаёт дополнительный экземпляр носителя ключевой информации, местонахождение и защищённость которого не контролируется установленным для СКЗИ порядком обращения с ключами.</t>
+        </is>
+      </c>
+      <c r="E366" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе прямого запрета на создание копий (снимков, снапшотов, клонов) текущего состояния виртуальных машин, использующих СКЗИ, в период, когда криптографические ключи загружены в оперативную память;
+2. Регламентацию порядка выгрузки (уничтожения в оперативной памяти) криптографических ключей перед выполнением плановых операций резервного копирования или технического обслуживания, требующих создания копии образа;
+3. Периодический контроль (аудит) отсутствия фактов копирования текущих образов виртуальных машин с СКЗИ в нарушение установленного запрета.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F366" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, содержащий запрет на копирование текущих образов виртуальных машин с СКЗИ с загруженными ключами;
+2. Регламент порядка выгрузки криптографических ключей перед операциями, требующими создания копии образа;
+3. Акты (отчёты) периодического контроля отсутствия фактов нарушения установленного запрета.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G366" s="151" t="inlineStr">
+        <is>
+          <t>1. Автоматическое резервное копирование виртуальных машин (снапшоты по расписанию) настроено без исключения для виртуальных машин, использующих СКЗИ;
+2. Порядок выгрузки криптографических ключей перед плановым обслуживанием, требующим копирования образа, не регламентирован;
+3. Периодический контроль отсутствия несанкционированных копий образов виртуальных машин с СКЗИ не проводится;
+4. Персонал, выполняющий резервное копирование виртуальной инфраструктуры, не осведомлён об исключении, связанном с виртуальными машинами, использующими СКЗИ.</t>
+        </is>
+      </c>
     </row>
     <row r="367" ht="42.75" customHeight="1">
       <c r="A367" s="20" t="inlineStr">
@@ -25094,10 +25255,55 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D367" s="21" t="n"/>
-      <c r="E367" s="31" t="n"/>
-      <c r="F367" s="31" t="n"/>
-      <c r="G367" s="31" t="n"/>
+      <c r="D367" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует запрета на копирование текущих образов виртуальных машин, используемых для реализации технологии виртуализации АРМ пользователей (VDI).
+Главная цель меры — не допустить неконтролируемого тиражирования копии виртуального АРМ пользователя с его текущим состоянием: снимок работающей пользовательской виртуальной машины способен содержать активные пользовательские сессии, локально сохранённые аутентификационные данные и иную чувствительную информацию текущего сеанса, распространение которой в виде неучтённой копии создаёт риск, не покрываемый контролем базового (эталонного) образа (мера ЗСВ.24).</t>
+        </is>
+      </c>
+      <c r="E367" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Закрепление во внутреннем нормативном документе прямого запрета на создание копий (снимков, снапшотов, клонов) текущего состояния виртуальных машин, используемых для виртуализации АРМ пользователей, за исключением случаев, предусмотренных регламентированной процедурой (например, для расследования инцидента);
+2. Регламентацию порядка выполнения исключений из данного запрета — с обязательным согласованием, документированием причины и последующим контролируемым уничтожением или изоляцией созданной копии;
+3. Периодический контроль (аудит) отсутствия несанкционированных копий текущих образов виртуальных АРМ пользователей.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F367" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, содержащий запрет на копирование текущих образов виртуальных машин, используемых для виртуализации АРМ пользователей;
+2. Регламент порядка согласования и документирования исключений из данного запрета;
+3. Акты (отчёты) периодического контроля отсутствия несанкционированных копий текущих образов виртуальных АРМ.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G367" s="151" t="inlineStr">
+        <is>
+          <t>1. Запрет на копирование текущих образов виртуальных АРМ не распространяется на резервное копирование, выполняемое общей системой backup без учёта данного исключения;
+2. Случаи создания копии текущего образа виртуального АРМ (для расследования инцидента) не документируются и не согласовываются;
+3. Созданные в рамках исключения копии не уничтожаются и не изолируются по завершении обосновавшей их задачи;
+4. Периодический контроль отсутствия несанкционированных копий текущих образов виртуальных АРМ не проводится.</t>
+        </is>
+      </c>
     </row>
     <row r="368" ht="71.25" customHeight="1">
       <c r="A368" s="20" t="inlineStr">
@@ -25115,14 +25321,59 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D368" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы пользователи не могли записывать изменения, сделанные ими в процессе работы на виртуальной машине, непосредственно в её базовый эталонный образ. Это предотвращает накопление несанкционированных модификаций или вредоносного ПО в образе.</t>
-        </is>
-      </c>
-      <c r="E368" s="31" t="n"/>
-      <c r="F368" s="31" t="n"/>
-      <c r="G368" s="31" t="n"/>
+      <c r="D368" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы пользователи не могли записывать изменения, сделанные ими в процессе работы на виртуальной машине, непосредственно в её базовый эталонный образ.
+Главная цель меры — предотвратить накопление несанкционированных модификаций или вредоносного программного обеспечения в базовом образе: если бы изменения пользователя сохранялись в самом базовом образе, каждая последующая виртуальная машина, созданная из него, унаследовала бы эти изменения, включая случайно или намеренно внесённые вредоносные компоненты, — что подрывает саму идею контролируемого эталонного образа (мера ЗСВ.26).</t>
+        </is>
+      </c>
+      <c r="E368" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением технологии недифференцированных (non-persistent) виртуальных машин, при которой все изменения, вносимые пользователем в ходе сеанса работы, записываются в отдельный, изолированный от базового образа слой (differencing disk, delta-диск, overlay), не затрагивающий сам эталонный образ:
+1. Настройку виртуальных машин пользователей на использование связанных клонов (linked clones) или иного механизма разностных дисков, при котором пользовательские изменения физически не могут быть записаны в файл базового образа;
+2. Установку прав доступа к файлу базового образа, технически исключающих его изменение с виртуальных машин, созданных на его основе;
+3. Периодический контроль неизменности базового образа (контрольная сумма, дата последнего изменения) как подтверждение отсутствия записи пользовательских изменений в него.
+Класс используемых средств — встроенный механизм связанных клонов (linked clones) и разностных дисков платформы виртуализации.
+Иностранные: VMware Horizon (Instant Clones/Linked Clones), Citrix Virtual Apps and Desktops (MCS) и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», vGate и др.
+Открытый код: oVirt (снапшоты как разностные диски), Proxmox VE (linked clones) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F368" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация виртуальных машин пользователей, подтверждающая использование связанных клонов или разностных дисков.
+2. Результат тестовой проверки: изменение, внесённое в ходе тестового сеанса, не отражается в контрольной сумме базового образа после завершения сеанса.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G368" s="151" t="inlineStr">
+        <is>
+          <t>1. Часть виртуальных машин пользователей развёрнута в режиме полного (persistent) клона, а не связанного клона, что допускает случайное изменение общего образа;
+2. Права доступа к файлу базового образа технически не ограничивают его изменение со стороны обычной пользовательской виртуальной машины;
+3. Контрольная сумма базового образа не проверяется на периодической основе, изменение образа может остаться незамеченным;
+4. Механизм разностных дисков применяется не для всех пулов виртуальных АРМ, часть пулов создана без данной защиты.</t>
+        </is>
+      </c>
     </row>
     <row r="369" ht="156.75" customHeight="1">
       <c r="A369" s="20" t="inlineStr">
@@ -25140,47 +25391,28 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D369" s="44" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы система фиксировала каждый факт завершения сеанса работы пользователя с виртуальной машиной (штатное или аварийное отключение, приостановка, завершение сеанса по таймауту). Это способствует прослеживанию сбоев или попыток несанкционированного вмешательства в работу виртуальной инфраструктуры.</t>
-        </is>
-      </c>
-      <c r="E369" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Настройка систем управления виртуализацией (VMware vCenter, Microsoft SCVMM, OpenStack, Astra Linux ПК СВ) на регистрацию всех событий завершения сеанса работы с виртуальными машинами.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware vCenter, Microsoft SCVMM, OpenStack и пр.
-Российские сертифицированные (ФСТЭК):  ROSA Virtualization, РЕД Виртуализация и пр.
-Открытый код: Libvirt, OpenNebula и пр.                            </t>
+      <c r="D369" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы система фиксировала каждый факт завершения сеанса работы пользователя с виртуальной машиной — штатное или аварийное отключение, приостановку, завершение сеанса по тайм-ауту.
+Главная цель меры — обеспечить возможность проследить сбои или попытки несанкционированного вмешательства в работу виртуальной инфраструктуры: без регистрации фактов завершения сеанса невозможно ретроспективно установить, было ли конкретное завершение штатным действием пользователя, техническим сбоем или результатом стороннего вмешательства.</t>
+        </is>
+      </c>
+      <c r="E369" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Настройка систем управления виртуализацией (VMware vCenter, Microsoft SCVMM, OpenStack, Astra Linux ПК СВ) на регистрацию всех событий завершения сеанса работы с виртуальными машинами.
+Класс используемых средств — встроенные средства журналирования системы управления виртуализацией.
+Иностранные: VMware vCenter, Microsoft SCVMM, OpenStack и пр.
+Российские сертифицированные (ФСТЭК): ROSA Virtualization, «РЕД Виртуализация» и др.
+Открытый код: Libvirt, OpenNebula и др.</t>
           </r>
         </is>
       </c>
@@ -25205,12 +25437,12 @@
           </r>
         </is>
       </c>
-      <c r="G369" s="61" t="inlineStr">
-        <is>
-          <t>1) не включена регистрация событий завершения сеансов работы пользователей с виртуальной машиной (ВМ) (отключение питания, остановка, приостановка);
-2) регистрация ведётся не для всех типов завершения сеанса;
-3) отсутствуют правила auditd для libvirt-событий;
-4) журналы событий завершения сеансов не содержат обязательных полей (идентификатор инициатора, временная метка, идентификатор ВМ, тип завершения).</t>
+      <c r="G369" s="160" t="inlineStr">
+        <is>
+          <t>1. Не включена регистрация событий завершения сеансов работы пользователей с виртуальной машиной (отключение питания, остановка, приостановка);
+2. Регистрация ведётся не для всех типов завершения сеанса;
+3. Отсутствуют правила auditd для событий libvirt;
+4. Журналы событий завершения сеансов не содержат обязательных полей (идентификатор инициатора, временная метка, идентификатор виртуальной машины, тип завершения).</t>
         </is>
       </c>
     </row>
@@ -25230,14 +25462,59 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D370" s="34" t="inlineStr">
-        <is>
-          <t>Мера требует, чтобы после завершения сеанса пользователя ВМ возвращалась к исходному состоянию, задаваемому её базовым (эталонным) образом, а все изменения, внесённые пользователем в процессе работы, отбрасывались. Это минимизирует риск накопления нежелательных изменений, случайного или вредоносного ПО.</t>
-        </is>
-      </c>
-      <c r="E370" s="31" t="n"/>
-      <c r="F370" s="31" t="n"/>
-      <c r="G370" s="31" t="n"/>
+      <c r="D370" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы после завершения сеанса пользователя виртуальная машина возвращалась к исходному состоянию, задаваемому её базовым (эталонным) образом, а все изменения, внесённые пользователем в процессе работы, отбрасывались.
+Главная цель меры — минимизировать риск накопления нежелательных изменений, случайного или вредоносного программного обеспечения на виртуальной машине пользователя: гарантированный возврат к эталонному состоянию после каждого сеанса означает, что любая компрометация, произошедшая в течение сеанса, автоматически устраняется по его завершении, не требуя отдельного расследования или переустановки.</t>
+        </is>
+      </c>
+      <c r="E370" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой виртуальных машин пользователей (VDI-пула) в режиме недифференцированных (non-persistent, stateless) машин, при котором по завершении контроля сеанса (мера ЗСВ.30) все накопленные в ходе сеанса изменения (разностный диск, delta-диск) автоматически удаляются, а следующий сеанс начинается с чистого экземпляра, созданного из базового образа:
+1. Настройку VDI-пула на автоматическое пересоздание (recompose) или удаление разностного диска виртуальной машины по завершении каждого сеанса пользователя;
+2. Обеспечение технической невозможности продолжения предыдущего сеанса (восстановления накопленных изменений) после его завершения;
+3. Сохранение и восстановление пользовательских данных и настроек профиля отдельно от самой виртуальной машины (профиль пользователя, перенаправление папок), чтобы возврат машины к эталонному состоянию не приводил к потере рабочих данных пользователя.
+Класс используемых средств — встроенный механизм недифференцированных (non-persistent) виртуальных машин платформы VDI.
+Иностранные: VMware Horizon (Instant Clones с автоматическим пересозданием), Citrix Virtual Apps and Desktops (Random/Non-Persistent) и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», vGate и др.
+Открытый код: oVirt, Proxmox VE (пересоздание из шаблона по расписанию) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F370" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация VDI-пула, подтверждающая режим недифференцированных (non-persistent) виртуальных машин с автоматическим пересозданием по завершении сеанса.
+2. Результат тестовой проверки: изменение, внесённое в тестовом сеансе, отсутствует в виртуальной машине после начала нового сеанса.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G370" s="151" t="inlineStr">
+        <is>
+          <t>1. Часть VDI-пулов настроена в режиме persistent (постоянного) назначения, автоматический возврат к эталонному состоянию для них не выполняется;
+2. Автоматическое пересоздание виртуальной машины по завершении сеанса технически не гарантировано (зависит от ручного запуска администратором);
+3. Пользовательские данные и настройки профиля не отделены от виртуальной машины, из-за чего возврат к эталонному состоянию приводит к потере рабочих данных и провоцирует отключение данной защиты пользователями;
+4. Аварийное завершение сеанса (сбой, разрыв соединения) не всегда приводит к последующему пересозданию виртуальной машины.</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="13" t="inlineStr">
@@ -33205,8 +33482,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -25545,17 +25545,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D372" s="21" t="n"/>
-      <c r="E372" s="31" t="n"/>
-      <c r="F372" s="31" t="n"/>
-      <c r="G372" s="31" t="n"/>
-      <c r="H372" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.
-Реализация слабая</t>
-        </is>
-      </c>
+      <c r="D372" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с запуском (остановкой) виртуальных машин.
+Главная цель меры — обеспечить прослеживаемость жизненного цикла виртуальных машин на уровне их включения и выключения: без такой регистрации незамеченным может остаться как несанкционированный запуск виртуальной машины (например, для временного использования в интересах злоумышленника), так и остановка критичной виртуальной машины, приводящая к простою бизнес-процесса.</t>
+        </is>
+      </c>
+      <c r="E372" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой системы управления виртуализацией (vCenter/ESXi, Hyper-V/SCVMM, OpenStack, Proxmox) на журналирование каждого факта запуска и остановки виртуальной машины с фиксацией инициатора операции, времени и идентификатора виртуальной машины, с последующей передачей событий в SIEM-систему для централизованного хранения и корреляции.
+Класс используемых средств — встроенный механизм журналирования системы управления виртуализацией, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware vCenter/ESXi syslog, Microsoft SCVMM/Windows Event Forwarding, OpenStack telemetry/logging и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: Libvirt (события jobs), Wazuh (сбор и корреляция) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F372" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования операций запуска и остановки виртуальных машин в системе управления виртуализацией.
+2. Выгрузка зарегистрированных событий запуска/остановки виртуальных машин за проверяемый период.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G372" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируется факт запуска/остановки, но не инициатор операции, что не позволяет установить ответственного;
+2. События запуска и остановки собираются локально на каждом хосте гипервизора, но не передаются в SIEM-систему для централизованного анализа;
+3. Регистрация не охватывает все платформы виртуализации, используемые в организации (например, тестовый контур на отдельном гипервизоре);
+4. Массовый или внеплановый запуск/остановка виртуальных машин не сопоставляется с плановым окном изменений для выявления аномалий.</t>
+        </is>
+      </c>
+      <c r="H372" s="168" t="n"/>
     </row>
     <row r="373" ht="42.75" customHeight="1">
       <c r="A373" s="20" t="inlineStr">
@@ -25573,16 +25613,57 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D373" s="21" t="n"/>
-      <c r="E373" s="31" t="n"/>
-      <c r="F373" s="31" t="n"/>
-      <c r="G373" s="31" t="n"/>
-      <c r="H373" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D373" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с изменением параметров настроек виртуальных сетевых сегментов, реализованных средствами гипервизора.
+Главная цель меры — обеспечить прослеживаемость изменений виртуальной сетевой топологии, от которой напрямую зависит сегментация и изоляция контуров безопасности (меры ЗСВ.13—ЗСВ.19): без регистрации таких изменений несанкционированное изменение виртуального сетевого сегмента (например, расширение VLAN на сегмент другого контура) способно нарушить изоляцию контуров, оставшись незамеченным до момента фактического инцидента.</t>
+        </is>
+      </c>
+      <c r="E373" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средств управления виртуальной сетевой инфраструктурой гипервизора (распределённого коммутатора, SDN-контроллера) на журналирование каждого факта изменения параметров настроек виртуальных сетевых сегментов (создание, удаление, изменение VLAN ID, порт-групп, правил микросегментации), с передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования виртуальной сетевой инфраструктуры гипервизора (распределённый виртуальный коммутатор, SDN-контроллер), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware NSX (журнал изменений конфигурации), Cisco ACI и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: Open vSwitch (журнал изменений через OVSDB), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F373" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования изменений параметров виртуальных сетевых сегментов на образце гипервизора.
+2. Выгрузка зарегистрированных событий изменения виртуальной сетевой конфигурации за проверяемый период.
+3. Итоги интервью с ответственным за администрирование виртуальной сетевой инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G373" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только изменения, выполненные через централизованную консоль управления, но не изменения, внесённые напрямую на отдельном хосте гипервизора;
+2. События изменения виртуальных сетевых сегментов не сопоставляются с утверждённой матрицей сетевых потоков (мера ЗСВ.17) для выявления несогласованных изменений;
+3. События не передаются в SIEM-систему, доступны только в локальном журнале консоли управления виртуализацией;
+4. Изменения параметров настроек виртуальных сетевых сегментов, выполненные в рамках экстренных (внеплановых) работ, не сопоставляются впоследствии с последующим согласованием.</t>
+        </is>
+      </c>
+      <c r="H373" s="168" t="n"/>
     </row>
     <row r="374" ht="258" customHeight="1">
       <c r="A374" s="20" t="inlineStr">
@@ -25600,47 +25681,28 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D374" s="44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Мера требует фиксировать в защищённых журналах все факты создания и удаления ВМ в среде виртуализации с указанием инициатора операции, времени, идентификатора ВМ и использованных шаблонов или образов, что исключает создание злоумышленником временной ВМ для закрепления, сканирования, обхода EDR, вывода и удаления данных. </t>
-        </is>
-      </c>
-      <c r="E374" s="61" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Включить централизованную регистрацию событий создания, удаления, клонирования, миграции, изменения конфигурации и запуска виртуальных машин (ВМ); логируются события vCenter/ESXi, NSX, Hyper-V/SCVMM, OpenStack Nova/Keystone/Glance, Proxmox и СХД, также рекомендуется передать их в SIEM. Настроить корреляции на: создание ВМ вне окна изменений, создание из неутвержденного шаблона, массовое удаление, появление ВМ вне CMDB, операции сервисных учетных записей и отключение журналирования.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Иностранные: VMware vCenter/ESXi syslog, Aria Operations for Logs/Splunk V/SCVMM/Windows Event Forwarding/Microsoft Sentinel, OpenStack telemetry/logging и пр.
-Российские сертифицированные средства (ФСТЭК): vGate, СЗИ ВИ Dallas Lock и пр.
-Открытый код: OpenStack, Proxmox VE  и пр.                                              </t>
+      <c r="D374" s="153" t="inlineStr">
+        <is>
+          <t>Мера требует фиксировать в защищённых журналах все факты создания и удаления виртуальных машин в среде виртуализации с указанием инициатора операции, времени, идентификатора виртуальной машины и использованных шаблонов или образов.
+Главная цель меры — исключить создание злоумышленником временной виртуальной машины для закрепления в инфраструктуре, сканирования сети, обхода средств защиты (EDR), вывода и последующего удаления данных, оставаясь незамеченным: без регистрации самих фактов создания и удаления такая временная машина способна появиться и исчезнуть, не оставив следов для расследования.</t>
+        </is>
+      </c>
+      <c r="E374" s="160" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Включается централизованная регистрация событий создания, удаления, клонирования, миграции, изменения конфигурации и запуска виртуальных машин; логируются события vCenter/ESXi, NSX, Hyper-V/SCVMM, OpenStack Nova/Keystone/Glance, Proxmox и СХД, также рекомендуется передавать их в SIEM-систему. Настраиваются правила корреляции на выявление: создания виртуальной машины вне окна изменений, создания из неутверждённого шаблона, массового удаления, появления виртуальной машины вне CMDB, операций сервисных учётных записей и отключения журналирования.
+Класс используемых средств — встроенный механизм журналирования системы управления виртуализацией, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware vCenter/ESXi syslog, Aria Operations for Logs/Splunk, Microsoft SCVMM/Windows Event Forwarding/Microsoft Sentinel, OpenStack telemetry/logging и пр.
+Российские сертифицированные (ФСТЭК): vGate, СЗИ ВИ Dallas Lock, MaxPatrol SIEM, KUMA и др.
+Открытый код: OpenStack, Proxmox VE, Wazuh и др.</t>
           </r>
         </is>
       </c>
@@ -25675,10 +25737,12 @@
           </r>
         </is>
       </c>
-      <c r="G374" s="61" t="inlineStr">
-        <is>
-          <t>1) аудит операций создания и удаления ВМ не включён в системе управления виртуализацией (или настроен только для части операций, например, для создания, но не для удаления);
-2) журналы событий не содержат обязательных полей (идентификатор пользователя, временная метка, идентификатор ВМ) или хранятся локально без защиты от изменений.</t>
+      <c r="G374" s="160" t="inlineStr">
+        <is>
+          <t>1. Аудит операций создания и удаления виртуальных машин не включён в системе управления виртуализацией (или настроен только для части операций, например, для создания, но не для удаления);
+2. Журналы событий не содержат обязательных полей (идентификатор пользователя, временная метка, идентификатор виртуальной машины) или хранятся локально без защиты от изменений;
+3. Зарегистрированные операции не сопоставляются с электронными заявками на создание/удаление виртуальных машин для выявления несанкционированных операций;
+4. События создания и удаления виртуальных машин не передаются в SIEM-систему, доступны только в локальном журнале консоли управления.</t>
         </is>
       </c>
     </row>
@@ -25698,16 +25762,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D375" s="21" t="n"/>
-      <c r="E375" s="31" t="n"/>
-      <c r="F375" s="31" t="n"/>
-      <c r="G375" s="31" t="n"/>
-      <c r="H375" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D375" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с созданием, изменением, копированием и удалением базовых образов виртуальных машин.
+Главная цель меры — обеспечить прослеживаемость всех операций с эталонными образами, определяющими защищённость каждой создаваемой из них виртуальной машины (меры ЗСВ.23, ЗСВ.24, ЗСВ.26): без регистрации таких операций несанкционированное изменение базового образа (например, внедрение вредоносного компонента) способно остаться незамеченным до момента массового развёртывания заражённых виртуальных машин.</t>
+        </is>
+      </c>
+      <c r="E375" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой репозитория (библиотеки) базовых образов виртуальных машин на журналирование каждой операции создания, изменения, копирования и удаления образа с фиксацией инициатора, времени и контрольной суммы образа до и после изменения, с передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования репозитория (библиотеки) образов виртуальных машин, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware vSphere Content Library (журнал операций), OpenStack Glance (журнал операций с образами) и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: OpenStack Glance, Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F375" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования операций с базовыми образами виртуальных машин в репозитории (библиотеке) образов.
+2. Выгрузка зарегистрированных операций создания, изменения, копирования и удаления базовых образов за проверяемый период.
+3. Итоги интервью с ответственным за администрирование репозитория образов.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G375" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только операции удаления образов, изменения содержимого существующего образа отдельно не фиксируются;
+2. События операций с образами не сопоставляются с реестром утверждённых базовых образов (мера ЗСВ.23) для выявления несанкционированных изменений;
+3. События не передаются в SIEM-систему, доступны только в локальном журнале репозитория образов;
+4. Регистрация не охватывает копирование образа за пределы репозитория (например, экспорт на внешний носитель).</t>
+        </is>
+      </c>
+      <c r="H375" s="168" t="n"/>
     </row>
     <row r="376" ht="30" customHeight="1">
       <c r="A376" s="20" t="inlineStr">
@@ -25725,16 +25830,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D376" s="21" t="n"/>
-      <c r="E376" s="31" t="n"/>
-      <c r="F376" s="31" t="n"/>
-      <c r="G376" s="31" t="n"/>
-      <c r="H376" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D376" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с копированием текущих образов виртуальных машин.
+Главная цель меры — обеспечить контроль за соблюдением запретов на копирование текущих образов, установленных мерами ЗСВ.27 (для виртуальных машин с СКЗИ) и ЗСВ.28 (для виртуальных АРМ пользователей): без регистрации самих фактов копирования невозможно подтвердить соблюдение указанных запретов и выявить их нарушение.</t>
+        </is>
+      </c>
+      <c r="E376" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой системы управления виртуализацией на журналирование каждого факта создания снимка (снапшота), клона или экспорта текущего образа виртуальной машины с фиксацией инициатора, времени и идентификатора исходной виртуальной машины, с передачей событий в SIEM-систему и сопоставлением с перечнем виртуальных машин, для которых копирование текущего образа запрещено (меры ЗСВ.27/ЗСВ.28).
+Класс используемых средств — встроенный механизм журналирования операций снапшотов/клонирования системы управления виртуализацией, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware vCenter (журнал операций Snapshot/Clone), Microsoft SCVMM и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: Libvirt/Proxmox VE (журнал операций снапшотов), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F376" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования операций копирования (снапшотов, клонирования, экспорта) текущих образов виртуальных машин.
+2. Выгрузка зарегистрированных фактов копирования текущих образов за проверяемый период с сопоставлением перечню виртуальных машин, для которых копирование запрещено (меры ЗСВ.27/ЗСВ.28).
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G376" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только операции создания снапшота через центральную консоль, но не экспорт образа в файл на уровне хоста гипервизора;
+2. События копирования текущих образов не сопоставляются с перечнем виртуальных машин, для которых копирование запрещено (меры ЗСВ.27/ЗСВ.28), автоматически;
+3. Автоматическое резервное копирование виртуальных машин по расписанию не фиксируется отдельным событием, приравненным к операции копирования;
+4. События не передаются в SIEM-систему, доступны только в локальном журнале консоли управления виртуализацией.</t>
+        </is>
+      </c>
+      <c r="H376" s="168" t="n"/>
     </row>
     <row r="377" ht="30" customHeight="1">
       <c r="A377" s="20" t="inlineStr">
@@ -25752,16 +25898,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D377" s="21" t="n"/>
-      <c r="E377" s="31" t="n"/>
-      <c r="F377" s="31" t="n"/>
-      <c r="G377" s="31" t="n"/>
-      <c r="H377" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D377" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с изменением прав логического доступа к серверным компонентам виртуализации.
+Главная цель меры — обеспечить прослеживаемость изменений в разграничении доступа к управляющему уровню виртуальной инфраструктуры (меры ЗСВ.9, ЗСВ.11): без регистрации таких изменений несанкционированное расширение прав доступа (например, самим скомпрометированным администратором в целях сокрытия дальнейших действий) способно остаться незамеченным.</t>
+        </is>
+      </c>
+      <c r="E377" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой платформы виртуализации на журналирование каждого факта изменения прав логического доступа (назначения, отзыва роли, изменения полномочий учётной записи) к серверным компонентам виртуализации, с фиксацией инициатора изменения, затронутой учётной записи и характера изменения, и передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм журналирования ролевой модели (RBAC) платформы виртуализации, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware vCenter (журнал изменений разрешений), OpenStack Keystone (журнал изменений ролей) и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: OpenStack Keystone, Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F377" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования изменений прав логического доступа к серверным компонентам виртуализации.
+2. Выгрузка зарегистрированных изменений прав доступа за проверяемый период с сопоставлением заявкам на изменение полномочий.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G377" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только изменения ролей на уровне центральной консоли управления, но не изменения прав доступа, выполненные напрямую на отдельном хосте гипервизора;
+2. Зарегистрированные изменения прав доступа не сопоставляются с утверждёнными заявками на изменение полномочий (мера ЗСВ.11);
+3. События изменения прав доступа не передаются в SIEM-систему, доступны только в локальном журнале консоли управления;
+4. Изменения прав доступа, выполненные встроенной (root/administrator) учётной записью, не подлежат тому же уровню контроля, что и изменения, выполненные именованными учётными записями.</t>
+        </is>
+      </c>
+      <c r="H377" s="168" t="n"/>
     </row>
     <row r="378" ht="60" customHeight="1">
       <c r="A378" s="20" t="inlineStr">
@@ -25779,18 +25966,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D378" s="21" t="n"/>
-      <c r="E378" s="31" t="n"/>
-      <c r="F378" s="31" t="n"/>
-      <c r="G378" s="31" t="n"/>
-      <c r="H378" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.
-Список без списка
-Нет пояснения</t>
-        </is>
-      </c>
+      <c r="D378" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с изменением параметров настроек серверных компонентов виртуализации.
+Главная цель меры — обеспечить прослеживаемость изменений конфигурации управляющего уровня виртуальной инфраструктуры: гипервизора, консоли управления, настроек кластера — от которых напрямую зависит защищённость всей размещённой на них среды, и без регистрации которых несанкционированное ослабление конфигурации способно остаться незамеченным вплоть до наступления инцидента.</t>
+        </is>
+      </c>
+      <c r="E378" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой аудита конфигурации на серверных компонентах виртуализации (гипервизоре, консоли управления, кластере) на журналирование каждого факта изменения параметров настроек с фиксацией инициатора, времени, изменённого параметра и его значений до и после изменения, с передачей событий в SIEM-систему и сопоставлением с эталонной (безопасной) конфигурацией (мера ЦЗИ.7 в части контроля конфигураций).
+Класс используемых средств — встроенный механизм аудита конфигурации платформы виртуализации, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware vCenter (журнал изменений конфигурации хоста/кластера), Microsoft SCVMM и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: Libvirt/Proxmox VE (журнал изменений конфигурации), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F378" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования изменений параметров настроек серверных компонентов виртуализации.
+2. Выгрузка зарегистрированных изменений конфигурации за проверяемый период с сопоставлением эталонной (безопасной) конфигурации.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G378" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только изменения, выполненные через центральную консоль управления, но не изменения, внесённые напрямую в конфигурационные файлы на хосте гипервизора;
+2. Зарегистрированные изменения конфигурации не сопоставляются с эталонной (безопасной) конфигурацией для выявления отклонений;
+3. События изменения конфигурации не передаются в SIEM-систему, доступны только в локальном журнале консоли управления;
+4. Изменения параметров настроек, выполненные в рамках экстренных (внеплановых) работ, не сопоставляются впоследствии с последующим согласованием.</t>
+        </is>
+      </c>
+      <c r="H378" s="168" t="n"/>
     </row>
     <row r="379" ht="60" customHeight="1">
       <c r="A379" s="20" t="inlineStr">
@@ -25808,18 +26034,57 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D379" s="21" t="n"/>
-      <c r="E379" s="31" t="n"/>
-      <c r="F379" s="31" t="n"/>
-      <c r="G379" s="31" t="n"/>
-      <c r="H379" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.
-Список без списка
-Нет пояснения</t>
-        </is>
-      </c>
+      <c r="D379" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с аутентификацией и авторизацией эксплуатационного персонала при осуществлении доступа к серверным компонентам виртуализации.
+Главная цель меры — обеспечить полную историю попыток доступа к управляющему уровню виртуальной инфраструктуры, включая неуспешные: без регистрации таких попыток невозможно выявить подбор пароля администратора виртуализации или использование скомпрометированной учётной записи эксплуатационного персонала до момента наступления более серьёзных последствий.</t>
+        </is>
+      </c>
+      <c r="E379" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой серверных компонентов виртуализации (гипервизора, консоли управления) и интегрированного с ними сервиса аутентификации на журналирование каждой попытки аутентификации и авторизации эксплуатационного персонала — как успешной, так и неуспешной — с фиксацией учётной записи, времени, источника подключения и результата, с передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм аудита аутентификации платформы виртуализации и службы каталогов, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware vCenter (журнал событий Login/Logout), Microsoft Active Directory (Audit Logon Events) и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор событий аутентификации) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F379" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования аутентификации и авторизации эксплуатационного персонала на образце серверного компонента виртуализации.
+2. Выгрузка зарегистрированных событий аутентификации (успешных и неуспешных) за проверяемый период.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G379" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только успешные попытки аутентификации, неуспешные (в том числе последовательные) попытки не фиксируются;
+2. События аутентификации не сопоставляются с правилами выявления подбора пароля (несколько неуспешных попыток подряд);
+3. События не передаются в SIEM-систему, доступны только в локальном журнале консоли управления виртуализацией;
+4. Регистрация не охватывает аутентификацию через альтернативные интерфейсы доступа (например, прямое подключение к гипервизору в обход центральной консоли).</t>
+        </is>
+      </c>
+      <c r="H379" s="168" t="n"/>
     </row>
     <row r="380" ht="60" customHeight="1">
       <c r="A380" s="20" t="inlineStr">
@@ -25837,18 +26102,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D380" s="21" t="n"/>
-      <c r="E380" s="31" t="n"/>
-      <c r="F380" s="31" t="n"/>
-      <c r="G380" s="31" t="n"/>
-      <c r="H380" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.
-Список без списка
-Нет пояснения</t>
-        </is>
-      </c>
+      <c r="D380" s="144" t="inlineStr">
+        <is>
+          <t>Мера аналогична ЗСВ.39, но требует регистрации операций аутентификации и авторизации пользователей (а не эксплуатационного персонала) при осуществлении доступа к виртуальным машинам.
+Главная цель меры — обеспечить ту же полноту истории попыток доступа, что и мера ЗСВ.39, но применительно к обычным пользователям, обращающимся к своим виртуальным машинам: без регистрации таких попыток компрометация пользовательских учётных данных или подбор пароля к виртуальному АРМ способны остаться незамеченными.</t>
+        </is>
+      </c>
+      <c r="E380" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой брокера подключений (VDI) и (или) гипервизора на журналирование каждой попытки аутентификации и авторизации пользователя при подключении к виртуальной машине — как успешной, так и неуспешной — с фиксацией учётной записи, времени, источника подключения (АРМ) и результата, с передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм аудита аутентификации брокера подключений VDI, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: VMware Horizon (журнал событий подключения), Microsoft RDS и пр.
+Российские сертифицированные (ФСТЭК): «Термидеск», vGate, MaxPatrol SIEM и др.
+Открытый код: Apache Guacamole (журнал подключений), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F380" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования аутентификации и авторизации пользователей на образце брокера подключений/гипервизора.
+2. Выгрузка зарегистрированных событий аутентификации пользователей (успешных и неуспешных) за проверяемый период.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G380" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируются только успешные подключения пользователей, неуспешные попытки аутентификации не фиксируются;
+2. События аутентификации пользователей не сопоставляются с привязкой «учётные данные — виртуальная машина — АРМ» (меры ЗСВ.6/ЗСВ.7) для выявления нарушений;
+3. События не передаются в SIEM-систему, доступны только в локальном журнале брокера подключений;
+4. Регистрация не различает подключение через штатный брокер и прямое подключение к виртуальной машине в обход него.</t>
+        </is>
+      </c>
+      <c r="H380" s="168" t="n"/>
     </row>
     <row r="381" ht="60" customHeight="1">
       <c r="A381" s="20" t="inlineStr">
@@ -25867,18 +26171,57 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D381" s="21" t="n"/>
-      <c r="E381" s="31" t="n"/>
-      <c r="F381" s="31" t="n"/>
-      <c r="G381" s="31" t="n"/>
-      <c r="H381" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.
-Список без списка
-Нет пояснения</t>
-        </is>
-      </c>
+      <c r="D381" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с запуском (остановкой) программного обеспечения (ПО) серверных компонентов виртуализации — то есть самого ПО гипервизора, консоли управления и связанных с ним служб, в отличие от меры ЗСВ.32, которая регистрирует запуск/остановку виртуальных машин.
+Главная цель меры — обеспечить видимость фактов остановки или перезапуска критичных служб платформы виртуализации: незамеченная остановка службы гипервизора или консоли управления (в том числе намеренная, для сокрытия последующих несанкционированных действий) способна временно вывести из-под контроля весь массив размещённых на нём виртуальных машин.</t>
+        </is>
+      </c>
+      <c r="E381" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой операционной системы или платформы, на которой функционируют серверные компоненты виртуализации, на журналирование каждого факта запуска и остановки соответствующих служб (гипервизора, консоли управления, службы аутентификации) с фиксацией времени, инициатора и результата, с передачей событий в SIEM-систему.
+Класс используемых средств — встроенные средства журналирования служб операционной системы серверных компонентов виртуализации, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: Microsoft Windows Event Log (события служб SCVMM/Hyper-V), VMware ESXi (события служб hostd/vpxa) и пр.
+Российские сертифицированные (ФСТЭК): vGate, MaxPatrol SIEM, KUMA и др.
+Открытый код: journalctl/systemd (события служб libvirtd), Wazuh и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F381" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования запуска и остановки служб серверных компонентов виртуализации.
+2. Выгрузка зарегистрированных событий запуска/остановки служб за проверяемый период.
+3. Итоги интервью с ответственным за администрирование виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G381" s="151" t="inlineStr">
+        <is>
+          <t>1. Регистрируется только штатная остановка службы (например, при плановом обслуживании), но не аварийное завершение процесса;
+2. События остановки критичных служб платформы виртуализации не имеют повышенного приоритета обработки в SIEM-системе;
+3. Регистрация не охватывает все узлы кластера виртуализации, часть хостов исключена из мониторинга состояния служб;
+4. Оповещение ответственных лиц о незапланированной остановке критичной службы платформы виртуализации не настроено.</t>
+        </is>
+      </c>
+      <c r="H381" s="168" t="n"/>
     </row>
     <row r="382" ht="60" customHeight="1">
       <c r="A382" s="20" t="inlineStr">
@@ -25896,18 +26239,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D382" s="21" t="n"/>
-      <c r="E382" s="31" t="n"/>
-      <c r="F382" s="31" t="n"/>
-      <c r="G382" s="31" t="n"/>
-      <c r="H382" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.
-Список без списка
-Нет пояснения</t>
-        </is>
-      </c>
+      <c r="D382" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с изменением параметров настроек технических мер защиты информации, используемых для реализации контроля доступа к серверным компонентам виртуализации.
+Главная цель меры — обеспечить видимость изменений самих защитных механизмов, обеспечивающих контроль доступа к управляющему уровню виртуальной инфраструктуры (меры ЗСВ.9, ЗСВ.10): без регистрации таких изменений отключение или ослабление, например, требования двухфакторной аутентификации способно остаться незамеченным, открывая путь к дальнейшей компрометации.</t>
+        </is>
+      </c>
+      <c r="E382" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средств защиты информации (PAM/bastion, средств двухфакторной аутентификации, специализированных СЗИ виртуальной инфраструктуры), реализующих контроль доступа к серверным компонентам виртуализации, на журналирование каждого факта изменения их собственных параметров настроек с фиксацией инициатора, времени и характера изменения, с передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм аудита изменения конфигурации средств контроля доступа (PAM, MFA, специализированных СЗИ виртуальной инфраструктуры), система централизованного сбора и корреляции событий (SIEM).
+Иностранные: журнал изменения политик Cisco ISE/PAM-решений, Splunk и пр.
+Российские сертифицированные (ФСТЭК): vGate (журнал изменения политик), MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор событий изменения конфигурации) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F382" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования изменений параметров настроек средств контроля доступа к серверным компонентам виртуализации.
+2. Выгрузка зарегистрированных изменений конфигурации за проверяемый период с сопоставлением регламенту внесения изменений.
+3. Итоги интервью с ответственным за администрирование средств защиты виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G382" s="151" t="inlineStr">
+        <is>
+          <t>1. Изменения параметров двухфакторной аутентификации (например, её временное отключение) не регистрируются как отдельное событие повышенного приоритета;
+2. Зарегистрированные изменения не сопоставляются с утверждённым регламентом внесения изменений, любое изменение считается допустимым без проверки согласования;
+3. События изменения конфигурации средств контроля доступа не передаются в SIEM-систему, доступны только в локальном журнале самого средства;
+4. Изменения, выполненные встроенной (root/administrator) учётной записью средства защиты, не подлежат тому же уровню контроля, что и изменения именованных учётных записей.</t>
+        </is>
+      </c>
+      <c r="H382" s="168" t="n"/>
     </row>
     <row r="383" ht="45" customHeight="1">
       <c r="A383" s="20" t="inlineStr">
@@ -25925,17 +26307,57 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D383" s="21" t="n"/>
-      <c r="E383" s="31" t="n"/>
-      <c r="F383" s="31" t="n"/>
-      <c r="G383" s="31" t="n"/>
-      <c r="H383" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки Не выявлены.
-Список без списка
-Пояснения нет</t>
-        </is>
-      </c>
+      <c r="D383" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует регистрации в качестве события защиты информации каждой операции, связанной с изменением настроек технических мер защиты информации, используемых для обеспечения защиты виртуальных машин, — то есть мера параллельна ЗСВ.42, но охватывает средства защиты уровня самих виртуальных машин (контроль целостности, антивирус, замкнутую программную среду), а не средства контроля доступа к серверным компонентам виртуализации.
+Главная цель меры — обеспечить видимость изменений защитных механизмов, действующих непосредственно внутри виртуальных машин или на уровне гипервизора применительно к ним (например, контроля целостности при запуске, мера ЗСВ.26): без регистрации таких изменений отключение или ослабление защиты конкретной виртуальной машины способно остаться незамеченным.</t>
+        </is>
+      </c>
+      <c r="E383" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Регистрация обеспечивается настройкой средств защиты информации, применяемых для защиты виртуальных машин (контроль целостности при запуске, антивирус, замкнутая программная среда), на журналирование каждого факта изменения их параметров настроек с фиксацией инициатора, времени, затронутой виртуальной машины и характера изменения, с передачей событий в SIEM-систему.
+Класс используемых средств — встроенный механизм аудита изменения конфигурации средств защиты виртуальных машин, система централизованного сбора и корреляции событий (SIEM).
+Иностранные: журнал изменения политик защиты Carbon Black/Tripwire, Splunk и пр.
+Российские сертифицированные (ФСТЭК): vGate, Secret Net, MaxPatrol SIEM, KUMA и др.
+Открытый код: Wazuh (сбор событий изменения конфигурации) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F383" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация журналирования изменений параметров настроек средств защиты виртуальных машин.
+2. Выгрузка зарегистрированных изменений конфигурации за проверяемый период с сопоставлением регламенту внесения изменений.
+3. Итоги интервью с ответственным за администрирование средств защиты виртуальной инфраструктуры.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G383" s="151" t="inlineStr">
+        <is>
+          <t>1. Отключение контроля целостности или антивирусной защиты для конкретной виртуальной машины не регистрируется как отдельное событие повышенного приоритета;
+2. Зарегистрированные изменения не сопоставляются с эталонной (утверждённой) конфигурацией средств защиты виртуальных машин;
+3. События изменения конфигурации средств защиты виртуальных машин не передаются в SIEM-систему, доступны только локально;
+4. Регистрация изменений настроена не для всех виртуальных машин, а только для отнесённых к наиболее критичному контуру безопасности.</t>
+        </is>
+      </c>
+      <c r="H383" s="168" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="13" t="inlineStr">
@@ -33482,8 +33904,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -26401,9 +26401,10 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D386" s="34" t="inlineStr">
-        <is>
-          <t>Организация должна заранее и документально определить, кому, каким способом и к каким именно ресурсам разрешён удалённый доступ, а не предоставлять его по факту запроса без единых правил, чтобы избежать разнообразия и необоснованного расширения прав удалённого доступа у разных сотрудников.</t>
+      <c r="D386" s="144" t="inlineStr">
+        <is>
+          <t>Организация должна заранее и документально определить, кому, каким способом и к каким именно ресурсам разрешён удалённый доступ, а не предоставлять его по факту запроса без единых правил.
+Главная цель меры — избежать разнообразия и необоснованного расширения прав удалённого доступа у разных сотрудников: без заранее закреплённых правил и перечня ресурсов каждый случай удалённого доступа согласовывается ситуативно, что со временем приводит к разрастанию фактически предоставленных полномочий, не соответствующих реальной служебной необходимости.</t>
         </is>
       </c>
       <c r="E386" s="36" t="inlineStr">
@@ -26428,35 +26429,29 @@
           </r>
         </is>
       </c>
-      <c r="F386" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="F386" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Проверочные процедуры (свидетельства) - О</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-1) ВНД, регламентирующий правила удалённого доступа и перечень разрешённых ресурсов;
-2) Выборка фактически предоставленного удалённого доступа на соответствие перечню из ВНД;
-3) Итоги интервью с ответственным за предоставление удалённого доступа.</t>
-          </r>
-        </is>
-      </c>
-      <c r="G386" s="36" t="inlineStr">
-        <is>
-          <t>1) Перечень ресурсов, доступных удалённо, не актуализирован и не соответствует фактической инфраструктуре;
-2) Правила удалённого доступа не охватывают отдельные категории субъектов (например, подрядчиков);
-3) Согласование доступа к ресурсам происходит без опоры на закреплённый в ВНД перечень.</t>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, регламентирующий правила удалённого доступа и перечень разрешённых ресурсов;
+2. Выборка фактически предоставленного удалённого доступа на соответствие перечню из внутреннего нормативного документа;
+3. Итоги интервью с ответственным за предоставление удалённого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G386" s="151" t="inlineStr">
+        <is>
+          <t>1. Перечень ресурсов, доступных удалённо, не актуализирован и не соответствует фактической инфраструктуре;
+2. Правила удалённого доступа не охватывают отдельные категории субъектов (например, подрядчиков);
+3. Согласование доступа к ресурсам происходит без опоры на закреплённый во внутреннем нормативном документе перечень;
+4. Предоставленный ранее удалённый доступ не пересматривается при изменении должностных обязанностей сотрудника.</t>
         </is>
       </c>
     </row>
@@ -26476,16 +26471,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D387" s="21" t="n"/>
-      <c r="E387" s="31" t="n"/>
-      <c r="F387" s="31" t="n"/>
-      <c r="G387" s="31" t="n"/>
-      <c r="H387" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D387" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует аутентификации не только субъекта, обращающегося за удалённым доступом, но и самого мобильного (переносного) устройства, с которого этот доступ осуществляется, — то есть подтверждения, что подключение выполняется именно с доверенного, учтённого организацией устройства.
+Главная цель меры — исключить возможность удалённого доступа с постороннего, неучтённого или скомпрометированного устройства даже при корректно предъявленных аутентификационных данных пользователя: без аутентификации устройства кража или подбор пароля позволили бы получить удалённый доступ с любого мобильного устройства, а не только с легитимного, находящегося под контролем организации.</t>
+        </is>
+      </c>
+      <c r="E387" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Использование сертификатов устройств (машинных сертификатов, выпущенных внутренним удостоверяющим центром) или иных технических признаков (регистрации устройства в MDM-системе, привязки по уникальному идентификатору устройства), подтверждающих легитимность мобильного устройства;
+2. Настройку VPN-шлюза или иного средства организации удалённого доступа таким образом, чтобы подключение предоставлялось только с устройств, прошедших аутентификацию по сертификату или иному техническому признаку;
+3. Технический запрет удалённого доступа с устройств, не прошедших аутентификацию (в том числе с личных и неучтённых устройств).
+Класс используемых средств — инфраструктура открытых ключей (PKI) для аутентификации устройств, VPN-шлюзы и системы централизованного управления мобильными устройствами (MDM) с проверкой сертификата устройства.
+Иностранные: Cisco AnyConnect (с проверкой сертификата устройства), VMware Workspace ONE и пр.
+Российские сертифицированные (ФСТЭК/ФСБ): «С-Терра Шлюз», ViPNet Coordinator и др.
+Открытый код: OpenVPN/WireGuard (с проверкой сертификата клиента) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F387" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация VPN-шлюза (или иного средства удалённого доступа) в части аутентификации устройства.
+2. Результат тестовой попытки удалённого подключения с непривязанного устройства, подтверждающий блокирование такого подключения.
+3. Итоги интервью с ответственным за администрирование удалённого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G387" s="151" t="inlineStr">
+        <is>
+          <t>1. Аутентификация устройства подменяется только аутентификацией пользователя, само устройство отдельно не проверяется;
+2. Признак аутентификации устройства (например, сертификат) технически возможно перенести на постороннее устройство без обнаружения;
+3. Аутентификация устройства не распространяется на все каналы удалённого доступа (например, настроена для VPN-клиента, но не для веб-портала удалённого доступа);
+4. Перечень зарегистрированных (доверенных) устройств не пересматривается при увольнении сотрудника или утрате устройства.</t>
+        </is>
+      </c>
+      <c r="H387" s="168" t="n"/>
     </row>
     <row r="388" ht="57" customHeight="1">
       <c r="A388" s="20" t="inlineStr">
@@ -26503,17 +26542,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D388" s="21" t="n"/>
-      <c r="E388" s="31" t="n"/>
-      <c r="F388" s="31" t="n"/>
-      <c r="G388" s="31" t="n"/>
-      <c r="H388" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки Не выявлены.
-Список без списка
-Нет примеров средств</t>
-        </is>
-      </c>
+      <c r="D388" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы удалённый доступ предоставлялся только с использованием мобильных (переносных) устройств, находящихся под контролем системы централизованного управления и мониторинга (MDM-системы, мера ЗУД.10).
+Главная цель меры — не допустить удалённый доступ с устройства, на которое не распространяются политики защиты MDM-системы (шифрование, блокировка по бездействию, контроль состава ПО): устройство вне управления MDM представляет неконтролируемый риск, поскольку организация не имеет технической возможности ни проверить его защищённость перед подключением, ни удалённо стереть данные в случае утраты.</t>
+        </is>
+      </c>
+      <c r="E388" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой шлюза удалённого доступа (VPN-концентратора) на проверку статуса регистрации устройства в MDM-системе и соответствия его текущей конфигурации установленным политикам (compliance-статус) перед предоставлением сетевого доступа:
+1. Интеграцию шлюза удалённого доступа с MDM-системой для проверки статуса устройства (зарегистрировано, соответствует политикам) на этапе установления соединения;
+2. Технический отказ в предоставлении удалённого доступа устройствам, не зарегистрированным в MDM-системе или не соответствующим установленным политикам (compliance policy);
+3. Периодическую (не только на этапе подключения) проверку соответствия подключённого устройства политикам MDM, с принудительным отключением при выявлении несоответствия.
+Класс используемых средств — система централизованного управления мобильными устройствами (MDM), интегрированная со шлюзом удалённого доступа (VPN) для проверки compliance-статуса устройства.
+Иностранные: VMware Workspace ONE (интеграция с VPN по compliance-статусу), Microsoft Intune (условный доступ) и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для мобильных устройств в связке с VPN-шлюзом и др.
+Открытый код: полноценной интеграции MDM-compliance с VPN-шлюзом в открытых решениях практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F388" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация интеграции шлюза удалённого доступа с MDM-системой в части проверки compliance-статуса устройства.
+2. Результат тестовой попытки подключения незарегистрированного в MDM устройства, подтверждающий отказ в доступе.
+3. Итоги интервью с ответственным за администрирование удалённого доступа и MDM-системы.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G388" s="151" t="inlineStr">
+        <is>
+          <t>1. Проверка регистрации устройства в MDM выполняется только на этапе первого подключения, а не при каждом установлении соединения;
+2. Устройство, переставшее соответствовать политикам MDM после подключения (например, отключение шифрования пользователем), не отключается от удалённого доступа принудительно;
+3. Часть каналов удалённого доступа (например, веб-версия почтового клиента) не интегрирована с проверкой compliance-статуса MDM и доступна с любого устройства;
+4. Перечень политик, проверяемых при подключении, не покрывает все требования MDM-системы (мера ЗУД.10), а только часть из них.</t>
+        </is>
+      </c>
+      <c r="H388" s="168" t="n"/>
     </row>
     <row r="389" ht="57" customHeight="1">
       <c r="A389" s="20" t="inlineStr">
@@ -26531,16 +26613,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D389" s="21" t="n"/>
-      <c r="E389" s="31" t="n"/>
-      <c r="F389" s="31" t="n"/>
-      <c r="G389" s="31" t="n"/>
-      <c r="H389" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки
-Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D389" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует реализации защиты информации от раскрытия и модификации при её передаче в рамках удалённого логического доступа, с применением двухсторонней взаимной аутентификации участников информационного обмена.
+Главная цель меры — обеспечить, что канал удалённого доступа защищён симметрично с обеих сторон: без двухсторонней (mutual) аутентификации устройство доступа не может достоверно убедиться, что оно подключается именно к легитимной инфраструктуре организации, а не к поддельному (фишинговому) шлюзу, имитирующему её, что делает пользователя уязвимым к атаке «человек посередине» (man-in-the-middle).</t>
+        </is>
+      </c>
+      <c r="E389" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Применение криптографического протокола защищённого удалённого доступа (VPN на основе TLS или IPsec) с шифрованием передаваемых данных и контролем их целостности;
+2. Настройку взаимной (двухсторонней) аутентификации сторон соединения — проверки сертификата или иного криптографического признака как со стороны устройства доступа (проверка легитимности шлюза организации), так и со стороны шлюза (проверка легитимности устройства, см. также меру ЗУД.2);
+3. Технический запрет на установление соединения при несовпадении сертификата шлюза удалённого доступа с ожидаемым значением, закреплённым на устройстве (защита от подмены шлюза).
+Класс используемых средств — VPN-шлюзы и клиенты с поддержкой взаимной (mutual) TLS/IPsec-аутентификации, инфраструктура открытых ключей (PKI).
+Иностранные: Cisco AnyConnect, Palo Alto GlobalProtect и пр.
+Российские сертифицированные (ФСТЭК/ФСБ): «С-Терра Шлюз», ViPNet Coordinator, «Континент» (VPN) и др.
+Открытый код: OpenVPN, WireGuard (с внешним PKI) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F389" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация VPN-шлюза и клиента в части взаимной аутентификации сторон и шифрования канала.
+2. Результат тестовой попытки подключения к поддельному (нелегитимному) шлюзу, подтверждающий отказ клиента от установления соединения.
+3. Итоги интервью с ответственным за администрирование удалённого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G389" s="151" t="inlineStr">
+        <is>
+          <t>1. Реализована только односторонняя аутентификация (устройство проверяет сертификат шлюза либо наоборот, но не оба направления одновременно);
+2. Используются устаревшие версии протокола (например, TLS ниже рекомендованной версии), не обеспечивающие достаточную криптографическую стойкость;
+3. Клиент удалённого доступа не проверяет отзыв (revocation) сертификата шлюза или устройства при установлении соединения;
+4. Резервный (аварийный) канал удалённого доступа не покрыт теми же требованиями к взаимной аутентификации, что и основной.</t>
+        </is>
+      </c>
+      <c r="H389" s="168" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="13" t="inlineStr">
@@ -26571,16 +26697,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D391" s="21" t="n"/>
-      <c r="E391" s="31" t="n"/>
-      <c r="F391" s="31" t="n"/>
-      <c r="G391" s="31" t="n"/>
-      <c r="H391" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки Не выявлены.
-Список без списка</t>
-        </is>
-      </c>
+      <c r="D391" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует идентификации, двухфакторной аутентификации и авторизации субъектов доступа уже после установления защищённого сетевого взаимодействия и выполнения аутентификации устройства и канала связи (меры ЗУД.2 и ЗУД.4) — то есть добавляет отдельный, следующий за сетевым, уровень проверки именно личности пользователя.
+Главная цель меры — не допустить смешения уровней доверия «устройство»/«канал связи» и «пользователь»: успешно пройденная аутентификация устройства (мера ЗУД.2) подтверждает лишь легитимность самого устройства, но не личность оператора, фактически им пользующегося, — устройство может быть похищено вместе с сохранёнными на нём сертификатами, поэтому требуется отдельная, притом двухфакторная, проверка именно субъекта.</t>
+        </is>
+      </c>
+      <c r="E391" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Настройку шлюза удалённого доступа (VPN-концентратора, портала удалённого доступа) на обязательное выполнение идентификации и двухфакторной аутентификации пользователя после установления защищённого сетевого соединения (мера ЗУД.4), но до предоставления доступа к внутренним ресурсам;
+2. Применение второго независимого фактора аутентификации (одноразовый код, аппаратный/программный токен, биометрия), не совпадающего с фактором, использованным при аутентификации устройства;
+3. Настройку авторизации пользователя (разграничения прав доступа к конкретным ресурсам) на основании подтверждённой личности, в соответствии с утверждённым перечнем ресурсов удалённого доступа (мера ЗУД.1).
+Класс используемых средств — VPN-шлюз или портал удалённого доступа с поддержкой многофакторной аутентификации (MFA), интегрированный со службой каталогов.
+Иностранные: Cisco AnyConnect + Duo, Palo Alto GlobalProtect + MFA и пр.
+Российские сертифицированные (ФСТЭК/ФСБ): «С-Терра Шлюз», ViPNet Coordinator (в связке со средствами МФА) и др.
+Открытый код: OpenVPN/WireGuard в сочетании с FreeRADIUS (TOTP) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F391" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация шлюза удалённого доступа в части двухфакторной аутентификации пользователя после установления защищённого канала.
+2. Результат тестового подключения, подтверждающий обязательность прохождения второго фактора после аутентификации устройства.
+3. Итоги интервью с ответственным за администрирование удалённого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G391" s="151" t="inlineStr">
+        <is>
+          <t>1. Второй фактор аутентификации пользователя фактически совпадает с фактором, уже использованным для аутентификации устройства (например, тот же сертификат), что не обеспечивает независимой проверки личности;
+2. Двухфакторная аутентификация пользователя настроена не для всех каналов удалённого доступа, часть каналов ограничивается только аутентификацией устройства;
+3. Авторизация пользователя после успешной аутентификации предоставляет доступ шире перечня ресурсов, утверждённого мерой ЗУД.1;
+4. Повторная аутентификация пользователя при возобновлении прерванного соединения не требуется, сессия продолжается автоматически.</t>
+        </is>
+      </c>
+      <c r="H391" s="168" t="n"/>
     </row>
     <row r="392" ht="71.25" customHeight="1">
       <c r="A392" s="20" t="inlineStr">
@@ -26598,17 +26768,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D392" s="21" t="n"/>
-      <c r="E392" s="31" t="n"/>
-      <c r="F392" s="31" t="n"/>
-      <c r="G392" s="31" t="n"/>
-      <c r="H392" s="26" t="inlineStr">
-        <is>
-          <t>Пояснение слабое
-Список без списка
-Типичные недостатки Не выявлены.</t>
-        </is>
-      </c>
+      <c r="D392" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует запрета прямого сетевого взаимодействия мобильных (переносных) устройств доступа и внутренних сетей финансовой организации на уровне выше второго (канального) по семиуровневой модели ГОСТ Р ИСО/МЭК 7498-1.
+Главная цель меры — исключить полноценное «растворение» устройства удалённого доступа во внутренней сети организации: если бы мобильное устройство получало сетевой доступ на уровне выше канального (например, полноценное включение в общий широковещательный домен), оно фактически становилось бы неотличимо от доверенного внутреннего узла, тогда как ограничение на канальном уровне обеспечивает, что взаимодействие происходит только через контролируемый шлюзовой узел, выполняющий проверки более высокого уровня (маршрутизацию, фильтрацию, инспекцию трафика).</t>
+        </is>
+      </c>
+      <c r="E392" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается терминированием удалённого подключения мобильного устройства на VPN-шлюзе (VPN-концентраторе), который выступает единственной точкой сетевого взаимодействия устройства с внутренней сетью, без предоставления устройству собственного сетевого адреса из адресного пространства внутренней сети иначе как через контролируемый туннель:
+1. Настройку VPN-шлюза на терминирование туннеля удалённого доступа с назначением устройству адреса из выделенного (изолированного) адресного пространства, отличного от внутренних сегментов сети;
+2. Технический запрет на организацию моста (bridging) канального уровня между сетевым интерфейсом мобильного устройства и внутренней сетью организации;
+3. Настройку маршрутизации трафика от VPN-шлюза к ресурсам внутренней сети исключительно через контролируемые точки фильтрации (межсетевые экраны), в соответствии с установленными правилами (мера ЗУД.9).
+Класс используемых средств — VPN-шлюзы (VPN-концентраторы) с терминированием туннеля на сетевом уровне, без организации канального моста с внутренней сетью.
+Иностранные: Cisco AnyConnect (VPN-концентратор), Palo Alto GlobalProtect и пр.
+Российские сертифицированные (ФСТЭК/ФСБ): «С-Терра Шлюз», ViPNet Coordinator, «Континент» (VPN) и др.
+Открытый код: OpenVPN, WireGuard и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F392" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация VPN-шлюза в части терминирования туннеля и назначения адресного пространства устройствам удалённого доступа.
+2. Схема сетевого взаимодействия, подтверждающая отсутствие канального моста между устройствами удалённого доступа и внутренней сетью.
+3. Итоги интервью с ответственным за администрирование сетевой инфраструктуры удалённого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G392" s="151" t="inlineStr">
+        <is>
+          <t>1. VPN-шлюз настроен в режиме канального моста (bridge), фактически включающего устройство удалённого доступа во внутреннюю сеть на уровне выше канального;
+2. Адресное пространство, выделяемое устройствам удалённого доступа, не изолировано от внутренних сегментов сети;
+3. Маршрутизация трафика от VPN-шлюза к внутренним ресурсам не проходит через контролируемые точки фильтрации;
+4. Настройки VPN-шлюза не пересматриваются при изменении топологии внутренней сети организации.</t>
+        </is>
+      </c>
+      <c r="H392" s="168" t="n"/>
     </row>
     <row r="393" ht="71.25" customHeight="1">
       <c r="A393" s="20" t="inlineStr">
@@ -26626,16 +26839,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D393" s="21" t="n"/>
-      <c r="E393" s="31" t="n"/>
-      <c r="F393" s="31" t="n"/>
-      <c r="G393" s="31" t="n"/>
-      <c r="H393" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки Не выявлены.
-Свидетельства съехали</t>
-        </is>
-      </c>
+      <c r="D393" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует, чтобы доступ к ресурсам сети Интернет с мобильного (переносного) устройства осуществлялся только через информационную инфраструктуру финансовой организации — то есть после установления защищённого сетевого взаимодействия и выполнения аутентификации, предусмотренной мерами ЗУД.2 и ЗУД.4, а не напрямую через локальное (домашнее, публичное) подключение устройства к сети Интернет в обход инфраструктуры организации.
+Главная цель меры — исключить раздельное туннелирование (split tunneling), при котором корпоративный трафик идёт через защищённый канал, а обращения к сети Интернет — напрямую, минуя периметровый контроль организации: без принудительного пропуска всего интернет-трафика мобильного устройства через инфраструктуру организации становится невозможным применение к нему тех же средств защиты (контентный анализ, фильтрация, антивирусная проверка), что действуют для стационарных АРМ.</t>
+        </is>
+      </c>
+      <c r="E393" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается настройкой клиента удалённого доступа на принудительную маршрутизацию всего трафика мобильного устройства, включая обращения к сети Интернет, через VPN-туннель и периметровую инфраструктуру организации (full tunneling), с техническим запретом раздельного туннелирования (split tunneling):
+1. Настройку профиля VPN-клиента на принудительную маршрутизацию всего исходящего трафика устройства (в том числе интернет-трафика) через туннель удалённого доступа;
+2. Технический запрет на изменение пользователем настроек маршрутизации VPN-клиента в сторону раздельного туннелирования;
+3. Контроль на стороне VPN-шлюза фактического отсутствия обращений к сети Интернет в обход установленного туннеля за время активного сеанса удалённого доступа.
+Класс используемых средств — VPN-клиент с поддержкой принудительной полной маршрутизации трафика (full tunneling) и технической блокировкой изменения профиля пользователем.
+Иностранные: Cisco AnyConnect (профиль Tunnel All Traffic), Palo Alto GlobalProtect и пр.
+Российские сертифицированные (ФСТЭК/ФСБ): «С-Терра Шлюз», ViPNet Coordinator и др.
+Открытый код: OpenVPN/WireGuard (профиль с маршрутом по умолчанию через туннель) и др.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F393" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация профиля VPN-клиента, подтверждающая принудительную полную маршрутизацию трафика через туннель удалённого доступа.
+2. Результат тестовой проверки: обращение к внешнему ресурсу сети Интернет с подключённого устройства проходит через периметровую инфраструктуру организации.
+3. Итоги интервью с ответственным за администрирование удалённого доступа.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G393" s="151" t="inlineStr">
+        <is>
+          <t>1. Профиль VPN-клиента допускает раздельное туннелирование (split tunneling) для отдельных категорий трафика (например, потокового видео) без должного обоснования;
+2. Пользователь с правами локального администратора устройства технически способен изменить настройки маршрутизации VPN-клиента;
+3. Контроль фактического отсутствия обращений к сети Интернет в обход туннеля не осуществляется;
+4. Полная маршрутизация трафика настроена не для всех платформ устройств удалённого доступа (например, отсутствует для части мобильных операционных систем).</t>
+        </is>
+      </c>
+      <c r="H393" s="168" t="n"/>
     </row>
     <row r="394" ht="45" customHeight="1">
       <c r="A394" s="20" t="inlineStr">
@@ -26653,17 +26910,60 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D394" s="21" t="n"/>
-      <c r="E394" s="31" t="n"/>
-      <c r="F394" s="31" t="n"/>
-      <c r="G394" s="31" t="n"/>
-      <c r="H394" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки Не выявлены.
-Список без списка
-Пояснение и реализация слабые</t>
-        </is>
-      </c>
+      <c r="D394" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует контентного анализа информации, передаваемой мобильными (переносными) устройствами в сеть Интернет с использованием информационной инфраструктуры финансовой организации, — то есть распространяет контроль за содержимым передаваемых данных (аналогичный мере ПУИ.11 для стационарных АРМ) на трафик, пропускаемый через организацию с мобильных устройств удалённого доступа (мера ЗУД.7).
+Главная цель меры — не допустить, чтобы принудительное туннелирование интернет-трафика мобильных устройств через инфраструктуру организации (мера ЗУД.7) осталось только сетевым, но не содержательным контролем: без контентного анализа сам факт прохождения трафика через периметр организации не предотвращает утечку конфиденциальной информации через веб-форму, чат или облачный сервис, инициированную с мобильного устройства.</t>
+        </is>
+      </c>
+      <c r="E394" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Техническая реализация обеспечивается применением на веб-прокси (шлюзе доступа в Интернет), через который проходит туннелированный трафик мобильных устройств (мера ЗУД.7), модуля контентного анализа DLP-системы, аналогично тому, как это реализовано для стационарных АРМ (мера ПУИ.11):
+1. Направление интернет-трафика мобильных устройств удалённого доступа через тот же веб-прокси с модулем контентного анализа, что используется для стационарных АРМ;
+2. Настройку контентного анализа передаваемых данных (форм, файлов, загрузок в облачные сервисы) с расшифровкой TLS-сессий в объёме, установленном внутренними регламентами;
+3. Автоматическую блокировку передачи данных при выявлении признаков конфиденциальной информации, с применением тех же правил, что используются для стационарных АРМ.
+Класс используемых средств — системы предотвращения утечек информации (DLP) с модулем контентного анализа веб-канала (Web DLP), интегрированным с точкой терминирования VPN-туннеля мобильных устройств.
+Иностранные: Forcepoint DLP (Web), Zscaler (модуль DLP) и пр.
+Российские сертифицированные (ФСТЭК): InfoWatch Traffic Monitor, Solar Dozor и др.
+Открытый код: полноценных Web DLP-решений данного класса в открытом коде практически не представлено.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F394" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Конфигурация маршрутизации трафика мобильных устройств через веб-прокси с модулем контентного анализа.
+2. Конфигурация правил контентного анализа, применяемых к трафику мобильных устройств удалённого доступа.
+3. Журнал (отчёт) о заблокированных попытках передачи конфиденциальной информации с мобильных устройств за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G394" s="151" t="inlineStr">
+        <is>
+          <t>1. Контентный анализ трафика мобильных устройств не настроен отдельно и не совпадает по составу правил с анализом трафика стационарных АРМ;
+2. Расшифровка TLS-трафика для контентного анализа не распространяется на мобильные операционные системы с ограничениями на установку корневого сертификата организации;
+3. Контентный анализ применяется только к части каналов (например, к веб-трафику, но не к трафику мобильных приложений, использующих собственные протоколы);
+4. Правила выявления конфиденциальной информации в трафике мобильных устройств не пересматриваются при изменении аналогичных правил для стационарных АРМ.</t>
+        </is>
+      </c>
+      <c r="H394" s="168" t="n"/>
     </row>
     <row r="395" ht="71.25" customHeight="1">
       <c r="A395" s="20" t="inlineStr">
@@ -26681,16 +26981,60 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D395" s="21" t="n"/>
-      <c r="E395" s="31" t="n"/>
-      <c r="F395" s="31" t="n"/>
-      <c r="G395" s="31" t="n"/>
-      <c r="H395" s="26" t="inlineStr">
-        <is>
-          <t>Типичные недостатки Не выявлены.
-Список без списка</t>
-        </is>
-      </c>
+      <c r="D395" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует реализации и контроля информационного взаимодействия внутренних вычислительных сетей финансовой организации и мобильных (переносных) устройств в соответствии с установленными правилами и протоколами сетевого взаимодействия — то есть ограничения состава протоколов и направлений трафика между шлюзом удалённого доступа и внутренними ресурсами строго утверждённым перечнем, а не произвольным набором.
+Главная цель меры — исключить неконтролируемое расширение состава протоколов и правил взаимодействия между устройствами удалённого доступа и внутренней сетью: без ограничения перечня разрешённых протоколов канал удалённого доступа способен постепенно «обрасти» доступом к ресурсам и сервисам, не связанным с исходно обоснованной служебной необходимостью (мера ЗУД.1).</t>
+        </is>
+      </c>
+      <c r="E395" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Так как мера реализуется только техническими методами, её внедрение предполагает:
+1. Документальное закрепление перечня разрешённых протоколов и направлений сетевого взаимодействия между устройствами удалённого доступа и внутренними ресурсами, в соответствии с перечнем ресурсов удалённого доступа (мера ЗУД.1);
+2. Настройку правил межсетевого экранирования на границе сегмента удалённого доступа (за VPN-шлюзом), ограничивающих взаимодействие строго утверждённым перечнем протоколов и направлений (deny by default для прочего трафика);
+3. Периодическую сверку фактической конфигурации правил межсетевого экранирования с утверждённым перечнем разрешённого взаимодействия.
+Класс используемых средств — межсетевой экран на границе сегмента удалённого доступа, средства анализа и контроля соответствия конфигураций сетевой политике.
+Иностранные: Cisco (ACL на границе VPN-сегмента), Palo Alto Networks и пр.
+Российские сертифицированные (ФСТЭК): «Континент», UserGate и др.
+Открытый код: iptables/nftables совместно со скриптами сверки конфигурации с эталоном.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F395" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень разрешённых протоколов и направлений сетевого взаимодействия между устройствами удалённого доступа и внутренними ресурсами.
+2. Конфигурация правил межсетевого экранирования на границе сегмента удалённого доступа.
+3. Акты (отчёты) периодической сверки фактической конфигурации правил с утверждённым перечнем.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G395" s="151" t="inlineStr">
+        <is>
+          <t>1. Правила межсетевого экранирования на границе сегмента удалённого доступа допускают трафик, явно не включённый в утверждённый перечень («любой-любой» вместо allow-list);
+2. Перечень разрешённых протоколов и направлений не пересматривается при изменении перечня ресурсов удалённого доступа (мера ЗУД.1);
+3. Периодическая сверка фактической конфигурации правил с утверждённым перечнем не проводится;
+4. Изменения правил межсетевого экранирования на границе сегмента удалённого доступа вносятся без предварительного согласования с утверждённым перечнем.</t>
+        </is>
+      </c>
+      <c r="H395" s="168" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="13" t="inlineStr">
@@ -26733,52 +27077,28 @@
           <t>Н-Т-Т</t>
         </is>
       </c>
-      <c r="D397" s="90" t="inlineStr">
-        <is>
-          <t>Система управления мобильными (корпоративных) устройствами (MDM-система) для  удалённого доступа должна закрывать весь перечисленный набор функций разом, а не отдельные из них — устройство доступа фактически превращается в управляемую конечную точку с тем же уровнем контроля, что и корпоративный АРМ. Поэтому первоочередной задачей является недопущение случаев, когда утерянное или украденное мобильное устройство без функции удалённого стирания даёт постороннему лицу доступ к корпоративным данным неограниченно долго или позволяет использовать устройство в режиме USB-накопителя или отладки, чтобы открыть канал для несанкционированного извлечения данных в обход всех остальных механизмов защиты MDM.</t>
-        </is>
-      </c>
-      <c r="E397" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D397" s="155" t="inlineStr">
+        <is>
+          <t>Система централизованного управления и мониторинга мобильными устройствами (MDM-система) для удалённого доступа должна закрывать весь перечисленный в мере набор функций разом, а не отдельные из них, — устройство доступа фактически превращается в управляемую конечную точку с тем же уровнем контроля, что и корпоративный АРМ.
+Главная цель меры — не допустить случаев, когда утерянное или украденное мобильное устройство без функции удалённого стирания даёт постороннему лицу доступ к корпоративным данным неограниченно долго, либо позволяет использовать устройство в режиме USB-накопителя или отладки, открывая канал для несанкционированного извлечения данных в обход всех остальных механизмов защиты MDM.</t>
+        </is>
+      </c>
+      <c r="E397" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-MDM-агент устанавливается на все мобильные устройства, используемые для удалённого доступа, и централизованно настраивается на полный перечень политик: шифрование корпоративных данных с возможностью удалённого стирания информации с устройства, обязательная локальная аутентификация пользователя, автоблокировка по времени неактивности, централизованное управление обновлениями ОС и приложений, блокировка режимов USB-mass-storage и отладки (ADB/USB debugging), управление ключами VPN и сертификатами, геолокация устройства, отслеживание смены SIM-карты и запрет синхронизации с публичными облачными хранилищами.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: VMware Workspace ONE, Microsoft Intune и пр.
-- Российские сертифицированные: Kaspersky Security для мобильных устройств в связке с Kaspersky Endpoint Security для бизнеса и прочие
-</t>
+            <t xml:space="preserve">
+MDM-агент устанавливается на все мобильные устройства, используемые для удалённого доступа, и централизованно настраивается на полный перечень политик: шифрование корпоративных данных с возможностью удалённого стирания информации с устройства, обязательная локальная аутентификация пользователя, автоблокировка по времени неактивности, централизованное управление обновлениями операционной системы и приложений, блокировка режимов USB mass storage и отладки (ADB/USB debugging), управление ключами VPN и сертификатами, геолокация устройства, отслеживание смены SIM-карты и запрет синхронизации с публичными облачными хранилищами.
+Класс используемых средств — система централизованного управления мобильными устройствами (Mobile Device Management, MDM).
+Иностранные: VMware Workspace ONE, Microsoft Intune и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для мобильных устройств в связке с Kaspersky Endpoint Security для бизнеса и др.
+Открытый код: полноценных MDM-платформ данного класса с сертификацией ФСТЭК в открытом коде практически не представлено.</t>
           </r>
         </is>
       </c>
@@ -26833,50 +27153,28 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D398" s="34" t="inlineStr">
-        <is>
-          <t>На мобильных устройствах удалённого доступа должны функционировать средства антивирусной защиты — аналогично требованиям к стационарным АРМ во избежание заражения мобильного устройства вредоносным ПО (например, через стороннее приложение или фишинговую ссылку), чтобы не дать злоумышленнику точку входа в корпоративную инфраструктуру через установленное защищённое соединение. Отсутствие антивирусной защиты на мобильных устройствах делает их заведомо слабым звеном по сравнению с хорошо защищёнными стационарными АРМ.</t>
-        </is>
-      </c>
-      <c r="E398" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
+      <c r="D398" s="144" t="inlineStr">
+        <is>
+          <t>На мобильных устройствах удалённого доступа должны функционировать средства антивирусной защиты — аналогично требованиям к стационарным АРМ, во избежание заражения мобильного устройства вредоносным программным обеспечением (например, через стороннее приложение или фишинговую ссылку).
+Главная цель меры — не дать злоумышленнику точку входа в корпоративную инфраструктуру через установленное защищённое соединение: отсутствие антивирусной защиты на мобильных устройствах делает их заведомо слабым звеном по сравнению с хорошо защищёнными стационарными АРМ, а компрометация мобильного устройства через вредоносный код способна предоставить злоумышленнику тот же уровень доступа, что и легитимному пользователю.</t>
+        </is>
+      </c>
+      <c r="E398" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
             </rPr>
             <t>Реализация - Т</t>
           </r>
           <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-На мобильных устройствах устанавливается мобильный антивирусный агент (как правило, интегрированный с MDM-системой из ЗУД.10), обеспечивающий сканирование устройства и устанавливаемых приложений с централизованным контролем актуальности сигнатурных баз.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Примеры средств защиты:
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>- Иностранные: Lookout Mobile Endpoint Security, Sophos Intercept X for Mobile и пр.
-- Российские сертифицированные: Kaspersky Security для мобильных устройств и пр.</t>
+            <t xml:space="preserve">
+На мобильных устройствах устанавливается мобильный антивирусный агент (как правило, интегрированный с MDM-системой, мера ЗУД.10), обеспечивающий сканирование устройства и устанавливаемых приложений с централизованным контролем актуальности сигнатурных баз.
+Класс используемых средств — средства защиты мобильных устройств от вредоносного кода (Mobile Threat Defense).
+Иностранные: Lookout Mobile Endpoint Security, Sophos Intercept X for Mobile и пр.
+Российские сертифицированные (ФСТЭК): Kaspersky Security для мобильных устройств и др.
+Открытый код: полноценных решений данного класса с сертификацией ФСТЭК в открытом коде практически не представлено.</t>
           </r>
         </is>
       </c>
@@ -26928,51 +27226,28 @@
           <t>Т-Т-Т</t>
         </is>
       </c>
-      <c r="D399" s="34" t="inlineStr">
-        <is>
-          <t>При выводе мобильного устройства из эксплуатации, его передаче в стороннюю организацию (ремонт, утилизация) или другому работнику информация должна стираться средствами полной перезаписи, средствами гарантированного удаления информации — аналогично требованиям к машинным носителям информации (ПУИ.23), но применительно к мобильным устройствам удалённого доступа, чтобы новые или временные владельцы устройств не могли случайно получить конфиденциальную информацию.</t>
-        </is>
-      </c>
-      <c r="E399" s="36" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Реализация - Т
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">Процедура вывода из эксплуатации/передачи мобильного устройства включает обязательный этап удалённого или локального стирания корпоративных данных средствами полной перезаписи — как правило, через функцию remote wipe MDM-системы (ЗУД.10) либо штатный сброс к заводским настройкам с подтверждённой перезаписью накопителя устройства.
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-Примеры средств защиты:</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">
-- Иностранные: встроенные функции remote wipe в VMware Workspace ONE, Microsoft Intune и пр.
-- Российские сертифицированные: функция удалённого стирания Kaspersky Security для мобильных устройств в составе MDM-решения и пр.</t>
+      <c r="D399" s="144" t="inlineStr">
+        <is>
+          <t>При выводе мобильного устройства из эксплуатации, его передаче в стороннюю организацию (ремонт, утилизация) или другому работнику информация должна стираться средствами полной перезаписи, обеспечивающими гарантированное удаление, — аналогично требованиям к машинным носителям информации (мера ПУИ.23), но применительно к мобильным устройствам удалённого доступа.
+Главная цель меры — не допустить, чтобы новые или временные владельцы устройства могли случайно или намеренно получить доступ к оставшейся на нём конфиденциальной информации: обычный сброс к заводским настройкам, в отличие от гарантированной перезаписи, не исключает восстановление данных стандартными средствами.</t>
+        </is>
+      </c>
+      <c r="E399" s="151" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - Т</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Процедура вывода из эксплуатации/передачи мобильного устройства включает обязательный этап удалённого или локального стирания корпоративных данных средствами полной перезаписи — как правило, через функцию remote wipe MDM-системы (мера ЗУД.10) либо штатный сброс к заводским настройкам с подтверждённой перезаписью накопителя устройства.
+Класс используемых средств — функция удалённого гарантированного стирания данных (remote wipe) в составе системы централизованного управления мобильными устройствами (MDM).
+Иностранные: встроенные функции remote wipe в VMware Workspace ONE, Microsoft Intune и пр.
+Российские сертифицированные (ФСТЭК): функция удалённого стирания Kaspersky Security для мобильных устройств в составе MDM-решения и др.
+Открытый код: встроенные функции сброса к заводским настройкам мобильных операционных систем (ограниченно применимо без централизованного подтверждения выполнения).</t>
           </r>
         </is>
       </c>
@@ -33904,8 +34179,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A309:G309"/>
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>

--- a/docs/WIKI GOST R 57580.1.xlsx
+++ b/docs/WIKI GOST R 57580.1.xlsx
@@ -334,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -839,6 +839,15 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -27312,9 +27321,10 @@
           <t>О</t>
         </is>
       </c>
-      <c r="D401" s="34" t="inlineStr">
-        <is>
-          <t>Данная мера, представляет собой формализованный процесс установления четких границ (периметра) применения требований безопасности каждого процесса защиты информации ГОСТ 57580.1, при котором для каждого иерархического уровня информационной инфраструктуры — от физического оборудования и сетевых компонентов до виртуализации, ОС, СУБД и прикладных систем — документально закрепляются конкретные объекты защиты. Область применения процесса системы защиты информации определяется в соответствии с положениями актуальных нормативных актов Банка России.</t>
+      <c r="D401" s="144" t="inlineStr">
+        <is>
+          <t>Данная мера представляет собой формализованный процесс установления чётких границ (периметра) применения требований безопасности каждого процесса защиты информации ГОСТ Р 57580.1, при котором для каждого иерархического уровня информационной инфраструктуры — от физического оборудования и сетевых компонентов до виртуализации, ОС, СУБД и прикладных систем — документально закрепляются конкретные объекты защиты. Область применения процесса системы защиты информации определяется в соответствии с положениями актуальных нормативных актов Банка России.
+Главная цель меры — исключить неопределённость в том, какие именно объекты информационной инфраструктуры подпадают под действие каждого процесса защиты информации: без документально закреплённой области применения контроль реализации и эффективности мер защиты становится невозможным, поскольку неясно, что именно должно быть защищено и проверено.</t>
         </is>
       </c>
       <c r="E401" s="36" t="inlineStr">
@@ -27395,9 +27405,10 @@
           <t>О</t>
         </is>
       </c>
-      <c r="D402" s="34" t="inlineStr">
-        <is>
-          <t>Организационные меры защиты информации — это  управленческие и регламентные действия: политики, процедуры, правила работы с персоналом, назначение ответственных, обучение, реагирование на инциденты и т.д. Данная мера требует, чтобы в документе был зафиксирован полный перечень выбранных организацией для реализации организационных мер защиты в отношении каждого процесса защиты информации ГОСТ Р 57580.1-2017. Ключевое требование — указание соответствия  ГОСТ Р 57580.1-2017 - это означает, что в документе должно быть прямое указание на то, какая именно организационная мера из базового состава  ГОСТ Р 57580.1-2017 реализуется данным пунктом вашего внутреннего документа.</t>
+      <c r="D402" s="144" t="inlineStr">
+        <is>
+          <t>Организационные меры защиты информации — это управленческие и регламентные действия: политики, процедуры, правила работы с персоналом, назначение ответственных, обучение, реагирование на инциденты и т. д. Данная мера требует, чтобы в документе был зафиксирован полный перечень выбранных организацией для реализации организационных мер защиты в отношении каждого процесса защиты информации ГОСТ Р 57580.1-2017. Ключевое требование — указание соответствия ГОСТ Р 57580.1-2017: в документе должно быть прямое указание на то, какая именно организационная мера из базового состава ГОСТ Р 57580.1-2017 реализуется данным пунктом внутреннего документа.
+Главная цель меры — обеспечить прослеживаемую связь между требованиями ГОСТ Р 57580.1-2017 и фактически реализуемыми организационными мерами: без прямого указания соответствия конкретному пункту стандарта невозможно ни подтвердить полноту выполнения требований при проверке регулятором, ни выявить меры, оставшиеся нереализованными.</t>
         </is>
       </c>
       <c r="E402" s="92" t="inlineStr">
@@ -27471,9 +27482,10 @@
           <t>О</t>
         </is>
       </c>
-      <c r="D403" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Данная мера направлена на закрепление в документах чётких и детальных регламентов применения всех организационных мер защиты информации, которые выбраны организацией к реализации в рамках каждого из процессов защиты информации  ГОСТ Р 57580.1-2017. </t>
+      <c r="D403" s="144" t="inlineStr">
+        <is>
+          <t>Данная мера направлена на закрепление в документах чётких и детальных регламентов применения всех организационных мер защиты информации, которые выбраны организацией к реализации в рамках каждого из процессов защиты информации ГОСТ Р 57580.1-2017.
+Главная цель меры — исключить ситуацию, при которой организационная мера формально выбрана к реализации (мера ПЗИ.2), но не имеет детального регламента применения: без конкретного, детализированного порядка действий исполнители трактуют и применяют меру произвольно, что делает её фактическую реализацию непредсказуемой и непроверяемой.</t>
         </is>
       </c>
       <c r="E403" s="92" t="inlineStr">
@@ -27546,9 +27558,10 @@
           <t>О</t>
         </is>
       </c>
-      <c r="D404" s="65" t="inlineStr">
-        <is>
-          <t>Технические меры защиты информации — это меры, реализуемые с помощью аппаратных, программных, аппаратно-программных средств и (или) систем. Данная мера требует, чтобы в документе был зафиксирован полный перечень выбранных организацией для реализации технических мер защиты в отношении каждого процесса защиты информации ГОСТ Р 57580.1-2017. Ключевое требование — указание соответствия  ГОСТ Р 57580.1-2017 - это означает, что в документе должно быть прямое указание на то, какая именно техническая мера из базового состава  ГОСТ Р 57580.1-2017 реализуется данным пунктом вашего внутреннего документа.</t>
+      <c r="D404" s="163" t="inlineStr">
+        <is>
+          <t>Технические меры защиты информации — это меры, реализуемые с помощью аппаратных, программных, аппаратно-программных средств и (или) систем. Данная мера требует, чтобы в документе был зафиксирован полный перечень выбранных организацией для реализации технических мер защиты в отношении каждого процесса защиты информации ГОСТ Р 57580.1-2017. Ключевое требование — указание соответствия ГОСТ Р 57580.1-2017: в документе должно быть прямое указание на то, какая именно техническая мера из базового состава ГОСТ Р 57580.1-2017 реализуется данным пунктом внутреннего документа.
+Главная цель меры — обеспечить ту же прослеживаемую связь между требованиями стандарта и фактически применяемыми техническими мерами, что и мера ПЗИ.2 для организационных мер: без прямого указания соответствия конкретному пункту ГОСТ Р 57580.1-2017 невозможно подтвердить полноту технической реализации требований стандарта.</t>
         </is>
       </c>
       <c r="E404" s="92" t="inlineStr">
@@ -27620,9 +27633,10 @@
           <t>О</t>
         </is>
       </c>
-      <c r="D405" s="90" t="inlineStr">
-        <is>
-          <t>Данная мера направлена на закрепление в документах чётких и детальных регламентов применения всех технических мер защиты информации, которые выбраны организацией к реализации в рамках каждого из процессов защиты информации  ГОСТ Р 57580.1-2017. Данная мера обязывает организацию разработать комплект документов, который обеспечивает единообразное, контролируемое и безопасное применение каждого технического средства защиты на всех этапах — установка, настройка, эксплуатация, мониторинг и вывод из эксплуатации.</t>
+      <c r="D405" s="155" t="inlineStr">
+        <is>
+          <t>Данная мера направлена на закрепление в документах чётких и детальных регламентов применения всех технических мер защиты информации, которые выбраны организацией к реализации в рамках каждого из процессов защиты информации ГОСТ Р 57580.1-2017. Мера обязывает организацию разработать комплект документов, который обеспечивает единообразное, контролируемое и безопасное применение каждого технического средства защиты на всех этапах — установка, настройка, эксплуатация, мониторинг и вывод из эксплуатации.
+Главная цель меры — исключить ситуацию, при которой техническая мера формально выбрана к реализации (мера ПЗИ.4), но не имеет детального регламента применения: без конкретного порядка действий на каждом этапе жизненного цикла технического средства защиты его эксплуатация становится зависимой от личной квалификации и добросовестности конкретного администратора, а не от формализованного и проверяемого процесса.</t>
         </is>
       </c>
       <c r="E405" s="92" t="inlineStr">
@@ -27714,9 +27728,10 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D407" s="34" t="inlineStr">
-        <is>
-          <t>Данная мера направлена на создание и поддержание единой достоверной инвентаризационной базы всех объектов информатизации в каждом процессе защиты информации ГОСТ Р 57580.1-2017.</t>
+      <c r="D407" s="144" t="inlineStr">
+        <is>
+          <t>Данная мера направлена на создание и поддержание единой достоверной инвентаризационной базы всех объектов информатизации в каждом процессе защиты информации ГОСТ Р 57580.1-2017.
+Главная цель меры — обеспечить, чтобы решения о применении мер защиты информации (меры ПЗИ.1—ПЗИ.5) опирались на достоверные и актуальные сведения о реальном составе защищаемых объектов: без единой инвентаризационной базы область применения процесса защиты информации, зафиксированная документально, рискует разойтись с фактическим состоянием инфраструктуры.</t>
         </is>
       </c>
       <c r="E407" s="36" t="inlineStr">
@@ -27848,12 +27863,13 @@
           <t>О-О-Т</t>
         </is>
       </c>
-      <c r="D408" s="34" t="inlineStr">
+      <c r="D408" s="144" t="inlineStr">
         <is>
           <t>Данная мера требует, чтобы выбранные на этапе планирования технические средства защиты информации были физически установлены (размещены) в информационной инфраструктуре и настроены (сконфигурированы) в соответствии с утверждёнными параметрами безопасности в каждом процессе защиты информации ГОСТ Р 57580.1-2017.
-На практике это означает, что все средства защиты — межсетевые экраны, антивирусы, системы обнаружения вторжений, средства криптографической защиты и т.д. — должны быть:
+На практике это означает, что все средства защиты — межсетевые экраны, антивирусы, системы обнаружения вторжений, средства криптографической защиты и т. д. — должны быть:
 - размещены на определённых узлах инфраструктуры (серверах, сетевых сегментах, рабочих станциях, банкоматах) согласно проектной документации и правилам размещения;
-- настроены с конкретными параметрами (политики фильтрации, правила сканирования, криптографические алгоритмы, пороговые значения), зафиксированными в документации по настройке.</t>
+- настроены с конкретными параметрами (политики фильтрации, правила сканирования, криптографические алгоритмы, пороговые значения), зафиксированными в документации по настройке.
+Главная цель меры — подтвердить, что запланированные на этапе ПЗИ технические меры защиты не остались только на бумаге: между утверждением перечня технических мер (мера ПЗИ.4) и их фактическим функционированием лежит этап физического размещения и настройки, без которого мера защиты не может считаться реализованной, вне зависимости от того, насколько качественно она спланирована.</t>
         </is>
       </c>
       <c r="E408" s="37" t="inlineStr">
@@ -27970,9 +27986,10 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D409" s="34" t="inlineStr">
-        <is>
-          <t>Данная мера относится к этапу реализации процесса системы защиты информации. Её суть заключается в том, чтобы проверить и подтвердить, что все запланированные технические меры защиты информации (межсетевые экраны, антивирусы, СОВ, СКЗИ и т.д.) были в полном объёме реализованы — то есть фактически установлены, развёрнуты и настроены в информационной инфраструктуре организации в соответствии с утверждёнными параметрами в каждом процессе защиты информации ГОСТ Р 57580.1-2017. Эта мера является проверочной и отвечает на ключевой вопрос: «А соответствует ли реальное состояние защиты тому, что было запланировано в документах ПЗИ.4?».</t>
+      <c r="D409" s="144" t="inlineStr">
+        <is>
+          <t>Данная мера относится к этапу реализации процесса системы защиты информации. Её суть заключается в том, чтобы проверить и подтвердить, что все запланированные технические меры защиты информации (межсетевые экраны, антивирусы, СОВ, СКЗИ и т. д.) были в полном объёме реализованы — то есть фактически установлены, развёрнуты и настроены в информационной инфраструктуре организации в соответствии с утверждёнными параметрами в каждом процессе защиты информации ГОСТ Р 57580.1-2017. Эта мера является проверочной и отвечает на ключевой вопрос: «Соответствует ли реальное состояние защиты тому, что было запланировано в документах ПЗИ.4?».
+Главная цель меры — независимо подтвердить полноту и корректность реализации технических мер защиты информации, а не полагаться на факт их формального развёртывания (мера РЗИ.2): расхождение между запланированным и фактическим состоянием защиты способно долгое время оставаться незамеченным без отдельного контрольного этапа, проверяющего именно это соответствие.</t>
         </is>
       </c>
       <c r="E409" s="92" t="inlineStr">
@@ -28403,10 +28420,12 @@
           </r>
         </is>
       </c>
-      <c r="G414" s="96" t="inlineStr">
-        <is>
-          <t>1. Отсутствие системы централизованного управления.
-2. Система централизованного управления внедрена, но охватывает не все АРМ организации (например, удалённые офисы, филиалы, мобильные устройства).</t>
+      <c r="G414" s="172" t="inlineStr">
+        <is>
+          <t>1. Отсутствует система централизованного управления техническими мерами защиты информации;
+2. Система централизованного управления внедрена, но охватывает не все объекты организации (например, удалённые офисы, филиалы, мобильные устройства);
+3. Централизованное управление реализовано для одного класса СЗИ (например, антивируса), но отсутствует для других (межсетевых экранов, СКЗИ, DLP);
+4. Изменения политик через централизованную консоль не журналируются отдельно от изменений, внесённых локально на отдельном объекте.</t>
         </is>
       </c>
     </row>
@@ -28596,9 +28615,10 @@
           <t>Н-Н-Т</t>
         </is>
       </c>
-      <c r="D417" s="34" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в применении в финансовой организации сертифицированных по требованиям безопасности информации средств защиты информации (СЗИ), имеющих класс не ниже 4-го в каждом процессе защиты информации ГОСТ Р 57580.1-2017.</t>
+      <c r="D417" s="144" t="inlineStr">
+        <is>
+          <t>Суть меры заключается в применении в финансовой организации сертифицированных по требованиям безопасности информации средств защиты информации (СЗИ), имеющих класс не ниже 4-го, в каждом процессе защиты информации ГОСТ Р 57580.1-2017.
+Главная цель меры — обеспечить, что для объектов защиты, требующих применения сертифицированных СЗИ, используются средства, чей класс сертификации формально подтверждает способность противостоять актуальным для организации угрозам: применение несертифицированного средства или средства более низкого класса лишает организацию документального подтверждения соответствия заявленным требованиям безопасности.</t>
         </is>
       </c>
       <c r="E417" s="98" t="inlineStr">
@@ -28649,10 +28669,12 @@
           </r>
         </is>
       </c>
-      <c r="G417" s="100" t="inlineStr">
+      <c r="G417" s="173" t="inlineStr">
         <is>
           <t>1. Применяется сертифицированное СЗИ, но с несертифицированными обновлениями или модификациями, что аннулирует действие сертификата;
-2. В модели угроз не обоснована необходимость применения сертифицированных СЗИ или отсутствие такой необходимости.</t>
+2. В модели угроз не обоснована необходимость применения сертифицированных СЗИ либо отсутствие такой необходимости;
+3. Применяется СЗИ класса ниже требуемого (например, 5 класса вместо 4) для объектов, для которых требуется более высокий класс;
+4. Срок действия сертификата соответствия истёк, но использование СЗИ продолжается без переоформления или замены.</t>
         </is>
       </c>
     </row>
@@ -28672,9 +28694,10 @@
           <t>Н-Т-Н</t>
         </is>
       </c>
-      <c r="D418" s="34" t="inlineStr">
-        <is>
-          <t>Суть меры заключается в применении в финансовой организации сертифицированных по требованиям безопасности информации средств защиты информации (СЗИ), имеющих класс не ниже 5-го в каждом процессе защиты информации ГОСТ Р 57580.1-2017.</t>
+      <c r="D418" s="144" t="inlineStr">
+        <is>
+          <t>Суть меры заключается в применении в финансовой организации сертифицированных по требованиям безопасности информации средств защиты информации (СЗИ), имеющих класс не ниже 5-го, в каждом процессе защиты информации ГОСТ Р 57580.1-2017.
+Главная цель меры — обеспечить тот же результат, что и мера РЗИ.11, но для объектов защиты, для которых достаточен менее строгий (5-й) класс сертификации: применение несертифицированного средства или средства более низкого класса лишает организацию документального подтверждения соответствия заявленным требованиям безопасности применительно к данной категории объектов.</t>
         </is>
       </c>
       <c r="E418" s="99" t="inlineStr">
@@ -28724,10 +28747,12 @@
           </r>
         </is>
       </c>
-      <c r="G418" s="100" t="inlineStr">
+      <c r="G418" s="173" t="inlineStr">
         <is>
           <t>1. Применяется сертифицированное СЗИ, но с несертифицированными обновлениями или модификациями, что аннулирует действие сертификата;
-2. В модели угроз не обоснована необходимость применения сертифицированных СЗИ или отсутствие такой необходимости.</t>
+2. В модели угроз не обоснована необходимость применения сертифицированных СЗИ либо отсутствие такой необходимости;
+3. Применяется СЗИ класса ниже требуемого (например, 6 класса вместо 5) для объектов, для которых требуется более высокий класс;
+4. Срок действия сертификата соответствия истёк, но использование СЗИ продолжается без переоформления или замены.</t>
         </is>
       </c>
     </row>
@@ -28877,10 +28902,12 @@
           </r>
         </is>
       </c>
-      <c r="G420" s="100" t="inlineStr">
+      <c r="G420" s="173" t="inlineStr">
         <is>
           <t>1. Применяются несертифицированные по требуемому классу СКЗИ;
-2. В модели угроз не обоснована необходимость применения сертифицированных СКЗИ или отсутствие такой необходимости.</t>
+2. В модели угроз не обоснована необходимость применения сертифицированных СКЗИ либо отсутствие такой необходимости;
+3. Применяется СКЗИ класса ниже требуемого (например, КС1 вместо КС2);
+4. Эксплуатационная документация на СКЗИ (правила пользования) не соблюдается, что способно повлечь фактическое несоответствие заявленному классу защиты.</t>
         </is>
       </c>
     </row>
@@ -28900,10 +28927,56 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D421" s="21" t="n"/>
-      <c r="E421" s="101" t="n"/>
-      <c r="F421" s="102" t="n"/>
-      <c r="G421" s="25" t="n"/>
+      <c r="D421" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует организации обучения и практической подготовки (переподготовки) именно тех работников финансовой организации, которые непосредственно отвечают за применение мер защиты информации в рамках процесса системы защиты информации, — то есть не общего инструктажа для всех сотрудников (мера РЗИ.16), а специализированной подготовки конкретных исполнителей.
+Главная цель меры — обеспечить, чтобы ответственные за применение мер защиты информации обладали необходимыми знаниями и практическими навыками для их корректной реализации: без целевого обучения даже правильно спроектированная и внедрённая мера защиты рискует применяться некорректно из-за недостаточной квалификации исполнителя, что фактически обесценивает результат этапа реализации (меры РЗИ.6/РЗИ.7).</t>
+        </is>
+      </c>
+      <c r="E421" s="174" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Определение перечня должностей (ролей), ответственных за применение мер защиты информации, для которых обязательно обучение и практическая подготовка;
+2. Разработку или приобретение программ обучения, охватывающих как теоретическую подготовку, так и практическую отработку навыков применения конкретных мер защиты информации, закреплённых за соответствующей должностью;
+3. Установление периодичности переподготовки (повышения квалификации) ответственных работников с учётом изменения состава применяемых мер защиты информации и технологий;
+4. Документальное подтверждение факта прохождения обучения (сертификаты, удостоверения, протоколы внутреннего обучения) каждым ответственным работником.</t>
+          </r>
+        </is>
+      </c>
+      <c r="F421" s="172" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Перечень должностей (ролей), ответственных за применение мер защиты информации, с указанием обязательности обучения;
+2. Программы обучения и практической подготовки по применению мер защиты информации;
+3. Документы, подтверждающие фактическое прохождение обучения (сертификаты, удостоверения, протоколы) ответственными работниками за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G421" s="173" t="inlineStr">
+        <is>
+          <t>1. Обучение пройдено не всеми работниками, ответственными за применение мер защиты информации, а только частью из них;
+2. Программа обучения не охватывает практическую отработку навыков, ограничивается только теоретической частью;
+3. Периодичность переподготовки не установлена или не соблюдается на практике;
+4. Содержание программы обучения не актуализируется при внедрении новых мер защиты информации или изменении применяемых технологий.</t>
+        </is>
+      </c>
     </row>
     <row r="422" ht="57" customHeight="1">
       <c r="A422" s="20" t="inlineStr">
@@ -28921,10 +28994,56 @@
           <t>О</t>
         </is>
       </c>
-      <c r="D422" s="21" t="n"/>
-      <c r="E422" s="101" t="n"/>
-      <c r="F422" s="102" t="n"/>
-      <c r="G422" s="25" t="n"/>
+      <c r="D422" s="144" t="inlineStr">
+        <is>
+          <t>Мера требует повышения осведомлённости (проведения инструктажа) работников финансовой организации в области реализации процесса защиты информации в целом — применения организационных мер защиты информации и использования по назначению технических мер защиты информации, — то есть распространяется на весь персонал организации, а не только на работников, ответственных за непосредственное применение мер защиты (мера РЗИ.15).
+Главная цель меры — сформировать базовый уровень осведомлённости у каждого сотрудника вне зависимости от его роли: значительная часть инцидентов защиты информации связана не с действиями специалистов по защите информации, а с ошибками или неосторожностью рядовых пользователей (переход по фишинговой ссылке, использование слабого пароля, разглашение конфиденциальной информации), и без общего инструктажа эта категория риска остаётся неохваченной.</t>
+        </is>
+      </c>
+      <c r="E422" s="174" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Реализация - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+Мера реализуется исключительно организационными методами и предполагает:
+1. Проведение вводного инструктажа по вопросам защиты информации для каждого вновь принятого работника до предоставления ему доступа к информационным ресурсам организации;
+2. Проведение периодического (не реже установленной внутренним нормативным документом периодичности) повторного инструктажа для всех работников организации;
+3. Информирование работников об актуальных угрозах и типовых сценариях социальной инженерии (фишинг, вишинг) по мере их выявления;
+4. Документальную фиксацию факта прохождения инструктажа каждым работником (лист ознакомления, электронная отметка в системе обучения).</t>
+          </r>
+        </is>
+      </c>
+      <c r="F422" s="172" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
+            <t xml:space="preserve">
+1. Внутренний нормативный документ, регламентирующий порядок и периодичность проведения инструктажа по вопросам защиты информации;
+2. Материалы вводного и периодического инструктажа;
+3. Листы ознакомления (или выгрузка из системы обучения), подтверждающие фактическое прохождение инструктажа работниками за проверяемый период.</t>
+          </r>
+        </is>
+      </c>
+      <c r="G422" s="173" t="inlineStr">
+        <is>
+          <t>1. Вводный инструктаж по вопросам защиты информации не проводится или проводится формально, без реальной проверки усвоения материала;
+2. Периодический повторный инструктаж не проводится, ограничиваются однократным вводным инструктажем при приёме на работу;
+3. Информирование работников об актуальных угрозах (фишинг и подобные) не обновляется, используются устаревшие материалы;
+4. Факт прохождения инструктажа не документируется, что не позволяет подтвердить охват всех работников.</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="13" t="inlineStr">
@@ -29675,10 +29794,12 @@
           </r>
         </is>
       </c>
-      <c r="G430" s="36" t="inlineStr">
+      <c r="G430" s="151" t="inlineStr">
         <is>
           <t>1. Проверки знаний проводятся от случая к случаю, без закреплённой периодичности и чёткого порядка;
-2. Проверке подвергаются не все категории работников, а только часть (например, проверяются только администраторы, но не пользователи или проверка осуществляется только для субъектов относящихся к процессу управления доступом без учета иных процессов ГОСТ 57580.1).</t>
+2. Проверке подвергаются не все категории работников, а только часть (например, проверяются только администраторы, но не пользователи, либо проверка охватывает только субъектов, относящихся к процессу управления доступом, без учёта иных процессов ГОСТ Р 57580.1);
+3. Результаты проверки знаний не оформляются документально, что не позволяет подтвердить факт их проведения;
+4. Работники, не прошедшие проверку знаний, продолжают выполнять функции, связанные с применением мер защиты информации, без повторной проверки.</t>
         </is>
       </c>
     </row>
@@ -29758,10 +29879,12 @@
           </r>
         </is>
       </c>
-      <c r="G431" s="36" t="inlineStr">
+      <c r="G431" s="151" t="inlineStr">
         <is>
           <t>1. Результаты контроля оформляются хаотично, без единых правил и форм;
-2. Документируются результаты не всех контрольных мероприятий, а только части (например, по КЗИ.1 и КЗИ.2 есть акты, а по КЗИ.5 — нет).</t>
+2. Документируются результаты не всех контрольных мероприятий, а только части (например, по КЗИ.1 и КЗИ.2 есть акты, а по КЗИ.5 — нет);
+3. Зафиксированные результаты контроля не хранятся установленный срок, часть более ранних актов утрачена;
+4. Выявленные в ходе контроля недостатки фиксируются, но не сопровождаются сведениями о принятых мерах по их устранению.</t>
         </is>
       </c>
     </row>
@@ -31034,10 +31157,10 @@
           <t>О-О-О</t>
         </is>
       </c>
-      <c r="D449" s="34" t="inlineStr">
+      <c r="D449" s="144" t="inlineStr">
         <is>
           <t>Мера требует, чтобы в сегментах разработки и тестирования обрабатывалась только та информация, которая не подлежит защите (например, тестовые данные), за исключением конфигурационной информации, необходимой для настройки параметров работы АС.
-Главная суть меры —  исключение утечки или компрометации защищаемой информации (коммерческой тайны, персональные данные, информации о параметрах или настройках и т.д.) из сегментов разработки и тестирования АС.</t>
+Главная цель меры — исключение утечки или компрометации защищаемой информации (коммерческой тайны, персональных данных, информации о параметрах или настройках и т. д.) из сегментов разработки и тестирования АС.</t>
         </is>
       </c>
       <c r="E449" s="37" t="inlineStr">
@@ -31098,11 +31221,12 @@
           </r>
         </is>
       </c>
-      <c r="G449" s="37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. В ВНД отсутствует порядок действий (удаление данных, блокировка доступа к ним, информирование службы безопасности) с информацией в сегменте разработки и тестирования.
-2. В ВНД отсутствует перечень конфигурационной информации, которая может использоваться в сегменте разработки и тестирования.
-</t>
+      <c r="G449" s="164" t="inlineStr">
+        <is>
+          <t>1. Во внутреннем нормативном документе отсутствует порядок действий (удаление данных, блокировка доступа к ним, информирование службы безопасности) с информацией, ошибочно попавшей в сегмент разработки и тестирования;
+2. Во внутреннем нормативном документе отсутствует перечень конфигурационной информации, которая может использоваться в сегменте разработки и тестирования;
+3. Фактический состав данных в сегменте разработки и тестирования не проверяется на периодической основе на предмет присутствия защищаемой информации;
+4. Разработчики и тестировщики не проинформированы о запрете использования защищаемой информации в сегменте разработки и тестирования.</t>
         </is>
       </c>
     </row>
@@ -31270,11 +31394,12 @@
           </r>
         </is>
       </c>
-      <c r="G451" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Результаты контроля не фиксируются.
-2. Перечень реализованных мер не соответствует утвержденному перечню технических и организационных мер, утвержденных в ВНД.
-</t>
+      <c r="G451" s="151" t="inlineStr">
+        <is>
+          <t>1. Результаты контроля (тестирования) не фиксируются документально;
+2. Перечень фактически реализованных мер не соответствует утверждённому перечню технических и организационных мер, закреплённому во внутреннем нормативном документе;
+3. Контроль (тестирование) полноты реализации мер проводится только на этапе ввода в эксплуатацию, но не повторяется при последующих изменениях АС;
+4. Тестирование охватывает только техническую часть мер защиты, организационные меры системы защиты информации АС не проверяются.</t>
         </is>
       </c>
     </row>
@@ -31353,10 +31478,12 @@
           </r>
         </is>
       </c>
-      <c r="G452" s="36" t="inlineStr">
+      <c r="G452" s="151" t="inlineStr">
         <is>
           <t>1. Изменение требований к мерам защиты информации зафиксировано, но модернизация АС не инициирована;
-2. Документ состава и содержания мер системы защиты информации АС не актуализирован после модернизации.</t>
+2. Документ состава и содержания мер системы защиты информации АС не актуализирован после модернизации;
+3. Модернизация АС проводится без предварительного контроля (тестирования) полноты реализации новых мер защиты информации (мера ЖЦ.9);
+4. Сроки проведения модернизации не устанавливаются или систематически не соблюдаются с момента фиксации изменившихся требований.</t>
         </is>
       </c>
     </row>
@@ -31833,10 +31960,12 @@
           </r>
         </is>
       </c>
-      <c r="G459" s="91" t="inlineStr">
-        <is>
-          <t>1. Отсутствует проектная и эксплуатационная документация на АС.
-1. Отсутствует акт сверки реализованных технических  мер защиты и их параметров настройки на этапе эксплуатации АС с утвержденными на этапе ввода в эксплуатацию и создание (модернизации).</t>
+      <c r="G459" s="145" t="inlineStr">
+        <is>
+          <t>1. Отсутствует проектная и эксплуатационная документация на АС;
+2. Отсутствует акт сверки реализованных технических мер защиты и их параметров настройки на этапе эксплуатации АС с утверждёнными на этапе ввода в эксплуатацию и создания (модернизации);
+3. Контроль фактического размещения технических мер защиты в промышленной среде проводится нерегулярно, без установленной периодичности;
+4. Выявленные расхождения фактических параметров настройки технических мер защиты с утверждёнными не устраняются в разумный срок.</t>
         </is>
       </c>
       <c r="H459" s="10" t="n"/>
@@ -31916,10 +32045,12 @@
           </r>
         </is>
       </c>
-      <c r="G460" s="36" t="inlineStr">
-        <is>
-          <t>1. Выявленные отклонения не устраняются и не эскалируются.
-2. Контроль охватывает только технические меры, а организационные меры (соблюдение регламентов) не проверяются.</t>
+      <c r="G460" s="151" t="inlineStr">
+        <is>
+          <t>1. Выявленные отклонения не устраняются и не эскалируются;
+2. Контроль охватывает только технические меры, а организационные меры (соблюдение регламентов) не проверяются;
+3. Периодичность контроля применения мер защиты информации АС не установлена внутренним нормативным документом;
+4. Результаты контроля применения мер защиты информации АС не фиксируются документально.</t>
         </is>
       </c>
     </row>
@@ -32004,9 +32135,12 @@
           </r>
         </is>
       </c>
-      <c r="G461" s="36" t="inlineStr">
-        <is>
-          <t>1. Отсутствуют отчёты/акты по результатам проведённого контроля за ответственными лицами.</t>
+      <c r="G461" s="151" t="inlineStr">
+        <is>
+          <t>1. Отсутствуют отчёты (акты) по результатам проведённого контроля за ответственными лицами;
+2. Лица, ответственные за контроль деятельности эксплуатационного персонала системы защиты информации АС, не назначены отдельным распорядительным документом;
+3. Контроль деятельности ответственных лиц проводится нерегулярно, без установленной периодичности;
+4. Выявленные в ходе контроля нарушения со стороны ответственных лиц не влекут каких-либо последствий (разбирательства, корректирующих действий).</t>
         </is>
       </c>
     </row>
@@ -32222,23 +32356,16 @@
           </r>
         </is>
       </c>
-      <c r="F464" s="91" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <b val="1"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Проверочные процедуры и свидетельства - О</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Roboto"/>
-              <color theme="1"/>
-              <sz val="11"/>
-            </rPr>
+      <c r="F464" s="145" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Roboto"/>
+              <b val="1"/>
+            </rPr>
+            <t>Проверочные процедуры (свидетельства) - О</t>
+          </r>
+          <r>
             <t xml:space="preserve">
 1. Регламент, устанавливающий периодичность проведения контроля защищённости АС.
 2. Отчёты по тестированию на проникновение и анализу уязвимостей за каждый проверяемый год.
@@ -32448,9 +32575,12 @@
           </r>
         </is>
       </c>
-      <c r="G466" s="36" t="inlineStr">
-        <is>
-          <t>1. Не все типы изменений регистрируются — например, обновления прикладного ПО фиксируются, а изменения конфигурации — нет.</t>
+      <c r="G466" s="151" t="inlineStr">
+        <is>
+          <t>1. Не все типы изменений регистрируются — например, обновления прикладного ПО фиксируются, а изменения конфигурации — нет;
+2. Регистрация изменений не содержит сведений об инициаторе и обосновании внесённого изменения;
+3. Записи о внесённых изменениях не сопоставляются с утверждёнными заявками на изменение (регламентом управления изменениями);
+4. Регистрация изменений ведётся не централизованно, а разрозненно по отдельным компонентам АС.</t>
         </is>
       </c>
     </row>
@@ -32580,10 +32710,12 @@
           </r>
         </is>
       </c>
-      <c r="G467" s="36" t="inlineStr">
-        <is>
-          <t>1. Не на всех СЗИ настроена регистрация событий изменения параметров настроек.
-2. Отсутствует ВНД регламентирующие реализацию указанной в мере регистрации посредством организационных способов.</t>
+      <c r="G467" s="151" t="inlineStr">
+        <is>
+          <t>1. Не на всех СЗИ настроена регистрация событий изменения параметров настроек;
+2. Отсутствует внутренний нормативный документ, регламентирующий реализацию указанной в мере регистрации организационными способами;
+3. Зарегистрированные события изменения параметров настроек не передаются в SIEM-систему для централизованного хранения и анализа;
+4. Срок хранения зарегистрированных событий изменения настроек не соответствует установленным требованиям к данным регистрации.</t>
         </is>
       </c>
     </row>
@@ -32837,10 +32969,12 @@
           </r>
         </is>
       </c>
-      <c r="G471" s="36" t="inlineStr">
-        <is>
-          <t>1. Копирование данных в тестовые/аналитические среды происходит без согласования;
-2. Технические меры контроля копирования (ПУИ) не распространяются на информацию, специфичную именно для данной АС.</t>
+      <c r="G471" s="151" t="inlineStr">
+        <is>
+          <t>1. Копирование данных в тестовые (аналитические) среды происходит без согласования;
+2. Технические меры контроля копирования (меры ПУИ) не распространяются на информацию, специфичную именно для данной АС;
+3. Перечень информации АС, подлежащей защите от несанкционированного копирования, не определён документально;
+4. Контроль соблюдения установленных ограничений на копирование информации АС не проводится на периодической основе.</t>
         </is>
       </c>
     </row>
@@ -34179,8 +34313,8 @@
     <mergeCell ref="A423:G423"/>
     <mergeCell ref="A174:G174"/>
     <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A309:G309"/>
     <mergeCell ref="A133:G133"/>
     <mergeCell ref="A84:G84"/>
     <mergeCell ref="A286:G286"/>
